--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,17 +559,17 @@
         <v>46217</v>
       </c>
       <c r="B7" t="n">
-        <v>1063</v>
+        <v>610</v>
       </c>
       <c r="C7" t="n">
         <v>8888</v>
       </c>
       <c r="D7" t="n">
-        <v>1251.14</v>
+        <v>590.08</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
         <v>46217</v>
       </c>
       <c r="B8" t="n">
-        <v>325</v>
+        <v>1063</v>
       </c>
       <c r="C8" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D8" t="n">
-        <v>868.83</v>
+        <v>1251.14</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -597,17 +597,17 @@
         <v>46217</v>
       </c>
       <c r="B9" t="n">
-        <v>610</v>
+        <v>325</v>
       </c>
       <c r="C9" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D9" t="n">
-        <v>235.34</v>
+        <v>868.83</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -616,17 +616,17 @@
         <v>46217</v>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>610</v>
       </c>
       <c r="C10" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D10" t="n">
-        <v>325.04</v>
+        <v>235.34</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -635,17 +635,17 @@
         <v>46217</v>
       </c>
       <c r="B11" t="n">
-        <v>1117</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D11" t="n">
-        <v>349.47</v>
+        <v>325.04</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -654,17 +654,17 @@
         <v>46217</v>
       </c>
       <c r="B12" t="n">
-        <v>949</v>
+        <v>1117</v>
       </c>
       <c r="C12" t="n">
-        <v>998</v>
+        <v>8888</v>
       </c>
       <c r="D12" t="n">
-        <v>129.85</v>
+        <v>349.47</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -673,17 +673,17 @@
         <v>46217</v>
       </c>
       <c r="B13" t="n">
-        <v>2250</v>
+        <v>949</v>
       </c>
       <c r="C13" t="n">
-        <v>8888</v>
+        <v>998</v>
       </c>
       <c r="D13" t="n">
-        <v>2693.99</v>
+        <v>129.85</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -692,17 +692,17 @@
         <v>46217</v>
       </c>
       <c r="B14" t="n">
-        <v>2663</v>
+        <v>2250</v>
       </c>
       <c r="C14" t="n">
         <v>8888</v>
       </c>
       <c r="D14" t="n">
-        <v>2146.08</v>
+        <v>3180.11</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -711,17 +711,17 @@
         <v>46217</v>
       </c>
       <c r="B15" t="n">
-        <v>664</v>
+        <v>2663</v>
       </c>
       <c r="C15" t="n">
         <v>8888</v>
       </c>
       <c r="D15" t="n">
-        <v>350.72</v>
+        <v>2146.08</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -730,17 +730,17 @@
         <v>46217</v>
       </c>
       <c r="B16" t="n">
-        <v>1063</v>
+        <v>664</v>
       </c>
       <c r="C16" t="n">
         <v>8888</v>
       </c>
       <c r="D16" t="n">
-        <v>1902.46</v>
+        <v>350.72</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
         <v>46217</v>
       </c>
       <c r="B17" t="n">
-        <v>949</v>
+        <v>1063</v>
       </c>
       <c r="C17" t="n">
-        <v>1134</v>
+        <v>8888</v>
       </c>
       <c r="D17" t="n">
-        <v>327.6</v>
+        <v>1902.46</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -768,17 +768,17 @@
         <v>46217</v>
       </c>
       <c r="B18" t="n">
-        <v>326</v>
+        <v>949</v>
       </c>
       <c r="C18" t="n">
-        <v>8888</v>
+        <v>1134</v>
       </c>
       <c r="D18" t="n">
-        <v>116.94</v>
+        <v>327.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
         <v>46217</v>
       </c>
       <c r="B19" t="n">
-        <v>1116</v>
+        <v>326</v>
       </c>
       <c r="C19" t="n">
         <v>8888</v>
       </c>
       <c r="D19" t="n">
-        <v>971.6</v>
+        <v>116.94</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -806,17 +806,17 @@
         <v>46217</v>
       </c>
       <c r="B20" t="n">
-        <v>1983</v>
+        <v>1116</v>
       </c>
       <c r="C20" t="n">
         <v>8888</v>
       </c>
       <c r="D20" t="n">
-        <v>412.16</v>
+        <v>971.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -825,17 +825,17 @@
         <v>46217</v>
       </c>
       <c r="B21" t="n">
-        <v>451</v>
+        <v>1983</v>
       </c>
       <c r="C21" t="n">
         <v>8888</v>
       </c>
       <c r="D21" t="n">
-        <v>2583.46</v>
+        <v>412.16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -844,17 +844,17 @@
         <v>46217</v>
       </c>
       <c r="B22" t="n">
-        <v>325</v>
+        <v>451</v>
       </c>
       <c r="C22" t="n">
         <v>8888</v>
       </c>
       <c r="D22" t="n">
-        <v>459.43</v>
+        <v>2583.46</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -863,17 +863,17 @@
         <v>46217</v>
       </c>
       <c r="B23" t="n">
-        <v>1063</v>
+        <v>325</v>
       </c>
       <c r="C23" t="n">
         <v>8888</v>
       </c>
       <c r="D23" t="n">
-        <v>352.87</v>
+        <v>459.43</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -882,13 +882,13 @@
         <v>46217</v>
       </c>
       <c r="B24" t="n">
-        <v>629</v>
+        <v>1063</v>
       </c>
       <c r="C24" t="n">
         <v>8888</v>
       </c>
       <c r="D24" t="n">
-        <v>277.36</v>
+        <v>352.87</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -907,11 +907,11 @@
         <v>8888</v>
       </c>
       <c r="D25" t="n">
-        <v>2049.78</v>
+        <v>277.36</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -920,17 +920,17 @@
         <v>46217</v>
       </c>
       <c r="B26" t="n">
-        <v>949</v>
+        <v>629</v>
       </c>
       <c r="C26" t="n">
-        <v>1762</v>
+        <v>8888</v>
       </c>
       <c r="D26" t="n">
-        <v>325.65</v>
+        <v>2049.78</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -939,17 +939,17 @@
         <v>46217</v>
       </c>
       <c r="B27" t="n">
-        <v>2463</v>
+        <v>949</v>
       </c>
       <c r="C27" t="n">
-        <v>8888</v>
+        <v>1762</v>
       </c>
       <c r="D27" t="n">
-        <v>8336.43</v>
+        <v>325.65</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
         <v>46217</v>
       </c>
       <c r="B28" t="n">
-        <v>451</v>
+        <v>2463</v>
       </c>
       <c r="C28" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D28" t="n">
-        <v>327.28</v>
+        <v>8336.43</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -977,17 +977,17 @@
         <v>46217</v>
       </c>
       <c r="B29" t="n">
-        <v>610</v>
+        <v>451</v>
       </c>
       <c r="C29" t="n">
-        <v>8888</v>
+        <v>3403</v>
       </c>
       <c r="D29" t="n">
-        <v>335.61</v>
+        <v>327.28</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -996,17 +996,17 @@
         <v>46217</v>
       </c>
       <c r="B30" t="n">
-        <v>341</v>
+        <v>610</v>
       </c>
       <c r="C30" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D30" t="n">
-        <v>366.88</v>
+        <v>335.61</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1015,17 +1015,17 @@
         <v>46217</v>
       </c>
       <c r="B31" t="n">
-        <v>1064</v>
+        <v>341</v>
       </c>
       <c r="C31" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D31" t="n">
-        <v>692.0599999999999</v>
+        <v>366.88</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1034,13 +1034,13 @@
         <v>46217</v>
       </c>
       <c r="B32" t="n">
-        <v>663</v>
+        <v>1064</v>
       </c>
       <c r="C32" t="n">
         <v>8888</v>
       </c>
       <c r="D32" t="n">
-        <v>824.5599999999999</v>
+        <v>692.0599999999999</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1053,17 +1053,17 @@
         <v>46217</v>
       </c>
       <c r="B33" t="n">
-        <v>1064</v>
+        <v>663</v>
       </c>
       <c r="C33" t="n">
         <v>8888</v>
       </c>
       <c r="D33" t="n">
-        <v>2383.39</v>
+        <v>824.5599999999999</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1072,13 +1072,13 @@
         <v>46217</v>
       </c>
       <c r="B34" t="n">
-        <v>451</v>
+        <v>1064</v>
       </c>
       <c r="C34" t="n">
         <v>8888</v>
       </c>
       <c r="D34" t="n">
-        <v>1371.26</v>
+        <v>2383.39</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1091,17 +1091,17 @@
         <v>46217</v>
       </c>
       <c r="B35" t="n">
-        <v>40</v>
+        <v>451</v>
       </c>
       <c r="C35" t="n">
         <v>8888</v>
       </c>
       <c r="D35" t="n">
-        <v>488.35</v>
+        <v>1371.26</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1110,17 +1110,17 @@
         <v>46217</v>
       </c>
       <c r="B36" t="n">
-        <v>530</v>
+        <v>40</v>
       </c>
       <c r="C36" t="n">
         <v>8888</v>
       </c>
       <c r="D36" t="n">
-        <v>180.08</v>
+        <v>1093.47</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1129,13 +1129,13 @@
         <v>46217</v>
       </c>
       <c r="B37" t="n">
-        <v>559</v>
+        <v>530</v>
       </c>
       <c r="C37" t="n">
         <v>8888</v>
       </c>
       <c r="D37" t="n">
-        <v>512.59</v>
+        <v>180.08</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1148,13 +1148,13 @@
         <v>46217</v>
       </c>
       <c r="B38" t="n">
-        <v>1937</v>
+        <v>559</v>
       </c>
       <c r="C38" t="n">
         <v>8888</v>
       </c>
       <c r="D38" t="n">
-        <v>937.47</v>
+        <v>512.59</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1167,17 +1167,17 @@
         <v>46217</v>
       </c>
       <c r="B39" t="n">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="C39" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D39" t="n">
-        <v>211.41</v>
+        <v>1506.42</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1186,17 +1186,17 @@
         <v>46217</v>
       </c>
       <c r="B40" t="n">
-        <v>2250</v>
+        <v>1937</v>
       </c>
       <c r="C40" t="n">
         <v>8888</v>
       </c>
       <c r="D40" t="n">
-        <v>1943.54</v>
+        <v>937.47</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1205,17 +1205,17 @@
         <v>46217</v>
       </c>
       <c r="B41" t="n">
-        <v>89</v>
+        <v>131</v>
       </c>
       <c r="C41" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D41" t="n">
-        <v>573.46</v>
+        <v>211.41</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1224,17 +1224,17 @@
         <v>46217</v>
       </c>
       <c r="B42" t="n">
-        <v>1299</v>
+        <v>2250</v>
       </c>
       <c r="C42" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D42" t="n">
-        <v>262.02</v>
+        <v>1943.54</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
         <v>46217</v>
       </c>
       <c r="B43" t="n">
-        <v>131</v>
+        <v>1299</v>
       </c>
       <c r="C43" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D43" t="n">
-        <v>609.86</v>
+        <v>262.02</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1262,17 +1262,17 @@
         <v>46217</v>
       </c>
       <c r="B44" t="n">
-        <v>40</v>
+        <v>131</v>
       </c>
       <c r="C44" t="n">
         <v>8888</v>
       </c>
       <c r="D44" t="n">
-        <v>733.37</v>
+        <v>609.86</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1281,13 +1281,13 @@
         <v>46217</v>
       </c>
       <c r="B45" t="n">
-        <v>559</v>
+        <v>40</v>
       </c>
       <c r="C45" t="n">
         <v>8888</v>
       </c>
       <c r="D45" t="n">
-        <v>1562.5</v>
+        <v>733.37</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1300,13 +1300,13 @@
         <v>46217</v>
       </c>
       <c r="B46" t="n">
-        <v>2550</v>
+        <v>40</v>
       </c>
       <c r="C46" t="n">
         <v>8888</v>
       </c>
       <c r="D46" t="n">
-        <v>321.05</v>
+        <v>799.86</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1319,17 +1319,17 @@
         <v>46217</v>
       </c>
       <c r="B47" t="n">
-        <v>2250</v>
+        <v>2651</v>
       </c>
       <c r="C47" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D47" t="n">
-        <v>1512.17</v>
+        <v>316.61</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1338,13 +1338,13 @@
         <v>46217</v>
       </c>
       <c r="B48" t="n">
-        <v>1465</v>
+        <v>559</v>
       </c>
       <c r="C48" t="n">
         <v>8888</v>
       </c>
       <c r="D48" t="n">
-        <v>8550.709999999999</v>
+        <v>1562.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1357,15 +1357,72 @@
         <v>46217</v>
       </c>
       <c r="B49" t="n">
+        <v>2550</v>
+      </c>
+      <c r="C49" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D49" t="n">
+        <v>321.05</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B50" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C50" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1512.17</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B51" t="n">
+        <v>1465</v>
+      </c>
+      <c r="C51" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D51" t="n">
+        <v>8550.709999999999</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B52" t="n">
         <v>483</v>
       </c>
-      <c r="C49" t="n">
-        <v>8888</v>
-      </c>
-      <c r="D49" t="n">
+      <c r="C52" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D52" t="n">
         <v>720.66</v>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>FORÇA DE VENDAS</t>
         </is>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,17 +464,17 @@
         <v>46217</v>
       </c>
       <c r="B2" t="n">
-        <v>42</v>
+        <v>1756</v>
       </c>
       <c r="C2" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D2" t="n">
-        <v>22505.79</v>
+        <v>556.23</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -483,17 +483,17 @@
         <v>46217</v>
       </c>
       <c r="B3" t="n">
-        <v>1102</v>
+        <v>42</v>
       </c>
       <c r="C3" t="n">
         <v>8888</v>
       </c>
       <c r="D3" t="n">
-        <v>1199.81</v>
+        <v>22505.79</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -502,13 +502,13 @@
         <v>46217</v>
       </c>
       <c r="B4" t="n">
-        <v>89</v>
+        <v>2109</v>
       </c>
       <c r="C4" t="n">
         <v>8888</v>
       </c>
       <c r="D4" t="n">
-        <v>4572.01</v>
+        <v>4813.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -521,13 +521,13 @@
         <v>46217</v>
       </c>
       <c r="B5" t="n">
-        <v>949</v>
+        <v>2015</v>
       </c>
       <c r="C5" t="n">
-        <v>1258</v>
+        <v>2571</v>
       </c>
       <c r="D5" t="n">
-        <v>196.87</v>
+        <v>679.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -540,17 +540,17 @@
         <v>46217</v>
       </c>
       <c r="B6" t="n">
-        <v>285</v>
+        <v>1293</v>
       </c>
       <c r="C6" t="n">
-        <v>8888</v>
+        <v>1281</v>
       </c>
       <c r="D6" t="n">
-        <v>1081.17</v>
+        <v>1337.87</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -559,17 +559,17 @@
         <v>46217</v>
       </c>
       <c r="B7" t="n">
-        <v>610</v>
+        <v>1102</v>
       </c>
       <c r="C7" t="n">
         <v>8888</v>
       </c>
       <c r="D7" t="n">
-        <v>590.08</v>
+        <v>1199.81</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
         <v>46217</v>
       </c>
       <c r="B8" t="n">
-        <v>1063</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
         <v>8888</v>
       </c>
       <c r="D8" t="n">
-        <v>1251.14</v>
+        <v>4572.01</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -597,17 +597,17 @@
         <v>46217</v>
       </c>
       <c r="B9" t="n">
-        <v>325</v>
+        <v>2768</v>
       </c>
       <c r="C9" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D9" t="n">
-        <v>868.83</v>
+        <v>3436.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -616,17 +616,17 @@
         <v>46217</v>
       </c>
       <c r="B10" t="n">
-        <v>610</v>
+        <v>949</v>
       </c>
       <c r="C10" t="n">
-        <v>8888</v>
+        <v>1258</v>
       </c>
       <c r="D10" t="n">
-        <v>235.34</v>
+        <v>196.87</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -635,17 +635,17 @@
         <v>46217</v>
       </c>
       <c r="B11" t="n">
-        <v>40</v>
+        <v>1756</v>
       </c>
       <c r="C11" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D11" t="n">
-        <v>325.04</v>
+        <v>1799.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -654,17 +654,17 @@
         <v>46217</v>
       </c>
       <c r="B12" t="n">
-        <v>1117</v>
+        <v>285</v>
       </c>
       <c r="C12" t="n">
         <v>8888</v>
       </c>
       <c r="D12" t="n">
-        <v>349.47</v>
+        <v>1081.17</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -673,17 +673,17 @@
         <v>46217</v>
       </c>
       <c r="B13" t="n">
-        <v>949</v>
+        <v>610</v>
       </c>
       <c r="C13" t="n">
-        <v>998</v>
+        <v>8888</v>
       </c>
       <c r="D13" t="n">
-        <v>129.85</v>
+        <v>590.08</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -692,17 +692,17 @@
         <v>46217</v>
       </c>
       <c r="B14" t="n">
-        <v>2250</v>
+        <v>2755</v>
       </c>
       <c r="C14" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D14" t="n">
-        <v>3180.11</v>
+        <v>1133.17</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -711,17 +711,17 @@
         <v>46217</v>
       </c>
       <c r="B15" t="n">
-        <v>2663</v>
+        <v>2767</v>
       </c>
       <c r="C15" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D15" t="n">
-        <v>2146.08</v>
+        <v>5000.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -730,13 +730,13 @@
         <v>46217</v>
       </c>
       <c r="B16" t="n">
-        <v>664</v>
+        <v>2767</v>
       </c>
       <c r="C16" t="n">
         <v>8888</v>
       </c>
       <c r="D16" t="n">
-        <v>350.72</v>
+        <v>1175.73</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -755,11 +755,11 @@
         <v>8888</v>
       </c>
       <c r="D17" t="n">
-        <v>1902.46</v>
+        <v>1251.14</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -768,13 +768,13 @@
         <v>46217</v>
       </c>
       <c r="B18" t="n">
-        <v>949</v>
+        <v>325</v>
       </c>
       <c r="C18" t="n">
-        <v>1134</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>327.6</v>
+        <v>868.83</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -787,17 +787,17 @@
         <v>46217</v>
       </c>
       <c r="B19" t="n">
-        <v>326</v>
+        <v>610</v>
       </c>
       <c r="C19" t="n">
         <v>8888</v>
       </c>
       <c r="D19" t="n">
-        <v>116.94</v>
+        <v>235.34</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -806,17 +806,17 @@
         <v>46217</v>
       </c>
       <c r="B20" t="n">
-        <v>1116</v>
+        <v>1906</v>
       </c>
       <c r="C20" t="n">
         <v>8888</v>
       </c>
       <c r="D20" t="n">
-        <v>971.6</v>
+        <v>889.22</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -825,17 +825,17 @@
         <v>46217</v>
       </c>
       <c r="B21" t="n">
-        <v>1983</v>
+        <v>40</v>
       </c>
       <c r="C21" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D21" t="n">
-        <v>412.16</v>
+        <v>325.04</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -844,17 +844,17 @@
         <v>46217</v>
       </c>
       <c r="B22" t="n">
-        <v>451</v>
+        <v>1117</v>
       </c>
       <c r="C22" t="n">
         <v>8888</v>
       </c>
       <c r="D22" t="n">
-        <v>2583.46</v>
+        <v>349.47</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -863,17 +863,17 @@
         <v>46217</v>
       </c>
       <c r="B23" t="n">
-        <v>325</v>
+        <v>949</v>
       </c>
       <c r="C23" t="n">
-        <v>8888</v>
+        <v>998</v>
       </c>
       <c r="D23" t="n">
-        <v>459.43</v>
+        <v>129.85</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -882,13 +882,13 @@
         <v>46217</v>
       </c>
       <c r="B24" t="n">
-        <v>1063</v>
+        <v>2250</v>
       </c>
       <c r="C24" t="n">
         <v>8888</v>
       </c>
       <c r="D24" t="n">
-        <v>352.87</v>
+        <v>3180.11</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -901,17 +901,17 @@
         <v>46217</v>
       </c>
       <c r="B25" t="n">
-        <v>629</v>
+        <v>2507</v>
       </c>
       <c r="C25" t="n">
         <v>8888</v>
       </c>
       <c r="D25" t="n">
-        <v>277.36</v>
+        <v>4167.12</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -920,17 +920,17 @@
         <v>46217</v>
       </c>
       <c r="B26" t="n">
-        <v>629</v>
+        <v>664</v>
       </c>
       <c r="C26" t="n">
         <v>8888</v>
       </c>
       <c r="D26" t="n">
-        <v>2049.78</v>
+        <v>3523.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -939,13 +939,13 @@
         <v>46217</v>
       </c>
       <c r="B27" t="n">
-        <v>949</v>
+        <v>1906</v>
       </c>
       <c r="C27" t="n">
-        <v>1762</v>
+        <v>1954</v>
       </c>
       <c r="D27" t="n">
-        <v>325.65</v>
+        <v>1445.21</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -958,17 +958,17 @@
         <v>46217</v>
       </c>
       <c r="B28" t="n">
-        <v>2463</v>
+        <v>1075</v>
       </c>
       <c r="C28" t="n">
         <v>8888</v>
       </c>
       <c r="D28" t="n">
-        <v>8336.43</v>
+        <v>470.95</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -977,13 +977,13 @@
         <v>46217</v>
       </c>
       <c r="B29" t="n">
-        <v>451</v>
+        <v>2696</v>
       </c>
       <c r="C29" t="n">
-        <v>3403</v>
+        <v>1312</v>
       </c>
       <c r="D29" t="n">
-        <v>327.28</v>
+        <v>677.76</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -996,17 +996,17 @@
         <v>46217</v>
       </c>
       <c r="B30" t="n">
-        <v>610</v>
+        <v>360</v>
       </c>
       <c r="C30" t="n">
-        <v>8888</v>
+        <v>546</v>
       </c>
       <c r="D30" t="n">
-        <v>335.61</v>
+        <v>4515.36</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1015,17 +1015,17 @@
         <v>46217</v>
       </c>
       <c r="B31" t="n">
-        <v>341</v>
+        <v>1293</v>
       </c>
       <c r="C31" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D31" t="n">
-        <v>366.88</v>
+        <v>381.82</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
         <v>46217</v>
       </c>
       <c r="B32" t="n">
-        <v>1064</v>
+        <v>2663</v>
       </c>
       <c r="C32" t="n">
         <v>8888</v>
       </c>
       <c r="D32" t="n">
-        <v>692.0599999999999</v>
+        <v>2146.08</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1053,13 +1053,13 @@
         <v>46217</v>
       </c>
       <c r="B33" t="n">
-        <v>663</v>
+        <v>675</v>
       </c>
       <c r="C33" t="n">
         <v>8888</v>
       </c>
       <c r="D33" t="n">
-        <v>824.5599999999999</v>
+        <v>289.67</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1072,13 +1072,13 @@
         <v>46217</v>
       </c>
       <c r="B34" t="n">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="C34" t="n">
         <v>8888</v>
       </c>
       <c r="D34" t="n">
-        <v>2383.39</v>
+        <v>1902.46</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1091,17 +1091,17 @@
         <v>46217</v>
       </c>
       <c r="B35" t="n">
-        <v>451</v>
+        <v>1392</v>
       </c>
       <c r="C35" t="n">
         <v>8888</v>
       </c>
       <c r="D35" t="n">
-        <v>1371.26</v>
+        <v>814.61</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1110,17 +1110,17 @@
         <v>46217</v>
       </c>
       <c r="B36" t="n">
-        <v>40</v>
+        <v>360</v>
       </c>
       <c r="C36" t="n">
         <v>8888</v>
       </c>
       <c r="D36" t="n">
-        <v>1093.47</v>
+        <v>749.13</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1129,17 +1129,17 @@
         <v>46217</v>
       </c>
       <c r="B37" t="n">
-        <v>530</v>
+        <v>2491</v>
       </c>
       <c r="C37" t="n">
         <v>8888</v>
       </c>
       <c r="D37" t="n">
-        <v>180.08</v>
+        <v>398.66</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1148,17 +1148,17 @@
         <v>46217</v>
       </c>
       <c r="B38" t="n">
-        <v>559</v>
+        <v>949</v>
       </c>
       <c r="C38" t="n">
-        <v>8888</v>
+        <v>1134</v>
       </c>
       <c r="D38" t="n">
-        <v>512.59</v>
+        <v>327.6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1167,13 +1167,13 @@
         <v>46217</v>
       </c>
       <c r="B39" t="n">
-        <v>89</v>
+        <v>326</v>
       </c>
       <c r="C39" t="n">
         <v>8888</v>
       </c>
       <c r="D39" t="n">
-        <v>1506.42</v>
+        <v>212.63</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1186,13 +1186,13 @@
         <v>46217</v>
       </c>
       <c r="B40" t="n">
-        <v>1937</v>
+        <v>1116</v>
       </c>
       <c r="C40" t="n">
         <v>8888</v>
       </c>
       <c r="D40" t="n">
-        <v>937.47</v>
+        <v>971.6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1205,17 +1205,17 @@
         <v>46217</v>
       </c>
       <c r="B41" t="n">
-        <v>131</v>
+        <v>325</v>
       </c>
       <c r="C41" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D41" t="n">
-        <v>211.41</v>
+        <v>538.37</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1224,17 +1224,17 @@
         <v>46217</v>
       </c>
       <c r="B42" t="n">
-        <v>2250</v>
+        <v>1293</v>
       </c>
       <c r="C42" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D42" t="n">
-        <v>1943.54</v>
+        <v>3534.85</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
         <v>46217</v>
       </c>
       <c r="B43" t="n">
-        <v>1299</v>
+        <v>1983</v>
       </c>
       <c r="C43" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D43" t="n">
-        <v>262.02</v>
+        <v>412.16</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1262,13 +1262,13 @@
         <v>46217</v>
       </c>
       <c r="B44" t="n">
-        <v>131</v>
+        <v>451</v>
       </c>
       <c r="C44" t="n">
         <v>8888</v>
       </c>
       <c r="D44" t="n">
-        <v>609.86</v>
+        <v>2583.46</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1281,13 +1281,13 @@
         <v>46217</v>
       </c>
       <c r="B45" t="n">
-        <v>40</v>
+        <v>2767</v>
       </c>
       <c r="C45" t="n">
         <v>8888</v>
       </c>
       <c r="D45" t="n">
-        <v>733.37</v>
+        <v>596.88</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1300,13 +1300,13 @@
         <v>46217</v>
       </c>
       <c r="B46" t="n">
-        <v>40</v>
+        <v>1063</v>
       </c>
       <c r="C46" t="n">
         <v>8888</v>
       </c>
       <c r="D46" t="n">
-        <v>799.86</v>
+        <v>352.87</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1319,17 +1319,17 @@
         <v>46217</v>
       </c>
       <c r="B47" t="n">
-        <v>2651</v>
+        <v>58</v>
       </c>
       <c r="C47" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D47" t="n">
-        <v>316.61</v>
+        <v>2637.19</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1338,17 @@
         <v>46217</v>
       </c>
       <c r="B48" t="n">
-        <v>559</v>
+        <v>2211</v>
       </c>
       <c r="C48" t="n">
-        <v>8888</v>
+        <v>874</v>
       </c>
       <c r="D48" t="n">
-        <v>1562.5</v>
+        <v>967.05</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1357,13 +1357,13 @@
         <v>46217</v>
       </c>
       <c r="B49" t="n">
-        <v>2550</v>
+        <v>629</v>
       </c>
       <c r="C49" t="n">
         <v>8888</v>
       </c>
       <c r="D49" t="n">
-        <v>321.05</v>
+        <v>277.36</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1376,13 +1376,13 @@
         <v>46217</v>
       </c>
       <c r="B50" t="n">
-        <v>2250</v>
+        <v>629</v>
       </c>
       <c r="C50" t="n">
         <v>8888</v>
       </c>
       <c r="D50" t="n">
-        <v>1512.17</v>
+        <v>2049.78</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1395,17 +1395,17 @@
         <v>46217</v>
       </c>
       <c r="B51" t="n">
-        <v>1465</v>
+        <v>949</v>
       </c>
       <c r="C51" t="n">
-        <v>8888</v>
+        <v>1762</v>
       </c>
       <c r="D51" t="n">
-        <v>8550.709999999999</v>
+        <v>325.65</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1414,15 +1414,1231 @@
         <v>46217</v>
       </c>
       <c r="B52" t="n">
+        <v>2463</v>
+      </c>
+      <c r="C52" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D52" t="n">
+        <v>8336.43</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B53" t="n">
+        <v>1064</v>
+      </c>
+      <c r="C53" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1513.21</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B54" t="n">
+        <v>1478</v>
+      </c>
+      <c r="C54" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1294.76</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B55" t="n">
+        <v>358</v>
+      </c>
+      <c r="C55" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1918.33</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B56" t="n">
+        <v>2107</v>
+      </c>
+      <c r="C56" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2745.11</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B57" t="n">
+        <v>675</v>
+      </c>
+      <c r="C57" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D57" t="n">
+        <v>275.17</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B58" t="n">
+        <v>451</v>
+      </c>
+      <c r="C58" t="n">
+        <v>3403</v>
+      </c>
+      <c r="D58" t="n">
+        <v>327.28</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B59" t="n">
+        <v>2571</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1312</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2202.75</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B60" t="n">
+        <v>610</v>
+      </c>
+      <c r="C60" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D60" t="n">
+        <v>335.61</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1108</v>
+      </c>
+      <c r="C61" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D61" t="n">
+        <v>508.54</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B62" t="n">
+        <v>341</v>
+      </c>
+      <c r="C62" t="n">
+        <v>58</v>
+      </c>
+      <c r="D62" t="n">
+        <v>366.88</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B63" t="n">
+        <v>1653</v>
+      </c>
+      <c r="C63" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D63" t="n">
+        <v>4383.69</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B64" t="n">
+        <v>663</v>
+      </c>
+      <c r="C64" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D64" t="n">
+        <v>824.5599999999999</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B65" t="n">
+        <v>58</v>
+      </c>
+      <c r="C65" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D65" t="n">
+        <v>660.1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B66" t="n">
+        <v>429</v>
+      </c>
+      <c r="C66" t="n">
+        <v>2571</v>
+      </c>
+      <c r="D66" t="n">
+        <v>667.12</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B67" t="n">
         <v>483</v>
       </c>
-      <c r="C52" t="n">
-        <v>8888</v>
-      </c>
-      <c r="D52" t="n">
+      <c r="C67" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D67" t="n">
+        <v>938.34</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B68" t="n">
+        <v>2709</v>
+      </c>
+      <c r="C68" t="n">
+        <v>2220</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1663.5</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B69" t="n">
+        <v>1937</v>
+      </c>
+      <c r="C69" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1332.89</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B70" t="n">
+        <v>429</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1281</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1333.52</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B71" t="n">
+        <v>2211</v>
+      </c>
+      <c r="C71" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D71" t="n">
+        <v>797.61</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B72" t="n">
+        <v>1064</v>
+      </c>
+      <c r="C72" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D72" t="n">
+        <v>2383.39</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B73" t="n">
+        <v>451</v>
+      </c>
+      <c r="C73" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1371.26</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B74" t="n">
+        <v>40</v>
+      </c>
+      <c r="C74" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1093.47</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B75" t="n">
+        <v>360</v>
+      </c>
+      <c r="C75" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D75" t="n">
+        <v>7017.48</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B76" t="n">
+        <v>530</v>
+      </c>
+      <c r="C76" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D76" t="n">
+        <v>180.08</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B77" t="n">
+        <v>1137</v>
+      </c>
+      <c r="C77" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D77" t="n">
+        <v>2833.69</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B78" t="n">
+        <v>1293</v>
+      </c>
+      <c r="C78" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D78" t="n">
+        <v>3201.32</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B79" t="n">
+        <v>1293</v>
+      </c>
+      <c r="C79" t="n">
+        <v>601</v>
+      </c>
+      <c r="D79" t="n">
+        <v>456.47</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B80" t="n">
+        <v>2118</v>
+      </c>
+      <c r="C80" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D80" t="n">
+        <v>311.54</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B81" t="n">
+        <v>559</v>
+      </c>
+      <c r="C81" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D81" t="n">
+        <v>512.59</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B82" t="n">
+        <v>89</v>
+      </c>
+      <c r="C82" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1506.42</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B83" t="n">
+        <v>131</v>
+      </c>
+      <c r="C83" t="n">
+        <v>27</v>
+      </c>
+      <c r="D83" t="n">
+        <v>211.41</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B84" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C84" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1943.54</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B85" t="n">
+        <v>1299</v>
+      </c>
+      <c r="C85" t="n">
+        <v>27</v>
+      </c>
+      <c r="D85" t="n">
+        <v>262.02</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B86" t="n">
+        <v>131</v>
+      </c>
+      <c r="C86" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D86" t="n">
+        <v>609.86</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B87" t="n">
+        <v>2651</v>
+      </c>
+      <c r="C87" t="n">
+        <v>58</v>
+      </c>
+      <c r="D87" t="n">
+        <v>648.71</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B88" t="n">
+        <v>40</v>
+      </c>
+      <c r="C88" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D88" t="n">
+        <v>733.37</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B89" t="n">
+        <v>40</v>
+      </c>
+      <c r="C89" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D89" t="n">
+        <v>2529.31</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B90" t="n">
+        <v>626</v>
+      </c>
+      <c r="C90" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D90" t="n">
+        <v>13218.02</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B91" t="n">
+        <v>363</v>
+      </c>
+      <c r="C91" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D91" t="n">
+        <v>739.17</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B92" t="n">
+        <v>675</v>
+      </c>
+      <c r="C92" t="n">
+        <v>1898</v>
+      </c>
+      <c r="D92" t="n">
+        <v>107.13</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B93" t="n">
+        <v>636</v>
+      </c>
+      <c r="C93" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D93" t="n">
+        <v>5631.89</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B94" t="n">
+        <v>1075</v>
+      </c>
+      <c r="C94" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D94" t="n">
+        <v>421.29</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B95" t="n">
+        <v>2245</v>
+      </c>
+      <c r="C95" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D95" t="n">
+        <v>883.75</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B96" t="n">
+        <v>477</v>
+      </c>
+      <c r="C96" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D96" t="n">
+        <v>994.15</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B97" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C97" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D97" t="n">
+        <v>2931.07</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B98" t="n">
+        <v>2118</v>
+      </c>
+      <c r="C98" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D98" t="n">
+        <v>2646.39</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B99" t="n">
+        <v>2680</v>
+      </c>
+      <c r="C99" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D99" t="n">
+        <v>824.67</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B100" t="n">
+        <v>1653</v>
+      </c>
+      <c r="C100" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D100" t="n">
+        <v>2848.57</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B101" t="n">
+        <v>629</v>
+      </c>
+      <c r="C101" t="n">
+        <v>675</v>
+      </c>
+      <c r="D101" t="n">
+        <v>267.79</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B102" t="n">
+        <v>559</v>
+      </c>
+      <c r="C102" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1562.5</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B103" t="n">
+        <v>1465</v>
+      </c>
+      <c r="C103" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D103" t="n">
+        <v>9346.120000000001</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B104" t="n">
+        <v>2550</v>
+      </c>
+      <c r="C104" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D104" t="n">
+        <v>321.05</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B105" t="n">
+        <v>1756</v>
+      </c>
+      <c r="C105" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D105" t="n">
+        <v>2445</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B106" t="n">
+        <v>363</v>
+      </c>
+      <c r="C106" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D106" t="n">
+        <v>649.08</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B107" t="n">
+        <v>2698</v>
+      </c>
+      <c r="C107" t="n">
+        <v>874</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1183.42</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B108" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C108" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D108" t="n">
+        <v>1512.17</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B109" t="n">
+        <v>2681</v>
+      </c>
+      <c r="C109" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D109" t="n">
+        <v>2775.8</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B110" t="n">
+        <v>535</v>
+      </c>
+      <c r="C110" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D110" t="n">
+        <v>2806.71</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B111" t="n">
+        <v>2330</v>
+      </c>
+      <c r="C111" t="n">
+        <v>1954</v>
+      </c>
+      <c r="D111" t="n">
+        <v>1923.09</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B112" t="n">
+        <v>363</v>
+      </c>
+      <c r="C112" t="n">
+        <v>1898</v>
+      </c>
+      <c r="D112" t="n">
+        <v>1058.27</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B113" t="n">
+        <v>2709</v>
+      </c>
+      <c r="C113" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D113" t="n">
+        <v>1667.47</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B114" t="n">
+        <v>1137</v>
+      </c>
+      <c r="C114" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D114" t="n">
+        <v>3185.1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B115" t="n">
+        <v>2251</v>
+      </c>
+      <c r="C115" t="n">
+        <v>3403</v>
+      </c>
+      <c r="D115" t="n">
+        <v>510.18</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B116" t="n">
+        <v>483</v>
+      </c>
+      <c r="C116" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D116" t="n">
         <v>720.66</v>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E116" t="inlineStr">
         <is>
           <t>FORÇA DE VENDAS</t>
         </is>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E116"/>
+  <dimension ref="A1:E129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,7 +489,7 @@
         <v>8888</v>
       </c>
       <c r="D3" t="n">
-        <v>22505.79</v>
+        <v>24542.62</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -521,17 +521,17 @@
         <v>46217</v>
       </c>
       <c r="B5" t="n">
-        <v>2015</v>
+        <v>1993</v>
       </c>
       <c r="C5" t="n">
-        <v>2571</v>
+        <v>8888</v>
       </c>
       <c r="D5" t="n">
-        <v>679.9</v>
+        <v>1785.44</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -540,17 +540,17 @@
         <v>46217</v>
       </c>
       <c r="B6" t="n">
-        <v>1293</v>
+        <v>1102</v>
       </c>
       <c r="C6" t="n">
-        <v>1281</v>
+        <v>8888</v>
       </c>
       <c r="D6" t="n">
-        <v>1337.87</v>
+        <v>1264.43</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -559,17 +559,17 @@
         <v>46217</v>
       </c>
       <c r="B7" t="n">
-        <v>1102</v>
+        <v>2015</v>
       </c>
       <c r="C7" t="n">
-        <v>8888</v>
+        <v>2571</v>
       </c>
       <c r="D7" t="n">
-        <v>1199.81</v>
+        <v>679.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
         <v>46217</v>
       </c>
       <c r="B8" t="n">
-        <v>89</v>
+        <v>1293</v>
       </c>
       <c r="C8" t="n">
-        <v>8888</v>
+        <v>1281</v>
       </c>
       <c r="D8" t="n">
-        <v>4572.01</v>
+        <v>1337.87</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -597,13 +597,13 @@
         <v>46217</v>
       </c>
       <c r="B9" t="n">
-        <v>2768</v>
+        <v>89</v>
       </c>
       <c r="C9" t="n">
         <v>8888</v>
       </c>
       <c r="D9" t="n">
-        <v>3436.6</v>
+        <v>4572.01</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -616,17 +616,17 @@
         <v>46217</v>
       </c>
       <c r="B10" t="n">
-        <v>949</v>
+        <v>2768</v>
       </c>
       <c r="C10" t="n">
-        <v>1258</v>
+        <v>8888</v>
       </c>
       <c r="D10" t="n">
-        <v>196.87</v>
+        <v>3436.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -635,17 +635,17 @@
         <v>46217</v>
       </c>
       <c r="B11" t="n">
-        <v>1756</v>
+        <v>949</v>
       </c>
       <c r="C11" t="n">
-        <v>8888</v>
+        <v>1258</v>
       </c>
       <c r="D11" t="n">
-        <v>1799.7</v>
+        <v>196.87</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -654,17 +654,17 @@
         <v>46217</v>
       </c>
       <c r="B12" t="n">
-        <v>285</v>
+        <v>1756</v>
       </c>
       <c r="C12" t="n">
         <v>8888</v>
       </c>
       <c r="D12" t="n">
-        <v>1081.17</v>
+        <v>1799.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -673,13 +673,13 @@
         <v>46217</v>
       </c>
       <c r="B13" t="n">
-        <v>610</v>
+        <v>285</v>
       </c>
       <c r="C13" t="n">
         <v>8888</v>
       </c>
       <c r="D13" t="n">
-        <v>590.08</v>
+        <v>1081.17</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -692,17 +692,17 @@
         <v>46217</v>
       </c>
       <c r="B14" t="n">
-        <v>2755</v>
+        <v>610</v>
       </c>
       <c r="C14" t="n">
-        <v>2220</v>
+        <v>8888</v>
       </c>
       <c r="D14" t="n">
-        <v>1133.17</v>
+        <v>590.08</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -711,17 +711,17 @@
         <v>46217</v>
       </c>
       <c r="B15" t="n">
-        <v>2767</v>
+        <v>619</v>
       </c>
       <c r="C15" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D15" t="n">
-        <v>5000.2</v>
+        <v>236.34</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -730,17 +730,17 @@
         <v>46217</v>
       </c>
       <c r="B16" t="n">
-        <v>2767</v>
+        <v>2755</v>
       </c>
       <c r="C16" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D16" t="n">
-        <v>1175.73</v>
+        <v>1133.17</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
         <v>46217</v>
       </c>
       <c r="B17" t="n">
-        <v>1063</v>
+        <v>2767</v>
       </c>
       <c r="C17" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D17" t="n">
-        <v>1251.14</v>
+        <v>5000.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -768,17 +768,17 @@
         <v>46217</v>
       </c>
       <c r="B18" t="n">
-        <v>325</v>
+        <v>559</v>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D18" t="n">
-        <v>868.83</v>
+        <v>517.0700000000001</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
         <v>46217</v>
       </c>
       <c r="B19" t="n">
-        <v>610</v>
+        <v>2767</v>
       </c>
       <c r="C19" t="n">
         <v>8888</v>
       </c>
       <c r="D19" t="n">
-        <v>235.34</v>
+        <v>1175.73</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -806,17 +806,17 @@
         <v>46217</v>
       </c>
       <c r="B20" t="n">
-        <v>1906</v>
+        <v>1063</v>
       </c>
       <c r="C20" t="n">
         <v>8888</v>
       </c>
       <c r="D20" t="n">
-        <v>889.22</v>
+        <v>1251.14</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -825,13 +825,13 @@
         <v>46217</v>
       </c>
       <c r="B21" t="n">
-        <v>40</v>
+        <v>325</v>
       </c>
       <c r="C21" t="n">
         <v>58</v>
       </c>
       <c r="D21" t="n">
-        <v>325.04</v>
+        <v>868.83</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -844,17 +844,17 @@
         <v>46217</v>
       </c>
       <c r="B22" t="n">
-        <v>1117</v>
+        <v>610</v>
       </c>
       <c r="C22" t="n">
         <v>8888</v>
       </c>
       <c r="D22" t="n">
-        <v>349.47</v>
+        <v>235.34</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -863,17 +863,17 @@
         <v>46217</v>
       </c>
       <c r="B23" t="n">
-        <v>949</v>
+        <v>1906</v>
       </c>
       <c r="C23" t="n">
-        <v>998</v>
+        <v>8888</v>
       </c>
       <c r="D23" t="n">
-        <v>129.85</v>
+        <v>889.22</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -882,13 +882,13 @@
         <v>46217</v>
       </c>
       <c r="B24" t="n">
-        <v>2250</v>
+        <v>424</v>
       </c>
       <c r="C24" t="n">
         <v>8888</v>
       </c>
       <c r="D24" t="n">
-        <v>3180.11</v>
+        <v>2575.64</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -901,17 +901,17 @@
         <v>46217</v>
       </c>
       <c r="B25" t="n">
-        <v>2507</v>
+        <v>40</v>
       </c>
       <c r="C25" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D25" t="n">
-        <v>4167.12</v>
+        <v>325.04</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -920,17 +920,17 @@
         <v>46217</v>
       </c>
       <c r="B26" t="n">
-        <v>664</v>
+        <v>1117</v>
       </c>
       <c r="C26" t="n">
         <v>8888</v>
       </c>
       <c r="D26" t="n">
-        <v>3523.8</v>
+        <v>349.47</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -939,13 +939,13 @@
         <v>46217</v>
       </c>
       <c r="B27" t="n">
-        <v>1906</v>
+        <v>949</v>
       </c>
       <c r="C27" t="n">
-        <v>1954</v>
+        <v>998</v>
       </c>
       <c r="D27" t="n">
-        <v>1445.21</v>
+        <v>129.85</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -958,17 +958,17 @@
         <v>46217</v>
       </c>
       <c r="B28" t="n">
-        <v>1075</v>
+        <v>2250</v>
       </c>
       <c r="C28" t="n">
         <v>8888</v>
       </c>
       <c r="D28" t="n">
-        <v>470.95</v>
+        <v>3627.44</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -977,17 +977,17 @@
         <v>46217</v>
       </c>
       <c r="B29" t="n">
-        <v>2696</v>
+        <v>2507</v>
       </c>
       <c r="C29" t="n">
-        <v>1312</v>
+        <v>8888</v>
       </c>
       <c r="D29" t="n">
-        <v>677.76</v>
+        <v>4167.12</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -996,17 +996,17 @@
         <v>46217</v>
       </c>
       <c r="B30" t="n">
-        <v>360</v>
+        <v>664</v>
       </c>
       <c r="C30" t="n">
-        <v>546</v>
+        <v>8888</v>
       </c>
       <c r="D30" t="n">
-        <v>4515.36</v>
+        <v>3523.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1015,17 +1015,17 @@
         <v>46217</v>
       </c>
       <c r="B31" t="n">
-        <v>1293</v>
+        <v>1906</v>
       </c>
       <c r="C31" t="n">
-        <v>8888</v>
+        <v>1954</v>
       </c>
       <c r="D31" t="n">
-        <v>381.82</v>
+        <v>1445.21</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1034,13 +1034,13 @@
         <v>46217</v>
       </c>
       <c r="B32" t="n">
-        <v>2663</v>
+        <v>1075</v>
       </c>
       <c r="C32" t="n">
         <v>8888</v>
       </c>
       <c r="D32" t="n">
-        <v>2146.08</v>
+        <v>470.95</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1053,17 +1053,17 @@
         <v>46217</v>
       </c>
       <c r="B33" t="n">
-        <v>675</v>
+        <v>2696</v>
       </c>
       <c r="C33" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D33" t="n">
-        <v>289.67</v>
+        <v>677.76</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1072,17 +1072,17 @@
         <v>46217</v>
       </c>
       <c r="B34" t="n">
-        <v>1063</v>
+        <v>360</v>
       </c>
       <c r="C34" t="n">
-        <v>8888</v>
+        <v>546</v>
       </c>
       <c r="D34" t="n">
-        <v>1902.46</v>
+        <v>4515.36</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1091,13 +1091,13 @@
         <v>46217</v>
       </c>
       <c r="B35" t="n">
-        <v>1392</v>
+        <v>1293</v>
       </c>
       <c r="C35" t="n">
         <v>8888</v>
       </c>
       <c r="D35" t="n">
-        <v>814.61</v>
+        <v>381.82</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1110,17 +1110,17 @@
         <v>46217</v>
       </c>
       <c r="B36" t="n">
-        <v>360</v>
+        <v>2663</v>
       </c>
       <c r="C36" t="n">
         <v>8888</v>
       </c>
       <c r="D36" t="n">
-        <v>749.13</v>
+        <v>2146.08</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1129,17 +1129,17 @@
         <v>46217</v>
       </c>
       <c r="B37" t="n">
-        <v>2491</v>
+        <v>675</v>
       </c>
       <c r="C37" t="n">
         <v>8888</v>
       </c>
       <c r="D37" t="n">
-        <v>398.66</v>
+        <v>289.67</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1148,17 +1148,17 @@
         <v>46217</v>
       </c>
       <c r="B38" t="n">
-        <v>949</v>
+        <v>1063</v>
       </c>
       <c r="C38" t="n">
-        <v>1134</v>
+        <v>8888</v>
       </c>
       <c r="D38" t="n">
-        <v>327.6</v>
+        <v>1902.46</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1167,13 +1167,13 @@
         <v>46217</v>
       </c>
       <c r="B39" t="n">
-        <v>326</v>
+        <v>1392</v>
       </c>
       <c r="C39" t="n">
         <v>8888</v>
       </c>
       <c r="D39" t="n">
-        <v>212.63</v>
+        <v>814.61</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1186,13 +1186,13 @@
         <v>46217</v>
       </c>
       <c r="B40" t="n">
-        <v>1116</v>
+        <v>360</v>
       </c>
       <c r="C40" t="n">
         <v>8888</v>
       </c>
       <c r="D40" t="n">
-        <v>971.6</v>
+        <v>749.13</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1205,17 +1205,17 @@
         <v>46217</v>
       </c>
       <c r="B41" t="n">
-        <v>325</v>
+        <v>2491</v>
       </c>
       <c r="C41" t="n">
         <v>8888</v>
       </c>
       <c r="D41" t="n">
-        <v>538.37</v>
+        <v>398.66</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1224,13 +1224,13 @@
         <v>46217</v>
       </c>
       <c r="B42" t="n">
-        <v>1293</v>
+        <v>949</v>
       </c>
       <c r="C42" t="n">
-        <v>1898</v>
+        <v>1134</v>
       </c>
       <c r="D42" t="n">
-        <v>3534.85</v>
+        <v>327.6</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1243,13 +1243,13 @@
         <v>46217</v>
       </c>
       <c r="B43" t="n">
-        <v>1983</v>
+        <v>326</v>
       </c>
       <c r="C43" t="n">
         <v>8888</v>
       </c>
       <c r="D43" t="n">
-        <v>412.16</v>
+        <v>212.63</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1262,17 +1262,17 @@
         <v>46217</v>
       </c>
       <c r="B44" t="n">
-        <v>451</v>
+        <v>131</v>
       </c>
       <c r="C44" t="n">
         <v>8888</v>
       </c>
       <c r="D44" t="n">
-        <v>2583.46</v>
+        <v>360.06</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1281,13 +1281,13 @@
         <v>46217</v>
       </c>
       <c r="B45" t="n">
-        <v>2767</v>
+        <v>2279</v>
       </c>
       <c r="C45" t="n">
         <v>8888</v>
       </c>
       <c r="D45" t="n">
-        <v>596.88</v>
+        <v>1034.25</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1300,13 +1300,13 @@
         <v>46217</v>
       </c>
       <c r="B46" t="n">
-        <v>1063</v>
+        <v>1116</v>
       </c>
       <c r="C46" t="n">
         <v>8888</v>
       </c>
       <c r="D46" t="n">
-        <v>352.87</v>
+        <v>971.6</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1319,17 +1319,17 @@
         <v>46217</v>
       </c>
       <c r="B47" t="n">
-        <v>58</v>
+        <v>131</v>
       </c>
       <c r="C47" t="n">
         <v>8888</v>
       </c>
       <c r="D47" t="n">
-        <v>2637.19</v>
+        <v>1528.41</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1338,17 @@
         <v>46217</v>
       </c>
       <c r="B48" t="n">
-        <v>2211</v>
+        <v>325</v>
       </c>
       <c r="C48" t="n">
-        <v>874</v>
+        <v>8888</v>
       </c>
       <c r="D48" t="n">
-        <v>967.05</v>
+        <v>538.37</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1357,17 +1357,17 @@
         <v>46217</v>
       </c>
       <c r="B49" t="n">
-        <v>629</v>
+        <v>1293</v>
       </c>
       <c r="C49" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D49" t="n">
-        <v>277.36</v>
+        <v>3534.85</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1376,17 +1376,17 @@
         <v>46217</v>
       </c>
       <c r="B50" t="n">
-        <v>629</v>
+        <v>1983</v>
       </c>
       <c r="C50" t="n">
         <v>8888</v>
       </c>
       <c r="D50" t="n">
-        <v>2049.78</v>
+        <v>412.16</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1395,17 +1395,17 @@
         <v>46217</v>
       </c>
       <c r="B51" t="n">
-        <v>949</v>
+        <v>451</v>
       </c>
       <c r="C51" t="n">
-        <v>1762</v>
+        <v>8888</v>
       </c>
       <c r="D51" t="n">
-        <v>325.65</v>
+        <v>2583.46</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1414,17 +1414,17 @@
         <v>46217</v>
       </c>
       <c r="B52" t="n">
-        <v>2463</v>
+        <v>2767</v>
       </c>
       <c r="C52" t="n">
         <v>8888</v>
       </c>
       <c r="D52" t="n">
-        <v>8336.43</v>
+        <v>596.88</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1433,13 +1433,13 @@
         <v>46217</v>
       </c>
       <c r="B53" t="n">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="C53" t="n">
         <v>8888</v>
       </c>
       <c r="D53" t="n">
-        <v>1513.21</v>
+        <v>352.87</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -1452,13 +1452,13 @@
         <v>46217</v>
       </c>
       <c r="B54" t="n">
-        <v>1478</v>
+        <v>629</v>
       </c>
       <c r="C54" t="n">
         <v>8888</v>
       </c>
       <c r="D54" t="n">
-        <v>1294.76</v>
+        <v>559.15</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -1471,17 +1471,17 @@
         <v>46217</v>
       </c>
       <c r="B55" t="n">
-        <v>358</v>
+        <v>58</v>
       </c>
       <c r="C55" t="n">
         <v>8888</v>
       </c>
       <c r="D55" t="n">
-        <v>1918.33</v>
+        <v>2637.19</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1490,17 +1490,17 @@
         <v>46217</v>
       </c>
       <c r="B56" t="n">
-        <v>2107</v>
+        <v>2211</v>
       </c>
       <c r="C56" t="n">
-        <v>8888</v>
+        <v>874</v>
       </c>
       <c r="D56" t="n">
-        <v>2745.11</v>
+        <v>967.05</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1509,13 +1509,13 @@
         <v>46217</v>
       </c>
       <c r="B57" t="n">
-        <v>675</v>
+        <v>629</v>
       </c>
       <c r="C57" t="n">
         <v>8888</v>
       </c>
       <c r="D57" t="n">
-        <v>275.17</v>
+        <v>2049.78</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -1528,13 +1528,13 @@
         <v>46217</v>
       </c>
       <c r="B58" t="n">
-        <v>451</v>
+        <v>949</v>
       </c>
       <c r="C58" t="n">
-        <v>3403</v>
+        <v>1762</v>
       </c>
       <c r="D58" t="n">
-        <v>327.28</v>
+        <v>325.65</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -1547,17 +1547,17 @@
         <v>46217</v>
       </c>
       <c r="B59" t="n">
-        <v>2571</v>
+        <v>2463</v>
       </c>
       <c r="C59" t="n">
-        <v>1312</v>
+        <v>8888</v>
       </c>
       <c r="D59" t="n">
-        <v>2202.75</v>
+        <v>8336.43</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1566,17 +1566,17 @@
         <v>46217</v>
       </c>
       <c r="B60" t="n">
-        <v>610</v>
+        <v>1064</v>
       </c>
       <c r="C60" t="n">
         <v>8888</v>
       </c>
       <c r="D60" t="n">
-        <v>335.61</v>
+        <v>1513.21</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1585,17 +1585,17 @@
         <v>46217</v>
       </c>
       <c r="B61" t="n">
-        <v>1108</v>
+        <v>1478</v>
       </c>
       <c r="C61" t="n">
         <v>8888</v>
       </c>
       <c r="D61" t="n">
-        <v>508.54</v>
+        <v>1294.76</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1604,17 +1604,17 @@
         <v>46217</v>
       </c>
       <c r="B62" t="n">
-        <v>341</v>
+        <v>358</v>
       </c>
       <c r="C62" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D62" t="n">
-        <v>366.88</v>
+        <v>1918.33</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
         <v>46217</v>
       </c>
       <c r="B63" t="n">
-        <v>1653</v>
+        <v>2107</v>
       </c>
       <c r="C63" t="n">
         <v>8888</v>
       </c>
       <c r="D63" t="n">
-        <v>4383.69</v>
+        <v>2745.11</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1642,17 +1642,17 @@
         <v>46217</v>
       </c>
       <c r="B64" t="n">
-        <v>663</v>
+        <v>675</v>
       </c>
       <c r="C64" t="n">
         <v>8888</v>
       </c>
       <c r="D64" t="n">
-        <v>824.5599999999999</v>
+        <v>275.17</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1661,17 +1661,17 @@
         <v>46217</v>
       </c>
       <c r="B65" t="n">
-        <v>58</v>
+        <v>2279</v>
       </c>
       <c r="C65" t="n">
         <v>8888</v>
       </c>
       <c r="D65" t="n">
-        <v>660.1</v>
+        <v>1165.17</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1680,13 +1680,13 @@
         <v>46217</v>
       </c>
       <c r="B66" t="n">
-        <v>429</v>
+        <v>451</v>
       </c>
       <c r="C66" t="n">
-        <v>2571</v>
+        <v>3403</v>
       </c>
       <c r="D66" t="n">
-        <v>667.12</v>
+        <v>327.28</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -1699,17 +1699,17 @@
         <v>46217</v>
       </c>
       <c r="B67" t="n">
-        <v>483</v>
+        <v>2571</v>
       </c>
       <c r="C67" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D67" t="n">
-        <v>938.34</v>
+        <v>2202.75</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
         <v>46217</v>
       </c>
       <c r="B68" t="n">
-        <v>2709</v>
+        <v>610</v>
       </c>
       <c r="C68" t="n">
-        <v>2220</v>
+        <v>8888</v>
       </c>
       <c r="D68" t="n">
-        <v>1663.5</v>
+        <v>335.61</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1737,17 +1737,17 @@
         <v>46217</v>
       </c>
       <c r="B69" t="n">
-        <v>1937</v>
+        <v>1108</v>
       </c>
       <c r="C69" t="n">
         <v>8888</v>
       </c>
       <c r="D69" t="n">
-        <v>1332.89</v>
+        <v>508.54</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1756,13 +1756,13 @@
         <v>46217</v>
       </c>
       <c r="B70" t="n">
-        <v>429</v>
+        <v>341</v>
       </c>
       <c r="C70" t="n">
-        <v>1281</v>
+        <v>58</v>
       </c>
       <c r="D70" t="n">
-        <v>1333.52</v>
+        <v>366.88</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -1775,17 +1775,17 @@
         <v>46217</v>
       </c>
       <c r="B71" t="n">
-        <v>2211</v>
+        <v>1653</v>
       </c>
       <c r="C71" t="n">
         <v>8888</v>
       </c>
       <c r="D71" t="n">
-        <v>797.61</v>
+        <v>4383.69</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1794,13 +1794,13 @@
         <v>46217</v>
       </c>
       <c r="B72" t="n">
-        <v>1064</v>
+        <v>619</v>
       </c>
       <c r="C72" t="n">
         <v>8888</v>
       </c>
       <c r="D72" t="n">
-        <v>2383.39</v>
+        <v>779.87</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -1813,17 +1813,17 @@
         <v>46217</v>
       </c>
       <c r="B73" t="n">
-        <v>451</v>
+        <v>663</v>
       </c>
       <c r="C73" t="n">
         <v>8888</v>
       </c>
       <c r="D73" t="n">
-        <v>1371.26</v>
+        <v>824.5599999999999</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1832,17 +1832,17 @@
         <v>46217</v>
       </c>
       <c r="B74" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="C74" t="n">
         <v>8888</v>
       </c>
       <c r="D74" t="n">
-        <v>1093.47</v>
+        <v>660.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1851,17 +1851,17 @@
         <v>46217</v>
       </c>
       <c r="B75" t="n">
-        <v>360</v>
+        <v>429</v>
       </c>
       <c r="C75" t="n">
-        <v>8888</v>
+        <v>2571</v>
       </c>
       <c r="D75" t="n">
-        <v>7017.48</v>
+        <v>667.12</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1870,13 +1870,13 @@
         <v>46217</v>
       </c>
       <c r="B76" t="n">
-        <v>530</v>
+        <v>483</v>
       </c>
       <c r="C76" t="n">
         <v>8888</v>
       </c>
       <c r="D76" t="n">
-        <v>180.08</v>
+        <v>1290.28</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -1889,17 +1889,17 @@
         <v>46217</v>
       </c>
       <c r="B77" t="n">
-        <v>1137</v>
+        <v>2709</v>
       </c>
       <c r="C77" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D77" t="n">
-        <v>2833.69</v>
+        <v>1663.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1908,17 +1908,17 @@
         <v>46217</v>
       </c>
       <c r="B78" t="n">
-        <v>1293</v>
+        <v>1937</v>
       </c>
       <c r="C78" t="n">
         <v>8888</v>
       </c>
       <c r="D78" t="n">
-        <v>3201.32</v>
+        <v>1332.89</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1927,13 +1927,13 @@
         <v>46217</v>
       </c>
       <c r="B79" t="n">
-        <v>1293</v>
+        <v>429</v>
       </c>
       <c r="C79" t="n">
-        <v>601</v>
+        <v>1281</v>
       </c>
       <c r="D79" t="n">
-        <v>456.47</v>
+        <v>1333.52</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -1946,17 +1946,17 @@
         <v>46217</v>
       </c>
       <c r="B80" t="n">
-        <v>2118</v>
+        <v>2211</v>
       </c>
       <c r="C80" t="n">
         <v>8888</v>
       </c>
       <c r="D80" t="n">
-        <v>311.54</v>
+        <v>797.61</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1965,13 +1965,13 @@
         <v>46217</v>
       </c>
       <c r="B81" t="n">
-        <v>559</v>
+        <v>131</v>
       </c>
       <c r="C81" t="n">
         <v>8888</v>
       </c>
       <c r="D81" t="n">
-        <v>512.59</v>
+        <v>2340.29</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -1984,17 +1984,17 @@
         <v>46217</v>
       </c>
       <c r="B82" t="n">
-        <v>89</v>
+        <v>131</v>
       </c>
       <c r="C82" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D82" t="n">
-        <v>1506.42</v>
+        <v>669.39</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2003,17 +2003,17 @@
         <v>46217</v>
       </c>
       <c r="B83" t="n">
-        <v>131</v>
+        <v>1064</v>
       </c>
       <c r="C83" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D83" t="n">
-        <v>211.41</v>
+        <v>2383.39</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2022,17 +2022,17 @@
         <v>46217</v>
       </c>
       <c r="B84" t="n">
-        <v>2250</v>
+        <v>2251</v>
       </c>
       <c r="C84" t="n">
         <v>8888</v>
       </c>
       <c r="D84" t="n">
-        <v>1943.54</v>
+        <v>797.58</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2041,17 +2041,17 @@
         <v>46217</v>
       </c>
       <c r="B85" t="n">
-        <v>1299</v>
+        <v>451</v>
       </c>
       <c r="C85" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D85" t="n">
-        <v>262.02</v>
+        <v>1371.26</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2060,17 +2060,17 @@
         <v>46217</v>
       </c>
       <c r="B86" t="n">
-        <v>131</v>
+        <v>40</v>
       </c>
       <c r="C86" t="n">
         <v>8888</v>
       </c>
       <c r="D86" t="n">
-        <v>609.86</v>
+        <v>1093.47</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2079,17 +2079,17 @@
         <v>46217</v>
       </c>
       <c r="B87" t="n">
-        <v>2651</v>
+        <v>360</v>
       </c>
       <c r="C87" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D87" t="n">
-        <v>648.71</v>
+        <v>7017.48</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2098,17 +2098,17 @@
         <v>46217</v>
       </c>
       <c r="B88" t="n">
-        <v>40</v>
+        <v>530</v>
       </c>
       <c r="C88" t="n">
         <v>8888</v>
       </c>
       <c r="D88" t="n">
-        <v>733.37</v>
+        <v>180.08</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2117,17 +2117,17 @@
         <v>46217</v>
       </c>
       <c r="B89" t="n">
-        <v>40</v>
+        <v>1137</v>
       </c>
       <c r="C89" t="n">
         <v>8888</v>
       </c>
       <c r="D89" t="n">
-        <v>2529.31</v>
+        <v>2833.69</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2136,17 +2136,17 @@
         <v>46217</v>
       </c>
       <c r="B90" t="n">
-        <v>626</v>
+        <v>1293</v>
       </c>
       <c r="C90" t="n">
         <v>8888</v>
       </c>
       <c r="D90" t="n">
-        <v>13218.02</v>
+        <v>3201.32</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2155,17 +2155,17 @@
         <v>46217</v>
       </c>
       <c r="B91" t="n">
-        <v>363</v>
+        <v>1293</v>
       </c>
       <c r="C91" t="n">
-        <v>8888</v>
+        <v>601</v>
       </c>
       <c r="D91" t="n">
-        <v>739.17</v>
+        <v>456.47</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2174,17 +2174,17 @@
         <v>46217</v>
       </c>
       <c r="B92" t="n">
-        <v>675</v>
+        <v>2118</v>
       </c>
       <c r="C92" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D92" t="n">
-        <v>107.13</v>
+        <v>311.54</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2193,17 +2193,17 @@
         <v>46217</v>
       </c>
       <c r="B93" t="n">
-        <v>636</v>
+        <v>424</v>
       </c>
       <c r="C93" t="n">
         <v>8888</v>
       </c>
       <c r="D93" t="n">
-        <v>5631.89</v>
+        <v>349.68</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2212,13 +2212,13 @@
         <v>46217</v>
       </c>
       <c r="B94" t="n">
-        <v>1075</v>
+        <v>559</v>
       </c>
       <c r="C94" t="n">
         <v>8888</v>
       </c>
       <c r="D94" t="n">
-        <v>421.29</v>
+        <v>1064.63</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -2231,17 +2231,17 @@
         <v>46217</v>
       </c>
       <c r="B95" t="n">
-        <v>2245</v>
+        <v>89</v>
       </c>
       <c r="C95" t="n">
         <v>8888</v>
       </c>
       <c r="D95" t="n">
-        <v>883.75</v>
+        <v>1506.42</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2250,17 +2250,17 @@
         <v>46217</v>
       </c>
       <c r="B96" t="n">
-        <v>477</v>
+        <v>2250</v>
       </c>
       <c r="C96" t="n">
         <v>8888</v>
       </c>
       <c r="D96" t="n">
-        <v>994.15</v>
+        <v>1943.54</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2269,17 +2269,17 @@
         <v>46217</v>
       </c>
       <c r="B97" t="n">
-        <v>2015</v>
+        <v>1299</v>
       </c>
       <c r="C97" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D97" t="n">
-        <v>2931.07</v>
+        <v>262.02</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
         <v>46217</v>
       </c>
       <c r="B98" t="n">
-        <v>2118</v>
+        <v>2651</v>
       </c>
       <c r="C98" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D98" t="n">
-        <v>2646.39</v>
+        <v>648.71</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2307,13 +2307,13 @@
         <v>46217</v>
       </c>
       <c r="B99" t="n">
-        <v>2680</v>
+        <v>40</v>
       </c>
       <c r="C99" t="n">
         <v>8888</v>
       </c>
       <c r="D99" t="n">
-        <v>824.67</v>
+        <v>733.37</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -2326,17 +2326,17 @@
         <v>46217</v>
       </c>
       <c r="B100" t="n">
-        <v>1653</v>
+        <v>40</v>
       </c>
       <c r="C100" t="n">
         <v>8888</v>
       </c>
       <c r="D100" t="n">
-        <v>2848.57</v>
+        <v>2529.31</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2345,17 +2345,17 @@
         <v>46217</v>
       </c>
       <c r="B101" t="n">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="C101" t="n">
-        <v>675</v>
+        <v>8888</v>
       </c>
       <c r="D101" t="n">
-        <v>267.79</v>
+        <v>13218.02</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2364,17 +2364,17 @@
         <v>46217</v>
       </c>
       <c r="B102" t="n">
-        <v>559</v>
+        <v>363</v>
       </c>
       <c r="C102" t="n">
         <v>8888</v>
       </c>
       <c r="D102" t="n">
-        <v>1562.5</v>
+        <v>739.17</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2383,17 +2383,17 @@
         <v>46217</v>
       </c>
       <c r="B103" t="n">
-        <v>1465</v>
+        <v>675</v>
       </c>
       <c r="C103" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D103" t="n">
-        <v>9346.120000000001</v>
+        <v>107.13</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2402,17 +2402,17 @@
         <v>46217</v>
       </c>
       <c r="B104" t="n">
-        <v>2550</v>
+        <v>636</v>
       </c>
       <c r="C104" t="n">
         <v>8888</v>
       </c>
       <c r="D104" t="n">
-        <v>321.05</v>
+        <v>5631.89</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2421,13 +2421,13 @@
         <v>46217</v>
       </c>
       <c r="B105" t="n">
-        <v>1756</v>
+        <v>1075</v>
       </c>
       <c r="C105" t="n">
         <v>8888</v>
       </c>
       <c r="D105" t="n">
-        <v>2445</v>
+        <v>1331.89</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -2440,17 +2440,17 @@
         <v>46217</v>
       </c>
       <c r="B106" t="n">
-        <v>363</v>
+        <v>2245</v>
       </c>
       <c r="C106" t="n">
         <v>8888</v>
       </c>
       <c r="D106" t="n">
-        <v>649.08</v>
+        <v>883.75</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2459,17 +2459,17 @@
         <v>46217</v>
       </c>
       <c r="B107" t="n">
-        <v>2698</v>
+        <v>477</v>
       </c>
       <c r="C107" t="n">
-        <v>874</v>
+        <v>8888</v>
       </c>
       <c r="D107" t="n">
-        <v>1183.42</v>
+        <v>994.15</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2478,13 +2478,13 @@
         <v>46217</v>
       </c>
       <c r="B108" t="n">
-        <v>2250</v>
+        <v>2015</v>
       </c>
       <c r="C108" t="n">
         <v>8888</v>
       </c>
       <c r="D108" t="n">
-        <v>1512.17</v>
+        <v>2931.07</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -2497,17 +2497,17 @@
         <v>46217</v>
       </c>
       <c r="B109" t="n">
-        <v>2681</v>
+        <v>1064</v>
       </c>
       <c r="C109" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D109" t="n">
-        <v>2775.8</v>
+        <v>451.38</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2516,17 +2516,17 @@
         <v>46217</v>
       </c>
       <c r="B110" t="n">
-        <v>535</v>
+        <v>1983</v>
       </c>
       <c r="C110" t="n">
         <v>8888</v>
       </c>
       <c r="D110" t="n">
-        <v>2806.71</v>
+        <v>680.42</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2535,17 +2535,17 @@
         <v>46217</v>
       </c>
       <c r="B111" t="n">
-        <v>2330</v>
+        <v>2118</v>
       </c>
       <c r="C111" t="n">
-        <v>1954</v>
+        <v>8888</v>
       </c>
       <c r="D111" t="n">
-        <v>1923.09</v>
+        <v>2646.39</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2554,17 +2554,17 @@
         <v>46217</v>
       </c>
       <c r="B112" t="n">
-        <v>363</v>
+        <v>2680</v>
       </c>
       <c r="C112" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D112" t="n">
-        <v>1058.27</v>
+        <v>824.67</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2573,13 +2573,13 @@
         <v>46217</v>
       </c>
       <c r="B113" t="n">
-        <v>2709</v>
+        <v>1653</v>
       </c>
       <c r="C113" t="n">
         <v>8888</v>
       </c>
       <c r="D113" t="n">
-        <v>1667.47</v>
+        <v>2848.57</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -2592,17 +2592,17 @@
         <v>46217</v>
       </c>
       <c r="B114" t="n">
-        <v>1137</v>
+        <v>629</v>
       </c>
       <c r="C114" t="n">
-        <v>8888</v>
+        <v>675</v>
       </c>
       <c r="D114" t="n">
-        <v>3185.1</v>
+        <v>267.79</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2611,17 +2611,17 @@
         <v>46217</v>
       </c>
       <c r="B115" t="n">
-        <v>2251</v>
+        <v>559</v>
       </c>
       <c r="C115" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D115" t="n">
-        <v>510.18</v>
+        <v>1562.5</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2630,17 +2630,264 @@
         <v>46217</v>
       </c>
       <c r="B116" t="n">
+        <v>1465</v>
+      </c>
+      <c r="C116" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D116" t="n">
+        <v>9346.120000000001</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B117" t="n">
+        <v>2550</v>
+      </c>
+      <c r="C117" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D117" t="n">
+        <v>321.05</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B118" t="n">
+        <v>1756</v>
+      </c>
+      <c r="C118" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D118" t="n">
+        <v>2445</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B119" t="n">
+        <v>363</v>
+      </c>
+      <c r="C119" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D119" t="n">
+        <v>649.08</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B120" t="n">
+        <v>2698</v>
+      </c>
+      <c r="C120" t="n">
+        <v>874</v>
+      </c>
+      <c r="D120" t="n">
+        <v>1183.42</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B121" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C121" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1512.17</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B122" t="n">
+        <v>2681</v>
+      </c>
+      <c r="C122" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D122" t="n">
+        <v>2775.8</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B123" t="n">
+        <v>535</v>
+      </c>
+      <c r="C123" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D123" t="n">
+        <v>2806.71</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B124" t="n">
         <v>483</v>
       </c>
-      <c r="C116" t="n">
-        <v>8888</v>
-      </c>
-      <c r="D116" t="n">
-        <v>720.66</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>FORÇA DE VENDAS</t>
+      <c r="C124" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D124" t="n">
+        <v>2100.84</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B125" t="n">
+        <v>2330</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1954</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1923.09</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B126" t="n">
+        <v>363</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1898</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1058.27</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B127" t="n">
+        <v>2709</v>
+      </c>
+      <c r="C127" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1667.47</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B128" t="n">
+        <v>1137</v>
+      </c>
+      <c r="C128" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D128" t="n">
+        <v>3185.1</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B129" t="n">
+        <v>2251</v>
+      </c>
+      <c r="C129" t="n">
+        <v>3403</v>
+      </c>
+      <c r="D129" t="n">
+        <v>510.18</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E129"/>
+  <dimension ref="A1:E131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,7 +603,7 @@
         <v>8888</v>
       </c>
       <c r="D9" t="n">
-        <v>4572.01</v>
+        <v>5652.15</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
         <v>8888</v>
       </c>
       <c r="D13" t="n">
-        <v>1081.17</v>
+        <v>2593.28</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1091,17 +1091,17 @@
         <v>46217</v>
       </c>
       <c r="B35" t="n">
-        <v>1293</v>
+        <v>2651</v>
       </c>
       <c r="C35" t="n">
         <v>8888</v>
       </c>
       <c r="D35" t="n">
-        <v>381.82</v>
+        <v>638.64</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1110,17 +1110,17 @@
         <v>46217</v>
       </c>
       <c r="B36" t="n">
-        <v>2663</v>
+        <v>1293</v>
       </c>
       <c r="C36" t="n">
         <v>8888</v>
       </c>
       <c r="D36" t="n">
-        <v>2146.08</v>
+        <v>381.82</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1129,17 +1129,17 @@
         <v>46217</v>
       </c>
       <c r="B37" t="n">
-        <v>675</v>
+        <v>2663</v>
       </c>
       <c r="C37" t="n">
         <v>8888</v>
       </c>
       <c r="D37" t="n">
-        <v>289.67</v>
+        <v>2146.08</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1148,17 +1148,17 @@
         <v>46217</v>
       </c>
       <c r="B38" t="n">
-        <v>1063</v>
+        <v>675</v>
       </c>
       <c r="C38" t="n">
         <v>8888</v>
       </c>
       <c r="D38" t="n">
-        <v>1902.46</v>
+        <v>289.67</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1167,17 +1167,17 @@
         <v>46217</v>
       </c>
       <c r="B39" t="n">
-        <v>1392</v>
+        <v>1063</v>
       </c>
       <c r="C39" t="n">
         <v>8888</v>
       </c>
       <c r="D39" t="n">
-        <v>814.61</v>
+        <v>1902.46</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1186,17 +1186,17 @@
         <v>46217</v>
       </c>
       <c r="B40" t="n">
-        <v>360</v>
+        <v>1392</v>
       </c>
       <c r="C40" t="n">
         <v>8888</v>
       </c>
       <c r="D40" t="n">
-        <v>749.13</v>
+        <v>814.61</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1205,17 +1205,17 @@
         <v>46217</v>
       </c>
       <c r="B41" t="n">
-        <v>2491</v>
+        <v>360</v>
       </c>
       <c r="C41" t="n">
         <v>8888</v>
       </c>
       <c r="D41" t="n">
-        <v>398.66</v>
+        <v>749.13</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1224,17 +1224,17 @@
         <v>46217</v>
       </c>
       <c r="B42" t="n">
-        <v>949</v>
+        <v>2491</v>
       </c>
       <c r="C42" t="n">
-        <v>1134</v>
+        <v>8888</v>
       </c>
       <c r="D42" t="n">
-        <v>327.6</v>
+        <v>398.66</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
         <v>46217</v>
       </c>
       <c r="B43" t="n">
-        <v>326</v>
+        <v>949</v>
       </c>
       <c r="C43" t="n">
-        <v>8888</v>
+        <v>1134</v>
       </c>
       <c r="D43" t="n">
-        <v>212.63</v>
+        <v>327.6</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1262,13 +1262,13 @@
         <v>46217</v>
       </c>
       <c r="B44" t="n">
-        <v>131</v>
+        <v>326</v>
       </c>
       <c r="C44" t="n">
         <v>8888</v>
       </c>
       <c r="D44" t="n">
-        <v>360.06</v>
+        <v>212.63</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1281,17 +1281,17 @@
         <v>46217</v>
       </c>
       <c r="B45" t="n">
-        <v>2279</v>
+        <v>325</v>
       </c>
       <c r="C45" t="n">
         <v>8888</v>
       </c>
       <c r="D45" t="n">
-        <v>1034.25</v>
+        <v>584.27</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1300,17 +1300,17 @@
         <v>46217</v>
       </c>
       <c r="B46" t="n">
-        <v>1116</v>
+        <v>131</v>
       </c>
       <c r="C46" t="n">
         <v>8888</v>
       </c>
       <c r="D46" t="n">
-        <v>971.6</v>
+        <v>360.06</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1319,13 +1319,13 @@
         <v>46217</v>
       </c>
       <c r="B47" t="n">
-        <v>131</v>
+        <v>2279</v>
       </c>
       <c r="C47" t="n">
         <v>8888</v>
       </c>
       <c r="D47" t="n">
-        <v>1528.41</v>
+        <v>1034.25</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1338,17 +1338,17 @@
         <v>46217</v>
       </c>
       <c r="B48" t="n">
-        <v>325</v>
+        <v>1116</v>
       </c>
       <c r="C48" t="n">
         <v>8888</v>
       </c>
       <c r="D48" t="n">
-        <v>538.37</v>
+        <v>1293.89</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1357,17 +1357,17 @@
         <v>46217</v>
       </c>
       <c r="B49" t="n">
-        <v>1293</v>
+        <v>131</v>
       </c>
       <c r="C49" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D49" t="n">
-        <v>3534.85</v>
+        <v>1528.41</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1376,17 +1376,17 @@
         <v>46217</v>
       </c>
       <c r="B50" t="n">
-        <v>1983</v>
+        <v>1293</v>
       </c>
       <c r="C50" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D50" t="n">
-        <v>412.16</v>
+        <v>3534.85</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1395,17 +1395,17 @@
         <v>46217</v>
       </c>
       <c r="B51" t="n">
-        <v>451</v>
+        <v>1983</v>
       </c>
       <c r="C51" t="n">
         <v>8888</v>
       </c>
       <c r="D51" t="n">
-        <v>2583.46</v>
+        <v>412.16</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1414,17 +1414,17 @@
         <v>46217</v>
       </c>
       <c r="B52" t="n">
-        <v>2767</v>
+        <v>451</v>
       </c>
       <c r="C52" t="n">
         <v>8888</v>
       </c>
       <c r="D52" t="n">
-        <v>596.88</v>
+        <v>2583.46</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1433,17 +1433,17 @@
         <v>46217</v>
       </c>
       <c r="B53" t="n">
-        <v>1063</v>
+        <v>2767</v>
       </c>
       <c r="C53" t="n">
         <v>8888</v>
       </c>
       <c r="D53" t="n">
-        <v>352.87</v>
+        <v>596.88</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1452,13 +1452,13 @@
         <v>46217</v>
       </c>
       <c r="B54" t="n">
-        <v>629</v>
+        <v>1063</v>
       </c>
       <c r="C54" t="n">
         <v>8888</v>
       </c>
       <c r="D54" t="n">
-        <v>559.15</v>
+        <v>352.87</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -1471,17 +1471,17 @@
         <v>46217</v>
       </c>
       <c r="B55" t="n">
-        <v>58</v>
+        <v>629</v>
       </c>
       <c r="C55" t="n">
         <v>8888</v>
       </c>
       <c r="D55" t="n">
-        <v>2637.19</v>
+        <v>559.15</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1490,17 +1490,17 @@
         <v>46217</v>
       </c>
       <c r="B56" t="n">
-        <v>2211</v>
+        <v>58</v>
       </c>
       <c r="C56" t="n">
-        <v>874</v>
+        <v>8888</v>
       </c>
       <c r="D56" t="n">
-        <v>967.05</v>
+        <v>2637.19</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1509,17 +1509,17 @@
         <v>46217</v>
       </c>
       <c r="B57" t="n">
-        <v>629</v>
+        <v>2211</v>
       </c>
       <c r="C57" t="n">
-        <v>8888</v>
+        <v>874</v>
       </c>
       <c r="D57" t="n">
-        <v>2049.78</v>
+        <v>967.05</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1528,17 +1528,17 @@
         <v>46217</v>
       </c>
       <c r="B58" t="n">
-        <v>949</v>
+        <v>1117</v>
       </c>
       <c r="C58" t="n">
-        <v>1762</v>
+        <v>8888</v>
       </c>
       <c r="D58" t="n">
-        <v>325.65</v>
+        <v>581.51</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1547,17 +1547,17 @@
         <v>46217</v>
       </c>
       <c r="B59" t="n">
-        <v>2463</v>
+        <v>629</v>
       </c>
       <c r="C59" t="n">
         <v>8888</v>
       </c>
       <c r="D59" t="n">
-        <v>8336.43</v>
+        <v>2049.78</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1566,17 +1566,17 @@
         <v>46217</v>
       </c>
       <c r="B60" t="n">
-        <v>1064</v>
+        <v>949</v>
       </c>
       <c r="C60" t="n">
-        <v>8888</v>
+        <v>1762</v>
       </c>
       <c r="D60" t="n">
-        <v>1513.21</v>
+        <v>325.65</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1585,17 +1585,17 @@
         <v>46217</v>
       </c>
       <c r="B61" t="n">
-        <v>1478</v>
+        <v>2463</v>
       </c>
       <c r="C61" t="n">
         <v>8888</v>
       </c>
       <c r="D61" t="n">
-        <v>1294.76</v>
+        <v>8336.43</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1604,13 +1604,13 @@
         <v>46217</v>
       </c>
       <c r="B62" t="n">
-        <v>358</v>
+        <v>1064</v>
       </c>
       <c r="C62" t="n">
         <v>8888</v>
       </c>
       <c r="D62" t="n">
-        <v>1918.33</v>
+        <v>1513.21</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -1623,17 +1623,17 @@
         <v>46217</v>
       </c>
       <c r="B63" t="n">
-        <v>2107</v>
+        <v>1478</v>
       </c>
       <c r="C63" t="n">
         <v>8888</v>
       </c>
       <c r="D63" t="n">
-        <v>2745.11</v>
+        <v>1294.76</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1642,17 +1642,17 @@
         <v>46217</v>
       </c>
       <c r="B64" t="n">
-        <v>675</v>
+        <v>358</v>
       </c>
       <c r="C64" t="n">
         <v>8888</v>
       </c>
       <c r="D64" t="n">
-        <v>275.17</v>
+        <v>1918.33</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1661,17 +1661,17 @@
         <v>46217</v>
       </c>
       <c r="B65" t="n">
-        <v>2279</v>
+        <v>2107</v>
       </c>
       <c r="C65" t="n">
         <v>8888</v>
       </c>
       <c r="D65" t="n">
-        <v>1165.17</v>
+        <v>2745.11</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1680,17 +1680,17 @@
         <v>46217</v>
       </c>
       <c r="B66" t="n">
-        <v>451</v>
+        <v>675</v>
       </c>
       <c r="C66" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D66" t="n">
-        <v>327.28</v>
+        <v>275.17</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1699,17 +1699,17 @@
         <v>46217</v>
       </c>
       <c r="B67" t="n">
-        <v>2571</v>
+        <v>2279</v>
       </c>
       <c r="C67" t="n">
-        <v>1312</v>
+        <v>8888</v>
       </c>
       <c r="D67" t="n">
-        <v>2202.75</v>
+        <v>1165.17</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
         <v>46217</v>
       </c>
       <c r="B68" t="n">
-        <v>610</v>
+        <v>451</v>
       </c>
       <c r="C68" t="n">
-        <v>8888</v>
+        <v>3403</v>
       </c>
       <c r="D68" t="n">
-        <v>335.61</v>
+        <v>327.28</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1737,17 +1737,17 @@
         <v>46217</v>
       </c>
       <c r="B69" t="n">
-        <v>1108</v>
+        <v>2571</v>
       </c>
       <c r="C69" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D69" t="n">
-        <v>508.54</v>
+        <v>2202.75</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1756,17 +1756,17 @@
         <v>46217</v>
       </c>
       <c r="B70" t="n">
-        <v>341</v>
+        <v>610</v>
       </c>
       <c r="C70" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D70" t="n">
-        <v>366.88</v>
+        <v>335.61</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1775,17 +1775,17 @@
         <v>46217</v>
       </c>
       <c r="B71" t="n">
-        <v>1653</v>
+        <v>1108</v>
       </c>
       <c r="C71" t="n">
         <v>8888</v>
       </c>
       <c r="D71" t="n">
-        <v>4383.69</v>
+        <v>508.54</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1794,17 +1794,17 @@
         <v>46217</v>
       </c>
       <c r="B72" t="n">
-        <v>619</v>
+        <v>341</v>
       </c>
       <c r="C72" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D72" t="n">
-        <v>779.87</v>
+        <v>366.88</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1813,13 +1813,13 @@
         <v>46217</v>
       </c>
       <c r="B73" t="n">
-        <v>663</v>
+        <v>1653</v>
       </c>
       <c r="C73" t="n">
         <v>8888</v>
       </c>
       <c r="D73" t="n">
-        <v>824.5599999999999</v>
+        <v>4383.69</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -1832,13 +1832,13 @@
         <v>46217</v>
       </c>
       <c r="B74" t="n">
-        <v>58</v>
+        <v>619</v>
       </c>
       <c r="C74" t="n">
         <v>8888</v>
       </c>
       <c r="D74" t="n">
-        <v>660.1</v>
+        <v>779.87</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -1851,17 +1851,17 @@
         <v>46217</v>
       </c>
       <c r="B75" t="n">
-        <v>429</v>
+        <v>663</v>
       </c>
       <c r="C75" t="n">
-        <v>2571</v>
+        <v>8888</v>
       </c>
       <c r="D75" t="n">
-        <v>667.12</v>
+        <v>824.5599999999999</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1870,17 +1870,17 @@
         <v>46217</v>
       </c>
       <c r="B76" t="n">
-        <v>483</v>
+        <v>58</v>
       </c>
       <c r="C76" t="n">
         <v>8888</v>
       </c>
       <c r="D76" t="n">
-        <v>1290.28</v>
+        <v>660.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1889,13 +1889,13 @@
         <v>46217</v>
       </c>
       <c r="B77" t="n">
-        <v>2709</v>
+        <v>429</v>
       </c>
       <c r="C77" t="n">
-        <v>2220</v>
+        <v>2571</v>
       </c>
       <c r="D77" t="n">
-        <v>1663.5</v>
+        <v>667.12</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -1908,13 +1908,13 @@
         <v>46217</v>
       </c>
       <c r="B78" t="n">
-        <v>1937</v>
+        <v>483</v>
       </c>
       <c r="C78" t="n">
         <v>8888</v>
       </c>
       <c r="D78" t="n">
-        <v>1332.89</v>
+        <v>1290.28</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -1927,13 +1927,13 @@
         <v>46217</v>
       </c>
       <c r="B79" t="n">
-        <v>429</v>
+        <v>2709</v>
       </c>
       <c r="C79" t="n">
-        <v>1281</v>
+        <v>2220</v>
       </c>
       <c r="D79" t="n">
-        <v>1333.52</v>
+        <v>1663.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -1946,17 +1946,17 @@
         <v>46217</v>
       </c>
       <c r="B80" t="n">
-        <v>2211</v>
+        <v>1937</v>
       </c>
       <c r="C80" t="n">
         <v>8888</v>
       </c>
       <c r="D80" t="n">
-        <v>797.61</v>
+        <v>1332.89</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1965,17 +1965,17 @@
         <v>46217</v>
       </c>
       <c r="B81" t="n">
-        <v>131</v>
+        <v>429</v>
       </c>
       <c r="C81" t="n">
-        <v>8888</v>
+        <v>1281</v>
       </c>
       <c r="D81" t="n">
-        <v>2340.29</v>
+        <v>1333.52</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1984,17 +1984,17 @@
         <v>46217</v>
       </c>
       <c r="B82" t="n">
-        <v>131</v>
+        <v>2211</v>
       </c>
       <c r="C82" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D82" t="n">
-        <v>669.39</v>
+        <v>797.61</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2003,17 +2003,17 @@
         <v>46217</v>
       </c>
       <c r="B83" t="n">
-        <v>1064</v>
+        <v>131</v>
       </c>
       <c r="C83" t="n">
         <v>8888</v>
       </c>
       <c r="D83" t="n">
-        <v>2383.39</v>
+        <v>2340.29</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2022,17 +2022,17 @@
         <v>46217</v>
       </c>
       <c r="B84" t="n">
-        <v>2251</v>
+        <v>131</v>
       </c>
       <c r="C84" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D84" t="n">
-        <v>797.58</v>
+        <v>669.39</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2041,13 +2041,13 @@
         <v>46217</v>
       </c>
       <c r="B85" t="n">
-        <v>451</v>
+        <v>1064</v>
       </c>
       <c r="C85" t="n">
         <v>8888</v>
       </c>
       <c r="D85" t="n">
-        <v>1371.26</v>
+        <v>2383.39</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -2060,17 +2060,17 @@
         <v>46217</v>
       </c>
       <c r="B86" t="n">
-        <v>40</v>
+        <v>2251</v>
       </c>
       <c r="C86" t="n">
         <v>8888</v>
       </c>
       <c r="D86" t="n">
-        <v>1093.47</v>
+        <v>797.58</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2079,13 +2079,13 @@
         <v>46217</v>
       </c>
       <c r="B87" t="n">
-        <v>360</v>
+        <v>451</v>
       </c>
       <c r="C87" t="n">
         <v>8888</v>
       </c>
       <c r="D87" t="n">
-        <v>7017.48</v>
+        <v>1371.26</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -2098,17 +2098,17 @@
         <v>46217</v>
       </c>
       <c r="B88" t="n">
-        <v>530</v>
+        <v>40</v>
       </c>
       <c r="C88" t="n">
         <v>8888</v>
       </c>
       <c r="D88" t="n">
-        <v>180.08</v>
+        <v>1093.47</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2117,17 +2117,17 @@
         <v>46217</v>
       </c>
       <c r="B89" t="n">
-        <v>1137</v>
+        <v>360</v>
       </c>
       <c r="C89" t="n">
         <v>8888</v>
       </c>
       <c r="D89" t="n">
-        <v>2833.69</v>
+        <v>7017.48</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2136,17 +2136,17 @@
         <v>46217</v>
       </c>
       <c r="B90" t="n">
-        <v>1293</v>
+        <v>530</v>
       </c>
       <c r="C90" t="n">
         <v>8888</v>
       </c>
       <c r="D90" t="n">
-        <v>3201.32</v>
+        <v>180.08</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2155,17 +2155,17 @@
         <v>46217</v>
       </c>
       <c r="B91" t="n">
-        <v>1293</v>
+        <v>1137</v>
       </c>
       <c r="C91" t="n">
-        <v>601</v>
+        <v>8888</v>
       </c>
       <c r="D91" t="n">
-        <v>456.47</v>
+        <v>2833.69</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2174,17 +2174,17 @@
         <v>46217</v>
       </c>
       <c r="B92" t="n">
-        <v>2118</v>
+        <v>1293</v>
       </c>
       <c r="C92" t="n">
         <v>8888</v>
       </c>
       <c r="D92" t="n">
-        <v>311.54</v>
+        <v>3201.32</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2193,17 +2193,17 @@
         <v>46217</v>
       </c>
       <c r="B93" t="n">
-        <v>424</v>
+        <v>1293</v>
       </c>
       <c r="C93" t="n">
-        <v>8888</v>
+        <v>601</v>
       </c>
       <c r="D93" t="n">
-        <v>349.68</v>
+        <v>456.47</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2212,17 +2212,17 @@
         <v>46217</v>
       </c>
       <c r="B94" t="n">
-        <v>559</v>
+        <v>2118</v>
       </c>
       <c r="C94" t="n">
         <v>8888</v>
       </c>
       <c r="D94" t="n">
-        <v>1064.63</v>
+        <v>311.54</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2231,13 +2231,13 @@
         <v>46217</v>
       </c>
       <c r="B95" t="n">
-        <v>89</v>
+        <v>424</v>
       </c>
       <c r="C95" t="n">
         <v>8888</v>
       </c>
       <c r="D95" t="n">
-        <v>1506.42</v>
+        <v>349.68</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -2250,17 +2250,17 @@
         <v>46217</v>
       </c>
       <c r="B96" t="n">
-        <v>2250</v>
+        <v>559</v>
       </c>
       <c r="C96" t="n">
         <v>8888</v>
       </c>
       <c r="D96" t="n">
-        <v>1943.54</v>
+        <v>1064.63</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2269,17 +2269,17 @@
         <v>46217</v>
       </c>
       <c r="B97" t="n">
-        <v>1299</v>
+        <v>89</v>
       </c>
       <c r="C97" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D97" t="n">
-        <v>262.02</v>
+        <v>1506.42</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
         <v>46217</v>
       </c>
       <c r="B98" t="n">
-        <v>2651</v>
+        <v>2250</v>
       </c>
       <c r="C98" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D98" t="n">
-        <v>648.71</v>
+        <v>1943.54</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2307,17 +2307,17 @@
         <v>46217</v>
       </c>
       <c r="B99" t="n">
-        <v>40</v>
+        <v>1299</v>
       </c>
       <c r="C99" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D99" t="n">
-        <v>733.37</v>
+        <v>262.02</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2326,17 +2326,17 @@
         <v>46217</v>
       </c>
       <c r="B100" t="n">
-        <v>40</v>
+        <v>2651</v>
       </c>
       <c r="C100" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D100" t="n">
-        <v>2529.31</v>
+        <v>648.71</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2345,17 +2345,17 @@
         <v>46217</v>
       </c>
       <c r="B101" t="n">
-        <v>626</v>
+        <v>40</v>
       </c>
       <c r="C101" t="n">
         <v>8888</v>
       </c>
       <c r="D101" t="n">
-        <v>13218.02</v>
+        <v>3583.39</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2364,13 +2364,13 @@
         <v>46217</v>
       </c>
       <c r="B102" t="n">
-        <v>363</v>
+        <v>40</v>
       </c>
       <c r="C102" t="n">
         <v>8888</v>
       </c>
       <c r="D102" t="n">
-        <v>739.17</v>
+        <v>2529.31</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -2383,17 +2383,17 @@
         <v>46217</v>
       </c>
       <c r="B103" t="n">
-        <v>675</v>
+        <v>626</v>
       </c>
       <c r="C103" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D103" t="n">
-        <v>107.13</v>
+        <v>13218.02</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2402,17 +2402,17 @@
         <v>46217</v>
       </c>
       <c r="B104" t="n">
-        <v>636</v>
+        <v>363</v>
       </c>
       <c r="C104" t="n">
         <v>8888</v>
       </c>
       <c r="D104" t="n">
-        <v>5631.89</v>
+        <v>739.17</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2421,17 +2421,17 @@
         <v>46217</v>
       </c>
       <c r="B105" t="n">
-        <v>1075</v>
+        <v>675</v>
       </c>
       <c r="C105" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D105" t="n">
-        <v>1331.89</v>
+        <v>107.13</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2440,17 +2440,17 @@
         <v>46217</v>
       </c>
       <c r="B106" t="n">
-        <v>2245</v>
+        <v>636</v>
       </c>
       <c r="C106" t="n">
         <v>8888</v>
       </c>
       <c r="D106" t="n">
-        <v>883.75</v>
+        <v>5631.89</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2459,13 +2459,13 @@
         <v>46217</v>
       </c>
       <c r="B107" t="n">
-        <v>477</v>
+        <v>1075</v>
       </c>
       <c r="C107" t="n">
         <v>8888</v>
       </c>
       <c r="D107" t="n">
-        <v>994.15</v>
+        <v>1331.89</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -2478,17 +2478,17 @@
         <v>46217</v>
       </c>
       <c r="B108" t="n">
-        <v>2015</v>
+        <v>2245</v>
       </c>
       <c r="C108" t="n">
         <v>8888</v>
       </c>
       <c r="D108" t="n">
-        <v>2931.07</v>
+        <v>883.75</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2497,17 +2497,17 @@
         <v>46217</v>
       </c>
       <c r="B109" t="n">
-        <v>1064</v>
+        <v>477</v>
       </c>
       <c r="C109" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D109" t="n">
-        <v>451.38</v>
+        <v>994.15</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2516,17 +2516,17 @@
         <v>46217</v>
       </c>
       <c r="B110" t="n">
-        <v>1983</v>
+        <v>2015</v>
       </c>
       <c r="C110" t="n">
         <v>8888</v>
       </c>
       <c r="D110" t="n">
-        <v>680.42</v>
+        <v>2931.07</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2535,17 +2535,17 @@
         <v>46217</v>
       </c>
       <c r="B111" t="n">
-        <v>2118</v>
+        <v>1064</v>
       </c>
       <c r="C111" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D111" t="n">
-        <v>2646.39</v>
+        <v>451.38</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2554,17 +2554,17 @@
         <v>46217</v>
       </c>
       <c r="B112" t="n">
-        <v>2680</v>
+        <v>1983</v>
       </c>
       <c r="C112" t="n">
         <v>8888</v>
       </c>
       <c r="D112" t="n">
-        <v>824.67</v>
+        <v>1246.33</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2573,13 +2573,13 @@
         <v>46217</v>
       </c>
       <c r="B113" t="n">
-        <v>1653</v>
+        <v>2118</v>
       </c>
       <c r="C113" t="n">
         <v>8888</v>
       </c>
       <c r="D113" t="n">
-        <v>2848.57</v>
+        <v>2646.39</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -2592,17 +2592,17 @@
         <v>46217</v>
       </c>
       <c r="B114" t="n">
-        <v>629</v>
+        <v>2680</v>
       </c>
       <c r="C114" t="n">
-        <v>675</v>
+        <v>8888</v>
       </c>
       <c r="D114" t="n">
-        <v>267.79</v>
+        <v>824.67</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2611,13 +2611,13 @@
         <v>46217</v>
       </c>
       <c r="B115" t="n">
-        <v>559</v>
+        <v>1653</v>
       </c>
       <c r="C115" t="n">
         <v>8888</v>
       </c>
       <c r="D115" t="n">
-        <v>1562.5</v>
+        <v>2848.57</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -2630,17 +2630,17 @@
         <v>46217</v>
       </c>
       <c r="B116" t="n">
-        <v>1465</v>
+        <v>629</v>
       </c>
       <c r="C116" t="n">
-        <v>8888</v>
+        <v>675</v>
       </c>
       <c r="D116" t="n">
-        <v>9346.120000000001</v>
+        <v>267.79</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2649,17 +2649,17 @@
         <v>46217</v>
       </c>
       <c r="B117" t="n">
-        <v>2550</v>
+        <v>559</v>
       </c>
       <c r="C117" t="n">
         <v>8888</v>
       </c>
       <c r="D117" t="n">
-        <v>321.05</v>
+        <v>1562.5</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2668,17 +2668,17 @@
         <v>46217</v>
       </c>
       <c r="B118" t="n">
-        <v>1756</v>
+        <v>1465</v>
       </c>
       <c r="C118" t="n">
         <v>8888</v>
       </c>
       <c r="D118" t="n">
-        <v>2445</v>
+        <v>9346.120000000001</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2687,17 +2687,17 @@
         <v>46217</v>
       </c>
       <c r="B119" t="n">
-        <v>363</v>
+        <v>2550</v>
       </c>
       <c r="C119" t="n">
         <v>8888</v>
       </c>
       <c r="D119" t="n">
-        <v>649.08</v>
+        <v>321.05</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2706,17 +2706,17 @@
         <v>46217</v>
       </c>
       <c r="B120" t="n">
-        <v>2698</v>
+        <v>1756</v>
       </c>
       <c r="C120" t="n">
-        <v>874</v>
+        <v>8888</v>
       </c>
       <c r="D120" t="n">
-        <v>1183.42</v>
+        <v>2445</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2725,13 +2725,13 @@
         <v>46217</v>
       </c>
       <c r="B121" t="n">
-        <v>2250</v>
+        <v>363</v>
       </c>
       <c r="C121" t="n">
         <v>8888</v>
       </c>
       <c r="D121" t="n">
-        <v>1512.17</v>
+        <v>649.08</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -2744,17 +2744,17 @@
         <v>46217</v>
       </c>
       <c r="B122" t="n">
-        <v>2681</v>
+        <v>2698</v>
       </c>
       <c r="C122" t="n">
-        <v>8888</v>
+        <v>874</v>
       </c>
       <c r="D122" t="n">
-        <v>2775.8</v>
+        <v>1183.42</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2763,13 +2763,13 @@
         <v>46217</v>
       </c>
       <c r="B123" t="n">
-        <v>535</v>
+        <v>2250</v>
       </c>
       <c r="C123" t="n">
         <v>8888</v>
       </c>
       <c r="D123" t="n">
-        <v>2806.71</v>
+        <v>1512.17</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -2782,17 +2782,17 @@
         <v>46217</v>
       </c>
       <c r="B124" t="n">
-        <v>483</v>
+        <v>2681</v>
       </c>
       <c r="C124" t="n">
         <v>8888</v>
       </c>
       <c r="D124" t="n">
-        <v>2100.84</v>
+        <v>2775.8</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2801,17 +2801,17 @@
         <v>46217</v>
       </c>
       <c r="B125" t="n">
-        <v>2330</v>
+        <v>535</v>
       </c>
       <c r="C125" t="n">
-        <v>1954</v>
+        <v>8888</v>
       </c>
       <c r="D125" t="n">
-        <v>1923.09</v>
+        <v>2806.71</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2820,17 +2820,17 @@
         <v>46217</v>
       </c>
       <c r="B126" t="n">
-        <v>363</v>
+        <v>483</v>
       </c>
       <c r="C126" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D126" t="n">
-        <v>1058.27</v>
+        <v>2100.84</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2839,17 +2839,17 @@
         <v>46217</v>
       </c>
       <c r="B127" t="n">
-        <v>2709</v>
+        <v>2330</v>
       </c>
       <c r="C127" t="n">
-        <v>8888</v>
+        <v>1954</v>
       </c>
       <c r="D127" t="n">
-        <v>1667.47</v>
+        <v>1923.09</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2858,17 +2858,17 @@
         <v>46217</v>
       </c>
       <c r="B128" t="n">
-        <v>1137</v>
+        <v>363</v>
       </c>
       <c r="C128" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D128" t="n">
-        <v>3185.1</v>
+        <v>1058.27</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2877,15 +2877,53 @@
         <v>46217</v>
       </c>
       <c r="B129" t="n">
+        <v>2709</v>
+      </c>
+      <c r="C129" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D129" t="n">
+        <v>1667.47</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B130" t="n">
+        <v>1137</v>
+      </c>
+      <c r="C130" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D130" t="n">
+        <v>3185.1</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B131" t="n">
         <v>2251</v>
       </c>
-      <c r="C129" t="n">
+      <c r="C131" t="n">
         <v>3403</v>
       </c>
-      <c r="D129" t="n">
+      <c r="D131" t="n">
         <v>510.18</v>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="E131" t="inlineStr">
         <is>
           <t>TELEMARKETING</t>
         </is>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E131"/>
+  <dimension ref="A1:E152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,17 +502,17 @@
         <v>46217</v>
       </c>
       <c r="B4" t="n">
-        <v>2109</v>
+        <v>1653</v>
       </c>
       <c r="C4" t="n">
-        <v>8888</v>
+        <v>1281</v>
       </c>
       <c r="D4" t="n">
-        <v>4813.6</v>
+        <v>4524.08</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -521,17 +521,17 @@
         <v>46217</v>
       </c>
       <c r="B5" t="n">
-        <v>1993</v>
+        <v>2109</v>
       </c>
       <c r="C5" t="n">
         <v>8888</v>
       </c>
       <c r="D5" t="n">
-        <v>1785.44</v>
+        <v>4813.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -540,17 +540,17 @@
         <v>46217</v>
       </c>
       <c r="B6" t="n">
-        <v>1102</v>
+        <v>2015</v>
       </c>
       <c r="C6" t="n">
-        <v>8888</v>
+        <v>2571</v>
       </c>
       <c r="D6" t="n">
-        <v>1264.43</v>
+        <v>1790.54</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -559,17 +559,17 @@
         <v>46217</v>
       </c>
       <c r="B7" t="n">
-        <v>2015</v>
+        <v>1993</v>
       </c>
       <c r="C7" t="n">
-        <v>2571</v>
+        <v>8888</v>
       </c>
       <c r="D7" t="n">
-        <v>679.9</v>
+        <v>1785.44</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
         <v>46217</v>
       </c>
       <c r="B8" t="n">
-        <v>1293</v>
+        <v>1102</v>
       </c>
       <c r="C8" t="n">
-        <v>1281</v>
+        <v>8888</v>
       </c>
       <c r="D8" t="n">
-        <v>1337.87</v>
+        <v>2432.31</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -597,17 +597,17 @@
         <v>46217</v>
       </c>
       <c r="B9" t="n">
-        <v>89</v>
+        <v>1293</v>
       </c>
       <c r="C9" t="n">
-        <v>8888</v>
+        <v>1281</v>
       </c>
       <c r="D9" t="n">
-        <v>5652.15</v>
+        <v>1337.87</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -616,13 +616,13 @@
         <v>46217</v>
       </c>
       <c r="B10" t="n">
-        <v>2768</v>
+        <v>1254</v>
       </c>
       <c r="C10" t="n">
         <v>8888</v>
       </c>
       <c r="D10" t="n">
-        <v>3436.6</v>
+        <v>428.16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -635,13 +635,13 @@
         <v>46217</v>
       </c>
       <c r="B11" t="n">
-        <v>949</v>
+        <v>2726</v>
       </c>
       <c r="C11" t="n">
-        <v>1258</v>
+        <v>1929</v>
       </c>
       <c r="D11" t="n">
-        <v>196.87</v>
+        <v>640.1799999999999</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -654,13 +654,13 @@
         <v>46217</v>
       </c>
       <c r="B12" t="n">
-        <v>1756</v>
+        <v>89</v>
       </c>
       <c r="C12" t="n">
         <v>8888</v>
       </c>
       <c r="D12" t="n">
-        <v>1799.7</v>
+        <v>5652.15</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -673,17 +673,17 @@
         <v>46217</v>
       </c>
       <c r="B13" t="n">
-        <v>285</v>
+        <v>2768</v>
       </c>
       <c r="C13" t="n">
         <v>8888</v>
       </c>
       <c r="D13" t="n">
-        <v>2593.28</v>
+        <v>3436.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -692,17 +692,17 @@
         <v>46217</v>
       </c>
       <c r="B14" t="n">
-        <v>610</v>
+        <v>1890</v>
       </c>
       <c r="C14" t="n">
-        <v>8888</v>
+        <v>3449</v>
       </c>
       <c r="D14" t="n">
-        <v>590.08</v>
+        <v>589.0599999999999</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -711,13 +711,13 @@
         <v>46217</v>
       </c>
       <c r="B15" t="n">
-        <v>619</v>
+        <v>2641</v>
       </c>
       <c r="C15" t="n">
         <v>8888</v>
       </c>
       <c r="D15" t="n">
-        <v>236.34</v>
+        <v>607.79</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -730,13 +730,13 @@
         <v>46217</v>
       </c>
       <c r="B16" t="n">
-        <v>2755</v>
+        <v>949</v>
       </c>
       <c r="C16" t="n">
-        <v>2220</v>
+        <v>1258</v>
       </c>
       <c r="D16" t="n">
-        <v>1133.17</v>
+        <v>196.87</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -749,17 +749,17 @@
         <v>46217</v>
       </c>
       <c r="B17" t="n">
-        <v>2767</v>
+        <v>1756</v>
       </c>
       <c r="C17" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D17" t="n">
-        <v>5000.2</v>
+        <v>1799.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -768,17 +768,17 @@
         <v>46217</v>
       </c>
       <c r="B18" t="n">
-        <v>559</v>
+        <v>285</v>
       </c>
       <c r="C18" t="n">
         <v>8888</v>
       </c>
       <c r="D18" t="n">
-        <v>517.0700000000001</v>
+        <v>2593.28</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -787,13 +787,13 @@
         <v>46217</v>
       </c>
       <c r="B19" t="n">
-        <v>2767</v>
+        <v>610</v>
       </c>
       <c r="C19" t="n">
         <v>8888</v>
       </c>
       <c r="D19" t="n">
-        <v>1175.73</v>
+        <v>590.08</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -806,17 +806,17 @@
         <v>46217</v>
       </c>
       <c r="B20" t="n">
-        <v>1063</v>
+        <v>1906</v>
       </c>
       <c r="C20" t="n">
         <v>8888</v>
       </c>
       <c r="D20" t="n">
-        <v>1251.14</v>
+        <v>1580.84</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -825,17 +825,17 @@
         <v>46217</v>
       </c>
       <c r="B21" t="n">
-        <v>325</v>
+        <v>619</v>
       </c>
       <c r="C21" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D21" t="n">
-        <v>868.83</v>
+        <v>236.34</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -844,17 +844,17 @@
         <v>46217</v>
       </c>
       <c r="B22" t="n">
-        <v>610</v>
+        <v>2755</v>
       </c>
       <c r="C22" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D22" t="n">
-        <v>235.34</v>
+        <v>1133.17</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -863,17 +863,17 @@
         <v>46217</v>
       </c>
       <c r="B23" t="n">
-        <v>1906</v>
+        <v>2767</v>
       </c>
       <c r="C23" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D23" t="n">
-        <v>889.22</v>
+        <v>5000.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
         <v>46217</v>
       </c>
       <c r="B24" t="n">
-        <v>424</v>
+        <v>559</v>
       </c>
       <c r="C24" t="n">
         <v>8888</v>
       </c>
       <c r="D24" t="n">
-        <v>2575.64</v>
+        <v>1200.99</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
         <v>46217</v>
       </c>
       <c r="B25" t="n">
-        <v>40</v>
+        <v>2767</v>
       </c>
       <c r="C25" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D25" t="n">
-        <v>325.04</v>
+        <v>1175.73</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -920,13 +920,13 @@
         <v>46217</v>
       </c>
       <c r="B26" t="n">
-        <v>1117</v>
+        <v>1063</v>
       </c>
       <c r="C26" t="n">
         <v>8888</v>
       </c>
       <c r="D26" t="n">
-        <v>349.47</v>
+        <v>1251.14</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -939,13 +939,13 @@
         <v>46217</v>
       </c>
       <c r="B27" t="n">
-        <v>949</v>
+        <v>325</v>
       </c>
       <c r="C27" t="n">
-        <v>998</v>
+        <v>58</v>
       </c>
       <c r="D27" t="n">
-        <v>129.85</v>
+        <v>868.83</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -958,17 +958,17 @@
         <v>46217</v>
       </c>
       <c r="B28" t="n">
-        <v>2250</v>
+        <v>2660</v>
       </c>
       <c r="C28" t="n">
         <v>8888</v>
       </c>
       <c r="D28" t="n">
-        <v>3627.44</v>
+        <v>281.24</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -977,13 +977,13 @@
         <v>46217</v>
       </c>
       <c r="B29" t="n">
-        <v>2507</v>
+        <v>610</v>
       </c>
       <c r="C29" t="n">
         <v>8888</v>
       </c>
       <c r="D29" t="n">
-        <v>4167.12</v>
+        <v>235.34</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -996,13 +996,13 @@
         <v>46217</v>
       </c>
       <c r="B30" t="n">
-        <v>664</v>
+        <v>424</v>
       </c>
       <c r="C30" t="n">
         <v>8888</v>
       </c>
       <c r="D30" t="n">
-        <v>3523.8</v>
+        <v>3214.29</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1015,13 +1015,13 @@
         <v>46217</v>
       </c>
       <c r="B31" t="n">
-        <v>1906</v>
+        <v>40</v>
       </c>
       <c r="C31" t="n">
-        <v>1954</v>
+        <v>58</v>
       </c>
       <c r="D31" t="n">
-        <v>1445.21</v>
+        <v>325.04</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1034,17 +1034,17 @@
         <v>46217</v>
       </c>
       <c r="B32" t="n">
-        <v>1075</v>
+        <v>1117</v>
       </c>
       <c r="C32" t="n">
         <v>8888</v>
       </c>
       <c r="D32" t="n">
-        <v>470.95</v>
+        <v>349.47</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1053,13 +1053,13 @@
         <v>46217</v>
       </c>
       <c r="B33" t="n">
-        <v>2696</v>
+        <v>949</v>
       </c>
       <c r="C33" t="n">
-        <v>1312</v>
+        <v>998</v>
       </c>
       <c r="D33" t="n">
-        <v>677.76</v>
+        <v>129.85</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1072,17 +1072,17 @@
         <v>46217</v>
       </c>
       <c r="B34" t="n">
-        <v>360</v>
+        <v>2250</v>
       </c>
       <c r="C34" t="n">
-        <v>546</v>
+        <v>8888</v>
       </c>
       <c r="D34" t="n">
-        <v>4515.36</v>
+        <v>3627.44</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1091,17 +1091,17 @@
         <v>46217</v>
       </c>
       <c r="B35" t="n">
-        <v>2651</v>
+        <v>2507</v>
       </c>
       <c r="C35" t="n">
         <v>8888</v>
       </c>
       <c r="D35" t="n">
-        <v>638.64</v>
+        <v>4167.12</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1110,17 +1110,17 @@
         <v>46217</v>
       </c>
       <c r="B36" t="n">
-        <v>1293</v>
+        <v>664</v>
       </c>
       <c r="C36" t="n">
         <v>8888</v>
       </c>
       <c r="D36" t="n">
-        <v>381.82</v>
+        <v>3523.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1129,17 +1129,17 @@
         <v>46217</v>
       </c>
       <c r="B37" t="n">
-        <v>2663</v>
+        <v>1906</v>
       </c>
       <c r="C37" t="n">
-        <v>8888</v>
+        <v>1954</v>
       </c>
       <c r="D37" t="n">
-        <v>2146.08</v>
+        <v>1445.21</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1148,17 +1148,17 @@
         <v>46217</v>
       </c>
       <c r="B38" t="n">
-        <v>675</v>
+        <v>1075</v>
       </c>
       <c r="C38" t="n">
         <v>8888</v>
       </c>
       <c r="D38" t="n">
-        <v>289.67</v>
+        <v>470.95</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1167,17 +1167,17 @@
         <v>46217</v>
       </c>
       <c r="B39" t="n">
-        <v>1063</v>
+        <v>2696</v>
       </c>
       <c r="C39" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D39" t="n">
-        <v>1902.46</v>
+        <v>677.76</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1186,17 +1186,17 @@
         <v>46217</v>
       </c>
       <c r="B40" t="n">
-        <v>1392</v>
+        <v>360</v>
       </c>
       <c r="C40" t="n">
-        <v>8888</v>
+        <v>546</v>
       </c>
       <c r="D40" t="n">
-        <v>814.61</v>
+        <v>5188.86</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1205,17 +1205,17 @@
         <v>46217</v>
       </c>
       <c r="B41" t="n">
-        <v>360</v>
+        <v>2491</v>
       </c>
       <c r="C41" t="n">
         <v>8888</v>
       </c>
       <c r="D41" t="n">
-        <v>749.13</v>
+        <v>2031.53</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1224,17 +1224,17 @@
         <v>46217</v>
       </c>
       <c r="B42" t="n">
-        <v>2491</v>
+        <v>2651</v>
       </c>
       <c r="C42" t="n">
         <v>8888</v>
       </c>
       <c r="D42" t="n">
-        <v>398.66</v>
+        <v>638.64</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
         <v>46217</v>
       </c>
       <c r="B43" t="n">
-        <v>949</v>
+        <v>1293</v>
       </c>
       <c r="C43" t="n">
-        <v>1134</v>
+        <v>8888</v>
       </c>
       <c r="D43" t="n">
-        <v>327.6</v>
+        <v>381.82</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1262,17 +1262,17 @@
         <v>46217</v>
       </c>
       <c r="B44" t="n">
-        <v>326</v>
+        <v>2663</v>
       </c>
       <c r="C44" t="n">
         <v>8888</v>
       </c>
       <c r="D44" t="n">
-        <v>212.63</v>
+        <v>2146.08</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1281,17 +1281,17 @@
         <v>46217</v>
       </c>
       <c r="B45" t="n">
-        <v>325</v>
+        <v>525</v>
       </c>
       <c r="C45" t="n">
         <v>8888</v>
       </c>
       <c r="D45" t="n">
-        <v>584.27</v>
+        <v>639.9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1300,17 +1300,17 @@
         <v>46217</v>
       </c>
       <c r="B46" t="n">
-        <v>131</v>
+        <v>2711</v>
       </c>
       <c r="C46" t="n">
         <v>8888</v>
       </c>
       <c r="D46" t="n">
-        <v>360.06</v>
+        <v>750.3200000000001</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1319,17 +1319,17 @@
         <v>46217</v>
       </c>
       <c r="B47" t="n">
-        <v>2279</v>
+        <v>675</v>
       </c>
       <c r="C47" t="n">
         <v>8888</v>
       </c>
       <c r="D47" t="n">
-        <v>1034.25</v>
+        <v>289.67</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1338,17 @@
         <v>46217</v>
       </c>
       <c r="B48" t="n">
-        <v>1116</v>
+        <v>1063</v>
       </c>
       <c r="C48" t="n">
         <v>8888</v>
       </c>
       <c r="D48" t="n">
-        <v>1293.89</v>
+        <v>1902.46</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1357,17 +1357,17 @@
         <v>46217</v>
       </c>
       <c r="B49" t="n">
-        <v>131</v>
+        <v>1392</v>
       </c>
       <c r="C49" t="n">
         <v>8888</v>
       </c>
       <c r="D49" t="n">
-        <v>1528.41</v>
+        <v>814.61</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1376,17 +1376,17 @@
         <v>46217</v>
       </c>
       <c r="B50" t="n">
-        <v>1293</v>
+        <v>360</v>
       </c>
       <c r="C50" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D50" t="n">
-        <v>3534.85</v>
+        <v>749.13</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1395,17 +1395,17 @@
         <v>46217</v>
       </c>
       <c r="B51" t="n">
-        <v>1983</v>
+        <v>949</v>
       </c>
       <c r="C51" t="n">
-        <v>8888</v>
+        <v>1134</v>
       </c>
       <c r="D51" t="n">
-        <v>412.16</v>
+        <v>327.6</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1414,17 +1414,17 @@
         <v>46217</v>
       </c>
       <c r="B52" t="n">
-        <v>451</v>
+        <v>326</v>
       </c>
       <c r="C52" t="n">
         <v>8888</v>
       </c>
       <c r="D52" t="n">
-        <v>2583.46</v>
+        <v>212.63</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1433,17 +1433,17 @@
         <v>46217</v>
       </c>
       <c r="B53" t="n">
-        <v>2767</v>
+        <v>325</v>
       </c>
       <c r="C53" t="n">
         <v>8888</v>
       </c>
       <c r="D53" t="n">
-        <v>596.88</v>
+        <v>616.95</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1452,17 +1452,17 @@
         <v>46217</v>
       </c>
       <c r="B54" t="n">
-        <v>1063</v>
+        <v>131</v>
       </c>
       <c r="C54" t="n">
         <v>8888</v>
       </c>
       <c r="D54" t="n">
-        <v>352.87</v>
+        <v>360.06</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1471,17 +1471,17 @@
         <v>46217</v>
       </c>
       <c r="B55" t="n">
-        <v>629</v>
+        <v>2697</v>
       </c>
       <c r="C55" t="n">
         <v>8888</v>
       </c>
       <c r="D55" t="n">
-        <v>559.15</v>
+        <v>420.48</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1490,17 +1490,17 @@
         <v>46217</v>
       </c>
       <c r="B56" t="n">
-        <v>58</v>
+        <v>2279</v>
       </c>
       <c r="C56" t="n">
         <v>8888</v>
       </c>
       <c r="D56" t="n">
-        <v>2637.19</v>
+        <v>1034.25</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1509,17 +1509,17 @@
         <v>46217</v>
       </c>
       <c r="B57" t="n">
-        <v>2211</v>
+        <v>1116</v>
       </c>
       <c r="C57" t="n">
-        <v>874</v>
+        <v>8888</v>
       </c>
       <c r="D57" t="n">
-        <v>967.05</v>
+        <v>1293.89</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1528,17 +1528,17 @@
         <v>46217</v>
       </c>
       <c r="B58" t="n">
-        <v>1117</v>
+        <v>131</v>
       </c>
       <c r="C58" t="n">
         <v>8888</v>
       </c>
       <c r="D58" t="n">
-        <v>581.51</v>
+        <v>1528.41</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1547,17 +1547,17 @@
         <v>46217</v>
       </c>
       <c r="B59" t="n">
-        <v>629</v>
+        <v>1293</v>
       </c>
       <c r="C59" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D59" t="n">
-        <v>2049.78</v>
+        <v>3534.85</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1566,17 +1566,17 @@
         <v>46217</v>
       </c>
       <c r="B60" t="n">
-        <v>949</v>
+        <v>451</v>
       </c>
       <c r="C60" t="n">
-        <v>1762</v>
+        <v>8888</v>
       </c>
       <c r="D60" t="n">
-        <v>325.65</v>
+        <v>2583.46</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1585,13 +1585,13 @@
         <v>46217</v>
       </c>
       <c r="B61" t="n">
-        <v>2463</v>
+        <v>1983</v>
       </c>
       <c r="C61" t="n">
         <v>8888</v>
       </c>
       <c r="D61" t="n">
-        <v>8336.43</v>
+        <v>412.16</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -1604,17 +1604,17 @@
         <v>46217</v>
       </c>
       <c r="B62" t="n">
-        <v>1064</v>
+        <v>2767</v>
       </c>
       <c r="C62" t="n">
         <v>8888</v>
       </c>
       <c r="D62" t="n">
-        <v>1513.21</v>
+        <v>596.88</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
         <v>46217</v>
       </c>
       <c r="B63" t="n">
-        <v>1478</v>
+        <v>2697</v>
       </c>
       <c r="C63" t="n">
         <v>8888</v>
       </c>
       <c r="D63" t="n">
-        <v>1294.76</v>
+        <v>2055.26</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1642,13 +1642,13 @@
         <v>46217</v>
       </c>
       <c r="B64" t="n">
-        <v>358</v>
+        <v>569</v>
       </c>
       <c r="C64" t="n">
         <v>8888</v>
       </c>
       <c r="D64" t="n">
-        <v>1918.33</v>
+        <v>2291.64</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -1661,17 +1661,17 @@
         <v>46217</v>
       </c>
       <c r="B65" t="n">
-        <v>2107</v>
+        <v>1063</v>
       </c>
       <c r="C65" t="n">
         <v>8888</v>
       </c>
       <c r="D65" t="n">
-        <v>2745.11</v>
+        <v>352.87</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1680,13 +1680,13 @@
         <v>46217</v>
       </c>
       <c r="B66" t="n">
-        <v>675</v>
+        <v>2687</v>
       </c>
       <c r="C66" t="n">
         <v>8888</v>
       </c>
       <c r="D66" t="n">
-        <v>275.17</v>
+        <v>1760.22</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -1699,13 +1699,13 @@
         <v>46217</v>
       </c>
       <c r="B67" t="n">
-        <v>2279</v>
+        <v>629</v>
       </c>
       <c r="C67" t="n">
         <v>8888</v>
       </c>
       <c r="D67" t="n">
-        <v>1165.17</v>
+        <v>559.15</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>46217</v>
       </c>
       <c r="B68" t="n">
-        <v>451</v>
+        <v>1890</v>
       </c>
       <c r="C68" t="n">
-        <v>3403</v>
+        <v>1953</v>
       </c>
       <c r="D68" t="n">
-        <v>327.28</v>
+        <v>697.04</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -1737,17 +1737,17 @@
         <v>46217</v>
       </c>
       <c r="B69" t="n">
-        <v>2571</v>
+        <v>58</v>
       </c>
       <c r="C69" t="n">
-        <v>1312</v>
+        <v>8888</v>
       </c>
       <c r="D69" t="n">
-        <v>2202.75</v>
+        <v>2637.19</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1756,17 +1756,17 @@
         <v>46217</v>
       </c>
       <c r="B70" t="n">
-        <v>610</v>
+        <v>2211</v>
       </c>
       <c r="C70" t="n">
-        <v>8888</v>
+        <v>874</v>
       </c>
       <c r="D70" t="n">
-        <v>335.61</v>
+        <v>967.05</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1775,17 +1775,17 @@
         <v>46217</v>
       </c>
       <c r="B71" t="n">
-        <v>1108</v>
+        <v>1117</v>
       </c>
       <c r="C71" t="n">
         <v>8888</v>
       </c>
       <c r="D71" t="n">
-        <v>508.54</v>
+        <v>581.51</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1794,17 +1794,17 @@
         <v>46217</v>
       </c>
       <c r="B72" t="n">
-        <v>341</v>
+        <v>629</v>
       </c>
       <c r="C72" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D72" t="n">
-        <v>366.88</v>
+        <v>2049.78</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1813,17 +1813,17 @@
         <v>46217</v>
       </c>
       <c r="B73" t="n">
-        <v>1653</v>
+        <v>949</v>
       </c>
       <c r="C73" t="n">
-        <v>8888</v>
+        <v>1762</v>
       </c>
       <c r="D73" t="n">
-        <v>4383.69</v>
+        <v>325.65</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1832,17 +1832,17 @@
         <v>46217</v>
       </c>
       <c r="B74" t="n">
-        <v>619</v>
+        <v>2463</v>
       </c>
       <c r="C74" t="n">
         <v>8888</v>
       </c>
       <c r="D74" t="n">
-        <v>779.87</v>
+        <v>8336.43</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1851,13 +1851,13 @@
         <v>46217</v>
       </c>
       <c r="B75" t="n">
-        <v>663</v>
+        <v>1064</v>
       </c>
       <c r="C75" t="n">
         <v>8888</v>
       </c>
       <c r="D75" t="n">
-        <v>824.5599999999999</v>
+        <v>1513.21</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -1870,17 +1870,17 @@
         <v>46217</v>
       </c>
       <c r="B76" t="n">
-        <v>58</v>
+        <v>1478</v>
       </c>
       <c r="C76" t="n">
         <v>8888</v>
       </c>
       <c r="D76" t="n">
-        <v>660.1</v>
+        <v>1294.76</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1889,17 +1889,17 @@
         <v>46217</v>
       </c>
       <c r="B77" t="n">
-        <v>429</v>
+        <v>358</v>
       </c>
       <c r="C77" t="n">
-        <v>2571</v>
+        <v>8888</v>
       </c>
       <c r="D77" t="n">
-        <v>667.12</v>
+        <v>1918.33</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1908,17 +1908,17 @@
         <v>46217</v>
       </c>
       <c r="B78" t="n">
-        <v>483</v>
+        <v>2107</v>
       </c>
       <c r="C78" t="n">
         <v>8888</v>
       </c>
       <c r="D78" t="n">
-        <v>1290.28</v>
+        <v>2745.11</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1927,17 +1927,17 @@
         <v>46217</v>
       </c>
       <c r="B79" t="n">
-        <v>2709</v>
+        <v>675</v>
       </c>
       <c r="C79" t="n">
-        <v>2220</v>
+        <v>8888</v>
       </c>
       <c r="D79" t="n">
-        <v>1663.5</v>
+        <v>275.17</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1946,13 +1946,13 @@
         <v>46217</v>
       </c>
       <c r="B80" t="n">
-        <v>1937</v>
+        <v>2279</v>
       </c>
       <c r="C80" t="n">
         <v>8888</v>
       </c>
       <c r="D80" t="n">
-        <v>1332.89</v>
+        <v>1165.17</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -1965,13 +1965,13 @@
         <v>46217</v>
       </c>
       <c r="B81" t="n">
-        <v>429</v>
+        <v>451</v>
       </c>
       <c r="C81" t="n">
-        <v>1281</v>
+        <v>3403</v>
       </c>
       <c r="D81" t="n">
-        <v>1333.52</v>
+        <v>327.28</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -1984,17 +1984,17 @@
         <v>46217</v>
       </c>
       <c r="B82" t="n">
-        <v>2211</v>
+        <v>2571</v>
       </c>
       <c r="C82" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D82" t="n">
-        <v>797.61</v>
+        <v>2202.75</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2003,17 +2003,17 @@
         <v>46217</v>
       </c>
       <c r="B83" t="n">
-        <v>131</v>
+        <v>610</v>
       </c>
       <c r="C83" t="n">
         <v>8888</v>
       </c>
       <c r="D83" t="n">
-        <v>2340.29</v>
+        <v>335.61</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2022,17 +2022,17 @@
         <v>46217</v>
       </c>
       <c r="B84" t="n">
-        <v>131</v>
+        <v>1108</v>
       </c>
       <c r="C84" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D84" t="n">
-        <v>669.39</v>
+        <v>508.54</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2041,17 +2041,17 @@
         <v>46217</v>
       </c>
       <c r="B85" t="n">
-        <v>1064</v>
+        <v>341</v>
       </c>
       <c r="C85" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D85" t="n">
-        <v>2383.39</v>
+        <v>366.88</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2060,17 +2060,17 @@
         <v>46217</v>
       </c>
       <c r="B86" t="n">
-        <v>2251</v>
+        <v>1653</v>
       </c>
       <c r="C86" t="n">
         <v>8888</v>
       </c>
       <c r="D86" t="n">
-        <v>797.58</v>
+        <v>4383.69</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2079,13 +2079,13 @@
         <v>46217</v>
       </c>
       <c r="B87" t="n">
-        <v>451</v>
+        <v>619</v>
       </c>
       <c r="C87" t="n">
         <v>8888</v>
       </c>
       <c r="D87" t="n">
-        <v>1371.26</v>
+        <v>1557.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -2098,17 +2098,17 @@
         <v>46217</v>
       </c>
       <c r="B88" t="n">
-        <v>40</v>
+        <v>663</v>
       </c>
       <c r="C88" t="n">
         <v>8888</v>
       </c>
       <c r="D88" t="n">
-        <v>1093.47</v>
+        <v>824.5599999999999</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2117,13 +2117,13 @@
         <v>46217</v>
       </c>
       <c r="B89" t="n">
-        <v>360</v>
+        <v>58</v>
       </c>
       <c r="C89" t="n">
         <v>8888</v>
       </c>
       <c r="D89" t="n">
-        <v>7017.48</v>
+        <v>660.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -2136,17 +2136,17 @@
         <v>46217</v>
       </c>
       <c r="B90" t="n">
-        <v>530</v>
+        <v>429</v>
       </c>
       <c r="C90" t="n">
-        <v>8888</v>
+        <v>2571</v>
       </c>
       <c r="D90" t="n">
-        <v>180.08</v>
+        <v>667.12</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2155,17 +2155,17 @@
         <v>46217</v>
       </c>
       <c r="B91" t="n">
-        <v>1137</v>
+        <v>2641</v>
       </c>
       <c r="C91" t="n">
         <v>8888</v>
       </c>
       <c r="D91" t="n">
-        <v>2833.69</v>
+        <v>252.41</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
         <v>8888</v>
       </c>
       <c r="D92" t="n">
-        <v>3201.32</v>
+        <v>8102.01</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -2193,17 +2193,17 @@
         <v>46217</v>
       </c>
       <c r="B93" t="n">
-        <v>1293</v>
+        <v>483</v>
       </c>
       <c r="C93" t="n">
-        <v>601</v>
+        <v>8888</v>
       </c>
       <c r="D93" t="n">
-        <v>456.47</v>
+        <v>1290.28</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2212,17 +2212,17 @@
         <v>46217</v>
       </c>
       <c r="B94" t="n">
-        <v>2118</v>
+        <v>2308</v>
       </c>
       <c r="C94" t="n">
-        <v>8888</v>
+        <v>546</v>
       </c>
       <c r="D94" t="n">
-        <v>311.54</v>
+        <v>1292.23</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2231,17 +2231,17 @@
         <v>46217</v>
       </c>
       <c r="B95" t="n">
-        <v>424</v>
+        <v>2709</v>
       </c>
       <c r="C95" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D95" t="n">
-        <v>349.68</v>
+        <v>1663.5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2250,13 +2250,13 @@
         <v>46217</v>
       </c>
       <c r="B96" t="n">
-        <v>559</v>
+        <v>1937</v>
       </c>
       <c r="C96" t="n">
         <v>8888</v>
       </c>
       <c r="D96" t="n">
-        <v>1064.63</v>
+        <v>1332.89</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -2269,17 +2269,17 @@
         <v>46217</v>
       </c>
       <c r="B97" t="n">
-        <v>89</v>
+        <v>429</v>
       </c>
       <c r="C97" t="n">
-        <v>8888</v>
+        <v>1281</v>
       </c>
       <c r="D97" t="n">
-        <v>1506.42</v>
+        <v>2195.97</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
         <v>46217</v>
       </c>
       <c r="B98" t="n">
-        <v>2250</v>
+        <v>2211</v>
       </c>
       <c r="C98" t="n">
         <v>8888</v>
       </c>
       <c r="D98" t="n">
-        <v>1943.54</v>
+        <v>797.61</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2307,17 +2307,17 @@
         <v>46217</v>
       </c>
       <c r="B99" t="n">
-        <v>1299</v>
+        <v>360</v>
       </c>
       <c r="C99" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D99" t="n">
-        <v>262.02</v>
+        <v>13118.46</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2326,17 +2326,17 @@
         <v>46217</v>
       </c>
       <c r="B100" t="n">
-        <v>2651</v>
+        <v>131</v>
       </c>
       <c r="C100" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D100" t="n">
-        <v>648.71</v>
+        <v>2340.29</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2345,17 +2345,17 @@
         <v>46217</v>
       </c>
       <c r="B101" t="n">
-        <v>40</v>
+        <v>131</v>
       </c>
       <c r="C101" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D101" t="n">
-        <v>3583.39</v>
+        <v>669.39</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2364,17 +2364,17 @@
         <v>46217</v>
       </c>
       <c r="B102" t="n">
-        <v>40</v>
+        <v>1064</v>
       </c>
       <c r="C102" t="n">
         <v>8888</v>
       </c>
       <c r="D102" t="n">
-        <v>2529.31</v>
+        <v>103288.88</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2383,17 +2383,17 @@
         <v>46217</v>
       </c>
       <c r="B103" t="n">
-        <v>626</v>
+        <v>2251</v>
       </c>
       <c r="C103" t="n">
         <v>8888</v>
       </c>
       <c r="D103" t="n">
-        <v>13218.02</v>
+        <v>797.58</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2402,17 +2402,17 @@
         <v>46217</v>
       </c>
       <c r="B104" t="n">
-        <v>363</v>
+        <v>451</v>
       </c>
       <c r="C104" t="n">
         <v>8888</v>
       </c>
       <c r="D104" t="n">
-        <v>739.17</v>
+        <v>1371.26</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2421,17 +2421,17 @@
         <v>46217</v>
       </c>
       <c r="B105" t="n">
-        <v>675</v>
+        <v>40</v>
       </c>
       <c r="C105" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D105" t="n">
-        <v>107.13</v>
+        <v>1093.47</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2440,17 +2440,17 @@
         <v>46217</v>
       </c>
       <c r="B106" t="n">
-        <v>636</v>
+        <v>530</v>
       </c>
       <c r="C106" t="n">
         <v>8888</v>
       </c>
       <c r="D106" t="n">
-        <v>5631.89</v>
+        <v>180.08</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2459,17 +2459,17 @@
         <v>46217</v>
       </c>
       <c r="B107" t="n">
-        <v>1075</v>
+        <v>1137</v>
       </c>
       <c r="C107" t="n">
         <v>8888</v>
       </c>
       <c r="D107" t="n">
-        <v>1331.89</v>
+        <v>2833.69</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2478,17 +2478,17 @@
         <v>46217</v>
       </c>
       <c r="B108" t="n">
-        <v>2245</v>
+        <v>1293</v>
       </c>
       <c r="C108" t="n">
-        <v>8888</v>
+        <v>601</v>
       </c>
       <c r="D108" t="n">
-        <v>883.75</v>
+        <v>456.47</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2497,17 +2497,17 @@
         <v>46217</v>
       </c>
       <c r="B109" t="n">
-        <v>477</v>
+        <v>2118</v>
       </c>
       <c r="C109" t="n">
         <v>8888</v>
       </c>
       <c r="D109" t="n">
-        <v>994.15</v>
+        <v>311.54</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2516,17 +2516,17 @@
         <v>46217</v>
       </c>
       <c r="B110" t="n">
-        <v>2015</v>
+        <v>424</v>
       </c>
       <c r="C110" t="n">
         <v>8888</v>
       </c>
       <c r="D110" t="n">
-        <v>2931.07</v>
+        <v>349.68</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2535,13 +2535,13 @@
         <v>46217</v>
       </c>
       <c r="B111" t="n">
-        <v>1064</v>
+        <v>1299</v>
       </c>
       <c r="C111" t="n">
         <v>27</v>
       </c>
       <c r="D111" t="n">
-        <v>451.38</v>
+        <v>1425.22</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -2554,13 +2554,13 @@
         <v>46217</v>
       </c>
       <c r="B112" t="n">
-        <v>1983</v>
+        <v>559</v>
       </c>
       <c r="C112" t="n">
         <v>8888</v>
       </c>
       <c r="D112" t="n">
-        <v>1246.33</v>
+        <v>1064.63</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -2573,17 +2573,17 @@
         <v>46217</v>
       </c>
       <c r="B113" t="n">
-        <v>2118</v>
+        <v>89</v>
       </c>
       <c r="C113" t="n">
         <v>8888</v>
       </c>
       <c r="D113" t="n">
-        <v>2646.39</v>
+        <v>1506.42</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2592,17 +2592,17 @@
         <v>46217</v>
       </c>
       <c r="B114" t="n">
-        <v>2680</v>
+        <v>2250</v>
       </c>
       <c r="C114" t="n">
         <v>8888</v>
       </c>
       <c r="D114" t="n">
-        <v>824.67</v>
+        <v>1943.54</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2611,13 +2611,13 @@
         <v>46217</v>
       </c>
       <c r="B115" t="n">
-        <v>1653</v>
+        <v>767</v>
       </c>
       <c r="C115" t="n">
         <v>8888</v>
       </c>
       <c r="D115" t="n">
-        <v>2848.57</v>
+        <v>472.62</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -2630,13 +2630,13 @@
         <v>46217</v>
       </c>
       <c r="B116" t="n">
-        <v>629</v>
+        <v>2651</v>
       </c>
       <c r="C116" t="n">
-        <v>675</v>
+        <v>58</v>
       </c>
       <c r="D116" t="n">
-        <v>267.79</v>
+        <v>648.71</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -2649,17 +2649,17 @@
         <v>46217</v>
       </c>
       <c r="B117" t="n">
-        <v>559</v>
+        <v>2114</v>
       </c>
       <c r="C117" t="n">
-        <v>8888</v>
+        <v>1954</v>
       </c>
       <c r="D117" t="n">
-        <v>1562.5</v>
+        <v>879.03</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2668,13 +2668,13 @@
         <v>46217</v>
       </c>
       <c r="B118" t="n">
-        <v>1465</v>
+        <v>40</v>
       </c>
       <c r="C118" t="n">
         <v>8888</v>
       </c>
       <c r="D118" t="n">
-        <v>9346.120000000001</v>
+        <v>3583.39</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -2687,13 +2687,13 @@
         <v>46217</v>
       </c>
       <c r="B119" t="n">
-        <v>2550</v>
+        <v>40</v>
       </c>
       <c r="C119" t="n">
         <v>8888</v>
       </c>
       <c r="D119" t="n">
-        <v>321.05</v>
+        <v>2529.31</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -2706,13 +2706,13 @@
         <v>46217</v>
       </c>
       <c r="B120" t="n">
-        <v>1756</v>
+        <v>626</v>
       </c>
       <c r="C120" t="n">
         <v>8888</v>
       </c>
       <c r="D120" t="n">
-        <v>2445</v>
+        <v>13218.02</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -2731,11 +2731,11 @@
         <v>8888</v>
       </c>
       <c r="D121" t="n">
-        <v>649.08</v>
+        <v>739.17</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2744,13 +2744,13 @@
         <v>46217</v>
       </c>
       <c r="B122" t="n">
-        <v>2698</v>
+        <v>675</v>
       </c>
       <c r="C122" t="n">
-        <v>874</v>
+        <v>1898</v>
       </c>
       <c r="D122" t="n">
-        <v>1183.42</v>
+        <v>107.13</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -2763,13 +2763,13 @@
         <v>46217</v>
       </c>
       <c r="B123" t="n">
-        <v>2250</v>
+        <v>636</v>
       </c>
       <c r="C123" t="n">
         <v>8888</v>
       </c>
       <c r="D123" t="n">
-        <v>1512.17</v>
+        <v>5631.89</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -2782,13 +2782,13 @@
         <v>46217</v>
       </c>
       <c r="B124" t="n">
-        <v>2681</v>
+        <v>1075</v>
       </c>
       <c r="C124" t="n">
         <v>8888</v>
       </c>
       <c r="D124" t="n">
-        <v>2775.8</v>
+        <v>1331.89</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -2801,17 +2801,17 @@
         <v>46217</v>
       </c>
       <c r="B125" t="n">
-        <v>535</v>
+        <v>2245</v>
       </c>
       <c r="C125" t="n">
         <v>8888</v>
       </c>
       <c r="D125" t="n">
-        <v>2806.71</v>
+        <v>883.75</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2820,17 +2820,17 @@
         <v>46217</v>
       </c>
       <c r="B126" t="n">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="C126" t="n">
         <v>8888</v>
       </c>
       <c r="D126" t="n">
-        <v>2100.84</v>
+        <v>994.15</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2839,17 +2839,17 @@
         <v>46217</v>
       </c>
       <c r="B127" t="n">
-        <v>2330</v>
+        <v>2015</v>
       </c>
       <c r="C127" t="n">
-        <v>1954</v>
+        <v>8888</v>
       </c>
       <c r="D127" t="n">
-        <v>1923.09</v>
+        <v>2931.07</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2858,17 +2858,17 @@
         <v>46217</v>
       </c>
       <c r="B128" t="n">
-        <v>363</v>
+        <v>1653</v>
       </c>
       <c r="C128" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D128" t="n">
-        <v>1058.27</v>
+        <v>4115.53</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2877,17 +2877,17 @@
         <v>46217</v>
       </c>
       <c r="B129" t="n">
-        <v>2709</v>
+        <v>1064</v>
       </c>
       <c r="C129" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D129" t="n">
-        <v>1667.47</v>
+        <v>451.38</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2896,17 +2896,17 @@
         <v>46217</v>
       </c>
       <c r="B130" t="n">
-        <v>1137</v>
+        <v>1983</v>
       </c>
       <c r="C130" t="n">
         <v>8888</v>
       </c>
       <c r="D130" t="n">
-        <v>3185.1</v>
+        <v>1246.33</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2915,15 +2915,414 @@
         <v>46217</v>
       </c>
       <c r="B131" t="n">
+        <v>2118</v>
+      </c>
+      <c r="C131" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D131" t="n">
+        <v>2646.39</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B132" t="n">
+        <v>2680</v>
+      </c>
+      <c r="C132" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D132" t="n">
+        <v>824.67</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B133" t="n">
+        <v>2637</v>
+      </c>
+      <c r="C133" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1302.18</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B134" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C134" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D134" t="n">
+        <v>699.05</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B135" t="n">
+        <v>629</v>
+      </c>
+      <c r="C135" t="n">
+        <v>675</v>
+      </c>
+      <c r="D135" t="n">
+        <v>267.79</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B136" t="n">
+        <v>559</v>
+      </c>
+      <c r="C136" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D136" t="n">
+        <v>1562.5</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B137" t="n">
+        <v>1465</v>
+      </c>
+      <c r="C137" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D137" t="n">
+        <v>9346.120000000001</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B138" t="n">
+        <v>2550</v>
+      </c>
+      <c r="C138" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D138" t="n">
+        <v>321.05</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B139" t="n">
+        <v>1756</v>
+      </c>
+      <c r="C139" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D139" t="n">
+        <v>2445</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B140" t="n">
+        <v>363</v>
+      </c>
+      <c r="C140" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D140" t="n">
+        <v>2517.01</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B141" t="n">
+        <v>2698</v>
+      </c>
+      <c r="C141" t="n">
+        <v>874</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1183.42</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B142" t="n">
+        <v>535</v>
+      </c>
+      <c r="C142" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D142" t="n">
+        <v>5293.96</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B143" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C143" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1512.17</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B144" t="n">
+        <v>2681</v>
+      </c>
+      <c r="C144" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D144" t="n">
+        <v>2775.8</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B145" t="n">
+        <v>363</v>
+      </c>
+      <c r="C145" t="n">
+        <v>1898</v>
+      </c>
+      <c r="D145" t="n">
+        <v>3635.16</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B146" t="n">
+        <v>483</v>
+      </c>
+      <c r="C146" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D146" t="n">
+        <v>2527.71</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B147" t="n">
+        <v>2607</v>
+      </c>
+      <c r="C147" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1075.36</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B148" t="n">
+        <v>2330</v>
+      </c>
+      <c r="C148" t="n">
+        <v>1954</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1923.09</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B149" t="n">
+        <v>2709</v>
+      </c>
+      <c r="C149" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D149" t="n">
+        <v>1667.47</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B150" t="n">
+        <v>374</v>
+      </c>
+      <c r="C150" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D150" t="n">
+        <v>1150.97</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B151" t="n">
+        <v>1137</v>
+      </c>
+      <c r="C151" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D151" t="n">
+        <v>4413.34</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B152" t="n">
         <v>2251</v>
       </c>
-      <c r="C131" t="n">
+      <c r="C152" t="n">
         <v>3403</v>
       </c>
-      <c r="D131" t="n">
+      <c r="D152" t="n">
         <v>510.18</v>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="E152" t="inlineStr">
         <is>
           <t>TELEMARKETING</t>
         </is>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E152"/>
+  <dimension ref="A1:E166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,17 +464,17 @@
         <v>46217</v>
       </c>
       <c r="B2" t="n">
-        <v>1756</v>
+        <v>42</v>
       </c>
       <c r="C2" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D2" t="n">
-        <v>556.23</v>
+        <v>26575.79</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -483,17 +483,17 @@
         <v>46217</v>
       </c>
       <c r="B3" t="n">
-        <v>42</v>
+        <v>1756</v>
       </c>
       <c r="C3" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D3" t="n">
-        <v>24542.62</v>
+        <v>556.23</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -502,17 +502,17 @@
         <v>46217</v>
       </c>
       <c r="B4" t="n">
-        <v>1653</v>
+        <v>1254</v>
       </c>
       <c r="C4" t="n">
-        <v>1281</v>
+        <v>8888</v>
       </c>
       <c r="D4" t="n">
-        <v>4524.08</v>
+        <v>1508.08</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -521,17 +521,17 @@
         <v>46217</v>
       </c>
       <c r="B5" t="n">
-        <v>2109</v>
+        <v>1653</v>
       </c>
       <c r="C5" t="n">
-        <v>8888</v>
+        <v>1281</v>
       </c>
       <c r="D5" t="n">
-        <v>4813.6</v>
+        <v>4524.08</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -540,17 +540,17 @@
         <v>46217</v>
       </c>
       <c r="B6" t="n">
-        <v>2015</v>
+        <v>2109</v>
       </c>
       <c r="C6" t="n">
-        <v>2571</v>
+        <v>8888</v>
       </c>
       <c r="D6" t="n">
-        <v>1790.54</v>
+        <v>4813.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -559,17 +559,17 @@
         <v>46217</v>
       </c>
       <c r="B7" t="n">
-        <v>1993</v>
+        <v>2015</v>
       </c>
       <c r="C7" t="n">
-        <v>8888</v>
+        <v>2571</v>
       </c>
       <c r="D7" t="n">
-        <v>1785.44</v>
+        <v>2593.26</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
         <v>46217</v>
       </c>
       <c r="B8" t="n">
-        <v>1102</v>
+        <v>1993</v>
       </c>
       <c r="C8" t="n">
         <v>8888</v>
       </c>
       <c r="D8" t="n">
-        <v>2432.31</v>
+        <v>1785.44</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -597,17 +597,17 @@
         <v>46217</v>
       </c>
       <c r="B9" t="n">
-        <v>1293</v>
+        <v>1102</v>
       </c>
       <c r="C9" t="n">
-        <v>1281</v>
+        <v>8888</v>
       </c>
       <c r="D9" t="n">
-        <v>1337.87</v>
+        <v>2432.31</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -616,17 +616,17 @@
         <v>46217</v>
       </c>
       <c r="B10" t="n">
-        <v>1254</v>
+        <v>1293</v>
       </c>
       <c r="C10" t="n">
-        <v>8888</v>
+        <v>1281</v>
       </c>
       <c r="D10" t="n">
-        <v>428.16</v>
+        <v>1337.87</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -635,17 +635,17 @@
         <v>46217</v>
       </c>
       <c r="B11" t="n">
-        <v>2726</v>
+        <v>2768</v>
       </c>
       <c r="C11" t="n">
-        <v>1929</v>
+        <v>8888</v>
       </c>
       <c r="D11" t="n">
-        <v>640.1799999999999</v>
+        <v>4890.12</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -654,17 +654,17 @@
         <v>46217</v>
       </c>
       <c r="B12" t="n">
-        <v>89</v>
+        <v>2726</v>
       </c>
       <c r="C12" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D12" t="n">
-        <v>5652.15</v>
+        <v>640.1799999999999</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -673,13 +673,13 @@
         <v>46217</v>
       </c>
       <c r="B13" t="n">
-        <v>2768</v>
+        <v>89</v>
       </c>
       <c r="C13" t="n">
         <v>8888</v>
       </c>
       <c r="D13" t="n">
-        <v>3436.6</v>
+        <v>5652.15</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -749,17 +749,17 @@
         <v>46217</v>
       </c>
       <c r="B17" t="n">
-        <v>1756</v>
+        <v>353</v>
       </c>
       <c r="C17" t="n">
         <v>8888</v>
       </c>
       <c r="D17" t="n">
-        <v>1799.7</v>
+        <v>2121.12</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -768,17 +768,17 @@
         <v>46217</v>
       </c>
       <c r="B18" t="n">
-        <v>285</v>
+        <v>1756</v>
       </c>
       <c r="C18" t="n">
         <v>8888</v>
       </c>
       <c r="D18" t="n">
-        <v>2593.28</v>
+        <v>1799.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -787,13 +787,13 @@
         <v>46217</v>
       </c>
       <c r="B19" t="n">
-        <v>610</v>
+        <v>285</v>
       </c>
       <c r="C19" t="n">
         <v>8888</v>
       </c>
       <c r="D19" t="n">
-        <v>590.08</v>
+        <v>3092.58</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -806,17 +806,17 @@
         <v>46217</v>
       </c>
       <c r="B20" t="n">
-        <v>1906</v>
+        <v>610</v>
       </c>
       <c r="C20" t="n">
         <v>8888</v>
       </c>
       <c r="D20" t="n">
-        <v>1580.84</v>
+        <v>590.08</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -825,17 +825,17 @@
         <v>46217</v>
       </c>
       <c r="B21" t="n">
-        <v>619</v>
+        <v>1906</v>
       </c>
       <c r="C21" t="n">
         <v>8888</v>
       </c>
       <c r="D21" t="n">
-        <v>236.34</v>
+        <v>2437.98</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -844,17 +844,17 @@
         <v>46217</v>
       </c>
       <c r="B22" t="n">
-        <v>2755</v>
+        <v>619</v>
       </c>
       <c r="C22" t="n">
-        <v>2220</v>
+        <v>8888</v>
       </c>
       <c r="D22" t="n">
-        <v>1133.17</v>
+        <v>236.34</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -863,13 +863,13 @@
         <v>46217</v>
       </c>
       <c r="B23" t="n">
-        <v>2767</v>
+        <v>2755</v>
       </c>
       <c r="C23" t="n">
-        <v>1898</v>
+        <v>2220</v>
       </c>
       <c r="D23" t="n">
-        <v>5000.2</v>
+        <v>1133.17</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -882,17 +882,17 @@
         <v>46217</v>
       </c>
       <c r="B24" t="n">
-        <v>559</v>
+        <v>2767</v>
       </c>
       <c r="C24" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D24" t="n">
-        <v>1200.99</v>
+        <v>5000.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
         <v>46217</v>
       </c>
       <c r="B25" t="n">
-        <v>2767</v>
+        <v>559</v>
       </c>
       <c r="C25" t="n">
         <v>8888</v>
       </c>
       <c r="D25" t="n">
-        <v>1175.73</v>
+        <v>1200.99</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -920,17 +920,17 @@
         <v>46217</v>
       </c>
       <c r="B26" t="n">
-        <v>1063</v>
+        <v>2767</v>
       </c>
       <c r="C26" t="n">
         <v>8888</v>
       </c>
       <c r="D26" t="n">
-        <v>1251.14</v>
+        <v>1175.73</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -939,17 +939,17 @@
         <v>46217</v>
       </c>
       <c r="B27" t="n">
-        <v>325</v>
+        <v>1063</v>
       </c>
       <c r="C27" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D27" t="n">
-        <v>868.83</v>
+        <v>1251.14</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
         <v>46217</v>
       </c>
       <c r="B28" t="n">
-        <v>2660</v>
+        <v>325</v>
       </c>
       <c r="C28" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D28" t="n">
-        <v>281.24</v>
+        <v>868.83</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -977,13 +977,13 @@
         <v>46217</v>
       </c>
       <c r="B29" t="n">
-        <v>610</v>
+        <v>2660</v>
       </c>
       <c r="C29" t="n">
         <v>8888</v>
       </c>
       <c r="D29" t="n">
-        <v>235.34</v>
+        <v>281.24</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -996,17 +996,17 @@
         <v>46217</v>
       </c>
       <c r="B30" t="n">
-        <v>424</v>
+        <v>610</v>
       </c>
       <c r="C30" t="n">
         <v>8888</v>
       </c>
       <c r="D30" t="n">
-        <v>3214.29</v>
+        <v>235.34</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1015,17 +1015,17 @@
         <v>46217</v>
       </c>
       <c r="B31" t="n">
-        <v>40</v>
+        <v>424</v>
       </c>
       <c r="C31" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D31" t="n">
-        <v>325.04</v>
+        <v>3214.29</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
         <v>46217</v>
       </c>
       <c r="B32" t="n">
-        <v>1117</v>
+        <v>40</v>
       </c>
       <c r="C32" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D32" t="n">
-        <v>349.47</v>
+        <v>325.04</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
         <v>46217</v>
       </c>
       <c r="B33" t="n">
-        <v>949</v>
+        <v>1117</v>
       </c>
       <c r="C33" t="n">
-        <v>998</v>
+        <v>8888</v>
       </c>
       <c r="D33" t="n">
-        <v>129.85</v>
+        <v>349.47</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1072,17 +1072,17 @@
         <v>46217</v>
       </c>
       <c r="B34" t="n">
-        <v>2250</v>
+        <v>949</v>
       </c>
       <c r="C34" t="n">
-        <v>8888</v>
+        <v>998</v>
       </c>
       <c r="D34" t="n">
-        <v>3627.44</v>
+        <v>129.85</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1091,13 +1091,13 @@
         <v>46217</v>
       </c>
       <c r="B35" t="n">
-        <v>2507</v>
+        <v>1853</v>
       </c>
       <c r="C35" t="n">
         <v>8888</v>
       </c>
       <c r="D35" t="n">
-        <v>4167.12</v>
+        <v>522.4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1110,13 +1110,13 @@
         <v>46217</v>
       </c>
       <c r="B36" t="n">
-        <v>664</v>
+        <v>2250</v>
       </c>
       <c r="C36" t="n">
         <v>8888</v>
       </c>
       <c r="D36" t="n">
-        <v>3523.8</v>
+        <v>4131.57</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1129,17 +1129,17 @@
         <v>46217</v>
       </c>
       <c r="B37" t="n">
-        <v>1906</v>
+        <v>2507</v>
       </c>
       <c r="C37" t="n">
-        <v>1954</v>
+        <v>8888</v>
       </c>
       <c r="D37" t="n">
-        <v>1445.21</v>
+        <v>4167.12</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1148,17 +1148,17 @@
         <v>46217</v>
       </c>
       <c r="B38" t="n">
-        <v>1075</v>
+        <v>664</v>
       </c>
       <c r="C38" t="n">
         <v>8888</v>
       </c>
       <c r="D38" t="n">
-        <v>470.95</v>
+        <v>3815.91</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1167,17 +1167,17 @@
         <v>46217</v>
       </c>
       <c r="B39" t="n">
-        <v>2696</v>
+        <v>1075</v>
       </c>
       <c r="C39" t="n">
-        <v>1312</v>
+        <v>8888</v>
       </c>
       <c r="D39" t="n">
-        <v>677.76</v>
+        <v>1013.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1186,13 +1186,13 @@
         <v>46217</v>
       </c>
       <c r="B40" t="n">
-        <v>360</v>
+        <v>1906</v>
       </c>
       <c r="C40" t="n">
-        <v>546</v>
+        <v>1954</v>
       </c>
       <c r="D40" t="n">
-        <v>5188.86</v>
+        <v>1445.21</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1205,17 +1205,17 @@
         <v>46217</v>
       </c>
       <c r="B41" t="n">
-        <v>2491</v>
+        <v>2696</v>
       </c>
       <c r="C41" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D41" t="n">
-        <v>2031.53</v>
+        <v>677.76</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1224,17 +1224,17 @@
         <v>46217</v>
       </c>
       <c r="B42" t="n">
-        <v>2651</v>
+        <v>360</v>
       </c>
       <c r="C42" t="n">
-        <v>8888</v>
+        <v>546</v>
       </c>
       <c r="D42" t="n">
-        <v>638.64</v>
+        <v>5741.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
         <v>46217</v>
       </c>
       <c r="B43" t="n">
-        <v>1293</v>
+        <v>2491</v>
       </c>
       <c r="C43" t="n">
         <v>8888</v>
       </c>
       <c r="D43" t="n">
-        <v>381.82</v>
+        <v>2031.53</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1262,17 +1262,17 @@
         <v>46217</v>
       </c>
       <c r="B44" t="n">
-        <v>2663</v>
+        <v>2651</v>
       </c>
       <c r="C44" t="n">
         <v>8888</v>
       </c>
       <c r="D44" t="n">
-        <v>2146.08</v>
+        <v>638.64</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1281,17 +1281,17 @@
         <v>46217</v>
       </c>
       <c r="B45" t="n">
-        <v>525</v>
+        <v>2695</v>
       </c>
       <c r="C45" t="n">
         <v>8888</v>
       </c>
       <c r="D45" t="n">
-        <v>639.9</v>
+        <v>532.53</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1300,17 +1300,17 @@
         <v>46217</v>
       </c>
       <c r="B46" t="n">
-        <v>2711</v>
+        <v>1293</v>
       </c>
       <c r="C46" t="n">
         <v>8888</v>
       </c>
       <c r="D46" t="n">
-        <v>750.3200000000001</v>
+        <v>381.82</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1319,17 +1319,17 @@
         <v>46217</v>
       </c>
       <c r="B47" t="n">
-        <v>675</v>
+        <v>2663</v>
       </c>
       <c r="C47" t="n">
         <v>8888</v>
       </c>
       <c r="D47" t="n">
-        <v>289.67</v>
+        <v>2146.08</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1338,13 +1338,13 @@
         <v>46217</v>
       </c>
       <c r="B48" t="n">
-        <v>1063</v>
+        <v>525</v>
       </c>
       <c r="C48" t="n">
         <v>8888</v>
       </c>
       <c r="D48" t="n">
-        <v>1902.46</v>
+        <v>1240.79</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1357,17 +1357,17 @@
         <v>46217</v>
       </c>
       <c r="B49" t="n">
-        <v>1392</v>
+        <v>2711</v>
       </c>
       <c r="C49" t="n">
         <v>8888</v>
       </c>
       <c r="D49" t="n">
-        <v>814.61</v>
+        <v>1953.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1376,13 +1376,13 @@
         <v>46217</v>
       </c>
       <c r="B50" t="n">
-        <v>360</v>
+        <v>675</v>
       </c>
       <c r="C50" t="n">
         <v>8888</v>
       </c>
       <c r="D50" t="n">
-        <v>749.13</v>
+        <v>289.67</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1395,17 +1395,17 @@
         <v>46217</v>
       </c>
       <c r="B51" t="n">
-        <v>949</v>
+        <v>1063</v>
       </c>
       <c r="C51" t="n">
-        <v>1134</v>
+        <v>8888</v>
       </c>
       <c r="D51" t="n">
-        <v>327.6</v>
+        <v>1902.46</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1414,13 +1414,13 @@
         <v>46217</v>
       </c>
       <c r="B52" t="n">
-        <v>326</v>
+        <v>1392</v>
       </c>
       <c r="C52" t="n">
         <v>8888</v>
       </c>
       <c r="D52" t="n">
-        <v>212.63</v>
+        <v>814.61</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -1433,17 +1433,17 @@
         <v>46217</v>
       </c>
       <c r="B53" t="n">
-        <v>325</v>
+        <v>360</v>
       </c>
       <c r="C53" t="n">
         <v>8888</v>
       </c>
       <c r="D53" t="n">
-        <v>616.95</v>
+        <v>749.13</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1452,17 +1452,17 @@
         <v>46217</v>
       </c>
       <c r="B54" t="n">
-        <v>131</v>
+        <v>949</v>
       </c>
       <c r="C54" t="n">
-        <v>8888</v>
+        <v>1134</v>
       </c>
       <c r="D54" t="n">
-        <v>360.06</v>
+        <v>327.6</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1471,13 +1471,13 @@
         <v>46217</v>
       </c>
       <c r="B55" t="n">
-        <v>2697</v>
+        <v>326</v>
       </c>
       <c r="C55" t="n">
         <v>8888</v>
       </c>
       <c r="D55" t="n">
-        <v>420.48</v>
+        <v>212.63</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -1490,17 +1490,17 @@
         <v>46217</v>
       </c>
       <c r="B56" t="n">
-        <v>2279</v>
+        <v>325</v>
       </c>
       <c r="C56" t="n">
         <v>8888</v>
       </c>
       <c r="D56" t="n">
-        <v>1034.25</v>
+        <v>616.95</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1509,17 +1509,17 @@
         <v>46217</v>
       </c>
       <c r="B57" t="n">
-        <v>1116</v>
+        <v>131</v>
       </c>
       <c r="C57" t="n">
         <v>8888</v>
       </c>
       <c r="D57" t="n">
-        <v>1293.89</v>
+        <v>1969.93</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1528,17 +1528,17 @@
         <v>46217</v>
       </c>
       <c r="B58" t="n">
-        <v>131</v>
+        <v>2697</v>
       </c>
       <c r="C58" t="n">
         <v>8888</v>
       </c>
       <c r="D58" t="n">
-        <v>1528.41</v>
+        <v>420.48</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1547,17 +1547,17 @@
         <v>46217</v>
       </c>
       <c r="B59" t="n">
-        <v>1293</v>
+        <v>2279</v>
       </c>
       <c r="C59" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D59" t="n">
-        <v>3534.85</v>
+        <v>1034.25</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1566,13 +1566,13 @@
         <v>46217</v>
       </c>
       <c r="B60" t="n">
-        <v>451</v>
+        <v>1116</v>
       </c>
       <c r="C60" t="n">
         <v>8888</v>
       </c>
       <c r="D60" t="n">
-        <v>2583.46</v>
+        <v>1293.89</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -1585,17 +1585,17 @@
         <v>46217</v>
       </c>
       <c r="B61" t="n">
-        <v>1983</v>
+        <v>131</v>
       </c>
       <c r="C61" t="n">
         <v>8888</v>
       </c>
       <c r="D61" t="n">
-        <v>412.16</v>
+        <v>5470.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1604,17 +1604,17 @@
         <v>46217</v>
       </c>
       <c r="B62" t="n">
-        <v>2767</v>
+        <v>1293</v>
       </c>
       <c r="C62" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D62" t="n">
-        <v>596.88</v>
+        <v>5154.68</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1623,13 +1623,13 @@
         <v>46217</v>
       </c>
       <c r="B63" t="n">
-        <v>2697</v>
+        <v>1937</v>
       </c>
       <c r="C63" t="n">
         <v>8888</v>
       </c>
       <c r="D63" t="n">
-        <v>2055.26</v>
+        <v>692.86</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -1642,17 +1642,17 @@
         <v>46217</v>
       </c>
       <c r="B64" t="n">
-        <v>569</v>
+        <v>1983</v>
       </c>
       <c r="C64" t="n">
         <v>8888</v>
       </c>
       <c r="D64" t="n">
-        <v>2291.64</v>
+        <v>412.16</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1661,13 +1661,13 @@
         <v>46217</v>
       </c>
       <c r="B65" t="n">
-        <v>1063</v>
+        <v>451</v>
       </c>
       <c r="C65" t="n">
         <v>8888</v>
       </c>
       <c r="D65" t="n">
-        <v>352.87</v>
+        <v>2583.46</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -1680,13 +1680,13 @@
         <v>46217</v>
       </c>
       <c r="B66" t="n">
-        <v>2687</v>
+        <v>2767</v>
       </c>
       <c r="C66" t="n">
         <v>8888</v>
       </c>
       <c r="D66" t="n">
-        <v>1760.22</v>
+        <v>596.88</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -1699,17 +1699,17 @@
         <v>46217</v>
       </c>
       <c r="B67" t="n">
-        <v>629</v>
+        <v>2697</v>
       </c>
       <c r="C67" t="n">
         <v>8888</v>
       </c>
       <c r="D67" t="n">
-        <v>559.15</v>
+        <v>2880.19</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
         <v>46217</v>
       </c>
       <c r="B68" t="n">
-        <v>1890</v>
+        <v>569</v>
       </c>
       <c r="C68" t="n">
-        <v>1953</v>
+        <v>8888</v>
       </c>
       <c r="D68" t="n">
-        <v>697.04</v>
+        <v>2291.64</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1737,17 +1737,17 @@
         <v>46217</v>
       </c>
       <c r="B69" t="n">
-        <v>58</v>
+        <v>2211</v>
       </c>
       <c r="C69" t="n">
-        <v>8888</v>
+        <v>874</v>
       </c>
       <c r="D69" t="n">
-        <v>2637.19</v>
+        <v>1833.56</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1756,17 +1756,17 @@
         <v>46217</v>
       </c>
       <c r="B70" t="n">
-        <v>2211</v>
+        <v>1063</v>
       </c>
       <c r="C70" t="n">
-        <v>874</v>
+        <v>8888</v>
       </c>
       <c r="D70" t="n">
-        <v>967.05</v>
+        <v>352.87</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1775,17 +1775,17 @@
         <v>46217</v>
       </c>
       <c r="B71" t="n">
-        <v>1117</v>
+        <v>2687</v>
       </c>
       <c r="C71" t="n">
         <v>8888</v>
       </c>
       <c r="D71" t="n">
-        <v>581.51</v>
+        <v>1760.22</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1800,11 +1800,11 @@
         <v>8888</v>
       </c>
       <c r="D72" t="n">
-        <v>2049.78</v>
+        <v>559.15</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1813,13 +1813,13 @@
         <v>46217</v>
       </c>
       <c r="B73" t="n">
-        <v>949</v>
+        <v>1890</v>
       </c>
       <c r="C73" t="n">
-        <v>1762</v>
+        <v>1953</v>
       </c>
       <c r="D73" t="n">
-        <v>325.65</v>
+        <v>1122</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -1832,17 +1832,17 @@
         <v>46217</v>
       </c>
       <c r="B74" t="n">
-        <v>2463</v>
+        <v>1289</v>
       </c>
       <c r="C74" t="n">
         <v>8888</v>
       </c>
       <c r="D74" t="n">
-        <v>8336.43</v>
+        <v>1214.09</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1851,17 +1851,17 @@
         <v>46217</v>
       </c>
       <c r="B75" t="n">
-        <v>1064</v>
+        <v>2107</v>
       </c>
       <c r="C75" t="n">
-        <v>8888</v>
+        <v>1954</v>
       </c>
       <c r="D75" t="n">
-        <v>1513.21</v>
+        <v>2000.86</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1870,17 +1870,17 @@
         <v>46217</v>
       </c>
       <c r="B76" t="n">
-        <v>1478</v>
+        <v>1116</v>
       </c>
       <c r="C76" t="n">
         <v>8888</v>
       </c>
       <c r="D76" t="n">
-        <v>1294.76</v>
+        <v>1065.24</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1889,17 +1889,17 @@
         <v>46217</v>
       </c>
       <c r="B77" t="n">
-        <v>358</v>
+        <v>58</v>
       </c>
       <c r="C77" t="n">
         <v>8888</v>
       </c>
       <c r="D77" t="n">
-        <v>1918.33</v>
+        <v>2637.19</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1908,17 +1908,17 @@
         <v>46217</v>
       </c>
       <c r="B78" t="n">
-        <v>2107</v>
+        <v>1117</v>
       </c>
       <c r="C78" t="n">
         <v>8888</v>
       </c>
       <c r="D78" t="n">
-        <v>2745.11</v>
+        <v>581.51</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1927,13 +1927,13 @@
         <v>46217</v>
       </c>
       <c r="B79" t="n">
-        <v>675</v>
+        <v>58</v>
       </c>
       <c r="C79" t="n">
         <v>8888</v>
       </c>
       <c r="D79" t="n">
-        <v>275.17</v>
+        <v>1411.43</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -1946,17 +1946,17 @@
         <v>46217</v>
       </c>
       <c r="B80" t="n">
-        <v>2279</v>
+        <v>629</v>
       </c>
       <c r="C80" t="n">
         <v>8888</v>
       </c>
       <c r="D80" t="n">
-        <v>1165.17</v>
+        <v>2049.78</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1965,13 +1965,13 @@
         <v>46217</v>
       </c>
       <c r="B81" t="n">
-        <v>451</v>
+        <v>949</v>
       </c>
       <c r="C81" t="n">
-        <v>3403</v>
+        <v>1762</v>
       </c>
       <c r="D81" t="n">
-        <v>327.28</v>
+        <v>325.65</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -1984,17 +1984,17 @@
         <v>46217</v>
       </c>
       <c r="B82" t="n">
-        <v>2571</v>
+        <v>2463</v>
       </c>
       <c r="C82" t="n">
-        <v>1312</v>
+        <v>8888</v>
       </c>
       <c r="D82" t="n">
-        <v>2202.75</v>
+        <v>8336.43</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2003,17 +2003,17 @@
         <v>46217</v>
       </c>
       <c r="B83" t="n">
-        <v>610</v>
+        <v>1064</v>
       </c>
       <c r="C83" t="n">
         <v>8888</v>
       </c>
       <c r="D83" t="n">
-        <v>335.61</v>
+        <v>1513.21</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2022,17 +2022,17 @@
         <v>46217</v>
       </c>
       <c r="B84" t="n">
-        <v>1108</v>
+        <v>1478</v>
       </c>
       <c r="C84" t="n">
         <v>8888</v>
       </c>
       <c r="D84" t="n">
-        <v>508.54</v>
+        <v>2261.67</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2041,17 +2041,17 @@
         <v>46217</v>
       </c>
       <c r="B85" t="n">
-        <v>341</v>
+        <v>358</v>
       </c>
       <c r="C85" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D85" t="n">
-        <v>366.88</v>
+        <v>1918.33</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2060,17 +2060,17 @@
         <v>46217</v>
       </c>
       <c r="B86" t="n">
-        <v>1653</v>
+        <v>2107</v>
       </c>
       <c r="C86" t="n">
         <v>8888</v>
       </c>
       <c r="D86" t="n">
-        <v>4383.69</v>
+        <v>2745.11</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2079,13 +2079,13 @@
         <v>46217</v>
       </c>
       <c r="B87" t="n">
-        <v>619</v>
+        <v>675</v>
       </c>
       <c r="C87" t="n">
         <v>8888</v>
       </c>
       <c r="D87" t="n">
-        <v>1557.5</v>
+        <v>678.88</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -2098,13 +2098,13 @@
         <v>46217</v>
       </c>
       <c r="B88" t="n">
-        <v>663</v>
+        <v>2279</v>
       </c>
       <c r="C88" t="n">
         <v>8888</v>
       </c>
       <c r="D88" t="n">
-        <v>824.5599999999999</v>
+        <v>1165.17</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -2117,17 +2117,17 @@
         <v>46217</v>
       </c>
       <c r="B89" t="n">
-        <v>58</v>
+        <v>451</v>
       </c>
       <c r="C89" t="n">
-        <v>8888</v>
+        <v>3403</v>
       </c>
       <c r="D89" t="n">
-        <v>660.1</v>
+        <v>327.28</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2136,13 +2136,13 @@
         <v>46217</v>
       </c>
       <c r="B90" t="n">
-        <v>429</v>
+        <v>2571</v>
       </c>
       <c r="C90" t="n">
-        <v>2571</v>
+        <v>1312</v>
       </c>
       <c r="D90" t="n">
-        <v>667.12</v>
+        <v>2202.75</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -2155,13 +2155,13 @@
         <v>46217</v>
       </c>
       <c r="B91" t="n">
-        <v>2641</v>
+        <v>2782</v>
       </c>
       <c r="C91" t="n">
         <v>8888</v>
       </c>
       <c r="D91" t="n">
-        <v>252.41</v>
+        <v>753.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -2174,17 +2174,17 @@
         <v>46217</v>
       </c>
       <c r="B92" t="n">
-        <v>1293</v>
+        <v>610</v>
       </c>
       <c r="C92" t="n">
         <v>8888</v>
       </c>
       <c r="D92" t="n">
-        <v>8102.01</v>
+        <v>335.61</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2193,17 +2193,17 @@
         <v>46217</v>
       </c>
       <c r="B93" t="n">
-        <v>483</v>
+        <v>2245</v>
       </c>
       <c r="C93" t="n">
         <v>8888</v>
       </c>
       <c r="D93" t="n">
-        <v>1290.28</v>
+        <v>355.88</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2212,17 +2212,17 @@
         <v>46217</v>
       </c>
       <c r="B94" t="n">
-        <v>2308</v>
+        <v>1108</v>
       </c>
       <c r="C94" t="n">
-        <v>546</v>
+        <v>8888</v>
       </c>
       <c r="D94" t="n">
-        <v>1292.23</v>
+        <v>508.54</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2231,13 +2231,13 @@
         <v>46217</v>
       </c>
       <c r="B95" t="n">
-        <v>2709</v>
+        <v>341</v>
       </c>
       <c r="C95" t="n">
-        <v>2220</v>
+        <v>58</v>
       </c>
       <c r="D95" t="n">
-        <v>1663.5</v>
+        <v>366.88</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -2250,13 +2250,13 @@
         <v>46217</v>
       </c>
       <c r="B96" t="n">
-        <v>1937</v>
+        <v>1653</v>
       </c>
       <c r="C96" t="n">
         <v>8888</v>
       </c>
       <c r="D96" t="n">
-        <v>1332.89</v>
+        <v>4383.69</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -2269,17 +2269,17 @@
         <v>46217</v>
       </c>
       <c r="B97" t="n">
-        <v>429</v>
+        <v>619</v>
       </c>
       <c r="C97" t="n">
-        <v>1281</v>
+        <v>8888</v>
       </c>
       <c r="D97" t="n">
-        <v>2195.97</v>
+        <v>1557.5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
         <v>46217</v>
       </c>
       <c r="B98" t="n">
-        <v>2211</v>
+        <v>663</v>
       </c>
       <c r="C98" t="n">
         <v>8888</v>
       </c>
       <c r="D98" t="n">
-        <v>797.61</v>
+        <v>824.5599999999999</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2307,17 +2307,17 @@
         <v>46217</v>
       </c>
       <c r="B99" t="n">
-        <v>360</v>
+        <v>429</v>
       </c>
       <c r="C99" t="n">
-        <v>8888</v>
+        <v>2571</v>
       </c>
       <c r="D99" t="n">
-        <v>13118.46</v>
+        <v>667.12</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2326,17 +2326,17 @@
         <v>46217</v>
       </c>
       <c r="B100" t="n">
-        <v>131</v>
+        <v>2641</v>
       </c>
       <c r="C100" t="n">
         <v>8888</v>
       </c>
       <c r="D100" t="n">
-        <v>2340.29</v>
+        <v>252.41</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2345,17 +2345,17 @@
         <v>46217</v>
       </c>
       <c r="B101" t="n">
-        <v>131</v>
+        <v>1293</v>
       </c>
       <c r="C101" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D101" t="n">
-        <v>669.39</v>
+        <v>8102.01</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2364,17 +2364,17 @@
         <v>46217</v>
       </c>
       <c r="B102" t="n">
-        <v>1064</v>
+        <v>1465</v>
       </c>
       <c r="C102" t="n">
         <v>8888</v>
       </c>
       <c r="D102" t="n">
-        <v>103288.88</v>
+        <v>814.65</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2383,17 +2383,17 @@
         <v>46217</v>
       </c>
       <c r="B103" t="n">
-        <v>2251</v>
+        <v>483</v>
       </c>
       <c r="C103" t="n">
         <v>8888</v>
       </c>
       <c r="D103" t="n">
-        <v>797.58</v>
+        <v>1290.28</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2402,13 +2402,13 @@
         <v>46217</v>
       </c>
       <c r="B104" t="n">
-        <v>451</v>
+        <v>1064</v>
       </c>
       <c r="C104" t="n">
         <v>8888</v>
       </c>
       <c r="D104" t="n">
-        <v>1371.26</v>
+        <v>104632.21</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -2421,17 +2421,17 @@
         <v>46217</v>
       </c>
       <c r="B105" t="n">
-        <v>40</v>
+        <v>131</v>
       </c>
       <c r="C105" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D105" t="n">
-        <v>1093.47</v>
+        <v>876.48</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2440,17 +2440,17 @@
         <v>46217</v>
       </c>
       <c r="B106" t="n">
-        <v>530</v>
+        <v>663</v>
       </c>
       <c r="C106" t="n">
         <v>8888</v>
       </c>
       <c r="D106" t="n">
-        <v>180.08</v>
+        <v>979.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2459,17 +2459,17 @@
         <v>46217</v>
       </c>
       <c r="B107" t="n">
-        <v>1137</v>
+        <v>131</v>
       </c>
       <c r="C107" t="n">
         <v>8888</v>
       </c>
       <c r="D107" t="n">
-        <v>2833.69</v>
+        <v>4787.28</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2478,13 +2478,13 @@
         <v>46217</v>
       </c>
       <c r="B108" t="n">
-        <v>1293</v>
+        <v>2308</v>
       </c>
       <c r="C108" t="n">
-        <v>601</v>
+        <v>546</v>
       </c>
       <c r="D108" t="n">
-        <v>456.47</v>
+        <v>1292.23</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -2497,17 +2497,17 @@
         <v>46217</v>
       </c>
       <c r="B109" t="n">
-        <v>2118</v>
+        <v>2709</v>
       </c>
       <c r="C109" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D109" t="n">
-        <v>311.54</v>
+        <v>1663.5</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2516,17 +2516,17 @@
         <v>46217</v>
       </c>
       <c r="B110" t="n">
-        <v>424</v>
+        <v>1937</v>
       </c>
       <c r="C110" t="n">
         <v>8888</v>
       </c>
       <c r="D110" t="n">
-        <v>349.68</v>
+        <v>1492.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2535,13 +2535,13 @@
         <v>46217</v>
       </c>
       <c r="B111" t="n">
-        <v>1299</v>
+        <v>429</v>
       </c>
       <c r="C111" t="n">
-        <v>27</v>
+        <v>1281</v>
       </c>
       <c r="D111" t="n">
-        <v>1425.22</v>
+        <v>2195.97</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -2554,17 +2554,17 @@
         <v>46217</v>
       </c>
       <c r="B112" t="n">
-        <v>559</v>
+        <v>2211</v>
       </c>
       <c r="C112" t="n">
         <v>8888</v>
       </c>
       <c r="D112" t="n">
-        <v>1064.63</v>
+        <v>797.61</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2573,17 +2573,17 @@
         <v>46217</v>
       </c>
       <c r="B113" t="n">
-        <v>89</v>
+        <v>360</v>
       </c>
       <c r="C113" t="n">
         <v>8888</v>
       </c>
       <c r="D113" t="n">
-        <v>1506.42</v>
+        <v>13786.36</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2592,17 +2592,17 @@
         <v>46217</v>
       </c>
       <c r="B114" t="n">
-        <v>2250</v>
+        <v>2251</v>
       </c>
       <c r="C114" t="n">
         <v>8888</v>
       </c>
       <c r="D114" t="n">
-        <v>1943.54</v>
+        <v>797.58</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2611,13 +2611,13 @@
         <v>46217</v>
       </c>
       <c r="B115" t="n">
-        <v>767</v>
+        <v>451</v>
       </c>
       <c r="C115" t="n">
         <v>8888</v>
       </c>
       <c r="D115" t="n">
-        <v>472.62</v>
+        <v>1371.26</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -2630,17 +2630,17 @@
         <v>46217</v>
       </c>
       <c r="B116" t="n">
-        <v>2651</v>
+        <v>40</v>
       </c>
       <c r="C116" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D116" t="n">
-        <v>648.71</v>
+        <v>1093.47</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2649,17 +2649,17 @@
         <v>46217</v>
       </c>
       <c r="B117" t="n">
-        <v>2114</v>
+        <v>530</v>
       </c>
       <c r="C117" t="n">
-        <v>1954</v>
+        <v>8888</v>
       </c>
       <c r="D117" t="n">
-        <v>879.03</v>
+        <v>180.08</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2668,17 +2668,17 @@
         <v>46217</v>
       </c>
       <c r="B118" t="n">
-        <v>40</v>
+        <v>1137</v>
       </c>
       <c r="C118" t="n">
         <v>8888</v>
       </c>
       <c r="D118" t="n">
-        <v>3583.39</v>
+        <v>2833.69</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2687,17 +2687,17 @@
         <v>46217</v>
       </c>
       <c r="B119" t="n">
-        <v>40</v>
+        <v>1293</v>
       </c>
       <c r="C119" t="n">
-        <v>8888</v>
+        <v>601</v>
       </c>
       <c r="D119" t="n">
-        <v>2529.31</v>
+        <v>456.47</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2706,17 +2706,17 @@
         <v>46217</v>
       </c>
       <c r="B120" t="n">
-        <v>626</v>
+        <v>2118</v>
       </c>
       <c r="C120" t="n">
         <v>8888</v>
       </c>
       <c r="D120" t="n">
-        <v>13218.02</v>
+        <v>311.54</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2725,17 +2725,17 @@
         <v>46217</v>
       </c>
       <c r="B121" t="n">
-        <v>363</v>
+        <v>424</v>
       </c>
       <c r="C121" t="n">
         <v>8888</v>
       </c>
       <c r="D121" t="n">
-        <v>739.17</v>
+        <v>349.68</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2744,13 +2744,13 @@
         <v>46217</v>
       </c>
       <c r="B122" t="n">
-        <v>675</v>
+        <v>1299</v>
       </c>
       <c r="C122" t="n">
-        <v>1898</v>
+        <v>27</v>
       </c>
       <c r="D122" t="n">
-        <v>107.13</v>
+        <v>3625.32</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -2763,17 +2763,17 @@
         <v>46217</v>
       </c>
       <c r="B123" t="n">
-        <v>636</v>
+        <v>559</v>
       </c>
       <c r="C123" t="n">
         <v>8888</v>
       </c>
       <c r="D123" t="n">
-        <v>5631.89</v>
+        <v>1064.63</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2782,17 +2782,17 @@
         <v>46217</v>
       </c>
       <c r="B124" t="n">
-        <v>1075</v>
+        <v>89</v>
       </c>
       <c r="C124" t="n">
         <v>8888</v>
       </c>
       <c r="D124" t="n">
-        <v>1331.89</v>
+        <v>1506.42</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2801,17 +2801,17 @@
         <v>46217</v>
       </c>
       <c r="B125" t="n">
-        <v>2245</v>
+        <v>2250</v>
       </c>
       <c r="C125" t="n">
         <v>8888</v>
       </c>
       <c r="D125" t="n">
-        <v>883.75</v>
+        <v>1943.54</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2820,17 +2820,17 @@
         <v>46217</v>
       </c>
       <c r="B126" t="n">
-        <v>477</v>
+        <v>767</v>
       </c>
       <c r="C126" t="n">
         <v>8888</v>
       </c>
       <c r="D126" t="n">
-        <v>994.15</v>
+        <v>472.62</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2839,17 +2839,17 @@
         <v>46217</v>
       </c>
       <c r="B127" t="n">
-        <v>2015</v>
+        <v>2651</v>
       </c>
       <c r="C127" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D127" t="n">
-        <v>2931.07</v>
+        <v>648.71</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2858,17 +2858,17 @@
         <v>46217</v>
       </c>
       <c r="B128" t="n">
-        <v>1653</v>
+        <v>2114</v>
       </c>
       <c r="C128" t="n">
-        <v>8888</v>
+        <v>1954</v>
       </c>
       <c r="D128" t="n">
-        <v>4115.53</v>
+        <v>879.03</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2877,17 +2877,17 @@
         <v>46217</v>
       </c>
       <c r="B129" t="n">
-        <v>1064</v>
+        <v>40</v>
       </c>
       <c r="C129" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D129" t="n">
-        <v>451.38</v>
+        <v>3583.39</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2896,13 +2896,13 @@
         <v>46217</v>
       </c>
       <c r="B130" t="n">
-        <v>1983</v>
+        <v>40</v>
       </c>
       <c r="C130" t="n">
         <v>8888</v>
       </c>
       <c r="D130" t="n">
-        <v>1246.33</v>
+        <v>2529.31</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -2915,17 +2915,17 @@
         <v>46217</v>
       </c>
       <c r="B131" t="n">
-        <v>2118</v>
+        <v>626</v>
       </c>
       <c r="C131" t="n">
         <v>8888</v>
       </c>
       <c r="D131" t="n">
-        <v>2646.39</v>
+        <v>13218.02</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2934,17 +2934,17 @@
         <v>46217</v>
       </c>
       <c r="B132" t="n">
-        <v>2680</v>
+        <v>363</v>
       </c>
       <c r="C132" t="n">
         <v>8888</v>
       </c>
       <c r="D132" t="n">
-        <v>824.67</v>
+        <v>739.17</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2953,17 +2953,17 @@
         <v>46217</v>
       </c>
       <c r="B133" t="n">
-        <v>2637</v>
+        <v>675</v>
       </c>
       <c r="C133" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D133" t="n">
-        <v>1302.18</v>
+        <v>107.13</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2972,17 +2972,17 @@
         <v>46217</v>
       </c>
       <c r="B134" t="n">
-        <v>2026</v>
+        <v>636</v>
       </c>
       <c r="C134" t="n">
         <v>8888</v>
       </c>
       <c r="D134" t="n">
-        <v>699.05</v>
+        <v>5631.89</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2991,17 +2991,17 @@
         <v>46217</v>
       </c>
       <c r="B135" t="n">
-        <v>629</v>
+        <v>1075</v>
       </c>
       <c r="C135" t="n">
-        <v>675</v>
+        <v>8888</v>
       </c>
       <c r="D135" t="n">
-        <v>267.79</v>
+        <v>1331.89</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3010,17 +3010,17 @@
         <v>46217</v>
       </c>
       <c r="B136" t="n">
-        <v>559</v>
+        <v>2245</v>
       </c>
       <c r="C136" t="n">
         <v>8888</v>
       </c>
       <c r="D136" t="n">
-        <v>1562.5</v>
+        <v>883.75</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3029,17 +3029,17 @@
         <v>46217</v>
       </c>
       <c r="B137" t="n">
-        <v>1465</v>
+        <v>477</v>
       </c>
       <c r="C137" t="n">
         <v>8888</v>
       </c>
       <c r="D137" t="n">
-        <v>9346.120000000001</v>
+        <v>994.15</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3048,17 +3048,17 @@
         <v>46217</v>
       </c>
       <c r="B138" t="n">
-        <v>2550</v>
+        <v>2015</v>
       </c>
       <c r="C138" t="n">
         <v>8888</v>
       </c>
       <c r="D138" t="n">
-        <v>321.05</v>
+        <v>2931.07</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3067,17 +3067,17 @@
         <v>46217</v>
       </c>
       <c r="B139" t="n">
-        <v>1756</v>
+        <v>1653</v>
       </c>
       <c r="C139" t="n">
         <v>8888</v>
       </c>
       <c r="D139" t="n">
-        <v>2445</v>
+        <v>4115.53</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3086,17 +3086,17 @@
         <v>46217</v>
       </c>
       <c r="B140" t="n">
-        <v>363</v>
+        <v>1064</v>
       </c>
       <c r="C140" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D140" t="n">
-        <v>2517.01</v>
+        <v>1052.68</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3105,17 +3105,17 @@
         <v>46217</v>
       </c>
       <c r="B141" t="n">
-        <v>2698</v>
+        <v>1983</v>
       </c>
       <c r="C141" t="n">
-        <v>874</v>
+        <v>8888</v>
       </c>
       <c r="D141" t="n">
-        <v>1183.42</v>
+        <v>1246.33</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3124,13 +3124,13 @@
         <v>46217</v>
       </c>
       <c r="B142" t="n">
-        <v>535</v>
+        <v>2118</v>
       </c>
       <c r="C142" t="n">
         <v>8888</v>
       </c>
       <c r="D142" t="n">
-        <v>5293.96</v>
+        <v>4886.49</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -3143,13 +3143,13 @@
         <v>46217</v>
       </c>
       <c r="B143" t="n">
-        <v>2250</v>
+        <v>2680</v>
       </c>
       <c r="C143" t="n">
         <v>8888</v>
       </c>
       <c r="D143" t="n">
-        <v>1512.17</v>
+        <v>2285.31</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -3162,17 +3162,17 @@
         <v>46217</v>
       </c>
       <c r="B144" t="n">
-        <v>2681</v>
+        <v>2637</v>
       </c>
       <c r="C144" t="n">
         <v>8888</v>
       </c>
       <c r="D144" t="n">
-        <v>2775.8</v>
+        <v>1302.18</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3181,17 +3181,17 @@
         <v>46217</v>
       </c>
       <c r="B145" t="n">
-        <v>363</v>
+        <v>1632</v>
       </c>
       <c r="C145" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D145" t="n">
-        <v>3635.16</v>
+        <v>689.76</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3200,17 +3200,17 @@
         <v>46217</v>
       </c>
       <c r="B146" t="n">
-        <v>483</v>
+        <v>1299</v>
       </c>
       <c r="C146" t="n">
-        <v>8888</v>
+        <v>2522</v>
       </c>
       <c r="D146" t="n">
-        <v>2527.71</v>
+        <v>3319.01</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3219,17 +3219,17 @@
         <v>46217</v>
       </c>
       <c r="B147" t="n">
-        <v>2607</v>
+        <v>2026</v>
       </c>
       <c r="C147" t="n">
         <v>8888</v>
       </c>
       <c r="D147" t="n">
-        <v>1075.36</v>
+        <v>699.05</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3238,17 +3238,17 @@
         <v>46217</v>
       </c>
       <c r="B148" t="n">
-        <v>2330</v>
+        <v>664</v>
       </c>
       <c r="C148" t="n">
-        <v>1954</v>
+        <v>8888</v>
       </c>
       <c r="D148" t="n">
-        <v>1923.09</v>
+        <v>440.92</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3257,17 +3257,17 @@
         <v>46217</v>
       </c>
       <c r="B149" t="n">
-        <v>2709</v>
+        <v>629</v>
       </c>
       <c r="C149" t="n">
-        <v>8888</v>
+        <v>675</v>
       </c>
       <c r="D149" t="n">
-        <v>1667.47</v>
+        <v>267.79</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3276,17 +3276,17 @@
         <v>46217</v>
       </c>
       <c r="B150" t="n">
-        <v>374</v>
+        <v>559</v>
       </c>
       <c r="C150" t="n">
         <v>8888</v>
       </c>
       <c r="D150" t="n">
-        <v>1150.97</v>
+        <v>1562.5</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3295,13 +3295,13 @@
         <v>46217</v>
       </c>
       <c r="B151" t="n">
-        <v>1137</v>
+        <v>1465</v>
       </c>
       <c r="C151" t="n">
         <v>8888</v>
       </c>
       <c r="D151" t="n">
-        <v>4413.34</v>
+        <v>10920.6</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -3314,15 +3314,281 @@
         <v>46217</v>
       </c>
       <c r="B152" t="n">
+        <v>2550</v>
+      </c>
+      <c r="C152" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D152" t="n">
+        <v>321.05</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B153" t="n">
+        <v>1756</v>
+      </c>
+      <c r="C153" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D153" t="n">
+        <v>2445</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B154" t="n">
+        <v>363</v>
+      </c>
+      <c r="C154" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D154" t="n">
+        <v>2517.01</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B155" t="n">
+        <v>2698</v>
+      </c>
+      <c r="C155" t="n">
+        <v>874</v>
+      </c>
+      <c r="D155" t="n">
+        <v>1183.42</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B156" t="n">
+        <v>535</v>
+      </c>
+      <c r="C156" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D156" t="n">
+        <v>5293.96</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B157" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C157" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D157" t="n">
+        <v>2650.33</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B158" t="n">
+        <v>2681</v>
+      </c>
+      <c r="C158" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D158" t="n">
+        <v>2775.8</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B159" t="n">
+        <v>363</v>
+      </c>
+      <c r="C159" t="n">
+        <v>1898</v>
+      </c>
+      <c r="D159" t="n">
+        <v>3635.16</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B160" t="n">
+        <v>483</v>
+      </c>
+      <c r="C160" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D160" t="n">
+        <v>2527.71</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B161" t="n">
+        <v>2607</v>
+      </c>
+      <c r="C161" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D161" t="n">
+        <v>1075.36</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B162" t="n">
+        <v>2330</v>
+      </c>
+      <c r="C162" t="n">
+        <v>1954</v>
+      </c>
+      <c r="D162" t="n">
+        <v>1923.09</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B163" t="n">
+        <v>2709</v>
+      </c>
+      <c r="C163" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1667.47</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B164" t="n">
+        <v>374</v>
+      </c>
+      <c r="C164" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1150.97</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B165" t="n">
+        <v>1137</v>
+      </c>
+      <c r="C165" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D165" t="n">
+        <v>4413.34</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B166" t="n">
         <v>2251</v>
       </c>
-      <c r="C152" t="n">
+      <c r="C166" t="n">
         <v>3403</v>
       </c>
-      <c r="D152" t="n">
+      <c r="D166" t="n">
         <v>510.18</v>
       </c>
-      <c r="E152" t="inlineStr">
+      <c r="E166" t="inlineStr">
         <is>
           <t>TELEMARKETING</t>
         </is>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E166"/>
+  <dimension ref="A1:E192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,13 +521,13 @@
         <v>46217</v>
       </c>
       <c r="B5" t="n">
-        <v>1653</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>1281</v>
+        <v>1533</v>
       </c>
       <c r="D5" t="n">
-        <v>4524.08</v>
+        <v>1154.58</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -540,13 +540,13 @@
         <v>46217</v>
       </c>
       <c r="B6" t="n">
-        <v>2109</v>
+        <v>1298</v>
       </c>
       <c r="C6" t="n">
         <v>8888</v>
       </c>
       <c r="D6" t="n">
-        <v>4813.6</v>
+        <v>6359.39</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -559,17 +559,17 @@
         <v>46217</v>
       </c>
       <c r="B7" t="n">
-        <v>2015</v>
+        <v>415</v>
       </c>
       <c r="C7" t="n">
-        <v>2571</v>
+        <v>8888</v>
       </c>
       <c r="D7" t="n">
-        <v>2593.26</v>
+        <v>10705.35</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
         <v>46217</v>
       </c>
       <c r="B8" t="n">
-        <v>1993</v>
+        <v>1653</v>
       </c>
       <c r="C8" t="n">
-        <v>8888</v>
+        <v>1281</v>
       </c>
       <c r="D8" t="n">
-        <v>1785.44</v>
+        <v>4524.08</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -597,13 +597,13 @@
         <v>46217</v>
       </c>
       <c r="B9" t="n">
-        <v>1102</v>
+        <v>2109</v>
       </c>
       <c r="C9" t="n">
         <v>8888</v>
       </c>
       <c r="D9" t="n">
-        <v>2432.31</v>
+        <v>4813.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -616,13 +616,13 @@
         <v>46217</v>
       </c>
       <c r="B10" t="n">
-        <v>1293</v>
+        <v>2015</v>
       </c>
       <c r="C10" t="n">
-        <v>1281</v>
+        <v>2571</v>
       </c>
       <c r="D10" t="n">
-        <v>1337.87</v>
+        <v>2593.26</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -635,17 +635,17 @@
         <v>46217</v>
       </c>
       <c r="B11" t="n">
-        <v>2768</v>
+        <v>1993</v>
       </c>
       <c r="C11" t="n">
         <v>8888</v>
       </c>
       <c r="D11" t="n">
-        <v>4890.12</v>
+        <v>1785.44</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -654,17 +654,17 @@
         <v>46217</v>
       </c>
       <c r="B12" t="n">
-        <v>2726</v>
+        <v>1102</v>
       </c>
       <c r="C12" t="n">
-        <v>1929</v>
+        <v>8888</v>
       </c>
       <c r="D12" t="n">
-        <v>640.1799999999999</v>
+        <v>3129.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -673,17 +673,17 @@
         <v>46217</v>
       </c>
       <c r="B13" t="n">
-        <v>89</v>
+        <v>1293</v>
       </c>
       <c r="C13" t="n">
-        <v>8888</v>
+        <v>1281</v>
       </c>
       <c r="D13" t="n">
-        <v>5652.15</v>
+        <v>1337.87</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -692,17 +692,17 @@
         <v>46217</v>
       </c>
       <c r="B14" t="n">
-        <v>1890</v>
+        <v>2657</v>
       </c>
       <c r="C14" t="n">
-        <v>3449</v>
+        <v>8888</v>
       </c>
       <c r="D14" t="n">
-        <v>589.0599999999999</v>
+        <v>877.0700000000001</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -711,17 +711,17 @@
         <v>46217</v>
       </c>
       <c r="B15" t="n">
-        <v>2641</v>
+        <v>2768</v>
       </c>
       <c r="C15" t="n">
         <v>8888</v>
       </c>
       <c r="D15" t="n">
-        <v>607.79</v>
+        <v>4890.12</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -730,17 +730,17 @@
         <v>46217</v>
       </c>
       <c r="B16" t="n">
-        <v>949</v>
+        <v>2686</v>
       </c>
       <c r="C16" t="n">
-        <v>1258</v>
+        <v>8888</v>
       </c>
       <c r="D16" t="n">
-        <v>196.87</v>
+        <v>422.71</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
         <v>46217</v>
       </c>
       <c r="B17" t="n">
-        <v>353</v>
+        <v>1890</v>
       </c>
       <c r="C17" t="n">
-        <v>8888</v>
+        <v>3449</v>
       </c>
       <c r="D17" t="n">
-        <v>2121.12</v>
+        <v>809.78</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -768,17 +768,17 @@
         <v>46217</v>
       </c>
       <c r="B18" t="n">
-        <v>1756</v>
+        <v>2726</v>
       </c>
       <c r="C18" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D18" t="n">
-        <v>1799.7</v>
+        <v>640.1799999999999</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
         <v>46217</v>
       </c>
       <c r="B19" t="n">
-        <v>285</v>
+        <v>89</v>
       </c>
       <c r="C19" t="n">
         <v>8888</v>
       </c>
       <c r="D19" t="n">
-        <v>3092.58</v>
+        <v>5652.15</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -806,13 +806,13 @@
         <v>46217</v>
       </c>
       <c r="B20" t="n">
-        <v>610</v>
+        <v>2641</v>
       </c>
       <c r="C20" t="n">
         <v>8888</v>
       </c>
       <c r="D20" t="n">
-        <v>590.08</v>
+        <v>607.79</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
         <v>46217</v>
       </c>
       <c r="B21" t="n">
-        <v>1906</v>
+        <v>949</v>
       </c>
       <c r="C21" t="n">
-        <v>8888</v>
+        <v>1258</v>
       </c>
       <c r="D21" t="n">
-        <v>2437.98</v>
+        <v>196.87</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -844,17 +844,17 @@
         <v>46217</v>
       </c>
       <c r="B22" t="n">
-        <v>619</v>
+        <v>353</v>
       </c>
       <c r="C22" t="n">
         <v>8888</v>
       </c>
       <c r="D22" t="n">
-        <v>236.34</v>
+        <v>2121.12</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -863,17 +863,17 @@
         <v>46217</v>
       </c>
       <c r="B23" t="n">
-        <v>2755</v>
+        <v>1756</v>
       </c>
       <c r="C23" t="n">
-        <v>2220</v>
+        <v>8888</v>
       </c>
       <c r="D23" t="n">
-        <v>1133.17</v>
+        <v>1799.7</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
         <v>46217</v>
       </c>
       <c r="B24" t="n">
-        <v>2767</v>
+        <v>285</v>
       </c>
       <c r="C24" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D24" t="n">
-        <v>5000.2</v>
+        <v>3092.58</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
         <v>46217</v>
       </c>
       <c r="B25" t="n">
-        <v>559</v>
+        <v>1906</v>
       </c>
       <c r="C25" t="n">
         <v>8888</v>
       </c>
       <c r="D25" t="n">
-        <v>1200.99</v>
+        <v>3142.54</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -920,17 +920,17 @@
         <v>46217</v>
       </c>
       <c r="B26" t="n">
-        <v>2767</v>
+        <v>1308</v>
       </c>
       <c r="C26" t="n">
         <v>8888</v>
       </c>
       <c r="D26" t="n">
-        <v>1175.73</v>
+        <v>3127.35</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -939,17 +939,17 @@
         <v>46217</v>
       </c>
       <c r="B27" t="n">
-        <v>1063</v>
+        <v>610</v>
       </c>
       <c r="C27" t="n">
         <v>8888</v>
       </c>
       <c r="D27" t="n">
-        <v>1251.14</v>
+        <v>590.08</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
         <v>46217</v>
       </c>
       <c r="B28" t="n">
-        <v>325</v>
+        <v>619</v>
       </c>
       <c r="C28" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D28" t="n">
-        <v>868.83</v>
+        <v>236.34</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -977,17 +977,17 @@
         <v>46217</v>
       </c>
       <c r="B29" t="n">
-        <v>2660</v>
+        <v>2755</v>
       </c>
       <c r="C29" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D29" t="n">
-        <v>281.24</v>
+        <v>1133.17</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -996,17 +996,17 @@
         <v>46217</v>
       </c>
       <c r="B30" t="n">
-        <v>610</v>
+        <v>2767</v>
       </c>
       <c r="C30" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D30" t="n">
-        <v>235.34</v>
+        <v>5000.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1015,17 +1015,17 @@
         <v>46217</v>
       </c>
       <c r="B31" t="n">
-        <v>424</v>
+        <v>559</v>
       </c>
       <c r="C31" t="n">
         <v>8888</v>
       </c>
       <c r="D31" t="n">
-        <v>3214.29</v>
+        <v>1200.99</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
         <v>46217</v>
       </c>
       <c r="B32" t="n">
-        <v>40</v>
+        <v>358</v>
       </c>
       <c r="C32" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D32" t="n">
-        <v>325.04</v>
+        <v>1301.77</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
         <v>46217</v>
       </c>
       <c r="B33" t="n">
-        <v>1117</v>
+        <v>609</v>
       </c>
       <c r="C33" t="n">
         <v>8888</v>
       </c>
       <c r="D33" t="n">
-        <v>349.47</v>
+        <v>962.08</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1072,17 +1072,17 @@
         <v>46217</v>
       </c>
       <c r="B34" t="n">
-        <v>949</v>
+        <v>2507</v>
       </c>
       <c r="C34" t="n">
-        <v>998</v>
+        <v>8888</v>
       </c>
       <c r="D34" t="n">
-        <v>129.85</v>
+        <v>448.36</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1091,17 +1091,17 @@
         <v>46217</v>
       </c>
       <c r="B35" t="n">
-        <v>1853</v>
+        <v>2767</v>
       </c>
       <c r="C35" t="n">
         <v>8888</v>
       </c>
       <c r="D35" t="n">
-        <v>522.4</v>
+        <v>1175.73</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1110,17 +1110,17 @@
         <v>46217</v>
       </c>
       <c r="B36" t="n">
-        <v>2250</v>
+        <v>1063</v>
       </c>
       <c r="C36" t="n">
         <v>8888</v>
       </c>
       <c r="D36" t="n">
-        <v>4131.57</v>
+        <v>1251.14</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1129,17 +1129,17 @@
         <v>46217</v>
       </c>
       <c r="B37" t="n">
-        <v>2507</v>
+        <v>325</v>
       </c>
       <c r="C37" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D37" t="n">
-        <v>4167.12</v>
+        <v>868.83</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1148,17 +1148,17 @@
         <v>46217</v>
       </c>
       <c r="B38" t="n">
-        <v>664</v>
+        <v>2660</v>
       </c>
       <c r="C38" t="n">
         <v>8888</v>
       </c>
       <c r="D38" t="n">
-        <v>3815.91</v>
+        <v>281.24</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1167,13 +1167,13 @@
         <v>46217</v>
       </c>
       <c r="B39" t="n">
-        <v>1075</v>
+        <v>610</v>
       </c>
       <c r="C39" t="n">
         <v>8888</v>
       </c>
       <c r="D39" t="n">
-        <v>1013.2</v>
+        <v>235.34</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1186,17 +1186,17 @@
         <v>46217</v>
       </c>
       <c r="B40" t="n">
-        <v>1906</v>
+        <v>424</v>
       </c>
       <c r="C40" t="n">
-        <v>1954</v>
+        <v>8888</v>
       </c>
       <c r="D40" t="n">
-        <v>1445.21</v>
+        <v>3214.29</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1205,13 +1205,13 @@
         <v>46217</v>
       </c>
       <c r="B41" t="n">
-        <v>2696</v>
+        <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>1312</v>
+        <v>58</v>
       </c>
       <c r="D41" t="n">
-        <v>677.76</v>
+        <v>325.04</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1224,17 +1224,17 @@
         <v>46217</v>
       </c>
       <c r="B42" t="n">
-        <v>360</v>
+        <v>1117</v>
       </c>
       <c r="C42" t="n">
-        <v>546</v>
+        <v>8888</v>
       </c>
       <c r="D42" t="n">
-        <v>5741.5</v>
+        <v>349.47</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
         <v>46217</v>
       </c>
       <c r="B43" t="n">
-        <v>2491</v>
+        <v>949</v>
       </c>
       <c r="C43" t="n">
-        <v>8888</v>
+        <v>998</v>
       </c>
       <c r="D43" t="n">
-        <v>2031.53</v>
+        <v>129.85</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1262,17 +1262,17 @@
         <v>46217</v>
       </c>
       <c r="B44" t="n">
-        <v>2651</v>
+        <v>1853</v>
       </c>
       <c r="C44" t="n">
         <v>8888</v>
       </c>
       <c r="D44" t="n">
-        <v>638.64</v>
+        <v>522.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1281,13 +1281,13 @@
         <v>46217</v>
       </c>
       <c r="B45" t="n">
-        <v>2695</v>
+        <v>2250</v>
       </c>
       <c r="C45" t="n">
         <v>8888</v>
       </c>
       <c r="D45" t="n">
-        <v>532.53</v>
+        <v>4131.57</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1300,17 +1300,17 @@
         <v>46217</v>
       </c>
       <c r="B46" t="n">
-        <v>1293</v>
+        <v>2507</v>
       </c>
       <c r="C46" t="n">
         <v>8888</v>
       </c>
       <c r="D46" t="n">
-        <v>381.82</v>
+        <v>4167.12</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1319,17 +1319,17 @@
         <v>46217</v>
       </c>
       <c r="B47" t="n">
-        <v>2663</v>
+        <v>664</v>
       </c>
       <c r="C47" t="n">
         <v>8888</v>
       </c>
       <c r="D47" t="n">
-        <v>2146.08</v>
+        <v>3815.91</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1338,13 +1338,13 @@
         <v>46217</v>
       </c>
       <c r="B48" t="n">
-        <v>525</v>
+        <v>1075</v>
       </c>
       <c r="C48" t="n">
         <v>8888</v>
       </c>
       <c r="D48" t="n">
-        <v>1240.79</v>
+        <v>1013.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1357,17 +1357,17 @@
         <v>46217</v>
       </c>
       <c r="B49" t="n">
-        <v>2711</v>
+        <v>1906</v>
       </c>
       <c r="C49" t="n">
-        <v>8888</v>
+        <v>1954</v>
       </c>
       <c r="D49" t="n">
-        <v>1953.5</v>
+        <v>1445.21</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1376,17 +1376,17 @@
         <v>46217</v>
       </c>
       <c r="B50" t="n">
-        <v>675</v>
+        <v>595</v>
       </c>
       <c r="C50" t="n">
-        <v>8888</v>
+        <v>691</v>
       </c>
       <c r="D50" t="n">
-        <v>289.67</v>
+        <v>314.52</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1395,17 +1395,17 @@
         <v>46217</v>
       </c>
       <c r="B51" t="n">
-        <v>1063</v>
+        <v>2696</v>
       </c>
       <c r="C51" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D51" t="n">
-        <v>1902.46</v>
+        <v>677.76</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1414,13 +1414,13 @@
         <v>46217</v>
       </c>
       <c r="B52" t="n">
-        <v>1392</v>
+        <v>525</v>
       </c>
       <c r="C52" t="n">
         <v>8888</v>
       </c>
       <c r="D52" t="n">
-        <v>814.61</v>
+        <v>490.08</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -1433,17 +1433,17 @@
         <v>46217</v>
       </c>
       <c r="B53" t="n">
-        <v>360</v>
+        <v>2491</v>
       </c>
       <c r="C53" t="n">
         <v>8888</v>
       </c>
       <c r="D53" t="n">
-        <v>749.13</v>
+        <v>2909.58</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1452,13 +1452,13 @@
         <v>46217</v>
       </c>
       <c r="B54" t="n">
-        <v>949</v>
+        <v>360</v>
       </c>
       <c r="C54" t="n">
-        <v>1134</v>
+        <v>546</v>
       </c>
       <c r="D54" t="n">
-        <v>327.6</v>
+        <v>6094.25</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -1471,17 +1471,17 @@
         <v>46217</v>
       </c>
       <c r="B55" t="n">
-        <v>326</v>
+        <v>2651</v>
       </c>
       <c r="C55" t="n">
         <v>8888</v>
       </c>
       <c r="D55" t="n">
-        <v>212.63</v>
+        <v>638.64</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1490,17 +1490,17 @@
         <v>46217</v>
       </c>
       <c r="B56" t="n">
-        <v>325</v>
+        <v>2695</v>
       </c>
       <c r="C56" t="n">
         <v>8888</v>
       </c>
       <c r="D56" t="n">
-        <v>616.95</v>
+        <v>532.53</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1509,13 +1509,13 @@
         <v>46217</v>
       </c>
       <c r="B57" t="n">
-        <v>131</v>
+        <v>1293</v>
       </c>
       <c r="C57" t="n">
         <v>8888</v>
       </c>
       <c r="D57" t="n">
-        <v>1969.93</v>
+        <v>381.82</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -1528,17 +1528,17 @@
         <v>46217</v>
       </c>
       <c r="B58" t="n">
-        <v>2697</v>
+        <v>2663</v>
       </c>
       <c r="C58" t="n">
         <v>8888</v>
       </c>
       <c r="D58" t="n">
-        <v>420.48</v>
+        <v>2146.08</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1547,13 +1547,13 @@
         <v>46217</v>
       </c>
       <c r="B59" t="n">
-        <v>2279</v>
+        <v>525</v>
       </c>
       <c r="C59" t="n">
         <v>8888</v>
       </c>
       <c r="D59" t="n">
-        <v>1034.25</v>
+        <v>1240.79</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -1566,17 +1566,17 @@
         <v>46217</v>
       </c>
       <c r="B60" t="n">
-        <v>1116</v>
+        <v>2711</v>
       </c>
       <c r="C60" t="n">
         <v>8888</v>
       </c>
       <c r="D60" t="n">
-        <v>1293.89</v>
+        <v>2193.56</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1585,13 +1585,13 @@
         <v>46217</v>
       </c>
       <c r="B61" t="n">
-        <v>131</v>
+        <v>1317</v>
       </c>
       <c r="C61" t="n">
         <v>8888</v>
       </c>
       <c r="D61" t="n">
-        <v>5470.1</v>
+        <v>787.51</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -1604,17 +1604,17 @@
         <v>46217</v>
       </c>
       <c r="B62" t="n">
-        <v>1293</v>
+        <v>675</v>
       </c>
       <c r="C62" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D62" t="n">
-        <v>5154.68</v>
+        <v>289.67</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1623,13 +1623,13 @@
         <v>46217</v>
       </c>
       <c r="B63" t="n">
-        <v>1937</v>
+        <v>1063</v>
       </c>
       <c r="C63" t="n">
         <v>8888</v>
       </c>
       <c r="D63" t="n">
-        <v>692.86</v>
+        <v>1902.46</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -1642,17 +1642,17 @@
         <v>46217</v>
       </c>
       <c r="B64" t="n">
-        <v>1983</v>
+        <v>1658</v>
       </c>
       <c r="C64" t="n">
         <v>8888</v>
       </c>
       <c r="D64" t="n">
-        <v>412.16</v>
+        <v>1357.94</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1661,17 +1661,17 @@
         <v>46217</v>
       </c>
       <c r="B65" t="n">
-        <v>451</v>
+        <v>1392</v>
       </c>
       <c r="C65" t="n">
         <v>8888</v>
       </c>
       <c r="D65" t="n">
-        <v>2583.46</v>
+        <v>814.61</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1680,17 +1680,17 @@
         <v>46217</v>
       </c>
       <c r="B66" t="n">
-        <v>2767</v>
+        <v>360</v>
       </c>
       <c r="C66" t="n">
         <v>8888</v>
       </c>
       <c r="D66" t="n">
-        <v>596.88</v>
+        <v>749.13</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1699,17 +1699,17 @@
         <v>46217</v>
       </c>
       <c r="B67" t="n">
-        <v>2697</v>
+        <v>949</v>
       </c>
       <c r="C67" t="n">
-        <v>8888</v>
+        <v>1134</v>
       </c>
       <c r="D67" t="n">
-        <v>2880.19</v>
+        <v>327.6</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1718,13 +1718,13 @@
         <v>46217</v>
       </c>
       <c r="B68" t="n">
-        <v>569</v>
+        <v>2133</v>
       </c>
       <c r="C68" t="n">
         <v>8888</v>
       </c>
       <c r="D68" t="n">
-        <v>2291.64</v>
+        <v>66030.34</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -1737,17 +1737,17 @@
         <v>46217</v>
       </c>
       <c r="B69" t="n">
-        <v>2211</v>
+        <v>326</v>
       </c>
       <c r="C69" t="n">
-        <v>874</v>
+        <v>8888</v>
       </c>
       <c r="D69" t="n">
-        <v>1833.56</v>
+        <v>360.45</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1756,17 +1756,17 @@
         <v>46217</v>
       </c>
       <c r="B70" t="n">
-        <v>1063</v>
+        <v>325</v>
       </c>
       <c r="C70" t="n">
         <v>8888</v>
       </c>
       <c r="D70" t="n">
-        <v>352.87</v>
+        <v>774.73</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1775,17 +1775,17 @@
         <v>46217</v>
       </c>
       <c r="B71" t="n">
-        <v>2687</v>
+        <v>1293</v>
       </c>
       <c r="C71" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D71" t="n">
-        <v>1760.22</v>
+        <v>8365.559999999999</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1794,17 +1794,17 @@
         <v>46217</v>
       </c>
       <c r="B72" t="n">
-        <v>629</v>
+        <v>131</v>
       </c>
       <c r="C72" t="n">
         <v>8888</v>
       </c>
       <c r="D72" t="n">
-        <v>559.15</v>
+        <v>1969.93</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1813,17 +1813,17 @@
         <v>46217</v>
       </c>
       <c r="B73" t="n">
-        <v>1890</v>
+        <v>2697</v>
       </c>
       <c r="C73" t="n">
-        <v>1953</v>
+        <v>8888</v>
       </c>
       <c r="D73" t="n">
-        <v>1122</v>
+        <v>420.48</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1832,13 +1832,13 @@
         <v>46217</v>
       </c>
       <c r="B74" t="n">
-        <v>1289</v>
+        <v>2279</v>
       </c>
       <c r="C74" t="n">
         <v>8888</v>
       </c>
       <c r="D74" t="n">
-        <v>1214.09</v>
+        <v>1034.25</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -1851,17 +1851,17 @@
         <v>46217</v>
       </c>
       <c r="B75" t="n">
-        <v>2107</v>
+        <v>1116</v>
       </c>
       <c r="C75" t="n">
-        <v>1954</v>
+        <v>8888</v>
       </c>
       <c r="D75" t="n">
-        <v>2000.86</v>
+        <v>1293.89</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1870,13 +1870,13 @@
         <v>46217</v>
       </c>
       <c r="B76" t="n">
-        <v>1116</v>
+        <v>131</v>
       </c>
       <c r="C76" t="n">
         <v>8888</v>
       </c>
       <c r="D76" t="n">
-        <v>1065.24</v>
+        <v>5470.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -1889,17 +1889,17 @@
         <v>46217</v>
       </c>
       <c r="B77" t="n">
-        <v>58</v>
+        <v>1937</v>
       </c>
       <c r="C77" t="n">
         <v>8888</v>
       </c>
       <c r="D77" t="n">
-        <v>2637.19</v>
+        <v>692.86</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1908,17 +1908,17 @@
         <v>46217</v>
       </c>
       <c r="B78" t="n">
-        <v>1117</v>
+        <v>1983</v>
       </c>
       <c r="C78" t="n">
         <v>8888</v>
       </c>
       <c r="D78" t="n">
-        <v>581.51</v>
+        <v>412.16</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1927,17 +1927,17 @@
         <v>46217</v>
       </c>
       <c r="B79" t="n">
-        <v>58</v>
+        <v>451</v>
       </c>
       <c r="C79" t="n">
         <v>8888</v>
       </c>
       <c r="D79" t="n">
-        <v>1411.43</v>
+        <v>2583.46</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1946,13 +1946,13 @@
         <v>46217</v>
       </c>
       <c r="B80" t="n">
-        <v>629</v>
+        <v>2767</v>
       </c>
       <c r="C80" t="n">
         <v>8888</v>
       </c>
       <c r="D80" t="n">
-        <v>2049.78</v>
+        <v>920.85</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -1965,17 +1965,17 @@
         <v>46217</v>
       </c>
       <c r="B81" t="n">
-        <v>949</v>
+        <v>2697</v>
       </c>
       <c r="C81" t="n">
-        <v>1762</v>
+        <v>8888</v>
       </c>
       <c r="D81" t="n">
-        <v>325.65</v>
+        <v>2880.19</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1984,17 +1984,17 @@
         <v>46217</v>
       </c>
       <c r="B82" t="n">
-        <v>2463</v>
+        <v>569</v>
       </c>
       <c r="C82" t="n">
         <v>8888</v>
       </c>
       <c r="D82" t="n">
-        <v>8336.43</v>
+        <v>2291.64</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2003,17 +2003,17 @@
         <v>46217</v>
       </c>
       <c r="B83" t="n">
-        <v>1064</v>
+        <v>2211</v>
       </c>
       <c r="C83" t="n">
-        <v>8888</v>
+        <v>874</v>
       </c>
       <c r="D83" t="n">
-        <v>1513.21</v>
+        <v>1833.56</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2022,13 +2022,13 @@
         <v>46217</v>
       </c>
       <c r="B84" t="n">
-        <v>1478</v>
+        <v>1063</v>
       </c>
       <c r="C84" t="n">
         <v>8888</v>
       </c>
       <c r="D84" t="n">
-        <v>2261.67</v>
+        <v>352.87</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2041,17 +2041,17 @@
         <v>46217</v>
       </c>
       <c r="B85" t="n">
-        <v>358</v>
+        <v>2687</v>
       </c>
       <c r="C85" t="n">
         <v>8888</v>
       </c>
       <c r="D85" t="n">
-        <v>1918.33</v>
+        <v>1760.22</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2060,17 +2060,17 @@
         <v>46217</v>
       </c>
       <c r="B86" t="n">
-        <v>2107</v>
+        <v>629</v>
       </c>
       <c r="C86" t="n">
         <v>8888</v>
       </c>
       <c r="D86" t="n">
-        <v>2745.11</v>
+        <v>559.15</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2079,17 +2079,17 @@
         <v>46217</v>
       </c>
       <c r="B87" t="n">
-        <v>675</v>
+        <v>1890</v>
       </c>
       <c r="C87" t="n">
-        <v>8888</v>
+        <v>1953</v>
       </c>
       <c r="D87" t="n">
-        <v>678.88</v>
+        <v>1122</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2098,17 +2098,17 @@
         <v>46217</v>
       </c>
       <c r="B88" t="n">
-        <v>2279</v>
+        <v>1289</v>
       </c>
       <c r="C88" t="n">
         <v>8888</v>
       </c>
       <c r="D88" t="n">
-        <v>1165.17</v>
+        <v>1214.09</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2117,13 +2117,13 @@
         <v>46217</v>
       </c>
       <c r="B89" t="n">
-        <v>451</v>
+        <v>2107</v>
       </c>
       <c r="C89" t="n">
-        <v>3403</v>
+        <v>1954</v>
       </c>
       <c r="D89" t="n">
-        <v>327.28</v>
+        <v>2000.86</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -2136,17 +2136,17 @@
         <v>46217</v>
       </c>
       <c r="B90" t="n">
-        <v>2571</v>
+        <v>1116</v>
       </c>
       <c r="C90" t="n">
-        <v>1312</v>
+        <v>8888</v>
       </c>
       <c r="D90" t="n">
-        <v>2202.75</v>
+        <v>1065.24</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2155,17 +2155,17 @@
         <v>46217</v>
       </c>
       <c r="B91" t="n">
-        <v>2782</v>
+        <v>58</v>
       </c>
       <c r="C91" t="n">
         <v>8888</v>
       </c>
       <c r="D91" t="n">
-        <v>753.8</v>
+        <v>2637.19</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2174,17 +2174,17 @@
         <v>46217</v>
       </c>
       <c r="B92" t="n">
-        <v>610</v>
+        <v>1117</v>
       </c>
       <c r="C92" t="n">
         <v>8888</v>
       </c>
       <c r="D92" t="n">
-        <v>335.61</v>
+        <v>581.51</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2193,13 +2193,13 @@
         <v>46217</v>
       </c>
       <c r="B93" t="n">
-        <v>2245</v>
+        <v>58</v>
       </c>
       <c r="C93" t="n">
         <v>8888</v>
       </c>
       <c r="D93" t="n">
-        <v>355.88</v>
+        <v>1411.43</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -2212,17 +2212,17 @@
         <v>46217</v>
       </c>
       <c r="B94" t="n">
-        <v>1108</v>
+        <v>629</v>
       </c>
       <c r="C94" t="n">
         <v>8888</v>
       </c>
       <c r="D94" t="n">
-        <v>508.54</v>
+        <v>2049.78</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2231,17 +2231,17 @@
         <v>46217</v>
       </c>
       <c r="B95" t="n">
-        <v>341</v>
+        <v>595</v>
       </c>
       <c r="C95" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D95" t="n">
-        <v>366.88</v>
+        <v>3191</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2250,17 +2250,17 @@
         <v>46217</v>
       </c>
       <c r="B96" t="n">
-        <v>1653</v>
+        <v>949</v>
       </c>
       <c r="C96" t="n">
-        <v>8888</v>
+        <v>1762</v>
       </c>
       <c r="D96" t="n">
-        <v>4383.69</v>
+        <v>325.65</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2269,17 +2269,17 @@
         <v>46217</v>
       </c>
       <c r="B97" t="n">
-        <v>619</v>
+        <v>2463</v>
       </c>
       <c r="C97" t="n">
         <v>8888</v>
       </c>
       <c r="D97" t="n">
-        <v>1557.5</v>
+        <v>8336.43</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2288,13 +2288,13 @@
         <v>46217</v>
       </c>
       <c r="B98" t="n">
-        <v>663</v>
+        <v>1064</v>
       </c>
       <c r="C98" t="n">
         <v>8888</v>
       </c>
       <c r="D98" t="n">
-        <v>824.5599999999999</v>
+        <v>1513.21</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -2307,17 +2307,17 @@
         <v>46217</v>
       </c>
       <c r="B99" t="n">
-        <v>429</v>
+        <v>1478</v>
       </c>
       <c r="C99" t="n">
-        <v>2571</v>
+        <v>8888</v>
       </c>
       <c r="D99" t="n">
-        <v>667.12</v>
+        <v>2261.67</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2326,17 +2326,17 @@
         <v>46217</v>
       </c>
       <c r="B100" t="n">
-        <v>2641</v>
+        <v>358</v>
       </c>
       <c r="C100" t="n">
         <v>8888</v>
       </c>
       <c r="D100" t="n">
-        <v>252.41</v>
+        <v>1918.33</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2345,13 +2345,13 @@
         <v>46217</v>
       </c>
       <c r="B101" t="n">
-        <v>1293</v>
+        <v>2107</v>
       </c>
       <c r="C101" t="n">
         <v>8888</v>
       </c>
       <c r="D101" t="n">
-        <v>8102.01</v>
+        <v>2745.11</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -2364,17 +2364,17 @@
         <v>46217</v>
       </c>
       <c r="B102" t="n">
-        <v>1465</v>
+        <v>675</v>
       </c>
       <c r="C102" t="n">
         <v>8888</v>
       </c>
       <c r="D102" t="n">
-        <v>814.65</v>
+        <v>678.88</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2383,13 +2383,13 @@
         <v>46217</v>
       </c>
       <c r="B103" t="n">
-        <v>483</v>
+        <v>2279</v>
       </c>
       <c r="C103" t="n">
         <v>8888</v>
       </c>
       <c r="D103" t="n">
-        <v>1290.28</v>
+        <v>1165.17</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -2402,17 +2402,17 @@
         <v>46217</v>
       </c>
       <c r="B104" t="n">
-        <v>1064</v>
+        <v>451</v>
       </c>
       <c r="C104" t="n">
-        <v>8888</v>
+        <v>3403</v>
       </c>
       <c r="D104" t="n">
-        <v>104632.21</v>
+        <v>327.28</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2421,13 +2421,13 @@
         <v>46217</v>
       </c>
       <c r="B105" t="n">
-        <v>131</v>
+        <v>2571</v>
       </c>
       <c r="C105" t="n">
-        <v>27</v>
+        <v>1312</v>
       </c>
       <c r="D105" t="n">
-        <v>876.48</v>
+        <v>2202.75</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -2440,17 +2440,17 @@
         <v>46217</v>
       </c>
       <c r="B106" t="n">
-        <v>663</v>
+        <v>2782</v>
       </c>
       <c r="C106" t="n">
         <v>8888</v>
       </c>
       <c r="D106" t="n">
-        <v>979.4</v>
+        <v>753.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2459,17 +2459,17 @@
         <v>46217</v>
       </c>
       <c r="B107" t="n">
-        <v>131</v>
+        <v>610</v>
       </c>
       <c r="C107" t="n">
         <v>8888</v>
       </c>
       <c r="D107" t="n">
-        <v>4787.28</v>
+        <v>335.61</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2478,17 +2478,17 @@
         <v>46217</v>
       </c>
       <c r="B108" t="n">
-        <v>2308</v>
+        <v>2245</v>
       </c>
       <c r="C108" t="n">
-        <v>546</v>
+        <v>8888</v>
       </c>
       <c r="D108" t="n">
-        <v>1292.23</v>
+        <v>355.88</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2497,17 +2497,17 @@
         <v>46217</v>
       </c>
       <c r="B109" t="n">
-        <v>2709</v>
+        <v>1108</v>
       </c>
       <c r="C109" t="n">
-        <v>2220</v>
+        <v>8888</v>
       </c>
       <c r="D109" t="n">
-        <v>1663.5</v>
+        <v>508.54</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2516,17 +2516,17 @@
         <v>46217</v>
       </c>
       <c r="B110" t="n">
-        <v>1937</v>
+        <v>341</v>
       </c>
       <c r="C110" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D110" t="n">
-        <v>1492.4</v>
+        <v>366.88</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2535,13 +2535,13 @@
         <v>46217</v>
       </c>
       <c r="B111" t="n">
-        <v>429</v>
+        <v>525</v>
       </c>
       <c r="C111" t="n">
-        <v>1281</v>
+        <v>1087</v>
       </c>
       <c r="D111" t="n">
-        <v>2195.97</v>
+        <v>1830.26</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -2554,17 +2554,17 @@
         <v>46217</v>
       </c>
       <c r="B112" t="n">
-        <v>2211</v>
+        <v>1653</v>
       </c>
       <c r="C112" t="n">
         <v>8888</v>
       </c>
       <c r="D112" t="n">
-        <v>797.61</v>
+        <v>4383.69</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2573,13 +2573,13 @@
         <v>46217</v>
       </c>
       <c r="B113" t="n">
-        <v>360</v>
+        <v>619</v>
       </c>
       <c r="C113" t="n">
         <v>8888</v>
       </c>
       <c r="D113" t="n">
-        <v>13786.36</v>
+        <v>1557.5</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -2592,17 +2592,17 @@
         <v>46217</v>
       </c>
       <c r="B114" t="n">
-        <v>2251</v>
+        <v>1518</v>
       </c>
       <c r="C114" t="n">
-        <v>8888</v>
+        <v>1533</v>
       </c>
       <c r="D114" t="n">
-        <v>797.58</v>
+        <v>479.84</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2611,17 +2611,17 @@
         <v>46217</v>
       </c>
       <c r="B115" t="n">
-        <v>451</v>
+        <v>663</v>
       </c>
       <c r="C115" t="n">
         <v>8888</v>
       </c>
       <c r="D115" t="n">
-        <v>1371.26</v>
+        <v>824.5599999999999</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2630,17 +2630,17 @@
         <v>46217</v>
       </c>
       <c r="B116" t="n">
-        <v>40</v>
+        <v>2089</v>
       </c>
       <c r="C116" t="n">
-        <v>8888</v>
+        <v>1533</v>
       </c>
       <c r="D116" t="n">
-        <v>1093.47</v>
+        <v>822.05</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2649,17 +2649,17 @@
         <v>46217</v>
       </c>
       <c r="B117" t="n">
-        <v>530</v>
+        <v>2133</v>
       </c>
       <c r="C117" t="n">
-        <v>8888</v>
+        <v>691</v>
       </c>
       <c r="D117" t="n">
-        <v>180.08</v>
+        <v>1414.98</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2668,17 +2668,17 @@
         <v>46217</v>
       </c>
       <c r="B118" t="n">
-        <v>1137</v>
+        <v>429</v>
       </c>
       <c r="C118" t="n">
-        <v>8888</v>
+        <v>2571</v>
       </c>
       <c r="D118" t="n">
-        <v>2833.69</v>
+        <v>667.12</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2687,17 +2687,17 @@
         <v>46217</v>
       </c>
       <c r="B119" t="n">
-        <v>1293</v>
+        <v>2641</v>
       </c>
       <c r="C119" t="n">
-        <v>601</v>
+        <v>8888</v>
       </c>
       <c r="D119" t="n">
-        <v>456.47</v>
+        <v>252.41</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2706,17 +2706,17 @@
         <v>46217</v>
       </c>
       <c r="B120" t="n">
-        <v>2118</v>
+        <v>1293</v>
       </c>
       <c r="C120" t="n">
         <v>8888</v>
       </c>
       <c r="D120" t="n">
-        <v>311.54</v>
+        <v>8102.01</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2725,17 +2725,17 @@
         <v>46217</v>
       </c>
       <c r="B121" t="n">
-        <v>424</v>
+        <v>1465</v>
       </c>
       <c r="C121" t="n">
         <v>8888</v>
       </c>
       <c r="D121" t="n">
-        <v>349.68</v>
+        <v>814.65</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2744,17 +2744,17 @@
         <v>46217</v>
       </c>
       <c r="B122" t="n">
-        <v>1299</v>
+        <v>483</v>
       </c>
       <c r="C122" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D122" t="n">
-        <v>3625.32</v>
+        <v>1980.79</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2763,17 +2763,17 @@
         <v>46217</v>
       </c>
       <c r="B123" t="n">
-        <v>559</v>
+        <v>1064</v>
       </c>
       <c r="C123" t="n">
         <v>8888</v>
       </c>
       <c r="D123" t="n">
-        <v>1064.63</v>
+        <v>104632.21</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2782,17 +2782,17 @@
         <v>46217</v>
       </c>
       <c r="B124" t="n">
-        <v>89</v>
+        <v>131</v>
       </c>
       <c r="C124" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D124" t="n">
-        <v>1506.42</v>
+        <v>876.48</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2801,13 +2801,13 @@
         <v>46217</v>
       </c>
       <c r="B125" t="n">
-        <v>2250</v>
+        <v>663</v>
       </c>
       <c r="C125" t="n">
         <v>8888</v>
       </c>
       <c r="D125" t="n">
-        <v>1943.54</v>
+        <v>1769.59</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -2820,17 +2820,17 @@
         <v>46217</v>
       </c>
       <c r="B126" t="n">
-        <v>767</v>
+        <v>131</v>
       </c>
       <c r="C126" t="n">
         <v>8888</v>
       </c>
       <c r="D126" t="n">
-        <v>472.62</v>
+        <v>4787.28</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2839,13 +2839,13 @@
         <v>46217</v>
       </c>
       <c r="B127" t="n">
-        <v>2651</v>
+        <v>2308</v>
       </c>
       <c r="C127" t="n">
-        <v>58</v>
+        <v>546</v>
       </c>
       <c r="D127" t="n">
-        <v>648.71</v>
+        <v>1292.23</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -2858,13 +2858,13 @@
         <v>46217</v>
       </c>
       <c r="B128" t="n">
-        <v>2114</v>
+        <v>2709</v>
       </c>
       <c r="C128" t="n">
-        <v>1954</v>
+        <v>2220</v>
       </c>
       <c r="D128" t="n">
-        <v>879.03</v>
+        <v>1663.5</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -2877,17 +2877,17 @@
         <v>46217</v>
       </c>
       <c r="B129" t="n">
-        <v>40</v>
+        <v>1937</v>
       </c>
       <c r="C129" t="n">
         <v>8888</v>
       </c>
       <c r="D129" t="n">
-        <v>3583.39</v>
+        <v>1492.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2896,17 +2896,17 @@
         <v>46217</v>
       </c>
       <c r="B130" t="n">
-        <v>40</v>
+        <v>429</v>
       </c>
       <c r="C130" t="n">
-        <v>8888</v>
+        <v>1281</v>
       </c>
       <c r="D130" t="n">
-        <v>2529.31</v>
+        <v>2195.97</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2915,17 +2915,17 @@
         <v>46217</v>
       </c>
       <c r="B131" t="n">
-        <v>626</v>
+        <v>2211</v>
       </c>
       <c r="C131" t="n">
         <v>8888</v>
       </c>
       <c r="D131" t="n">
-        <v>13218.02</v>
+        <v>1563.28</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2934,17 +2934,17 @@
         <v>46217</v>
       </c>
       <c r="B132" t="n">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C132" t="n">
         <v>8888</v>
       </c>
       <c r="D132" t="n">
-        <v>739.17</v>
+        <v>15052.63</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2953,17 +2953,17 @@
         <v>46217</v>
       </c>
       <c r="B133" t="n">
-        <v>675</v>
+        <v>2251</v>
       </c>
       <c r="C133" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D133" t="n">
-        <v>107.13</v>
+        <v>797.58</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2972,13 +2972,13 @@
         <v>46217</v>
       </c>
       <c r="B134" t="n">
-        <v>636</v>
+        <v>451</v>
       </c>
       <c r="C134" t="n">
         <v>8888</v>
       </c>
       <c r="D134" t="n">
-        <v>5631.89</v>
+        <v>1371.26</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -2991,17 +2991,17 @@
         <v>46217</v>
       </c>
       <c r="B135" t="n">
-        <v>1075</v>
+        <v>40</v>
       </c>
       <c r="C135" t="n">
         <v>8888</v>
       </c>
       <c r="D135" t="n">
-        <v>1331.89</v>
+        <v>1093.47</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3010,13 +3010,13 @@
         <v>46217</v>
       </c>
       <c r="B136" t="n">
-        <v>2245</v>
+        <v>530</v>
       </c>
       <c r="C136" t="n">
         <v>8888</v>
       </c>
       <c r="D136" t="n">
-        <v>883.75</v>
+        <v>180.08</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -3029,17 +3029,17 @@
         <v>46217</v>
       </c>
       <c r="B137" t="n">
-        <v>477</v>
+        <v>1137</v>
       </c>
       <c r="C137" t="n">
         <v>8888</v>
       </c>
       <c r="D137" t="n">
-        <v>994.15</v>
+        <v>3528.55</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3048,17 +3048,17 @@
         <v>46217</v>
       </c>
       <c r="B138" t="n">
-        <v>2015</v>
+        <v>1293</v>
       </c>
       <c r="C138" t="n">
-        <v>8888</v>
+        <v>601</v>
       </c>
       <c r="D138" t="n">
-        <v>2931.07</v>
+        <v>456.47</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3067,17 +3067,17 @@
         <v>46217</v>
       </c>
       <c r="B139" t="n">
-        <v>1653</v>
+        <v>2118</v>
       </c>
       <c r="C139" t="n">
         <v>8888</v>
       </c>
       <c r="D139" t="n">
-        <v>4115.53</v>
+        <v>311.54</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3086,17 +3086,17 @@
         <v>46217</v>
       </c>
       <c r="B140" t="n">
-        <v>1064</v>
+        <v>424</v>
       </c>
       <c r="C140" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D140" t="n">
-        <v>1052.68</v>
+        <v>349.68</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3105,17 +3105,17 @@
         <v>46217</v>
       </c>
       <c r="B141" t="n">
-        <v>1983</v>
+        <v>1299</v>
       </c>
       <c r="C141" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D141" t="n">
-        <v>1246.33</v>
+        <v>3625.32</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3124,17 +3124,17 @@
         <v>46217</v>
       </c>
       <c r="B142" t="n">
-        <v>2118</v>
+        <v>559</v>
       </c>
       <c r="C142" t="n">
         <v>8888</v>
       </c>
       <c r="D142" t="n">
-        <v>4886.49</v>
+        <v>1064.63</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3143,17 +3143,17 @@
         <v>46217</v>
       </c>
       <c r="B143" t="n">
-        <v>2680</v>
+        <v>89</v>
       </c>
       <c r="C143" t="n">
         <v>8888</v>
       </c>
       <c r="D143" t="n">
-        <v>2285.31</v>
+        <v>1506.42</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3162,17 +3162,17 @@
         <v>46217</v>
       </c>
       <c r="B144" t="n">
-        <v>2637</v>
+        <v>2250</v>
       </c>
       <c r="C144" t="n">
         <v>8888</v>
       </c>
       <c r="D144" t="n">
-        <v>1302.18</v>
+        <v>1943.54</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3181,13 +3181,13 @@
         <v>46217</v>
       </c>
       <c r="B145" t="n">
-        <v>1632</v>
+        <v>767</v>
       </c>
       <c r="C145" t="n">
         <v>8888</v>
       </c>
       <c r="D145" t="n">
-        <v>689.76</v>
+        <v>472.62</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         <v>46217</v>
       </c>
       <c r="B146" t="n">
-        <v>1299</v>
+        <v>2651</v>
       </c>
       <c r="C146" t="n">
-        <v>2522</v>
+        <v>58</v>
       </c>
       <c r="D146" t="n">
-        <v>3319.01</v>
+        <v>648.71</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -3219,17 +3219,17 @@
         <v>46217</v>
       </c>
       <c r="B147" t="n">
-        <v>2026</v>
+        <v>2114</v>
       </c>
       <c r="C147" t="n">
-        <v>8888</v>
+        <v>1954</v>
       </c>
       <c r="D147" t="n">
-        <v>699.05</v>
+        <v>879.03</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3238,13 +3238,13 @@
         <v>46217</v>
       </c>
       <c r="B148" t="n">
-        <v>664</v>
+        <v>40</v>
       </c>
       <c r="C148" t="n">
         <v>8888</v>
       </c>
       <c r="D148" t="n">
-        <v>440.92</v>
+        <v>3583.39</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -3257,17 +3257,17 @@
         <v>46217</v>
       </c>
       <c r="B149" t="n">
-        <v>629</v>
+        <v>40</v>
       </c>
       <c r="C149" t="n">
-        <v>675</v>
+        <v>8888</v>
       </c>
       <c r="D149" t="n">
-        <v>267.79</v>
+        <v>2529.31</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3276,17 +3276,17 @@
         <v>46217</v>
       </c>
       <c r="B150" t="n">
-        <v>559</v>
+        <v>626</v>
       </c>
       <c r="C150" t="n">
         <v>8888</v>
       </c>
       <c r="D150" t="n">
-        <v>1562.5</v>
+        <v>18654.36</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3295,17 +3295,17 @@
         <v>46217</v>
       </c>
       <c r="B151" t="n">
-        <v>1465</v>
+        <v>363</v>
       </c>
       <c r="C151" t="n">
         <v>8888</v>
       </c>
       <c r="D151" t="n">
-        <v>10920.6</v>
+        <v>739.17</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3314,17 +3314,17 @@
         <v>46217</v>
       </c>
       <c r="B152" t="n">
-        <v>2550</v>
+        <v>675</v>
       </c>
       <c r="C152" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D152" t="n">
-        <v>321.05</v>
+        <v>107.13</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3333,17 +3333,17 @@
         <v>46217</v>
       </c>
       <c r="B153" t="n">
-        <v>1756</v>
+        <v>636</v>
       </c>
       <c r="C153" t="n">
         <v>8888</v>
       </c>
       <c r="D153" t="n">
-        <v>2445</v>
+        <v>7476.56</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
         <v>46217</v>
       </c>
       <c r="B154" t="n">
-        <v>363</v>
+        <v>1075</v>
       </c>
       <c r="C154" t="n">
         <v>8888</v>
       </c>
       <c r="D154" t="n">
-        <v>2517.01</v>
+        <v>1331.89</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3371,17 +3371,17 @@
         <v>46217</v>
       </c>
       <c r="B155" t="n">
-        <v>2698</v>
+        <v>2245</v>
       </c>
       <c r="C155" t="n">
-        <v>874</v>
+        <v>8888</v>
       </c>
       <c r="D155" t="n">
-        <v>1183.42</v>
+        <v>883.75</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3390,17 +3390,17 @@
         <v>46217</v>
       </c>
       <c r="B156" t="n">
-        <v>535</v>
+        <v>477</v>
       </c>
       <c r="C156" t="n">
         <v>8888</v>
       </c>
       <c r="D156" t="n">
-        <v>5293.96</v>
+        <v>994.15</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3409,13 +3409,13 @@
         <v>46217</v>
       </c>
       <c r="B157" t="n">
-        <v>2250</v>
+        <v>2015</v>
       </c>
       <c r="C157" t="n">
         <v>8888</v>
       </c>
       <c r="D157" t="n">
-        <v>2650.33</v>
+        <v>3243.05</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -3428,17 +3428,17 @@
         <v>46217</v>
       </c>
       <c r="B158" t="n">
-        <v>2681</v>
+        <v>1996</v>
       </c>
       <c r="C158" t="n">
-        <v>8888</v>
+        <v>691</v>
       </c>
       <c r="D158" t="n">
-        <v>2775.8</v>
+        <v>500.79</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3447,17 +3447,17 @@
         <v>46217</v>
       </c>
       <c r="B159" t="n">
-        <v>363</v>
+        <v>1653</v>
       </c>
       <c r="C159" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D159" t="n">
-        <v>3635.16</v>
+        <v>4115.53</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3466,17 +3466,17 @@
         <v>46217</v>
       </c>
       <c r="B160" t="n">
-        <v>483</v>
+        <v>1064</v>
       </c>
       <c r="C160" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D160" t="n">
-        <v>2527.71</v>
+        <v>1052.68</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3485,17 +3485,17 @@
         <v>46217</v>
       </c>
       <c r="B161" t="n">
-        <v>2607</v>
+        <v>1983</v>
       </c>
       <c r="C161" t="n">
         <v>8888</v>
       </c>
       <c r="D161" t="n">
-        <v>1075.36</v>
+        <v>1246.33</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3504,17 +3504,17 @@
         <v>46217</v>
       </c>
       <c r="B162" t="n">
-        <v>2330</v>
+        <v>2118</v>
       </c>
       <c r="C162" t="n">
-        <v>1954</v>
+        <v>8888</v>
       </c>
       <c r="D162" t="n">
-        <v>1923.09</v>
+        <v>4886.49</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3523,13 +3523,13 @@
         <v>46217</v>
       </c>
       <c r="B163" t="n">
-        <v>2709</v>
+        <v>2680</v>
       </c>
       <c r="C163" t="n">
         <v>8888</v>
       </c>
       <c r="D163" t="n">
-        <v>1667.47</v>
+        <v>2285.31</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -3542,17 +3542,17 @@
         <v>46217</v>
       </c>
       <c r="B164" t="n">
-        <v>374</v>
+        <v>2637</v>
       </c>
       <c r="C164" t="n">
         <v>8888</v>
       </c>
       <c r="D164" t="n">
-        <v>1150.97</v>
+        <v>1302.18</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3561,13 +3561,13 @@
         <v>46217</v>
       </c>
       <c r="B165" t="n">
-        <v>1137</v>
+        <v>1632</v>
       </c>
       <c r="C165" t="n">
         <v>8888</v>
       </c>
       <c r="D165" t="n">
-        <v>4413.34</v>
+        <v>689.76</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -3580,15 +3580,509 @@
         <v>46217</v>
       </c>
       <c r="B166" t="n">
+        <v>1299</v>
+      </c>
+      <c r="C166" t="n">
+        <v>2522</v>
+      </c>
+      <c r="D166" t="n">
+        <v>3319.01</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B167" t="n">
+        <v>2727</v>
+      </c>
+      <c r="C167" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D167" t="n">
+        <v>548.33</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B168" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C168" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D168" t="n">
+        <v>699.05</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B169" t="n">
+        <v>664</v>
+      </c>
+      <c r="C169" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D169" t="n">
+        <v>440.92</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B170" t="n">
+        <v>629</v>
+      </c>
+      <c r="C170" t="n">
+        <v>675</v>
+      </c>
+      <c r="D170" t="n">
+        <v>267.79</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B171" t="n">
+        <v>559</v>
+      </c>
+      <c r="C171" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D171" t="n">
+        <v>1562.5</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B172" t="n">
+        <v>1465</v>
+      </c>
+      <c r="C172" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D172" t="n">
+        <v>10920.6</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B173" t="n">
+        <v>2550</v>
+      </c>
+      <c r="C173" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D173" t="n">
+        <v>321.05</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B174" t="n">
+        <v>1756</v>
+      </c>
+      <c r="C174" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D174" t="n">
+        <v>2445</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B175" t="n">
+        <v>890</v>
+      </c>
+      <c r="C175" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D175" t="n">
+        <v>4287.14</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B176" t="n">
+        <v>363</v>
+      </c>
+      <c r="C176" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D176" t="n">
+        <v>2517.01</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B177" t="n">
+        <v>2698</v>
+      </c>
+      <c r="C177" t="n">
+        <v>874</v>
+      </c>
+      <c r="D177" t="n">
+        <v>1183.42</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B178" t="n">
+        <v>535</v>
+      </c>
+      <c r="C178" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D178" t="n">
+        <v>5293.96</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B179" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C179" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D179" t="n">
+        <v>2650.33</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B180" t="n">
+        <v>2681</v>
+      </c>
+      <c r="C180" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D180" t="n">
+        <v>2853.99</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B181" t="n">
+        <v>132</v>
+      </c>
+      <c r="C181" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D181" t="n">
+        <v>2623.22</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B182" t="n">
+        <v>2442</v>
+      </c>
+      <c r="C182" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D182" t="n">
+        <v>2822.22</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B183" t="n">
+        <v>363</v>
+      </c>
+      <c r="C183" t="n">
+        <v>1898</v>
+      </c>
+      <c r="D183" t="n">
+        <v>3635.16</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B184" t="n">
+        <v>483</v>
+      </c>
+      <c r="C184" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D184" t="n">
+        <v>2527.71</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B185" t="n">
+        <v>2607</v>
+      </c>
+      <c r="C185" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D185" t="n">
+        <v>1075.36</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B186" t="n">
+        <v>2330</v>
+      </c>
+      <c r="C186" t="n">
+        <v>1954</v>
+      </c>
+      <c r="D186" t="n">
+        <v>1923.09</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B187" t="n">
+        <v>2472</v>
+      </c>
+      <c r="C187" t="n">
+        <v>2853</v>
+      </c>
+      <c r="D187" t="n">
+        <v>824.0599999999999</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B188" t="n">
+        <v>1384</v>
+      </c>
+      <c r="C188" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D188" t="n">
+        <v>585.27</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B189" t="n">
+        <v>2709</v>
+      </c>
+      <c r="C189" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D189" t="n">
+        <v>1667.47</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B190" t="n">
+        <v>374</v>
+      </c>
+      <c r="C190" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D190" t="n">
+        <v>1150.97</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B191" t="n">
+        <v>1137</v>
+      </c>
+      <c r="C191" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D191" t="n">
+        <v>4413.34</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B192" t="n">
         <v>2251</v>
       </c>
-      <c r="C166" t="n">
+      <c r="C192" t="n">
         <v>3403</v>
       </c>
-      <c r="D166" t="n">
+      <c r="D192" t="n">
         <v>510.18</v>
       </c>
-      <c r="E166" t="inlineStr">
+      <c r="E192" t="inlineStr">
         <is>
           <t>TELEMARKETING</t>
         </is>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E192"/>
+  <dimension ref="A1:E245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,7 +489,7 @@
         <v>27</v>
       </c>
       <c r="D3" t="n">
-        <v>556.23</v>
+        <v>2389.55</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
         <v>8888</v>
       </c>
       <c r="D6" t="n">
-        <v>6359.39</v>
+        <v>13194.04</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -597,17 +597,17 @@
         <v>46217</v>
       </c>
       <c r="B9" t="n">
-        <v>2109</v>
+        <v>1064</v>
       </c>
       <c r="C9" t="n">
         <v>8888</v>
       </c>
       <c r="D9" t="n">
-        <v>4813.6</v>
+        <v>823.42</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -616,17 +616,17 @@
         <v>46217</v>
       </c>
       <c r="B10" t="n">
-        <v>2015</v>
+        <v>1381</v>
       </c>
       <c r="C10" t="n">
-        <v>2571</v>
+        <v>8888</v>
       </c>
       <c r="D10" t="n">
-        <v>2593.26</v>
+        <v>2196.92</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -635,17 +635,17 @@
         <v>46217</v>
       </c>
       <c r="B11" t="n">
-        <v>1993</v>
+        <v>703</v>
       </c>
       <c r="C11" t="n">
         <v>8888</v>
       </c>
       <c r="D11" t="n">
-        <v>1785.44</v>
+        <v>11161.25</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -654,13 +654,13 @@
         <v>46217</v>
       </c>
       <c r="B12" t="n">
-        <v>1102</v>
+        <v>2109</v>
       </c>
       <c r="C12" t="n">
         <v>8888</v>
       </c>
       <c r="D12" t="n">
-        <v>3129.4</v>
+        <v>4813.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -673,13 +673,13 @@
         <v>46217</v>
       </c>
       <c r="B13" t="n">
-        <v>1293</v>
+        <v>2015</v>
       </c>
       <c r="C13" t="n">
-        <v>1281</v>
+        <v>2571</v>
       </c>
       <c r="D13" t="n">
-        <v>1337.87</v>
+        <v>2593.26</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -692,17 +692,17 @@
         <v>46217</v>
       </c>
       <c r="B14" t="n">
-        <v>2657</v>
+        <v>1993</v>
       </c>
       <c r="C14" t="n">
         <v>8888</v>
       </c>
       <c r="D14" t="n">
-        <v>877.0700000000001</v>
+        <v>1785.44</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -711,13 +711,13 @@
         <v>46217</v>
       </c>
       <c r="B15" t="n">
-        <v>2768</v>
+        <v>1102</v>
       </c>
       <c r="C15" t="n">
         <v>8888</v>
       </c>
       <c r="D15" t="n">
-        <v>4890.12</v>
+        <v>3406.59</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
         <v>46217</v>
       </c>
       <c r="B16" t="n">
-        <v>2686</v>
+        <v>1937</v>
       </c>
       <c r="C16" t="n">
         <v>8888</v>
       </c>
       <c r="D16" t="n">
-        <v>422.71</v>
+        <v>3337.21</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -749,13 +749,13 @@
         <v>46217</v>
       </c>
       <c r="B17" t="n">
-        <v>1890</v>
+        <v>1293</v>
       </c>
       <c r="C17" t="n">
-        <v>3449</v>
+        <v>1281</v>
       </c>
       <c r="D17" t="n">
-        <v>809.78</v>
+        <v>1337.87</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -768,17 +768,17 @@
         <v>46217</v>
       </c>
       <c r="B18" t="n">
-        <v>2726</v>
+        <v>2657</v>
       </c>
       <c r="C18" t="n">
-        <v>1929</v>
+        <v>8888</v>
       </c>
       <c r="D18" t="n">
-        <v>640.1799999999999</v>
+        <v>877.0700000000001</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -787,13 +787,13 @@
         <v>46217</v>
       </c>
       <c r="B19" t="n">
-        <v>89</v>
+        <v>2768</v>
       </c>
       <c r="C19" t="n">
         <v>8888</v>
       </c>
       <c r="D19" t="n">
-        <v>5652.15</v>
+        <v>4890.12</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -806,17 +806,17 @@
         <v>46217</v>
       </c>
       <c r="B20" t="n">
-        <v>2641</v>
+        <v>2686</v>
       </c>
       <c r="C20" t="n">
         <v>8888</v>
       </c>
       <c r="D20" t="n">
-        <v>607.79</v>
+        <v>422.71</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -825,13 +825,13 @@
         <v>46217</v>
       </c>
       <c r="B21" t="n">
-        <v>949</v>
+        <v>1890</v>
       </c>
       <c r="C21" t="n">
-        <v>1258</v>
+        <v>3449</v>
       </c>
       <c r="D21" t="n">
-        <v>196.87</v>
+        <v>1575.78</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -844,17 +844,17 @@
         <v>46217</v>
       </c>
       <c r="B22" t="n">
-        <v>353</v>
+        <v>33</v>
       </c>
       <c r="C22" t="n">
         <v>8888</v>
       </c>
       <c r="D22" t="n">
-        <v>2121.12</v>
+        <v>1041.47</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -863,17 +863,17 @@
         <v>46217</v>
       </c>
       <c r="B23" t="n">
-        <v>1756</v>
+        <v>2726</v>
       </c>
       <c r="C23" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D23" t="n">
-        <v>1799.7</v>
+        <v>640.1799999999999</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
         <v>46217</v>
       </c>
       <c r="B24" t="n">
-        <v>285</v>
+        <v>89</v>
       </c>
       <c r="C24" t="n">
         <v>8888</v>
       </c>
       <c r="D24" t="n">
-        <v>3092.58</v>
+        <v>5652.15</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
         <v>46217</v>
       </c>
       <c r="B25" t="n">
-        <v>1906</v>
+        <v>2178</v>
       </c>
       <c r="C25" t="n">
-        <v>8888</v>
+        <v>738</v>
       </c>
       <c r="D25" t="n">
-        <v>3142.54</v>
+        <v>291.83</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -920,17 +920,17 @@
         <v>46217</v>
       </c>
       <c r="B26" t="n">
-        <v>1308</v>
+        <v>2209</v>
       </c>
       <c r="C26" t="n">
-        <v>8888</v>
+        <v>738</v>
       </c>
       <c r="D26" t="n">
-        <v>3127.35</v>
+        <v>2043.28</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -939,17 +939,17 @@
         <v>46217</v>
       </c>
       <c r="B27" t="n">
-        <v>610</v>
+        <v>429</v>
       </c>
       <c r="C27" t="n">
         <v>8888</v>
       </c>
       <c r="D27" t="n">
-        <v>590.08</v>
+        <v>3775.81</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -958,13 +958,13 @@
         <v>46217</v>
       </c>
       <c r="B28" t="n">
-        <v>619</v>
+        <v>2641</v>
       </c>
       <c r="C28" t="n">
         <v>8888</v>
       </c>
       <c r="D28" t="n">
-        <v>236.34</v>
+        <v>607.79</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -977,13 +977,13 @@
         <v>46217</v>
       </c>
       <c r="B29" t="n">
-        <v>2755</v>
+        <v>949</v>
       </c>
       <c r="C29" t="n">
-        <v>2220</v>
+        <v>1258</v>
       </c>
       <c r="D29" t="n">
-        <v>1133.17</v>
+        <v>196.87</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -996,17 +996,17 @@
         <v>46217</v>
       </c>
       <c r="B30" t="n">
-        <v>2767</v>
+        <v>353</v>
       </c>
       <c r="C30" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D30" t="n">
-        <v>5000.2</v>
+        <v>2121.12</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1015,17 +1015,17 @@
         <v>46217</v>
       </c>
       <c r="B31" t="n">
-        <v>559</v>
+        <v>1756</v>
       </c>
       <c r="C31" t="n">
         <v>8888</v>
       </c>
       <c r="D31" t="n">
-        <v>1200.99</v>
+        <v>1799.7</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
         <v>46217</v>
       </c>
       <c r="B32" t="n">
-        <v>358</v>
+        <v>285</v>
       </c>
       <c r="C32" t="n">
         <v>8888</v>
       </c>
       <c r="D32" t="n">
-        <v>1301.77</v>
+        <v>3937.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1053,13 +1053,13 @@
         <v>46217</v>
       </c>
       <c r="B33" t="n">
-        <v>609</v>
+        <v>1906</v>
       </c>
       <c r="C33" t="n">
         <v>8888</v>
       </c>
       <c r="D33" t="n">
-        <v>962.08</v>
+        <v>3142.54</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1072,17 +1072,17 @@
         <v>46217</v>
       </c>
       <c r="B34" t="n">
-        <v>2507</v>
+        <v>1308</v>
       </c>
       <c r="C34" t="n">
         <v>8888</v>
       </c>
       <c r="D34" t="n">
-        <v>448.36</v>
+        <v>3127.35</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1091,13 +1091,13 @@
         <v>46217</v>
       </c>
       <c r="B35" t="n">
-        <v>2767</v>
+        <v>610</v>
       </c>
       <c r="C35" t="n">
         <v>8888</v>
       </c>
       <c r="D35" t="n">
-        <v>1175.73</v>
+        <v>590.08</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1110,17 +1110,17 @@
         <v>46217</v>
       </c>
       <c r="B36" t="n">
-        <v>1063</v>
+        <v>619</v>
       </c>
       <c r="C36" t="n">
         <v>8888</v>
       </c>
       <c r="D36" t="n">
-        <v>1251.14</v>
+        <v>236.34</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1129,17 +1129,17 @@
         <v>46217</v>
       </c>
       <c r="B37" t="n">
-        <v>325</v>
+        <v>1324</v>
       </c>
       <c r="C37" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D37" t="n">
-        <v>868.83</v>
+        <v>2603.19</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1148,17 +1148,17 @@
         <v>46217</v>
       </c>
       <c r="B38" t="n">
-        <v>2660</v>
+        <v>483</v>
       </c>
       <c r="C38" t="n">
         <v>8888</v>
       </c>
       <c r="D38" t="n">
-        <v>281.24</v>
+        <v>461.28</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1167,17 +1167,17 @@
         <v>46217</v>
       </c>
       <c r="B39" t="n">
-        <v>610</v>
+        <v>1117</v>
       </c>
       <c r="C39" t="n">
         <v>8888</v>
       </c>
       <c r="D39" t="n">
-        <v>235.34</v>
+        <v>755.71</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1186,17 +1186,17 @@
         <v>46217</v>
       </c>
       <c r="B40" t="n">
-        <v>424</v>
+        <v>2755</v>
       </c>
       <c r="C40" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D40" t="n">
-        <v>3214.29</v>
+        <v>1133.17</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1205,13 +1205,13 @@
         <v>46217</v>
       </c>
       <c r="B41" t="n">
-        <v>40</v>
+        <v>2767</v>
       </c>
       <c r="C41" t="n">
-        <v>58</v>
+        <v>1898</v>
       </c>
       <c r="D41" t="n">
-        <v>325.04</v>
+        <v>5000.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1224,13 +1224,13 @@
         <v>46217</v>
       </c>
       <c r="B42" t="n">
-        <v>1117</v>
+        <v>559</v>
       </c>
       <c r="C42" t="n">
         <v>8888</v>
       </c>
       <c r="D42" t="n">
-        <v>349.47</v>
+        <v>1516.25</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1243,17 +1243,17 @@
         <v>46217</v>
       </c>
       <c r="B43" t="n">
-        <v>949</v>
+        <v>1277</v>
       </c>
       <c r="C43" t="n">
-        <v>998</v>
+        <v>8888</v>
       </c>
       <c r="D43" t="n">
-        <v>129.85</v>
+        <v>574.7</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1262,13 +1262,13 @@
         <v>46217</v>
       </c>
       <c r="B44" t="n">
-        <v>1853</v>
+        <v>358</v>
       </c>
       <c r="C44" t="n">
         <v>8888</v>
       </c>
       <c r="D44" t="n">
-        <v>522.4</v>
+        <v>1301.77</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1281,17 +1281,17 @@
         <v>46217</v>
       </c>
       <c r="B45" t="n">
-        <v>2250</v>
+        <v>1993</v>
       </c>
       <c r="C45" t="n">
         <v>8888</v>
       </c>
       <c r="D45" t="n">
-        <v>4131.57</v>
+        <v>5280</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1300,13 +1300,13 @@
         <v>46217</v>
       </c>
       <c r="B46" t="n">
-        <v>2507</v>
+        <v>609</v>
       </c>
       <c r="C46" t="n">
         <v>8888</v>
       </c>
       <c r="D46" t="n">
-        <v>4167.12</v>
+        <v>962.08</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1319,17 +1319,17 @@
         <v>46217</v>
       </c>
       <c r="B47" t="n">
-        <v>664</v>
+        <v>2507</v>
       </c>
       <c r="C47" t="n">
         <v>8888</v>
       </c>
       <c r="D47" t="n">
-        <v>3815.91</v>
+        <v>448.36</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1338,17 @@
         <v>46217</v>
       </c>
       <c r="B48" t="n">
-        <v>1075</v>
+        <v>2767</v>
       </c>
       <c r="C48" t="n">
         <v>8888</v>
       </c>
       <c r="D48" t="n">
-        <v>1013.2</v>
+        <v>1175.73</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1357,17 +1357,17 @@
         <v>46217</v>
       </c>
       <c r="B49" t="n">
-        <v>1906</v>
+        <v>1063</v>
       </c>
       <c r="C49" t="n">
-        <v>1954</v>
+        <v>8888</v>
       </c>
       <c r="D49" t="n">
-        <v>1445.21</v>
+        <v>1251.14</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1376,13 +1376,13 @@
         <v>46217</v>
       </c>
       <c r="B50" t="n">
-        <v>595</v>
+        <v>325</v>
       </c>
       <c r="C50" t="n">
-        <v>691</v>
+        <v>58</v>
       </c>
       <c r="D50" t="n">
-        <v>314.52</v>
+        <v>868.83</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1395,17 +1395,17 @@
         <v>46217</v>
       </c>
       <c r="B51" t="n">
-        <v>2696</v>
+        <v>2660</v>
       </c>
       <c r="C51" t="n">
-        <v>1312</v>
+        <v>8888</v>
       </c>
       <c r="D51" t="n">
-        <v>677.76</v>
+        <v>281.24</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1414,17 +1414,17 @@
         <v>46217</v>
       </c>
       <c r="B52" t="n">
-        <v>525</v>
+        <v>610</v>
       </c>
       <c r="C52" t="n">
         <v>8888</v>
       </c>
       <c r="D52" t="n">
-        <v>490.08</v>
+        <v>235.34</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1433,17 +1433,17 @@
         <v>46217</v>
       </c>
       <c r="B53" t="n">
-        <v>2491</v>
+        <v>424</v>
       </c>
       <c r="C53" t="n">
         <v>8888</v>
       </c>
       <c r="D53" t="n">
-        <v>2909.58</v>
+        <v>3214.29</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1452,17 +1452,17 @@
         <v>46217</v>
       </c>
       <c r="B54" t="n">
-        <v>360</v>
+        <v>664</v>
       </c>
       <c r="C54" t="n">
-        <v>546</v>
+        <v>8888</v>
       </c>
       <c r="D54" t="n">
-        <v>6094.25</v>
+        <v>364.07</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1471,17 +1471,17 @@
         <v>46217</v>
       </c>
       <c r="B55" t="n">
-        <v>2651</v>
+        <v>2279</v>
       </c>
       <c r="C55" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D55" t="n">
-        <v>638.64</v>
+        <v>448.78</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1490,17 +1490,17 @@
         <v>46217</v>
       </c>
       <c r="B56" t="n">
-        <v>2695</v>
+        <v>40</v>
       </c>
       <c r="C56" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D56" t="n">
-        <v>532.53</v>
+        <v>325.04</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1509,17 +1509,17 @@
         <v>46217</v>
       </c>
       <c r="B57" t="n">
-        <v>1293</v>
+        <v>2069</v>
       </c>
       <c r="C57" t="n">
         <v>8888</v>
       </c>
       <c r="D57" t="n">
-        <v>381.82</v>
+        <v>176.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1528,17 +1528,17 @@
         <v>46217</v>
       </c>
       <c r="B58" t="n">
-        <v>2663</v>
+        <v>522</v>
       </c>
       <c r="C58" t="n">
         <v>8888</v>
       </c>
       <c r="D58" t="n">
-        <v>2146.08</v>
+        <v>151.86</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1547,17 +1547,17 @@
         <v>46217</v>
       </c>
       <c r="B59" t="n">
-        <v>525</v>
+        <v>1304</v>
       </c>
       <c r="C59" t="n">
-        <v>8888</v>
+        <v>213</v>
       </c>
       <c r="D59" t="n">
-        <v>1240.79</v>
+        <v>297.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1566,13 +1566,13 @@
         <v>46217</v>
       </c>
       <c r="B60" t="n">
-        <v>2711</v>
+        <v>1869</v>
       </c>
       <c r="C60" t="n">
         <v>8888</v>
       </c>
       <c r="D60" t="n">
-        <v>2193.56</v>
+        <v>447.76</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -1585,17 +1585,17 @@
         <v>46217</v>
       </c>
       <c r="B61" t="n">
-        <v>1317</v>
+        <v>949</v>
       </c>
       <c r="C61" t="n">
-        <v>8888</v>
+        <v>998</v>
       </c>
       <c r="D61" t="n">
-        <v>787.51</v>
+        <v>129.85</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1604,17 +1604,17 @@
         <v>46217</v>
       </c>
       <c r="B62" t="n">
-        <v>675</v>
+        <v>1853</v>
       </c>
       <c r="C62" t="n">
         <v>8888</v>
       </c>
       <c r="D62" t="n">
-        <v>289.67</v>
+        <v>522.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
         <v>46217</v>
       </c>
       <c r="B63" t="n">
-        <v>1063</v>
+        <v>2250</v>
       </c>
       <c r="C63" t="n">
         <v>8888</v>
       </c>
       <c r="D63" t="n">
-        <v>1902.46</v>
+        <v>4131.57</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1642,13 +1642,13 @@
         <v>46217</v>
       </c>
       <c r="B64" t="n">
-        <v>1658</v>
+        <v>2507</v>
       </c>
       <c r="C64" t="n">
         <v>8888</v>
       </c>
       <c r="D64" t="n">
-        <v>1357.94</v>
+        <v>4167.12</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -1661,17 +1661,17 @@
         <v>46217</v>
       </c>
       <c r="B65" t="n">
-        <v>1392</v>
+        <v>664</v>
       </c>
       <c r="C65" t="n">
         <v>8888</v>
       </c>
       <c r="D65" t="n">
-        <v>814.61</v>
+        <v>4099.16</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1680,17 +1680,17 @@
         <v>46217</v>
       </c>
       <c r="B66" t="n">
-        <v>360</v>
+        <v>1075</v>
       </c>
       <c r="C66" t="n">
         <v>8888</v>
       </c>
       <c r="D66" t="n">
-        <v>749.13</v>
+        <v>1743.47</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1699,13 +1699,13 @@
         <v>46217</v>
       </c>
       <c r="B67" t="n">
-        <v>949</v>
+        <v>1324</v>
       </c>
       <c r="C67" t="n">
-        <v>1134</v>
+        <v>738</v>
       </c>
       <c r="D67" t="n">
-        <v>327.6</v>
+        <v>4548.42</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -1718,17 +1718,17 @@
         <v>46217</v>
       </c>
       <c r="B68" t="n">
-        <v>2133</v>
+        <v>1906</v>
       </c>
       <c r="C68" t="n">
-        <v>8888</v>
+        <v>1954</v>
       </c>
       <c r="D68" t="n">
-        <v>66030.34</v>
+        <v>1445.21</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1737,17 +1737,17 @@
         <v>46217</v>
       </c>
       <c r="B69" t="n">
-        <v>326</v>
+        <v>595</v>
       </c>
       <c r="C69" t="n">
-        <v>8888</v>
+        <v>691</v>
       </c>
       <c r="D69" t="n">
-        <v>360.45</v>
+        <v>314.52</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1756,17 +1756,17 @@
         <v>46217</v>
       </c>
       <c r="B70" t="n">
-        <v>325</v>
+        <v>2696</v>
       </c>
       <c r="C70" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D70" t="n">
-        <v>774.73</v>
+        <v>677.76</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1775,17 +1775,17 @@
         <v>46217</v>
       </c>
       <c r="B71" t="n">
-        <v>1293</v>
+        <v>525</v>
       </c>
       <c r="C71" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D71" t="n">
-        <v>8365.559999999999</v>
+        <v>490.08</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1794,17 +1794,17 @@
         <v>46217</v>
       </c>
       <c r="B72" t="n">
-        <v>131</v>
+        <v>2491</v>
       </c>
       <c r="C72" t="n">
         <v>8888</v>
       </c>
       <c r="D72" t="n">
-        <v>1969.93</v>
+        <v>2909.58</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1813,17 +1813,17 @@
         <v>46217</v>
       </c>
       <c r="B73" t="n">
-        <v>2697</v>
+        <v>360</v>
       </c>
       <c r="C73" t="n">
-        <v>8888</v>
+        <v>546</v>
       </c>
       <c r="D73" t="n">
-        <v>420.48</v>
+        <v>7463.12</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1832,17 +1832,17 @@
         <v>46217</v>
       </c>
       <c r="B74" t="n">
-        <v>2279</v>
+        <v>2651</v>
       </c>
       <c r="C74" t="n">
         <v>8888</v>
       </c>
       <c r="D74" t="n">
-        <v>1034.25</v>
+        <v>638.64</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1851,17 +1851,17 @@
         <v>46217</v>
       </c>
       <c r="B75" t="n">
-        <v>1116</v>
+        <v>525</v>
       </c>
       <c r="C75" t="n">
         <v>8888</v>
       </c>
       <c r="D75" t="n">
-        <v>1293.89</v>
+        <v>4351.19</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1870,13 +1870,13 @@
         <v>46217</v>
       </c>
       <c r="B76" t="n">
-        <v>131</v>
+        <v>2124</v>
       </c>
       <c r="C76" t="n">
         <v>8888</v>
       </c>
       <c r="D76" t="n">
-        <v>5470.1</v>
+        <v>3875.99</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -1889,17 +1889,17 @@
         <v>46217</v>
       </c>
       <c r="B77" t="n">
-        <v>1937</v>
+        <v>2695</v>
       </c>
       <c r="C77" t="n">
         <v>8888</v>
       </c>
       <c r="D77" t="n">
-        <v>692.86</v>
+        <v>1244.27</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1908,13 +1908,13 @@
         <v>46217</v>
       </c>
       <c r="B78" t="n">
-        <v>1983</v>
+        <v>1293</v>
       </c>
       <c r="C78" t="n">
         <v>8888</v>
       </c>
       <c r="D78" t="n">
-        <v>412.16</v>
+        <v>381.82</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -1927,17 +1927,17 @@
         <v>46217</v>
       </c>
       <c r="B79" t="n">
-        <v>451</v>
+        <v>2363</v>
       </c>
       <c r="C79" t="n">
         <v>8888</v>
       </c>
       <c r="D79" t="n">
-        <v>2583.46</v>
+        <v>2985.2</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1946,13 +1946,13 @@
         <v>46217</v>
       </c>
       <c r="B80" t="n">
-        <v>2767</v>
+        <v>2663</v>
       </c>
       <c r="C80" t="n">
         <v>8888</v>
       </c>
       <c r="D80" t="n">
-        <v>920.85</v>
+        <v>2146.08</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -1965,13 +1965,13 @@
         <v>46217</v>
       </c>
       <c r="B81" t="n">
-        <v>2697</v>
+        <v>2711</v>
       </c>
       <c r="C81" t="n">
         <v>8888</v>
       </c>
       <c r="D81" t="n">
-        <v>2880.19</v>
+        <v>2193.56</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -1984,17 +1984,17 @@
         <v>46217</v>
       </c>
       <c r="B82" t="n">
-        <v>569</v>
+        <v>1317</v>
       </c>
       <c r="C82" t="n">
         <v>8888</v>
       </c>
       <c r="D82" t="n">
-        <v>2291.64</v>
+        <v>787.51</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2003,17 +2003,17 @@
         <v>46217</v>
       </c>
       <c r="B83" t="n">
-        <v>2211</v>
+        <v>675</v>
       </c>
       <c r="C83" t="n">
-        <v>874</v>
+        <v>8888</v>
       </c>
       <c r="D83" t="n">
-        <v>1833.56</v>
+        <v>289.67</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2028,11 +2028,11 @@
         <v>8888</v>
       </c>
       <c r="D84" t="n">
-        <v>352.87</v>
+        <v>1902.46</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2041,13 +2041,13 @@
         <v>46217</v>
       </c>
       <c r="B85" t="n">
-        <v>2687</v>
+        <v>1658</v>
       </c>
       <c r="C85" t="n">
         <v>8888</v>
       </c>
       <c r="D85" t="n">
-        <v>1760.22</v>
+        <v>1357.94</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -2060,17 +2060,17 @@
         <v>46217</v>
       </c>
       <c r="B86" t="n">
-        <v>629</v>
+        <v>1392</v>
       </c>
       <c r="C86" t="n">
         <v>8888</v>
       </c>
       <c r="D86" t="n">
-        <v>559.15</v>
+        <v>814.61</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2079,17 +2079,17 @@
         <v>46217</v>
       </c>
       <c r="B87" t="n">
-        <v>1890</v>
+        <v>360</v>
       </c>
       <c r="C87" t="n">
-        <v>1953</v>
+        <v>8888</v>
       </c>
       <c r="D87" t="n">
-        <v>1122</v>
+        <v>749.13</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2098,17 +2098,17 @@
         <v>46217</v>
       </c>
       <c r="B88" t="n">
-        <v>1289</v>
+        <v>1324</v>
       </c>
       <c r="C88" t="n">
         <v>8888</v>
       </c>
       <c r="D88" t="n">
-        <v>1214.09</v>
+        <v>327.19</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2117,17 +2117,17 @@
         <v>46217</v>
       </c>
       <c r="B89" t="n">
-        <v>2107</v>
+        <v>525</v>
       </c>
       <c r="C89" t="n">
-        <v>1954</v>
+        <v>8888</v>
       </c>
       <c r="D89" t="n">
-        <v>2000.86</v>
+        <v>643.3</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2136,17 +2136,17 @@
         <v>46217</v>
       </c>
       <c r="B90" t="n">
-        <v>1116</v>
+        <v>949</v>
       </c>
       <c r="C90" t="n">
-        <v>8888</v>
+        <v>1134</v>
       </c>
       <c r="D90" t="n">
-        <v>1065.24</v>
+        <v>327.6</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2155,17 +2155,17 @@
         <v>46217</v>
       </c>
       <c r="B91" t="n">
-        <v>58</v>
+        <v>2133</v>
       </c>
       <c r="C91" t="n">
         <v>8888</v>
       </c>
       <c r="D91" t="n">
-        <v>2637.19</v>
+        <v>66030.34</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2174,17 +2174,17 @@
         <v>46217</v>
       </c>
       <c r="B92" t="n">
-        <v>1117</v>
+        <v>326</v>
       </c>
       <c r="C92" t="n">
         <v>8888</v>
       </c>
       <c r="D92" t="n">
-        <v>581.51</v>
+        <v>695.99</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2193,17 +2193,17 @@
         <v>46217</v>
       </c>
       <c r="B93" t="n">
-        <v>58</v>
+        <v>325</v>
       </c>
       <c r="C93" t="n">
         <v>8888</v>
       </c>
       <c r="D93" t="n">
-        <v>1411.43</v>
+        <v>774.73</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2212,17 +2212,17 @@
         <v>46217</v>
       </c>
       <c r="B94" t="n">
-        <v>629</v>
+        <v>1293</v>
       </c>
       <c r="C94" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D94" t="n">
-        <v>2049.78</v>
+        <v>8365.559999999999</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2231,17 +2231,17 @@
         <v>46217</v>
       </c>
       <c r="B95" t="n">
-        <v>595</v>
+        <v>131</v>
       </c>
       <c r="C95" t="n">
         <v>8888</v>
       </c>
       <c r="D95" t="n">
-        <v>3191</v>
+        <v>1969.93</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2250,17 +2250,17 @@
         <v>46217</v>
       </c>
       <c r="B96" t="n">
-        <v>949</v>
+        <v>2697</v>
       </c>
       <c r="C96" t="n">
-        <v>1762</v>
+        <v>8888</v>
       </c>
       <c r="D96" t="n">
-        <v>325.65</v>
+        <v>420.48</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2269,17 +2269,17 @@
         <v>46217</v>
       </c>
       <c r="B97" t="n">
-        <v>2463</v>
+        <v>2279</v>
       </c>
       <c r="C97" t="n">
         <v>8888</v>
       </c>
       <c r="D97" t="n">
-        <v>8336.43</v>
+        <v>1034.25</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
         <v>46217</v>
       </c>
       <c r="B98" t="n">
-        <v>1064</v>
+        <v>1340</v>
       </c>
       <c r="C98" t="n">
         <v>8888</v>
       </c>
       <c r="D98" t="n">
-        <v>1513.21</v>
+        <v>3037.55</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2307,17 +2307,17 @@
         <v>46217</v>
       </c>
       <c r="B99" t="n">
-        <v>1478</v>
+        <v>2641</v>
       </c>
       <c r="C99" t="n">
         <v>8888</v>
       </c>
       <c r="D99" t="n">
-        <v>2261.67</v>
+        <v>557.52</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2326,13 +2326,13 @@
         <v>46217</v>
       </c>
       <c r="B100" t="n">
-        <v>358</v>
+        <v>1116</v>
       </c>
       <c r="C100" t="n">
         <v>8888</v>
       </c>
       <c r="D100" t="n">
-        <v>1918.33</v>
+        <v>1293.89</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -2345,13 +2345,13 @@
         <v>46217</v>
       </c>
       <c r="B101" t="n">
-        <v>2107</v>
+        <v>2178</v>
       </c>
       <c r="C101" t="n">
         <v>8888</v>
       </c>
       <c r="D101" t="n">
-        <v>2745.11</v>
+        <v>5333.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -2364,17 +2364,17 @@
         <v>46217</v>
       </c>
       <c r="B102" t="n">
-        <v>675</v>
+        <v>1756</v>
       </c>
       <c r="C102" t="n">
         <v>8888</v>
       </c>
       <c r="D102" t="n">
-        <v>678.88</v>
+        <v>742.23</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2383,17 +2383,17 @@
         <v>46217</v>
       </c>
       <c r="B103" t="n">
-        <v>2279</v>
+        <v>131</v>
       </c>
       <c r="C103" t="n">
         <v>8888</v>
       </c>
       <c r="D103" t="n">
-        <v>1165.17</v>
+        <v>5470.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2402,17 +2402,17 @@
         <v>46217</v>
       </c>
       <c r="B104" t="n">
-        <v>451</v>
+        <v>2081</v>
       </c>
       <c r="C104" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D104" t="n">
-        <v>327.28</v>
+        <v>1022.42</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2421,13 +2421,13 @@
         <v>46217</v>
       </c>
       <c r="B105" t="n">
-        <v>2571</v>
+        <v>1374</v>
       </c>
       <c r="C105" t="n">
-        <v>1312</v>
+        <v>2845</v>
       </c>
       <c r="D105" t="n">
-        <v>2202.75</v>
+        <v>625.77</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -2440,17 +2440,17 @@
         <v>46217</v>
       </c>
       <c r="B106" t="n">
-        <v>2782</v>
+        <v>58</v>
       </c>
       <c r="C106" t="n">
         <v>8888</v>
       </c>
       <c r="D106" t="n">
-        <v>753.8</v>
+        <v>3050.12</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2459,17 +2459,17 @@
         <v>46217</v>
       </c>
       <c r="B107" t="n">
-        <v>610</v>
+        <v>1937</v>
       </c>
       <c r="C107" t="n">
         <v>8888</v>
       </c>
       <c r="D107" t="n">
-        <v>335.61</v>
+        <v>2199.57</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2478,17 +2478,17 @@
         <v>46217</v>
       </c>
       <c r="B108" t="n">
-        <v>2245</v>
+        <v>1983</v>
       </c>
       <c r="C108" t="n">
         <v>8888</v>
       </c>
       <c r="D108" t="n">
-        <v>355.88</v>
+        <v>412.16</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2497,17 +2497,17 @@
         <v>46217</v>
       </c>
       <c r="B109" t="n">
-        <v>1108</v>
+        <v>451</v>
       </c>
       <c r="C109" t="n">
         <v>8888</v>
       </c>
       <c r="D109" t="n">
-        <v>508.54</v>
+        <v>2583.46</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2516,13 +2516,13 @@
         <v>46217</v>
       </c>
       <c r="B110" t="n">
-        <v>341</v>
+        <v>1102</v>
       </c>
       <c r="C110" t="n">
-        <v>58</v>
+        <v>13148</v>
       </c>
       <c r="D110" t="n">
-        <v>366.88</v>
+        <v>1346.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -2535,17 +2535,17 @@
         <v>46217</v>
       </c>
       <c r="B111" t="n">
-        <v>525</v>
+        <v>2767</v>
       </c>
       <c r="C111" t="n">
-        <v>1087</v>
+        <v>8888</v>
       </c>
       <c r="D111" t="n">
-        <v>1830.26</v>
+        <v>920.85</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2554,17 +2554,17 @@
         <v>46217</v>
       </c>
       <c r="B112" t="n">
-        <v>1653</v>
+        <v>2697</v>
       </c>
       <c r="C112" t="n">
         <v>8888</v>
       </c>
       <c r="D112" t="n">
-        <v>4383.69</v>
+        <v>2880.19</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2573,17 +2573,17 @@
         <v>46217</v>
       </c>
       <c r="B113" t="n">
-        <v>619</v>
+        <v>569</v>
       </c>
       <c r="C113" t="n">
         <v>8888</v>
       </c>
       <c r="D113" t="n">
-        <v>1557.5</v>
+        <v>3002.06</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2592,13 +2592,13 @@
         <v>46217</v>
       </c>
       <c r="B114" t="n">
-        <v>1518</v>
+        <v>2211</v>
       </c>
       <c r="C114" t="n">
-        <v>1533</v>
+        <v>874</v>
       </c>
       <c r="D114" t="n">
-        <v>479.84</v>
+        <v>1833.56</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -2611,13 +2611,13 @@
         <v>46217</v>
       </c>
       <c r="B115" t="n">
-        <v>663</v>
+        <v>1063</v>
       </c>
       <c r="C115" t="n">
         <v>8888</v>
       </c>
       <c r="D115" t="n">
-        <v>824.5599999999999</v>
+        <v>352.87</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -2630,17 +2630,17 @@
         <v>46217</v>
       </c>
       <c r="B116" t="n">
-        <v>2089</v>
+        <v>2687</v>
       </c>
       <c r="C116" t="n">
-        <v>1533</v>
+        <v>8888</v>
       </c>
       <c r="D116" t="n">
-        <v>822.05</v>
+        <v>1760.22</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2649,17 +2649,17 @@
         <v>46217</v>
       </c>
       <c r="B117" t="n">
-        <v>2133</v>
+        <v>629</v>
       </c>
       <c r="C117" t="n">
-        <v>691</v>
+        <v>8888</v>
       </c>
       <c r="D117" t="n">
-        <v>1414.98</v>
+        <v>559.15</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2668,17 +2668,17 @@
         <v>46217</v>
       </c>
       <c r="B118" t="n">
-        <v>429</v>
+        <v>1117</v>
       </c>
       <c r="C118" t="n">
-        <v>2571</v>
+        <v>8888</v>
       </c>
       <c r="D118" t="n">
-        <v>667.12</v>
+        <v>1988.42</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2687,17 +2687,17 @@
         <v>46217</v>
       </c>
       <c r="B119" t="n">
-        <v>2641</v>
+        <v>1890</v>
       </c>
       <c r="C119" t="n">
-        <v>8888</v>
+        <v>1953</v>
       </c>
       <c r="D119" t="n">
-        <v>252.41</v>
+        <v>1122</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2706,13 +2706,13 @@
         <v>46217</v>
       </c>
       <c r="B120" t="n">
-        <v>1293</v>
+        <v>1289</v>
       </c>
       <c r="C120" t="n">
         <v>8888</v>
       </c>
       <c r="D120" t="n">
-        <v>8102.01</v>
+        <v>1214.09</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -2725,17 +2725,17 @@
         <v>46217</v>
       </c>
       <c r="B121" t="n">
-        <v>1465</v>
+        <v>2363</v>
       </c>
       <c r="C121" t="n">
         <v>8888</v>
       </c>
       <c r="D121" t="n">
-        <v>814.65</v>
+        <v>301.92</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2744,17 +2744,17 @@
         <v>46217</v>
       </c>
       <c r="B122" t="n">
-        <v>483</v>
+        <v>1075</v>
       </c>
       <c r="C122" t="n">
         <v>8888</v>
       </c>
       <c r="D122" t="n">
-        <v>1980.79</v>
+        <v>1845.09</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2763,17 +2763,17 @@
         <v>46217</v>
       </c>
       <c r="B123" t="n">
-        <v>1064</v>
+        <v>2107</v>
       </c>
       <c r="C123" t="n">
-        <v>8888</v>
+        <v>1954</v>
       </c>
       <c r="D123" t="n">
-        <v>104632.21</v>
+        <v>2000.86</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2782,17 +2782,17 @@
         <v>46217</v>
       </c>
       <c r="B124" t="n">
-        <v>131</v>
+        <v>1116</v>
       </c>
       <c r="C124" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D124" t="n">
-        <v>876.48</v>
+        <v>1065.24</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2801,17 +2801,17 @@
         <v>46217</v>
       </c>
       <c r="B125" t="n">
-        <v>663</v>
+        <v>2190</v>
       </c>
       <c r="C125" t="n">
         <v>8888</v>
       </c>
       <c r="D125" t="n">
-        <v>1769.59</v>
+        <v>2781.91</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2820,17 +2820,17 @@
         <v>46217</v>
       </c>
       <c r="B126" t="n">
-        <v>131</v>
+        <v>559</v>
       </c>
       <c r="C126" t="n">
-        <v>8888</v>
+        <v>3009</v>
       </c>
       <c r="D126" t="n">
-        <v>4787.28</v>
+        <v>1194.24</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2839,17 +2839,17 @@
         <v>46217</v>
       </c>
       <c r="B127" t="n">
-        <v>2308</v>
+        <v>1278</v>
       </c>
       <c r="C127" t="n">
-        <v>546</v>
+        <v>8888</v>
       </c>
       <c r="D127" t="n">
-        <v>1292.23</v>
+        <v>508.07</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2858,17 +2858,17 @@
         <v>46217</v>
       </c>
       <c r="B128" t="n">
-        <v>2709</v>
+        <v>58</v>
       </c>
       <c r="C128" t="n">
-        <v>2220</v>
+        <v>8888</v>
       </c>
       <c r="D128" t="n">
-        <v>1663.5</v>
+        <v>1411.43</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2877,17 +2877,17 @@
         <v>46217</v>
       </c>
       <c r="B129" t="n">
-        <v>1937</v>
+        <v>629</v>
       </c>
       <c r="C129" t="n">
         <v>8888</v>
       </c>
       <c r="D129" t="n">
-        <v>1492.4</v>
+        <v>2049.78</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2896,17 +2896,17 @@
         <v>46217</v>
       </c>
       <c r="B130" t="n">
-        <v>429</v>
+        <v>595</v>
       </c>
       <c r="C130" t="n">
-        <v>1281</v>
+        <v>8888</v>
       </c>
       <c r="D130" t="n">
-        <v>2195.97</v>
+        <v>3191</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2915,17 +2915,17 @@
         <v>46217</v>
       </c>
       <c r="B131" t="n">
-        <v>2211</v>
+        <v>949</v>
       </c>
       <c r="C131" t="n">
-        <v>8888</v>
+        <v>1762</v>
       </c>
       <c r="D131" t="n">
-        <v>1563.28</v>
+        <v>325.65</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2934,17 +2934,17 @@
         <v>46217</v>
       </c>
       <c r="B132" t="n">
-        <v>360</v>
+        <v>2463</v>
       </c>
       <c r="C132" t="n">
         <v>8888</v>
       </c>
       <c r="D132" t="n">
-        <v>15052.63</v>
+        <v>8336.43</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2953,17 +2953,17 @@
         <v>46217</v>
       </c>
       <c r="B133" t="n">
-        <v>2251</v>
+        <v>1064</v>
       </c>
       <c r="C133" t="n">
         <v>8888</v>
       </c>
       <c r="D133" t="n">
-        <v>797.58</v>
+        <v>1513.21</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2972,17 +2972,17 @@
         <v>46217</v>
       </c>
       <c r="B134" t="n">
-        <v>451</v>
+        <v>1478</v>
       </c>
       <c r="C134" t="n">
         <v>8888</v>
       </c>
       <c r="D134" t="n">
-        <v>1371.26</v>
+        <v>4067.5</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2991,17 +2991,17 @@
         <v>46217</v>
       </c>
       <c r="B135" t="n">
-        <v>40</v>
+        <v>438</v>
       </c>
       <c r="C135" t="n">
-        <v>8888</v>
+        <v>2845</v>
       </c>
       <c r="D135" t="n">
-        <v>1093.47</v>
+        <v>826.76</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3010,17 +3010,17 @@
         <v>46217</v>
       </c>
       <c r="B136" t="n">
-        <v>530</v>
+        <v>2539</v>
       </c>
       <c r="C136" t="n">
-        <v>8888</v>
+        <v>3009</v>
       </c>
       <c r="D136" t="n">
-        <v>180.08</v>
+        <v>1479.56</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3029,17 +3029,17 @@
         <v>46217</v>
       </c>
       <c r="B137" t="n">
-        <v>1137</v>
+        <v>358</v>
       </c>
       <c r="C137" t="n">
         <v>8888</v>
       </c>
       <c r="D137" t="n">
-        <v>3528.55</v>
+        <v>1918.33</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3048,17 +3048,17 @@
         <v>46217</v>
       </c>
       <c r="B138" t="n">
-        <v>1293</v>
+        <v>2107</v>
       </c>
       <c r="C138" t="n">
-        <v>601</v>
+        <v>8888</v>
       </c>
       <c r="D138" t="n">
-        <v>456.47</v>
+        <v>4459.75</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3067,17 +3067,17 @@
         <v>46217</v>
       </c>
       <c r="B139" t="n">
-        <v>2118</v>
+        <v>675</v>
       </c>
       <c r="C139" t="n">
         <v>8888</v>
       </c>
       <c r="D139" t="n">
-        <v>311.54</v>
+        <v>1559.23</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3086,17 +3086,17 @@
         <v>46217</v>
       </c>
       <c r="B140" t="n">
-        <v>424</v>
+        <v>2279</v>
       </c>
       <c r="C140" t="n">
         <v>8888</v>
       </c>
       <c r="D140" t="n">
-        <v>349.68</v>
+        <v>1165.17</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3105,13 +3105,13 @@
         <v>46217</v>
       </c>
       <c r="B141" t="n">
-        <v>1299</v>
+        <v>2727</v>
       </c>
       <c r="C141" t="n">
-        <v>27</v>
+        <v>3179</v>
       </c>
       <c r="D141" t="n">
-        <v>3625.32</v>
+        <v>514.7</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -3124,17 +3124,17 @@
         <v>46217</v>
       </c>
       <c r="B142" t="n">
-        <v>559</v>
+        <v>451</v>
       </c>
       <c r="C142" t="n">
-        <v>8888</v>
+        <v>3403</v>
       </c>
       <c r="D142" t="n">
-        <v>1064.63</v>
+        <v>327.28</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3143,17 +3143,17 @@
         <v>46217</v>
       </c>
       <c r="B143" t="n">
-        <v>89</v>
+        <v>535</v>
       </c>
       <c r="C143" t="n">
         <v>8888</v>
       </c>
       <c r="D143" t="n">
-        <v>1506.42</v>
+        <v>1369.04</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3162,17 +3162,17 @@
         <v>46217</v>
       </c>
       <c r="B144" t="n">
-        <v>2250</v>
+        <v>2571</v>
       </c>
       <c r="C144" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D144" t="n">
-        <v>1943.54</v>
+        <v>2202.75</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3181,13 +3181,13 @@
         <v>46217</v>
       </c>
       <c r="B145" t="n">
-        <v>767</v>
+        <v>2782</v>
       </c>
       <c r="C145" t="n">
         <v>8888</v>
       </c>
       <c r="D145" t="n">
-        <v>472.62</v>
+        <v>753.8</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -3200,17 +3200,17 @@
         <v>46217</v>
       </c>
       <c r="B146" t="n">
-        <v>2651</v>
+        <v>610</v>
       </c>
       <c r="C146" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D146" t="n">
-        <v>648.71</v>
+        <v>335.61</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3219,17 +3219,17 @@
         <v>46217</v>
       </c>
       <c r="B147" t="n">
-        <v>2114</v>
+        <v>2245</v>
       </c>
       <c r="C147" t="n">
-        <v>1954</v>
+        <v>8888</v>
       </c>
       <c r="D147" t="n">
-        <v>879.03</v>
+        <v>355.88</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3238,13 +3238,13 @@
         <v>46217</v>
       </c>
       <c r="B148" t="n">
-        <v>40</v>
+        <v>619</v>
       </c>
       <c r="C148" t="n">
         <v>8888</v>
       </c>
       <c r="D148" t="n">
-        <v>3583.39</v>
+        <v>3019.73</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -3257,17 +3257,17 @@
         <v>46217</v>
       </c>
       <c r="B149" t="n">
-        <v>40</v>
+        <v>1108</v>
       </c>
       <c r="C149" t="n">
         <v>8888</v>
       </c>
       <c r="D149" t="n">
-        <v>2529.31</v>
+        <v>508.54</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3276,17 +3276,17 @@
         <v>46217</v>
       </c>
       <c r="B150" t="n">
-        <v>626</v>
+        <v>341</v>
       </c>
       <c r="C150" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D150" t="n">
-        <v>18654.36</v>
+        <v>366.88</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3295,17 +3295,17 @@
         <v>46217</v>
       </c>
       <c r="B151" t="n">
-        <v>363</v>
+        <v>525</v>
       </c>
       <c r="C151" t="n">
-        <v>8888</v>
+        <v>1087</v>
       </c>
       <c r="D151" t="n">
-        <v>739.17</v>
+        <v>1830.26</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3314,13 +3314,13 @@
         <v>46217</v>
       </c>
       <c r="B152" t="n">
-        <v>675</v>
+        <v>1344</v>
       </c>
       <c r="C152" t="n">
-        <v>1898</v>
+        <v>2845</v>
       </c>
       <c r="D152" t="n">
-        <v>107.13</v>
+        <v>394.8</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -3333,17 +3333,17 @@
         <v>46217</v>
       </c>
       <c r="B153" t="n">
-        <v>636</v>
+        <v>1653</v>
       </c>
       <c r="C153" t="n">
         <v>8888</v>
       </c>
       <c r="D153" t="n">
-        <v>7476.56</v>
+        <v>4383.69</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
         <v>46217</v>
       </c>
       <c r="B154" t="n">
-        <v>1075</v>
+        <v>1518</v>
       </c>
       <c r="C154" t="n">
-        <v>8888</v>
+        <v>1533</v>
       </c>
       <c r="D154" t="n">
-        <v>1331.89</v>
+        <v>479.84</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3371,13 +3371,13 @@
         <v>46217</v>
       </c>
       <c r="B155" t="n">
-        <v>2245</v>
+        <v>663</v>
       </c>
       <c r="C155" t="n">
         <v>8888</v>
       </c>
       <c r="D155" t="n">
-        <v>883.75</v>
+        <v>824.5599999999999</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -3390,13 +3390,13 @@
         <v>46217</v>
       </c>
       <c r="B156" t="n">
-        <v>477</v>
+        <v>1278</v>
       </c>
       <c r="C156" t="n">
         <v>8888</v>
       </c>
       <c r="D156" t="n">
-        <v>994.15</v>
+        <v>1267.68</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -3409,17 +3409,17 @@
         <v>46217</v>
       </c>
       <c r="B157" t="n">
-        <v>2015</v>
+        <v>2089</v>
       </c>
       <c r="C157" t="n">
-        <v>8888</v>
+        <v>1533</v>
       </c>
       <c r="D157" t="n">
-        <v>3243.05</v>
+        <v>822.05</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3428,13 +3428,13 @@
         <v>46217</v>
       </c>
       <c r="B158" t="n">
-        <v>1996</v>
+        <v>2133</v>
       </c>
       <c r="C158" t="n">
         <v>691</v>
       </c>
       <c r="D158" t="n">
-        <v>500.79</v>
+        <v>1414.98</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -3447,17 +3447,17 @@
         <v>46217</v>
       </c>
       <c r="B159" t="n">
-        <v>1653</v>
+        <v>429</v>
       </c>
       <c r="C159" t="n">
-        <v>8888</v>
+        <v>2571</v>
       </c>
       <c r="D159" t="n">
-        <v>4115.53</v>
+        <v>667.12</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3466,17 +3466,17 @@
         <v>46217</v>
       </c>
       <c r="B160" t="n">
-        <v>1064</v>
+        <v>2641</v>
       </c>
       <c r="C160" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D160" t="n">
-        <v>1052.68</v>
+        <v>252.41</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3485,17 +3485,17 @@
         <v>46217</v>
       </c>
       <c r="B161" t="n">
-        <v>1983</v>
+        <v>351</v>
       </c>
       <c r="C161" t="n">
-        <v>8888</v>
+        <v>3009</v>
       </c>
       <c r="D161" t="n">
-        <v>1246.33</v>
+        <v>1007.64</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3504,17 +3504,17 @@
         <v>46217</v>
       </c>
       <c r="B162" t="n">
-        <v>2118</v>
+        <v>1137</v>
       </c>
       <c r="C162" t="n">
         <v>8888</v>
       </c>
       <c r="D162" t="n">
-        <v>4886.49</v>
+        <v>5032.13</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3523,13 +3523,13 @@
         <v>46217</v>
       </c>
       <c r="B163" t="n">
-        <v>2680</v>
+        <v>1293</v>
       </c>
       <c r="C163" t="n">
         <v>8888</v>
       </c>
       <c r="D163" t="n">
-        <v>2285.31</v>
+        <v>8102.01</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -3542,17 +3542,17 @@
         <v>46217</v>
       </c>
       <c r="B164" t="n">
-        <v>2637</v>
+        <v>1465</v>
       </c>
       <c r="C164" t="n">
         <v>8888</v>
       </c>
       <c r="D164" t="n">
-        <v>1302.18</v>
+        <v>1609</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3561,17 +3561,17 @@
         <v>46217</v>
       </c>
       <c r="B165" t="n">
-        <v>1632</v>
+        <v>483</v>
       </c>
       <c r="C165" t="n">
         <v>8888</v>
       </c>
       <c r="D165" t="n">
-        <v>689.76</v>
+        <v>2444.39</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3580,17 +3580,17 @@
         <v>46217</v>
       </c>
       <c r="B166" t="n">
-        <v>1299</v>
+        <v>1064</v>
       </c>
       <c r="C166" t="n">
-        <v>2522</v>
+        <v>8888</v>
       </c>
       <c r="D166" t="n">
-        <v>3319.01</v>
+        <v>104632.21</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3599,17 +3599,17 @@
         <v>46217</v>
       </c>
       <c r="B167" t="n">
-        <v>2727</v>
+        <v>131</v>
       </c>
       <c r="C167" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D167" t="n">
-        <v>548.33</v>
+        <v>876.48</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3618,17 +3618,17 @@
         <v>46217</v>
       </c>
       <c r="B168" t="n">
-        <v>2026</v>
+        <v>663</v>
       </c>
       <c r="C168" t="n">
         <v>8888</v>
       </c>
       <c r="D168" t="n">
-        <v>699.05</v>
+        <v>1769.59</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3637,17 +3637,17 @@
         <v>46217</v>
       </c>
       <c r="B169" t="n">
-        <v>664</v>
+        <v>131</v>
       </c>
       <c r="C169" t="n">
         <v>8888</v>
       </c>
       <c r="D169" t="n">
-        <v>440.92</v>
+        <v>4787.28</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3656,13 +3656,13 @@
         <v>46217</v>
       </c>
       <c r="B170" t="n">
-        <v>629</v>
+        <v>2308</v>
       </c>
       <c r="C170" t="n">
-        <v>675</v>
+        <v>546</v>
       </c>
       <c r="D170" t="n">
-        <v>267.79</v>
+        <v>1292.23</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -3675,17 +3675,17 @@
         <v>46217</v>
       </c>
       <c r="B171" t="n">
-        <v>559</v>
+        <v>2709</v>
       </c>
       <c r="C171" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D171" t="n">
-        <v>1562.5</v>
+        <v>1663.5</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3694,17 +3694,17 @@
         <v>46217</v>
       </c>
       <c r="B172" t="n">
-        <v>1465</v>
+        <v>1937</v>
       </c>
       <c r="C172" t="n">
         <v>8888</v>
       </c>
       <c r="D172" t="n">
-        <v>10920.6</v>
+        <v>1492.4</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3713,17 +3713,17 @@
         <v>46217</v>
       </c>
       <c r="B173" t="n">
-        <v>2550</v>
+        <v>429</v>
       </c>
       <c r="C173" t="n">
-        <v>8888</v>
+        <v>1281</v>
       </c>
       <c r="D173" t="n">
-        <v>321.05</v>
+        <v>2195.97</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3732,17 +3732,17 @@
         <v>46217</v>
       </c>
       <c r="B174" t="n">
-        <v>1756</v>
+        <v>2211</v>
       </c>
       <c r="C174" t="n">
         <v>8888</v>
       </c>
       <c r="D174" t="n">
-        <v>2445</v>
+        <v>8568.99</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3751,17 +3751,17 @@
         <v>46217</v>
       </c>
       <c r="B175" t="n">
-        <v>890</v>
+        <v>360</v>
       </c>
       <c r="C175" t="n">
         <v>8888</v>
       </c>
       <c r="D175" t="n">
-        <v>4287.14</v>
+        <v>15052.63</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3770,13 +3770,13 @@
         <v>46217</v>
       </c>
       <c r="B176" t="n">
-        <v>363</v>
+        <v>2251</v>
       </c>
       <c r="C176" t="n">
         <v>8888</v>
       </c>
       <c r="D176" t="n">
-        <v>2517.01</v>
+        <v>797.58</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -3789,17 +3789,17 @@
         <v>46217</v>
       </c>
       <c r="B177" t="n">
-        <v>2698</v>
+        <v>451</v>
       </c>
       <c r="C177" t="n">
-        <v>874</v>
+        <v>8888</v>
       </c>
       <c r="D177" t="n">
-        <v>1183.42</v>
+        <v>1371.26</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3808,17 +3808,17 @@
         <v>46217</v>
       </c>
       <c r="B178" t="n">
-        <v>535</v>
+        <v>40</v>
       </c>
       <c r="C178" t="n">
         <v>8888</v>
       </c>
       <c r="D178" t="n">
-        <v>5293.96</v>
+        <v>1093.47</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3827,17 +3827,17 @@
         <v>46217</v>
       </c>
       <c r="B179" t="n">
-        <v>2250</v>
+        <v>530</v>
       </c>
       <c r="C179" t="n">
         <v>8888</v>
       </c>
       <c r="D179" t="n">
-        <v>2650.33</v>
+        <v>180.08</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3846,17 +3846,17 @@
         <v>46217</v>
       </c>
       <c r="B180" t="n">
-        <v>2681</v>
+        <v>1327</v>
       </c>
       <c r="C180" t="n">
-        <v>8888</v>
+        <v>3009</v>
       </c>
       <c r="D180" t="n">
-        <v>2853.99</v>
+        <v>946.8</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3865,17 +3865,17 @@
         <v>46217</v>
       </c>
       <c r="B181" t="n">
-        <v>132</v>
+        <v>1293</v>
       </c>
       <c r="C181" t="n">
-        <v>8888</v>
+        <v>601</v>
       </c>
       <c r="D181" t="n">
-        <v>2623.22</v>
+        <v>456.47</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3884,17 +3884,17 @@
         <v>46217</v>
       </c>
       <c r="B182" t="n">
-        <v>2442</v>
+        <v>424</v>
       </c>
       <c r="C182" t="n">
         <v>8888</v>
       </c>
       <c r="D182" t="n">
-        <v>2822.22</v>
+        <v>1758.85</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3903,17 +3903,17 @@
         <v>46217</v>
       </c>
       <c r="B183" t="n">
-        <v>363</v>
+        <v>2118</v>
       </c>
       <c r="C183" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D183" t="n">
-        <v>3635.16</v>
+        <v>311.54</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3922,17 +3922,17 @@
         <v>46217</v>
       </c>
       <c r="B184" t="n">
-        <v>483</v>
+        <v>2251</v>
       </c>
       <c r="C184" t="n">
         <v>8888</v>
       </c>
       <c r="D184" t="n">
-        <v>2527.71</v>
+        <v>603.66</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3941,17 +3941,17 @@
         <v>46217</v>
       </c>
       <c r="B185" t="n">
-        <v>2607</v>
+        <v>1478</v>
       </c>
       <c r="C185" t="n">
-        <v>8888</v>
+        <v>675</v>
       </c>
       <c r="D185" t="n">
-        <v>1075.36</v>
+        <v>945.74</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3960,13 +3960,13 @@
         <v>46217</v>
       </c>
       <c r="B186" t="n">
-        <v>2330</v>
+        <v>1299</v>
       </c>
       <c r="C186" t="n">
-        <v>1954</v>
+        <v>27</v>
       </c>
       <c r="D186" t="n">
-        <v>1923.09</v>
+        <v>3625.32</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -3979,17 +3979,17 @@
         <v>46217</v>
       </c>
       <c r="B187" t="n">
-        <v>2472</v>
+        <v>559</v>
       </c>
       <c r="C187" t="n">
-        <v>2853</v>
+        <v>8888</v>
       </c>
       <c r="D187" t="n">
-        <v>824.0599999999999</v>
+        <v>1064.63</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3998,17 +3998,17 @@
         <v>46217</v>
       </c>
       <c r="B188" t="n">
-        <v>1384</v>
+        <v>89</v>
       </c>
       <c r="C188" t="n">
         <v>8888</v>
       </c>
       <c r="D188" t="n">
-        <v>585.27</v>
+        <v>1506.42</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4017,17 +4017,17 @@
         <v>46217</v>
       </c>
       <c r="B189" t="n">
-        <v>2709</v>
+        <v>2250</v>
       </c>
       <c r="C189" t="n">
         <v>8888</v>
       </c>
       <c r="D189" t="n">
-        <v>1667.47</v>
+        <v>1943.54</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4036,17 +4036,17 @@
         <v>46217</v>
       </c>
       <c r="B190" t="n">
-        <v>374</v>
+        <v>1327</v>
       </c>
       <c r="C190" t="n">
         <v>8888</v>
       </c>
       <c r="D190" t="n">
-        <v>1150.97</v>
+        <v>319.23</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4055,17 +4055,17 @@
         <v>46217</v>
       </c>
       <c r="B191" t="n">
-        <v>1137</v>
+        <v>326</v>
       </c>
       <c r="C191" t="n">
         <v>8888</v>
       </c>
       <c r="D191" t="n">
-        <v>4413.34</v>
+        <v>151.86</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4074,17 +4074,1024 @@
         <v>46217</v>
       </c>
       <c r="B192" t="n">
+        <v>1372</v>
+      </c>
+      <c r="C192" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D192" t="n">
+        <v>1088.02</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B193" t="n">
+        <v>767</v>
+      </c>
+      <c r="C193" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D193" t="n">
+        <v>472.62</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B194" t="n">
+        <v>626</v>
+      </c>
+      <c r="C194" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D194" t="n">
+        <v>24505.65</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B195" t="n">
+        <v>2651</v>
+      </c>
+      <c r="C195" t="n">
+        <v>58</v>
+      </c>
+      <c r="D195" t="n">
+        <v>648.71</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B196" t="n">
+        <v>2114</v>
+      </c>
+      <c r="C196" t="n">
+        <v>1954</v>
+      </c>
+      <c r="D196" t="n">
+        <v>879.03</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B197" t="n">
+        <v>40</v>
+      </c>
+      <c r="C197" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D197" t="n">
+        <v>3583.39</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B198" t="n">
+        <v>40</v>
+      </c>
+      <c r="C198" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D198" t="n">
+        <v>2529.31</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B199" t="n">
+        <v>363</v>
+      </c>
+      <c r="C199" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D199" t="n">
+        <v>739.17</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B200" t="n">
+        <v>675</v>
+      </c>
+      <c r="C200" t="n">
+        <v>1898</v>
+      </c>
+      <c r="D200" t="n">
+        <v>107.13</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B201" t="n">
+        <v>636</v>
+      </c>
+      <c r="C201" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D201" t="n">
+        <v>7476.56</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B202" t="n">
+        <v>1075</v>
+      </c>
+      <c r="C202" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D202" t="n">
+        <v>1331.89</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B203" t="n">
+        <v>2245</v>
+      </c>
+      <c r="C203" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D203" t="n">
+        <v>883.75</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B204" t="n">
+        <v>477</v>
+      </c>
+      <c r="C204" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D204" t="n">
+        <v>994.15</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B205" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C205" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D205" t="n">
+        <v>3243.05</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B206" t="n">
+        <v>1996</v>
+      </c>
+      <c r="C206" t="n">
+        <v>691</v>
+      </c>
+      <c r="D206" t="n">
+        <v>500.79</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B207" t="n">
+        <v>1653</v>
+      </c>
+      <c r="C207" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D207" t="n">
+        <v>4115.53</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B208" t="n">
+        <v>1064</v>
+      </c>
+      <c r="C208" t="n">
+        <v>27</v>
+      </c>
+      <c r="D208" t="n">
+        <v>1153.23</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B209" t="n">
+        <v>1983</v>
+      </c>
+      <c r="C209" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D209" t="n">
+        <v>1246.33</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B210" t="n">
+        <v>2118</v>
+      </c>
+      <c r="C210" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D210" t="n">
+        <v>5870.04</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B211" t="n">
+        <v>559</v>
+      </c>
+      <c r="C211" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D211" t="n">
+        <v>2189.12</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B212" t="n">
+        <v>2680</v>
+      </c>
+      <c r="C212" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D212" t="n">
+        <v>2285.31</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B213" t="n">
+        <v>2637</v>
+      </c>
+      <c r="C213" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D213" t="n">
+        <v>1302.18</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B214" t="n">
+        <v>1632</v>
+      </c>
+      <c r="C214" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D214" t="n">
+        <v>689.76</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B215" t="n">
+        <v>1299</v>
+      </c>
+      <c r="C215" t="n">
+        <v>2522</v>
+      </c>
+      <c r="D215" t="n">
+        <v>3319.01</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B216" t="n">
+        <v>2727</v>
+      </c>
+      <c r="C216" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D216" t="n">
+        <v>548.33</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B217" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C217" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D217" t="n">
+        <v>699.05</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B218" t="n">
+        <v>664</v>
+      </c>
+      <c r="C218" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D218" t="n">
+        <v>3483.46</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B219" t="n">
+        <v>629</v>
+      </c>
+      <c r="C219" t="n">
+        <v>675</v>
+      </c>
+      <c r="D219" t="n">
+        <v>267.79</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B220" t="n">
+        <v>1465</v>
+      </c>
+      <c r="C220" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D220" t="n">
+        <v>12894.64</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B221" t="n">
+        <v>2550</v>
+      </c>
+      <c r="C221" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D221" t="n">
+        <v>321.05</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B222" t="n">
+        <v>1756</v>
+      </c>
+      <c r="C222" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D222" t="n">
+        <v>2445</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B223" t="n">
+        <v>890</v>
+      </c>
+      <c r="C223" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D223" t="n">
+        <v>4287.14</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B224" t="n">
+        <v>363</v>
+      </c>
+      <c r="C224" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D224" t="n">
+        <v>2517.01</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B225" t="n">
+        <v>2698</v>
+      </c>
+      <c r="C225" t="n">
+        <v>874</v>
+      </c>
+      <c r="D225" t="n">
+        <v>1183.42</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B226" t="n">
+        <v>535</v>
+      </c>
+      <c r="C226" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D226" t="n">
+        <v>5293.96</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B227" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C227" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D227" t="n">
+        <v>2650.33</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B228" t="n">
+        <v>2681</v>
+      </c>
+      <c r="C228" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D228" t="n">
+        <v>2853.99</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B229" t="n">
+        <v>132</v>
+      </c>
+      <c r="C229" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D229" t="n">
+        <v>11123.92</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B230" t="n">
+        <v>2442</v>
+      </c>
+      <c r="C230" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D230" t="n">
+        <v>2822.22</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B231" t="n">
+        <v>363</v>
+      </c>
+      <c r="C231" t="n">
+        <v>1898</v>
+      </c>
+      <c r="D231" t="n">
+        <v>4028</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B232" t="n">
+        <v>483</v>
+      </c>
+      <c r="C232" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D232" t="n">
+        <v>3025.94</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B233" t="n">
+        <v>2279</v>
+      </c>
+      <c r="C233" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D233" t="n">
+        <v>740.38</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B234" t="n">
+        <v>2607</v>
+      </c>
+      <c r="C234" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D234" t="n">
+        <v>1075.36</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B235" t="n">
+        <v>2330</v>
+      </c>
+      <c r="C235" t="n">
+        <v>1954</v>
+      </c>
+      <c r="D235" t="n">
+        <v>1923.09</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B236" t="n">
+        <v>2472</v>
+      </c>
+      <c r="C236" t="n">
+        <v>2853</v>
+      </c>
+      <c r="D236" t="n">
+        <v>824.0599999999999</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B237" t="n">
+        <v>1384</v>
+      </c>
+      <c r="C237" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D237" t="n">
+        <v>585.27</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B238" t="n">
+        <v>2709</v>
+      </c>
+      <c r="C238" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D238" t="n">
+        <v>2210.08</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B239" t="n">
+        <v>619</v>
+      </c>
+      <c r="C239" t="n">
+        <v>1139</v>
+      </c>
+      <c r="D239" t="n">
+        <v>2098.5</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B240" t="n">
+        <v>374</v>
+      </c>
+      <c r="C240" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D240" t="n">
+        <v>1725.89</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B241" t="n">
+        <v>1137</v>
+      </c>
+      <c r="C241" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D241" t="n">
+        <v>4413.34</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B242" t="n">
         <v>2251</v>
       </c>
-      <c r="C192" t="n">
+      <c r="C242" t="n">
         <v>3403</v>
       </c>
-      <c r="D192" t="n">
+      <c r="D242" t="n">
         <v>510.18</v>
       </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>TELEMARKETING</t>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B243" t="n">
+        <v>2728</v>
+      </c>
+      <c r="C243" t="n">
+        <v>977</v>
+      </c>
+      <c r="D243" t="n">
+        <v>2256.87</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B244" t="n">
+        <v>1278</v>
+      </c>
+      <c r="C244" t="n">
+        <v>1533</v>
+      </c>
+      <c r="D244" t="n">
+        <v>620.97</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B245" t="n">
+        <v>1380</v>
+      </c>
+      <c r="C245" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D245" t="n">
+        <v>947.8200000000001</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E245"/>
+  <dimension ref="A1:E261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
         <v>8888</v>
       </c>
       <c r="D2" t="n">
-        <v>26575.79</v>
+        <v>27200.69</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -673,13 +673,13 @@
         <v>46217</v>
       </c>
       <c r="B13" t="n">
-        <v>2015</v>
+        <v>1876</v>
       </c>
       <c r="C13" t="n">
-        <v>2571</v>
+        <v>977</v>
       </c>
       <c r="D13" t="n">
-        <v>2593.26</v>
+        <v>312.66</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -692,17 +692,17 @@
         <v>46217</v>
       </c>
       <c r="B14" t="n">
-        <v>1993</v>
+        <v>2015</v>
       </c>
       <c r="C14" t="n">
-        <v>8888</v>
+        <v>2571</v>
       </c>
       <c r="D14" t="n">
-        <v>1785.44</v>
+        <v>2593.26</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -711,17 +711,17 @@
         <v>46217</v>
       </c>
       <c r="B15" t="n">
-        <v>1102</v>
+        <v>1993</v>
       </c>
       <c r="C15" t="n">
         <v>8888</v>
       </c>
       <c r="D15" t="n">
-        <v>3406.59</v>
+        <v>1785.44</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -730,17 +730,17 @@
         <v>46217</v>
       </c>
       <c r="B16" t="n">
-        <v>1937</v>
+        <v>1102</v>
       </c>
       <c r="C16" t="n">
         <v>8888</v>
       </c>
       <c r="D16" t="n">
-        <v>3337.21</v>
+        <v>3406.59</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
         <v>46217</v>
       </c>
       <c r="B17" t="n">
-        <v>1293</v>
+        <v>1937</v>
       </c>
       <c r="C17" t="n">
-        <v>1281</v>
+        <v>8888</v>
       </c>
       <c r="D17" t="n">
-        <v>1337.87</v>
+        <v>3337.21</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -768,17 +768,17 @@
         <v>46217</v>
       </c>
       <c r="B18" t="n">
-        <v>2657</v>
+        <v>1293</v>
       </c>
       <c r="C18" t="n">
-        <v>8888</v>
+        <v>1281</v>
       </c>
       <c r="D18" t="n">
-        <v>877.0700000000001</v>
+        <v>1337.87</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -787,13 +787,13 @@
         <v>46217</v>
       </c>
       <c r="B19" t="n">
-        <v>2768</v>
+        <v>2657</v>
       </c>
       <c r="C19" t="n">
         <v>8888</v>
       </c>
       <c r="D19" t="n">
-        <v>4890.12</v>
+        <v>877.0700000000001</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -806,13 +806,13 @@
         <v>46217</v>
       </c>
       <c r="B20" t="n">
-        <v>2686</v>
+        <v>2768</v>
       </c>
       <c r="C20" t="n">
         <v>8888</v>
       </c>
       <c r="D20" t="n">
-        <v>422.71</v>
+        <v>4890.12</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
         <v>46217</v>
       </c>
       <c r="B21" t="n">
-        <v>1890</v>
+        <v>2686</v>
       </c>
       <c r="C21" t="n">
-        <v>3449</v>
+        <v>8888</v>
       </c>
       <c r="D21" t="n">
-        <v>1575.78</v>
+        <v>422.71</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -844,17 +844,17 @@
         <v>46217</v>
       </c>
       <c r="B22" t="n">
-        <v>33</v>
+        <v>1890</v>
       </c>
       <c r="C22" t="n">
-        <v>8888</v>
+        <v>3449</v>
       </c>
       <c r="D22" t="n">
-        <v>1041.47</v>
+        <v>1575.78</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -863,17 +863,17 @@
         <v>46217</v>
       </c>
       <c r="B23" t="n">
-        <v>2726</v>
+        <v>33</v>
       </c>
       <c r="C23" t="n">
-        <v>1929</v>
+        <v>8888</v>
       </c>
       <c r="D23" t="n">
-        <v>640.1799999999999</v>
+        <v>1041.47</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
         <v>46217</v>
       </c>
       <c r="B24" t="n">
-        <v>89</v>
+        <v>2726</v>
       </c>
       <c r="C24" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D24" t="n">
-        <v>5652.15</v>
+        <v>640.1799999999999</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
         <v>46217</v>
       </c>
       <c r="B25" t="n">
-        <v>2178</v>
+        <v>89</v>
       </c>
       <c r="C25" t="n">
-        <v>738</v>
+        <v>8888</v>
       </c>
       <c r="D25" t="n">
-        <v>291.83</v>
+        <v>5652.15</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -920,13 +920,13 @@
         <v>46217</v>
       </c>
       <c r="B26" t="n">
-        <v>2209</v>
+        <v>2178</v>
       </c>
       <c r="C26" t="n">
         <v>738</v>
       </c>
       <c r="D26" t="n">
-        <v>2043.28</v>
+        <v>291.83</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -939,17 +939,17 @@
         <v>46217</v>
       </c>
       <c r="B27" t="n">
-        <v>429</v>
+        <v>2209</v>
       </c>
       <c r="C27" t="n">
-        <v>8888</v>
+        <v>738</v>
       </c>
       <c r="D27" t="n">
-        <v>3775.81</v>
+        <v>2043.28</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
         <v>46217</v>
       </c>
       <c r="B28" t="n">
-        <v>2641</v>
+        <v>429</v>
       </c>
       <c r="C28" t="n">
         <v>8888</v>
       </c>
       <c r="D28" t="n">
-        <v>607.79</v>
+        <v>3775.81</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -977,17 +977,17 @@
         <v>46217</v>
       </c>
       <c r="B29" t="n">
-        <v>949</v>
+        <v>2641</v>
       </c>
       <c r="C29" t="n">
-        <v>1258</v>
+        <v>8888</v>
       </c>
       <c r="D29" t="n">
-        <v>196.87</v>
+        <v>607.79</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -996,13 +996,13 @@
         <v>46217</v>
       </c>
       <c r="B30" t="n">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="C30" t="n">
         <v>8888</v>
       </c>
       <c r="D30" t="n">
-        <v>2121.12</v>
+        <v>802.59</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1015,17 +1015,17 @@
         <v>46217</v>
       </c>
       <c r="B31" t="n">
-        <v>1756</v>
+        <v>949</v>
       </c>
       <c r="C31" t="n">
-        <v>8888</v>
+        <v>1258</v>
       </c>
       <c r="D31" t="n">
-        <v>1799.7</v>
+        <v>196.87</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
         <v>46217</v>
       </c>
       <c r="B32" t="n">
-        <v>285</v>
+        <v>353</v>
       </c>
       <c r="C32" t="n">
         <v>8888</v>
       </c>
       <c r="D32" t="n">
-        <v>3937.9</v>
+        <v>2121.12</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1053,13 +1053,13 @@
         <v>46217</v>
       </c>
       <c r="B33" t="n">
-        <v>1906</v>
+        <v>1756</v>
       </c>
       <c r="C33" t="n">
         <v>8888</v>
       </c>
       <c r="D33" t="n">
-        <v>3142.54</v>
+        <v>2223.56</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1072,17 +1072,17 @@
         <v>46217</v>
       </c>
       <c r="B34" t="n">
-        <v>1308</v>
+        <v>285</v>
       </c>
       <c r="C34" t="n">
         <v>8888</v>
       </c>
       <c r="D34" t="n">
-        <v>3127.35</v>
+        <v>3937.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1091,17 +1091,17 @@
         <v>46217</v>
       </c>
       <c r="B35" t="n">
-        <v>610</v>
+        <v>1906</v>
       </c>
       <c r="C35" t="n">
         <v>8888</v>
       </c>
       <c r="D35" t="n">
-        <v>590.08</v>
+        <v>3142.54</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1110,13 +1110,13 @@
         <v>46217</v>
       </c>
       <c r="B36" t="n">
-        <v>619</v>
+        <v>2499</v>
       </c>
       <c r="C36" t="n">
         <v>8888</v>
       </c>
       <c r="D36" t="n">
-        <v>236.34</v>
+        <v>493.06</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         <v>46217</v>
       </c>
       <c r="B37" t="n">
-        <v>1324</v>
+        <v>1308</v>
       </c>
       <c r="C37" t="n">
         <v>8888</v>
       </c>
       <c r="D37" t="n">
-        <v>2603.19</v>
+        <v>3127.35</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1148,17 +1148,17 @@
         <v>46217</v>
       </c>
       <c r="B38" t="n">
-        <v>483</v>
+        <v>610</v>
       </c>
       <c r="C38" t="n">
         <v>8888</v>
       </c>
       <c r="D38" t="n">
-        <v>461.28</v>
+        <v>590.08</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1167,17 +1167,17 @@
         <v>46217</v>
       </c>
       <c r="B39" t="n">
-        <v>1117</v>
+        <v>619</v>
       </c>
       <c r="C39" t="n">
         <v>8888</v>
       </c>
       <c r="D39" t="n">
-        <v>755.71</v>
+        <v>236.34</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1186,17 +1186,17 @@
         <v>46217</v>
       </c>
       <c r="B40" t="n">
-        <v>2755</v>
+        <v>1324</v>
       </c>
       <c r="C40" t="n">
-        <v>2220</v>
+        <v>8888</v>
       </c>
       <c r="D40" t="n">
-        <v>1133.17</v>
+        <v>2603.19</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1205,17 +1205,17 @@
         <v>46217</v>
       </c>
       <c r="B41" t="n">
-        <v>2767</v>
+        <v>483</v>
       </c>
       <c r="C41" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D41" t="n">
-        <v>5000.2</v>
+        <v>461.28</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1224,13 +1224,13 @@
         <v>46217</v>
       </c>
       <c r="B42" t="n">
-        <v>559</v>
+        <v>1117</v>
       </c>
       <c r="C42" t="n">
         <v>8888</v>
       </c>
       <c r="D42" t="n">
-        <v>1516.25</v>
+        <v>755.71</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1243,17 +1243,17 @@
         <v>46217</v>
       </c>
       <c r="B43" t="n">
-        <v>1277</v>
+        <v>2755</v>
       </c>
       <c r="C43" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D43" t="n">
-        <v>574.7</v>
+        <v>1133.17</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1262,17 +1262,17 @@
         <v>46217</v>
       </c>
       <c r="B44" t="n">
-        <v>358</v>
+        <v>2767</v>
       </c>
       <c r="C44" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D44" t="n">
-        <v>1301.77</v>
+        <v>5000.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1281,13 +1281,13 @@
         <v>46217</v>
       </c>
       <c r="B45" t="n">
-        <v>1993</v>
+        <v>559</v>
       </c>
       <c r="C45" t="n">
         <v>8888</v>
       </c>
       <c r="D45" t="n">
-        <v>5280</v>
+        <v>1516.25</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1300,13 +1300,13 @@
         <v>46217</v>
       </c>
       <c r="B46" t="n">
-        <v>609</v>
+        <v>1277</v>
       </c>
       <c r="C46" t="n">
         <v>8888</v>
       </c>
       <c r="D46" t="n">
-        <v>962.08</v>
+        <v>574.7</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1319,17 +1319,17 @@
         <v>46217</v>
       </c>
       <c r="B47" t="n">
-        <v>2507</v>
+        <v>358</v>
       </c>
       <c r="C47" t="n">
         <v>8888</v>
       </c>
       <c r="D47" t="n">
-        <v>448.36</v>
+        <v>1301.77</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1338,17 @@
         <v>46217</v>
       </c>
       <c r="B48" t="n">
-        <v>2767</v>
+        <v>1993</v>
       </c>
       <c r="C48" t="n">
         <v>8888</v>
       </c>
       <c r="D48" t="n">
-        <v>1175.73</v>
+        <v>5280</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1357,17 +1357,17 @@
         <v>46217</v>
       </c>
       <c r="B49" t="n">
-        <v>1063</v>
+        <v>609</v>
       </c>
       <c r="C49" t="n">
         <v>8888</v>
       </c>
       <c r="D49" t="n">
-        <v>1251.14</v>
+        <v>2500.68</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1376,17 +1376,17 @@
         <v>46217</v>
       </c>
       <c r="B50" t="n">
-        <v>325</v>
+        <v>2507</v>
       </c>
       <c r="C50" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D50" t="n">
-        <v>868.83</v>
+        <v>448.36</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1395,17 +1395,17 @@
         <v>46217</v>
       </c>
       <c r="B51" t="n">
-        <v>2660</v>
+        <v>2767</v>
       </c>
       <c r="C51" t="n">
         <v>8888</v>
       </c>
       <c r="D51" t="n">
-        <v>281.24</v>
+        <v>1175.73</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1414,17 +1414,17 @@
         <v>46217</v>
       </c>
       <c r="B52" t="n">
-        <v>610</v>
+        <v>1063</v>
       </c>
       <c r="C52" t="n">
         <v>8888</v>
       </c>
       <c r="D52" t="n">
-        <v>235.34</v>
+        <v>1251.14</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1433,17 +1433,17 @@
         <v>46217</v>
       </c>
       <c r="B53" t="n">
-        <v>424</v>
+        <v>325</v>
       </c>
       <c r="C53" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D53" t="n">
-        <v>3214.29</v>
+        <v>868.83</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1452,17 +1452,17 @@
         <v>46217</v>
       </c>
       <c r="B54" t="n">
-        <v>664</v>
+        <v>2660</v>
       </c>
       <c r="C54" t="n">
         <v>8888</v>
       </c>
       <c r="D54" t="n">
-        <v>364.07</v>
+        <v>281.24</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1471,17 +1471,17 @@
         <v>46217</v>
       </c>
       <c r="B55" t="n">
-        <v>2279</v>
+        <v>610</v>
       </c>
       <c r="C55" t="n">
-        <v>1139</v>
+        <v>8888</v>
       </c>
       <c r="D55" t="n">
-        <v>448.78</v>
+        <v>235.34</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1490,17 +1490,17 @@
         <v>46217</v>
       </c>
       <c r="B56" t="n">
-        <v>40</v>
+        <v>424</v>
       </c>
       <c r="C56" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D56" t="n">
-        <v>325.04</v>
+        <v>3214.29</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1509,17 +1509,17 @@
         <v>46217</v>
       </c>
       <c r="B57" t="n">
-        <v>2069</v>
+        <v>664</v>
       </c>
       <c r="C57" t="n">
         <v>8888</v>
       </c>
       <c r="D57" t="n">
-        <v>176.8</v>
+        <v>364.07</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1528,17 +1528,17 @@
         <v>46217</v>
       </c>
       <c r="B58" t="n">
-        <v>522</v>
+        <v>2279</v>
       </c>
       <c r="C58" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D58" t="n">
-        <v>151.86</v>
+        <v>448.78</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1547,13 +1547,13 @@
         <v>46217</v>
       </c>
       <c r="B59" t="n">
-        <v>1304</v>
+        <v>40</v>
       </c>
       <c r="C59" t="n">
-        <v>213</v>
+        <v>58</v>
       </c>
       <c r="D59" t="n">
-        <v>297.1</v>
+        <v>325.04</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -1566,17 +1566,17 @@
         <v>46217</v>
       </c>
       <c r="B60" t="n">
-        <v>1869</v>
+        <v>2069</v>
       </c>
       <c r="C60" t="n">
         <v>8888</v>
       </c>
       <c r="D60" t="n">
-        <v>447.76</v>
+        <v>176.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1585,17 +1585,17 @@
         <v>46217</v>
       </c>
       <c r="B61" t="n">
-        <v>949</v>
+        <v>522</v>
       </c>
       <c r="C61" t="n">
-        <v>998</v>
+        <v>8888</v>
       </c>
       <c r="D61" t="n">
-        <v>129.85</v>
+        <v>151.86</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1604,17 +1604,17 @@
         <v>46217</v>
       </c>
       <c r="B62" t="n">
-        <v>1853</v>
+        <v>1304</v>
       </c>
       <c r="C62" t="n">
-        <v>8888</v>
+        <v>213</v>
       </c>
       <c r="D62" t="n">
-        <v>522.4</v>
+        <v>297.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
         <v>46217</v>
       </c>
       <c r="B63" t="n">
-        <v>2250</v>
+        <v>1869</v>
       </c>
       <c r="C63" t="n">
         <v>8888</v>
       </c>
       <c r="D63" t="n">
-        <v>4131.57</v>
+        <v>447.76</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1642,17 +1642,17 @@
         <v>46217</v>
       </c>
       <c r="B64" t="n">
-        <v>2507</v>
+        <v>949</v>
       </c>
       <c r="C64" t="n">
-        <v>8888</v>
+        <v>998</v>
       </c>
       <c r="D64" t="n">
-        <v>4167.12</v>
+        <v>129.85</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1661,17 +1661,17 @@
         <v>46217</v>
       </c>
       <c r="B65" t="n">
-        <v>664</v>
+        <v>1317</v>
       </c>
       <c r="C65" t="n">
         <v>8888</v>
       </c>
       <c r="D65" t="n">
-        <v>4099.16</v>
+        <v>1445.46</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1680,13 +1680,13 @@
         <v>46217</v>
       </c>
       <c r="B66" t="n">
-        <v>1075</v>
+        <v>1853</v>
       </c>
       <c r="C66" t="n">
         <v>8888</v>
       </c>
       <c r="D66" t="n">
-        <v>1743.47</v>
+        <v>522.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -1699,13 +1699,13 @@
         <v>46217</v>
       </c>
       <c r="B67" t="n">
-        <v>1324</v>
+        <v>360</v>
       </c>
       <c r="C67" t="n">
-        <v>738</v>
+        <v>546</v>
       </c>
       <c r="D67" t="n">
-        <v>4548.42</v>
+        <v>9262</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -1718,17 +1718,17 @@
         <v>46217</v>
       </c>
       <c r="B68" t="n">
-        <v>1906</v>
+        <v>2250</v>
       </c>
       <c r="C68" t="n">
-        <v>1954</v>
+        <v>8888</v>
       </c>
       <c r="D68" t="n">
-        <v>1445.21</v>
+        <v>4131.57</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1737,17 +1737,17 @@
         <v>46217</v>
       </c>
       <c r="B69" t="n">
-        <v>595</v>
+        <v>2507</v>
       </c>
       <c r="C69" t="n">
-        <v>691</v>
+        <v>8888</v>
       </c>
       <c r="D69" t="n">
-        <v>314.52</v>
+        <v>4167.12</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1756,17 +1756,17 @@
         <v>46217</v>
       </c>
       <c r="B70" t="n">
-        <v>2696</v>
+        <v>664</v>
       </c>
       <c r="C70" t="n">
-        <v>1312</v>
+        <v>8888</v>
       </c>
       <c r="D70" t="n">
-        <v>677.76</v>
+        <v>4099.16</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1775,17 +1775,17 @@
         <v>46217</v>
       </c>
       <c r="B71" t="n">
-        <v>525</v>
+        <v>1075</v>
       </c>
       <c r="C71" t="n">
         <v>8888</v>
       </c>
       <c r="D71" t="n">
-        <v>490.08</v>
+        <v>1743.47</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1794,17 +1794,17 @@
         <v>46217</v>
       </c>
       <c r="B72" t="n">
-        <v>2491</v>
+        <v>1324</v>
       </c>
       <c r="C72" t="n">
-        <v>8888</v>
+        <v>738</v>
       </c>
       <c r="D72" t="n">
-        <v>2909.58</v>
+        <v>4548.42</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1813,13 +1813,13 @@
         <v>46217</v>
       </c>
       <c r="B73" t="n">
-        <v>360</v>
+        <v>1906</v>
       </c>
       <c r="C73" t="n">
-        <v>546</v>
+        <v>1954</v>
       </c>
       <c r="D73" t="n">
-        <v>7463.12</v>
+        <v>1445.21</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -1832,17 +1832,17 @@
         <v>46217</v>
       </c>
       <c r="B74" t="n">
-        <v>2651</v>
+        <v>595</v>
       </c>
       <c r="C74" t="n">
-        <v>8888</v>
+        <v>691</v>
       </c>
       <c r="D74" t="n">
-        <v>638.64</v>
+        <v>314.52</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1851,17 +1851,17 @@
         <v>46217</v>
       </c>
       <c r="B75" t="n">
-        <v>525</v>
+        <v>2696</v>
       </c>
       <c r="C75" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D75" t="n">
-        <v>4351.19</v>
+        <v>677.76</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1870,17 +1870,17 @@
         <v>46217</v>
       </c>
       <c r="B76" t="n">
-        <v>2124</v>
+        <v>525</v>
       </c>
       <c r="C76" t="n">
         <v>8888</v>
       </c>
       <c r="D76" t="n">
-        <v>3875.99</v>
+        <v>490.08</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1889,17 +1889,17 @@
         <v>46217</v>
       </c>
       <c r="B77" t="n">
-        <v>2695</v>
+        <v>2491</v>
       </c>
       <c r="C77" t="n">
         <v>8888</v>
       </c>
       <c r="D77" t="n">
-        <v>1244.27</v>
+        <v>2909.58</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1908,17 +1908,17 @@
         <v>46217</v>
       </c>
       <c r="B78" t="n">
-        <v>1293</v>
+        <v>2651</v>
       </c>
       <c r="C78" t="n">
         <v>8888</v>
       </c>
       <c r="D78" t="n">
-        <v>381.82</v>
+        <v>638.64</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1927,13 +1927,13 @@
         <v>46217</v>
       </c>
       <c r="B79" t="n">
-        <v>2363</v>
+        <v>525</v>
       </c>
       <c r="C79" t="n">
         <v>8888</v>
       </c>
       <c r="D79" t="n">
-        <v>2985.2</v>
+        <v>4351.19</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -1946,13 +1946,13 @@
         <v>46217</v>
       </c>
       <c r="B80" t="n">
-        <v>2663</v>
+        <v>2124</v>
       </c>
       <c r="C80" t="n">
         <v>8888</v>
       </c>
       <c r="D80" t="n">
-        <v>2146.08</v>
+        <v>3875.99</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -1965,17 +1965,17 @@
         <v>46217</v>
       </c>
       <c r="B81" t="n">
-        <v>2711</v>
+        <v>2695</v>
       </c>
       <c r="C81" t="n">
         <v>8888</v>
       </c>
       <c r="D81" t="n">
-        <v>2193.56</v>
+        <v>1244.27</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1984,17 +1984,17 @@
         <v>46217</v>
       </c>
       <c r="B82" t="n">
-        <v>1317</v>
+        <v>1293</v>
       </c>
       <c r="C82" t="n">
         <v>8888</v>
       </c>
       <c r="D82" t="n">
-        <v>787.51</v>
+        <v>381.82</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2003,17 +2003,17 @@
         <v>46217</v>
       </c>
       <c r="B83" t="n">
-        <v>675</v>
+        <v>2363</v>
       </c>
       <c r="C83" t="n">
         <v>8888</v>
       </c>
       <c r="D83" t="n">
-        <v>289.67</v>
+        <v>2985.2</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2022,13 +2022,13 @@
         <v>46217</v>
       </c>
       <c r="B84" t="n">
-        <v>1063</v>
+        <v>2663</v>
       </c>
       <c r="C84" t="n">
         <v>8888</v>
       </c>
       <c r="D84" t="n">
-        <v>1902.46</v>
+        <v>2146.08</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2041,13 +2041,13 @@
         <v>46217</v>
       </c>
       <c r="B85" t="n">
-        <v>1658</v>
+        <v>2711</v>
       </c>
       <c r="C85" t="n">
         <v>8888</v>
       </c>
       <c r="D85" t="n">
-        <v>1357.94</v>
+        <v>2193.56</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -2060,17 +2060,17 @@
         <v>46217</v>
       </c>
       <c r="B86" t="n">
-        <v>1392</v>
+        <v>675</v>
       </c>
       <c r="C86" t="n">
         <v>8888</v>
       </c>
       <c r="D86" t="n">
-        <v>814.61</v>
+        <v>289.67</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2079,17 +2079,17 @@
         <v>46217</v>
       </c>
       <c r="B87" t="n">
-        <v>360</v>
+        <v>1063</v>
       </c>
       <c r="C87" t="n">
         <v>8888</v>
       </c>
       <c r="D87" t="n">
-        <v>749.13</v>
+        <v>1902.46</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2098,17 +2098,17 @@
         <v>46217</v>
       </c>
       <c r="B88" t="n">
-        <v>1324</v>
+        <v>1658</v>
       </c>
       <c r="C88" t="n">
         <v>8888</v>
       </c>
       <c r="D88" t="n">
-        <v>327.19</v>
+        <v>1357.94</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2117,17 +2117,17 @@
         <v>46217</v>
       </c>
       <c r="B89" t="n">
-        <v>525</v>
+        <v>1392</v>
       </c>
       <c r="C89" t="n">
         <v>8888</v>
       </c>
       <c r="D89" t="n">
-        <v>643.3</v>
+        <v>814.61</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2136,17 +2136,17 @@
         <v>46217</v>
       </c>
       <c r="B90" t="n">
-        <v>949</v>
+        <v>1007</v>
       </c>
       <c r="C90" t="n">
-        <v>1134</v>
+        <v>8888</v>
       </c>
       <c r="D90" t="n">
-        <v>327.6</v>
+        <v>335.77</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2155,13 +2155,13 @@
         <v>46217</v>
       </c>
       <c r="B91" t="n">
-        <v>2133</v>
+        <v>360</v>
       </c>
       <c r="C91" t="n">
         <v>8888</v>
       </c>
       <c r="D91" t="n">
-        <v>66030.34</v>
+        <v>749.13</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -2174,13 +2174,13 @@
         <v>46217</v>
       </c>
       <c r="B92" t="n">
-        <v>326</v>
+        <v>1324</v>
       </c>
       <c r="C92" t="n">
         <v>8888</v>
       </c>
       <c r="D92" t="n">
-        <v>695.99</v>
+        <v>327.19</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -2193,17 +2193,17 @@
         <v>46217</v>
       </c>
       <c r="B93" t="n">
-        <v>325</v>
+        <v>525</v>
       </c>
       <c r="C93" t="n">
         <v>8888</v>
       </c>
       <c r="D93" t="n">
-        <v>774.73</v>
+        <v>643.3</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2212,13 +2212,13 @@
         <v>46217</v>
       </c>
       <c r="B94" t="n">
-        <v>1293</v>
+        <v>1956</v>
       </c>
       <c r="C94" t="n">
-        <v>1898</v>
+        <v>423</v>
       </c>
       <c r="D94" t="n">
-        <v>8365.559999999999</v>
+        <v>503.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -2231,17 +2231,17 @@
         <v>46217</v>
       </c>
       <c r="B95" t="n">
-        <v>131</v>
+        <v>569</v>
       </c>
       <c r="C95" t="n">
         <v>8888</v>
       </c>
       <c r="D95" t="n">
-        <v>1969.93</v>
+        <v>13256.49</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2250,17 +2250,17 @@
         <v>46217</v>
       </c>
       <c r="B96" t="n">
-        <v>2697</v>
+        <v>949</v>
       </c>
       <c r="C96" t="n">
-        <v>8888</v>
+        <v>1134</v>
       </c>
       <c r="D96" t="n">
-        <v>420.48</v>
+        <v>327.6</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2269,17 +2269,17 @@
         <v>46217</v>
       </c>
       <c r="B97" t="n">
-        <v>2279</v>
+        <v>326</v>
       </c>
       <c r="C97" t="n">
-        <v>8888</v>
+        <v>1110</v>
       </c>
       <c r="D97" t="n">
-        <v>1034.25</v>
+        <v>2424.03</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
         <v>46217</v>
       </c>
       <c r="B98" t="n">
-        <v>1340</v>
+        <v>2133</v>
       </c>
       <c r="C98" t="n">
         <v>8888</v>
       </c>
       <c r="D98" t="n">
-        <v>3037.55</v>
+        <v>66030.34</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2307,13 +2307,13 @@
         <v>46217</v>
       </c>
       <c r="B99" t="n">
-        <v>2641</v>
+        <v>326</v>
       </c>
       <c r="C99" t="n">
         <v>8888</v>
       </c>
       <c r="D99" t="n">
-        <v>557.52</v>
+        <v>713</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -2326,13 +2326,13 @@
         <v>46217</v>
       </c>
       <c r="B100" t="n">
-        <v>1116</v>
+        <v>629</v>
       </c>
       <c r="C100" t="n">
         <v>8888</v>
       </c>
       <c r="D100" t="n">
-        <v>1293.89</v>
+        <v>1759.43</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -2345,17 +2345,17 @@
         <v>46217</v>
       </c>
       <c r="B101" t="n">
-        <v>2178</v>
+        <v>325</v>
       </c>
       <c r="C101" t="n">
         <v>8888</v>
       </c>
       <c r="D101" t="n">
-        <v>5333.4</v>
+        <v>774.73</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2364,17 +2364,17 @@
         <v>46217</v>
       </c>
       <c r="B102" t="n">
-        <v>1756</v>
+        <v>1293</v>
       </c>
       <c r="C102" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D102" t="n">
-        <v>742.23</v>
+        <v>8365.559999999999</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2389,11 +2389,11 @@
         <v>8888</v>
       </c>
       <c r="D103" t="n">
-        <v>5470.1</v>
+        <v>1969.93</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2402,17 +2402,17 @@
         <v>46217</v>
       </c>
       <c r="B104" t="n">
-        <v>2081</v>
+        <v>2697</v>
       </c>
       <c r="C104" t="n">
         <v>8888</v>
       </c>
       <c r="D104" t="n">
-        <v>1022.42</v>
+        <v>420.48</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2421,17 +2421,17 @@
         <v>46217</v>
       </c>
       <c r="B105" t="n">
-        <v>1374</v>
+        <v>2279</v>
       </c>
       <c r="C105" t="n">
-        <v>2845</v>
+        <v>8888</v>
       </c>
       <c r="D105" t="n">
-        <v>625.77</v>
+        <v>1034.25</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2440,17 +2440,17 @@
         <v>46217</v>
       </c>
       <c r="B106" t="n">
-        <v>58</v>
+        <v>1340</v>
       </c>
       <c r="C106" t="n">
         <v>8888</v>
       </c>
       <c r="D106" t="n">
-        <v>3050.12</v>
+        <v>3037.55</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2459,17 +2459,17 @@
         <v>46217</v>
       </c>
       <c r="B107" t="n">
-        <v>1937</v>
+        <v>2641</v>
       </c>
       <c r="C107" t="n">
         <v>8888</v>
       </c>
       <c r="D107" t="n">
-        <v>2199.57</v>
+        <v>557.52</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2478,17 +2478,17 @@
         <v>46217</v>
       </c>
       <c r="B108" t="n">
-        <v>1983</v>
+        <v>1116</v>
       </c>
       <c r="C108" t="n">
         <v>8888</v>
       </c>
       <c r="D108" t="n">
-        <v>412.16</v>
+        <v>1293.89</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2497,17 +2497,17 @@
         <v>46217</v>
       </c>
       <c r="B109" t="n">
-        <v>451</v>
+        <v>2178</v>
       </c>
       <c r="C109" t="n">
         <v>8888</v>
       </c>
       <c r="D109" t="n">
-        <v>2583.46</v>
+        <v>5333.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2516,17 +2516,17 @@
         <v>46217</v>
       </c>
       <c r="B110" t="n">
-        <v>1102</v>
+        <v>1756</v>
       </c>
       <c r="C110" t="n">
-        <v>13148</v>
+        <v>8888</v>
       </c>
       <c r="D110" t="n">
-        <v>1346.4</v>
+        <v>742.23</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2535,13 +2535,13 @@
         <v>46217</v>
       </c>
       <c r="B111" t="n">
-        <v>2767</v>
+        <v>131</v>
       </c>
       <c r="C111" t="n">
         <v>8888</v>
       </c>
       <c r="D111" t="n">
-        <v>920.85</v>
+        <v>6513.46</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -2554,13 +2554,13 @@
         <v>46217</v>
       </c>
       <c r="B112" t="n">
-        <v>2697</v>
+        <v>2081</v>
       </c>
       <c r="C112" t="n">
         <v>8888</v>
       </c>
       <c r="D112" t="n">
-        <v>2880.19</v>
+        <v>1022.42</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -2573,17 +2573,17 @@
         <v>46217</v>
       </c>
       <c r="B113" t="n">
-        <v>569</v>
+        <v>1374</v>
       </c>
       <c r="C113" t="n">
-        <v>8888</v>
+        <v>2845</v>
       </c>
       <c r="D113" t="n">
-        <v>3002.06</v>
+        <v>625.77</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2592,17 +2592,17 @@
         <v>46217</v>
       </c>
       <c r="B114" t="n">
-        <v>2211</v>
+        <v>58</v>
       </c>
       <c r="C114" t="n">
-        <v>874</v>
+        <v>8888</v>
       </c>
       <c r="D114" t="n">
-        <v>1833.56</v>
+        <v>3050.12</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2611,17 +2611,17 @@
         <v>46217</v>
       </c>
       <c r="B115" t="n">
-        <v>1063</v>
+        <v>1937</v>
       </c>
       <c r="C115" t="n">
         <v>8888</v>
       </c>
       <c r="D115" t="n">
-        <v>352.87</v>
+        <v>2199.57</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2630,17 +2630,17 @@
         <v>46217</v>
       </c>
       <c r="B116" t="n">
-        <v>2687</v>
+        <v>1983</v>
       </c>
       <c r="C116" t="n">
         <v>8888</v>
       </c>
       <c r="D116" t="n">
-        <v>1760.22</v>
+        <v>412.16</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2649,13 +2649,13 @@
         <v>46217</v>
       </c>
       <c r="B117" t="n">
-        <v>629</v>
+        <v>451</v>
       </c>
       <c r="C117" t="n">
         <v>8888</v>
       </c>
       <c r="D117" t="n">
-        <v>559.15</v>
+        <v>2583.46</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -2668,17 +2668,17 @@
         <v>46217</v>
       </c>
       <c r="B118" t="n">
-        <v>1117</v>
+        <v>1102</v>
       </c>
       <c r="C118" t="n">
-        <v>8888</v>
+        <v>13148</v>
       </c>
       <c r="D118" t="n">
-        <v>1988.42</v>
+        <v>1346.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2687,17 +2687,17 @@
         <v>46217</v>
       </c>
       <c r="B119" t="n">
-        <v>1890</v>
+        <v>2767</v>
       </c>
       <c r="C119" t="n">
-        <v>1953</v>
+        <v>8888</v>
       </c>
       <c r="D119" t="n">
-        <v>1122</v>
+        <v>920.85</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2706,13 +2706,13 @@
         <v>46217</v>
       </c>
       <c r="B120" t="n">
-        <v>1289</v>
+        <v>2697</v>
       </c>
       <c r="C120" t="n">
         <v>8888</v>
       </c>
       <c r="D120" t="n">
-        <v>1214.09</v>
+        <v>2880.19</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -2725,17 +2725,17 @@
         <v>46217</v>
       </c>
       <c r="B121" t="n">
-        <v>2363</v>
+        <v>2211</v>
       </c>
       <c r="C121" t="n">
-        <v>8888</v>
+        <v>874</v>
       </c>
       <c r="D121" t="n">
-        <v>301.92</v>
+        <v>1833.56</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2744,17 +2744,17 @@
         <v>46217</v>
       </c>
       <c r="B122" t="n">
-        <v>1075</v>
+        <v>1063</v>
       </c>
       <c r="C122" t="n">
         <v>8888</v>
       </c>
       <c r="D122" t="n">
-        <v>1845.09</v>
+        <v>352.87</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2763,17 +2763,17 @@
         <v>46217</v>
       </c>
       <c r="B123" t="n">
-        <v>2107</v>
+        <v>2687</v>
       </c>
       <c r="C123" t="n">
-        <v>1954</v>
+        <v>8888</v>
       </c>
       <c r="D123" t="n">
-        <v>2000.86</v>
+        <v>1760.22</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2782,17 +2782,17 @@
         <v>46217</v>
       </c>
       <c r="B124" t="n">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="C124" t="n">
         <v>8888</v>
       </c>
       <c r="D124" t="n">
-        <v>1065.24</v>
+        <v>1988.42</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2801,17 +2801,17 @@
         <v>46217</v>
       </c>
       <c r="B125" t="n">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="C125" t="n">
-        <v>8888</v>
+        <v>1953</v>
       </c>
       <c r="D125" t="n">
-        <v>2781.91</v>
+        <v>1122</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2820,17 +2820,17 @@
         <v>46217</v>
       </c>
       <c r="B126" t="n">
-        <v>559</v>
+        <v>1289</v>
       </c>
       <c r="C126" t="n">
-        <v>3009</v>
+        <v>8888</v>
       </c>
       <c r="D126" t="n">
-        <v>1194.24</v>
+        <v>1214.09</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2839,13 +2839,13 @@
         <v>46217</v>
       </c>
       <c r="B127" t="n">
-        <v>1278</v>
+        <v>2363</v>
       </c>
       <c r="C127" t="n">
         <v>8888</v>
       </c>
       <c r="D127" t="n">
-        <v>508.07</v>
+        <v>301.92</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -2858,17 +2858,17 @@
         <v>46217</v>
       </c>
       <c r="B128" t="n">
-        <v>58</v>
+        <v>1075</v>
       </c>
       <c r="C128" t="n">
         <v>8888</v>
       </c>
       <c r="D128" t="n">
-        <v>1411.43</v>
+        <v>1845.09</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2877,17 +2877,17 @@
         <v>46217</v>
       </c>
       <c r="B129" t="n">
-        <v>629</v>
+        <v>2107</v>
       </c>
       <c r="C129" t="n">
-        <v>8888</v>
+        <v>1954</v>
       </c>
       <c r="D129" t="n">
-        <v>2049.78</v>
+        <v>2000.86</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2896,13 +2896,13 @@
         <v>46217</v>
       </c>
       <c r="B130" t="n">
-        <v>595</v>
+        <v>1116</v>
       </c>
       <c r="C130" t="n">
         <v>8888</v>
       </c>
       <c r="D130" t="n">
-        <v>3191</v>
+        <v>1065.24</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -2915,17 +2915,17 @@
         <v>46217</v>
       </c>
       <c r="B131" t="n">
-        <v>949</v>
+        <v>2190</v>
       </c>
       <c r="C131" t="n">
-        <v>1762</v>
+        <v>8888</v>
       </c>
       <c r="D131" t="n">
-        <v>325.65</v>
+        <v>2781.91</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2934,17 +2934,17 @@
         <v>46217</v>
       </c>
       <c r="B132" t="n">
-        <v>2463</v>
+        <v>559</v>
       </c>
       <c r="C132" t="n">
-        <v>8888</v>
+        <v>3009</v>
       </c>
       <c r="D132" t="n">
-        <v>8336.43</v>
+        <v>1194.24</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2953,17 +2953,17 @@
         <v>46217</v>
       </c>
       <c r="B133" t="n">
-        <v>1064</v>
+        <v>1278</v>
       </c>
       <c r="C133" t="n">
         <v>8888</v>
       </c>
       <c r="D133" t="n">
-        <v>1513.21</v>
+        <v>508.07</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2972,17 +2972,17 @@
         <v>46217</v>
       </c>
       <c r="B134" t="n">
-        <v>1478</v>
+        <v>58</v>
       </c>
       <c r="C134" t="n">
         <v>8888</v>
       </c>
       <c r="D134" t="n">
-        <v>4067.5</v>
+        <v>1411.43</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2991,17 +2991,17 @@
         <v>46217</v>
       </c>
       <c r="B135" t="n">
-        <v>438</v>
+        <v>629</v>
       </c>
       <c r="C135" t="n">
-        <v>2845</v>
+        <v>8888</v>
       </c>
       <c r="D135" t="n">
-        <v>826.76</v>
+        <v>2740.86</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3010,17 +3010,17 @@
         <v>46217</v>
       </c>
       <c r="B136" t="n">
-        <v>2539</v>
+        <v>595</v>
       </c>
       <c r="C136" t="n">
-        <v>3009</v>
+        <v>8888</v>
       </c>
       <c r="D136" t="n">
-        <v>1479.56</v>
+        <v>3191</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3029,17 +3029,17 @@
         <v>46217</v>
       </c>
       <c r="B137" t="n">
-        <v>358</v>
+        <v>949</v>
       </c>
       <c r="C137" t="n">
-        <v>8888</v>
+        <v>1762</v>
       </c>
       <c r="D137" t="n">
-        <v>1918.33</v>
+        <v>325.65</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3048,17 +3048,17 @@
         <v>46217</v>
       </c>
       <c r="B138" t="n">
-        <v>2107</v>
+        <v>2463</v>
       </c>
       <c r="C138" t="n">
         <v>8888</v>
       </c>
       <c r="D138" t="n">
-        <v>4459.75</v>
+        <v>8336.43</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3067,17 +3067,17 @@
         <v>46217</v>
       </c>
       <c r="B139" t="n">
-        <v>675</v>
+        <v>1064</v>
       </c>
       <c r="C139" t="n">
         <v>8888</v>
       </c>
       <c r="D139" t="n">
-        <v>1559.23</v>
+        <v>1513.21</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3086,13 +3086,13 @@
         <v>46217</v>
       </c>
       <c r="B140" t="n">
-        <v>2279</v>
+        <v>1478</v>
       </c>
       <c r="C140" t="n">
         <v>8888</v>
       </c>
       <c r="D140" t="n">
-        <v>1165.17</v>
+        <v>4067.5</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -3105,13 +3105,13 @@
         <v>46217</v>
       </c>
       <c r="B141" t="n">
-        <v>2727</v>
+        <v>438</v>
       </c>
       <c r="C141" t="n">
-        <v>3179</v>
+        <v>2845</v>
       </c>
       <c r="D141" t="n">
-        <v>514.7</v>
+        <v>826.76</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -3124,13 +3124,13 @@
         <v>46217</v>
       </c>
       <c r="B142" t="n">
-        <v>451</v>
+        <v>2539</v>
       </c>
       <c r="C142" t="n">
-        <v>3403</v>
+        <v>3009</v>
       </c>
       <c r="D142" t="n">
-        <v>327.28</v>
+        <v>1479.56</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -3143,13 +3143,13 @@
         <v>46217</v>
       </c>
       <c r="B143" t="n">
-        <v>535</v>
+        <v>358</v>
       </c>
       <c r="C143" t="n">
         <v>8888</v>
       </c>
       <c r="D143" t="n">
-        <v>1369.04</v>
+        <v>1918.33</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -3162,17 +3162,17 @@
         <v>46217</v>
       </c>
       <c r="B144" t="n">
-        <v>2571</v>
+        <v>2107</v>
       </c>
       <c r="C144" t="n">
-        <v>1312</v>
+        <v>8888</v>
       </c>
       <c r="D144" t="n">
-        <v>2202.75</v>
+        <v>4459.75</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3181,13 +3181,13 @@
         <v>46217</v>
       </c>
       <c r="B145" t="n">
-        <v>2782</v>
+        <v>675</v>
       </c>
       <c r="C145" t="n">
         <v>8888</v>
       </c>
       <c r="D145" t="n">
-        <v>753.8</v>
+        <v>1559.23</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -3200,17 +3200,17 @@
         <v>46217</v>
       </c>
       <c r="B146" t="n">
-        <v>610</v>
+        <v>2516</v>
       </c>
       <c r="C146" t="n">
         <v>8888</v>
       </c>
       <c r="D146" t="n">
-        <v>335.61</v>
+        <v>502.61</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3219,17 +3219,17 @@
         <v>46217</v>
       </c>
       <c r="B147" t="n">
-        <v>2245</v>
+        <v>2279</v>
       </c>
       <c r="C147" t="n">
         <v>8888</v>
       </c>
       <c r="D147" t="n">
-        <v>355.88</v>
+        <v>1165.17</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3238,17 +3238,17 @@
         <v>46217</v>
       </c>
       <c r="B148" t="n">
-        <v>619</v>
+        <v>2727</v>
       </c>
       <c r="C148" t="n">
-        <v>8888</v>
+        <v>3179</v>
       </c>
       <c r="D148" t="n">
-        <v>3019.73</v>
+        <v>514.7</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3257,17 +3257,17 @@
         <v>46217</v>
       </c>
       <c r="B149" t="n">
-        <v>1108</v>
+        <v>451</v>
       </c>
       <c r="C149" t="n">
-        <v>8888</v>
+        <v>3403</v>
       </c>
       <c r="D149" t="n">
-        <v>508.54</v>
+        <v>327.28</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3276,17 +3276,17 @@
         <v>46217</v>
       </c>
       <c r="B150" t="n">
-        <v>341</v>
+        <v>535</v>
       </c>
       <c r="C150" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D150" t="n">
-        <v>366.88</v>
+        <v>1369.04</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3295,13 +3295,13 @@
         <v>46217</v>
       </c>
       <c r="B151" t="n">
-        <v>525</v>
+        <v>2571</v>
       </c>
       <c r="C151" t="n">
-        <v>1087</v>
+        <v>1312</v>
       </c>
       <c r="D151" t="n">
-        <v>1830.26</v>
+        <v>2202.75</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -3314,17 +3314,17 @@
         <v>46217</v>
       </c>
       <c r="B152" t="n">
-        <v>1344</v>
+        <v>2782</v>
       </c>
       <c r="C152" t="n">
-        <v>2845</v>
+        <v>8888</v>
       </c>
       <c r="D152" t="n">
-        <v>394.8</v>
+        <v>753.8</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3333,17 +3333,17 @@
         <v>46217</v>
       </c>
       <c r="B153" t="n">
-        <v>1653</v>
+        <v>610</v>
       </c>
       <c r="C153" t="n">
         <v>8888</v>
       </c>
       <c r="D153" t="n">
-        <v>4383.69</v>
+        <v>1073.07</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
         <v>46217</v>
       </c>
       <c r="B154" t="n">
-        <v>1518</v>
+        <v>2245</v>
       </c>
       <c r="C154" t="n">
-        <v>1533</v>
+        <v>8888</v>
       </c>
       <c r="D154" t="n">
-        <v>479.84</v>
+        <v>355.88</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3371,17 +3371,17 @@
         <v>46217</v>
       </c>
       <c r="B155" t="n">
-        <v>663</v>
+        <v>619</v>
       </c>
       <c r="C155" t="n">
         <v>8888</v>
       </c>
       <c r="D155" t="n">
-        <v>824.5599999999999</v>
+        <v>4404.7</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3390,17 +3390,17 @@
         <v>46217</v>
       </c>
       <c r="B156" t="n">
-        <v>1278</v>
+        <v>1108</v>
       </c>
       <c r="C156" t="n">
         <v>8888</v>
       </c>
       <c r="D156" t="n">
-        <v>1267.68</v>
+        <v>508.54</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3409,13 +3409,13 @@
         <v>46217</v>
       </c>
       <c r="B157" t="n">
-        <v>2089</v>
+        <v>341</v>
       </c>
       <c r="C157" t="n">
-        <v>1533</v>
+        <v>58</v>
       </c>
       <c r="D157" t="n">
-        <v>822.05</v>
+        <v>366.88</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -3428,13 +3428,13 @@
         <v>46217</v>
       </c>
       <c r="B158" t="n">
-        <v>2133</v>
+        <v>525</v>
       </c>
       <c r="C158" t="n">
-        <v>691</v>
+        <v>1087</v>
       </c>
       <c r="D158" t="n">
-        <v>1414.98</v>
+        <v>1830.26</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -3447,13 +3447,13 @@
         <v>46217</v>
       </c>
       <c r="B159" t="n">
-        <v>429</v>
+        <v>1344</v>
       </c>
       <c r="C159" t="n">
-        <v>2571</v>
+        <v>2845</v>
       </c>
       <c r="D159" t="n">
-        <v>667.12</v>
+        <v>394.8</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -3466,17 +3466,17 @@
         <v>46217</v>
       </c>
       <c r="B160" t="n">
-        <v>2641</v>
+        <v>1653</v>
       </c>
       <c r="C160" t="n">
         <v>8888</v>
       </c>
       <c r="D160" t="n">
-        <v>252.41</v>
+        <v>4383.69</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3485,13 +3485,13 @@
         <v>46217</v>
       </c>
       <c r="B161" t="n">
-        <v>351</v>
+        <v>1518</v>
       </c>
       <c r="C161" t="n">
-        <v>3009</v>
+        <v>1533</v>
       </c>
       <c r="D161" t="n">
-        <v>1007.64</v>
+        <v>479.84</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -3504,17 +3504,17 @@
         <v>46217</v>
       </c>
       <c r="B162" t="n">
-        <v>1137</v>
+        <v>663</v>
       </c>
       <c r="C162" t="n">
         <v>8888</v>
       </c>
       <c r="D162" t="n">
-        <v>5032.13</v>
+        <v>824.5599999999999</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3523,17 +3523,17 @@
         <v>46217</v>
       </c>
       <c r="B163" t="n">
-        <v>1293</v>
+        <v>1075</v>
       </c>
       <c r="C163" t="n">
-        <v>8888</v>
+        <v>675</v>
       </c>
       <c r="D163" t="n">
-        <v>8102.01</v>
+        <v>274.23</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3542,13 +3542,13 @@
         <v>46217</v>
       </c>
       <c r="B164" t="n">
-        <v>1465</v>
+        <v>1278</v>
       </c>
       <c r="C164" t="n">
         <v>8888</v>
       </c>
       <c r="D164" t="n">
-        <v>1609</v>
+        <v>1267.68</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -3561,17 +3561,17 @@
         <v>46217</v>
       </c>
       <c r="B165" t="n">
-        <v>483</v>
+        <v>2089</v>
       </c>
       <c r="C165" t="n">
-        <v>8888</v>
+        <v>1533</v>
       </c>
       <c r="D165" t="n">
-        <v>2444.39</v>
+        <v>822.05</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3580,17 +3580,17 @@
         <v>46217</v>
       </c>
       <c r="B166" t="n">
-        <v>1064</v>
+        <v>2133</v>
       </c>
       <c r="C166" t="n">
-        <v>8888</v>
+        <v>691</v>
       </c>
       <c r="D166" t="n">
-        <v>104632.21</v>
+        <v>1414.98</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3599,17 +3599,17 @@
         <v>46217</v>
       </c>
       <c r="B167" t="n">
-        <v>131</v>
+        <v>636</v>
       </c>
       <c r="C167" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D167" t="n">
-        <v>876.48</v>
+        <v>245.25</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3618,17 +3618,17 @@
         <v>46217</v>
       </c>
       <c r="B168" t="n">
-        <v>663</v>
+        <v>429</v>
       </c>
       <c r="C168" t="n">
-        <v>8888</v>
+        <v>2571</v>
       </c>
       <c r="D168" t="n">
-        <v>1769.59</v>
+        <v>667.12</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3637,17 +3637,17 @@
         <v>46217</v>
       </c>
       <c r="B169" t="n">
-        <v>131</v>
+        <v>2641</v>
       </c>
       <c r="C169" t="n">
         <v>8888</v>
       </c>
       <c r="D169" t="n">
-        <v>4787.28</v>
+        <v>252.41</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3656,13 +3656,13 @@
         <v>46217</v>
       </c>
       <c r="B170" t="n">
-        <v>2308</v>
+        <v>351</v>
       </c>
       <c r="C170" t="n">
-        <v>546</v>
+        <v>3009</v>
       </c>
       <c r="D170" t="n">
-        <v>1292.23</v>
+        <v>1007.64</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -3675,13 +3675,13 @@
         <v>46217</v>
       </c>
       <c r="B171" t="n">
-        <v>2709</v>
+        <v>716</v>
       </c>
       <c r="C171" t="n">
-        <v>2220</v>
+        <v>891</v>
       </c>
       <c r="D171" t="n">
-        <v>1663.5</v>
+        <v>17820</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -3694,17 +3694,17 @@
         <v>46217</v>
       </c>
       <c r="B172" t="n">
-        <v>1937</v>
+        <v>1137</v>
       </c>
       <c r="C172" t="n">
         <v>8888</v>
       </c>
       <c r="D172" t="n">
-        <v>1492.4</v>
+        <v>5032.13</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3713,17 +3713,17 @@
         <v>46217</v>
       </c>
       <c r="B173" t="n">
-        <v>429</v>
+        <v>1293</v>
       </c>
       <c r="C173" t="n">
-        <v>1281</v>
+        <v>8888</v>
       </c>
       <c r="D173" t="n">
-        <v>2195.97</v>
+        <v>8102.01</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3732,17 +3732,17 @@
         <v>46217</v>
       </c>
       <c r="B174" t="n">
-        <v>2211</v>
+        <v>1465</v>
       </c>
       <c r="C174" t="n">
         <v>8888</v>
       </c>
       <c r="D174" t="n">
-        <v>8568.99</v>
+        <v>2218.99</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3751,17 +3751,17 @@
         <v>46217</v>
       </c>
       <c r="B175" t="n">
-        <v>360</v>
+        <v>483</v>
       </c>
       <c r="C175" t="n">
         <v>8888</v>
       </c>
       <c r="D175" t="n">
-        <v>15052.63</v>
+        <v>2444.39</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3770,17 +3770,17 @@
         <v>46217</v>
       </c>
       <c r="B176" t="n">
-        <v>2251</v>
+        <v>2109</v>
       </c>
       <c r="C176" t="n">
         <v>8888</v>
       </c>
       <c r="D176" t="n">
-        <v>797.58</v>
+        <v>433.47</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3789,13 +3789,13 @@
         <v>46217</v>
       </c>
       <c r="B177" t="n">
-        <v>451</v>
+        <v>1064</v>
       </c>
       <c r="C177" t="n">
         <v>8888</v>
       </c>
       <c r="D177" t="n">
-        <v>1371.26</v>
+        <v>104632.21</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -3808,17 +3808,17 @@
         <v>46217</v>
       </c>
       <c r="B178" t="n">
-        <v>40</v>
+        <v>131</v>
       </c>
       <c r="C178" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D178" t="n">
-        <v>1093.47</v>
+        <v>876.48</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3827,17 +3827,17 @@
         <v>46217</v>
       </c>
       <c r="B179" t="n">
-        <v>530</v>
+        <v>663</v>
       </c>
       <c r="C179" t="n">
         <v>8888</v>
       </c>
       <c r="D179" t="n">
-        <v>180.08</v>
+        <v>1769.59</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3846,17 +3846,17 @@
         <v>46217</v>
       </c>
       <c r="B180" t="n">
-        <v>1327</v>
+        <v>767</v>
       </c>
       <c r="C180" t="n">
-        <v>3009</v>
+        <v>8888</v>
       </c>
       <c r="D180" t="n">
-        <v>946.8</v>
+        <v>1127.17</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3865,17 +3865,17 @@
         <v>46217</v>
       </c>
       <c r="B181" t="n">
-        <v>1293</v>
+        <v>131</v>
       </c>
       <c r="C181" t="n">
-        <v>601</v>
+        <v>8888</v>
       </c>
       <c r="D181" t="n">
-        <v>456.47</v>
+        <v>4787.28</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3884,17 +3884,17 @@
         <v>46217</v>
       </c>
       <c r="B182" t="n">
-        <v>424</v>
+        <v>2308</v>
       </c>
       <c r="C182" t="n">
-        <v>8888</v>
+        <v>546</v>
       </c>
       <c r="D182" t="n">
-        <v>1758.85</v>
+        <v>1292.23</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3903,17 +3903,17 @@
         <v>46217</v>
       </c>
       <c r="B183" t="n">
-        <v>2118</v>
+        <v>2709</v>
       </c>
       <c r="C183" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D183" t="n">
-        <v>311.54</v>
+        <v>1663.5</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3922,13 +3922,13 @@
         <v>46217</v>
       </c>
       <c r="B184" t="n">
-        <v>2251</v>
+        <v>1937</v>
       </c>
       <c r="C184" t="n">
         <v>8888</v>
       </c>
       <c r="D184" t="n">
-        <v>603.66</v>
+        <v>1492.4</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -3941,17 +3941,17 @@
         <v>46217</v>
       </c>
       <c r="B185" t="n">
-        <v>1478</v>
+        <v>2345</v>
       </c>
       <c r="C185" t="n">
-        <v>675</v>
+        <v>8888</v>
       </c>
       <c r="D185" t="n">
-        <v>945.74</v>
+        <v>1562.35</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3960,13 +3960,13 @@
         <v>46217</v>
       </c>
       <c r="B186" t="n">
-        <v>1299</v>
+        <v>429</v>
       </c>
       <c r="C186" t="n">
-        <v>27</v>
+        <v>1281</v>
       </c>
       <c r="D186" t="n">
-        <v>3625.32</v>
+        <v>2195.97</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -3979,17 +3979,17 @@
         <v>46217</v>
       </c>
       <c r="B187" t="n">
-        <v>559</v>
+        <v>2211</v>
       </c>
       <c r="C187" t="n">
         <v>8888</v>
       </c>
       <c r="D187" t="n">
-        <v>1064.63</v>
+        <v>8568.99</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3998,17 +3998,17 @@
         <v>46217</v>
       </c>
       <c r="B188" t="n">
-        <v>89</v>
+        <v>559</v>
       </c>
       <c r="C188" t="n">
         <v>8888</v>
       </c>
       <c r="D188" t="n">
-        <v>1506.42</v>
+        <v>4021.32</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4017,17 +4017,17 @@
         <v>46217</v>
       </c>
       <c r="B189" t="n">
-        <v>2250</v>
+        <v>360</v>
       </c>
       <c r="C189" t="n">
         <v>8888</v>
       </c>
       <c r="D189" t="n">
-        <v>1943.54</v>
+        <v>15052.63</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4036,17 +4036,17 @@
         <v>46217</v>
       </c>
       <c r="B190" t="n">
-        <v>1327</v>
+        <v>1478</v>
       </c>
       <c r="C190" t="n">
-        <v>8888</v>
+        <v>675</v>
       </c>
       <c r="D190" t="n">
-        <v>319.23</v>
+        <v>1662.17</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4055,17 +4055,17 @@
         <v>46217</v>
       </c>
       <c r="B191" t="n">
-        <v>326</v>
+        <v>2251</v>
       </c>
       <c r="C191" t="n">
         <v>8888</v>
       </c>
       <c r="D191" t="n">
-        <v>151.86</v>
+        <v>797.58</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4074,17 +4074,17 @@
         <v>46217</v>
       </c>
       <c r="B192" t="n">
-        <v>1372</v>
+        <v>2250</v>
       </c>
       <c r="C192" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D192" t="n">
-        <v>1088.02</v>
+        <v>2622.81</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4093,13 +4093,13 @@
         <v>46217</v>
       </c>
       <c r="B193" t="n">
-        <v>767</v>
+        <v>451</v>
       </c>
       <c r="C193" t="n">
         <v>8888</v>
       </c>
       <c r="D193" t="n">
-        <v>472.62</v>
+        <v>1371.26</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -4112,17 +4112,17 @@
         <v>46217</v>
       </c>
       <c r="B194" t="n">
-        <v>626</v>
+        <v>40</v>
       </c>
       <c r="C194" t="n">
         <v>8888</v>
       </c>
       <c r="D194" t="n">
-        <v>24505.65</v>
+        <v>1093.47</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4131,17 +4131,17 @@
         <v>46217</v>
       </c>
       <c r="B195" t="n">
-        <v>2651</v>
+        <v>530</v>
       </c>
       <c r="C195" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D195" t="n">
-        <v>648.71</v>
+        <v>180.08</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4150,13 +4150,13 @@
         <v>46217</v>
       </c>
       <c r="B196" t="n">
-        <v>2114</v>
+        <v>1327</v>
       </c>
       <c r="C196" t="n">
-        <v>1954</v>
+        <v>3009</v>
       </c>
       <c r="D196" t="n">
-        <v>879.03</v>
+        <v>946.8</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -4169,17 +4169,17 @@
         <v>46217</v>
       </c>
       <c r="B197" t="n">
-        <v>40</v>
+        <v>1293</v>
       </c>
       <c r="C197" t="n">
-        <v>8888</v>
+        <v>601</v>
       </c>
       <c r="D197" t="n">
-        <v>3583.39</v>
+        <v>456.47</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4188,17 +4188,17 @@
         <v>46217</v>
       </c>
       <c r="B198" t="n">
-        <v>40</v>
+        <v>424</v>
       </c>
       <c r="C198" t="n">
         <v>8888</v>
       </c>
       <c r="D198" t="n">
-        <v>2529.31</v>
+        <v>1758.85</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4207,17 +4207,17 @@
         <v>46217</v>
       </c>
       <c r="B199" t="n">
-        <v>363</v>
+        <v>2118</v>
       </c>
       <c r="C199" t="n">
         <v>8888</v>
       </c>
       <c r="D199" t="n">
-        <v>739.17</v>
+        <v>311.54</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4226,17 +4226,17 @@
         <v>46217</v>
       </c>
       <c r="B200" t="n">
-        <v>675</v>
+        <v>2251</v>
       </c>
       <c r="C200" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D200" t="n">
-        <v>107.13</v>
+        <v>603.66</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4245,17 +4245,17 @@
         <v>46217</v>
       </c>
       <c r="B201" t="n">
-        <v>636</v>
+        <v>1299</v>
       </c>
       <c r="C201" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D201" t="n">
-        <v>7476.56</v>
+        <v>3625.32</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4264,17 +4264,17 @@
         <v>46217</v>
       </c>
       <c r="B202" t="n">
-        <v>1075</v>
+        <v>89</v>
       </c>
       <c r="C202" t="n">
         <v>8888</v>
       </c>
       <c r="D202" t="n">
-        <v>1331.89</v>
+        <v>1506.42</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4283,17 +4283,17 @@
         <v>46217</v>
       </c>
       <c r="B203" t="n">
-        <v>2245</v>
+        <v>2250</v>
       </c>
       <c r="C203" t="n">
         <v>8888</v>
       </c>
       <c r="D203" t="n">
-        <v>883.75</v>
+        <v>1943.54</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4302,17 +4302,17 @@
         <v>46217</v>
       </c>
       <c r="B204" t="n">
-        <v>477</v>
+        <v>1327</v>
       </c>
       <c r="C204" t="n">
         <v>8888</v>
       </c>
       <c r="D204" t="n">
-        <v>994.15</v>
+        <v>319.23</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4321,17 +4321,17 @@
         <v>46217</v>
       </c>
       <c r="B205" t="n">
-        <v>2015</v>
+        <v>326</v>
       </c>
       <c r="C205" t="n">
         <v>8888</v>
       </c>
       <c r="D205" t="n">
-        <v>3243.05</v>
+        <v>151.86</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4340,17 +4340,17 @@
         <v>46217</v>
       </c>
       <c r="B206" t="n">
-        <v>1996</v>
+        <v>1372</v>
       </c>
       <c r="C206" t="n">
-        <v>691</v>
+        <v>8888</v>
       </c>
       <c r="D206" t="n">
-        <v>500.79</v>
+        <v>1088.02</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4359,17 +4359,17 @@
         <v>46217</v>
       </c>
       <c r="B207" t="n">
-        <v>1653</v>
+        <v>626</v>
       </c>
       <c r="C207" t="n">
         <v>8888</v>
       </c>
       <c r="D207" t="n">
-        <v>4115.53</v>
+        <v>28212.87</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4378,13 +4378,13 @@
         <v>46217</v>
       </c>
       <c r="B208" t="n">
-        <v>1064</v>
+        <v>629</v>
       </c>
       <c r="C208" t="n">
-        <v>27</v>
+        <v>675</v>
       </c>
       <c r="D208" t="n">
-        <v>1153.23</v>
+        <v>2975.45</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -4397,17 +4397,17 @@
         <v>46217</v>
       </c>
       <c r="B209" t="n">
-        <v>1983</v>
+        <v>2651</v>
       </c>
       <c r="C209" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D209" t="n">
-        <v>1246.33</v>
+        <v>648.71</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4416,17 +4416,17 @@
         <v>46217</v>
       </c>
       <c r="B210" t="n">
-        <v>2118</v>
+        <v>2114</v>
       </c>
       <c r="C210" t="n">
-        <v>8888</v>
+        <v>1954</v>
       </c>
       <c r="D210" t="n">
-        <v>5870.04</v>
+        <v>879.03</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4435,17 +4435,17 @@
         <v>46217</v>
       </c>
       <c r="B211" t="n">
-        <v>559</v>
+        <v>1299</v>
       </c>
       <c r="C211" t="n">
-        <v>8888</v>
+        <v>2522</v>
       </c>
       <c r="D211" t="n">
-        <v>2189.12</v>
+        <v>6680.93</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4454,13 +4454,13 @@
         <v>46217</v>
       </c>
       <c r="B212" t="n">
-        <v>2680</v>
+        <v>40</v>
       </c>
       <c r="C212" t="n">
         <v>8888</v>
       </c>
       <c r="D212" t="n">
-        <v>2285.31</v>
+        <v>3583.39</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -4473,17 +4473,17 @@
         <v>46217</v>
       </c>
       <c r="B213" t="n">
-        <v>2637</v>
+        <v>40</v>
       </c>
       <c r="C213" t="n">
         <v>8888</v>
       </c>
       <c r="D213" t="n">
-        <v>1302.18</v>
+        <v>2529.31</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4492,17 +4492,17 @@
         <v>46217</v>
       </c>
       <c r="B214" t="n">
-        <v>1632</v>
+        <v>363</v>
       </c>
       <c r="C214" t="n">
         <v>8888</v>
       </c>
       <c r="D214" t="n">
-        <v>689.76</v>
+        <v>739.17</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4511,13 +4511,13 @@
         <v>46217</v>
       </c>
       <c r="B215" t="n">
-        <v>1299</v>
+        <v>675</v>
       </c>
       <c r="C215" t="n">
-        <v>2522</v>
+        <v>1898</v>
       </c>
       <c r="D215" t="n">
-        <v>3319.01</v>
+        <v>107.13</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -4530,17 +4530,17 @@
         <v>46217</v>
       </c>
       <c r="B216" t="n">
-        <v>2727</v>
+        <v>636</v>
       </c>
       <c r="C216" t="n">
         <v>8888</v>
       </c>
       <c r="D216" t="n">
-        <v>548.33</v>
+        <v>7476.56</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4549,13 +4549,13 @@
         <v>46217</v>
       </c>
       <c r="B217" t="n">
-        <v>2026</v>
+        <v>1075</v>
       </c>
       <c r="C217" t="n">
         <v>8888</v>
       </c>
       <c r="D217" t="n">
-        <v>699.05</v>
+        <v>1970.3</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -4568,17 +4568,17 @@
         <v>46217</v>
       </c>
       <c r="B218" t="n">
-        <v>664</v>
+        <v>2245</v>
       </c>
       <c r="C218" t="n">
         <v>8888</v>
       </c>
       <c r="D218" t="n">
-        <v>3483.46</v>
+        <v>883.75</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4587,17 +4587,17 @@
         <v>46217</v>
       </c>
       <c r="B219" t="n">
-        <v>629</v>
+        <v>477</v>
       </c>
       <c r="C219" t="n">
-        <v>675</v>
+        <v>8888</v>
       </c>
       <c r="D219" t="n">
-        <v>267.79</v>
+        <v>994.15</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4606,13 +4606,13 @@
         <v>46217</v>
       </c>
       <c r="B220" t="n">
-        <v>1465</v>
+        <v>2015</v>
       </c>
       <c r="C220" t="n">
         <v>8888</v>
       </c>
       <c r="D220" t="n">
-        <v>12894.64</v>
+        <v>3243.05</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -4625,17 +4625,17 @@
         <v>46217</v>
       </c>
       <c r="B221" t="n">
-        <v>2550</v>
+        <v>1996</v>
       </c>
       <c r="C221" t="n">
-        <v>8888</v>
+        <v>691</v>
       </c>
       <c r="D221" t="n">
-        <v>321.05</v>
+        <v>500.79</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4644,17 +4644,17 @@
         <v>46217</v>
       </c>
       <c r="B222" t="n">
-        <v>1756</v>
+        <v>1653</v>
       </c>
       <c r="C222" t="n">
         <v>8888</v>
       </c>
       <c r="D222" t="n">
-        <v>2445</v>
+        <v>4115.53</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4663,17 +4663,17 @@
         <v>46217</v>
       </c>
       <c r="B223" t="n">
-        <v>890</v>
+        <v>1064</v>
       </c>
       <c r="C223" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D223" t="n">
-        <v>4287.14</v>
+        <v>1153.23</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4682,17 +4682,17 @@
         <v>46217</v>
       </c>
       <c r="B224" t="n">
-        <v>363</v>
+        <v>1983</v>
       </c>
       <c r="C224" t="n">
         <v>8888</v>
       </c>
       <c r="D224" t="n">
-        <v>2517.01</v>
+        <v>1246.33</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4701,17 +4701,17 @@
         <v>46217</v>
       </c>
       <c r="B225" t="n">
-        <v>2698</v>
+        <v>2118</v>
       </c>
       <c r="C225" t="n">
-        <v>874</v>
+        <v>8888</v>
       </c>
       <c r="D225" t="n">
-        <v>1183.42</v>
+        <v>5870.04</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4720,13 +4720,13 @@
         <v>46217</v>
       </c>
       <c r="B226" t="n">
-        <v>535</v>
+        <v>559</v>
       </c>
       <c r="C226" t="n">
         <v>8888</v>
       </c>
       <c r="D226" t="n">
-        <v>5293.96</v>
+        <v>2189.12</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>46217</v>
       </c>
       <c r="B227" t="n">
-        <v>2250</v>
+        <v>2680</v>
       </c>
       <c r="C227" t="n">
         <v>8888</v>
       </c>
       <c r="D227" t="n">
-        <v>2650.33</v>
+        <v>2285.31</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -4758,17 +4758,17 @@
         <v>46217</v>
       </c>
       <c r="B228" t="n">
-        <v>2681</v>
+        <v>2637</v>
       </c>
       <c r="C228" t="n">
         <v>8888</v>
       </c>
       <c r="D228" t="n">
-        <v>2853.99</v>
+        <v>1302.18</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4777,13 +4777,13 @@
         <v>46217</v>
       </c>
       <c r="B229" t="n">
-        <v>132</v>
+        <v>1632</v>
       </c>
       <c r="C229" t="n">
         <v>8888</v>
       </c>
       <c r="D229" t="n">
-        <v>11123.92</v>
+        <v>689.76</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -4796,17 +4796,17 @@
         <v>46217</v>
       </c>
       <c r="B230" t="n">
-        <v>2442</v>
+        <v>2727</v>
       </c>
       <c r="C230" t="n">
         <v>8888</v>
       </c>
       <c r="D230" t="n">
-        <v>2822.22</v>
+        <v>548.33</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4815,17 +4815,17 @@
         <v>46217</v>
       </c>
       <c r="B231" t="n">
-        <v>363</v>
+        <v>2026</v>
       </c>
       <c r="C231" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D231" t="n">
-        <v>4028</v>
+        <v>699.05</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4834,13 +4834,13 @@
         <v>46217</v>
       </c>
       <c r="B232" t="n">
-        <v>483</v>
+        <v>1117</v>
       </c>
       <c r="C232" t="n">
         <v>8888</v>
       </c>
       <c r="D232" t="n">
-        <v>3025.94</v>
+        <v>306.02</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -4853,17 +4853,17 @@
         <v>46217</v>
       </c>
       <c r="B233" t="n">
-        <v>2279</v>
+        <v>664</v>
       </c>
       <c r="C233" t="n">
         <v>8888</v>
       </c>
       <c r="D233" t="n">
-        <v>740.38</v>
+        <v>3483.46</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4872,13 +4872,13 @@
         <v>46217</v>
       </c>
       <c r="B234" t="n">
-        <v>2607</v>
+        <v>1465</v>
       </c>
       <c r="C234" t="n">
         <v>8888</v>
       </c>
       <c r="D234" t="n">
-        <v>1075.36</v>
+        <v>14048.78</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -4891,17 +4891,17 @@
         <v>46217</v>
       </c>
       <c r="B235" t="n">
-        <v>2330</v>
+        <v>2550</v>
       </c>
       <c r="C235" t="n">
-        <v>1954</v>
+        <v>8888</v>
       </c>
       <c r="D235" t="n">
-        <v>1923.09</v>
+        <v>321.05</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4910,17 +4910,17 @@
         <v>46217</v>
       </c>
       <c r="B236" t="n">
-        <v>2472</v>
+        <v>1756</v>
       </c>
       <c r="C236" t="n">
-        <v>2853</v>
+        <v>8888</v>
       </c>
       <c r="D236" t="n">
-        <v>824.0599999999999</v>
+        <v>2445</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4929,17 +4929,17 @@
         <v>46217</v>
       </c>
       <c r="B237" t="n">
-        <v>1384</v>
+        <v>890</v>
       </c>
       <c r="C237" t="n">
         <v>8888</v>
       </c>
       <c r="D237" t="n">
-        <v>585.27</v>
+        <v>4287.14</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4948,13 +4948,13 @@
         <v>46217</v>
       </c>
       <c r="B238" t="n">
-        <v>2709</v>
+        <v>363</v>
       </c>
       <c r="C238" t="n">
         <v>8888</v>
       </c>
       <c r="D238" t="n">
-        <v>2210.08</v>
+        <v>2517.01</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -4967,13 +4967,13 @@
         <v>46217</v>
       </c>
       <c r="B239" t="n">
-        <v>619</v>
+        <v>2698</v>
       </c>
       <c r="C239" t="n">
-        <v>1139</v>
+        <v>874</v>
       </c>
       <c r="D239" t="n">
-        <v>2098.5</v>
+        <v>1183.42</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -4986,17 +4986,17 @@
         <v>46217</v>
       </c>
       <c r="B240" t="n">
-        <v>374</v>
+        <v>535</v>
       </c>
       <c r="C240" t="n">
         <v>8888</v>
       </c>
       <c r="D240" t="n">
-        <v>1725.89</v>
+        <v>5293.96</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5005,13 +5005,13 @@
         <v>46217</v>
       </c>
       <c r="B241" t="n">
-        <v>1137</v>
+        <v>2250</v>
       </c>
       <c r="C241" t="n">
         <v>8888</v>
       </c>
       <c r="D241" t="n">
-        <v>4413.34</v>
+        <v>2650.33</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -5024,17 +5024,17 @@
         <v>46217</v>
       </c>
       <c r="B242" t="n">
-        <v>2251</v>
+        <v>2681</v>
       </c>
       <c r="C242" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D242" t="n">
-        <v>510.18</v>
+        <v>2853.99</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -5043,17 +5043,17 @@
         <v>46217</v>
       </c>
       <c r="B243" t="n">
-        <v>2728</v>
+        <v>132</v>
       </c>
       <c r="C243" t="n">
-        <v>977</v>
+        <v>8888</v>
       </c>
       <c r="D243" t="n">
-        <v>2256.87</v>
+        <v>11123.92</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5062,17 +5062,17 @@
         <v>46217</v>
       </c>
       <c r="B244" t="n">
-        <v>1278</v>
+        <v>2442</v>
       </c>
       <c r="C244" t="n">
-        <v>1533</v>
+        <v>8888</v>
       </c>
       <c r="D244" t="n">
-        <v>620.97</v>
+        <v>2822.22</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5081,15 +5081,319 @@
         <v>46217</v>
       </c>
       <c r="B245" t="n">
+        <v>363</v>
+      </c>
+      <c r="C245" t="n">
+        <v>1898</v>
+      </c>
+      <c r="D245" t="n">
+        <v>4028</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B246" t="n">
+        <v>483</v>
+      </c>
+      <c r="C246" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D246" t="n">
+        <v>3480.21</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B247" t="n">
+        <v>2279</v>
+      </c>
+      <c r="C247" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D247" t="n">
+        <v>740.38</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B248" t="n">
+        <v>767</v>
+      </c>
+      <c r="C248" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D248" t="n">
+        <v>718.65</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B249" t="n">
+        <v>2607</v>
+      </c>
+      <c r="C249" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D249" t="n">
+        <v>1075.36</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B250" t="n">
+        <v>2330</v>
+      </c>
+      <c r="C250" t="n">
+        <v>1954</v>
+      </c>
+      <c r="D250" t="n">
+        <v>1923.09</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B251" t="n">
+        <v>2472</v>
+      </c>
+      <c r="C251" t="n">
+        <v>2853</v>
+      </c>
+      <c r="D251" t="n">
+        <v>824.0599999999999</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B252" t="n">
+        <v>1384</v>
+      </c>
+      <c r="C252" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D252" t="n">
+        <v>585.27</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B253" t="n">
+        <v>2709</v>
+      </c>
+      <c r="C253" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D253" t="n">
+        <v>2210.08</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B254" t="n">
+        <v>619</v>
+      </c>
+      <c r="C254" t="n">
+        <v>1139</v>
+      </c>
+      <c r="D254" t="n">
+        <v>3330.07</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B255" t="n">
+        <v>374</v>
+      </c>
+      <c r="C255" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D255" t="n">
+        <v>1725.89</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B256" t="n">
+        <v>1137</v>
+      </c>
+      <c r="C256" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D256" t="n">
+        <v>4413.34</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B257" t="n">
+        <v>2251</v>
+      </c>
+      <c r="C257" t="n">
+        <v>3403</v>
+      </c>
+      <c r="D257" t="n">
+        <v>510.18</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B258" t="n">
+        <v>2728</v>
+      </c>
+      <c r="C258" t="n">
+        <v>977</v>
+      </c>
+      <c r="D258" t="n">
+        <v>2256.87</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B259" t="n">
+        <v>1293</v>
+      </c>
+      <c r="C259" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D259" t="n">
+        <v>529.2</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B260" t="n">
+        <v>1278</v>
+      </c>
+      <c r="C260" t="n">
+        <v>1533</v>
+      </c>
+      <c r="D260" t="n">
+        <v>620.97</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B261" t="n">
         <v>1380</v>
       </c>
-      <c r="C245" t="n">
-        <v>8888</v>
-      </c>
-      <c r="D245" t="n">
+      <c r="C261" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D261" t="n">
         <v>947.8200000000001</v>
       </c>
-      <c r="E245" t="inlineStr">
+      <c r="E261" t="inlineStr">
         <is>
           <t>FORÇA DE VENDAS</t>
         </is>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E261"/>
+  <dimension ref="A1:E278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,7 +565,7 @@
         <v>8888</v>
       </c>
       <c r="D7" t="n">
-        <v>10705.35</v>
+        <v>13540.93</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -616,17 +616,17 @@
         <v>46217</v>
       </c>
       <c r="B10" t="n">
-        <v>1381</v>
+        <v>2769</v>
       </c>
       <c r="C10" t="n">
-        <v>8888</v>
+        <v>977</v>
       </c>
       <c r="D10" t="n">
-        <v>2196.92</v>
+        <v>637.3200000000001</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -635,13 +635,13 @@
         <v>46217</v>
       </c>
       <c r="B11" t="n">
-        <v>703</v>
+        <v>1381</v>
       </c>
       <c r="C11" t="n">
         <v>8888</v>
       </c>
       <c r="D11" t="n">
-        <v>11161.25</v>
+        <v>2196.92</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -654,13 +654,13 @@
         <v>46217</v>
       </c>
       <c r="B12" t="n">
-        <v>2109</v>
+        <v>703</v>
       </c>
       <c r="C12" t="n">
         <v>8888</v>
       </c>
       <c r="D12" t="n">
-        <v>4813.6</v>
+        <v>11161.25</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -673,17 +673,17 @@
         <v>46217</v>
       </c>
       <c r="B13" t="n">
-        <v>1876</v>
+        <v>2109</v>
       </c>
       <c r="C13" t="n">
-        <v>977</v>
+        <v>8888</v>
       </c>
       <c r="D13" t="n">
-        <v>312.66</v>
+        <v>4813.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -692,13 +692,13 @@
         <v>46217</v>
       </c>
       <c r="B14" t="n">
-        <v>2015</v>
+        <v>1876</v>
       </c>
       <c r="C14" t="n">
-        <v>2571</v>
+        <v>977</v>
       </c>
       <c r="D14" t="n">
-        <v>2593.26</v>
+        <v>312.66</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -711,17 +711,17 @@
         <v>46217</v>
       </c>
       <c r="B15" t="n">
-        <v>1993</v>
+        <v>2015</v>
       </c>
       <c r="C15" t="n">
-        <v>8888</v>
+        <v>2571</v>
       </c>
       <c r="D15" t="n">
-        <v>1785.44</v>
+        <v>2593.26</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -730,17 +730,17 @@
         <v>46217</v>
       </c>
       <c r="B16" t="n">
-        <v>1102</v>
+        <v>1993</v>
       </c>
       <c r="C16" t="n">
         <v>8888</v>
       </c>
       <c r="D16" t="n">
-        <v>3406.59</v>
+        <v>1785.44</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
         <v>46217</v>
       </c>
       <c r="B17" t="n">
-        <v>1937</v>
+        <v>1102</v>
       </c>
       <c r="C17" t="n">
         <v>8888</v>
       </c>
       <c r="D17" t="n">
-        <v>3337.21</v>
+        <v>3406.59</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -768,17 +768,17 @@
         <v>46217</v>
       </c>
       <c r="B18" t="n">
-        <v>1293</v>
+        <v>1937</v>
       </c>
       <c r="C18" t="n">
-        <v>1281</v>
+        <v>8888</v>
       </c>
       <c r="D18" t="n">
-        <v>1337.87</v>
+        <v>3337.21</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
         <v>46217</v>
       </c>
       <c r="B19" t="n">
-        <v>2657</v>
+        <v>1293</v>
       </c>
       <c r="C19" t="n">
-        <v>8888</v>
+        <v>1281</v>
       </c>
       <c r="D19" t="n">
-        <v>877.0700000000001</v>
+        <v>1337.87</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -806,17 +806,17 @@
         <v>46217</v>
       </c>
       <c r="B20" t="n">
-        <v>2768</v>
+        <v>2769</v>
       </c>
       <c r="C20" t="n">
         <v>8888</v>
       </c>
       <c r="D20" t="n">
-        <v>4890.12</v>
+        <v>2679.02</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -825,13 +825,13 @@
         <v>46217</v>
       </c>
       <c r="B21" t="n">
-        <v>2686</v>
+        <v>2657</v>
       </c>
       <c r="C21" t="n">
         <v>8888</v>
       </c>
       <c r="D21" t="n">
-        <v>422.71</v>
+        <v>877.0700000000001</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -844,17 +844,17 @@
         <v>46217</v>
       </c>
       <c r="B22" t="n">
-        <v>1890</v>
+        <v>1993</v>
       </c>
       <c r="C22" t="n">
-        <v>3449</v>
+        <v>8888</v>
       </c>
       <c r="D22" t="n">
-        <v>1575.78</v>
+        <v>875.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -863,13 +863,13 @@
         <v>46217</v>
       </c>
       <c r="B23" t="n">
-        <v>33</v>
+        <v>2768</v>
       </c>
       <c r="C23" t="n">
         <v>8888</v>
       </c>
       <c r="D23" t="n">
-        <v>1041.47</v>
+        <v>4890.12</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -882,17 +882,17 @@
         <v>46217</v>
       </c>
       <c r="B24" t="n">
-        <v>2726</v>
+        <v>2686</v>
       </c>
       <c r="C24" t="n">
-        <v>1929</v>
+        <v>8888</v>
       </c>
       <c r="D24" t="n">
-        <v>640.1799999999999</v>
+        <v>1794.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
         <v>46217</v>
       </c>
       <c r="B25" t="n">
-        <v>89</v>
+        <v>1890</v>
       </c>
       <c r="C25" t="n">
-        <v>8888</v>
+        <v>3449</v>
       </c>
       <c r="D25" t="n">
-        <v>5652.15</v>
+        <v>1575.78</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -920,17 +920,17 @@
         <v>46217</v>
       </c>
       <c r="B26" t="n">
-        <v>2178</v>
+        <v>33</v>
       </c>
       <c r="C26" t="n">
-        <v>738</v>
+        <v>8888</v>
       </c>
       <c r="D26" t="n">
-        <v>291.83</v>
+        <v>1041.47</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -939,13 +939,13 @@
         <v>46217</v>
       </c>
       <c r="B27" t="n">
-        <v>2209</v>
+        <v>2726</v>
       </c>
       <c r="C27" t="n">
-        <v>738</v>
+        <v>1929</v>
       </c>
       <c r="D27" t="n">
-        <v>2043.28</v>
+        <v>640.1799999999999</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -958,13 +958,13 @@
         <v>46217</v>
       </c>
       <c r="B28" t="n">
-        <v>429</v>
+        <v>89</v>
       </c>
       <c r="C28" t="n">
         <v>8888</v>
       </c>
       <c r="D28" t="n">
-        <v>3775.81</v>
+        <v>5652.15</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -977,17 +977,17 @@
         <v>46217</v>
       </c>
       <c r="B29" t="n">
-        <v>2641</v>
+        <v>1983</v>
       </c>
       <c r="C29" t="n">
-        <v>8888</v>
+        <v>841</v>
       </c>
       <c r="D29" t="n">
-        <v>607.79</v>
+        <v>243.63</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -996,17 +996,17 @@
         <v>46217</v>
       </c>
       <c r="B30" t="n">
-        <v>360</v>
+        <v>2178</v>
       </c>
       <c r="C30" t="n">
-        <v>8888</v>
+        <v>738</v>
       </c>
       <c r="D30" t="n">
-        <v>802.59</v>
+        <v>1671.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1015,13 +1015,13 @@
         <v>46217</v>
       </c>
       <c r="B31" t="n">
-        <v>949</v>
+        <v>2209</v>
       </c>
       <c r="C31" t="n">
-        <v>1258</v>
+        <v>738</v>
       </c>
       <c r="D31" t="n">
-        <v>196.87</v>
+        <v>2043.28</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1034,17 +1034,17 @@
         <v>46217</v>
       </c>
       <c r="B32" t="n">
-        <v>353</v>
+        <v>429</v>
       </c>
       <c r="C32" t="n">
         <v>8888</v>
       </c>
       <c r="D32" t="n">
-        <v>2121.12</v>
+        <v>3775.81</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
         <v>46217</v>
       </c>
       <c r="B33" t="n">
-        <v>1756</v>
+        <v>2641</v>
       </c>
       <c r="C33" t="n">
         <v>8888</v>
       </c>
       <c r="D33" t="n">
-        <v>2223.56</v>
+        <v>607.79</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1072,17 +1072,17 @@
         <v>46217</v>
       </c>
       <c r="B34" t="n">
-        <v>285</v>
+        <v>360</v>
       </c>
       <c r="C34" t="n">
         <v>8888</v>
       </c>
       <c r="D34" t="n">
-        <v>3937.9</v>
+        <v>1151.67</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1091,17 +1091,17 @@
         <v>46217</v>
       </c>
       <c r="B35" t="n">
-        <v>1906</v>
+        <v>949</v>
       </c>
       <c r="C35" t="n">
-        <v>8888</v>
+        <v>1258</v>
       </c>
       <c r="D35" t="n">
-        <v>3142.54</v>
+        <v>196.87</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1110,17 +1110,17 @@
         <v>46217</v>
       </c>
       <c r="B36" t="n">
-        <v>2499</v>
+        <v>353</v>
       </c>
       <c r="C36" t="n">
         <v>8888</v>
       </c>
       <c r="D36" t="n">
-        <v>493.06</v>
+        <v>2121.12</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1129,13 +1129,13 @@
         <v>46217</v>
       </c>
       <c r="B37" t="n">
-        <v>1308</v>
+        <v>1756</v>
       </c>
       <c r="C37" t="n">
         <v>8888</v>
       </c>
       <c r="D37" t="n">
-        <v>3127.35</v>
+        <v>2223.56</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1148,13 +1148,13 @@
         <v>46217</v>
       </c>
       <c r="B38" t="n">
-        <v>610</v>
+        <v>285</v>
       </c>
       <c r="C38" t="n">
         <v>8888</v>
       </c>
       <c r="D38" t="n">
-        <v>590.08</v>
+        <v>9256.6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1167,17 +1167,17 @@
         <v>46217</v>
       </c>
       <c r="B39" t="n">
-        <v>619</v>
+        <v>1906</v>
       </c>
       <c r="C39" t="n">
         <v>8888</v>
       </c>
       <c r="D39" t="n">
-        <v>236.34</v>
+        <v>3142.54</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1186,17 +1186,17 @@
         <v>46217</v>
       </c>
       <c r="B40" t="n">
-        <v>1324</v>
+        <v>2499</v>
       </c>
       <c r="C40" t="n">
         <v>8888</v>
       </c>
       <c r="D40" t="n">
-        <v>2603.19</v>
+        <v>493.06</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1205,17 +1205,17 @@
         <v>46217</v>
       </c>
       <c r="B41" t="n">
-        <v>483</v>
+        <v>1308</v>
       </c>
       <c r="C41" t="n">
         <v>8888</v>
       </c>
       <c r="D41" t="n">
-        <v>461.28</v>
+        <v>3127.35</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1224,17 +1224,17 @@
         <v>46217</v>
       </c>
       <c r="B42" t="n">
-        <v>1117</v>
+        <v>610</v>
       </c>
       <c r="C42" t="n">
         <v>8888</v>
       </c>
       <c r="D42" t="n">
-        <v>755.71</v>
+        <v>590.08</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
         <v>46217</v>
       </c>
       <c r="B43" t="n">
-        <v>2755</v>
+        <v>619</v>
       </c>
       <c r="C43" t="n">
-        <v>2220</v>
+        <v>8888</v>
       </c>
       <c r="D43" t="n">
-        <v>1133.17</v>
+        <v>236.34</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1262,17 +1262,17 @@
         <v>46217</v>
       </c>
       <c r="B44" t="n">
-        <v>2767</v>
+        <v>1324</v>
       </c>
       <c r="C44" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D44" t="n">
-        <v>5000.2</v>
+        <v>2603.19</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1281,13 +1281,13 @@
         <v>46217</v>
       </c>
       <c r="B45" t="n">
-        <v>559</v>
+        <v>483</v>
       </c>
       <c r="C45" t="n">
         <v>8888</v>
       </c>
       <c r="D45" t="n">
-        <v>1516.25</v>
+        <v>2092.52</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1300,17 +1300,17 @@
         <v>46217</v>
       </c>
       <c r="B46" t="n">
-        <v>1277</v>
+        <v>1996</v>
       </c>
       <c r="C46" t="n">
         <v>8888</v>
       </c>
       <c r="D46" t="n">
-        <v>574.7</v>
+        <v>308.35</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1319,17 +1319,17 @@
         <v>46217</v>
       </c>
       <c r="B47" t="n">
-        <v>358</v>
+        <v>1117</v>
       </c>
       <c r="C47" t="n">
         <v>8888</v>
       </c>
       <c r="D47" t="n">
-        <v>1301.77</v>
+        <v>755.71</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1338,17 @@
         <v>46217</v>
       </c>
       <c r="B48" t="n">
-        <v>1993</v>
+        <v>2755</v>
       </c>
       <c r="C48" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D48" t="n">
-        <v>5280</v>
+        <v>1133.17</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1357,17 +1357,17 @@
         <v>46217</v>
       </c>
       <c r="B49" t="n">
-        <v>609</v>
+        <v>2767</v>
       </c>
       <c r="C49" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D49" t="n">
-        <v>2500.68</v>
+        <v>5000.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1376,17 +1376,17 @@
         <v>46217</v>
       </c>
       <c r="B50" t="n">
-        <v>2507</v>
+        <v>2789</v>
       </c>
       <c r="C50" t="n">
         <v>8888</v>
       </c>
       <c r="D50" t="n">
-        <v>448.36</v>
+        <v>747.21</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1395,17 +1395,17 @@
         <v>46217</v>
       </c>
       <c r="B51" t="n">
-        <v>2767</v>
+        <v>559</v>
       </c>
       <c r="C51" t="n">
         <v>8888</v>
       </c>
       <c r="D51" t="n">
-        <v>1175.73</v>
+        <v>1516.25</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1414,17 +1414,17 @@
         <v>46217</v>
       </c>
       <c r="B52" t="n">
-        <v>1063</v>
+        <v>1277</v>
       </c>
       <c r="C52" t="n">
         <v>8888</v>
       </c>
       <c r="D52" t="n">
-        <v>1251.14</v>
+        <v>574.7</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1433,17 +1433,17 @@
         <v>46217</v>
       </c>
       <c r="B53" t="n">
-        <v>325</v>
+        <v>358</v>
       </c>
       <c r="C53" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D53" t="n">
-        <v>868.83</v>
+        <v>1301.77</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1452,17 +1452,17 @@
         <v>46217</v>
       </c>
       <c r="B54" t="n">
-        <v>2660</v>
+        <v>1993</v>
       </c>
       <c r="C54" t="n">
         <v>8888</v>
       </c>
       <c r="D54" t="n">
-        <v>281.24</v>
+        <v>6182.38</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1471,13 +1471,13 @@
         <v>46217</v>
       </c>
       <c r="B55" t="n">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C55" t="n">
         <v>8888</v>
       </c>
       <c r="D55" t="n">
-        <v>235.34</v>
+        <v>2500.68</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -1490,17 +1490,17 @@
         <v>46217</v>
       </c>
       <c r="B56" t="n">
-        <v>424</v>
+        <v>2507</v>
       </c>
       <c r="C56" t="n">
         <v>8888</v>
       </c>
       <c r="D56" t="n">
-        <v>3214.29</v>
+        <v>448.36</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1509,17 +1509,17 @@
         <v>46217</v>
       </c>
       <c r="B57" t="n">
-        <v>664</v>
+        <v>285</v>
       </c>
       <c r="C57" t="n">
         <v>8888</v>
       </c>
       <c r="D57" t="n">
-        <v>364.07</v>
+        <v>1718.36</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1528,17 +1528,17 @@
         <v>46217</v>
       </c>
       <c r="B58" t="n">
-        <v>2279</v>
+        <v>2767</v>
       </c>
       <c r="C58" t="n">
-        <v>1139</v>
+        <v>8888</v>
       </c>
       <c r="D58" t="n">
-        <v>448.78</v>
+        <v>1175.73</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1547,13 +1547,13 @@
         <v>46217</v>
       </c>
       <c r="B59" t="n">
-        <v>40</v>
+        <v>2279</v>
       </c>
       <c r="C59" t="n">
-        <v>58</v>
+        <v>1139</v>
       </c>
       <c r="D59" t="n">
-        <v>325.04</v>
+        <v>1197.39</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -1566,17 +1566,17 @@
         <v>46217</v>
       </c>
       <c r="B60" t="n">
-        <v>2069</v>
+        <v>1063</v>
       </c>
       <c r="C60" t="n">
         <v>8888</v>
       </c>
       <c r="D60" t="n">
-        <v>176.8</v>
+        <v>1251.14</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1585,17 +1585,17 @@
         <v>46217</v>
       </c>
       <c r="B61" t="n">
-        <v>522</v>
+        <v>325</v>
       </c>
       <c r="C61" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D61" t="n">
-        <v>151.86</v>
+        <v>868.83</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1604,17 +1604,17 @@
         <v>46217</v>
       </c>
       <c r="B62" t="n">
-        <v>1304</v>
+        <v>2660</v>
       </c>
       <c r="C62" t="n">
-        <v>213</v>
+        <v>8888</v>
       </c>
       <c r="D62" t="n">
-        <v>297.1</v>
+        <v>281.24</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1623,13 +1623,13 @@
         <v>46217</v>
       </c>
       <c r="B63" t="n">
-        <v>1869</v>
+        <v>610</v>
       </c>
       <c r="C63" t="n">
         <v>8888</v>
       </c>
       <c r="D63" t="n">
-        <v>447.76</v>
+        <v>235.34</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -1642,17 +1642,17 @@
         <v>46217</v>
       </c>
       <c r="B64" t="n">
-        <v>949</v>
+        <v>424</v>
       </c>
       <c r="C64" t="n">
-        <v>998</v>
+        <v>8888</v>
       </c>
       <c r="D64" t="n">
-        <v>129.85</v>
+        <v>3214.29</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1661,17 +1661,17 @@
         <v>46217</v>
       </c>
       <c r="B65" t="n">
-        <v>1317</v>
+        <v>664</v>
       </c>
       <c r="C65" t="n">
         <v>8888</v>
       </c>
       <c r="D65" t="n">
-        <v>1445.46</v>
+        <v>364.07</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1680,17 +1680,17 @@
         <v>46217</v>
       </c>
       <c r="B66" t="n">
-        <v>1853</v>
+        <v>40</v>
       </c>
       <c r="C66" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D66" t="n">
-        <v>522.4</v>
+        <v>325.04</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1699,17 +1699,17 @@
         <v>46217</v>
       </c>
       <c r="B67" t="n">
-        <v>360</v>
+        <v>2069</v>
       </c>
       <c r="C67" t="n">
-        <v>546</v>
+        <v>8888</v>
       </c>
       <c r="D67" t="n">
-        <v>9262</v>
+        <v>176.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1718,13 +1718,13 @@
         <v>46217</v>
       </c>
       <c r="B68" t="n">
-        <v>2250</v>
+        <v>522</v>
       </c>
       <c r="C68" t="n">
         <v>8888</v>
       </c>
       <c r="D68" t="n">
-        <v>4131.57</v>
+        <v>151.86</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -1737,17 +1737,17 @@
         <v>46217</v>
       </c>
       <c r="B69" t="n">
-        <v>2507</v>
+        <v>1304</v>
       </c>
       <c r="C69" t="n">
-        <v>8888</v>
+        <v>213</v>
       </c>
       <c r="D69" t="n">
-        <v>4167.12</v>
+        <v>297.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1756,17 +1756,17 @@
         <v>46217</v>
       </c>
       <c r="B70" t="n">
-        <v>664</v>
+        <v>1869</v>
       </c>
       <c r="C70" t="n">
         <v>8888</v>
       </c>
       <c r="D70" t="n">
-        <v>4099.16</v>
+        <v>447.76</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1775,17 +1775,17 @@
         <v>46217</v>
       </c>
       <c r="B71" t="n">
-        <v>1075</v>
+        <v>949</v>
       </c>
       <c r="C71" t="n">
-        <v>8888</v>
+        <v>998</v>
       </c>
       <c r="D71" t="n">
-        <v>1743.47</v>
+        <v>129.85</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1794,17 +1794,17 @@
         <v>46217</v>
       </c>
       <c r="B72" t="n">
-        <v>1324</v>
+        <v>1317</v>
       </c>
       <c r="C72" t="n">
-        <v>738</v>
+        <v>8888</v>
       </c>
       <c r="D72" t="n">
-        <v>4548.42</v>
+        <v>1628.83</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1813,17 +1813,17 @@
         <v>46217</v>
       </c>
       <c r="B73" t="n">
-        <v>1906</v>
+        <v>1853</v>
       </c>
       <c r="C73" t="n">
-        <v>1954</v>
+        <v>8888</v>
       </c>
       <c r="D73" t="n">
-        <v>1445.21</v>
+        <v>522.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1832,13 +1832,13 @@
         <v>46217</v>
       </c>
       <c r="B74" t="n">
-        <v>595</v>
+        <v>360</v>
       </c>
       <c r="C74" t="n">
-        <v>691</v>
+        <v>546</v>
       </c>
       <c r="D74" t="n">
-        <v>314.52</v>
+        <v>9262</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -1851,17 +1851,17 @@
         <v>46217</v>
       </c>
       <c r="B75" t="n">
-        <v>2696</v>
+        <v>2250</v>
       </c>
       <c r="C75" t="n">
-        <v>1312</v>
+        <v>8888</v>
       </c>
       <c r="D75" t="n">
-        <v>677.76</v>
+        <v>4131.57</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1870,17 +1870,17 @@
         <v>46217</v>
       </c>
       <c r="B76" t="n">
-        <v>525</v>
+        <v>2507</v>
       </c>
       <c r="C76" t="n">
         <v>8888</v>
       </c>
       <c r="D76" t="n">
-        <v>490.08</v>
+        <v>4167.12</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1889,17 +1889,17 @@
         <v>46217</v>
       </c>
       <c r="B77" t="n">
-        <v>2491</v>
+        <v>664</v>
       </c>
       <c r="C77" t="n">
         <v>8888</v>
       </c>
       <c r="D77" t="n">
-        <v>2909.58</v>
+        <v>4099.16</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1908,17 +1908,17 @@
         <v>46217</v>
       </c>
       <c r="B78" t="n">
-        <v>2651</v>
+        <v>1075</v>
       </c>
       <c r="C78" t="n">
         <v>8888</v>
       </c>
       <c r="D78" t="n">
-        <v>638.64</v>
+        <v>1743.47</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1927,17 +1927,17 @@
         <v>46217</v>
       </c>
       <c r="B79" t="n">
-        <v>525</v>
+        <v>1324</v>
       </c>
       <c r="C79" t="n">
-        <v>8888</v>
+        <v>738</v>
       </c>
       <c r="D79" t="n">
-        <v>4351.19</v>
+        <v>4548.42</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1946,17 +1946,17 @@
         <v>46217</v>
       </c>
       <c r="B80" t="n">
-        <v>2124</v>
+        <v>1906</v>
       </c>
       <c r="C80" t="n">
-        <v>8888</v>
+        <v>1954</v>
       </c>
       <c r="D80" t="n">
-        <v>3875.99</v>
+        <v>1445.21</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1965,17 +1965,17 @@
         <v>46217</v>
       </c>
       <c r="B81" t="n">
-        <v>2695</v>
+        <v>595</v>
       </c>
       <c r="C81" t="n">
-        <v>8888</v>
+        <v>691</v>
       </c>
       <c r="D81" t="n">
-        <v>1244.27</v>
+        <v>314.52</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1984,17 +1984,17 @@
         <v>46217</v>
       </c>
       <c r="B82" t="n">
-        <v>1293</v>
+        <v>2696</v>
       </c>
       <c r="C82" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D82" t="n">
-        <v>381.82</v>
+        <v>677.76</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2003,17 +2003,17 @@
         <v>46217</v>
       </c>
       <c r="B83" t="n">
-        <v>2363</v>
+        <v>525</v>
       </c>
       <c r="C83" t="n">
         <v>8888</v>
       </c>
       <c r="D83" t="n">
-        <v>2985.2</v>
+        <v>490.08</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2022,13 +2022,13 @@
         <v>46217</v>
       </c>
       <c r="B84" t="n">
-        <v>2663</v>
+        <v>2491</v>
       </c>
       <c r="C84" t="n">
         <v>8888</v>
       </c>
       <c r="D84" t="n">
-        <v>2146.08</v>
+        <v>2909.58</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2041,17 +2041,17 @@
         <v>46217</v>
       </c>
       <c r="B85" t="n">
-        <v>2711</v>
+        <v>2651</v>
       </c>
       <c r="C85" t="n">
         <v>8888</v>
       </c>
       <c r="D85" t="n">
-        <v>2193.56</v>
+        <v>638.64</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2060,17 +2060,17 @@
         <v>46217</v>
       </c>
       <c r="B86" t="n">
-        <v>675</v>
+        <v>525</v>
       </c>
       <c r="C86" t="n">
         <v>8888</v>
       </c>
       <c r="D86" t="n">
-        <v>289.67</v>
+        <v>4351.19</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2079,13 +2079,13 @@
         <v>46217</v>
       </c>
       <c r="B87" t="n">
-        <v>1063</v>
+        <v>2124</v>
       </c>
       <c r="C87" t="n">
         <v>8888</v>
       </c>
       <c r="D87" t="n">
-        <v>1902.46</v>
+        <v>3875.99</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -2098,17 +2098,17 @@
         <v>46217</v>
       </c>
       <c r="B88" t="n">
-        <v>1658</v>
+        <v>2695</v>
       </c>
       <c r="C88" t="n">
         <v>8888</v>
       </c>
       <c r="D88" t="n">
-        <v>1357.94</v>
+        <v>1244.27</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2117,13 +2117,13 @@
         <v>46217</v>
       </c>
       <c r="B89" t="n">
-        <v>1392</v>
+        <v>1293</v>
       </c>
       <c r="C89" t="n">
         <v>8888</v>
       </c>
       <c r="D89" t="n">
-        <v>814.61</v>
+        <v>381.82</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -2136,13 +2136,13 @@
         <v>46217</v>
       </c>
       <c r="B90" t="n">
-        <v>1007</v>
+        <v>2363</v>
       </c>
       <c r="C90" t="n">
         <v>8888</v>
       </c>
       <c r="D90" t="n">
-        <v>335.77</v>
+        <v>2985.2</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -2155,17 +2155,17 @@
         <v>46217</v>
       </c>
       <c r="B91" t="n">
-        <v>360</v>
+        <v>2663</v>
       </c>
       <c r="C91" t="n">
         <v>8888</v>
       </c>
       <c r="D91" t="n">
-        <v>749.13</v>
+        <v>2146.08</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2174,17 +2174,17 @@
         <v>46217</v>
       </c>
       <c r="B92" t="n">
-        <v>1324</v>
+        <v>2711</v>
       </c>
       <c r="C92" t="n">
         <v>8888</v>
       </c>
       <c r="D92" t="n">
-        <v>327.19</v>
+        <v>2193.56</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2193,13 +2193,13 @@
         <v>46217</v>
       </c>
       <c r="B93" t="n">
-        <v>525</v>
+        <v>675</v>
       </c>
       <c r="C93" t="n">
         <v>8888</v>
       </c>
       <c r="D93" t="n">
-        <v>643.3</v>
+        <v>289.67</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -2212,17 +2212,17 @@
         <v>46217</v>
       </c>
       <c r="B94" t="n">
-        <v>1956</v>
+        <v>1063</v>
       </c>
       <c r="C94" t="n">
-        <v>423</v>
+        <v>8888</v>
       </c>
       <c r="D94" t="n">
-        <v>503.8</v>
+        <v>1902.46</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2231,17 +2231,17 @@
         <v>46217</v>
       </c>
       <c r="B95" t="n">
-        <v>569</v>
+        <v>1658</v>
       </c>
       <c r="C95" t="n">
         <v>8888</v>
       </c>
       <c r="D95" t="n">
-        <v>13256.49</v>
+        <v>1357.94</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2250,17 +2250,17 @@
         <v>46217</v>
       </c>
       <c r="B96" t="n">
-        <v>949</v>
+        <v>1392</v>
       </c>
       <c r="C96" t="n">
-        <v>1134</v>
+        <v>8888</v>
       </c>
       <c r="D96" t="n">
-        <v>327.6</v>
+        <v>814.61</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2269,17 +2269,17 @@
         <v>46217</v>
       </c>
       <c r="B97" t="n">
-        <v>326</v>
+        <v>1007</v>
       </c>
       <c r="C97" t="n">
-        <v>1110</v>
+        <v>8888</v>
       </c>
       <c r="D97" t="n">
-        <v>2424.03</v>
+        <v>335.77</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2288,13 +2288,13 @@
         <v>46217</v>
       </c>
       <c r="B98" t="n">
-        <v>2133</v>
+        <v>525</v>
       </c>
       <c r="C98" t="n">
         <v>8888</v>
       </c>
       <c r="D98" t="n">
-        <v>66030.34</v>
+        <v>1243.34</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -2307,17 +2307,17 @@
         <v>46217</v>
       </c>
       <c r="B99" t="n">
-        <v>326</v>
+        <v>360</v>
       </c>
       <c r="C99" t="n">
         <v>8888</v>
       </c>
       <c r="D99" t="n">
-        <v>713</v>
+        <v>749.13</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2326,17 +2326,17 @@
         <v>46217</v>
       </c>
       <c r="B100" t="n">
-        <v>629</v>
+        <v>1324</v>
       </c>
       <c r="C100" t="n">
         <v>8888</v>
       </c>
       <c r="D100" t="n">
-        <v>1759.43</v>
+        <v>327.19</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2345,17 +2345,17 @@
         <v>46217</v>
       </c>
       <c r="B101" t="n">
-        <v>325</v>
+        <v>1956</v>
       </c>
       <c r="C101" t="n">
-        <v>8888</v>
+        <v>423</v>
       </c>
       <c r="D101" t="n">
-        <v>774.73</v>
+        <v>503.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2364,17 +2364,17 @@
         <v>46217</v>
       </c>
       <c r="B102" t="n">
-        <v>1293</v>
+        <v>569</v>
       </c>
       <c r="C102" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D102" t="n">
-        <v>8365.559999999999</v>
+        <v>24022.25</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2383,17 +2383,17 @@
         <v>46217</v>
       </c>
       <c r="B103" t="n">
-        <v>131</v>
+        <v>949</v>
       </c>
       <c r="C103" t="n">
-        <v>8888</v>
+        <v>1134</v>
       </c>
       <c r="D103" t="n">
-        <v>1969.93</v>
+        <v>327.6</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2402,17 +2402,17 @@
         <v>46217</v>
       </c>
       <c r="B104" t="n">
-        <v>2697</v>
+        <v>326</v>
       </c>
       <c r="C104" t="n">
-        <v>8888</v>
+        <v>1110</v>
       </c>
       <c r="D104" t="n">
-        <v>420.48</v>
+        <v>2424.03</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2421,17 +2421,17 @@
         <v>46217</v>
       </c>
       <c r="B105" t="n">
-        <v>2279</v>
+        <v>2133</v>
       </c>
       <c r="C105" t="n">
         <v>8888</v>
       </c>
       <c r="D105" t="n">
-        <v>1034.25</v>
+        <v>66030.34</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2440,17 +2440,17 @@
         <v>46217</v>
       </c>
       <c r="B106" t="n">
-        <v>1340</v>
+        <v>326</v>
       </c>
       <c r="C106" t="n">
         <v>8888</v>
       </c>
       <c r="D106" t="n">
-        <v>3037.55</v>
+        <v>713</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2459,17 +2459,17 @@
         <v>46217</v>
       </c>
       <c r="B107" t="n">
-        <v>2641</v>
+        <v>629</v>
       </c>
       <c r="C107" t="n">
         <v>8888</v>
       </c>
       <c r="D107" t="n">
-        <v>557.52</v>
+        <v>1759.43</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2478,17 +2478,17 @@
         <v>46217</v>
       </c>
       <c r="B108" t="n">
-        <v>1116</v>
+        <v>325</v>
       </c>
       <c r="C108" t="n">
         <v>8888</v>
       </c>
       <c r="D108" t="n">
-        <v>1293.89</v>
+        <v>801.04</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2497,17 +2497,17 @@
         <v>46217</v>
       </c>
       <c r="B109" t="n">
-        <v>2178</v>
+        <v>1293</v>
       </c>
       <c r="C109" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D109" t="n">
-        <v>5333.4</v>
+        <v>8365.559999999999</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2516,13 +2516,13 @@
         <v>46217</v>
       </c>
       <c r="B110" t="n">
-        <v>1756</v>
+        <v>131</v>
       </c>
       <c r="C110" t="n">
         <v>8888</v>
       </c>
       <c r="D110" t="n">
-        <v>742.23</v>
+        <v>1969.93</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -2535,17 +2535,17 @@
         <v>46217</v>
       </c>
       <c r="B111" t="n">
-        <v>131</v>
+        <v>2697</v>
       </c>
       <c r="C111" t="n">
         <v>8888</v>
       </c>
       <c r="D111" t="n">
-        <v>6513.46</v>
+        <v>420.48</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2554,13 +2554,13 @@
         <v>46217</v>
       </c>
       <c r="B112" t="n">
-        <v>2081</v>
+        <v>2279</v>
       </c>
       <c r="C112" t="n">
         <v>8888</v>
       </c>
       <c r="D112" t="n">
-        <v>1022.42</v>
+        <v>1034.25</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -2573,17 +2573,17 @@
         <v>46217</v>
       </c>
       <c r="B113" t="n">
-        <v>1374</v>
+        <v>1340</v>
       </c>
       <c r="C113" t="n">
-        <v>2845</v>
+        <v>8888</v>
       </c>
       <c r="D113" t="n">
-        <v>625.77</v>
+        <v>4420.54</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2592,13 +2592,13 @@
         <v>46217</v>
       </c>
       <c r="B114" t="n">
-        <v>58</v>
+        <v>2641</v>
       </c>
       <c r="C114" t="n">
         <v>8888</v>
       </c>
       <c r="D114" t="n">
-        <v>3050.12</v>
+        <v>557.52</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -2611,17 +2611,17 @@
         <v>46217</v>
       </c>
       <c r="B115" t="n">
-        <v>1937</v>
+        <v>1116</v>
       </c>
       <c r="C115" t="n">
         <v>8888</v>
       </c>
       <c r="D115" t="n">
-        <v>2199.57</v>
+        <v>1293.89</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2630,17 +2630,17 @@
         <v>46217</v>
       </c>
       <c r="B116" t="n">
-        <v>1983</v>
+        <v>2178</v>
       </c>
       <c r="C116" t="n">
         <v>8888</v>
       </c>
       <c r="D116" t="n">
-        <v>412.16</v>
+        <v>5333.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2649,17 +2649,17 @@
         <v>46217</v>
       </c>
       <c r="B117" t="n">
-        <v>451</v>
+        <v>1756</v>
       </c>
       <c r="C117" t="n">
         <v>8888</v>
       </c>
       <c r="D117" t="n">
-        <v>2583.46</v>
+        <v>742.23</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2668,17 +2668,17 @@
         <v>46217</v>
       </c>
       <c r="B118" t="n">
-        <v>1102</v>
+        <v>131</v>
       </c>
       <c r="C118" t="n">
-        <v>13148</v>
+        <v>8888</v>
       </c>
       <c r="D118" t="n">
-        <v>1346.4</v>
+        <v>6513.46</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2687,13 +2687,13 @@
         <v>46217</v>
       </c>
       <c r="B119" t="n">
-        <v>2767</v>
+        <v>2081</v>
       </c>
       <c r="C119" t="n">
         <v>8888</v>
       </c>
       <c r="D119" t="n">
-        <v>920.85</v>
+        <v>1022.42</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -2706,17 +2706,17 @@
         <v>46217</v>
       </c>
       <c r="B120" t="n">
-        <v>2697</v>
+        <v>1374</v>
       </c>
       <c r="C120" t="n">
-        <v>8888</v>
+        <v>2845</v>
       </c>
       <c r="D120" t="n">
-        <v>2880.19</v>
+        <v>625.77</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2725,17 +2725,17 @@
         <v>46217</v>
       </c>
       <c r="B121" t="n">
-        <v>2211</v>
+        <v>58</v>
       </c>
       <c r="C121" t="n">
-        <v>874</v>
+        <v>8888</v>
       </c>
       <c r="D121" t="n">
-        <v>1833.56</v>
+        <v>3050.12</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2744,17 +2744,17 @@
         <v>46217</v>
       </c>
       <c r="B122" t="n">
-        <v>1063</v>
+        <v>1937</v>
       </c>
       <c r="C122" t="n">
         <v>8888</v>
       </c>
       <c r="D122" t="n">
-        <v>352.87</v>
+        <v>2199.57</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2763,17 +2763,17 @@
         <v>46217</v>
       </c>
       <c r="B123" t="n">
-        <v>2687</v>
+        <v>1983</v>
       </c>
       <c r="C123" t="n">
         <v>8888</v>
       </c>
       <c r="D123" t="n">
-        <v>1760.22</v>
+        <v>412.16</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2782,13 +2782,13 @@
         <v>46217</v>
       </c>
       <c r="B124" t="n">
-        <v>1117</v>
+        <v>451</v>
       </c>
       <c r="C124" t="n">
         <v>8888</v>
       </c>
       <c r="D124" t="n">
-        <v>1988.42</v>
+        <v>2583.46</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -2801,13 +2801,13 @@
         <v>46217</v>
       </c>
       <c r="B125" t="n">
-        <v>1890</v>
+        <v>1102</v>
       </c>
       <c r="C125" t="n">
-        <v>1953</v>
+        <v>13148</v>
       </c>
       <c r="D125" t="n">
-        <v>1122</v>
+        <v>1346.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -2820,13 +2820,13 @@
         <v>46217</v>
       </c>
       <c r="B126" t="n">
-        <v>1289</v>
+        <v>2767</v>
       </c>
       <c r="C126" t="n">
         <v>8888</v>
       </c>
       <c r="D126" t="n">
-        <v>1214.09</v>
+        <v>920.85</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -2839,17 +2839,17 @@
         <v>46217</v>
       </c>
       <c r="B127" t="n">
-        <v>2363</v>
+        <v>2697</v>
       </c>
       <c r="C127" t="n">
         <v>8888</v>
       </c>
       <c r="D127" t="n">
-        <v>301.92</v>
+        <v>2880.19</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2858,17 +2858,17 @@
         <v>46217</v>
       </c>
       <c r="B128" t="n">
-        <v>1075</v>
+        <v>1117</v>
       </c>
       <c r="C128" t="n">
         <v>8888</v>
       </c>
       <c r="D128" t="n">
-        <v>1845.09</v>
+        <v>4698.18</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2877,13 +2877,13 @@
         <v>46217</v>
       </c>
       <c r="B129" t="n">
-        <v>2107</v>
+        <v>2211</v>
       </c>
       <c r="C129" t="n">
-        <v>1954</v>
+        <v>874</v>
       </c>
       <c r="D129" t="n">
-        <v>2000.86</v>
+        <v>1833.56</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -2896,17 +2896,17 @@
         <v>46217</v>
       </c>
       <c r="B130" t="n">
-        <v>1116</v>
+        <v>1063</v>
       </c>
       <c r="C130" t="n">
         <v>8888</v>
       </c>
       <c r="D130" t="n">
-        <v>1065.24</v>
+        <v>352.87</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2915,13 +2915,13 @@
         <v>46217</v>
       </c>
       <c r="B131" t="n">
-        <v>2190</v>
+        <v>2687</v>
       </c>
       <c r="C131" t="n">
         <v>8888</v>
       </c>
       <c r="D131" t="n">
-        <v>2781.91</v>
+        <v>1760.22</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -2934,13 +2934,13 @@
         <v>46217</v>
       </c>
       <c r="B132" t="n">
-        <v>559</v>
+        <v>1890</v>
       </c>
       <c r="C132" t="n">
-        <v>3009</v>
+        <v>1953</v>
       </c>
       <c r="D132" t="n">
-        <v>1194.24</v>
+        <v>1122</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -2953,17 +2953,17 @@
         <v>46217</v>
       </c>
       <c r="B133" t="n">
-        <v>1278</v>
+        <v>1289</v>
       </c>
       <c r="C133" t="n">
         <v>8888</v>
       </c>
       <c r="D133" t="n">
-        <v>508.07</v>
+        <v>1214.09</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2972,17 +2972,17 @@
         <v>46217</v>
       </c>
       <c r="B134" t="n">
-        <v>58</v>
+        <v>2363</v>
       </c>
       <c r="C134" t="n">
         <v>8888</v>
       </c>
       <c r="D134" t="n">
-        <v>1411.43</v>
+        <v>301.92</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2991,17 +2991,17 @@
         <v>46217</v>
       </c>
       <c r="B135" t="n">
-        <v>629</v>
+        <v>1075</v>
       </c>
       <c r="C135" t="n">
         <v>8888</v>
       </c>
       <c r="D135" t="n">
-        <v>2740.86</v>
+        <v>1845.09</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3010,17 +3010,17 @@
         <v>46217</v>
       </c>
       <c r="B136" t="n">
-        <v>595</v>
+        <v>2107</v>
       </c>
       <c r="C136" t="n">
-        <v>8888</v>
+        <v>1954</v>
       </c>
       <c r="D136" t="n">
-        <v>3191</v>
+        <v>2000.86</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3029,17 +3029,17 @@
         <v>46217</v>
       </c>
       <c r="B137" t="n">
-        <v>949</v>
+        <v>1116</v>
       </c>
       <c r="C137" t="n">
-        <v>1762</v>
+        <v>8888</v>
       </c>
       <c r="D137" t="n">
-        <v>325.65</v>
+        <v>1065.24</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3048,17 +3048,17 @@
         <v>46217</v>
       </c>
       <c r="B138" t="n">
-        <v>2463</v>
+        <v>2190</v>
       </c>
       <c r="C138" t="n">
         <v>8888</v>
       </c>
       <c r="D138" t="n">
-        <v>8336.43</v>
+        <v>2781.91</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3067,17 +3067,17 @@
         <v>46217</v>
       </c>
       <c r="B139" t="n">
-        <v>1064</v>
+        <v>559</v>
       </c>
       <c r="C139" t="n">
-        <v>8888</v>
+        <v>3009</v>
       </c>
       <c r="D139" t="n">
-        <v>1513.21</v>
+        <v>1194.24</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3086,17 +3086,17 @@
         <v>46217</v>
       </c>
       <c r="B140" t="n">
-        <v>1478</v>
+        <v>1278</v>
       </c>
       <c r="C140" t="n">
         <v>8888</v>
       </c>
       <c r="D140" t="n">
-        <v>4067.5</v>
+        <v>508.07</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3105,17 +3105,17 @@
         <v>46217</v>
       </c>
       <c r="B141" t="n">
-        <v>438</v>
+        <v>58</v>
       </c>
       <c r="C141" t="n">
-        <v>2845</v>
+        <v>8888</v>
       </c>
       <c r="D141" t="n">
-        <v>826.76</v>
+        <v>1411.43</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3124,17 +3124,17 @@
         <v>46217</v>
       </c>
       <c r="B142" t="n">
-        <v>2539</v>
+        <v>629</v>
       </c>
       <c r="C142" t="n">
-        <v>3009</v>
+        <v>8888</v>
       </c>
       <c r="D142" t="n">
-        <v>1479.56</v>
+        <v>2740.86</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3143,17 +3143,17 @@
         <v>46217</v>
       </c>
       <c r="B143" t="n">
-        <v>358</v>
+        <v>595</v>
       </c>
       <c r="C143" t="n">
         <v>8888</v>
       </c>
       <c r="D143" t="n">
-        <v>1918.33</v>
+        <v>3191</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3162,17 +3162,17 @@
         <v>46217</v>
       </c>
       <c r="B144" t="n">
-        <v>2107</v>
+        <v>949</v>
       </c>
       <c r="C144" t="n">
-        <v>8888</v>
+        <v>1762</v>
       </c>
       <c r="D144" t="n">
-        <v>4459.75</v>
+        <v>325.65</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3181,17 +3181,17 @@
         <v>46217</v>
       </c>
       <c r="B145" t="n">
-        <v>675</v>
+        <v>2463</v>
       </c>
       <c r="C145" t="n">
         <v>8888</v>
       </c>
       <c r="D145" t="n">
-        <v>1559.23</v>
+        <v>8336.43</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3200,17 +3200,17 @@
         <v>46217</v>
       </c>
       <c r="B146" t="n">
-        <v>2516</v>
+        <v>1064</v>
       </c>
       <c r="C146" t="n">
         <v>8888</v>
       </c>
       <c r="D146" t="n">
-        <v>502.61</v>
+        <v>1513.21</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3219,13 +3219,13 @@
         <v>46217</v>
       </c>
       <c r="B147" t="n">
-        <v>2279</v>
+        <v>1478</v>
       </c>
       <c r="C147" t="n">
         <v>8888</v>
       </c>
       <c r="D147" t="n">
-        <v>1165.17</v>
+        <v>4067.5</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -3238,13 +3238,13 @@
         <v>46217</v>
       </c>
       <c r="B148" t="n">
-        <v>2727</v>
+        <v>438</v>
       </c>
       <c r="C148" t="n">
-        <v>3179</v>
+        <v>2845</v>
       </c>
       <c r="D148" t="n">
-        <v>514.7</v>
+        <v>826.76</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -3257,13 +3257,13 @@
         <v>46217</v>
       </c>
       <c r="B149" t="n">
-        <v>451</v>
+        <v>2539</v>
       </c>
       <c r="C149" t="n">
-        <v>3403</v>
+        <v>3009</v>
       </c>
       <c r="D149" t="n">
-        <v>327.28</v>
+        <v>1783.4</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -3276,13 +3276,13 @@
         <v>46217</v>
       </c>
       <c r="B150" t="n">
-        <v>535</v>
+        <v>358</v>
       </c>
       <c r="C150" t="n">
         <v>8888</v>
       </c>
       <c r="D150" t="n">
-        <v>1369.04</v>
+        <v>1918.33</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -3295,17 +3295,17 @@
         <v>46217</v>
       </c>
       <c r="B151" t="n">
-        <v>2571</v>
+        <v>2107</v>
       </c>
       <c r="C151" t="n">
-        <v>1312</v>
+        <v>8888</v>
       </c>
       <c r="D151" t="n">
-        <v>2202.75</v>
+        <v>4459.75</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3314,13 +3314,13 @@
         <v>46217</v>
       </c>
       <c r="B152" t="n">
-        <v>2782</v>
+        <v>675</v>
       </c>
       <c r="C152" t="n">
         <v>8888</v>
       </c>
       <c r="D152" t="n">
-        <v>753.8</v>
+        <v>1559.23</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -3333,17 +3333,17 @@
         <v>46217</v>
       </c>
       <c r="B153" t="n">
-        <v>610</v>
+        <v>2516</v>
       </c>
       <c r="C153" t="n">
         <v>8888</v>
       </c>
       <c r="D153" t="n">
-        <v>1073.07</v>
+        <v>502.61</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
         <v>46217</v>
       </c>
       <c r="B154" t="n">
-        <v>2245</v>
+        <v>2279</v>
       </c>
       <c r="C154" t="n">
         <v>8888</v>
       </c>
       <c r="D154" t="n">
-        <v>355.88</v>
+        <v>2918.05</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3377,7 +3377,7 @@
         <v>8888</v>
       </c>
       <c r="D155" t="n">
-        <v>4404.7</v>
+        <v>9053.030000000001</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -3390,17 +3390,17 @@
         <v>46217</v>
       </c>
       <c r="B156" t="n">
-        <v>1108</v>
+        <v>2197</v>
       </c>
       <c r="C156" t="n">
         <v>8888</v>
       </c>
       <c r="D156" t="n">
-        <v>508.54</v>
+        <v>1720.05</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3409,13 +3409,13 @@
         <v>46217</v>
       </c>
       <c r="B157" t="n">
-        <v>341</v>
+        <v>2727</v>
       </c>
       <c r="C157" t="n">
-        <v>58</v>
+        <v>3179</v>
       </c>
       <c r="D157" t="n">
-        <v>366.88</v>
+        <v>514.7</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -3428,17 +3428,17 @@
         <v>46217</v>
       </c>
       <c r="B158" t="n">
-        <v>525</v>
+        <v>2516</v>
       </c>
       <c r="C158" t="n">
-        <v>1087</v>
+        <v>8888</v>
       </c>
       <c r="D158" t="n">
-        <v>1830.26</v>
+        <v>896.35</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3447,13 +3447,13 @@
         <v>46217</v>
       </c>
       <c r="B159" t="n">
-        <v>1344</v>
+        <v>451</v>
       </c>
       <c r="C159" t="n">
-        <v>2845</v>
+        <v>3403</v>
       </c>
       <c r="D159" t="n">
-        <v>394.8</v>
+        <v>327.28</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -3466,13 +3466,13 @@
         <v>46217</v>
       </c>
       <c r="B160" t="n">
-        <v>1653</v>
+        <v>535</v>
       </c>
       <c r="C160" t="n">
         <v>8888</v>
       </c>
       <c r="D160" t="n">
-        <v>4383.69</v>
+        <v>1369.04</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -3485,13 +3485,13 @@
         <v>46217</v>
       </c>
       <c r="B161" t="n">
-        <v>1518</v>
+        <v>2571</v>
       </c>
       <c r="C161" t="n">
-        <v>1533</v>
+        <v>1312</v>
       </c>
       <c r="D161" t="n">
-        <v>479.84</v>
+        <v>2202.75</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -3504,17 +3504,17 @@
         <v>46217</v>
       </c>
       <c r="B162" t="n">
-        <v>663</v>
+        <v>2782</v>
       </c>
       <c r="C162" t="n">
         <v>8888</v>
       </c>
       <c r="D162" t="n">
-        <v>824.5599999999999</v>
+        <v>753.8</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3523,17 +3523,17 @@
         <v>46217</v>
       </c>
       <c r="B163" t="n">
-        <v>1075</v>
+        <v>610</v>
       </c>
       <c r="C163" t="n">
-        <v>675</v>
+        <v>8888</v>
       </c>
       <c r="D163" t="n">
-        <v>274.23</v>
+        <v>1073.07</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3542,17 +3542,17 @@
         <v>46217</v>
       </c>
       <c r="B164" t="n">
-        <v>1278</v>
+        <v>2245</v>
       </c>
       <c r="C164" t="n">
         <v>8888</v>
       </c>
       <c r="D164" t="n">
-        <v>1267.68</v>
+        <v>355.88</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3561,17 +3561,17 @@
         <v>46217</v>
       </c>
       <c r="B165" t="n">
-        <v>2089</v>
+        <v>1108</v>
       </c>
       <c r="C165" t="n">
-        <v>1533</v>
+        <v>8888</v>
       </c>
       <c r="D165" t="n">
-        <v>822.05</v>
+        <v>508.54</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3580,13 +3580,13 @@
         <v>46217</v>
       </c>
       <c r="B166" t="n">
-        <v>2133</v>
+        <v>341</v>
       </c>
       <c r="C166" t="n">
-        <v>691</v>
+        <v>58</v>
       </c>
       <c r="D166" t="n">
-        <v>1414.98</v>
+        <v>366.88</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -3599,17 +3599,17 @@
         <v>46217</v>
       </c>
       <c r="B167" t="n">
-        <v>636</v>
+        <v>525</v>
       </c>
       <c r="C167" t="n">
-        <v>8888</v>
+        <v>1087</v>
       </c>
       <c r="D167" t="n">
-        <v>245.25</v>
+        <v>1830.26</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3618,13 +3618,13 @@
         <v>46217</v>
       </c>
       <c r="B168" t="n">
-        <v>429</v>
+        <v>1344</v>
       </c>
       <c r="C168" t="n">
-        <v>2571</v>
+        <v>2845</v>
       </c>
       <c r="D168" t="n">
-        <v>667.12</v>
+        <v>394.8</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -3637,17 +3637,17 @@
         <v>46217</v>
       </c>
       <c r="B169" t="n">
-        <v>2641</v>
+        <v>1653</v>
       </c>
       <c r="C169" t="n">
         <v>8888</v>
       </c>
       <c r="D169" t="n">
-        <v>252.41</v>
+        <v>4383.69</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3656,17 +3656,17 @@
         <v>46217</v>
       </c>
       <c r="B170" t="n">
-        <v>351</v>
+        <v>619</v>
       </c>
       <c r="C170" t="n">
-        <v>3009</v>
+        <v>8888</v>
       </c>
       <c r="D170" t="n">
-        <v>1007.64</v>
+        <v>1809.66</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3675,13 +3675,13 @@
         <v>46217</v>
       </c>
       <c r="B171" t="n">
-        <v>716</v>
+        <v>1518</v>
       </c>
       <c r="C171" t="n">
-        <v>891</v>
+        <v>1533</v>
       </c>
       <c r="D171" t="n">
-        <v>17820</v>
+        <v>479.84</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -3694,17 +3694,17 @@
         <v>46217</v>
       </c>
       <c r="B172" t="n">
-        <v>1137</v>
+        <v>663</v>
       </c>
       <c r="C172" t="n">
         <v>8888</v>
       </c>
       <c r="D172" t="n">
-        <v>5032.13</v>
+        <v>824.5599999999999</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3713,17 +3713,17 @@
         <v>46217</v>
       </c>
       <c r="B173" t="n">
-        <v>1293</v>
+        <v>2734</v>
       </c>
       <c r="C173" t="n">
-        <v>8888</v>
+        <v>3179</v>
       </c>
       <c r="D173" t="n">
-        <v>8102.01</v>
+        <v>284.53</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3732,17 +3732,17 @@
         <v>46217</v>
       </c>
       <c r="B174" t="n">
-        <v>1465</v>
+        <v>353</v>
       </c>
       <c r="C174" t="n">
         <v>8888</v>
       </c>
       <c r="D174" t="n">
-        <v>2218.99</v>
+        <v>1847.54</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3751,17 +3751,17 @@
         <v>46217</v>
       </c>
       <c r="B175" t="n">
-        <v>483</v>
+        <v>1075</v>
       </c>
       <c r="C175" t="n">
-        <v>8888</v>
+        <v>675</v>
       </c>
       <c r="D175" t="n">
-        <v>2444.39</v>
+        <v>274.23</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3770,17 +3770,17 @@
         <v>46217</v>
       </c>
       <c r="B176" t="n">
-        <v>2109</v>
+        <v>2089</v>
       </c>
       <c r="C176" t="n">
-        <v>8888</v>
+        <v>1533</v>
       </c>
       <c r="D176" t="n">
-        <v>433.47</v>
+        <v>1167.99</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3789,17 +3789,17 @@
         <v>46217</v>
       </c>
       <c r="B177" t="n">
-        <v>1064</v>
+        <v>1278</v>
       </c>
       <c r="C177" t="n">
         <v>8888</v>
       </c>
       <c r="D177" t="n">
-        <v>104632.21</v>
+        <v>1267.68</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3808,13 +3808,13 @@
         <v>46217</v>
       </c>
       <c r="B178" t="n">
-        <v>131</v>
+        <v>2133</v>
       </c>
       <c r="C178" t="n">
-        <v>27</v>
+        <v>691</v>
       </c>
       <c r="D178" t="n">
-        <v>876.48</v>
+        <v>1414.98</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -3827,17 +3827,17 @@
         <v>46217</v>
       </c>
       <c r="B179" t="n">
-        <v>663</v>
+        <v>636</v>
       </c>
       <c r="C179" t="n">
         <v>8888</v>
       </c>
       <c r="D179" t="n">
-        <v>1769.59</v>
+        <v>245.25</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3846,17 +3846,17 @@
         <v>46217</v>
       </c>
       <c r="B180" t="n">
-        <v>767</v>
+        <v>429</v>
       </c>
       <c r="C180" t="n">
-        <v>8888</v>
+        <v>2571</v>
       </c>
       <c r="D180" t="n">
-        <v>1127.17</v>
+        <v>667.12</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3865,17 +3865,17 @@
         <v>46217</v>
       </c>
       <c r="B181" t="n">
-        <v>131</v>
+        <v>2641</v>
       </c>
       <c r="C181" t="n">
         <v>8888</v>
       </c>
       <c r="D181" t="n">
-        <v>4787.28</v>
+        <v>252.41</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3884,13 +3884,13 @@
         <v>46217</v>
       </c>
       <c r="B182" t="n">
-        <v>2308</v>
+        <v>351</v>
       </c>
       <c r="C182" t="n">
-        <v>546</v>
+        <v>3009</v>
       </c>
       <c r="D182" t="n">
-        <v>1292.23</v>
+        <v>1007.64</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -3903,13 +3903,13 @@
         <v>46217</v>
       </c>
       <c r="B183" t="n">
-        <v>2709</v>
+        <v>716</v>
       </c>
       <c r="C183" t="n">
-        <v>2220</v>
+        <v>891</v>
       </c>
       <c r="D183" t="n">
-        <v>1663.5</v>
+        <v>17820</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -3922,17 +3922,17 @@
         <v>46217</v>
       </c>
       <c r="B184" t="n">
-        <v>1937</v>
+        <v>1137</v>
       </c>
       <c r="C184" t="n">
         <v>8888</v>
       </c>
       <c r="D184" t="n">
-        <v>1492.4</v>
+        <v>5032.13</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3941,17 +3941,17 @@
         <v>46217</v>
       </c>
       <c r="B185" t="n">
-        <v>2345</v>
+        <v>1293</v>
       </c>
       <c r="C185" t="n">
         <v>8888</v>
       </c>
       <c r="D185" t="n">
-        <v>1562.35</v>
+        <v>8102.01</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3960,17 +3960,17 @@
         <v>46217</v>
       </c>
       <c r="B186" t="n">
-        <v>429</v>
+        <v>1465</v>
       </c>
       <c r="C186" t="n">
-        <v>1281</v>
+        <v>8888</v>
       </c>
       <c r="D186" t="n">
-        <v>2195.97</v>
+        <v>2218.99</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3979,17 +3979,17 @@
         <v>46217</v>
       </c>
       <c r="B187" t="n">
-        <v>2211</v>
+        <v>483</v>
       </c>
       <c r="C187" t="n">
         <v>8888</v>
       </c>
       <c r="D187" t="n">
-        <v>8568.99</v>
+        <v>2862.88</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3998,17 +3998,17 @@
         <v>46217</v>
       </c>
       <c r="B188" t="n">
-        <v>559</v>
+        <v>2109</v>
       </c>
       <c r="C188" t="n">
         <v>8888</v>
       </c>
       <c r="D188" t="n">
-        <v>4021.32</v>
+        <v>433.47</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4017,13 +4017,13 @@
         <v>46217</v>
       </c>
       <c r="B189" t="n">
-        <v>360</v>
+        <v>1064</v>
       </c>
       <c r="C189" t="n">
         <v>8888</v>
       </c>
       <c r="D189" t="n">
-        <v>15052.63</v>
+        <v>104632.21</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -4036,13 +4036,13 @@
         <v>46217</v>
       </c>
       <c r="B190" t="n">
-        <v>1478</v>
+        <v>131</v>
       </c>
       <c r="C190" t="n">
-        <v>675</v>
+        <v>27</v>
       </c>
       <c r="D190" t="n">
-        <v>1662.17</v>
+        <v>876.48</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -4055,17 +4055,17 @@
         <v>46217</v>
       </c>
       <c r="B191" t="n">
-        <v>2251</v>
+        <v>663</v>
       </c>
       <c r="C191" t="n">
         <v>8888</v>
       </c>
       <c r="D191" t="n">
-        <v>797.58</v>
+        <v>1769.59</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4074,17 +4074,17 @@
         <v>46217</v>
       </c>
       <c r="B192" t="n">
-        <v>2250</v>
+        <v>767</v>
       </c>
       <c r="C192" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D192" t="n">
-        <v>2622.81</v>
+        <v>1127.17</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4093,17 +4093,17 @@
         <v>46217</v>
       </c>
       <c r="B193" t="n">
-        <v>451</v>
+        <v>131</v>
       </c>
       <c r="C193" t="n">
         <v>8888</v>
       </c>
       <c r="D193" t="n">
-        <v>1371.26</v>
+        <v>4787.28</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4112,17 +4112,17 @@
         <v>46217</v>
       </c>
       <c r="B194" t="n">
-        <v>40</v>
+        <v>2308</v>
       </c>
       <c r="C194" t="n">
-        <v>8888</v>
+        <v>546</v>
       </c>
       <c r="D194" t="n">
-        <v>1093.47</v>
+        <v>1292.23</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4131,17 +4131,17 @@
         <v>46217</v>
       </c>
       <c r="B195" t="n">
-        <v>530</v>
+        <v>2709</v>
       </c>
       <c r="C195" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D195" t="n">
-        <v>180.08</v>
+        <v>1663.5</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4150,17 +4150,17 @@
         <v>46217</v>
       </c>
       <c r="B196" t="n">
-        <v>1327</v>
+        <v>1937</v>
       </c>
       <c r="C196" t="n">
-        <v>3009</v>
+        <v>8888</v>
       </c>
       <c r="D196" t="n">
-        <v>946.8</v>
+        <v>1492.4</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4169,17 +4169,17 @@
         <v>46217</v>
       </c>
       <c r="B197" t="n">
-        <v>1293</v>
+        <v>1317</v>
       </c>
       <c r="C197" t="n">
-        <v>601</v>
+        <v>8888</v>
       </c>
       <c r="D197" t="n">
-        <v>456.47</v>
+        <v>736.61</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4188,17 +4188,17 @@
         <v>46217</v>
       </c>
       <c r="B198" t="n">
-        <v>424</v>
+        <v>2345</v>
       </c>
       <c r="C198" t="n">
         <v>8888</v>
       </c>
       <c r="D198" t="n">
-        <v>1758.85</v>
+        <v>1562.35</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4207,17 +4207,17 @@
         <v>46217</v>
       </c>
       <c r="B199" t="n">
-        <v>2118</v>
+        <v>429</v>
       </c>
       <c r="C199" t="n">
-        <v>8888</v>
+        <v>1281</v>
       </c>
       <c r="D199" t="n">
-        <v>311.54</v>
+        <v>2195.97</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4226,17 +4226,17 @@
         <v>46217</v>
       </c>
       <c r="B200" t="n">
-        <v>2251</v>
+        <v>2211</v>
       </c>
       <c r="C200" t="n">
         <v>8888</v>
       </c>
       <c r="D200" t="n">
-        <v>603.66</v>
+        <v>8568.99</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4245,17 +4245,17 @@
         <v>46217</v>
       </c>
       <c r="B201" t="n">
-        <v>1299</v>
+        <v>559</v>
       </c>
       <c r="C201" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D201" t="n">
-        <v>3625.32</v>
+        <v>4283.57</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4264,17 +4264,17 @@
         <v>46217</v>
       </c>
       <c r="B202" t="n">
-        <v>89</v>
+        <v>360</v>
       </c>
       <c r="C202" t="n">
         <v>8888</v>
       </c>
       <c r="D202" t="n">
-        <v>1506.42</v>
+        <v>15052.63</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4283,17 +4283,17 @@
         <v>46217</v>
       </c>
       <c r="B203" t="n">
-        <v>2250</v>
+        <v>1478</v>
       </c>
       <c r="C203" t="n">
-        <v>8888</v>
+        <v>675</v>
       </c>
       <c r="D203" t="n">
-        <v>1943.54</v>
+        <v>1662.17</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4302,13 +4302,13 @@
         <v>46217</v>
       </c>
       <c r="B204" t="n">
-        <v>1327</v>
+        <v>2251</v>
       </c>
       <c r="C204" t="n">
         <v>8888</v>
       </c>
       <c r="D204" t="n">
-        <v>319.23</v>
+        <v>797.58</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -4321,17 +4321,17 @@
         <v>46217</v>
       </c>
       <c r="B205" t="n">
-        <v>326</v>
+        <v>2250</v>
       </c>
       <c r="C205" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D205" t="n">
-        <v>151.86</v>
+        <v>2622.81</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4340,13 +4340,13 @@
         <v>46217</v>
       </c>
       <c r="B206" t="n">
-        <v>1372</v>
+        <v>451</v>
       </c>
       <c r="C206" t="n">
         <v>8888</v>
       </c>
       <c r="D206" t="n">
-        <v>1088.02</v>
+        <v>1899.02</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -4359,17 +4359,17 @@
         <v>46217</v>
       </c>
       <c r="B207" t="n">
-        <v>626</v>
+        <v>40</v>
       </c>
       <c r="C207" t="n">
         <v>8888</v>
       </c>
       <c r="D207" t="n">
-        <v>28212.87</v>
+        <v>1093.47</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4378,17 +4378,17 @@
         <v>46217</v>
       </c>
       <c r="B208" t="n">
-        <v>629</v>
+        <v>530</v>
       </c>
       <c r="C208" t="n">
-        <v>675</v>
+        <v>8888</v>
       </c>
       <c r="D208" t="n">
-        <v>2975.45</v>
+        <v>180.08</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4397,13 +4397,13 @@
         <v>46217</v>
       </c>
       <c r="B209" t="n">
-        <v>2651</v>
+        <v>1327</v>
       </c>
       <c r="C209" t="n">
-        <v>58</v>
+        <v>3009</v>
       </c>
       <c r="D209" t="n">
-        <v>648.71</v>
+        <v>946.8</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -4416,13 +4416,13 @@
         <v>46217</v>
       </c>
       <c r="B210" t="n">
-        <v>2114</v>
+        <v>1293</v>
       </c>
       <c r="C210" t="n">
-        <v>1954</v>
+        <v>601</v>
       </c>
       <c r="D210" t="n">
-        <v>879.03</v>
+        <v>456.47</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -4435,17 +4435,17 @@
         <v>46217</v>
       </c>
       <c r="B211" t="n">
-        <v>1299</v>
+        <v>424</v>
       </c>
       <c r="C211" t="n">
-        <v>2522</v>
+        <v>8888</v>
       </c>
       <c r="D211" t="n">
-        <v>6680.93</v>
+        <v>1758.85</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4454,17 +4454,17 @@
         <v>46217</v>
       </c>
       <c r="B212" t="n">
-        <v>40</v>
+        <v>2118</v>
       </c>
       <c r="C212" t="n">
         <v>8888</v>
       </c>
       <c r="D212" t="n">
-        <v>3583.39</v>
+        <v>311.54</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4473,13 +4473,13 @@
         <v>46217</v>
       </c>
       <c r="B213" t="n">
-        <v>40</v>
+        <v>2251</v>
       </c>
       <c r="C213" t="n">
         <v>8888</v>
       </c>
       <c r="D213" t="n">
-        <v>2529.31</v>
+        <v>603.66</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -4492,17 +4492,17 @@
         <v>46217</v>
       </c>
       <c r="B214" t="n">
-        <v>363</v>
+        <v>1299</v>
       </c>
       <c r="C214" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D214" t="n">
-        <v>739.17</v>
+        <v>4140.12</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4511,17 +4511,17 @@
         <v>46217</v>
       </c>
       <c r="B215" t="n">
-        <v>675</v>
+        <v>89</v>
       </c>
       <c r="C215" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D215" t="n">
-        <v>107.13</v>
+        <v>1506.42</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4530,17 +4530,17 @@
         <v>46217</v>
       </c>
       <c r="B216" t="n">
-        <v>636</v>
+        <v>1317</v>
       </c>
       <c r="C216" t="n">
-        <v>8888</v>
+        <v>3179</v>
       </c>
       <c r="D216" t="n">
-        <v>7476.56</v>
+        <v>562.02</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4549,17 +4549,17 @@
         <v>46217</v>
       </c>
       <c r="B217" t="n">
-        <v>1075</v>
+        <v>2250</v>
       </c>
       <c r="C217" t="n">
         <v>8888</v>
       </c>
       <c r="D217" t="n">
-        <v>1970.3</v>
+        <v>1943.54</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4568,17 +4568,17 @@
         <v>46217</v>
       </c>
       <c r="B218" t="n">
-        <v>2245</v>
+        <v>1327</v>
       </c>
       <c r="C218" t="n">
         <v>8888</v>
       </c>
       <c r="D218" t="n">
-        <v>883.75</v>
+        <v>319.23</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4587,13 +4587,13 @@
         <v>46217</v>
       </c>
       <c r="B219" t="n">
-        <v>477</v>
+        <v>326</v>
       </c>
       <c r="C219" t="n">
         <v>8888</v>
       </c>
       <c r="D219" t="n">
-        <v>994.15</v>
+        <v>151.86</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -4606,13 +4606,13 @@
         <v>46217</v>
       </c>
       <c r="B220" t="n">
-        <v>2015</v>
+        <v>1372</v>
       </c>
       <c r="C220" t="n">
         <v>8888</v>
       </c>
       <c r="D220" t="n">
-        <v>3243.05</v>
+        <v>1088.02</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -4625,17 +4625,17 @@
         <v>46217</v>
       </c>
       <c r="B221" t="n">
-        <v>1996</v>
+        <v>1501</v>
       </c>
       <c r="C221" t="n">
-        <v>691</v>
+        <v>8888</v>
       </c>
       <c r="D221" t="n">
-        <v>500.79</v>
+        <v>699.91</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4644,17 +4644,17 @@
         <v>46217</v>
       </c>
       <c r="B222" t="n">
-        <v>1653</v>
+        <v>626</v>
       </c>
       <c r="C222" t="n">
         <v>8888</v>
       </c>
       <c r="D222" t="n">
-        <v>4115.53</v>
+        <v>28212.87</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4663,13 +4663,13 @@
         <v>46217</v>
       </c>
       <c r="B223" t="n">
-        <v>1064</v>
+        <v>629</v>
       </c>
       <c r="C223" t="n">
-        <v>27</v>
+        <v>675</v>
       </c>
       <c r="D223" t="n">
-        <v>1153.23</v>
+        <v>2975.45</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -4682,17 +4682,17 @@
         <v>46217</v>
       </c>
       <c r="B224" t="n">
-        <v>1983</v>
+        <v>2651</v>
       </c>
       <c r="C224" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D224" t="n">
-        <v>1246.33</v>
+        <v>648.71</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4701,17 +4701,17 @@
         <v>46217</v>
       </c>
       <c r="B225" t="n">
-        <v>2118</v>
+        <v>2114</v>
       </c>
       <c r="C225" t="n">
-        <v>8888</v>
+        <v>1954</v>
       </c>
       <c r="D225" t="n">
-        <v>5870.04</v>
+        <v>879.03</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4720,17 +4720,17 @@
         <v>46217</v>
       </c>
       <c r="B226" t="n">
-        <v>559</v>
+        <v>1299</v>
       </c>
       <c r="C226" t="n">
-        <v>8888</v>
+        <v>2522</v>
       </c>
       <c r="D226" t="n">
-        <v>2189.12</v>
+        <v>6680.93</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4739,13 +4739,13 @@
         <v>46217</v>
       </c>
       <c r="B227" t="n">
-        <v>2680</v>
+        <v>40</v>
       </c>
       <c r="C227" t="n">
         <v>8888</v>
       </c>
       <c r="D227" t="n">
-        <v>2285.31</v>
+        <v>3583.39</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -4758,17 +4758,17 @@
         <v>46217</v>
       </c>
       <c r="B228" t="n">
-        <v>2637</v>
+        <v>40</v>
       </c>
       <c r="C228" t="n">
         <v>8888</v>
       </c>
       <c r="D228" t="n">
-        <v>1302.18</v>
+        <v>2529.31</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4777,17 +4777,17 @@
         <v>46217</v>
       </c>
       <c r="B229" t="n">
-        <v>1632</v>
+        <v>363</v>
       </c>
       <c r="C229" t="n">
         <v>8888</v>
       </c>
       <c r="D229" t="n">
-        <v>689.76</v>
+        <v>739.17</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4796,17 +4796,17 @@
         <v>46217</v>
       </c>
       <c r="B230" t="n">
-        <v>2727</v>
+        <v>675</v>
       </c>
       <c r="C230" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D230" t="n">
-        <v>548.33</v>
+        <v>107.13</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4815,17 +4815,17 @@
         <v>46217</v>
       </c>
       <c r="B231" t="n">
-        <v>2026</v>
+        <v>636</v>
       </c>
       <c r="C231" t="n">
         <v>8888</v>
       </c>
       <c r="D231" t="n">
-        <v>699.05</v>
+        <v>7476.56</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4834,17 +4834,17 @@
         <v>46217</v>
       </c>
       <c r="B232" t="n">
-        <v>1117</v>
+        <v>1075</v>
       </c>
       <c r="C232" t="n">
         <v>8888</v>
       </c>
       <c r="D232" t="n">
-        <v>306.02</v>
+        <v>2845.63</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4853,17 +4853,17 @@
         <v>46217</v>
       </c>
       <c r="B233" t="n">
-        <v>664</v>
+        <v>2245</v>
       </c>
       <c r="C233" t="n">
         <v>8888</v>
       </c>
       <c r="D233" t="n">
-        <v>3483.46</v>
+        <v>883.75</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4872,17 +4872,17 @@
         <v>46217</v>
       </c>
       <c r="B234" t="n">
-        <v>1465</v>
+        <v>477</v>
       </c>
       <c r="C234" t="n">
         <v>8888</v>
       </c>
       <c r="D234" t="n">
-        <v>14048.78</v>
+        <v>994.15</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4891,17 +4891,17 @@
         <v>46217</v>
       </c>
       <c r="B235" t="n">
-        <v>2550</v>
+        <v>890</v>
       </c>
       <c r="C235" t="n">
         <v>8888</v>
       </c>
       <c r="D235" t="n">
-        <v>321.05</v>
+        <v>632.85</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4910,17 +4910,17 @@
         <v>46217</v>
       </c>
       <c r="B236" t="n">
-        <v>1756</v>
+        <v>2015</v>
       </c>
       <c r="C236" t="n">
         <v>8888</v>
       </c>
       <c r="D236" t="n">
-        <v>2445</v>
+        <v>3243.05</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4929,17 +4929,17 @@
         <v>46217</v>
       </c>
       <c r="B237" t="n">
-        <v>890</v>
+        <v>1996</v>
       </c>
       <c r="C237" t="n">
-        <v>8888</v>
+        <v>691</v>
       </c>
       <c r="D237" t="n">
-        <v>4287.14</v>
+        <v>500.79</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4948,13 +4948,13 @@
         <v>46217</v>
       </c>
       <c r="B238" t="n">
-        <v>363</v>
+        <v>1653</v>
       </c>
       <c r="C238" t="n">
         <v>8888</v>
       </c>
       <c r="D238" t="n">
-        <v>2517.01</v>
+        <v>4115.53</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -4967,13 +4967,13 @@
         <v>46217</v>
       </c>
       <c r="B239" t="n">
-        <v>2698</v>
+        <v>1064</v>
       </c>
       <c r="C239" t="n">
-        <v>874</v>
+        <v>27</v>
       </c>
       <c r="D239" t="n">
-        <v>1183.42</v>
+        <v>1153.23</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -4986,17 +4986,17 @@
         <v>46217</v>
       </c>
       <c r="B240" t="n">
-        <v>535</v>
+        <v>1983</v>
       </c>
       <c r="C240" t="n">
         <v>8888</v>
       </c>
       <c r="D240" t="n">
-        <v>5293.96</v>
+        <v>1246.33</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -5005,13 +5005,13 @@
         <v>46217</v>
       </c>
       <c r="B241" t="n">
-        <v>2250</v>
+        <v>2118</v>
       </c>
       <c r="C241" t="n">
         <v>8888</v>
       </c>
       <c r="D241" t="n">
-        <v>2650.33</v>
+        <v>5870.04</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -5024,17 +5024,17 @@
         <v>46217</v>
       </c>
       <c r="B242" t="n">
-        <v>2681</v>
+        <v>559</v>
       </c>
       <c r="C242" t="n">
         <v>8888</v>
       </c>
       <c r="D242" t="n">
-        <v>2853.99</v>
+        <v>2189.12</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5043,13 +5043,13 @@
         <v>46217</v>
       </c>
       <c r="B243" t="n">
-        <v>132</v>
+        <v>2680</v>
       </c>
       <c r="C243" t="n">
         <v>8888</v>
       </c>
       <c r="D243" t="n">
-        <v>11123.92</v>
+        <v>2285.31</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -5062,13 +5062,13 @@
         <v>46217</v>
       </c>
       <c r="B244" t="n">
-        <v>2442</v>
+        <v>2637</v>
       </c>
       <c r="C244" t="n">
         <v>8888</v>
       </c>
       <c r="D244" t="n">
-        <v>2822.22</v>
+        <v>1302.18</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -5081,17 +5081,17 @@
         <v>46217</v>
       </c>
       <c r="B245" t="n">
-        <v>363</v>
+        <v>1632</v>
       </c>
       <c r="C245" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D245" t="n">
-        <v>4028</v>
+        <v>689.76</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5100,17 +5100,17 @@
         <v>46217</v>
       </c>
       <c r="B246" t="n">
-        <v>483</v>
+        <v>285</v>
       </c>
       <c r="C246" t="n">
         <v>8888</v>
       </c>
       <c r="D246" t="n">
-        <v>3480.21</v>
+        <v>375.8</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -5119,17 +5119,17 @@
         <v>46217</v>
       </c>
       <c r="B247" t="n">
-        <v>2279</v>
+        <v>2727</v>
       </c>
       <c r="C247" t="n">
         <v>8888</v>
       </c>
       <c r="D247" t="n">
-        <v>740.38</v>
+        <v>548.33</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -5138,13 +5138,13 @@
         <v>46217</v>
       </c>
       <c r="B248" t="n">
-        <v>767</v>
+        <v>2026</v>
       </c>
       <c r="C248" t="n">
         <v>8888</v>
       </c>
       <c r="D248" t="n">
-        <v>718.65</v>
+        <v>699.05</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -5157,13 +5157,13 @@
         <v>46217</v>
       </c>
       <c r="B249" t="n">
-        <v>2607</v>
+        <v>1117</v>
       </c>
       <c r="C249" t="n">
         <v>8888</v>
       </c>
       <c r="D249" t="n">
-        <v>1075.36</v>
+        <v>306.02</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -5176,17 +5176,17 @@
         <v>46217</v>
       </c>
       <c r="B250" t="n">
-        <v>2330</v>
+        <v>664</v>
       </c>
       <c r="C250" t="n">
-        <v>1954</v>
+        <v>8888</v>
       </c>
       <c r="D250" t="n">
-        <v>1923.09</v>
+        <v>3483.46</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5195,17 +5195,17 @@
         <v>46217</v>
       </c>
       <c r="B251" t="n">
-        <v>2472</v>
+        <v>1465</v>
       </c>
       <c r="C251" t="n">
-        <v>2853</v>
+        <v>8888</v>
       </c>
       <c r="D251" t="n">
-        <v>824.0599999999999</v>
+        <v>14048.78</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5214,17 +5214,17 @@
         <v>46217</v>
       </c>
       <c r="B252" t="n">
-        <v>1384</v>
+        <v>2550</v>
       </c>
       <c r="C252" t="n">
         <v>8888</v>
       </c>
       <c r="D252" t="n">
-        <v>585.27</v>
+        <v>321.05</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -5233,17 +5233,17 @@
         <v>46217</v>
       </c>
       <c r="B253" t="n">
-        <v>2709</v>
+        <v>1756</v>
       </c>
       <c r="C253" t="n">
         <v>8888</v>
       </c>
       <c r="D253" t="n">
-        <v>2210.08</v>
+        <v>2445</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -5252,17 +5252,17 @@
         <v>46217</v>
       </c>
       <c r="B254" t="n">
-        <v>619</v>
+        <v>890</v>
       </c>
       <c r="C254" t="n">
-        <v>1139</v>
+        <v>8888</v>
       </c>
       <c r="D254" t="n">
-        <v>3330.07</v>
+        <v>4287.14</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -5271,17 +5271,17 @@
         <v>46217</v>
       </c>
       <c r="B255" t="n">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="C255" t="n">
         <v>8888</v>
       </c>
       <c r="D255" t="n">
-        <v>1725.89</v>
+        <v>2517.01</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5290,17 +5290,17 @@
         <v>46217</v>
       </c>
       <c r="B256" t="n">
-        <v>1137</v>
+        <v>2698</v>
       </c>
       <c r="C256" t="n">
-        <v>8888</v>
+        <v>874</v>
       </c>
       <c r="D256" t="n">
-        <v>4413.34</v>
+        <v>2253.73</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -5309,17 +5309,17 @@
         <v>46217</v>
       </c>
       <c r="B257" t="n">
-        <v>2251</v>
+        <v>535</v>
       </c>
       <c r="C257" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D257" t="n">
-        <v>510.18</v>
+        <v>5293.96</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5328,17 +5328,17 @@
         <v>46217</v>
       </c>
       <c r="B258" t="n">
-        <v>2728</v>
+        <v>2250</v>
       </c>
       <c r="C258" t="n">
-        <v>977</v>
+        <v>8888</v>
       </c>
       <c r="D258" t="n">
-        <v>2256.87</v>
+        <v>5398.63</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5347,13 +5347,13 @@
         <v>46217</v>
       </c>
       <c r="B259" t="n">
-        <v>1293</v>
+        <v>2681</v>
       </c>
       <c r="C259" t="n">
         <v>8888</v>
       </c>
       <c r="D259" t="n">
-        <v>529.2</v>
+        <v>2853.99</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -5366,17 +5366,17 @@
         <v>46217</v>
       </c>
       <c r="B260" t="n">
-        <v>1278</v>
+        <v>132</v>
       </c>
       <c r="C260" t="n">
-        <v>1533</v>
+        <v>8888</v>
       </c>
       <c r="D260" t="n">
-        <v>620.97</v>
+        <v>11963.23</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5385,15 +5385,338 @@
         <v>46217</v>
       </c>
       <c r="B261" t="n">
+        <v>2442</v>
+      </c>
+      <c r="C261" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D261" t="n">
+        <v>2822.22</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B262" t="n">
+        <v>2472</v>
+      </c>
+      <c r="C262" t="n">
+        <v>2853</v>
+      </c>
+      <c r="D262" t="n">
+        <v>2166</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B263" t="n">
+        <v>363</v>
+      </c>
+      <c r="C263" t="n">
+        <v>1898</v>
+      </c>
+      <c r="D263" t="n">
+        <v>4028</v>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B264" t="n">
+        <v>483</v>
+      </c>
+      <c r="C264" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D264" t="n">
+        <v>7612.06</v>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B265" t="n">
+        <v>2279</v>
+      </c>
+      <c r="C265" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D265" t="n">
+        <v>740.38</v>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B266" t="n">
+        <v>767</v>
+      </c>
+      <c r="C266" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D266" t="n">
+        <v>718.65</v>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B267" t="n">
+        <v>2607</v>
+      </c>
+      <c r="C267" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D267" t="n">
+        <v>1075.36</v>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B268" t="n">
+        <v>2330</v>
+      </c>
+      <c r="C268" t="n">
+        <v>1954</v>
+      </c>
+      <c r="D268" t="n">
+        <v>1923.09</v>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B269" t="n">
+        <v>619</v>
+      </c>
+      <c r="C269" t="n">
+        <v>1139</v>
+      </c>
+      <c r="D269" t="n">
+        <v>4840.54</v>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B270" t="n">
+        <v>1384</v>
+      </c>
+      <c r="C270" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D270" t="n">
+        <v>585.27</v>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B271" t="n">
+        <v>2709</v>
+      </c>
+      <c r="C271" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D271" t="n">
+        <v>2210.08</v>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B272" t="n">
+        <v>374</v>
+      </c>
+      <c r="C272" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D272" t="n">
+        <v>2840.69</v>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B273" t="n">
+        <v>1137</v>
+      </c>
+      <c r="C273" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D273" t="n">
+        <v>4413.34</v>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B274" t="n">
+        <v>2251</v>
+      </c>
+      <c r="C274" t="n">
+        <v>3403</v>
+      </c>
+      <c r="D274" t="n">
+        <v>510.18</v>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B275" t="n">
+        <v>2728</v>
+      </c>
+      <c r="C275" t="n">
+        <v>977</v>
+      </c>
+      <c r="D275" t="n">
+        <v>2256.87</v>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B276" t="n">
+        <v>1293</v>
+      </c>
+      <c r="C276" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D276" t="n">
+        <v>529.2</v>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B277" t="n">
+        <v>1278</v>
+      </c>
+      <c r="C277" t="n">
+        <v>1533</v>
+      </c>
+      <c r="D277" t="n">
+        <v>620.97</v>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B278" t="n">
         <v>1380</v>
       </c>
-      <c r="C261" t="n">
-        <v>8888</v>
-      </c>
-      <c r="D261" t="n">
+      <c r="C278" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D278" t="n">
         <v>947.8200000000001</v>
       </c>
-      <c r="E261" t="inlineStr">
+      <c r="E278" t="inlineStr">
         <is>
           <t>FORÇA DE VENDAS</t>
         </is>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E278"/>
+  <dimension ref="A1:E284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,13 +502,13 @@
         <v>46217</v>
       </c>
       <c r="B4" t="n">
-        <v>1254</v>
+        <v>429</v>
       </c>
       <c r="C4" t="n">
         <v>8888</v>
       </c>
       <c r="D4" t="n">
-        <v>1508.08</v>
+        <v>9627.74</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -521,17 +521,17 @@
         <v>46217</v>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>1254</v>
       </c>
       <c r="C5" t="n">
-        <v>1533</v>
+        <v>8888</v>
       </c>
       <c r="D5" t="n">
-        <v>1154.58</v>
+        <v>1508.08</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -540,17 +540,17 @@
         <v>46217</v>
       </c>
       <c r="B6" t="n">
-        <v>1298</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>8888</v>
+        <v>1533</v>
       </c>
       <c r="D6" t="n">
-        <v>13194.04</v>
+        <v>1154.58</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -559,13 +559,13 @@
         <v>46217</v>
       </c>
       <c r="B7" t="n">
-        <v>415</v>
+        <v>1298</v>
       </c>
       <c r="C7" t="n">
         <v>8888</v>
       </c>
       <c r="D7" t="n">
-        <v>13540.93</v>
+        <v>13194.04</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -578,17 +578,17 @@
         <v>46217</v>
       </c>
       <c r="B8" t="n">
-        <v>1653</v>
+        <v>415</v>
       </c>
       <c r="C8" t="n">
-        <v>1281</v>
+        <v>8888</v>
       </c>
       <c r="D8" t="n">
-        <v>4524.08</v>
+        <v>13540.93</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -597,17 +597,17 @@
         <v>46217</v>
       </c>
       <c r="B9" t="n">
-        <v>1064</v>
+        <v>1653</v>
       </c>
       <c r="C9" t="n">
-        <v>8888</v>
+        <v>1281</v>
       </c>
       <c r="D9" t="n">
-        <v>823.42</v>
+        <v>4524.08</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -616,17 +616,17 @@
         <v>46217</v>
       </c>
       <c r="B10" t="n">
-        <v>2769</v>
+        <v>1064</v>
       </c>
       <c r="C10" t="n">
-        <v>977</v>
+        <v>8888</v>
       </c>
       <c r="D10" t="n">
-        <v>637.3200000000001</v>
+        <v>823.42</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -635,17 +635,17 @@
         <v>46217</v>
       </c>
       <c r="B11" t="n">
-        <v>1381</v>
+        <v>2769</v>
       </c>
       <c r="C11" t="n">
-        <v>8888</v>
+        <v>977</v>
       </c>
       <c r="D11" t="n">
-        <v>2196.92</v>
+        <v>637.3200000000001</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -654,13 +654,13 @@
         <v>46217</v>
       </c>
       <c r="B12" t="n">
-        <v>703</v>
+        <v>1381</v>
       </c>
       <c r="C12" t="n">
         <v>8888</v>
       </c>
       <c r="D12" t="n">
-        <v>11161.25</v>
+        <v>2196.92</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -673,13 +673,13 @@
         <v>46217</v>
       </c>
       <c r="B13" t="n">
-        <v>2109</v>
+        <v>703</v>
       </c>
       <c r="C13" t="n">
         <v>8888</v>
       </c>
       <c r="D13" t="n">
-        <v>4813.6</v>
+        <v>11161.25</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -692,17 +692,17 @@
         <v>46217</v>
       </c>
       <c r="B14" t="n">
-        <v>1876</v>
+        <v>2109</v>
       </c>
       <c r="C14" t="n">
-        <v>977</v>
+        <v>8888</v>
       </c>
       <c r="D14" t="n">
-        <v>312.66</v>
+        <v>4813.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -711,13 +711,13 @@
         <v>46217</v>
       </c>
       <c r="B15" t="n">
-        <v>2015</v>
+        <v>1876</v>
       </c>
       <c r="C15" t="n">
-        <v>2571</v>
+        <v>977</v>
       </c>
       <c r="D15" t="n">
-        <v>2593.26</v>
+        <v>312.66</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
         <v>46217</v>
       </c>
       <c r="B16" t="n">
-        <v>1993</v>
+        <v>2015</v>
       </c>
       <c r="C16" t="n">
-        <v>8888</v>
+        <v>2571</v>
       </c>
       <c r="D16" t="n">
-        <v>1785.44</v>
+        <v>2593.26</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
         <v>46217</v>
       </c>
       <c r="B17" t="n">
-        <v>1102</v>
+        <v>1993</v>
       </c>
       <c r="C17" t="n">
         <v>8888</v>
       </c>
       <c r="D17" t="n">
-        <v>3406.59</v>
+        <v>1785.44</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -768,17 +768,17 @@
         <v>46217</v>
       </c>
       <c r="B18" t="n">
-        <v>1937</v>
+        <v>1102</v>
       </c>
       <c r="C18" t="n">
         <v>8888</v>
       </c>
       <c r="D18" t="n">
-        <v>3337.21</v>
+        <v>3406.59</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
         <v>46217</v>
       </c>
       <c r="B19" t="n">
-        <v>1293</v>
+        <v>1937</v>
       </c>
       <c r="C19" t="n">
-        <v>1281</v>
+        <v>8888</v>
       </c>
       <c r="D19" t="n">
-        <v>1337.87</v>
+        <v>3337.21</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -806,17 +806,17 @@
         <v>46217</v>
       </c>
       <c r="B20" t="n">
-        <v>2769</v>
+        <v>1293</v>
       </c>
       <c r="C20" t="n">
-        <v>8888</v>
+        <v>1281</v>
       </c>
       <c r="D20" t="n">
-        <v>2679.02</v>
+        <v>1337.87</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -825,17 +825,17 @@
         <v>46217</v>
       </c>
       <c r="B21" t="n">
-        <v>2657</v>
+        <v>2769</v>
       </c>
       <c r="C21" t="n">
         <v>8888</v>
       </c>
       <c r="D21" t="n">
-        <v>877.0700000000001</v>
+        <v>2679.02</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -844,13 +844,13 @@
         <v>46217</v>
       </c>
       <c r="B22" t="n">
-        <v>1993</v>
+        <v>2657</v>
       </c>
       <c r="C22" t="n">
         <v>8888</v>
       </c>
       <c r="D22" t="n">
-        <v>875.1</v>
+        <v>877.0700000000001</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -863,13 +863,13 @@
         <v>46217</v>
       </c>
       <c r="B23" t="n">
-        <v>2768</v>
+        <v>1993</v>
       </c>
       <c r="C23" t="n">
         <v>8888</v>
       </c>
       <c r="D23" t="n">
-        <v>4890.12</v>
+        <v>875.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -882,13 +882,13 @@
         <v>46217</v>
       </c>
       <c r="B24" t="n">
-        <v>2686</v>
+        <v>2768</v>
       </c>
       <c r="C24" t="n">
         <v>8888</v>
       </c>
       <c r="D24" t="n">
-        <v>1794.4</v>
+        <v>4890.12</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -901,17 +901,17 @@
         <v>46217</v>
       </c>
       <c r="B25" t="n">
-        <v>1890</v>
+        <v>2686</v>
       </c>
       <c r="C25" t="n">
-        <v>3449</v>
+        <v>8888</v>
       </c>
       <c r="D25" t="n">
-        <v>1575.78</v>
+        <v>1794.4</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -920,17 +920,17 @@
         <v>46217</v>
       </c>
       <c r="B26" t="n">
-        <v>33</v>
+        <v>1890</v>
       </c>
       <c r="C26" t="n">
-        <v>8888</v>
+        <v>3449</v>
       </c>
       <c r="D26" t="n">
-        <v>1041.47</v>
+        <v>1575.78</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -939,17 +939,17 @@
         <v>46217</v>
       </c>
       <c r="B27" t="n">
-        <v>2726</v>
+        <v>33</v>
       </c>
       <c r="C27" t="n">
-        <v>1929</v>
+        <v>8888</v>
       </c>
       <c r="D27" t="n">
-        <v>640.1799999999999</v>
+        <v>1041.47</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
         <v>46217</v>
       </c>
       <c r="B28" t="n">
-        <v>89</v>
+        <v>2726</v>
       </c>
       <c r="C28" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D28" t="n">
-        <v>5652.15</v>
+        <v>640.1799999999999</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -977,17 +977,17 @@
         <v>46217</v>
       </c>
       <c r="B29" t="n">
-        <v>1983</v>
+        <v>89</v>
       </c>
       <c r="C29" t="n">
-        <v>841</v>
+        <v>8888</v>
       </c>
       <c r="D29" t="n">
-        <v>243.63</v>
+        <v>5652.15</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -996,13 +996,13 @@
         <v>46217</v>
       </c>
       <c r="B30" t="n">
-        <v>2178</v>
+        <v>1983</v>
       </c>
       <c r="C30" t="n">
-        <v>738</v>
+        <v>841</v>
       </c>
       <c r="D30" t="n">
-        <v>1671.1</v>
+        <v>243.63</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1015,13 +1015,13 @@
         <v>46217</v>
       </c>
       <c r="B31" t="n">
-        <v>2209</v>
+        <v>2178</v>
       </c>
       <c r="C31" t="n">
         <v>738</v>
       </c>
       <c r="D31" t="n">
-        <v>2043.28</v>
+        <v>1671.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1034,17 +1034,17 @@
         <v>46217</v>
       </c>
       <c r="B32" t="n">
-        <v>429</v>
+        <v>2209</v>
       </c>
       <c r="C32" t="n">
-        <v>8888</v>
+        <v>738</v>
       </c>
       <c r="D32" t="n">
-        <v>3775.81</v>
+        <v>2043.28</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
         <v>8888</v>
       </c>
       <c r="D34" t="n">
-        <v>1151.67</v>
+        <v>1563.97</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>8888</v>
       </c>
       <c r="D53" t="n">
-        <v>1301.77</v>
+        <v>2868.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -1680,17 +1680,17 @@
         <v>46217</v>
       </c>
       <c r="B66" t="n">
-        <v>40</v>
+        <v>1137</v>
       </c>
       <c r="C66" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D66" t="n">
-        <v>325.04</v>
+        <v>175.92</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1699,17 +1699,17 @@
         <v>46217</v>
       </c>
       <c r="B67" t="n">
-        <v>2069</v>
+        <v>40</v>
       </c>
       <c r="C67" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D67" t="n">
-        <v>176.8</v>
+        <v>325.04</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1718,13 +1718,13 @@
         <v>46217</v>
       </c>
       <c r="B68" t="n">
-        <v>522</v>
+        <v>2069</v>
       </c>
       <c r="C68" t="n">
         <v>8888</v>
       </c>
       <c r="D68" t="n">
-        <v>151.86</v>
+        <v>176.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -1737,17 +1737,17 @@
         <v>46217</v>
       </c>
       <c r="B69" t="n">
-        <v>1304</v>
+        <v>522</v>
       </c>
       <c r="C69" t="n">
-        <v>213</v>
+        <v>8888</v>
       </c>
       <c r="D69" t="n">
-        <v>297.1</v>
+        <v>151.86</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1756,17 +1756,17 @@
         <v>46217</v>
       </c>
       <c r="B70" t="n">
-        <v>1869</v>
+        <v>1304</v>
       </c>
       <c r="C70" t="n">
-        <v>8888</v>
+        <v>213</v>
       </c>
       <c r="D70" t="n">
-        <v>447.76</v>
+        <v>297.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1775,17 +1775,17 @@
         <v>46217</v>
       </c>
       <c r="B71" t="n">
-        <v>949</v>
+        <v>1869</v>
       </c>
       <c r="C71" t="n">
-        <v>998</v>
+        <v>8888</v>
       </c>
       <c r="D71" t="n">
-        <v>129.85</v>
+        <v>447.76</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1794,17 +1794,17 @@
         <v>46217</v>
       </c>
       <c r="B72" t="n">
-        <v>1317</v>
+        <v>949</v>
       </c>
       <c r="C72" t="n">
-        <v>8888</v>
+        <v>998</v>
       </c>
       <c r="D72" t="n">
-        <v>1628.83</v>
+        <v>129.85</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1813,17 +1813,17 @@
         <v>46217</v>
       </c>
       <c r="B73" t="n">
-        <v>1853</v>
+        <v>363</v>
       </c>
       <c r="C73" t="n">
         <v>8888</v>
       </c>
       <c r="D73" t="n">
-        <v>522.4</v>
+        <v>389.27</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1832,17 +1832,17 @@
         <v>46217</v>
       </c>
       <c r="B74" t="n">
-        <v>360</v>
+        <v>1317</v>
       </c>
       <c r="C74" t="n">
-        <v>546</v>
+        <v>8888</v>
       </c>
       <c r="D74" t="n">
-        <v>9262</v>
+        <v>1628.83</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1851,17 +1851,17 @@
         <v>46217</v>
       </c>
       <c r="B75" t="n">
-        <v>2250</v>
+        <v>360</v>
       </c>
       <c r="C75" t="n">
-        <v>8888</v>
+        <v>546</v>
       </c>
       <c r="D75" t="n">
-        <v>4131.57</v>
+        <v>11823.27</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1870,13 +1870,13 @@
         <v>46217</v>
       </c>
       <c r="B76" t="n">
-        <v>2507</v>
+        <v>1853</v>
       </c>
       <c r="C76" t="n">
         <v>8888</v>
       </c>
       <c r="D76" t="n">
-        <v>4167.12</v>
+        <v>522.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -1889,13 +1889,13 @@
         <v>46217</v>
       </c>
       <c r="B77" t="n">
-        <v>664</v>
+        <v>2250</v>
       </c>
       <c r="C77" t="n">
         <v>8888</v>
       </c>
       <c r="D77" t="n">
-        <v>4099.16</v>
+        <v>4131.57</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -1908,13 +1908,13 @@
         <v>46217</v>
       </c>
       <c r="B78" t="n">
-        <v>1075</v>
+        <v>2507</v>
       </c>
       <c r="C78" t="n">
         <v>8888</v>
       </c>
       <c r="D78" t="n">
-        <v>1743.47</v>
+        <v>4167.12</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -1927,17 +1927,17 @@
         <v>46217</v>
       </c>
       <c r="B79" t="n">
-        <v>1324</v>
+        <v>664</v>
       </c>
       <c r="C79" t="n">
-        <v>738</v>
+        <v>8888</v>
       </c>
       <c r="D79" t="n">
-        <v>4548.42</v>
+        <v>4099.16</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1946,17 +1946,17 @@
         <v>46217</v>
       </c>
       <c r="B80" t="n">
-        <v>1906</v>
+        <v>1075</v>
       </c>
       <c r="C80" t="n">
-        <v>1954</v>
+        <v>8888</v>
       </c>
       <c r="D80" t="n">
-        <v>1445.21</v>
+        <v>1743.47</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1965,13 +1965,13 @@
         <v>46217</v>
       </c>
       <c r="B81" t="n">
-        <v>595</v>
+        <v>1324</v>
       </c>
       <c r="C81" t="n">
-        <v>691</v>
+        <v>738</v>
       </c>
       <c r="D81" t="n">
-        <v>314.52</v>
+        <v>4548.42</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -1984,13 +1984,13 @@
         <v>46217</v>
       </c>
       <c r="B82" t="n">
-        <v>2696</v>
+        <v>1906</v>
       </c>
       <c r="C82" t="n">
-        <v>1312</v>
+        <v>1954</v>
       </c>
       <c r="D82" t="n">
-        <v>677.76</v>
+        <v>1445.21</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2003,17 +2003,17 @@
         <v>46217</v>
       </c>
       <c r="B83" t="n">
-        <v>525</v>
+        <v>595</v>
       </c>
       <c r="C83" t="n">
-        <v>8888</v>
+        <v>691</v>
       </c>
       <c r="D83" t="n">
-        <v>490.08</v>
+        <v>314.52</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2022,17 +2022,17 @@
         <v>46217</v>
       </c>
       <c r="B84" t="n">
-        <v>2491</v>
+        <v>2696</v>
       </c>
       <c r="C84" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D84" t="n">
-        <v>2909.58</v>
+        <v>677.76</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2041,17 +2041,17 @@
         <v>46217</v>
       </c>
       <c r="B85" t="n">
-        <v>2651</v>
+        <v>525</v>
       </c>
       <c r="C85" t="n">
         <v>8888</v>
       </c>
       <c r="D85" t="n">
-        <v>638.64</v>
+        <v>490.08</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2060,13 +2060,13 @@
         <v>46217</v>
       </c>
       <c r="B86" t="n">
-        <v>525</v>
+        <v>2491</v>
       </c>
       <c r="C86" t="n">
         <v>8888</v>
       </c>
       <c r="D86" t="n">
-        <v>4351.19</v>
+        <v>2909.58</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -2079,17 +2079,17 @@
         <v>46217</v>
       </c>
       <c r="B87" t="n">
-        <v>2124</v>
+        <v>2651</v>
       </c>
       <c r="C87" t="n">
         <v>8888</v>
       </c>
       <c r="D87" t="n">
-        <v>3875.99</v>
+        <v>638.64</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2098,17 +2098,17 @@
         <v>46217</v>
       </c>
       <c r="B88" t="n">
-        <v>2695</v>
+        <v>525</v>
       </c>
       <c r="C88" t="n">
         <v>8888</v>
       </c>
       <c r="D88" t="n">
-        <v>1244.27</v>
+        <v>4351.19</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2117,17 +2117,17 @@
         <v>46217</v>
       </c>
       <c r="B89" t="n">
-        <v>1293</v>
+        <v>2124</v>
       </c>
       <c r="C89" t="n">
         <v>8888</v>
       </c>
       <c r="D89" t="n">
-        <v>381.82</v>
+        <v>3875.99</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2136,17 +2136,17 @@
         <v>46217</v>
       </c>
       <c r="B90" t="n">
-        <v>2363</v>
+        <v>2695</v>
       </c>
       <c r="C90" t="n">
         <v>8888</v>
       </c>
       <c r="D90" t="n">
-        <v>2985.2</v>
+        <v>1244.27</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2155,17 +2155,17 @@
         <v>46217</v>
       </c>
       <c r="B91" t="n">
-        <v>2663</v>
+        <v>1293</v>
       </c>
       <c r="C91" t="n">
         <v>8888</v>
       </c>
       <c r="D91" t="n">
-        <v>2146.08</v>
+        <v>381.82</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2174,13 +2174,13 @@
         <v>46217</v>
       </c>
       <c r="B92" t="n">
-        <v>2711</v>
+        <v>2363</v>
       </c>
       <c r="C92" t="n">
         <v>8888</v>
       </c>
       <c r="D92" t="n">
-        <v>2193.56</v>
+        <v>2985.2</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -2193,17 +2193,17 @@
         <v>46217</v>
       </c>
       <c r="B93" t="n">
-        <v>675</v>
+        <v>2663</v>
       </c>
       <c r="C93" t="n">
         <v>8888</v>
       </c>
       <c r="D93" t="n">
-        <v>289.67</v>
+        <v>2146.08</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2212,13 +2212,13 @@
         <v>46217</v>
       </c>
       <c r="B94" t="n">
-        <v>1063</v>
+        <v>2711</v>
       </c>
       <c r="C94" t="n">
         <v>8888</v>
       </c>
       <c r="D94" t="n">
-        <v>1902.46</v>
+        <v>2193.56</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -2231,17 +2231,17 @@
         <v>46217</v>
       </c>
       <c r="B95" t="n">
-        <v>1658</v>
+        <v>675</v>
       </c>
       <c r="C95" t="n">
         <v>8888</v>
       </c>
       <c r="D95" t="n">
-        <v>1357.94</v>
+        <v>289.67</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2250,17 +2250,17 @@
         <v>46217</v>
       </c>
       <c r="B96" t="n">
-        <v>1392</v>
+        <v>1063</v>
       </c>
       <c r="C96" t="n">
         <v>8888</v>
       </c>
       <c r="D96" t="n">
-        <v>814.61</v>
+        <v>1902.46</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2269,13 +2269,13 @@
         <v>46217</v>
       </c>
       <c r="B97" t="n">
-        <v>1007</v>
+        <v>1658</v>
       </c>
       <c r="C97" t="n">
         <v>8888</v>
       </c>
       <c r="D97" t="n">
-        <v>335.77</v>
+        <v>1357.94</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -2288,17 +2288,17 @@
         <v>46217</v>
       </c>
       <c r="B98" t="n">
-        <v>525</v>
+        <v>1289</v>
       </c>
       <c r="C98" t="n">
         <v>8888</v>
       </c>
       <c r="D98" t="n">
-        <v>1243.34</v>
+        <v>1033.43</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2307,17 +2307,17 @@
         <v>46217</v>
       </c>
       <c r="B99" t="n">
-        <v>360</v>
+        <v>1392</v>
       </c>
       <c r="C99" t="n">
         <v>8888</v>
       </c>
       <c r="D99" t="n">
-        <v>749.13</v>
+        <v>814.61</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2326,17 +2326,17 @@
         <v>46217</v>
       </c>
       <c r="B100" t="n">
-        <v>1324</v>
+        <v>1007</v>
       </c>
       <c r="C100" t="n">
         <v>8888</v>
       </c>
       <c r="D100" t="n">
-        <v>327.19</v>
+        <v>335.77</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2345,17 +2345,17 @@
         <v>46217</v>
       </c>
       <c r="B101" t="n">
-        <v>1956</v>
+        <v>525</v>
       </c>
       <c r="C101" t="n">
-        <v>423</v>
+        <v>8888</v>
       </c>
       <c r="D101" t="n">
-        <v>503.8</v>
+        <v>1243.34</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2364,13 +2364,13 @@
         <v>46217</v>
       </c>
       <c r="B102" t="n">
-        <v>569</v>
+        <v>360</v>
       </c>
       <c r="C102" t="n">
         <v>8888</v>
       </c>
       <c r="D102" t="n">
-        <v>24022.25</v>
+        <v>749.13</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -2383,17 +2383,17 @@
         <v>46217</v>
       </c>
       <c r="B103" t="n">
-        <v>949</v>
+        <v>1324</v>
       </c>
       <c r="C103" t="n">
-        <v>1134</v>
+        <v>8888</v>
       </c>
       <c r="D103" t="n">
-        <v>327.6</v>
+        <v>327.19</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2402,13 +2402,13 @@
         <v>46217</v>
       </c>
       <c r="B104" t="n">
-        <v>326</v>
+        <v>1956</v>
       </c>
       <c r="C104" t="n">
-        <v>1110</v>
+        <v>423</v>
       </c>
       <c r="D104" t="n">
-        <v>2424.03</v>
+        <v>503.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -2421,13 +2421,13 @@
         <v>46217</v>
       </c>
       <c r="B105" t="n">
-        <v>2133</v>
+        <v>569</v>
       </c>
       <c r="C105" t="n">
         <v>8888</v>
       </c>
       <c r="D105" t="n">
-        <v>66030.34</v>
+        <v>24402.61</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -2440,17 +2440,17 @@
         <v>46217</v>
       </c>
       <c r="B106" t="n">
-        <v>326</v>
+        <v>949</v>
       </c>
       <c r="C106" t="n">
-        <v>8888</v>
+        <v>1134</v>
       </c>
       <c r="D106" t="n">
-        <v>713</v>
+        <v>327.6</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2459,17 +2459,17 @@
         <v>46217</v>
       </c>
       <c r="B107" t="n">
-        <v>629</v>
+        <v>326</v>
       </c>
       <c r="C107" t="n">
-        <v>8888</v>
+        <v>1110</v>
       </c>
       <c r="D107" t="n">
-        <v>1759.43</v>
+        <v>2424.03</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2478,17 +2478,17 @@
         <v>46217</v>
       </c>
       <c r="B108" t="n">
-        <v>325</v>
+        <v>2133</v>
       </c>
       <c r="C108" t="n">
         <v>8888</v>
       </c>
       <c r="D108" t="n">
-        <v>801.04</v>
+        <v>66030.34</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2497,17 +2497,17 @@
         <v>46217</v>
       </c>
       <c r="B109" t="n">
-        <v>1293</v>
+        <v>326</v>
       </c>
       <c r="C109" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D109" t="n">
-        <v>8365.559999999999</v>
+        <v>997.17</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2516,17 +2516,17 @@
         <v>46217</v>
       </c>
       <c r="B110" t="n">
-        <v>131</v>
+        <v>629</v>
       </c>
       <c r="C110" t="n">
         <v>8888</v>
       </c>
       <c r="D110" t="n">
-        <v>1969.93</v>
+        <v>1759.43</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2535,13 +2535,13 @@
         <v>46217</v>
       </c>
       <c r="B111" t="n">
-        <v>2697</v>
+        <v>325</v>
       </c>
       <c r="C111" t="n">
         <v>8888</v>
       </c>
       <c r="D111" t="n">
-        <v>420.48</v>
+        <v>945.33</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -2554,17 +2554,17 @@
         <v>46217</v>
       </c>
       <c r="B112" t="n">
-        <v>2279</v>
+        <v>1293</v>
       </c>
       <c r="C112" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D112" t="n">
-        <v>1034.25</v>
+        <v>8365.559999999999</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2573,17 +2573,17 @@
         <v>46217</v>
       </c>
       <c r="B113" t="n">
-        <v>1340</v>
+        <v>131</v>
       </c>
       <c r="C113" t="n">
         <v>8888</v>
       </c>
       <c r="D113" t="n">
-        <v>4420.54</v>
+        <v>1969.93</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2592,13 +2592,13 @@
         <v>46217</v>
       </c>
       <c r="B114" t="n">
-        <v>2641</v>
+        <v>2697</v>
       </c>
       <c r="C114" t="n">
         <v>8888</v>
       </c>
       <c r="D114" t="n">
-        <v>557.52</v>
+        <v>420.48</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -2611,17 +2611,17 @@
         <v>46217</v>
       </c>
       <c r="B115" t="n">
-        <v>1116</v>
+        <v>2279</v>
       </c>
       <c r="C115" t="n">
         <v>8888</v>
       </c>
       <c r="D115" t="n">
-        <v>1293.89</v>
+        <v>1034.25</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2630,13 +2630,13 @@
         <v>46217</v>
       </c>
       <c r="B116" t="n">
-        <v>2178</v>
+        <v>1340</v>
       </c>
       <c r="C116" t="n">
         <v>8888</v>
       </c>
       <c r="D116" t="n">
-        <v>5333.4</v>
+        <v>4420.54</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -2649,13 +2649,13 @@
         <v>46217</v>
       </c>
       <c r="B117" t="n">
-        <v>1756</v>
+        <v>2641</v>
       </c>
       <c r="C117" t="n">
         <v>8888</v>
       </c>
       <c r="D117" t="n">
-        <v>742.23</v>
+        <v>557.52</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -2668,17 +2668,17 @@
         <v>46217</v>
       </c>
       <c r="B118" t="n">
-        <v>131</v>
+        <v>1116</v>
       </c>
       <c r="C118" t="n">
         <v>8888</v>
       </c>
       <c r="D118" t="n">
-        <v>6513.46</v>
+        <v>1293.89</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2687,13 +2687,13 @@
         <v>46217</v>
       </c>
       <c r="B119" t="n">
-        <v>2081</v>
+        <v>2178</v>
       </c>
       <c r="C119" t="n">
         <v>8888</v>
       </c>
       <c r="D119" t="n">
-        <v>1022.42</v>
+        <v>5333.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -2706,17 +2706,17 @@
         <v>46217</v>
       </c>
       <c r="B120" t="n">
-        <v>1374</v>
+        <v>1756</v>
       </c>
       <c r="C120" t="n">
-        <v>2845</v>
+        <v>8888</v>
       </c>
       <c r="D120" t="n">
-        <v>625.77</v>
+        <v>742.23</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2725,17 +2725,17 @@
         <v>46217</v>
       </c>
       <c r="B121" t="n">
-        <v>58</v>
+        <v>131</v>
       </c>
       <c r="C121" t="n">
         <v>8888</v>
       </c>
       <c r="D121" t="n">
-        <v>3050.12</v>
+        <v>6513.46</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2744,13 +2744,13 @@
         <v>46217</v>
       </c>
       <c r="B122" t="n">
-        <v>1937</v>
+        <v>2081</v>
       </c>
       <c r="C122" t="n">
         <v>8888</v>
       </c>
       <c r="D122" t="n">
-        <v>2199.57</v>
+        <v>1022.42</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -2763,17 +2763,17 @@
         <v>46217</v>
       </c>
       <c r="B123" t="n">
-        <v>1983</v>
+        <v>1374</v>
       </c>
       <c r="C123" t="n">
-        <v>8888</v>
+        <v>2845</v>
       </c>
       <c r="D123" t="n">
-        <v>412.16</v>
+        <v>625.77</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2782,17 +2782,17 @@
         <v>46217</v>
       </c>
       <c r="B124" t="n">
-        <v>451</v>
+        <v>58</v>
       </c>
       <c r="C124" t="n">
         <v>8888</v>
       </c>
       <c r="D124" t="n">
-        <v>2583.46</v>
+        <v>3050.12</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2801,17 +2801,17 @@
         <v>46217</v>
       </c>
       <c r="B125" t="n">
-        <v>1102</v>
+        <v>1937</v>
       </c>
       <c r="C125" t="n">
-        <v>13148</v>
+        <v>8888</v>
       </c>
       <c r="D125" t="n">
-        <v>1346.4</v>
+        <v>2199.57</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2820,17 +2820,17 @@
         <v>46217</v>
       </c>
       <c r="B126" t="n">
-        <v>2767</v>
+        <v>1983</v>
       </c>
       <c r="C126" t="n">
         <v>8888</v>
       </c>
       <c r="D126" t="n">
-        <v>920.85</v>
+        <v>412.16</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2839,17 +2839,17 @@
         <v>46217</v>
       </c>
       <c r="B127" t="n">
-        <v>2697</v>
+        <v>451</v>
       </c>
       <c r="C127" t="n">
         <v>8888</v>
       </c>
       <c r="D127" t="n">
-        <v>2880.19</v>
+        <v>2583.46</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2858,17 +2858,17 @@
         <v>46217</v>
       </c>
       <c r="B128" t="n">
-        <v>1117</v>
+        <v>1289</v>
       </c>
       <c r="C128" t="n">
         <v>8888</v>
       </c>
       <c r="D128" t="n">
-        <v>4698.18</v>
+        <v>2582.2</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2877,13 +2877,13 @@
         <v>46217</v>
       </c>
       <c r="B129" t="n">
-        <v>2211</v>
+        <v>1102</v>
       </c>
       <c r="C129" t="n">
-        <v>874</v>
+        <v>13148</v>
       </c>
       <c r="D129" t="n">
-        <v>1833.56</v>
+        <v>1346.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -2896,17 +2896,17 @@
         <v>46217</v>
       </c>
       <c r="B130" t="n">
-        <v>1063</v>
+        <v>2767</v>
       </c>
       <c r="C130" t="n">
         <v>8888</v>
       </c>
       <c r="D130" t="n">
-        <v>352.87</v>
+        <v>920.85</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2915,13 +2915,13 @@
         <v>46217</v>
       </c>
       <c r="B131" t="n">
-        <v>2687</v>
+        <v>2697</v>
       </c>
       <c r="C131" t="n">
         <v>8888</v>
       </c>
       <c r="D131" t="n">
-        <v>1760.22</v>
+        <v>2880.19</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -2934,17 +2934,17 @@
         <v>46217</v>
       </c>
       <c r="B132" t="n">
-        <v>1890</v>
+        <v>1117</v>
       </c>
       <c r="C132" t="n">
-        <v>1953</v>
+        <v>8888</v>
       </c>
       <c r="D132" t="n">
-        <v>1122</v>
+        <v>4698.18</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2953,17 +2953,17 @@
         <v>46217</v>
       </c>
       <c r="B133" t="n">
-        <v>1289</v>
+        <v>2211</v>
       </c>
       <c r="C133" t="n">
-        <v>8888</v>
+        <v>874</v>
       </c>
       <c r="D133" t="n">
-        <v>1214.09</v>
+        <v>1833.56</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2972,17 +2972,17 @@
         <v>46217</v>
       </c>
       <c r="B134" t="n">
-        <v>2363</v>
+        <v>1063</v>
       </c>
       <c r="C134" t="n">
         <v>8888</v>
       </c>
       <c r="D134" t="n">
-        <v>301.92</v>
+        <v>352.87</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2991,17 +2991,17 @@
         <v>46217</v>
       </c>
       <c r="B135" t="n">
-        <v>1075</v>
+        <v>2687</v>
       </c>
       <c r="C135" t="n">
         <v>8888</v>
       </c>
       <c r="D135" t="n">
-        <v>1845.09</v>
+        <v>1760.22</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3010,13 +3010,13 @@
         <v>46217</v>
       </c>
       <c r="B136" t="n">
-        <v>2107</v>
+        <v>1890</v>
       </c>
       <c r="C136" t="n">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="D136" t="n">
-        <v>2000.86</v>
+        <v>1122</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -3029,17 +3029,17 @@
         <v>46217</v>
       </c>
       <c r="B137" t="n">
-        <v>1116</v>
+        <v>2363</v>
       </c>
       <c r="C137" t="n">
         <v>8888</v>
       </c>
       <c r="D137" t="n">
-        <v>1065.24</v>
+        <v>301.92</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3048,17 +3048,17 @@
         <v>46217</v>
       </c>
       <c r="B138" t="n">
-        <v>2190</v>
+        <v>1075</v>
       </c>
       <c r="C138" t="n">
         <v>8888</v>
       </c>
       <c r="D138" t="n">
-        <v>2781.91</v>
+        <v>1845.09</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3067,13 +3067,13 @@
         <v>46217</v>
       </c>
       <c r="B139" t="n">
-        <v>559</v>
+        <v>2107</v>
       </c>
       <c r="C139" t="n">
-        <v>3009</v>
+        <v>1954</v>
       </c>
       <c r="D139" t="n">
-        <v>1194.24</v>
+        <v>2000.86</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -3086,17 +3086,17 @@
         <v>46217</v>
       </c>
       <c r="B140" t="n">
-        <v>1278</v>
+        <v>1116</v>
       </c>
       <c r="C140" t="n">
         <v>8888</v>
       </c>
       <c r="D140" t="n">
-        <v>508.07</v>
+        <v>1065.24</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3105,13 +3105,13 @@
         <v>46217</v>
       </c>
       <c r="B141" t="n">
-        <v>58</v>
+        <v>2190</v>
       </c>
       <c r="C141" t="n">
         <v>8888</v>
       </c>
       <c r="D141" t="n">
-        <v>1411.43</v>
+        <v>2781.91</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -3124,17 +3124,17 @@
         <v>46217</v>
       </c>
       <c r="B142" t="n">
-        <v>629</v>
+        <v>559</v>
       </c>
       <c r="C142" t="n">
-        <v>8888</v>
+        <v>3009</v>
       </c>
       <c r="D142" t="n">
-        <v>2740.86</v>
+        <v>1194.24</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3143,17 +3143,17 @@
         <v>46217</v>
       </c>
       <c r="B143" t="n">
-        <v>595</v>
+        <v>1278</v>
       </c>
       <c r="C143" t="n">
         <v>8888</v>
       </c>
       <c r="D143" t="n">
-        <v>3191</v>
+        <v>508.07</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3162,17 +3162,17 @@
         <v>46217</v>
       </c>
       <c r="B144" t="n">
-        <v>949</v>
+        <v>58</v>
       </c>
       <c r="C144" t="n">
-        <v>1762</v>
+        <v>8888</v>
       </c>
       <c r="D144" t="n">
-        <v>325.65</v>
+        <v>1411.43</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3181,17 +3181,17 @@
         <v>46217</v>
       </c>
       <c r="B145" t="n">
-        <v>2463</v>
+        <v>629</v>
       </c>
       <c r="C145" t="n">
         <v>8888</v>
       </c>
       <c r="D145" t="n">
-        <v>8336.43</v>
+        <v>2740.86</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3200,17 +3200,17 @@
         <v>46217</v>
       </c>
       <c r="B146" t="n">
-        <v>1064</v>
+        <v>595</v>
       </c>
       <c r="C146" t="n">
         <v>8888</v>
       </c>
       <c r="D146" t="n">
-        <v>1513.21</v>
+        <v>3191</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3219,17 +3219,17 @@
         <v>46217</v>
       </c>
       <c r="B147" t="n">
-        <v>1478</v>
+        <v>949</v>
       </c>
       <c r="C147" t="n">
-        <v>8888</v>
+        <v>1762</v>
       </c>
       <c r="D147" t="n">
-        <v>4067.5</v>
+        <v>325.65</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3238,17 +3238,17 @@
         <v>46217</v>
       </c>
       <c r="B148" t="n">
-        <v>438</v>
+        <v>2463</v>
       </c>
       <c r="C148" t="n">
-        <v>2845</v>
+        <v>8888</v>
       </c>
       <c r="D148" t="n">
-        <v>826.76</v>
+        <v>8336.43</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3257,17 +3257,17 @@
         <v>46217</v>
       </c>
       <c r="B149" t="n">
-        <v>2539</v>
+        <v>1064</v>
       </c>
       <c r="C149" t="n">
-        <v>3009</v>
+        <v>8888</v>
       </c>
       <c r="D149" t="n">
-        <v>1783.4</v>
+        <v>1513.21</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3276,13 +3276,13 @@
         <v>46217</v>
       </c>
       <c r="B150" t="n">
-        <v>358</v>
+        <v>1478</v>
       </c>
       <c r="C150" t="n">
         <v>8888</v>
       </c>
       <c r="D150" t="n">
-        <v>1918.33</v>
+        <v>4067.5</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -3295,17 +3295,17 @@
         <v>46217</v>
       </c>
       <c r="B151" t="n">
-        <v>2107</v>
+        <v>438</v>
       </c>
       <c r="C151" t="n">
-        <v>8888</v>
+        <v>2845</v>
       </c>
       <c r="D151" t="n">
-        <v>4459.75</v>
+        <v>826.76</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3314,17 +3314,17 @@
         <v>46217</v>
       </c>
       <c r="B152" t="n">
-        <v>675</v>
+        <v>2539</v>
       </c>
       <c r="C152" t="n">
-        <v>8888</v>
+        <v>3009</v>
       </c>
       <c r="D152" t="n">
-        <v>1559.23</v>
+        <v>1783.4</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3333,17 +3333,17 @@
         <v>46217</v>
       </c>
       <c r="B153" t="n">
-        <v>2516</v>
+        <v>358</v>
       </c>
       <c r="C153" t="n">
         <v>8888</v>
       </c>
       <c r="D153" t="n">
-        <v>502.61</v>
+        <v>1918.33</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
         <v>46217</v>
       </c>
       <c r="B154" t="n">
-        <v>2279</v>
+        <v>2107</v>
       </c>
       <c r="C154" t="n">
         <v>8888</v>
       </c>
       <c r="D154" t="n">
-        <v>2918.05</v>
+        <v>4459.75</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3371,13 +3371,13 @@
         <v>46217</v>
       </c>
       <c r="B155" t="n">
-        <v>619</v>
+        <v>675</v>
       </c>
       <c r="C155" t="n">
         <v>8888</v>
       </c>
       <c r="D155" t="n">
-        <v>9053.030000000001</v>
+        <v>1559.23</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -3390,13 +3390,13 @@
         <v>46217</v>
       </c>
       <c r="B156" t="n">
-        <v>2197</v>
+        <v>2516</v>
       </c>
       <c r="C156" t="n">
         <v>8888</v>
       </c>
       <c r="D156" t="n">
-        <v>1720.05</v>
+        <v>502.61</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -3409,17 +3409,17 @@
         <v>46217</v>
       </c>
       <c r="B157" t="n">
-        <v>2727</v>
+        <v>2279</v>
       </c>
       <c r="C157" t="n">
-        <v>3179</v>
+        <v>8888</v>
       </c>
       <c r="D157" t="n">
-        <v>514.7</v>
+        <v>2918.05</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3428,17 +3428,17 @@
         <v>46217</v>
       </c>
       <c r="B158" t="n">
-        <v>2516</v>
+        <v>619</v>
       </c>
       <c r="C158" t="n">
         <v>8888</v>
       </c>
       <c r="D158" t="n">
-        <v>896.35</v>
+        <v>9053.030000000001</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3447,17 +3447,17 @@
         <v>46217</v>
       </c>
       <c r="B159" t="n">
-        <v>451</v>
+        <v>2197</v>
       </c>
       <c r="C159" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D159" t="n">
-        <v>327.28</v>
+        <v>1720.05</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3466,17 +3466,17 @@
         <v>46217</v>
       </c>
       <c r="B160" t="n">
-        <v>535</v>
+        <v>2727</v>
       </c>
       <c r="C160" t="n">
-        <v>8888</v>
+        <v>3179</v>
       </c>
       <c r="D160" t="n">
-        <v>1369.04</v>
+        <v>514.7</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3485,17 +3485,17 @@
         <v>46217</v>
       </c>
       <c r="B161" t="n">
-        <v>2571</v>
+        <v>2516</v>
       </c>
       <c r="C161" t="n">
-        <v>1312</v>
+        <v>8888</v>
       </c>
       <c r="D161" t="n">
-        <v>2202.75</v>
+        <v>896.35</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3504,17 +3504,17 @@
         <v>46217</v>
       </c>
       <c r="B162" t="n">
-        <v>2782</v>
+        <v>451</v>
       </c>
       <c r="C162" t="n">
-        <v>8888</v>
+        <v>3403</v>
       </c>
       <c r="D162" t="n">
-        <v>753.8</v>
+        <v>327.28</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3523,17 +3523,17 @@
         <v>46217</v>
       </c>
       <c r="B163" t="n">
-        <v>610</v>
+        <v>535</v>
       </c>
       <c r="C163" t="n">
         <v>8888</v>
       </c>
       <c r="D163" t="n">
-        <v>1073.07</v>
+        <v>1369.04</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3542,17 +3542,17 @@
         <v>46217</v>
       </c>
       <c r="B164" t="n">
-        <v>2245</v>
+        <v>2571</v>
       </c>
       <c r="C164" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D164" t="n">
-        <v>355.88</v>
+        <v>2202.75</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3561,17 +3561,17 @@
         <v>46217</v>
       </c>
       <c r="B165" t="n">
-        <v>1108</v>
+        <v>2782</v>
       </c>
       <c r="C165" t="n">
         <v>8888</v>
       </c>
       <c r="D165" t="n">
-        <v>508.54</v>
+        <v>753.8</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3580,17 +3580,17 @@
         <v>46217</v>
       </c>
       <c r="B166" t="n">
-        <v>341</v>
+        <v>610</v>
       </c>
       <c r="C166" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D166" t="n">
-        <v>366.88</v>
+        <v>1073.07</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3599,17 +3599,17 @@
         <v>46217</v>
       </c>
       <c r="B167" t="n">
-        <v>525</v>
+        <v>2245</v>
       </c>
       <c r="C167" t="n">
-        <v>1087</v>
+        <v>8888</v>
       </c>
       <c r="D167" t="n">
-        <v>1830.26</v>
+        <v>355.88</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3618,17 +3618,17 @@
         <v>46217</v>
       </c>
       <c r="B168" t="n">
-        <v>1344</v>
+        <v>1108</v>
       </c>
       <c r="C168" t="n">
-        <v>2845</v>
+        <v>8888</v>
       </c>
       <c r="D168" t="n">
-        <v>394.8</v>
+        <v>508.54</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3637,17 +3637,17 @@
         <v>46217</v>
       </c>
       <c r="B169" t="n">
-        <v>1653</v>
+        <v>341</v>
       </c>
       <c r="C169" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D169" t="n">
-        <v>4383.69</v>
+        <v>366.88</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3656,17 +3656,17 @@
         <v>46217</v>
       </c>
       <c r="B170" t="n">
-        <v>619</v>
+        <v>525</v>
       </c>
       <c r="C170" t="n">
-        <v>8888</v>
+        <v>1087</v>
       </c>
       <c r="D170" t="n">
-        <v>1809.66</v>
+        <v>1830.26</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3675,13 +3675,13 @@
         <v>46217</v>
       </c>
       <c r="B171" t="n">
-        <v>1518</v>
+        <v>1344</v>
       </c>
       <c r="C171" t="n">
-        <v>1533</v>
+        <v>2845</v>
       </c>
       <c r="D171" t="n">
-        <v>479.84</v>
+        <v>394.8</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -3694,13 +3694,13 @@
         <v>46217</v>
       </c>
       <c r="B172" t="n">
-        <v>663</v>
+        <v>1653</v>
       </c>
       <c r="C172" t="n">
         <v>8888</v>
       </c>
       <c r="D172" t="n">
-        <v>824.5599999999999</v>
+        <v>4383.69</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -3713,17 +3713,17 @@
         <v>46217</v>
       </c>
       <c r="B173" t="n">
-        <v>2734</v>
+        <v>619</v>
       </c>
       <c r="C173" t="n">
-        <v>3179</v>
+        <v>8888</v>
       </c>
       <c r="D173" t="n">
-        <v>284.53</v>
+        <v>1809.66</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3732,17 +3732,17 @@
         <v>46217</v>
       </c>
       <c r="B174" t="n">
-        <v>353</v>
+        <v>1518</v>
       </c>
       <c r="C174" t="n">
-        <v>8888</v>
+        <v>1533</v>
       </c>
       <c r="D174" t="n">
-        <v>1847.54</v>
+        <v>479.84</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3751,17 +3751,17 @@
         <v>46217</v>
       </c>
       <c r="B175" t="n">
-        <v>1075</v>
+        <v>663</v>
       </c>
       <c r="C175" t="n">
-        <v>675</v>
+        <v>8888</v>
       </c>
       <c r="D175" t="n">
-        <v>274.23</v>
+        <v>824.5599999999999</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3770,13 +3770,13 @@
         <v>46217</v>
       </c>
       <c r="B176" t="n">
-        <v>2089</v>
+        <v>2734</v>
       </c>
       <c r="C176" t="n">
-        <v>1533</v>
+        <v>3179</v>
       </c>
       <c r="D176" t="n">
-        <v>1167.99</v>
+        <v>284.53</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -3789,17 +3789,17 @@
         <v>46217</v>
       </c>
       <c r="B177" t="n">
-        <v>1278</v>
+        <v>353</v>
       </c>
       <c r="C177" t="n">
         <v>8888</v>
       </c>
       <c r="D177" t="n">
-        <v>1267.68</v>
+        <v>1847.54</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3808,13 +3808,13 @@
         <v>46217</v>
       </c>
       <c r="B178" t="n">
-        <v>2133</v>
+        <v>1075</v>
       </c>
       <c r="C178" t="n">
-        <v>691</v>
+        <v>675</v>
       </c>
       <c r="D178" t="n">
-        <v>1414.98</v>
+        <v>274.23</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -3827,17 +3827,17 @@
         <v>46217</v>
       </c>
       <c r="B179" t="n">
-        <v>636</v>
+        <v>2089</v>
       </c>
       <c r="C179" t="n">
-        <v>8888</v>
+        <v>1533</v>
       </c>
       <c r="D179" t="n">
-        <v>245.25</v>
+        <v>1167.99</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3846,17 +3846,17 @@
         <v>46217</v>
       </c>
       <c r="B180" t="n">
-        <v>429</v>
+        <v>1278</v>
       </c>
       <c r="C180" t="n">
-        <v>2571</v>
+        <v>8888</v>
       </c>
       <c r="D180" t="n">
-        <v>667.12</v>
+        <v>1267.68</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3865,17 +3865,17 @@
         <v>46217</v>
       </c>
       <c r="B181" t="n">
-        <v>2641</v>
+        <v>2133</v>
       </c>
       <c r="C181" t="n">
-        <v>8888</v>
+        <v>691</v>
       </c>
       <c r="D181" t="n">
-        <v>252.41</v>
+        <v>1414.98</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3884,17 +3884,17 @@
         <v>46217</v>
       </c>
       <c r="B182" t="n">
-        <v>351</v>
+        <v>636</v>
       </c>
       <c r="C182" t="n">
-        <v>3009</v>
+        <v>8888</v>
       </c>
       <c r="D182" t="n">
-        <v>1007.64</v>
+        <v>245.25</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3903,13 +3903,13 @@
         <v>46217</v>
       </c>
       <c r="B183" t="n">
-        <v>716</v>
+        <v>429</v>
       </c>
       <c r="C183" t="n">
-        <v>891</v>
+        <v>2571</v>
       </c>
       <c r="D183" t="n">
-        <v>17820</v>
+        <v>667.12</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -3922,17 +3922,17 @@
         <v>46217</v>
       </c>
       <c r="B184" t="n">
-        <v>1137</v>
+        <v>2641</v>
       </c>
       <c r="C184" t="n">
         <v>8888</v>
       </c>
       <c r="D184" t="n">
-        <v>5032.13</v>
+        <v>252.41</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3941,17 +3941,17 @@
         <v>46217</v>
       </c>
       <c r="B185" t="n">
-        <v>1293</v>
+        <v>351</v>
       </c>
       <c r="C185" t="n">
-        <v>8888</v>
+        <v>3009</v>
       </c>
       <c r="D185" t="n">
-        <v>8102.01</v>
+        <v>1007.64</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3960,17 +3960,17 @@
         <v>46217</v>
       </c>
       <c r="B186" t="n">
-        <v>1465</v>
+        <v>716</v>
       </c>
       <c r="C186" t="n">
-        <v>8888</v>
+        <v>891</v>
       </c>
       <c r="D186" t="n">
-        <v>2218.99</v>
+        <v>17820</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3979,17 +3979,17 @@
         <v>46217</v>
       </c>
       <c r="B187" t="n">
-        <v>483</v>
+        <v>1137</v>
       </c>
       <c r="C187" t="n">
         <v>8888</v>
       </c>
       <c r="D187" t="n">
-        <v>2862.88</v>
+        <v>5655.06</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3998,17 +3998,17 @@
         <v>46217</v>
       </c>
       <c r="B188" t="n">
-        <v>2109</v>
+        <v>1293</v>
       </c>
       <c r="C188" t="n">
         <v>8888</v>
       </c>
       <c r="D188" t="n">
-        <v>433.47</v>
+        <v>8102.01</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4017,17 +4017,17 @@
         <v>46217</v>
       </c>
       <c r="B189" t="n">
-        <v>1064</v>
+        <v>1465</v>
       </c>
       <c r="C189" t="n">
         <v>8888</v>
       </c>
       <c r="D189" t="n">
-        <v>104632.21</v>
+        <v>2218.99</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4036,17 +4036,17 @@
         <v>46217</v>
       </c>
       <c r="B190" t="n">
-        <v>131</v>
+        <v>483</v>
       </c>
       <c r="C190" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D190" t="n">
-        <v>876.48</v>
+        <v>2862.88</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4055,13 +4055,13 @@
         <v>46217</v>
       </c>
       <c r="B191" t="n">
-        <v>663</v>
+        <v>2109</v>
       </c>
       <c r="C191" t="n">
         <v>8888</v>
       </c>
       <c r="D191" t="n">
-        <v>1769.59</v>
+        <v>433.47</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -4074,13 +4074,13 @@
         <v>46217</v>
       </c>
       <c r="B192" t="n">
-        <v>767</v>
+        <v>1064</v>
       </c>
       <c r="C192" t="n">
         <v>8888</v>
       </c>
       <c r="D192" t="n">
-        <v>1127.17</v>
+        <v>104632.21</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -4096,14 +4096,14 @@
         <v>131</v>
       </c>
       <c r="C193" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D193" t="n">
-        <v>4787.28</v>
+        <v>876.48</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4112,17 +4112,17 @@
         <v>46217</v>
       </c>
       <c r="B194" t="n">
-        <v>2308</v>
+        <v>663</v>
       </c>
       <c r="C194" t="n">
-        <v>546</v>
+        <v>8888</v>
       </c>
       <c r="D194" t="n">
-        <v>1292.23</v>
+        <v>1769.59</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4137,7 +4137,7 @@
         <v>2220</v>
       </c>
       <c r="D195" t="n">
-        <v>1663.5</v>
+        <v>2126.44</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -4150,17 +4150,17 @@
         <v>46217</v>
       </c>
       <c r="B196" t="n">
-        <v>1937</v>
+        <v>767</v>
       </c>
       <c r="C196" t="n">
         <v>8888</v>
       </c>
       <c r="D196" t="n">
-        <v>1492.4</v>
+        <v>1127.17</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4169,17 +4169,17 @@
         <v>46217</v>
       </c>
       <c r="B197" t="n">
-        <v>1317</v>
+        <v>131</v>
       </c>
       <c r="C197" t="n">
         <v>8888</v>
       </c>
       <c r="D197" t="n">
-        <v>736.61</v>
+        <v>4787.28</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4188,17 +4188,17 @@
         <v>46217</v>
       </c>
       <c r="B198" t="n">
-        <v>2345</v>
+        <v>2308</v>
       </c>
       <c r="C198" t="n">
-        <v>8888</v>
+        <v>546</v>
       </c>
       <c r="D198" t="n">
-        <v>1562.35</v>
+        <v>1292.23</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4207,17 +4207,17 @@
         <v>46217</v>
       </c>
       <c r="B199" t="n">
-        <v>429</v>
+        <v>1937</v>
       </c>
       <c r="C199" t="n">
-        <v>1281</v>
+        <v>8888</v>
       </c>
       <c r="D199" t="n">
-        <v>2195.97</v>
+        <v>1492.4</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4226,17 +4226,17 @@
         <v>46217</v>
       </c>
       <c r="B200" t="n">
-        <v>2211</v>
+        <v>1317</v>
       </c>
       <c r="C200" t="n">
         <v>8888</v>
       </c>
       <c r="D200" t="n">
-        <v>8568.99</v>
+        <v>736.61</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4245,13 +4245,13 @@
         <v>46217</v>
       </c>
       <c r="B201" t="n">
-        <v>559</v>
+        <v>2345</v>
       </c>
       <c r="C201" t="n">
         <v>8888</v>
       </c>
       <c r="D201" t="n">
-        <v>4283.57</v>
+        <v>1562.35</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -4264,17 +4264,17 @@
         <v>46217</v>
       </c>
       <c r="B202" t="n">
-        <v>360</v>
+        <v>429</v>
       </c>
       <c r="C202" t="n">
-        <v>8888</v>
+        <v>1281</v>
       </c>
       <c r="D202" t="n">
-        <v>15052.63</v>
+        <v>2195.97</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4283,17 +4283,17 @@
         <v>46217</v>
       </c>
       <c r="B203" t="n">
-        <v>1478</v>
+        <v>2211</v>
       </c>
       <c r="C203" t="n">
-        <v>675</v>
+        <v>8888</v>
       </c>
       <c r="D203" t="n">
-        <v>1662.17</v>
+        <v>8568.99</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4302,17 +4302,17 @@
         <v>46217</v>
       </c>
       <c r="B204" t="n">
-        <v>2251</v>
+        <v>559</v>
       </c>
       <c r="C204" t="n">
         <v>8888</v>
       </c>
       <c r="D204" t="n">
-        <v>797.58</v>
+        <v>4283.57</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4321,17 +4321,17 @@
         <v>46217</v>
       </c>
       <c r="B205" t="n">
-        <v>2250</v>
+        <v>360</v>
       </c>
       <c r="C205" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D205" t="n">
-        <v>2622.81</v>
+        <v>15052.63</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4340,17 +4340,17 @@
         <v>46217</v>
       </c>
       <c r="B206" t="n">
-        <v>451</v>
+        <v>1478</v>
       </c>
       <c r="C206" t="n">
-        <v>8888</v>
+        <v>675</v>
       </c>
       <c r="D206" t="n">
-        <v>1899.02</v>
+        <v>1662.17</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4359,17 +4359,17 @@
         <v>46217</v>
       </c>
       <c r="B207" t="n">
-        <v>40</v>
+        <v>2251</v>
       </c>
       <c r="C207" t="n">
         <v>8888</v>
       </c>
       <c r="D207" t="n">
-        <v>1093.47</v>
+        <v>797.58</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4378,17 +4378,17 @@
         <v>46217</v>
       </c>
       <c r="B208" t="n">
-        <v>530</v>
+        <v>2250</v>
       </c>
       <c r="C208" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D208" t="n">
-        <v>180.08</v>
+        <v>2622.81</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4397,17 +4397,17 @@
         <v>46217</v>
       </c>
       <c r="B209" t="n">
-        <v>1327</v>
+        <v>451</v>
       </c>
       <c r="C209" t="n">
-        <v>3009</v>
+        <v>8888</v>
       </c>
       <c r="D209" t="n">
-        <v>946.8</v>
+        <v>1899.02</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4416,17 +4416,17 @@
         <v>46217</v>
       </c>
       <c r="B210" t="n">
-        <v>1293</v>
+        <v>40</v>
       </c>
       <c r="C210" t="n">
-        <v>601</v>
+        <v>8888</v>
       </c>
       <c r="D210" t="n">
-        <v>456.47</v>
+        <v>1093.47</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4435,17 +4435,17 @@
         <v>46217</v>
       </c>
       <c r="B211" t="n">
-        <v>424</v>
+        <v>530</v>
       </c>
       <c r="C211" t="n">
         <v>8888</v>
       </c>
       <c r="D211" t="n">
-        <v>1758.85</v>
+        <v>180.08</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4454,17 +4454,17 @@
         <v>46217</v>
       </c>
       <c r="B212" t="n">
-        <v>2118</v>
+        <v>1327</v>
       </c>
       <c r="C212" t="n">
-        <v>8888</v>
+        <v>3009</v>
       </c>
       <c r="D212" t="n">
-        <v>311.54</v>
+        <v>946.8</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4473,17 +4473,17 @@
         <v>46217</v>
       </c>
       <c r="B213" t="n">
-        <v>2251</v>
+        <v>1293</v>
       </c>
       <c r="C213" t="n">
-        <v>8888</v>
+        <v>601</v>
       </c>
       <c r="D213" t="n">
-        <v>603.66</v>
+        <v>456.47</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4492,17 +4492,17 @@
         <v>46217</v>
       </c>
       <c r="B214" t="n">
-        <v>1299</v>
+        <v>424</v>
       </c>
       <c r="C214" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D214" t="n">
-        <v>4140.12</v>
+        <v>1758.85</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4511,13 +4511,13 @@
         <v>46217</v>
       </c>
       <c r="B215" t="n">
-        <v>89</v>
+        <v>2118</v>
       </c>
       <c r="C215" t="n">
         <v>8888</v>
       </c>
       <c r="D215" t="n">
-        <v>1506.42</v>
+        <v>311.54</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -4530,17 +4530,17 @@
         <v>46217</v>
       </c>
       <c r="B216" t="n">
-        <v>1317</v>
+        <v>2251</v>
       </c>
       <c r="C216" t="n">
-        <v>3179</v>
+        <v>8888</v>
       </c>
       <c r="D216" t="n">
-        <v>562.02</v>
+        <v>603.66</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4549,17 +4549,17 @@
         <v>46217</v>
       </c>
       <c r="B217" t="n">
-        <v>2250</v>
+        <v>1299</v>
       </c>
       <c r="C217" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D217" t="n">
-        <v>1943.54</v>
+        <v>4140.12</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4568,17 +4568,17 @@
         <v>46217</v>
       </c>
       <c r="B218" t="n">
-        <v>1327</v>
+        <v>89</v>
       </c>
       <c r="C218" t="n">
         <v>8888</v>
       </c>
       <c r="D218" t="n">
-        <v>319.23</v>
+        <v>1506.42</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4587,17 +4587,17 @@
         <v>46217</v>
       </c>
       <c r="B219" t="n">
-        <v>326</v>
+        <v>1317</v>
       </c>
       <c r="C219" t="n">
-        <v>8888</v>
+        <v>3179</v>
       </c>
       <c r="D219" t="n">
-        <v>151.86</v>
+        <v>562.02</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4606,17 +4606,17 @@
         <v>46217</v>
       </c>
       <c r="B220" t="n">
-        <v>1372</v>
+        <v>2250</v>
       </c>
       <c r="C220" t="n">
         <v>8888</v>
       </c>
       <c r="D220" t="n">
-        <v>1088.02</v>
+        <v>1943.54</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4625,13 +4625,13 @@
         <v>46217</v>
       </c>
       <c r="B221" t="n">
-        <v>1501</v>
+        <v>1327</v>
       </c>
       <c r="C221" t="n">
         <v>8888</v>
       </c>
       <c r="D221" t="n">
-        <v>699.91</v>
+        <v>319.23</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -4644,17 +4644,17 @@
         <v>46217</v>
       </c>
       <c r="B222" t="n">
-        <v>626</v>
+        <v>1137</v>
       </c>
       <c r="C222" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D222" t="n">
-        <v>28212.87</v>
+        <v>1645.29</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4663,17 +4663,17 @@
         <v>46217</v>
       </c>
       <c r="B223" t="n">
-        <v>629</v>
+        <v>1653</v>
       </c>
       <c r="C223" t="n">
-        <v>675</v>
+        <v>8888</v>
       </c>
       <c r="D223" t="n">
-        <v>2975.45</v>
+        <v>275.73</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4682,17 +4682,17 @@
         <v>46217</v>
       </c>
       <c r="B224" t="n">
-        <v>2651</v>
+        <v>326</v>
       </c>
       <c r="C224" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D224" t="n">
-        <v>648.71</v>
+        <v>151.86</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4701,17 +4701,17 @@
         <v>46217</v>
       </c>
       <c r="B225" t="n">
-        <v>2114</v>
+        <v>1372</v>
       </c>
       <c r="C225" t="n">
-        <v>1954</v>
+        <v>8888</v>
       </c>
       <c r="D225" t="n">
-        <v>879.03</v>
+        <v>1088.02</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4720,17 +4720,17 @@
         <v>46217</v>
       </c>
       <c r="B226" t="n">
-        <v>1299</v>
+        <v>1501</v>
       </c>
       <c r="C226" t="n">
-        <v>2522</v>
+        <v>8888</v>
       </c>
       <c r="D226" t="n">
-        <v>6680.93</v>
+        <v>699.91</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4739,17 +4739,17 @@
         <v>46217</v>
       </c>
       <c r="B227" t="n">
-        <v>40</v>
+        <v>626</v>
       </c>
       <c r="C227" t="n">
         <v>8888</v>
       </c>
       <c r="D227" t="n">
-        <v>3583.39</v>
+        <v>50766.01</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4758,17 +4758,17 @@
         <v>46217</v>
       </c>
       <c r="B228" t="n">
-        <v>40</v>
+        <v>629</v>
       </c>
       <c r="C228" t="n">
-        <v>8888</v>
+        <v>675</v>
       </c>
       <c r="D228" t="n">
-        <v>2529.31</v>
+        <v>2975.45</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4777,17 +4777,17 @@
         <v>46217</v>
       </c>
       <c r="B229" t="n">
-        <v>363</v>
+        <v>2651</v>
       </c>
       <c r="C229" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D229" t="n">
-        <v>739.17</v>
+        <v>648.71</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4796,13 +4796,13 @@
         <v>46217</v>
       </c>
       <c r="B230" t="n">
-        <v>675</v>
+        <v>2114</v>
       </c>
       <c r="C230" t="n">
-        <v>1898</v>
+        <v>1954</v>
       </c>
       <c r="D230" t="n">
-        <v>107.13</v>
+        <v>879.03</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -4815,13 +4815,13 @@
         <v>46217</v>
       </c>
       <c r="B231" t="n">
-        <v>636</v>
+        <v>1653</v>
       </c>
       <c r="C231" t="n">
         <v>8888</v>
       </c>
       <c r="D231" t="n">
-        <v>7476.56</v>
+        <v>7180.69</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -4834,17 +4834,17 @@
         <v>46217</v>
       </c>
       <c r="B232" t="n">
-        <v>1075</v>
+        <v>1299</v>
       </c>
       <c r="C232" t="n">
-        <v>8888</v>
+        <v>2522</v>
       </c>
       <c r="D232" t="n">
-        <v>2845.63</v>
+        <v>6680.93</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4853,17 +4853,17 @@
         <v>46217</v>
       </c>
       <c r="B233" t="n">
-        <v>2245</v>
+        <v>40</v>
       </c>
       <c r="C233" t="n">
         <v>8888</v>
       </c>
       <c r="D233" t="n">
-        <v>883.75</v>
+        <v>3583.39</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4872,13 +4872,13 @@
         <v>46217</v>
       </c>
       <c r="B234" t="n">
-        <v>477</v>
+        <v>40</v>
       </c>
       <c r="C234" t="n">
         <v>8888</v>
       </c>
       <c r="D234" t="n">
-        <v>994.15</v>
+        <v>2529.31</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -4891,17 +4891,17 @@
         <v>46217</v>
       </c>
       <c r="B235" t="n">
-        <v>890</v>
+        <v>363</v>
       </c>
       <c r="C235" t="n">
         <v>8888</v>
       </c>
       <c r="D235" t="n">
-        <v>632.85</v>
+        <v>739.17</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4910,17 +4910,17 @@
         <v>46217</v>
       </c>
       <c r="B236" t="n">
-        <v>2015</v>
+        <v>675</v>
       </c>
       <c r="C236" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D236" t="n">
-        <v>3243.05</v>
+        <v>107.13</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4929,17 +4929,17 @@
         <v>46217</v>
       </c>
       <c r="B237" t="n">
-        <v>1996</v>
+        <v>636</v>
       </c>
       <c r="C237" t="n">
-        <v>691</v>
+        <v>8888</v>
       </c>
       <c r="D237" t="n">
-        <v>500.79</v>
+        <v>7476.56</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4948,17 +4948,17 @@
         <v>46217</v>
       </c>
       <c r="B238" t="n">
-        <v>1653</v>
+        <v>1075</v>
       </c>
       <c r="C238" t="n">
         <v>8888</v>
       </c>
       <c r="D238" t="n">
-        <v>4115.53</v>
+        <v>2845.63</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4967,17 +4967,17 @@
         <v>46217</v>
       </c>
       <c r="B239" t="n">
-        <v>1064</v>
+        <v>2245</v>
       </c>
       <c r="C239" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D239" t="n">
-        <v>1153.23</v>
+        <v>883.75</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4986,13 +4986,13 @@
         <v>46217</v>
       </c>
       <c r="B240" t="n">
-        <v>1983</v>
+        <v>477</v>
       </c>
       <c r="C240" t="n">
         <v>8888</v>
       </c>
       <c r="D240" t="n">
-        <v>1246.33</v>
+        <v>994.15</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -5005,17 +5005,17 @@
         <v>46217</v>
       </c>
       <c r="B241" t="n">
-        <v>2118</v>
+        <v>890</v>
       </c>
       <c r="C241" t="n">
         <v>8888</v>
       </c>
       <c r="D241" t="n">
-        <v>5870.04</v>
+        <v>632.85</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -5024,13 +5024,13 @@
         <v>46217</v>
       </c>
       <c r="B242" t="n">
-        <v>559</v>
+        <v>2015</v>
       </c>
       <c r="C242" t="n">
         <v>8888</v>
       </c>
       <c r="D242" t="n">
-        <v>2189.12</v>
+        <v>3243.05</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -5043,17 +5043,17 @@
         <v>46217</v>
       </c>
       <c r="B243" t="n">
-        <v>2680</v>
+        <v>1996</v>
       </c>
       <c r="C243" t="n">
-        <v>8888</v>
+        <v>691</v>
       </c>
       <c r="D243" t="n">
-        <v>2285.31</v>
+        <v>500.79</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -5062,17 +5062,17 @@
         <v>46217</v>
       </c>
       <c r="B244" t="n">
-        <v>2637</v>
+        <v>1064</v>
       </c>
       <c r="C244" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D244" t="n">
-        <v>1302.18</v>
+        <v>1153.23</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -5081,17 +5081,17 @@
         <v>46217</v>
       </c>
       <c r="B245" t="n">
-        <v>1632</v>
+        <v>1983</v>
       </c>
       <c r="C245" t="n">
         <v>8888</v>
       </c>
       <c r="D245" t="n">
-        <v>689.76</v>
+        <v>1246.33</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -5100,17 +5100,17 @@
         <v>46217</v>
       </c>
       <c r="B246" t="n">
-        <v>285</v>
+        <v>2118</v>
       </c>
       <c r="C246" t="n">
         <v>8888</v>
       </c>
       <c r="D246" t="n">
-        <v>375.8</v>
+        <v>5870.04</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5119,17 +5119,17 @@
         <v>46217</v>
       </c>
       <c r="B247" t="n">
-        <v>2727</v>
+        <v>559</v>
       </c>
       <c r="C247" t="n">
         <v>8888</v>
       </c>
       <c r="D247" t="n">
-        <v>548.33</v>
+        <v>2189.12</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5138,17 +5138,17 @@
         <v>46217</v>
       </c>
       <c r="B248" t="n">
-        <v>2026</v>
+        <v>2680</v>
       </c>
       <c r="C248" t="n">
         <v>8888</v>
       </c>
       <c r="D248" t="n">
-        <v>699.05</v>
+        <v>2285.31</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5157,13 +5157,13 @@
         <v>46217</v>
       </c>
       <c r="B249" t="n">
-        <v>1117</v>
+        <v>2637</v>
       </c>
       <c r="C249" t="n">
         <v>8888</v>
       </c>
       <c r="D249" t="n">
-        <v>306.02</v>
+        <v>1302.18</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -5176,13 +5176,13 @@
         <v>46217</v>
       </c>
       <c r="B250" t="n">
-        <v>664</v>
+        <v>1632</v>
       </c>
       <c r="C250" t="n">
         <v>8888</v>
       </c>
       <c r="D250" t="n">
-        <v>3483.46</v>
+        <v>689.76</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -5195,17 +5195,17 @@
         <v>46217</v>
       </c>
       <c r="B251" t="n">
-        <v>1465</v>
+        <v>285</v>
       </c>
       <c r="C251" t="n">
         <v>8888</v>
       </c>
       <c r="D251" t="n">
-        <v>14048.78</v>
+        <v>375.8</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -5214,13 +5214,13 @@
         <v>46217</v>
       </c>
       <c r="B252" t="n">
-        <v>2550</v>
+        <v>2727</v>
       </c>
       <c r="C252" t="n">
         <v>8888</v>
       </c>
       <c r="D252" t="n">
-        <v>321.05</v>
+        <v>548.33</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -5233,13 +5233,13 @@
         <v>46217</v>
       </c>
       <c r="B253" t="n">
-        <v>1756</v>
+        <v>2026</v>
       </c>
       <c r="C253" t="n">
         <v>8888</v>
       </c>
       <c r="D253" t="n">
-        <v>2445</v>
+        <v>699.05</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -5252,17 +5252,17 @@
         <v>46217</v>
       </c>
       <c r="B254" t="n">
-        <v>890</v>
+        <v>1117</v>
       </c>
       <c r="C254" t="n">
         <v>8888</v>
       </c>
       <c r="D254" t="n">
-        <v>4287.14</v>
+        <v>306.02</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5271,13 +5271,13 @@
         <v>46217</v>
       </c>
       <c r="B255" t="n">
-        <v>363</v>
+        <v>664</v>
       </c>
       <c r="C255" t="n">
         <v>8888</v>
       </c>
       <c r="D255" t="n">
-        <v>2517.01</v>
+        <v>3483.46</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -5290,17 +5290,17 @@
         <v>46217</v>
       </c>
       <c r="B256" t="n">
-        <v>2698</v>
+        <v>1465</v>
       </c>
       <c r="C256" t="n">
-        <v>874</v>
+        <v>8888</v>
       </c>
       <c r="D256" t="n">
-        <v>2253.73</v>
+        <v>14048.78</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5309,13 +5309,13 @@
         <v>46217</v>
       </c>
       <c r="B257" t="n">
-        <v>535</v>
+        <v>2709</v>
       </c>
       <c r="C257" t="n">
         <v>8888</v>
       </c>
       <c r="D257" t="n">
-        <v>5293.96</v>
+        <v>2960.07</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -5328,17 +5328,17 @@
         <v>46217</v>
       </c>
       <c r="B258" t="n">
-        <v>2250</v>
+        <v>767</v>
       </c>
       <c r="C258" t="n">
         <v>8888</v>
       </c>
       <c r="D258" t="n">
-        <v>5398.63</v>
+        <v>4121.17</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -5347,13 +5347,13 @@
         <v>46217</v>
       </c>
       <c r="B259" t="n">
-        <v>2681</v>
+        <v>2550</v>
       </c>
       <c r="C259" t="n">
         <v>8888</v>
       </c>
       <c r="D259" t="n">
-        <v>2853.99</v>
+        <v>321.05</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -5366,17 +5366,17 @@
         <v>46217</v>
       </c>
       <c r="B260" t="n">
-        <v>132</v>
+        <v>1756</v>
       </c>
       <c r="C260" t="n">
         <v>8888</v>
       </c>
       <c r="D260" t="n">
-        <v>11963.23</v>
+        <v>2445</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -5385,17 +5385,17 @@
         <v>46217</v>
       </c>
       <c r="B261" t="n">
-        <v>2442</v>
+        <v>890</v>
       </c>
       <c r="C261" t="n">
         <v>8888</v>
       </c>
       <c r="D261" t="n">
-        <v>2822.22</v>
+        <v>4287.14</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -5404,17 +5404,17 @@
         <v>46217</v>
       </c>
       <c r="B262" t="n">
-        <v>2472</v>
+        <v>363</v>
       </c>
       <c r="C262" t="n">
-        <v>2853</v>
+        <v>8888</v>
       </c>
       <c r="D262" t="n">
-        <v>2166</v>
+        <v>2517.01</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5423,13 +5423,13 @@
         <v>46217</v>
       </c>
       <c r="B263" t="n">
-        <v>363</v>
+        <v>2698</v>
       </c>
       <c r="C263" t="n">
-        <v>1898</v>
+        <v>874</v>
       </c>
       <c r="D263" t="n">
-        <v>4028</v>
+        <v>2253.73</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -5442,13 +5442,13 @@
         <v>46217</v>
       </c>
       <c r="B264" t="n">
-        <v>483</v>
+        <v>535</v>
       </c>
       <c r="C264" t="n">
         <v>8888</v>
       </c>
       <c r="D264" t="n">
-        <v>7612.06</v>
+        <v>5293.96</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -5461,17 +5461,17 @@
         <v>46217</v>
       </c>
       <c r="B265" t="n">
-        <v>2279</v>
+        <v>2250</v>
       </c>
       <c r="C265" t="n">
         <v>8888</v>
       </c>
       <c r="D265" t="n">
-        <v>740.38</v>
+        <v>5398.63</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5480,13 +5480,13 @@
         <v>46217</v>
       </c>
       <c r="B266" t="n">
-        <v>767</v>
+        <v>2681</v>
       </c>
       <c r="C266" t="n">
         <v>8888</v>
       </c>
       <c r="D266" t="n">
-        <v>718.65</v>
+        <v>2853.99</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -5499,17 +5499,17 @@
         <v>46217</v>
       </c>
       <c r="B267" t="n">
-        <v>2607</v>
+        <v>1632</v>
       </c>
       <c r="C267" t="n">
-        <v>8888</v>
+        <v>423</v>
       </c>
       <c r="D267" t="n">
-        <v>1075.36</v>
+        <v>7156.83</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -5518,17 +5518,17 @@
         <v>46217</v>
       </c>
       <c r="B268" t="n">
-        <v>2330</v>
+        <v>132</v>
       </c>
       <c r="C268" t="n">
-        <v>1954</v>
+        <v>8888</v>
       </c>
       <c r="D268" t="n">
-        <v>1923.09</v>
+        <v>11963.23</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5537,17 +5537,17 @@
         <v>46217</v>
       </c>
       <c r="B269" t="n">
-        <v>619</v>
+        <v>2442</v>
       </c>
       <c r="C269" t="n">
-        <v>1139</v>
+        <v>8888</v>
       </c>
       <c r="D269" t="n">
-        <v>4840.54</v>
+        <v>2822.22</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5556,17 +5556,17 @@
         <v>46217</v>
       </c>
       <c r="B270" t="n">
-        <v>1384</v>
+        <v>2472</v>
       </c>
       <c r="C270" t="n">
-        <v>8888</v>
+        <v>2853</v>
       </c>
       <c r="D270" t="n">
-        <v>585.27</v>
+        <v>2166</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -5575,17 +5575,17 @@
         <v>46217</v>
       </c>
       <c r="B271" t="n">
-        <v>2709</v>
+        <v>363</v>
       </c>
       <c r="C271" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D271" t="n">
-        <v>2210.08</v>
+        <v>4565.72</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -5594,17 +5594,17 @@
         <v>46217</v>
       </c>
       <c r="B272" t="n">
-        <v>374</v>
+        <v>483</v>
       </c>
       <c r="C272" t="n">
         <v>8888</v>
       </c>
       <c r="D272" t="n">
-        <v>2840.69</v>
+        <v>7612.06</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5613,17 +5613,17 @@
         <v>46217</v>
       </c>
       <c r="B273" t="n">
-        <v>1137</v>
+        <v>2279</v>
       </c>
       <c r="C273" t="n">
         <v>8888</v>
       </c>
       <c r="D273" t="n">
-        <v>4413.34</v>
+        <v>740.38</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -5632,17 +5632,17 @@
         <v>46217</v>
       </c>
       <c r="B274" t="n">
-        <v>2251</v>
+        <v>2607</v>
       </c>
       <c r="C274" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D274" t="n">
-        <v>510.18</v>
+        <v>1075.36</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5651,13 +5651,13 @@
         <v>46217</v>
       </c>
       <c r="B275" t="n">
-        <v>2728</v>
+        <v>2330</v>
       </c>
       <c r="C275" t="n">
-        <v>977</v>
+        <v>1954</v>
       </c>
       <c r="D275" t="n">
-        <v>2256.87</v>
+        <v>1923.09</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -5670,17 +5670,17 @@
         <v>46217</v>
       </c>
       <c r="B276" t="n">
-        <v>1293</v>
+        <v>619</v>
       </c>
       <c r="C276" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D276" t="n">
-        <v>529.2</v>
+        <v>4840.54</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -5689,17 +5689,17 @@
         <v>46217</v>
       </c>
       <c r="B277" t="n">
-        <v>1278</v>
+        <v>1384</v>
       </c>
       <c r="C277" t="n">
-        <v>1533</v>
+        <v>8888</v>
       </c>
       <c r="D277" t="n">
-        <v>620.97</v>
+        <v>585.27</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5708,15 +5708,129 @@
         <v>46217</v>
       </c>
       <c r="B278" t="n">
+        <v>374</v>
+      </c>
+      <c r="C278" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D278" t="n">
+        <v>2840.69</v>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B279" t="n">
+        <v>1137</v>
+      </c>
+      <c r="C279" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D279" t="n">
+        <v>4413.34</v>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B280" t="n">
+        <v>2251</v>
+      </c>
+      <c r="C280" t="n">
+        <v>3403</v>
+      </c>
+      <c r="D280" t="n">
+        <v>510.18</v>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B281" t="n">
+        <v>2728</v>
+      </c>
+      <c r="C281" t="n">
+        <v>977</v>
+      </c>
+      <c r="D281" t="n">
+        <v>2256.87</v>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B282" t="n">
+        <v>1293</v>
+      </c>
+      <c r="C282" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D282" t="n">
+        <v>529.2</v>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B283" t="n">
+        <v>1278</v>
+      </c>
+      <c r="C283" t="n">
+        <v>1533</v>
+      </c>
+      <c r="D283" t="n">
+        <v>620.97</v>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B284" t="n">
         <v>1380</v>
       </c>
-      <c r="C278" t="n">
-        <v>8888</v>
-      </c>
-      <c r="D278" t="n">
+      <c r="C284" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D284" t="n">
         <v>947.8200000000001</v>
       </c>
-      <c r="E278" t="inlineStr">
+      <c r="E284" t="inlineStr">
         <is>
           <t>FORÇA DE VENDAS</t>
         </is>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,17 +521,17 @@
         <v>46218</v>
       </c>
       <c r="B5" t="n">
-        <v>438</v>
+        <v>949</v>
       </c>
       <c r="C5" t="n">
-        <v>8888</v>
+        <v>1134</v>
       </c>
       <c r="D5" t="n">
-        <v>220.06</v>
+        <v>30.46</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -540,13 +540,13 @@
         <v>46218</v>
       </c>
       <c r="B6" t="n">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="C6" t="n">
         <v>8888</v>
       </c>
       <c r="D6" t="n">
-        <v>368.93</v>
+        <v>220.06</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -559,17 +559,17 @@
         <v>46218</v>
       </c>
       <c r="B7" t="n">
-        <v>89</v>
+        <v>451</v>
       </c>
       <c r="C7" t="n">
-        <v>13148</v>
+        <v>8888</v>
       </c>
       <c r="D7" t="n">
-        <v>993.65</v>
+        <v>368.93</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
         <v>46218</v>
       </c>
       <c r="B8" t="n">
-        <v>1063</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>8888</v>
+        <v>13148</v>
       </c>
       <c r="D8" t="n">
-        <v>3137.87</v>
+        <v>993.65</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -603,11 +603,11 @@
         <v>8888</v>
       </c>
       <c r="D9" t="n">
-        <v>932.71</v>
+        <v>3137.87</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -616,17 +616,17 @@
         <v>46218</v>
       </c>
       <c r="B10" t="n">
-        <v>1007</v>
+        <v>1063</v>
       </c>
       <c r="C10" t="n">
         <v>8888</v>
       </c>
       <c r="D10" t="n">
-        <v>241.44</v>
+        <v>932.71</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -635,13 +635,13 @@
         <v>46218</v>
       </c>
       <c r="B11" t="n">
-        <v>1380</v>
+        <v>1007</v>
       </c>
       <c r="C11" t="n">
         <v>8888</v>
       </c>
       <c r="D11" t="n">
-        <v>520.2</v>
+        <v>241.44</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -654,17 +654,17 @@
         <v>46218</v>
       </c>
       <c r="B12" t="n">
-        <v>1756</v>
+        <v>1380</v>
       </c>
       <c r="C12" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D12" t="n">
-        <v>741.1799999999999</v>
+        <v>520.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -673,17 +673,17 @@
         <v>46218</v>
       </c>
       <c r="B13" t="n">
-        <v>816</v>
+        <v>1756</v>
       </c>
       <c r="C13" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D13" t="n">
-        <v>438.24</v>
+        <v>741.1799999999999</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -692,17 +692,17 @@
         <v>46218</v>
       </c>
       <c r="B14" t="n">
-        <v>953</v>
+        <v>816</v>
       </c>
       <c r="C14" t="n">
         <v>8888</v>
       </c>
       <c r="D14" t="n">
-        <v>926.16</v>
+        <v>438.24</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -711,15 +711,34 @@
         <v>46218</v>
       </c>
       <c r="B15" t="n">
+        <v>953</v>
+      </c>
+      <c r="C15" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D15" t="n">
+        <v>926.16</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B16" t="n">
         <v>1116</v>
       </c>
-      <c r="C15" t="n">
-        <v>8888</v>
-      </c>
-      <c r="D15" t="n">
+      <c r="C16" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D16" t="n">
         <v>2919.53</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>OPERADOR LOGÍSTICO</t>
         </is>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -744,6 +744,25 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B17" t="n">
+        <v>42</v>
+      </c>
+      <c r="C17" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D17" t="n">
+        <v>79947.14999999999</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,17 +464,17 @@
         <v>46218</v>
       </c>
       <c r="B2" t="n">
-        <v>451</v>
+        <v>1075</v>
       </c>
       <c r="C2" t="n">
-        <v>8888</v>
+        <v>675</v>
       </c>
       <c r="D2" t="n">
-        <v>1103.58</v>
+        <v>638.4299999999999</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -483,17 +483,17 @@
         <v>46218</v>
       </c>
       <c r="B3" t="n">
-        <v>1364</v>
+        <v>451</v>
       </c>
       <c r="C3" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D3" t="n">
-        <v>275.01</v>
+        <v>1103.58</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -502,13 +502,13 @@
         <v>46218</v>
       </c>
       <c r="B4" t="n">
-        <v>1075</v>
+        <v>1364</v>
       </c>
       <c r="C4" t="n">
-        <v>675</v>
+        <v>3403</v>
       </c>
       <c r="D4" t="n">
-        <v>233.83</v>
+        <v>275.01</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -540,17 +540,17 @@
         <v>46218</v>
       </c>
       <c r="B6" t="n">
-        <v>438</v>
+        <v>58</v>
       </c>
       <c r="C6" t="n">
         <v>8888</v>
       </c>
       <c r="D6" t="n">
-        <v>220.06</v>
+        <v>499.11</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -559,17 +559,17 @@
         <v>46218</v>
       </c>
       <c r="B7" t="n">
-        <v>451</v>
+        <v>2245</v>
       </c>
       <c r="C7" t="n">
         <v>8888</v>
       </c>
       <c r="D7" t="n">
-        <v>368.93</v>
+        <v>2433.47</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
         <v>46218</v>
       </c>
       <c r="B8" t="n">
-        <v>89</v>
+        <v>438</v>
       </c>
       <c r="C8" t="n">
-        <v>13148</v>
+        <v>8888</v>
       </c>
       <c r="D8" t="n">
-        <v>993.65</v>
+        <v>220.06</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -597,13 +597,13 @@
         <v>46218</v>
       </c>
       <c r="B9" t="n">
-        <v>1063</v>
+        <v>451</v>
       </c>
       <c r="C9" t="n">
         <v>8888</v>
       </c>
       <c r="D9" t="n">
-        <v>3137.87</v>
+        <v>368.93</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -616,13 +616,13 @@
         <v>46218</v>
       </c>
       <c r="B10" t="n">
-        <v>1063</v>
+        <v>1075</v>
       </c>
       <c r="C10" t="n">
         <v>8888</v>
       </c>
       <c r="D10" t="n">
-        <v>932.71</v>
+        <v>1813.45</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -635,17 +635,17 @@
         <v>46218</v>
       </c>
       <c r="B11" t="n">
-        <v>1007</v>
+        <v>89</v>
       </c>
       <c r="C11" t="n">
-        <v>8888</v>
+        <v>13148</v>
       </c>
       <c r="D11" t="n">
-        <v>241.44</v>
+        <v>1883.74</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -654,13 +654,13 @@
         <v>46218</v>
       </c>
       <c r="B12" t="n">
-        <v>1380</v>
+        <v>1063</v>
       </c>
       <c r="C12" t="n">
         <v>8888</v>
       </c>
       <c r="D12" t="n">
-        <v>520.2</v>
+        <v>3576.45</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -673,17 +673,17 @@
         <v>46218</v>
       </c>
       <c r="B13" t="n">
-        <v>1756</v>
+        <v>285</v>
       </c>
       <c r="C13" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D13" t="n">
-        <v>741.1799999999999</v>
+        <v>555.64</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -692,17 +692,17 @@
         <v>46218</v>
       </c>
       <c r="B14" t="n">
-        <v>816</v>
+        <v>1063</v>
       </c>
       <c r="C14" t="n">
         <v>8888</v>
       </c>
       <c r="D14" t="n">
-        <v>438.24</v>
+        <v>932.71</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -711,13 +711,13 @@
         <v>46218</v>
       </c>
       <c r="B15" t="n">
-        <v>953</v>
+        <v>1937</v>
       </c>
       <c r="C15" t="n">
         <v>8888</v>
       </c>
       <c r="D15" t="n">
-        <v>926.16</v>
+        <v>338.93</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
         <v>46218</v>
       </c>
       <c r="B16" t="n">
-        <v>1116</v>
+        <v>1063</v>
       </c>
       <c r="C16" t="n">
         <v>8888</v>
       </c>
       <c r="D16" t="n">
-        <v>2919.53</v>
+        <v>1113.08</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -749,15 +749,205 @@
         <v>46218</v>
       </c>
       <c r="B17" t="n">
+        <v>1007</v>
+      </c>
+      <c r="C17" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D17" t="n">
+        <v>241.44</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1380</v>
+      </c>
+      <c r="C18" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D18" t="n">
+        <v>520.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B19" t="n">
+        <v>285</v>
+      </c>
+      <c r="C19" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D19" t="n">
+        <v>364.44</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1756</v>
+      </c>
+      <c r="C20" t="n">
+        <v>27</v>
+      </c>
+      <c r="D20" t="n">
+        <v>741.1799999999999</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B21" t="n">
+        <v>816</v>
+      </c>
+      <c r="C21" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D21" t="n">
+        <v>438.24</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B22" t="n">
+        <v>953</v>
+      </c>
+      <c r="C22" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1254.07</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2782</v>
+      </c>
+      <c r="C23" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D23" t="n">
+        <v>532.91</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1478</v>
+      </c>
+      <c r="C24" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D24" t="n">
+        <v>251.69</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B25" t="n">
+        <v>131</v>
+      </c>
+      <c r="C25" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D25" t="n">
+        <v>765.99</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1116</v>
+      </c>
+      <c r="C26" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2919.53</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B27" t="n">
         <v>42</v>
       </c>
-      <c r="C17" t="n">
-        <v>8888</v>
-      </c>
-      <c r="D17" t="n">
+      <c r="C27" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D27" t="n">
         <v>79947.14999999999</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>OPERADOR LOGÍSTICO</t>
         </is>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,7 +622,7 @@
         <v>8888</v>
       </c>
       <c r="D10" t="n">
-        <v>1813.45</v>
+        <v>2568.51</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -635,17 +635,17 @@
         <v>46218</v>
       </c>
       <c r="B11" t="n">
-        <v>89</v>
+        <v>483</v>
       </c>
       <c r="C11" t="n">
-        <v>13148</v>
+        <v>8888</v>
       </c>
       <c r="D11" t="n">
-        <v>1883.74</v>
+        <v>2027.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -654,17 +654,17 @@
         <v>46218</v>
       </c>
       <c r="B12" t="n">
-        <v>1063</v>
+        <v>89</v>
       </c>
       <c r="C12" t="n">
-        <v>8888</v>
+        <v>13148</v>
       </c>
       <c r="D12" t="n">
-        <v>3576.45</v>
+        <v>1883.74</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -673,17 +673,17 @@
         <v>46218</v>
       </c>
       <c r="B13" t="n">
-        <v>285</v>
+        <v>1063</v>
       </c>
       <c r="C13" t="n">
         <v>8888</v>
       </c>
       <c r="D13" t="n">
-        <v>555.64</v>
+        <v>3576.45</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -692,13 +692,13 @@
         <v>46218</v>
       </c>
       <c r="B14" t="n">
-        <v>1063</v>
+        <v>285</v>
       </c>
       <c r="C14" t="n">
         <v>8888</v>
       </c>
       <c r="D14" t="n">
-        <v>932.71</v>
+        <v>555.64</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -711,13 +711,13 @@
         <v>46218</v>
       </c>
       <c r="B15" t="n">
-        <v>1937</v>
+        <v>1063</v>
       </c>
       <c r="C15" t="n">
         <v>8888</v>
       </c>
       <c r="D15" t="n">
-        <v>338.93</v>
+        <v>932.71</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
         <v>46218</v>
       </c>
       <c r="B16" t="n">
-        <v>1063</v>
+        <v>1937</v>
       </c>
       <c r="C16" t="n">
         <v>8888</v>
       </c>
       <c r="D16" t="n">
-        <v>1113.08</v>
+        <v>338.93</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
         <v>46218</v>
       </c>
       <c r="B17" t="n">
-        <v>1007</v>
+        <v>1063</v>
       </c>
       <c r="C17" t="n">
         <v>8888</v>
       </c>
       <c r="D17" t="n">
-        <v>241.44</v>
+        <v>1113.08</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -768,13 +768,13 @@
         <v>46218</v>
       </c>
       <c r="B18" t="n">
-        <v>1380</v>
+        <v>1007</v>
       </c>
       <c r="C18" t="n">
         <v>8888</v>
       </c>
       <c r="D18" t="n">
-        <v>520.2</v>
+        <v>241.44</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -787,17 +787,17 @@
         <v>46218</v>
       </c>
       <c r="B19" t="n">
-        <v>285</v>
+        <v>1380</v>
       </c>
       <c r="C19" t="n">
         <v>8888</v>
       </c>
       <c r="D19" t="n">
-        <v>364.44</v>
+        <v>520.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -806,13 +806,13 @@
         <v>46218</v>
       </c>
       <c r="B20" t="n">
-        <v>1756</v>
+        <v>483</v>
       </c>
       <c r="C20" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D20" t="n">
-        <v>741.1799999999999</v>
+        <v>2026.73</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
         <v>46218</v>
       </c>
       <c r="B21" t="n">
-        <v>816</v>
+        <v>285</v>
       </c>
       <c r="C21" t="n">
         <v>8888</v>
       </c>
       <c r="D21" t="n">
-        <v>438.24</v>
+        <v>364.44</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -844,17 +844,17 @@
         <v>46218</v>
       </c>
       <c r="B22" t="n">
-        <v>953</v>
+        <v>1756</v>
       </c>
       <c r="C22" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D22" t="n">
-        <v>1254.07</v>
+        <v>741.1799999999999</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -863,13 +863,13 @@
         <v>46218</v>
       </c>
       <c r="B23" t="n">
-        <v>2782</v>
+        <v>629</v>
       </c>
       <c r="C23" t="n">
         <v>8888</v>
       </c>
       <c r="D23" t="n">
-        <v>532.91</v>
+        <v>339.19</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -882,17 +882,17 @@
         <v>46218</v>
       </c>
       <c r="B24" t="n">
-        <v>1478</v>
+        <v>816</v>
       </c>
       <c r="C24" t="n">
         <v>8888</v>
       </c>
       <c r="D24" t="n">
-        <v>251.69</v>
+        <v>438.24</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -901,13 +901,13 @@
         <v>46218</v>
       </c>
       <c r="B25" t="n">
-        <v>131</v>
+        <v>953</v>
       </c>
       <c r="C25" t="n">
         <v>8888</v>
       </c>
       <c r="D25" t="n">
-        <v>765.99</v>
+        <v>1254.07</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -920,17 +920,17 @@
         <v>46218</v>
       </c>
       <c r="B26" t="n">
-        <v>1116</v>
+        <v>131</v>
       </c>
       <c r="C26" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D26" t="n">
-        <v>2919.53</v>
+        <v>91.86</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -939,15 +939,91 @@
         <v>46218</v>
       </c>
       <c r="B27" t="n">
+        <v>2782</v>
+      </c>
+      <c r="C27" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D27" t="n">
+        <v>532.91</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1478</v>
+      </c>
+      <c r="C28" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D28" t="n">
+        <v>251.69</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B29" t="n">
+        <v>131</v>
+      </c>
+      <c r="C29" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1125.63</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1116</v>
+      </c>
+      <c r="C30" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2919.53</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B31" t="n">
         <v>42</v>
       </c>
-      <c r="C27" t="n">
-        <v>8888</v>
-      </c>
-      <c r="D27" t="n">
+      <c r="C31" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D31" t="n">
         <v>79947.14999999999</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>OPERADOR LOGÍSTICO</t>
         </is>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -616,17 +616,17 @@
         <v>46218</v>
       </c>
       <c r="B10" t="n">
-        <v>1075</v>
+        <v>2714</v>
       </c>
       <c r="C10" t="n">
-        <v>8888</v>
+        <v>519</v>
       </c>
       <c r="D10" t="n">
-        <v>2568.51</v>
+        <v>61939.22</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -635,17 +635,17 @@
         <v>46218</v>
       </c>
       <c r="B11" t="n">
-        <v>483</v>
+        <v>1075</v>
       </c>
       <c r="C11" t="n">
         <v>8888</v>
       </c>
       <c r="D11" t="n">
-        <v>2027.7</v>
+        <v>5216.32</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -654,17 +654,17 @@
         <v>46218</v>
       </c>
       <c r="B12" t="n">
-        <v>89</v>
+        <v>483</v>
       </c>
       <c r="C12" t="n">
-        <v>13148</v>
+        <v>8888</v>
       </c>
       <c r="D12" t="n">
-        <v>1883.74</v>
+        <v>2027.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -673,17 +673,17 @@
         <v>46218</v>
       </c>
       <c r="B13" t="n">
-        <v>1063</v>
+        <v>89</v>
       </c>
       <c r="C13" t="n">
-        <v>8888</v>
+        <v>13148</v>
       </c>
       <c r="D13" t="n">
-        <v>3576.45</v>
+        <v>1883.74</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -692,17 +692,17 @@
         <v>46218</v>
       </c>
       <c r="B14" t="n">
-        <v>285</v>
+        <v>1063</v>
       </c>
       <c r="C14" t="n">
         <v>8888</v>
       </c>
       <c r="D14" t="n">
-        <v>555.64</v>
+        <v>3576.45</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -711,17 +711,17 @@
         <v>46218</v>
       </c>
       <c r="B15" t="n">
-        <v>1063</v>
+        <v>1299</v>
       </c>
       <c r="C15" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D15" t="n">
-        <v>932.71</v>
+        <v>990.24</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -730,13 +730,13 @@
         <v>46218</v>
       </c>
       <c r="B16" t="n">
-        <v>1937</v>
+        <v>285</v>
       </c>
       <c r="C16" t="n">
         <v>8888</v>
       </c>
       <c r="D16" t="n">
-        <v>338.93</v>
+        <v>555.64</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -755,11 +755,11 @@
         <v>8888</v>
       </c>
       <c r="D17" t="n">
-        <v>1113.08</v>
+        <v>932.71</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -768,13 +768,13 @@
         <v>46218</v>
       </c>
       <c r="B18" t="n">
-        <v>1007</v>
+        <v>1465</v>
       </c>
       <c r="C18" t="n">
         <v>8888</v>
       </c>
       <c r="D18" t="n">
-        <v>241.44</v>
+        <v>2431.47</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -787,17 +787,17 @@
         <v>46218</v>
       </c>
       <c r="B19" t="n">
-        <v>1380</v>
+        <v>1937</v>
       </c>
       <c r="C19" t="n">
         <v>8888</v>
       </c>
       <c r="D19" t="n">
-        <v>520.2</v>
+        <v>833.52</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -806,13 +806,13 @@
         <v>46218</v>
       </c>
       <c r="B20" t="n">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="C20" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
-        <v>2026.73</v>
+        <v>736.03</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -825,13 +825,13 @@
         <v>46218</v>
       </c>
       <c r="B21" t="n">
-        <v>285</v>
+        <v>1063</v>
       </c>
       <c r="C21" t="n">
         <v>8888</v>
       </c>
       <c r="D21" t="n">
-        <v>364.44</v>
+        <v>1113.08</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -844,17 +844,17 @@
         <v>46218</v>
       </c>
       <c r="B22" t="n">
-        <v>1756</v>
+        <v>1007</v>
       </c>
       <c r="C22" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D22" t="n">
-        <v>741.1799999999999</v>
+        <v>241.44</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -863,13 +863,13 @@
         <v>46218</v>
       </c>
       <c r="B23" t="n">
-        <v>629</v>
+        <v>1380</v>
       </c>
       <c r="C23" t="n">
         <v>8888</v>
       </c>
       <c r="D23" t="n">
-        <v>339.19</v>
+        <v>520.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -882,17 +882,17 @@
         <v>46218</v>
       </c>
       <c r="B24" t="n">
-        <v>816</v>
+        <v>483</v>
       </c>
       <c r="C24" t="n">
-        <v>8888</v>
+        <v>38</v>
       </c>
       <c r="D24" t="n">
-        <v>438.24</v>
+        <v>2026.73</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
         <v>46218</v>
       </c>
       <c r="B25" t="n">
-        <v>953</v>
+        <v>1075</v>
       </c>
       <c r="C25" t="n">
         <v>8888</v>
       </c>
       <c r="D25" t="n">
-        <v>1254.07</v>
+        <v>557.62</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -920,17 +920,17 @@
         <v>46218</v>
       </c>
       <c r="B26" t="n">
-        <v>131</v>
+        <v>285</v>
       </c>
       <c r="C26" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D26" t="n">
-        <v>91.86</v>
+        <v>364.44</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -939,17 +939,17 @@
         <v>46218</v>
       </c>
       <c r="B27" t="n">
-        <v>2782</v>
+        <v>1756</v>
       </c>
       <c r="C27" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D27" t="n">
-        <v>532.91</v>
+        <v>741.1799999999999</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
         <v>46218</v>
       </c>
       <c r="B28" t="n">
-        <v>1478</v>
+        <v>629</v>
       </c>
       <c r="C28" t="n">
         <v>8888</v>
       </c>
       <c r="D28" t="n">
-        <v>251.69</v>
+        <v>339.19</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -977,17 +977,17 @@
         <v>46218</v>
       </c>
       <c r="B29" t="n">
-        <v>131</v>
+        <v>816</v>
       </c>
       <c r="C29" t="n">
         <v>8888</v>
       </c>
       <c r="D29" t="n">
-        <v>1125.63</v>
+        <v>438.24</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -996,13 +996,13 @@
         <v>46218</v>
       </c>
       <c r="B30" t="n">
-        <v>1116</v>
+        <v>953</v>
       </c>
       <c r="C30" t="n">
         <v>8888</v>
       </c>
       <c r="D30" t="n">
-        <v>2919.53</v>
+        <v>1254.07</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1015,15 +1015,129 @@
         <v>46218</v>
       </c>
       <c r="B31" t="n">
+        <v>1465</v>
+      </c>
+      <c r="C31" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1342.74</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B32" t="n">
+        <v>131</v>
+      </c>
+      <c r="C32" t="n">
+        <v>27</v>
+      </c>
+      <c r="D32" t="n">
+        <v>91.86</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1478</v>
+      </c>
+      <c r="C33" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D33" t="n">
+        <v>459.57</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B34" t="n">
+        <v>2782</v>
+      </c>
+      <c r="C34" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D34" t="n">
+        <v>994.77</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B35" t="n">
+        <v>131</v>
+      </c>
+      <c r="C35" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1125.63</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1116</v>
+      </c>
+      <c r="C36" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2919.53</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B37" t="n">
         <v>42</v>
       </c>
-      <c r="C31" t="n">
-        <v>8888</v>
-      </c>
-      <c r="D31" t="n">
+      <c r="C37" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D37" t="n">
         <v>79947.14999999999</v>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>OPERADOR LOGÍSTICO</t>
         </is>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,17 +483,17 @@
         <v>46218</v>
       </c>
       <c r="B3" t="n">
-        <v>451</v>
+        <v>1364</v>
       </c>
       <c r="C3" t="n">
-        <v>8888</v>
+        <v>3403</v>
       </c>
       <c r="D3" t="n">
-        <v>1103.58</v>
+        <v>1300.54</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -502,17 +502,17 @@
         <v>46218</v>
       </c>
       <c r="B4" t="n">
-        <v>1364</v>
+        <v>451</v>
       </c>
       <c r="C4" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D4" t="n">
-        <v>275.01</v>
+        <v>1103.58</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -521,17 +521,17 @@
         <v>46218</v>
       </c>
       <c r="B5" t="n">
-        <v>949</v>
+        <v>2651</v>
       </c>
       <c r="C5" t="n">
-        <v>1134</v>
+        <v>8888</v>
       </c>
       <c r="D5" t="n">
-        <v>30.46</v>
+        <v>660.95</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -540,17 +540,17 @@
         <v>46218</v>
       </c>
       <c r="B6" t="n">
-        <v>58</v>
+        <v>2118</v>
       </c>
       <c r="C6" t="n">
         <v>8888</v>
       </c>
       <c r="D6" t="n">
-        <v>499.11</v>
+        <v>452.46</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -559,17 +559,17 @@
         <v>46218</v>
       </c>
       <c r="B7" t="n">
-        <v>2245</v>
+        <v>949</v>
       </c>
       <c r="C7" t="n">
-        <v>8888</v>
+        <v>1134</v>
       </c>
       <c r="D7" t="n">
-        <v>2433.47</v>
+        <v>30.46</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
         <v>46218</v>
       </c>
       <c r="B8" t="n">
-        <v>438</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
         <v>8888</v>
       </c>
       <c r="D8" t="n">
-        <v>220.06</v>
+        <v>499.11</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -597,17 +597,17 @@
         <v>46218</v>
       </c>
       <c r="B9" t="n">
-        <v>451</v>
+        <v>2245</v>
       </c>
       <c r="C9" t="n">
         <v>8888</v>
       </c>
       <c r="D9" t="n">
-        <v>368.93</v>
+        <v>2433.47</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -616,17 +616,17 @@
         <v>46218</v>
       </c>
       <c r="B10" t="n">
-        <v>2714</v>
+        <v>535</v>
       </c>
       <c r="C10" t="n">
-        <v>519</v>
+        <v>8888</v>
       </c>
       <c r="D10" t="n">
-        <v>61939.22</v>
+        <v>583.85</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -635,17 +635,17 @@
         <v>46218</v>
       </c>
       <c r="B11" t="n">
-        <v>1075</v>
+        <v>438</v>
       </c>
       <c r="C11" t="n">
         <v>8888</v>
       </c>
       <c r="D11" t="n">
-        <v>5216.32</v>
+        <v>220.06</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -654,17 +654,17 @@
         <v>46218</v>
       </c>
       <c r="B12" t="n">
-        <v>483</v>
+        <v>325</v>
       </c>
       <c r="C12" t="n">
         <v>8888</v>
       </c>
       <c r="D12" t="n">
-        <v>2027.7</v>
+        <v>57.46</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -673,17 +673,17 @@
         <v>46218</v>
       </c>
       <c r="B13" t="n">
-        <v>89</v>
+        <v>451</v>
       </c>
       <c r="C13" t="n">
-        <v>13148</v>
+        <v>8888</v>
       </c>
       <c r="D13" t="n">
-        <v>1883.74</v>
+        <v>368.93</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -692,17 +692,17 @@
         <v>46218</v>
       </c>
       <c r="B14" t="n">
-        <v>1063</v>
+        <v>2714</v>
       </c>
       <c r="C14" t="n">
-        <v>8888</v>
+        <v>519</v>
       </c>
       <c r="D14" t="n">
-        <v>3576.45</v>
+        <v>61939.22</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -711,17 +711,17 @@
         <v>46218</v>
       </c>
       <c r="B15" t="n">
-        <v>1299</v>
+        <v>1075</v>
       </c>
       <c r="C15" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D15" t="n">
-        <v>990.24</v>
+        <v>11607.79</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -730,17 +730,17 @@
         <v>46218</v>
       </c>
       <c r="B16" t="n">
-        <v>285</v>
+        <v>2651</v>
       </c>
       <c r="C16" t="n">
         <v>8888</v>
       </c>
       <c r="D16" t="n">
-        <v>555.64</v>
+        <v>1296.58</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
         <v>46218</v>
       </c>
       <c r="B17" t="n">
-        <v>1063</v>
+        <v>89</v>
       </c>
       <c r="C17" t="n">
-        <v>8888</v>
+        <v>13148</v>
       </c>
       <c r="D17" t="n">
-        <v>932.71</v>
+        <v>1883.74</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -768,17 +768,17 @@
         <v>46218</v>
       </c>
       <c r="B18" t="n">
-        <v>1465</v>
+        <v>629</v>
       </c>
       <c r="C18" t="n">
         <v>8888</v>
       </c>
       <c r="D18" t="n">
-        <v>2431.47</v>
+        <v>553.13</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
         <v>46218</v>
       </c>
       <c r="B19" t="n">
-        <v>1937</v>
+        <v>2211</v>
       </c>
       <c r="C19" t="n">
-        <v>8888</v>
+        <v>874</v>
       </c>
       <c r="D19" t="n">
-        <v>833.52</v>
+        <v>1526.94</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -806,17 +806,17 @@
         <v>46218</v>
       </c>
       <c r="B20" t="n">
-        <v>477</v>
+        <v>1063</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D20" t="n">
-        <v>736.03</v>
+        <v>4487.11</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -825,17 +825,17 @@
         <v>46218</v>
       </c>
       <c r="B21" t="n">
-        <v>1063</v>
+        <v>1299</v>
       </c>
       <c r="C21" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D21" t="n">
-        <v>1113.08</v>
+        <v>990.24</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -844,17 +844,17 @@
         <v>46218</v>
       </c>
       <c r="B22" t="n">
-        <v>1007</v>
+        <v>285</v>
       </c>
       <c r="C22" t="n">
         <v>8888</v>
       </c>
       <c r="D22" t="n">
-        <v>241.44</v>
+        <v>555.64</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -863,17 +863,17 @@
         <v>46218</v>
       </c>
       <c r="B23" t="n">
-        <v>1380</v>
+        <v>477</v>
       </c>
       <c r="C23" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D23" t="n">
-        <v>520.2</v>
+        <v>1540.55</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
         <v>46218</v>
       </c>
       <c r="B24" t="n">
-        <v>483</v>
+        <v>1063</v>
       </c>
       <c r="C24" t="n">
-        <v>38</v>
+        <v>8888</v>
       </c>
       <c r="D24" t="n">
-        <v>2026.73</v>
+        <v>2549.86</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -901,13 +901,13 @@
         <v>46218</v>
       </c>
       <c r="B25" t="n">
-        <v>1075</v>
+        <v>1465</v>
       </c>
       <c r="C25" t="n">
         <v>8888</v>
       </c>
       <c r="D25" t="n">
-        <v>557.62</v>
+        <v>2431.47</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -920,13 +920,13 @@
         <v>46218</v>
       </c>
       <c r="B26" t="n">
-        <v>285</v>
+        <v>89</v>
       </c>
       <c r="C26" t="n">
         <v>8888</v>
       </c>
       <c r="D26" t="n">
-        <v>364.44</v>
+        <v>479</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -939,13 +939,13 @@
         <v>46218</v>
       </c>
       <c r="B27" t="n">
-        <v>1756</v>
+        <v>1465</v>
       </c>
       <c r="C27" t="n">
-        <v>27</v>
+        <v>3403</v>
       </c>
       <c r="D27" t="n">
-        <v>741.1799999999999</v>
+        <v>777.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -958,17 +958,17 @@
         <v>46218</v>
       </c>
       <c r="B28" t="n">
-        <v>629</v>
+        <v>1937</v>
       </c>
       <c r="C28" t="n">
         <v>8888</v>
       </c>
       <c r="D28" t="n">
-        <v>339.19</v>
+        <v>833.52</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -977,17 +977,17 @@
         <v>46218</v>
       </c>
       <c r="B29" t="n">
-        <v>816</v>
+        <v>1063</v>
       </c>
       <c r="C29" t="n">
         <v>8888</v>
       </c>
       <c r="D29" t="n">
-        <v>438.24</v>
+        <v>1113.08</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -996,13 +996,13 @@
         <v>46218</v>
       </c>
       <c r="B30" t="n">
-        <v>953</v>
+        <v>1293</v>
       </c>
       <c r="C30" t="n">
         <v>8888</v>
       </c>
       <c r="D30" t="n">
-        <v>1254.07</v>
+        <v>386.33</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1015,17 +1015,17 @@
         <v>46218</v>
       </c>
       <c r="B31" t="n">
-        <v>1465</v>
+        <v>2089</v>
       </c>
       <c r="C31" t="n">
-        <v>8888</v>
+        <v>1533</v>
       </c>
       <c r="D31" t="n">
-        <v>1342.74</v>
+        <v>442.44</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
         <v>46218</v>
       </c>
       <c r="B32" t="n">
-        <v>131</v>
+        <v>1007</v>
       </c>
       <c r="C32" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D32" t="n">
-        <v>91.86</v>
+        <v>241.44</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
         <v>46218</v>
       </c>
       <c r="B33" t="n">
-        <v>1478</v>
+        <v>1380</v>
       </c>
       <c r="C33" t="n">
         <v>8888</v>
       </c>
       <c r="D33" t="n">
-        <v>459.57</v>
+        <v>520.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1072,13 +1072,13 @@
         <v>46218</v>
       </c>
       <c r="B34" t="n">
-        <v>2782</v>
+        <v>1075</v>
       </c>
       <c r="C34" t="n">
         <v>8888</v>
       </c>
       <c r="D34" t="n">
-        <v>994.77</v>
+        <v>2179.03</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1091,17 +1091,17 @@
         <v>46218</v>
       </c>
       <c r="B35" t="n">
-        <v>131</v>
+        <v>2245</v>
       </c>
       <c r="C35" t="n">
         <v>8888</v>
       </c>
       <c r="D35" t="n">
-        <v>1125.63</v>
+        <v>361.58</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1110,17 +1110,17 @@
         <v>46218</v>
       </c>
       <c r="B36" t="n">
-        <v>1116</v>
+        <v>285</v>
       </c>
       <c r="C36" t="n">
         <v>8888</v>
       </c>
       <c r="D36" t="n">
-        <v>2919.53</v>
+        <v>364.44</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1129,17 +1129,378 @@
         <v>46218</v>
       </c>
       <c r="B37" t="n">
+        <v>1756</v>
+      </c>
+      <c r="C37" t="n">
+        <v>27</v>
+      </c>
+      <c r="D37" t="n">
+        <v>741.1799999999999</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B38" t="n">
+        <v>2651</v>
+      </c>
+      <c r="C38" t="n">
+        <v>58</v>
+      </c>
+      <c r="D38" t="n">
+        <v>363.7</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1064</v>
+      </c>
+      <c r="C39" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1274.3</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B40" t="n">
+        <v>2698</v>
+      </c>
+      <c r="C40" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D40" t="n">
+        <v>552.15</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B41" t="n">
+        <v>629</v>
+      </c>
+      <c r="C41" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D41" t="n">
+        <v>339.19</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B42" t="n">
+        <v>664</v>
+      </c>
+      <c r="C42" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1595.68</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B43" t="n">
+        <v>816</v>
+      </c>
+      <c r="C43" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D43" t="n">
+        <v>438.24</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B44" t="n">
+        <v>953</v>
+      </c>
+      <c r="C44" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2618.89</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B45" t="n">
+        <v>1465</v>
+      </c>
+      <c r="C45" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D45" t="n">
+        <v>3504</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B46" t="n">
+        <v>2245</v>
+      </c>
+      <c r="C46" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D46" t="n">
+        <v>427.51</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B47" t="n">
+        <v>131</v>
+      </c>
+      <c r="C47" t="n">
+        <v>27</v>
+      </c>
+      <c r="D47" t="n">
+        <v>91.86</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B48" t="n">
+        <v>451</v>
+      </c>
+      <c r="C48" t="n">
+        <v>3403</v>
+      </c>
+      <c r="D48" t="n">
+        <v>445.58</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B49" t="n">
+        <v>2114</v>
+      </c>
+      <c r="C49" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D49" t="n">
+        <v>641.92</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B50" t="n">
+        <v>2782</v>
+      </c>
+      <c r="C50" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1786.32</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B51" t="n">
+        <v>1478</v>
+      </c>
+      <c r="C51" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D51" t="n">
+        <v>459.57</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B52" t="n">
+        <v>131</v>
+      </c>
+      <c r="C52" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1125.63</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B53" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C53" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2599.69</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B54" t="n">
+        <v>1116</v>
+      </c>
+      <c r="C54" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2919.53</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B55" t="n">
         <v>42</v>
       </c>
-      <c r="C37" t="n">
-        <v>8888</v>
-      </c>
-      <c r="D37" t="n">
+      <c r="C55" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D55" t="n">
         <v>79947.14999999999</v>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B56" t="n">
+        <v>2109</v>
+      </c>
+      <c r="C56" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D56" t="n">
+        <v>788.98</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1110,17 +1110,17 @@
         <v>46218</v>
       </c>
       <c r="B36" t="n">
-        <v>285</v>
+        <v>452</v>
       </c>
       <c r="C36" t="n">
         <v>8888</v>
       </c>
       <c r="D36" t="n">
-        <v>364.44</v>
+        <v>608.78</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1129,17 +1129,17 @@
         <v>46218</v>
       </c>
       <c r="B37" t="n">
-        <v>1756</v>
+        <v>285</v>
       </c>
       <c r="C37" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D37" t="n">
-        <v>741.1799999999999</v>
+        <v>364.44</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1148,13 +1148,13 @@
         <v>46218</v>
       </c>
       <c r="B38" t="n">
-        <v>2651</v>
+        <v>1756</v>
       </c>
       <c r="C38" t="n">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="D38" t="n">
-        <v>363.7</v>
+        <v>741.1799999999999</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1167,17 +1167,17 @@
         <v>46218</v>
       </c>
       <c r="B39" t="n">
-        <v>1064</v>
+        <v>2651</v>
       </c>
       <c r="C39" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D39" t="n">
-        <v>1274.3</v>
+        <v>363.7</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1186,13 +1186,13 @@
         <v>46218</v>
       </c>
       <c r="B40" t="n">
-        <v>2698</v>
+        <v>1064</v>
       </c>
       <c r="C40" t="n">
         <v>8888</v>
       </c>
       <c r="D40" t="n">
-        <v>552.15</v>
+        <v>1274.3</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1205,13 +1205,13 @@
         <v>46218</v>
       </c>
       <c r="B41" t="n">
-        <v>629</v>
+        <v>2698</v>
       </c>
       <c r="C41" t="n">
         <v>8888</v>
       </c>
       <c r="D41" t="n">
-        <v>339.19</v>
+        <v>552.15</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1224,17 +1224,17 @@
         <v>46218</v>
       </c>
       <c r="B42" t="n">
-        <v>664</v>
+        <v>629</v>
       </c>
       <c r="C42" t="n">
         <v>8888</v>
       </c>
       <c r="D42" t="n">
-        <v>1595.68</v>
+        <v>339.19</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
         <v>46218</v>
       </c>
       <c r="B43" t="n">
-        <v>816</v>
+        <v>664</v>
       </c>
       <c r="C43" t="n">
         <v>8888</v>
       </c>
       <c r="D43" t="n">
-        <v>438.24</v>
+        <v>1595.68</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1262,17 +1262,17 @@
         <v>46218</v>
       </c>
       <c r="B44" t="n">
-        <v>953</v>
+        <v>816</v>
       </c>
       <c r="C44" t="n">
         <v>8888</v>
       </c>
       <c r="D44" t="n">
-        <v>2618.89</v>
+        <v>438.24</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1281,13 +1281,13 @@
         <v>46218</v>
       </c>
       <c r="B45" t="n">
-        <v>1465</v>
+        <v>953</v>
       </c>
       <c r="C45" t="n">
         <v>8888</v>
       </c>
       <c r="D45" t="n">
-        <v>3504</v>
+        <v>2618.89</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1300,17 +1300,17 @@
         <v>46218</v>
       </c>
       <c r="B46" t="n">
-        <v>2245</v>
+        <v>1465</v>
       </c>
       <c r="C46" t="n">
         <v>8888</v>
       </c>
       <c r="D46" t="n">
-        <v>427.51</v>
+        <v>3504</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1319,17 +1319,17 @@
         <v>46218</v>
       </c>
       <c r="B47" t="n">
-        <v>131</v>
+        <v>2245</v>
       </c>
       <c r="C47" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D47" t="n">
-        <v>91.86</v>
+        <v>427.51</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1338,13 +1338,13 @@
         <v>46218</v>
       </c>
       <c r="B48" t="n">
-        <v>451</v>
+        <v>131</v>
       </c>
       <c r="C48" t="n">
-        <v>3403</v>
+        <v>27</v>
       </c>
       <c r="D48" t="n">
-        <v>445.58</v>
+        <v>91.86</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1357,17 +1357,17 @@
         <v>46218</v>
       </c>
       <c r="B49" t="n">
-        <v>2114</v>
+        <v>451</v>
       </c>
       <c r="C49" t="n">
-        <v>8888</v>
+        <v>3403</v>
       </c>
       <c r="D49" t="n">
-        <v>641.92</v>
+        <v>445.58</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1376,13 +1376,13 @@
         <v>46218</v>
       </c>
       <c r="B50" t="n">
-        <v>2782</v>
+        <v>2114</v>
       </c>
       <c r="C50" t="n">
         <v>8888</v>
       </c>
       <c r="D50" t="n">
-        <v>1786.32</v>
+        <v>641.92</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1395,17 +1395,17 @@
         <v>46218</v>
       </c>
       <c r="B51" t="n">
-        <v>1478</v>
+        <v>2782</v>
       </c>
       <c r="C51" t="n">
         <v>8888</v>
       </c>
       <c r="D51" t="n">
-        <v>459.57</v>
+        <v>1786.32</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1414,13 +1414,13 @@
         <v>46218</v>
       </c>
       <c r="B52" t="n">
-        <v>131</v>
+        <v>1478</v>
       </c>
       <c r="C52" t="n">
         <v>8888</v>
       </c>
       <c r="D52" t="n">
-        <v>1125.63</v>
+        <v>459.57</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -1433,17 +1433,17 @@
         <v>46218</v>
       </c>
       <c r="B53" t="n">
-        <v>2015</v>
+        <v>131</v>
       </c>
       <c r="C53" t="n">
         <v>8888</v>
       </c>
       <c r="D53" t="n">
-        <v>2599.69</v>
+        <v>1125.63</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1452,17 +1452,17 @@
         <v>46218</v>
       </c>
       <c r="B54" t="n">
-        <v>1116</v>
+        <v>2015</v>
       </c>
       <c r="C54" t="n">
         <v>8888</v>
       </c>
       <c r="D54" t="n">
-        <v>2919.53</v>
+        <v>2599.69</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1471,13 +1471,13 @@
         <v>46218</v>
       </c>
       <c r="B55" t="n">
-        <v>42</v>
+        <v>1116</v>
       </c>
       <c r="C55" t="n">
         <v>8888</v>
       </c>
       <c r="D55" t="n">
-        <v>79947.14999999999</v>
+        <v>2919.53</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -1490,15 +1490,34 @@
         <v>46218</v>
       </c>
       <c r="B56" t="n">
+        <v>42</v>
+      </c>
+      <c r="C56" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D56" t="n">
+        <v>79947.14999999999</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B57" t="n">
         <v>2109</v>
       </c>
-      <c r="C56" t="n">
-        <v>8888</v>
-      </c>
-      <c r="D56" t="n">
+      <c r="C57" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D57" t="n">
         <v>788.98</v>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>FORÇA DE VENDAS</t>
         </is>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,17 +521,17 @@
         <v>46218</v>
       </c>
       <c r="B5" t="n">
-        <v>2651</v>
+        <v>131</v>
       </c>
       <c r="C5" t="n">
         <v>8888</v>
       </c>
       <c r="D5" t="n">
-        <v>660.95</v>
+        <v>1469.86</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -540,17 +540,17 @@
         <v>46218</v>
       </c>
       <c r="B6" t="n">
-        <v>2118</v>
+        <v>2651</v>
       </c>
       <c r="C6" t="n">
         <v>8888</v>
       </c>
       <c r="D6" t="n">
-        <v>452.46</v>
+        <v>660.95</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -559,17 +559,17 @@
         <v>46218</v>
       </c>
       <c r="B7" t="n">
-        <v>949</v>
+        <v>2118</v>
       </c>
       <c r="C7" t="n">
-        <v>1134</v>
+        <v>8888</v>
       </c>
       <c r="D7" t="n">
-        <v>30.46</v>
+        <v>452.46</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
         <v>46218</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>949</v>
       </c>
       <c r="C8" t="n">
-        <v>8888</v>
+        <v>1134</v>
       </c>
       <c r="D8" t="n">
-        <v>499.11</v>
+        <v>30.46</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -597,13 +597,13 @@
         <v>46218</v>
       </c>
       <c r="B9" t="n">
-        <v>2245</v>
+        <v>2499</v>
       </c>
       <c r="C9" t="n">
         <v>8888</v>
       </c>
       <c r="D9" t="n">
-        <v>2433.47</v>
+        <v>261.63</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -616,17 +616,17 @@
         <v>46218</v>
       </c>
       <c r="B10" t="n">
-        <v>535</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
         <v>8888</v>
       </c>
       <c r="D10" t="n">
-        <v>583.85</v>
+        <v>499.11</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -635,17 +635,17 @@
         <v>46218</v>
       </c>
       <c r="B11" t="n">
-        <v>438</v>
+        <v>2245</v>
       </c>
       <c r="C11" t="n">
         <v>8888</v>
       </c>
       <c r="D11" t="n">
-        <v>220.06</v>
+        <v>2433.47</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -654,17 +654,17 @@
         <v>46218</v>
       </c>
       <c r="B12" t="n">
-        <v>325</v>
+        <v>2383</v>
       </c>
       <c r="C12" t="n">
         <v>8888</v>
       </c>
       <c r="D12" t="n">
-        <v>57.46</v>
+        <v>6204.03</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -673,17 +673,17 @@
         <v>46218</v>
       </c>
       <c r="B13" t="n">
-        <v>451</v>
+        <v>1117</v>
       </c>
       <c r="C13" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D13" t="n">
-        <v>368.93</v>
+        <v>916.72</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -692,17 +692,17 @@
         <v>46218</v>
       </c>
       <c r="B14" t="n">
-        <v>2714</v>
+        <v>2279</v>
       </c>
       <c r="C14" t="n">
-        <v>519</v>
+        <v>8888</v>
       </c>
       <c r="D14" t="n">
-        <v>61939.22</v>
+        <v>712.66</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -711,17 +711,17 @@
         <v>46218</v>
       </c>
       <c r="B15" t="n">
-        <v>1075</v>
+        <v>535</v>
       </c>
       <c r="C15" t="n">
         <v>8888</v>
       </c>
       <c r="D15" t="n">
-        <v>11607.79</v>
+        <v>2144.17</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -730,17 +730,17 @@
         <v>46218</v>
       </c>
       <c r="B16" t="n">
-        <v>2651</v>
+        <v>535</v>
       </c>
       <c r="C16" t="n">
         <v>8888</v>
       </c>
       <c r="D16" t="n">
-        <v>1296.58</v>
+        <v>1056.19</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
         <v>46218</v>
       </c>
       <c r="B17" t="n">
-        <v>89</v>
+        <v>438</v>
       </c>
       <c r="C17" t="n">
-        <v>13148</v>
+        <v>8888</v>
       </c>
       <c r="D17" t="n">
-        <v>1883.74</v>
+        <v>220.06</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -768,17 +768,17 @@
         <v>46218</v>
       </c>
       <c r="B18" t="n">
-        <v>629</v>
+        <v>1293</v>
       </c>
       <c r="C18" t="n">
         <v>8888</v>
       </c>
       <c r="D18" t="n">
-        <v>553.13</v>
+        <v>1388.12</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
         <v>46218</v>
       </c>
       <c r="B19" t="n">
-        <v>2211</v>
+        <v>2279</v>
       </c>
       <c r="C19" t="n">
-        <v>874</v>
+        <v>8888</v>
       </c>
       <c r="D19" t="n">
-        <v>1526.94</v>
+        <v>2753.96</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -806,17 +806,17 @@
         <v>46218</v>
       </c>
       <c r="B20" t="n">
-        <v>1063</v>
+        <v>1137</v>
       </c>
       <c r="C20" t="n">
         <v>8888</v>
       </c>
       <c r="D20" t="n">
-        <v>4487.11</v>
+        <v>952.95</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -825,17 +825,17 @@
         <v>46218</v>
       </c>
       <c r="B21" t="n">
-        <v>1299</v>
+        <v>325</v>
       </c>
       <c r="C21" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D21" t="n">
-        <v>990.24</v>
+        <v>57.46</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -844,17 +844,17 @@
         <v>46218</v>
       </c>
       <c r="B22" t="n">
-        <v>285</v>
+        <v>451</v>
       </c>
       <c r="C22" t="n">
         <v>8888</v>
       </c>
       <c r="D22" t="n">
-        <v>555.64</v>
+        <v>368.93</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -863,13 +863,13 @@
         <v>46218</v>
       </c>
       <c r="B23" t="n">
-        <v>477</v>
+        <v>2714</v>
       </c>
       <c r="C23" t="n">
-        <v>58</v>
+        <v>519</v>
       </c>
       <c r="D23" t="n">
-        <v>1540.55</v>
+        <v>61939.22</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -882,17 +882,17 @@
         <v>46218</v>
       </c>
       <c r="B24" t="n">
-        <v>1063</v>
+        <v>483</v>
       </c>
       <c r="C24" t="n">
         <v>8888</v>
       </c>
       <c r="D24" t="n">
-        <v>2549.86</v>
+        <v>2532.06</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
         <v>46218</v>
       </c>
       <c r="B25" t="n">
-        <v>1465</v>
+        <v>1075</v>
       </c>
       <c r="C25" t="n">
         <v>8888</v>
       </c>
       <c r="D25" t="n">
-        <v>2431.47</v>
+        <v>11607.79</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -920,17 +920,17 @@
         <v>46218</v>
       </c>
       <c r="B26" t="n">
-        <v>89</v>
+        <v>629</v>
       </c>
       <c r="C26" t="n">
         <v>8888</v>
       </c>
       <c r="D26" t="n">
-        <v>479</v>
+        <v>4569.78</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -939,13 +939,13 @@
         <v>46218</v>
       </c>
       <c r="B27" t="n">
-        <v>1465</v>
+        <v>1983</v>
       </c>
       <c r="C27" t="n">
-        <v>3403</v>
+        <v>841</v>
       </c>
       <c r="D27" t="n">
-        <v>777.2</v>
+        <v>105.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -958,17 +958,17 @@
         <v>46218</v>
       </c>
       <c r="B28" t="n">
-        <v>1937</v>
+        <v>2651</v>
       </c>
       <c r="C28" t="n">
         <v>8888</v>
       </c>
       <c r="D28" t="n">
-        <v>833.52</v>
+        <v>1296.58</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -977,17 +977,17 @@
         <v>46218</v>
       </c>
       <c r="B29" t="n">
-        <v>1063</v>
+        <v>89</v>
       </c>
       <c r="C29" t="n">
-        <v>8888</v>
+        <v>13148</v>
       </c>
       <c r="D29" t="n">
-        <v>1113.08</v>
+        <v>1883.74</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -996,17 +996,17 @@
         <v>46218</v>
       </c>
       <c r="B30" t="n">
-        <v>1293</v>
+        <v>2211</v>
       </c>
       <c r="C30" t="n">
-        <v>8888</v>
+        <v>874</v>
       </c>
       <c r="D30" t="n">
-        <v>386.33</v>
+        <v>1526.94</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1015,17 +1015,17 @@
         <v>46218</v>
       </c>
       <c r="B31" t="n">
-        <v>2089</v>
+        <v>559</v>
       </c>
       <c r="C31" t="n">
-        <v>1533</v>
+        <v>8888</v>
       </c>
       <c r="D31" t="n">
-        <v>442.44</v>
+        <v>859.92</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1034,13 +1034,13 @@
         <v>46218</v>
       </c>
       <c r="B32" t="n">
-        <v>1007</v>
+        <v>1063</v>
       </c>
       <c r="C32" t="n">
         <v>8888</v>
       </c>
       <c r="D32" t="n">
-        <v>241.44</v>
+        <v>4487.11</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1053,17 +1053,17 @@
         <v>46218</v>
       </c>
       <c r="B33" t="n">
-        <v>1380</v>
+        <v>2279</v>
       </c>
       <c r="C33" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D33" t="n">
-        <v>520.2</v>
+        <v>652.51</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1072,17 +1072,17 @@
         <v>46218</v>
       </c>
       <c r="B34" t="n">
-        <v>1075</v>
+        <v>1299</v>
       </c>
       <c r="C34" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D34" t="n">
-        <v>2179.03</v>
+        <v>990.24</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1091,17 +1091,17 @@
         <v>46218</v>
       </c>
       <c r="B35" t="n">
-        <v>2245</v>
+        <v>285</v>
       </c>
       <c r="C35" t="n">
         <v>8888</v>
       </c>
       <c r="D35" t="n">
-        <v>361.58</v>
+        <v>3349.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1110,17 +1110,17 @@
         <v>46218</v>
       </c>
       <c r="B36" t="n">
-        <v>452</v>
+        <v>1983</v>
       </c>
       <c r="C36" t="n">
         <v>8888</v>
       </c>
       <c r="D36" t="n">
-        <v>608.78</v>
+        <v>2451.28</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1129,17 +1129,17 @@
         <v>46218</v>
       </c>
       <c r="B37" t="n">
-        <v>285</v>
+        <v>477</v>
       </c>
       <c r="C37" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D37" t="n">
-        <v>364.44</v>
+        <v>1540.55</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1148,17 +1148,17 @@
         <v>46218</v>
       </c>
       <c r="B38" t="n">
-        <v>1756</v>
+        <v>1063</v>
       </c>
       <c r="C38" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D38" t="n">
-        <v>741.1799999999999</v>
+        <v>2549.86</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1167,17 +1167,17 @@
         <v>46218</v>
       </c>
       <c r="B39" t="n">
-        <v>2651</v>
+        <v>424</v>
       </c>
       <c r="C39" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D39" t="n">
-        <v>363.7</v>
+        <v>1035.17</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1186,13 +1186,13 @@
         <v>46218</v>
       </c>
       <c r="B40" t="n">
-        <v>1064</v>
+        <v>675</v>
       </c>
       <c r="C40" t="n">
         <v>8888</v>
       </c>
       <c r="D40" t="n">
-        <v>1274.3</v>
+        <v>616.73</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1205,17 +1205,17 @@
         <v>46218</v>
       </c>
       <c r="B41" t="n">
-        <v>2698</v>
+        <v>1993</v>
       </c>
       <c r="C41" t="n">
         <v>8888</v>
       </c>
       <c r="D41" t="n">
-        <v>552.15</v>
+        <v>362.63</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1224,13 +1224,13 @@
         <v>46218</v>
       </c>
       <c r="B42" t="n">
-        <v>629</v>
+        <v>1465</v>
       </c>
       <c r="C42" t="n">
         <v>8888</v>
       </c>
       <c r="D42" t="n">
-        <v>339.19</v>
+        <v>2431.47</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1243,13 +1243,13 @@
         <v>46218</v>
       </c>
       <c r="B43" t="n">
-        <v>664</v>
+        <v>89</v>
       </c>
       <c r="C43" t="n">
         <v>8888</v>
       </c>
       <c r="D43" t="n">
-        <v>1595.68</v>
+        <v>479</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1262,17 +1262,17 @@
         <v>46218</v>
       </c>
       <c r="B44" t="n">
-        <v>816</v>
+        <v>1465</v>
       </c>
       <c r="C44" t="n">
-        <v>8888</v>
+        <v>3403</v>
       </c>
       <c r="D44" t="n">
-        <v>438.24</v>
+        <v>777.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1281,13 +1281,13 @@
         <v>46218</v>
       </c>
       <c r="B45" t="n">
-        <v>953</v>
+        <v>1937</v>
       </c>
       <c r="C45" t="n">
         <v>8888</v>
       </c>
       <c r="D45" t="n">
-        <v>2618.89</v>
+        <v>833.52</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1300,17 +1300,17 @@
         <v>46218</v>
       </c>
       <c r="B46" t="n">
-        <v>1465</v>
+        <v>360</v>
       </c>
       <c r="C46" t="n">
         <v>8888</v>
       </c>
       <c r="D46" t="n">
-        <v>3504</v>
+        <v>731.37</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1319,17 +1319,17 @@
         <v>46218</v>
       </c>
       <c r="B47" t="n">
-        <v>2245</v>
+        <v>1063</v>
       </c>
       <c r="C47" t="n">
         <v>8888</v>
       </c>
       <c r="D47" t="n">
-        <v>427.51</v>
+        <v>1113.08</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1338,17 @@
         <v>46218</v>
       </c>
       <c r="B48" t="n">
-        <v>131</v>
+        <v>1293</v>
       </c>
       <c r="C48" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D48" t="n">
-        <v>91.86</v>
+        <v>386.33</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1357,13 +1357,13 @@
         <v>46218</v>
       </c>
       <c r="B49" t="n">
-        <v>451</v>
+        <v>2089</v>
       </c>
       <c r="C49" t="n">
-        <v>3403</v>
+        <v>1533</v>
       </c>
       <c r="D49" t="n">
-        <v>445.58</v>
+        <v>442.44</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1376,13 +1376,13 @@
         <v>46218</v>
       </c>
       <c r="B50" t="n">
-        <v>2114</v>
+        <v>1007</v>
       </c>
       <c r="C50" t="n">
         <v>8888</v>
       </c>
       <c r="D50" t="n">
-        <v>641.92</v>
+        <v>241.44</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         <v>46218</v>
       </c>
       <c r="B51" t="n">
-        <v>2782</v>
+        <v>1380</v>
       </c>
       <c r="C51" t="n">
         <v>8888</v>
       </c>
       <c r="D51" t="n">
-        <v>1786.32</v>
+        <v>520.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -1414,17 +1414,17 @@
         <v>46218</v>
       </c>
       <c r="B52" t="n">
-        <v>1478</v>
+        <v>1102</v>
       </c>
       <c r="C52" t="n">
         <v>8888</v>
       </c>
       <c r="D52" t="n">
-        <v>459.57</v>
+        <v>349.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1433,17 +1433,17 @@
         <v>46218</v>
       </c>
       <c r="B53" t="n">
-        <v>131</v>
+        <v>1075</v>
       </c>
       <c r="C53" t="n">
         <v>8888</v>
       </c>
       <c r="D53" t="n">
-        <v>1125.63</v>
+        <v>2179.03</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1452,17 +1452,17 @@
         <v>46218</v>
       </c>
       <c r="B54" t="n">
-        <v>2015</v>
+        <v>2245</v>
       </c>
       <c r="C54" t="n">
         <v>8888</v>
       </c>
       <c r="D54" t="n">
-        <v>2599.69</v>
+        <v>361.58</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1471,17 +1471,17 @@
         <v>46218</v>
       </c>
       <c r="B55" t="n">
-        <v>1116</v>
+        <v>452</v>
       </c>
       <c r="C55" t="n">
         <v>8888</v>
       </c>
       <c r="D55" t="n">
-        <v>2919.53</v>
+        <v>608.78</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1490,17 +1490,17 @@
         <v>46218</v>
       </c>
       <c r="B56" t="n">
-        <v>42</v>
+        <v>285</v>
       </c>
       <c r="C56" t="n">
         <v>8888</v>
       </c>
       <c r="D56" t="n">
-        <v>79947.14999999999</v>
+        <v>2090.81</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1509,17 +1509,644 @@
         <v>46218</v>
       </c>
       <c r="B57" t="n">
+        <v>1102</v>
+      </c>
+      <c r="C57" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1119.32</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B58" t="n">
+        <v>626</v>
+      </c>
+      <c r="C58" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3520.98</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B59" t="n">
+        <v>1756</v>
+      </c>
+      <c r="C59" t="n">
+        <v>27</v>
+      </c>
+      <c r="D59" t="n">
+        <v>741.1799999999999</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B60" t="n">
+        <v>2651</v>
+      </c>
+      <c r="C60" t="n">
+        <v>58</v>
+      </c>
+      <c r="D60" t="n">
+        <v>363.7</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1064</v>
+      </c>
+      <c r="C61" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1274.3</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B62" t="n">
+        <v>2698</v>
+      </c>
+      <c r="C62" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D62" t="n">
+        <v>552.15</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B63" t="n">
+        <v>629</v>
+      </c>
+      <c r="C63" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D63" t="n">
+        <v>721.25</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B64" t="n">
+        <v>664</v>
+      </c>
+      <c r="C64" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1595.68</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B65" t="n">
+        <v>816</v>
+      </c>
+      <c r="C65" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D65" t="n">
+        <v>438.24</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B66" t="n">
+        <v>285</v>
+      </c>
+      <c r="C66" t="n">
+        <v>58</v>
+      </c>
+      <c r="D66" t="n">
+        <v>364.99</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B67" t="n">
+        <v>2114</v>
+      </c>
+      <c r="C67" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1682.3</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B68" t="n">
+        <v>953</v>
+      </c>
+      <c r="C68" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D68" t="n">
+        <v>2618.89</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B69" t="n">
+        <v>1102</v>
+      </c>
+      <c r="C69" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1771.61</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B70" t="n">
+        <v>619</v>
+      </c>
+      <c r="C70" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D70" t="n">
+        <v>2021.67</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B71" t="n">
+        <v>1465</v>
+      </c>
+      <c r="C71" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D71" t="n">
+        <v>3504</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B72" t="n">
+        <v>2767</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1898</v>
+      </c>
+      <c r="D72" t="n">
+        <v>466.12</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B73" t="n">
+        <v>2245</v>
+      </c>
+      <c r="C73" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D73" t="n">
+        <v>427.51</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B74" t="n">
+        <v>131</v>
+      </c>
+      <c r="C74" t="n">
+        <v>27</v>
+      </c>
+      <c r="D74" t="n">
+        <v>299.37</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B75" t="n">
+        <v>1993</v>
+      </c>
+      <c r="C75" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1864.73</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B76" t="n">
+        <v>451</v>
+      </c>
+      <c r="C76" t="n">
+        <v>3403</v>
+      </c>
+      <c r="D76" t="n">
+        <v>445.58</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B77" t="n">
+        <v>2749</v>
+      </c>
+      <c r="C77" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1860.64</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B78" t="n">
+        <v>1117</v>
+      </c>
+      <c r="C78" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D78" t="n">
+        <v>342.2</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B79" t="n">
+        <v>2491</v>
+      </c>
+      <c r="C79" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D79" t="n">
+        <v>650.4299999999999</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B80" t="n">
+        <v>2782</v>
+      </c>
+      <c r="C80" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1786.32</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B81" t="n">
+        <v>483</v>
+      </c>
+      <c r="C81" t="n">
+        <v>841</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1393.15</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B82" t="n">
+        <v>1478</v>
+      </c>
+      <c r="C82" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D82" t="n">
+        <v>459.57</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B83" t="n">
+        <v>131</v>
+      </c>
+      <c r="C83" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1369.91</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B84" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C84" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D84" t="n">
+        <v>2599.69</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B85" t="n">
         <v>2109</v>
       </c>
-      <c r="C57" t="n">
-        <v>8888</v>
-      </c>
-      <c r="D57" t="n">
-        <v>788.98</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>FORÇA DE VENDAS</t>
+      <c r="C85" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D85" t="n">
+        <v>2293.78</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B86" t="n">
+        <v>1116</v>
+      </c>
+      <c r="C86" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D86" t="n">
+        <v>2919.53</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B87" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C87" t="n">
+        <v>27</v>
+      </c>
+      <c r="D87" t="n">
+        <v>1573.32</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B88" t="n">
+        <v>42</v>
+      </c>
+      <c r="C88" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D88" t="n">
+        <v>79947.14999999999</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B89" t="n">
+        <v>1993</v>
+      </c>
+      <c r="C89" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D89" t="n">
+        <v>456.62</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B90" t="n">
+        <v>629</v>
+      </c>
+      <c r="C90" t="n">
+        <v>675</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1054.76</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:E137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,17 +483,17 @@
         <v>46218</v>
       </c>
       <c r="B3" t="n">
-        <v>1364</v>
+        <v>664</v>
       </c>
       <c r="C3" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D3" t="n">
-        <v>1300.54</v>
+        <v>463.88</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -502,17 +502,17 @@
         <v>46218</v>
       </c>
       <c r="B4" t="n">
-        <v>451</v>
+        <v>1364</v>
       </c>
       <c r="C4" t="n">
-        <v>8888</v>
+        <v>3403</v>
       </c>
       <c r="D4" t="n">
-        <v>1103.58</v>
+        <v>1300.54</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -521,17 +521,17 @@
         <v>46218</v>
       </c>
       <c r="B5" t="n">
-        <v>131</v>
+        <v>451</v>
       </c>
       <c r="C5" t="n">
         <v>8888</v>
       </c>
       <c r="D5" t="n">
-        <v>1469.86</v>
+        <v>1103.58</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -540,17 +540,17 @@
         <v>46218</v>
       </c>
       <c r="B6" t="n">
-        <v>2651</v>
+        <v>131</v>
       </c>
       <c r="C6" t="n">
         <v>8888</v>
       </c>
       <c r="D6" t="n">
-        <v>660.95</v>
+        <v>1469.86</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -559,13 +559,13 @@
         <v>46218</v>
       </c>
       <c r="B7" t="n">
-        <v>2118</v>
+        <v>2211</v>
       </c>
       <c r="C7" t="n">
         <v>8888</v>
       </c>
       <c r="D7" t="n">
-        <v>452.46</v>
+        <v>2190.93</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -578,17 +578,17 @@
         <v>46218</v>
       </c>
       <c r="B8" t="n">
-        <v>949</v>
+        <v>2660</v>
       </c>
       <c r="C8" t="n">
-        <v>1134</v>
+        <v>8888</v>
       </c>
       <c r="D8" t="n">
-        <v>30.46</v>
+        <v>875.61</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -597,13 +597,13 @@
         <v>46218</v>
       </c>
       <c r="B9" t="n">
-        <v>2499</v>
+        <v>2651</v>
       </c>
       <c r="C9" t="n">
         <v>8888</v>
       </c>
       <c r="D9" t="n">
-        <v>261.63</v>
+        <v>660.95</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -616,13 +616,13 @@
         <v>46218</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>2197</v>
       </c>
       <c r="C10" t="n">
         <v>8888</v>
       </c>
       <c r="D10" t="n">
-        <v>499.11</v>
+        <v>892.66</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -635,17 +635,17 @@
         <v>46218</v>
       </c>
       <c r="B11" t="n">
-        <v>2245</v>
+        <v>609</v>
       </c>
       <c r="C11" t="n">
-        <v>8888</v>
+        <v>3179</v>
       </c>
       <c r="D11" t="n">
-        <v>2433.47</v>
+        <v>1611.48</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -654,13 +654,13 @@
         <v>46218</v>
       </c>
       <c r="B12" t="n">
-        <v>2383</v>
+        <v>2118</v>
       </c>
       <c r="C12" t="n">
         <v>8888</v>
       </c>
       <c r="D12" t="n">
-        <v>6204.03</v>
+        <v>452.46</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -673,13 +673,13 @@
         <v>46218</v>
       </c>
       <c r="B13" t="n">
-        <v>1117</v>
+        <v>931</v>
       </c>
       <c r="C13" t="n">
-        <v>1139</v>
+        <v>423</v>
       </c>
       <c r="D13" t="n">
-        <v>916.72</v>
+        <v>492.34</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -692,17 +692,17 @@
         <v>46218</v>
       </c>
       <c r="B14" t="n">
-        <v>2279</v>
+        <v>525</v>
       </c>
       <c r="C14" t="n">
         <v>8888</v>
       </c>
       <c r="D14" t="n">
-        <v>712.66</v>
+        <v>408.25</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -711,17 +711,17 @@
         <v>46218</v>
       </c>
       <c r="B15" t="n">
-        <v>535</v>
+        <v>1808</v>
       </c>
       <c r="C15" t="n">
         <v>8888</v>
       </c>
       <c r="D15" t="n">
-        <v>2144.17</v>
+        <v>695.3200000000001</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -730,17 +730,17 @@
         <v>46218</v>
       </c>
       <c r="B16" t="n">
-        <v>535</v>
+        <v>949</v>
       </c>
       <c r="C16" t="n">
-        <v>8888</v>
+        <v>1134</v>
       </c>
       <c r="D16" t="n">
-        <v>1056.19</v>
+        <v>30.46</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
         <v>46218</v>
       </c>
       <c r="B17" t="n">
-        <v>438</v>
+        <v>2499</v>
       </c>
       <c r="C17" t="n">
         <v>8888</v>
       </c>
       <c r="D17" t="n">
-        <v>220.06</v>
+        <v>261.63</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -768,17 +768,17 @@
         <v>46218</v>
       </c>
       <c r="B18" t="n">
-        <v>1293</v>
+        <v>58</v>
       </c>
       <c r="C18" t="n">
         <v>8888</v>
       </c>
       <c r="D18" t="n">
-        <v>1388.12</v>
+        <v>499.11</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
         <v>46218</v>
       </c>
       <c r="B19" t="n">
-        <v>2279</v>
+        <v>2245</v>
       </c>
       <c r="C19" t="n">
         <v>8888</v>
       </c>
       <c r="D19" t="n">
-        <v>2753.96</v>
+        <v>2740.06</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -806,17 +806,17 @@
         <v>46218</v>
       </c>
       <c r="B20" t="n">
-        <v>1137</v>
+        <v>2383</v>
       </c>
       <c r="C20" t="n">
         <v>8888</v>
       </c>
       <c r="D20" t="n">
-        <v>952.95</v>
+        <v>7926.02</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -825,17 +825,17 @@
         <v>46218</v>
       </c>
       <c r="B21" t="n">
-        <v>325</v>
+        <v>1117</v>
       </c>
       <c r="C21" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D21" t="n">
-        <v>57.46</v>
+        <v>916.72</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -844,17 +844,17 @@
         <v>46218</v>
       </c>
       <c r="B22" t="n">
-        <v>451</v>
+        <v>2279</v>
       </c>
       <c r="C22" t="n">
         <v>8888</v>
       </c>
       <c r="D22" t="n">
-        <v>368.93</v>
+        <v>712.66</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -863,17 +863,17 @@
         <v>46218</v>
       </c>
       <c r="B23" t="n">
-        <v>2714</v>
+        <v>535</v>
       </c>
       <c r="C23" t="n">
-        <v>519</v>
+        <v>8888</v>
       </c>
       <c r="D23" t="n">
-        <v>61939.22</v>
+        <v>3228.46</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
         <v>46218</v>
       </c>
       <c r="B24" t="n">
-        <v>483</v>
+        <v>535</v>
       </c>
       <c r="C24" t="n">
         <v>8888</v>
       </c>
       <c r="D24" t="n">
-        <v>2532.06</v>
+        <v>1352.51</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
         <v>46218</v>
       </c>
       <c r="B25" t="n">
-        <v>1075</v>
+        <v>2678</v>
       </c>
       <c r="C25" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D25" t="n">
-        <v>11607.79</v>
+        <v>364.96</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -920,17 +920,17 @@
         <v>46218</v>
       </c>
       <c r="B26" t="n">
-        <v>629</v>
+        <v>438</v>
       </c>
       <c r="C26" t="n">
         <v>8888</v>
       </c>
       <c r="D26" t="n">
-        <v>4569.78</v>
+        <v>220.06</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -939,17 +939,17 @@
         <v>46218</v>
       </c>
       <c r="B27" t="n">
-        <v>1983</v>
+        <v>1293</v>
       </c>
       <c r="C27" t="n">
-        <v>841</v>
+        <v>8888</v>
       </c>
       <c r="D27" t="n">
-        <v>105.6</v>
+        <v>1388.12</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
         <v>46218</v>
       </c>
       <c r="B28" t="n">
-        <v>2651</v>
+        <v>2279</v>
       </c>
       <c r="C28" t="n">
         <v>8888</v>
       </c>
       <c r="D28" t="n">
-        <v>1296.58</v>
+        <v>2753.96</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -977,17 +977,17 @@
         <v>46218</v>
       </c>
       <c r="B29" t="n">
-        <v>89</v>
+        <v>1137</v>
       </c>
       <c r="C29" t="n">
-        <v>13148</v>
+        <v>8888</v>
       </c>
       <c r="D29" t="n">
-        <v>1883.74</v>
+        <v>952.95</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -996,17 +996,17 @@
         <v>46218</v>
       </c>
       <c r="B30" t="n">
-        <v>2211</v>
+        <v>325</v>
       </c>
       <c r="C30" t="n">
-        <v>874</v>
+        <v>8888</v>
       </c>
       <c r="D30" t="n">
-        <v>1526.94</v>
+        <v>399.62</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1015,17 +1015,17 @@
         <v>46218</v>
       </c>
       <c r="B31" t="n">
-        <v>559</v>
+        <v>664</v>
       </c>
       <c r="C31" t="n">
         <v>8888</v>
       </c>
       <c r="D31" t="n">
-        <v>859.92</v>
+        <v>682.3200000000001</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
         <v>46218</v>
       </c>
       <c r="B32" t="n">
-        <v>1063</v>
+        <v>945</v>
       </c>
       <c r="C32" t="n">
         <v>8888</v>
       </c>
       <c r="D32" t="n">
-        <v>4487.11</v>
+        <v>365.11</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>PEDIDO ELETRÔNICO</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
         <v>46218</v>
       </c>
       <c r="B33" t="n">
-        <v>2279</v>
+        <v>451</v>
       </c>
       <c r="C33" t="n">
-        <v>1139</v>
+        <v>8888</v>
       </c>
       <c r="D33" t="n">
-        <v>652.51</v>
+        <v>368.93</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1072,17 +1072,17 @@
         <v>46218</v>
       </c>
       <c r="B34" t="n">
-        <v>1299</v>
+        <v>1756</v>
       </c>
       <c r="C34" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D34" t="n">
-        <v>990.24</v>
+        <v>824.3200000000001</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1091,17 +1091,17 @@
         <v>46218</v>
       </c>
       <c r="B35" t="n">
-        <v>285</v>
+        <v>2631</v>
       </c>
       <c r="C35" t="n">
-        <v>8888</v>
+        <v>2853</v>
       </c>
       <c r="D35" t="n">
-        <v>3349.8</v>
+        <v>509.88</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1110,17 +1110,17 @@
         <v>46218</v>
       </c>
       <c r="B36" t="n">
-        <v>1983</v>
+        <v>2714</v>
       </c>
       <c r="C36" t="n">
-        <v>8888</v>
+        <v>519</v>
       </c>
       <c r="D36" t="n">
-        <v>2451.28</v>
+        <v>61939.22</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1129,17 +1129,17 @@
         <v>46218</v>
       </c>
       <c r="B37" t="n">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="C37" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D37" t="n">
-        <v>1540.55</v>
+        <v>4920.11</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1148,13 +1148,13 @@
         <v>46218</v>
       </c>
       <c r="B38" t="n">
-        <v>1063</v>
+        <v>1075</v>
       </c>
       <c r="C38" t="n">
         <v>8888</v>
       </c>
       <c r="D38" t="n">
-        <v>2549.86</v>
+        <v>11607.79</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1167,13 +1167,13 @@
         <v>46218</v>
       </c>
       <c r="B39" t="n">
-        <v>424</v>
+        <v>629</v>
       </c>
       <c r="C39" t="n">
         <v>8888</v>
       </c>
       <c r="D39" t="n">
-        <v>1035.17</v>
+        <v>9233.719999999999</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1186,17 +1186,17 @@
         <v>46218</v>
       </c>
       <c r="B40" t="n">
-        <v>675</v>
+        <v>1983</v>
       </c>
       <c r="C40" t="n">
-        <v>8888</v>
+        <v>841</v>
       </c>
       <c r="D40" t="n">
-        <v>616.73</v>
+        <v>105.6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1205,17 +1205,17 @@
         <v>46218</v>
       </c>
       <c r="B41" t="n">
-        <v>1993</v>
+        <v>1137</v>
       </c>
       <c r="C41" t="n">
         <v>8888</v>
       </c>
       <c r="D41" t="n">
-        <v>362.63</v>
+        <v>3578.51</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1224,17 +1224,17 @@
         <v>46218</v>
       </c>
       <c r="B42" t="n">
-        <v>1465</v>
+        <v>2651</v>
       </c>
       <c r="C42" t="n">
         <v>8888</v>
       </c>
       <c r="D42" t="n">
-        <v>2431.47</v>
+        <v>1296.58</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
         <v>46218</v>
       </c>
       <c r="B43" t="n">
-        <v>89</v>
+        <v>2709</v>
       </c>
       <c r="C43" t="n">
         <v>8888</v>
       </c>
       <c r="D43" t="n">
-        <v>479</v>
+        <v>547.6900000000001</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1262,13 +1262,13 @@
         <v>46218</v>
       </c>
       <c r="B44" t="n">
-        <v>1465</v>
+        <v>89</v>
       </c>
       <c r="C44" t="n">
-        <v>3403</v>
+        <v>13148</v>
       </c>
       <c r="D44" t="n">
-        <v>777.2</v>
+        <v>1883.74</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1281,17 +1281,17 @@
         <v>46218</v>
       </c>
       <c r="B45" t="n">
-        <v>1937</v>
+        <v>2709</v>
       </c>
       <c r="C45" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D45" t="n">
-        <v>833.52</v>
+        <v>390.19</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1300,13 +1300,13 @@
         <v>46218</v>
       </c>
       <c r="B46" t="n">
-        <v>360</v>
+        <v>2345</v>
       </c>
       <c r="C46" t="n">
         <v>8888</v>
       </c>
       <c r="D46" t="n">
-        <v>731.37</v>
+        <v>748.86</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1319,17 +1319,17 @@
         <v>46218</v>
       </c>
       <c r="B47" t="n">
-        <v>1063</v>
+        <v>1308</v>
       </c>
       <c r="C47" t="n">
         <v>8888</v>
       </c>
       <c r="D47" t="n">
-        <v>1113.08</v>
+        <v>276.16</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1338,17 @@
         <v>46218</v>
       </c>
       <c r="B48" t="n">
-        <v>1293</v>
+        <v>2211</v>
       </c>
       <c r="C48" t="n">
-        <v>8888</v>
+        <v>874</v>
       </c>
       <c r="D48" t="n">
-        <v>386.33</v>
+        <v>1526.94</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1357,17 +1357,17 @@
         <v>46218</v>
       </c>
       <c r="B49" t="n">
-        <v>2089</v>
+        <v>559</v>
       </c>
       <c r="C49" t="n">
-        <v>1533</v>
+        <v>8888</v>
       </c>
       <c r="D49" t="n">
-        <v>442.44</v>
+        <v>859.92</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1376,13 +1376,13 @@
         <v>46218</v>
       </c>
       <c r="B50" t="n">
-        <v>1007</v>
+        <v>1063</v>
       </c>
       <c r="C50" t="n">
         <v>8888</v>
       </c>
       <c r="D50" t="n">
-        <v>241.44</v>
+        <v>4487.11</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1395,17 +1395,17 @@
         <v>46218</v>
       </c>
       <c r="B51" t="n">
-        <v>1380</v>
+        <v>2279</v>
       </c>
       <c r="C51" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D51" t="n">
-        <v>520.2</v>
+        <v>652.51</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1414,17 +1414,17 @@
         <v>46218</v>
       </c>
       <c r="B52" t="n">
-        <v>1102</v>
+        <v>1299</v>
       </c>
       <c r="C52" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D52" t="n">
-        <v>349.4</v>
+        <v>1435.52</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1433,17 +1433,17 @@
         <v>46218</v>
       </c>
       <c r="B53" t="n">
-        <v>1075</v>
+        <v>1478</v>
       </c>
       <c r="C53" t="n">
-        <v>8888</v>
+        <v>675</v>
       </c>
       <c r="D53" t="n">
-        <v>2179.03</v>
+        <v>511.84</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1452,17 +1452,17 @@
         <v>46218</v>
       </c>
       <c r="B54" t="n">
-        <v>2245</v>
+        <v>285</v>
       </c>
       <c r="C54" t="n">
         <v>8888</v>
       </c>
       <c r="D54" t="n">
-        <v>361.58</v>
+        <v>3349.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1471,17 +1471,17 @@
         <v>46218</v>
       </c>
       <c r="B55" t="n">
-        <v>452</v>
+        <v>1983</v>
       </c>
       <c r="C55" t="n">
         <v>8888</v>
       </c>
       <c r="D55" t="n">
-        <v>608.78</v>
+        <v>2451.28</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1490,17 +1490,17 @@
         <v>46218</v>
       </c>
       <c r="B56" t="n">
-        <v>285</v>
+        <v>477</v>
       </c>
       <c r="C56" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D56" t="n">
-        <v>2090.81</v>
+        <v>1540.55</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1509,17 +1509,17 @@
         <v>46218</v>
       </c>
       <c r="B57" t="n">
-        <v>1102</v>
+        <v>1063</v>
       </c>
       <c r="C57" t="n">
         <v>8888</v>
       </c>
       <c r="D57" t="n">
-        <v>1119.32</v>
+        <v>2549.86</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1528,13 +1528,13 @@
         <v>46218</v>
       </c>
       <c r="B58" t="n">
-        <v>626</v>
+        <v>424</v>
       </c>
       <c r="C58" t="n">
         <v>8888</v>
       </c>
       <c r="D58" t="n">
-        <v>3520.98</v>
+        <v>1035.17</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -1547,17 +1547,17 @@
         <v>46218</v>
       </c>
       <c r="B59" t="n">
-        <v>1756</v>
+        <v>675</v>
       </c>
       <c r="C59" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D59" t="n">
-        <v>741.1799999999999</v>
+        <v>616.73</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1566,17 +1566,17 @@
         <v>46218</v>
       </c>
       <c r="B60" t="n">
-        <v>2651</v>
+        <v>1993</v>
       </c>
       <c r="C60" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D60" t="n">
-        <v>363.7</v>
+        <v>362.63</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1585,13 +1585,13 @@
         <v>46218</v>
       </c>
       <c r="B61" t="n">
-        <v>1064</v>
+        <v>1465</v>
       </c>
       <c r="C61" t="n">
         <v>8888</v>
       </c>
       <c r="D61" t="n">
-        <v>1274.3</v>
+        <v>3373.83</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -1604,17 +1604,17 @@
         <v>46218</v>
       </c>
       <c r="B62" t="n">
-        <v>2698</v>
+        <v>89</v>
       </c>
       <c r="C62" t="n">
         <v>8888</v>
       </c>
       <c r="D62" t="n">
-        <v>552.15</v>
+        <v>479</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
         <v>46218</v>
       </c>
       <c r="B63" t="n">
-        <v>629</v>
+        <v>2696</v>
       </c>
       <c r="C63" t="n">
-        <v>8888</v>
+        <v>1954</v>
       </c>
       <c r="D63" t="n">
-        <v>721.25</v>
+        <v>259.97</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1642,17 +1642,17 @@
         <v>46218</v>
       </c>
       <c r="B64" t="n">
-        <v>664</v>
+        <v>360</v>
       </c>
       <c r="C64" t="n">
         <v>8888</v>
       </c>
       <c r="D64" t="n">
-        <v>1595.68</v>
+        <v>2023.17</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1661,17 +1661,17 @@
         <v>46218</v>
       </c>
       <c r="B65" t="n">
-        <v>816</v>
+        <v>1465</v>
       </c>
       <c r="C65" t="n">
-        <v>8888</v>
+        <v>3403</v>
       </c>
       <c r="D65" t="n">
-        <v>438.24</v>
+        <v>777.2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1680,17 +1680,17 @@
         <v>46218</v>
       </c>
       <c r="B66" t="n">
-        <v>285</v>
+        <v>1937</v>
       </c>
       <c r="C66" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D66" t="n">
-        <v>364.99</v>
+        <v>833.52</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1699,17 +1699,17 @@
         <v>46218</v>
       </c>
       <c r="B67" t="n">
-        <v>2114</v>
+        <v>1293</v>
       </c>
       <c r="C67" t="n">
         <v>8888</v>
       </c>
       <c r="D67" t="n">
-        <v>1682.3</v>
+        <v>1607.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
         <v>46218</v>
       </c>
       <c r="B68" t="n">
-        <v>953</v>
+        <v>630</v>
       </c>
       <c r="C68" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D68" t="n">
-        <v>2618.89</v>
+        <v>1210.85</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1737,17 +1737,17 @@
         <v>46218</v>
       </c>
       <c r="B69" t="n">
-        <v>1102</v>
+        <v>2571</v>
       </c>
       <c r="C69" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D69" t="n">
-        <v>1771.61</v>
+        <v>268.53</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1756,17 +1756,17 @@
         <v>46218</v>
       </c>
       <c r="B70" t="n">
-        <v>619</v>
+        <v>1063</v>
       </c>
       <c r="C70" t="n">
         <v>8888</v>
       </c>
       <c r="D70" t="n">
-        <v>2021.67</v>
+        <v>1113.08</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1775,17 +1775,17 @@
         <v>46218</v>
       </c>
       <c r="B71" t="n">
-        <v>1465</v>
+        <v>1756</v>
       </c>
       <c r="C71" t="n">
         <v>8888</v>
       </c>
       <c r="D71" t="n">
-        <v>3504</v>
+        <v>1357.12</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1794,17 +1794,17 @@
         <v>46218</v>
       </c>
       <c r="B72" t="n">
-        <v>2767</v>
+        <v>569</v>
       </c>
       <c r="C72" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D72" t="n">
-        <v>466.12</v>
+        <v>4504.72</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1813,17 +1813,17 @@
         <v>46218</v>
       </c>
       <c r="B73" t="n">
-        <v>2245</v>
+        <v>2089</v>
       </c>
       <c r="C73" t="n">
-        <v>8888</v>
+        <v>1533</v>
       </c>
       <c r="D73" t="n">
-        <v>427.51</v>
+        <v>442.44</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1832,17 +1832,17 @@
         <v>46218</v>
       </c>
       <c r="B74" t="n">
-        <v>131</v>
+        <v>1007</v>
       </c>
       <c r="C74" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D74" t="n">
-        <v>299.37</v>
+        <v>241.44</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1851,13 +1851,13 @@
         <v>46218</v>
       </c>
       <c r="B75" t="n">
-        <v>1993</v>
+        <v>1380</v>
       </c>
       <c r="C75" t="n">
         <v>8888</v>
       </c>
       <c r="D75" t="n">
-        <v>1864.73</v>
+        <v>520.2</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -1870,17 +1870,17 @@
         <v>46218</v>
       </c>
       <c r="B76" t="n">
-        <v>451</v>
+        <v>1102</v>
       </c>
       <c r="C76" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D76" t="n">
-        <v>445.58</v>
+        <v>1137.04</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1889,17 +1889,17 @@
         <v>46218</v>
       </c>
       <c r="B77" t="n">
-        <v>2749</v>
+        <v>1075</v>
       </c>
       <c r="C77" t="n">
         <v>8888</v>
       </c>
       <c r="D77" t="n">
-        <v>1860.64</v>
+        <v>2179.03</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1908,13 +1908,13 @@
         <v>46218</v>
       </c>
       <c r="B78" t="n">
-        <v>1117</v>
+        <v>2245</v>
       </c>
       <c r="C78" t="n">
         <v>8888</v>
       </c>
       <c r="D78" t="n">
-        <v>342.2</v>
+        <v>361.58</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -1927,17 +1927,17 @@
         <v>46218</v>
       </c>
       <c r="B79" t="n">
-        <v>2491</v>
+        <v>2660</v>
       </c>
       <c r="C79" t="n">
         <v>8888</v>
       </c>
       <c r="D79" t="n">
-        <v>650.4299999999999</v>
+        <v>528.4299999999999</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1946,13 +1946,13 @@
         <v>46218</v>
       </c>
       <c r="B80" t="n">
-        <v>2782</v>
+        <v>452</v>
       </c>
       <c r="C80" t="n">
         <v>8888</v>
       </c>
       <c r="D80" t="n">
-        <v>1786.32</v>
+        <v>608.78</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -1965,13 +1965,13 @@
         <v>46218</v>
       </c>
       <c r="B81" t="n">
-        <v>483</v>
+        <v>1293</v>
       </c>
       <c r="C81" t="n">
-        <v>841</v>
+        <v>1281</v>
       </c>
       <c r="D81" t="n">
-        <v>1393.15</v>
+        <v>1780.93</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -1984,17 +1984,17 @@
         <v>46218</v>
       </c>
       <c r="B82" t="n">
-        <v>1478</v>
+        <v>525</v>
       </c>
       <c r="C82" t="n">
         <v>8888</v>
       </c>
       <c r="D82" t="n">
-        <v>459.57</v>
+        <v>4599.72</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2003,13 +2003,13 @@
         <v>46218</v>
       </c>
       <c r="B83" t="n">
-        <v>131</v>
+        <v>609</v>
       </c>
       <c r="C83" t="n">
         <v>8888</v>
       </c>
       <c r="D83" t="n">
-        <v>1369.91</v>
+        <v>886.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2022,17 +2022,17 @@
         <v>46218</v>
       </c>
       <c r="B84" t="n">
-        <v>2015</v>
+        <v>619</v>
       </c>
       <c r="C84" t="n">
         <v>8888</v>
       </c>
       <c r="D84" t="n">
-        <v>2599.69</v>
+        <v>2330.47</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2041,17 +2041,17 @@
         <v>46218</v>
       </c>
       <c r="B85" t="n">
-        <v>2109</v>
+        <v>285</v>
       </c>
       <c r="C85" t="n">
         <v>8888</v>
       </c>
       <c r="D85" t="n">
-        <v>2293.78</v>
+        <v>2090.81</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2060,17 +2060,17 @@
         <v>46218</v>
       </c>
       <c r="B86" t="n">
-        <v>1116</v>
+        <v>1102</v>
       </c>
       <c r="C86" t="n">
         <v>8888</v>
       </c>
       <c r="D86" t="n">
-        <v>2919.53</v>
+        <v>1119.32</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2079,17 +2079,17 @@
         <v>46218</v>
       </c>
       <c r="B87" t="n">
-        <v>2250</v>
+        <v>626</v>
       </c>
       <c r="C87" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D87" t="n">
-        <v>1573.32</v>
+        <v>5211.29</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2098,17 +2098,17 @@
         <v>46218</v>
       </c>
       <c r="B88" t="n">
-        <v>42</v>
+        <v>1137</v>
       </c>
       <c r="C88" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D88" t="n">
-        <v>79947.14999999999</v>
+        <v>1370.86</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2117,17 +2117,17 @@
         <v>46218</v>
       </c>
       <c r="B89" t="n">
-        <v>1993</v>
+        <v>1756</v>
       </c>
       <c r="C89" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D89" t="n">
-        <v>456.62</v>
+        <v>5078.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2136,15 +2136,908 @@
         <v>46218</v>
       </c>
       <c r="B90" t="n">
+        <v>2651</v>
+      </c>
+      <c r="C90" t="n">
+        <v>58</v>
+      </c>
+      <c r="D90" t="n">
+        <v>363.7</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B91" t="n">
+        <v>360</v>
+      </c>
+      <c r="C91" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1594.84</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B92" t="n">
+        <v>2582</v>
+      </c>
+      <c r="C92" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D92" t="n">
+        <v>379.33</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B93" t="n">
+        <v>1756</v>
+      </c>
+      <c r="C93" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D93" t="n">
+        <v>1715.26</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B94" t="n">
+        <v>1289</v>
+      </c>
+      <c r="C94" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D94" t="n">
+        <v>2396.98</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B95" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C95" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D95" t="n">
+        <v>315.69</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B96" t="n">
+        <v>1064</v>
+      </c>
+      <c r="C96" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1274.3</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B97" t="n">
+        <v>2698</v>
+      </c>
+      <c r="C97" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D97" t="n">
+        <v>552.15</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B98" t="n">
         <v>629</v>
       </c>
-      <c r="C90" t="n">
+      <c r="C98" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D98" t="n">
+        <v>721.25</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B99" t="n">
+        <v>2686</v>
+      </c>
+      <c r="C99" t="n">
+        <v>1929</v>
+      </c>
+      <c r="D99" t="n">
+        <v>521.79</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B100" t="n">
+        <v>2584</v>
+      </c>
+      <c r="C100" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D100" t="n">
+        <v>1852.83</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B101" t="n">
+        <v>2641</v>
+      </c>
+      <c r="C101" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D101" t="n">
+        <v>820</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B102" t="n">
+        <v>664</v>
+      </c>
+      <c r="C102" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1595.68</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B103" t="n">
+        <v>816</v>
+      </c>
+      <c r="C103" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D103" t="n">
+        <v>438.24</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B104" t="n">
+        <v>285</v>
+      </c>
+      <c r="C104" t="n">
+        <v>58</v>
+      </c>
+      <c r="D104" t="n">
+        <v>364.99</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B105" t="n">
+        <v>2114</v>
+      </c>
+      <c r="C105" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D105" t="n">
+        <v>1682.3</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B106" t="n">
+        <v>953</v>
+      </c>
+      <c r="C106" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D106" t="n">
+        <v>2618.89</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B107" t="n">
+        <v>1102</v>
+      </c>
+      <c r="C107" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D107" t="n">
+        <v>2344.41</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B108" t="n">
+        <v>619</v>
+      </c>
+      <c r="C108" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D108" t="n">
+        <v>2021.67</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B109" t="n">
+        <v>1465</v>
+      </c>
+      <c r="C109" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D109" t="n">
+        <v>3504</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B110" t="n">
+        <v>2767</v>
+      </c>
+      <c r="C110" t="n">
+        <v>1898</v>
+      </c>
+      <c r="D110" t="n">
+        <v>466.12</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B111" t="n">
+        <v>2245</v>
+      </c>
+      <c r="C111" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D111" t="n">
+        <v>427.51</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B112" t="n">
+        <v>2657</v>
+      </c>
+      <c r="C112" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D112" t="n">
+        <v>703.6799999999999</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B113" t="n">
+        <v>131</v>
+      </c>
+      <c r="C113" t="n">
+        <v>27</v>
+      </c>
+      <c r="D113" t="n">
+        <v>299.37</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B114" t="n">
+        <v>2692</v>
+      </c>
+      <c r="C114" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D114" t="n">
+        <v>731.28</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B115" t="n">
+        <v>1317</v>
+      </c>
+      <c r="C115" t="n">
+        <v>3179</v>
+      </c>
+      <c r="D115" t="n">
+        <v>991.6799999999999</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B116" t="n">
+        <v>1993</v>
+      </c>
+      <c r="C116" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D116" t="n">
+        <v>2875.39</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B117" t="n">
+        <v>1632</v>
+      </c>
+      <c r="C117" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D117" t="n">
+        <v>564.55</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B118" t="n">
+        <v>1890</v>
+      </c>
+      <c r="C118" t="n">
+        <v>3449</v>
+      </c>
+      <c r="D118" t="n">
+        <v>3063.24</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B119" t="n">
+        <v>451</v>
+      </c>
+      <c r="C119" t="n">
+        <v>3403</v>
+      </c>
+      <c r="D119" t="n">
+        <v>445.58</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B120" t="n">
+        <v>2749</v>
+      </c>
+      <c r="C120" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D120" t="n">
+        <v>1860.64</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B121" t="n">
+        <v>1117</v>
+      </c>
+      <c r="C121" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D121" t="n">
+        <v>342.2</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B122" t="n">
+        <v>1478</v>
+      </c>
+      <c r="C122" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D122" t="n">
+        <v>875.34</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B123" t="n">
+        <v>2491</v>
+      </c>
+      <c r="C123" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D123" t="n">
+        <v>650.4299999999999</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B124" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C124" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D124" t="n">
+        <v>4436.15</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B125" t="n">
+        <v>2782</v>
+      </c>
+      <c r="C125" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1786.32</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B126" t="n">
+        <v>483</v>
+      </c>
+      <c r="C126" t="n">
+        <v>841</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1393.15</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B127" t="n">
+        <v>2648</v>
+      </c>
+      <c r="C127" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1873.52</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B128" t="n">
+        <v>131</v>
+      </c>
+      <c r="C128" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D128" t="n">
+        <v>1369.91</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B129" t="n">
+        <v>2109</v>
+      </c>
+      <c r="C129" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D129" t="n">
+        <v>2293.78</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B130" t="n">
+        <v>1116</v>
+      </c>
+      <c r="C130" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D130" t="n">
+        <v>2919.53</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B131" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C131" t="n">
+        <v>27</v>
+      </c>
+      <c r="D131" t="n">
+        <v>1573.32</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B132" t="n">
+        <v>2698</v>
+      </c>
+      <c r="C132" t="n">
+        <v>874</v>
+      </c>
+      <c r="D132" t="n">
+        <v>1230.43</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B133" t="n">
+        <v>42</v>
+      </c>
+      <c r="C133" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D133" t="n">
+        <v>79947.14999999999</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B134" t="n">
+        <v>2716</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1929</v>
+      </c>
+      <c r="D134" t="n">
+        <v>750.4299999999999</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B135" t="n">
+        <v>2716</v>
+      </c>
+      <c r="C135" t="n">
+        <v>977</v>
+      </c>
+      <c r="D135" t="n">
+        <v>729.29</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B136" t="n">
+        <v>1993</v>
+      </c>
+      <c r="C136" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D136" t="n">
+        <v>456.62</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B137" t="n">
+        <v>629</v>
+      </c>
+      <c r="C137" t="n">
         <v>675</v>
       </c>
-      <c r="D90" t="n">
+      <c r="D137" t="n">
         <v>1054.76</v>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E137" t="inlineStr">
         <is>
           <t>TELEMARKETING</t>
         </is>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E137"/>
+  <dimension ref="A1:E189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,17 +464,17 @@
         <v>46218</v>
       </c>
       <c r="B2" t="n">
-        <v>1075</v>
+        <v>326</v>
       </c>
       <c r="C2" t="n">
-        <v>675</v>
+        <v>8888</v>
       </c>
       <c r="D2" t="n">
-        <v>638.4299999999999</v>
+        <v>312.98</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -483,17 +483,17 @@
         <v>46218</v>
       </c>
       <c r="B3" t="n">
-        <v>664</v>
+        <v>1075</v>
       </c>
       <c r="C3" t="n">
-        <v>8888</v>
+        <v>675</v>
       </c>
       <c r="D3" t="n">
-        <v>463.88</v>
+        <v>638.4299999999999</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -502,17 +502,17 @@
         <v>46218</v>
       </c>
       <c r="B4" t="n">
-        <v>1364</v>
+        <v>664</v>
       </c>
       <c r="C4" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D4" t="n">
-        <v>1300.54</v>
+        <v>463.88</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -521,17 +521,17 @@
         <v>46218</v>
       </c>
       <c r="B5" t="n">
-        <v>451</v>
+        <v>1364</v>
       </c>
       <c r="C5" t="n">
-        <v>8888</v>
+        <v>3403</v>
       </c>
       <c r="D5" t="n">
-        <v>1103.58</v>
+        <v>1300.54</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -540,17 +540,17 @@
         <v>46218</v>
       </c>
       <c r="B6" t="n">
-        <v>131</v>
+        <v>451</v>
       </c>
       <c r="C6" t="n">
         <v>8888</v>
       </c>
       <c r="D6" t="n">
-        <v>1469.86</v>
+        <v>1103.58</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -559,13 +559,13 @@
         <v>46218</v>
       </c>
       <c r="B7" t="n">
-        <v>2211</v>
+        <v>131</v>
       </c>
       <c r="C7" t="n">
         <v>8888</v>
       </c>
       <c r="D7" t="n">
-        <v>2190.93</v>
+        <v>7071.12</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -578,17 +578,17 @@
         <v>46218</v>
       </c>
       <c r="B8" t="n">
-        <v>2660</v>
+        <v>2015</v>
       </c>
       <c r="C8" t="n">
-        <v>8888</v>
+        <v>2571</v>
       </c>
       <c r="D8" t="n">
-        <v>875.61</v>
+        <v>714.53</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -597,17 +597,17 @@
         <v>46218</v>
       </c>
       <c r="B9" t="n">
-        <v>2651</v>
+        <v>1289</v>
       </c>
       <c r="C9" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D9" t="n">
-        <v>660.95</v>
+        <v>727.05</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -616,17 +616,17 @@
         <v>46218</v>
       </c>
       <c r="B10" t="n">
-        <v>2197</v>
+        <v>609</v>
       </c>
       <c r="C10" t="n">
-        <v>8888</v>
+        <v>3179</v>
       </c>
       <c r="D10" t="n">
-        <v>892.66</v>
+        <v>2603.16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -635,17 +635,17 @@
         <v>46218</v>
       </c>
       <c r="B11" t="n">
-        <v>609</v>
+        <v>2211</v>
       </c>
       <c r="C11" t="n">
-        <v>3179</v>
+        <v>8888</v>
       </c>
       <c r="D11" t="n">
-        <v>1611.48</v>
+        <v>2190.93</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -654,13 +654,13 @@
         <v>46218</v>
       </c>
       <c r="B12" t="n">
-        <v>2118</v>
+        <v>2660</v>
       </c>
       <c r="C12" t="n">
         <v>8888</v>
       </c>
       <c r="D12" t="n">
-        <v>452.46</v>
+        <v>875.61</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -673,17 +673,17 @@
         <v>46218</v>
       </c>
       <c r="B13" t="n">
-        <v>931</v>
+        <v>890</v>
       </c>
       <c r="C13" t="n">
-        <v>423</v>
+        <v>8888</v>
       </c>
       <c r="D13" t="n">
-        <v>492.34</v>
+        <v>1051.23</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -692,13 +692,13 @@
         <v>46218</v>
       </c>
       <c r="B14" t="n">
-        <v>525</v>
+        <v>2190</v>
       </c>
       <c r="C14" t="n">
         <v>8888</v>
       </c>
       <c r="D14" t="n">
-        <v>408.25</v>
+        <v>1307.13</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -711,17 +711,17 @@
         <v>46218</v>
       </c>
       <c r="B15" t="n">
-        <v>1808</v>
+        <v>2651</v>
       </c>
       <c r="C15" t="n">
         <v>8888</v>
       </c>
       <c r="D15" t="n">
-        <v>695.3200000000001</v>
+        <v>660.95</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -730,17 +730,17 @@
         <v>46218</v>
       </c>
       <c r="B16" t="n">
-        <v>949</v>
+        <v>2118</v>
       </c>
       <c r="C16" t="n">
-        <v>1134</v>
+        <v>8888</v>
       </c>
       <c r="D16" t="n">
-        <v>30.46</v>
+        <v>5535.71</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -749,13 +749,13 @@
         <v>46218</v>
       </c>
       <c r="B17" t="n">
-        <v>2499</v>
+        <v>2197</v>
       </c>
       <c r="C17" t="n">
         <v>8888</v>
       </c>
       <c r="D17" t="n">
-        <v>261.63</v>
+        <v>892.66</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -768,17 +768,17 @@
         <v>46218</v>
       </c>
       <c r="B18" t="n">
-        <v>58</v>
+        <v>1869</v>
       </c>
       <c r="C18" t="n">
         <v>8888</v>
       </c>
       <c r="D18" t="n">
-        <v>499.11</v>
+        <v>1263.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
         <v>46218</v>
       </c>
       <c r="B19" t="n">
-        <v>2245</v>
+        <v>2133</v>
       </c>
       <c r="C19" t="n">
-        <v>8888</v>
+        <v>691</v>
       </c>
       <c r="D19" t="n">
-        <v>2740.06</v>
+        <v>2058.93</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -806,17 +806,17 @@
         <v>46218</v>
       </c>
       <c r="B20" t="n">
-        <v>2383</v>
+        <v>452</v>
       </c>
       <c r="C20" t="n">
         <v>8888</v>
       </c>
       <c r="D20" t="n">
-        <v>7926.02</v>
+        <v>1832.74</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -825,17 +825,17 @@
         <v>46218</v>
       </c>
       <c r="B21" t="n">
-        <v>1117</v>
+        <v>2250</v>
       </c>
       <c r="C21" t="n">
-        <v>1139</v>
+        <v>8888</v>
       </c>
       <c r="D21" t="n">
-        <v>916.72</v>
+        <v>1686.37</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -844,17 +844,17 @@
         <v>46218</v>
       </c>
       <c r="B22" t="n">
-        <v>2279</v>
+        <v>931</v>
       </c>
       <c r="C22" t="n">
-        <v>8888</v>
+        <v>423</v>
       </c>
       <c r="D22" t="n">
-        <v>712.66</v>
+        <v>492.34</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -863,13 +863,13 @@
         <v>46218</v>
       </c>
       <c r="B23" t="n">
-        <v>535</v>
+        <v>951</v>
       </c>
       <c r="C23" t="n">
         <v>8888</v>
       </c>
       <c r="D23" t="n">
-        <v>3228.46</v>
+        <v>2171.08</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -882,13 +882,13 @@
         <v>46218</v>
       </c>
       <c r="B24" t="n">
-        <v>535</v>
+        <v>2695</v>
       </c>
       <c r="C24" t="n">
         <v>8888</v>
       </c>
       <c r="D24" t="n">
-        <v>1352.51</v>
+        <v>411.42</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -901,17 +901,17 @@
         <v>46218</v>
       </c>
       <c r="B25" t="n">
-        <v>2678</v>
+        <v>525</v>
       </c>
       <c r="C25" t="n">
-        <v>1312</v>
+        <v>8888</v>
       </c>
       <c r="D25" t="n">
-        <v>364.96</v>
+        <v>408.25</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -920,17 +920,17 @@
         <v>46218</v>
       </c>
       <c r="B26" t="n">
-        <v>438</v>
+        <v>1808</v>
       </c>
       <c r="C26" t="n">
         <v>8888</v>
       </c>
       <c r="D26" t="n">
-        <v>220.06</v>
+        <v>695.3200000000001</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -939,17 +939,17 @@
         <v>46218</v>
       </c>
       <c r="B27" t="n">
-        <v>1293</v>
+        <v>949</v>
       </c>
       <c r="C27" t="n">
-        <v>8888</v>
+        <v>1134</v>
       </c>
       <c r="D27" t="n">
-        <v>1388.12</v>
+        <v>30.46</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
         <v>46218</v>
       </c>
       <c r="B28" t="n">
-        <v>2279</v>
+        <v>2499</v>
       </c>
       <c r="C28" t="n">
         <v>8888</v>
       </c>
       <c r="D28" t="n">
-        <v>2753.96</v>
+        <v>261.63</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -977,13 +977,13 @@
         <v>46218</v>
       </c>
       <c r="B29" t="n">
-        <v>1137</v>
+        <v>58</v>
       </c>
       <c r="C29" t="n">
         <v>8888</v>
       </c>
       <c r="D29" t="n">
-        <v>952.95</v>
+        <v>499.11</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -996,17 +996,17 @@
         <v>46218</v>
       </c>
       <c r="B30" t="n">
-        <v>325</v>
+        <v>2245</v>
       </c>
       <c r="C30" t="n">
         <v>8888</v>
       </c>
       <c r="D30" t="n">
-        <v>399.62</v>
+        <v>2740.06</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1015,17 +1015,17 @@
         <v>46218</v>
       </c>
       <c r="B31" t="n">
-        <v>664</v>
+        <v>325</v>
       </c>
       <c r="C31" t="n">
         <v>8888</v>
       </c>
       <c r="D31" t="n">
-        <v>682.3200000000001</v>
+        <v>524.36</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
         <v>46218</v>
       </c>
       <c r="B32" t="n">
-        <v>945</v>
+        <v>2383</v>
       </c>
       <c r="C32" t="n">
         <v>8888</v>
       </c>
       <c r="D32" t="n">
-        <v>365.11</v>
+        <v>7926.02</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PEDIDO ELETRÔNICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
         <v>46218</v>
       </c>
       <c r="B33" t="n">
-        <v>451</v>
+        <v>1117</v>
       </c>
       <c r="C33" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D33" t="n">
-        <v>368.93</v>
+        <v>916.72</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1072,13 +1072,13 @@
         <v>46218</v>
       </c>
       <c r="B34" t="n">
-        <v>1756</v>
+        <v>2279</v>
       </c>
       <c r="C34" t="n">
         <v>8888</v>
       </c>
       <c r="D34" t="n">
-        <v>824.3200000000001</v>
+        <v>712.66</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1091,17 +1091,17 @@
         <v>46218</v>
       </c>
       <c r="B35" t="n">
-        <v>2631</v>
+        <v>535</v>
       </c>
       <c r="C35" t="n">
-        <v>2853</v>
+        <v>8888</v>
       </c>
       <c r="D35" t="n">
-        <v>509.88</v>
+        <v>4810</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1110,17 +1110,17 @@
         <v>46218</v>
       </c>
       <c r="B36" t="n">
-        <v>2714</v>
+        <v>535</v>
       </c>
       <c r="C36" t="n">
-        <v>519</v>
+        <v>8888</v>
       </c>
       <c r="D36" t="n">
-        <v>61939.22</v>
+        <v>1352.51</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1129,17 +1129,17 @@
         <v>46218</v>
       </c>
       <c r="B37" t="n">
-        <v>483</v>
+        <v>2678</v>
       </c>
       <c r="C37" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D37" t="n">
-        <v>4920.11</v>
+        <v>364.96</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1148,13 +1148,13 @@
         <v>46218</v>
       </c>
       <c r="B38" t="n">
-        <v>1075</v>
+        <v>2345</v>
       </c>
       <c r="C38" t="n">
         <v>8888</v>
       </c>
       <c r="D38" t="n">
-        <v>11607.79</v>
+        <v>863.16</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1167,17 +1167,17 @@
         <v>46218</v>
       </c>
       <c r="B39" t="n">
-        <v>629</v>
+        <v>438</v>
       </c>
       <c r="C39" t="n">
         <v>8888</v>
       </c>
       <c r="D39" t="n">
-        <v>9233.719999999999</v>
+        <v>220.06</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1186,13 +1186,13 @@
         <v>46218</v>
       </c>
       <c r="B40" t="n">
-        <v>1983</v>
+        <v>353</v>
       </c>
       <c r="C40" t="n">
-        <v>841</v>
+        <v>3179</v>
       </c>
       <c r="D40" t="n">
-        <v>105.6</v>
+        <v>495.84</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1205,13 +1205,13 @@
         <v>46218</v>
       </c>
       <c r="B41" t="n">
-        <v>1137</v>
+        <v>1293</v>
       </c>
       <c r="C41" t="n">
         <v>8888</v>
       </c>
       <c r="D41" t="n">
-        <v>3578.51</v>
+        <v>3129.07</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1224,17 +1224,17 @@
         <v>46218</v>
       </c>
       <c r="B42" t="n">
-        <v>2651</v>
+        <v>2279</v>
       </c>
       <c r="C42" t="n">
         <v>8888</v>
       </c>
       <c r="D42" t="n">
-        <v>1296.58</v>
+        <v>2753.96</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
         <v>46218</v>
       </c>
       <c r="B43" t="n">
-        <v>2709</v>
+        <v>1137</v>
       </c>
       <c r="C43" t="n">
         <v>8888</v>
       </c>
       <c r="D43" t="n">
-        <v>547.6900000000001</v>
+        <v>1437.44</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1262,13 +1262,13 @@
         <v>46218</v>
       </c>
       <c r="B44" t="n">
-        <v>89</v>
+        <v>2793</v>
       </c>
       <c r="C44" t="n">
-        <v>13148</v>
+        <v>977</v>
       </c>
       <c r="D44" t="n">
-        <v>1883.74</v>
+        <v>695.72</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1281,17 +1281,17 @@
         <v>46218</v>
       </c>
       <c r="B45" t="n">
-        <v>2709</v>
+        <v>945</v>
       </c>
       <c r="C45" t="n">
-        <v>2220</v>
+        <v>8888</v>
       </c>
       <c r="D45" t="n">
-        <v>390.19</v>
+        <v>1934.84</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>PEDIDO ELETRÔNICO</t>
         </is>
       </c>
     </row>
@@ -1300,17 +1300,17 @@
         <v>46218</v>
       </c>
       <c r="B46" t="n">
-        <v>2345</v>
+        <v>374</v>
       </c>
       <c r="C46" t="n">
         <v>8888</v>
       </c>
       <c r="D46" t="n">
-        <v>748.86</v>
+        <v>22.62</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1319,13 +1319,13 @@
         <v>46218</v>
       </c>
       <c r="B47" t="n">
-        <v>1308</v>
+        <v>664</v>
       </c>
       <c r="C47" t="n">
         <v>8888</v>
       </c>
       <c r="D47" t="n">
-        <v>276.16</v>
+        <v>1510.56</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1338,17 +1338,17 @@
         <v>46218</v>
       </c>
       <c r="B48" t="n">
-        <v>2211</v>
+        <v>703</v>
       </c>
       <c r="C48" t="n">
-        <v>874</v>
+        <v>8888</v>
       </c>
       <c r="D48" t="n">
-        <v>1526.94</v>
+        <v>12155.46</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1357,17 +1357,17 @@
         <v>46218</v>
       </c>
       <c r="B49" t="n">
-        <v>559</v>
+        <v>1937</v>
       </c>
       <c r="C49" t="n">
         <v>8888</v>
       </c>
       <c r="D49" t="n">
-        <v>859.92</v>
+        <v>1032.73</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1376,13 +1376,13 @@
         <v>46218</v>
       </c>
       <c r="B50" t="n">
-        <v>1063</v>
+        <v>451</v>
       </c>
       <c r="C50" t="n">
         <v>8888</v>
       </c>
       <c r="D50" t="n">
-        <v>4487.11</v>
+        <v>368.93</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1395,17 +1395,17 @@
         <v>46218</v>
       </c>
       <c r="B51" t="n">
-        <v>2279</v>
+        <v>1756</v>
       </c>
       <c r="C51" t="n">
-        <v>1139</v>
+        <v>8888</v>
       </c>
       <c r="D51" t="n">
-        <v>652.51</v>
+        <v>996.17</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1414,17 +1414,17 @@
         <v>46218</v>
       </c>
       <c r="B52" t="n">
-        <v>1299</v>
+        <v>1956</v>
       </c>
       <c r="C52" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D52" t="n">
-        <v>1435.52</v>
+        <v>4557.34</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1433,17 +1433,17 @@
         <v>46218</v>
       </c>
       <c r="B53" t="n">
-        <v>1478</v>
+        <v>925</v>
       </c>
       <c r="C53" t="n">
-        <v>675</v>
+        <v>8888</v>
       </c>
       <c r="D53" t="n">
-        <v>511.84</v>
+        <v>651.59</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1452,17 +1452,17 @@
         <v>46218</v>
       </c>
       <c r="B54" t="n">
-        <v>285</v>
+        <v>2631</v>
       </c>
       <c r="C54" t="n">
-        <v>8888</v>
+        <v>2853</v>
       </c>
       <c r="D54" t="n">
-        <v>3349.8</v>
+        <v>509.88</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1471,13 +1471,13 @@
         <v>46218</v>
       </c>
       <c r="B55" t="n">
-        <v>1983</v>
+        <v>2648</v>
       </c>
       <c r="C55" t="n">
         <v>8888</v>
       </c>
       <c r="D55" t="n">
-        <v>2451.28</v>
+        <v>1594.42</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -1490,13 +1490,13 @@
         <v>46218</v>
       </c>
       <c r="B56" t="n">
-        <v>477</v>
+        <v>2714</v>
       </c>
       <c r="C56" t="n">
-        <v>58</v>
+        <v>519</v>
       </c>
       <c r="D56" t="n">
-        <v>1540.55</v>
+        <v>61939.22</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -1509,17 +1509,17 @@
         <v>46218</v>
       </c>
       <c r="B57" t="n">
-        <v>1063</v>
+        <v>483</v>
       </c>
       <c r="C57" t="n">
         <v>8888</v>
       </c>
       <c r="D57" t="n">
-        <v>2549.86</v>
+        <v>6625.87</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1528,13 +1528,13 @@
         <v>46218</v>
       </c>
       <c r="B58" t="n">
-        <v>424</v>
+        <v>1075</v>
       </c>
       <c r="C58" t="n">
         <v>8888</v>
       </c>
       <c r="D58" t="n">
-        <v>1035.17</v>
+        <v>11607.79</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -1547,17 +1547,17 @@
         <v>46218</v>
       </c>
       <c r="B59" t="n">
-        <v>675</v>
+        <v>629</v>
       </c>
       <c r="C59" t="n">
         <v>8888</v>
       </c>
       <c r="D59" t="n">
-        <v>616.73</v>
+        <v>9233.719999999999</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1566,17 +1566,17 @@
         <v>46218</v>
       </c>
       <c r="B60" t="n">
-        <v>1993</v>
+        <v>1983</v>
       </c>
       <c r="C60" t="n">
-        <v>8888</v>
+        <v>841</v>
       </c>
       <c r="D60" t="n">
-        <v>362.63</v>
+        <v>243.92</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1585,13 +1585,13 @@
         <v>46218</v>
       </c>
       <c r="B61" t="n">
-        <v>1465</v>
+        <v>1137</v>
       </c>
       <c r="C61" t="n">
         <v>8888</v>
       </c>
       <c r="D61" t="n">
-        <v>3373.83</v>
+        <v>3578.51</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -1604,13 +1604,13 @@
         <v>46218</v>
       </c>
       <c r="B62" t="n">
-        <v>89</v>
+        <v>2651</v>
       </c>
       <c r="C62" t="n">
         <v>8888</v>
       </c>
       <c r="D62" t="n">
-        <v>479</v>
+        <v>1296.58</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -1623,13 +1623,13 @@
         <v>46218</v>
       </c>
       <c r="B63" t="n">
-        <v>2696</v>
+        <v>1956</v>
       </c>
       <c r="C63" t="n">
-        <v>1954</v>
+        <v>423</v>
       </c>
       <c r="D63" t="n">
-        <v>259.97</v>
+        <v>455.37</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -1642,13 +1642,13 @@
         <v>46218</v>
       </c>
       <c r="B64" t="n">
-        <v>360</v>
+        <v>2709</v>
       </c>
       <c r="C64" t="n">
         <v>8888</v>
       </c>
       <c r="D64" t="n">
-        <v>2023.17</v>
+        <v>547.6900000000001</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -1661,17 +1661,17 @@
         <v>46218</v>
       </c>
       <c r="B65" t="n">
-        <v>1465</v>
+        <v>2026</v>
       </c>
       <c r="C65" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D65" t="n">
-        <v>777.2</v>
+        <v>2237.62</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1680,17 +1680,17 @@
         <v>46218</v>
       </c>
       <c r="B66" t="n">
-        <v>1937</v>
+        <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>8888</v>
+        <v>13148</v>
       </c>
       <c r="D66" t="n">
-        <v>833.52</v>
+        <v>1883.74</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1699,17 +1699,17 @@
         <v>46218</v>
       </c>
       <c r="B67" t="n">
-        <v>1293</v>
+        <v>2709</v>
       </c>
       <c r="C67" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D67" t="n">
-        <v>1607.2</v>
+        <v>390.19</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
         <v>46218</v>
       </c>
       <c r="B68" t="n">
-        <v>630</v>
+        <v>2345</v>
       </c>
       <c r="C68" t="n">
-        <v>1929</v>
+        <v>8888</v>
       </c>
       <c r="D68" t="n">
-        <v>1210.85</v>
+        <v>748.86</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1737,17 +1737,17 @@
         <v>46218</v>
       </c>
       <c r="B69" t="n">
-        <v>2571</v>
+        <v>1308</v>
       </c>
       <c r="C69" t="n">
-        <v>1312</v>
+        <v>8888</v>
       </c>
       <c r="D69" t="n">
-        <v>268.53</v>
+        <v>276.16</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1756,13 +1756,13 @@
         <v>46218</v>
       </c>
       <c r="B70" t="n">
-        <v>1063</v>
+        <v>2308</v>
       </c>
       <c r="C70" t="n">
         <v>8888</v>
       </c>
       <c r="D70" t="n">
-        <v>1113.08</v>
+        <v>488.69</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -1775,17 +1775,17 @@
         <v>46218</v>
       </c>
       <c r="B71" t="n">
-        <v>1756</v>
+        <v>360</v>
       </c>
       <c r="C71" t="n">
-        <v>8888</v>
+        <v>546</v>
       </c>
       <c r="D71" t="n">
-        <v>1357.12</v>
+        <v>709.75</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1794,17 +1794,17 @@
         <v>46218</v>
       </c>
       <c r="B72" t="n">
-        <v>569</v>
+        <v>2211</v>
       </c>
       <c r="C72" t="n">
-        <v>8888</v>
+        <v>874</v>
       </c>
       <c r="D72" t="n">
-        <v>4504.72</v>
+        <v>1526.94</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1813,17 +1813,17 @@
         <v>46218</v>
       </c>
       <c r="B73" t="n">
-        <v>2089</v>
+        <v>559</v>
       </c>
       <c r="C73" t="n">
-        <v>1533</v>
+        <v>8888</v>
       </c>
       <c r="D73" t="n">
-        <v>442.44</v>
+        <v>859.92</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1832,17 +1832,17 @@
         <v>46218</v>
       </c>
       <c r="B74" t="n">
-        <v>1007</v>
+        <v>569</v>
       </c>
       <c r="C74" t="n">
         <v>8888</v>
       </c>
       <c r="D74" t="n">
-        <v>241.44</v>
+        <v>673.01</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1851,17 +1851,17 @@
         <v>46218</v>
       </c>
       <c r="B75" t="n">
-        <v>1380</v>
+        <v>890</v>
       </c>
       <c r="C75" t="n">
         <v>8888</v>
       </c>
       <c r="D75" t="n">
-        <v>520.2</v>
+        <v>387.2</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1870,13 +1870,13 @@
         <v>46218</v>
       </c>
       <c r="B76" t="n">
-        <v>1102</v>
+        <v>1063</v>
       </c>
       <c r="C76" t="n">
         <v>8888</v>
       </c>
       <c r="D76" t="n">
-        <v>1137.04</v>
+        <v>4487.11</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -1889,17 +1889,17 @@
         <v>46218</v>
       </c>
       <c r="B77" t="n">
-        <v>1075</v>
+        <v>2279</v>
       </c>
       <c r="C77" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D77" t="n">
-        <v>2179.03</v>
+        <v>652.51</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1908,17 +1908,17 @@
         <v>46218</v>
       </c>
       <c r="B78" t="n">
-        <v>2245</v>
+        <v>1299</v>
       </c>
       <c r="C78" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D78" t="n">
-        <v>361.58</v>
+        <v>1435.52</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1927,17 +1927,17 @@
         <v>46218</v>
       </c>
       <c r="B79" t="n">
-        <v>2660</v>
+        <v>1478</v>
       </c>
       <c r="C79" t="n">
-        <v>8888</v>
+        <v>675</v>
       </c>
       <c r="D79" t="n">
-        <v>528.4299999999999</v>
+        <v>1600.01</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1946,17 +1946,17 @@
         <v>46218</v>
       </c>
       <c r="B80" t="n">
-        <v>452</v>
+        <v>285</v>
       </c>
       <c r="C80" t="n">
         <v>8888</v>
       </c>
       <c r="D80" t="n">
-        <v>608.78</v>
+        <v>3349.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1965,17 +1965,17 @@
         <v>46218</v>
       </c>
       <c r="B81" t="n">
-        <v>1293</v>
+        <v>1983</v>
       </c>
       <c r="C81" t="n">
-        <v>1281</v>
+        <v>8888</v>
       </c>
       <c r="D81" t="n">
-        <v>1780.93</v>
+        <v>2451.28</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1984,17 +1984,17 @@
         <v>46218</v>
       </c>
       <c r="B82" t="n">
-        <v>525</v>
+        <v>477</v>
       </c>
       <c r="C82" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D82" t="n">
-        <v>4599.72</v>
+        <v>1540.55</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2003,13 +2003,13 @@
         <v>46218</v>
       </c>
       <c r="B83" t="n">
-        <v>609</v>
+        <v>1063</v>
       </c>
       <c r="C83" t="n">
         <v>8888</v>
       </c>
       <c r="D83" t="n">
-        <v>886.1</v>
+        <v>2549.86</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2022,17 +2022,17 @@
         <v>46218</v>
       </c>
       <c r="B84" t="n">
-        <v>619</v>
+        <v>424</v>
       </c>
       <c r="C84" t="n">
         <v>8888</v>
       </c>
       <c r="D84" t="n">
-        <v>2330.47</v>
+        <v>1035.17</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2041,17 +2041,17 @@
         <v>46218</v>
       </c>
       <c r="B85" t="n">
-        <v>285</v>
+        <v>675</v>
       </c>
       <c r="C85" t="n">
         <v>8888</v>
       </c>
       <c r="D85" t="n">
-        <v>2090.81</v>
+        <v>616.73</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2060,17 +2060,17 @@
         <v>46218</v>
       </c>
       <c r="B86" t="n">
-        <v>1102</v>
+        <v>2768</v>
       </c>
       <c r="C86" t="n">
         <v>8888</v>
       </c>
       <c r="D86" t="n">
-        <v>1119.32</v>
+        <v>4245.73</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2079,17 +2079,17 @@
         <v>46218</v>
       </c>
       <c r="B87" t="n">
-        <v>626</v>
+        <v>1993</v>
       </c>
       <c r="C87" t="n">
         <v>8888</v>
       </c>
       <c r="D87" t="n">
-        <v>5211.29</v>
+        <v>362.63</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2098,17 +2098,17 @@
         <v>46218</v>
       </c>
       <c r="B88" t="n">
-        <v>1137</v>
+        <v>1465</v>
       </c>
       <c r="C88" t="n">
-        <v>2220</v>
+        <v>8888</v>
       </c>
       <c r="D88" t="n">
-        <v>1370.86</v>
+        <v>3373.83</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2117,17 +2117,17 @@
         <v>46218</v>
       </c>
       <c r="B89" t="n">
-        <v>1756</v>
+        <v>89</v>
       </c>
       <c r="C89" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D89" t="n">
-        <v>5078.1</v>
+        <v>479</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2136,17 +2136,17 @@
         <v>46218</v>
       </c>
       <c r="B90" t="n">
-        <v>2651</v>
+        <v>595</v>
       </c>
       <c r="C90" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D90" t="n">
-        <v>363.7</v>
+        <v>18084.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2155,17 +2155,17 @@
         <v>46218</v>
       </c>
       <c r="B91" t="n">
-        <v>360</v>
+        <v>2696</v>
       </c>
       <c r="C91" t="n">
-        <v>8888</v>
+        <v>1954</v>
       </c>
       <c r="D91" t="n">
-        <v>1594.84</v>
+        <v>259.97</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2174,17 +2174,17 @@
         <v>46218</v>
       </c>
       <c r="B92" t="n">
-        <v>2582</v>
+        <v>360</v>
       </c>
       <c r="C92" t="n">
         <v>8888</v>
       </c>
       <c r="D92" t="n">
-        <v>379.33</v>
+        <v>2023.17</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2193,17 +2193,17 @@
         <v>46218</v>
       </c>
       <c r="B93" t="n">
-        <v>1756</v>
+        <v>1465</v>
       </c>
       <c r="C93" t="n">
-        <v>8888</v>
+        <v>3403</v>
       </c>
       <c r="D93" t="n">
-        <v>1715.26</v>
+        <v>777.2</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2212,17 +2212,17 @@
         <v>46218</v>
       </c>
       <c r="B94" t="n">
-        <v>1289</v>
+        <v>947</v>
       </c>
       <c r="C94" t="n">
         <v>8888</v>
       </c>
       <c r="D94" t="n">
-        <v>2396.98</v>
+        <v>2087.97</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>PEDIDO ELETRÔNICO</t>
         </is>
       </c>
     </row>
@@ -2231,13 +2231,13 @@
         <v>46218</v>
       </c>
       <c r="B95" t="n">
-        <v>2015</v>
+        <v>2178</v>
       </c>
       <c r="C95" t="n">
         <v>8888</v>
       </c>
       <c r="D95" t="n">
-        <v>315.69</v>
+        <v>619.92</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -2250,17 +2250,17 @@
         <v>46218</v>
       </c>
       <c r="B96" t="n">
-        <v>1064</v>
+        <v>630</v>
       </c>
       <c r="C96" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D96" t="n">
-        <v>1274.3</v>
+        <v>1801.63</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2269,17 +2269,17 @@
         <v>46218</v>
       </c>
       <c r="B97" t="n">
-        <v>2698</v>
+        <v>1937</v>
       </c>
       <c r="C97" t="n">
         <v>8888</v>
       </c>
       <c r="D97" t="n">
-        <v>552.15</v>
+        <v>2132.95</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2288,13 +2288,13 @@
         <v>46218</v>
       </c>
       <c r="B98" t="n">
-        <v>629</v>
+        <v>2577</v>
       </c>
       <c r="C98" t="n">
         <v>8888</v>
       </c>
       <c r="D98" t="n">
-        <v>721.25</v>
+        <v>1647.08</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -2307,17 +2307,17 @@
         <v>46218</v>
       </c>
       <c r="B99" t="n">
-        <v>2686</v>
+        <v>1293</v>
       </c>
       <c r="C99" t="n">
-        <v>1929</v>
+        <v>8888</v>
       </c>
       <c r="D99" t="n">
-        <v>521.79</v>
+        <v>1607.2</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2326,17 +2326,17 @@
         <v>46218</v>
       </c>
       <c r="B100" t="n">
-        <v>2584</v>
+        <v>1317</v>
       </c>
       <c r="C100" t="n">
         <v>8888</v>
       </c>
       <c r="D100" t="n">
-        <v>1852.83</v>
+        <v>907.72</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2345,17 +2345,17 @@
         <v>46218</v>
       </c>
       <c r="B101" t="n">
-        <v>2641</v>
+        <v>2571</v>
       </c>
       <c r="C101" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D101" t="n">
-        <v>820</v>
+        <v>268.53</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2364,13 +2364,13 @@
         <v>46218</v>
       </c>
       <c r="B102" t="n">
-        <v>664</v>
+        <v>1937</v>
       </c>
       <c r="C102" t="n">
         <v>8888</v>
       </c>
       <c r="D102" t="n">
-        <v>1595.68</v>
+        <v>1803.32</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -2383,17 +2383,17 @@
         <v>46218</v>
       </c>
       <c r="B103" t="n">
-        <v>816</v>
+        <v>1063</v>
       </c>
       <c r="C103" t="n">
         <v>8888</v>
       </c>
       <c r="D103" t="n">
-        <v>438.24</v>
+        <v>1113.08</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2402,17 +2402,17 @@
         <v>46218</v>
       </c>
       <c r="B104" t="n">
-        <v>285</v>
+        <v>1906</v>
       </c>
       <c r="C104" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D104" t="n">
-        <v>364.99</v>
+        <v>990.22</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2421,13 +2421,13 @@
         <v>46218</v>
       </c>
       <c r="B105" t="n">
-        <v>2114</v>
+        <v>1756</v>
       </c>
       <c r="C105" t="n">
         <v>8888</v>
       </c>
       <c r="D105" t="n">
-        <v>1682.3</v>
+        <v>1357.12</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -2440,17 +2440,17 @@
         <v>46218</v>
       </c>
       <c r="B106" t="n">
-        <v>953</v>
+        <v>20</v>
       </c>
       <c r="C106" t="n">
         <v>8888</v>
       </c>
       <c r="D106" t="n">
-        <v>2618.89</v>
+        <v>276.64</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2459,13 +2459,13 @@
         <v>46218</v>
       </c>
       <c r="B107" t="n">
-        <v>1102</v>
+        <v>477</v>
       </c>
       <c r="C107" t="n">
         <v>8888</v>
       </c>
       <c r="D107" t="n">
-        <v>2344.41</v>
+        <v>372.69</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -2478,17 +2478,17 @@
         <v>46218</v>
       </c>
       <c r="B108" t="n">
-        <v>619</v>
+        <v>477</v>
       </c>
       <c r="C108" t="n">
         <v>8888</v>
       </c>
       <c r="D108" t="n">
-        <v>2021.67</v>
+        <v>707.52</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2497,17 +2497,17 @@
         <v>46218</v>
       </c>
       <c r="B109" t="n">
-        <v>1465</v>
+        <v>2660</v>
       </c>
       <c r="C109" t="n">
         <v>8888</v>
       </c>
       <c r="D109" t="n">
-        <v>3504</v>
+        <v>2684.97</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2516,17 +2516,17 @@
         <v>46218</v>
       </c>
       <c r="B110" t="n">
-        <v>2767</v>
+        <v>569</v>
       </c>
       <c r="C110" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D110" t="n">
-        <v>466.12</v>
+        <v>18512.6</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2535,17 +2535,17 @@
         <v>46218</v>
       </c>
       <c r="B111" t="n">
-        <v>2245</v>
+        <v>2089</v>
       </c>
       <c r="C111" t="n">
-        <v>8888</v>
+        <v>1533</v>
       </c>
       <c r="D111" t="n">
-        <v>427.51</v>
+        <v>969.24</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2554,13 +2554,13 @@
         <v>46218</v>
       </c>
       <c r="B112" t="n">
-        <v>2657</v>
+        <v>1007</v>
       </c>
       <c r="C112" t="n">
         <v>8888</v>
       </c>
       <c r="D112" t="n">
-        <v>703.6799999999999</v>
+        <v>241.44</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -2573,17 +2573,17 @@
         <v>46218</v>
       </c>
       <c r="B113" t="n">
-        <v>131</v>
+        <v>1380</v>
       </c>
       <c r="C113" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D113" t="n">
-        <v>299.37</v>
+        <v>520.2</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2592,17 +2592,17 @@
         <v>46218</v>
       </c>
       <c r="B114" t="n">
-        <v>2692</v>
+        <v>1102</v>
       </c>
       <c r="C114" t="n">
         <v>8888</v>
       </c>
       <c r="D114" t="n">
-        <v>731.28</v>
+        <v>1137.04</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2611,17 +2611,17 @@
         <v>46218</v>
       </c>
       <c r="B115" t="n">
-        <v>1317</v>
+        <v>1075</v>
       </c>
       <c r="C115" t="n">
-        <v>3179</v>
+        <v>8888</v>
       </c>
       <c r="D115" t="n">
-        <v>991.6799999999999</v>
+        <v>2179.03</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2630,17 +2630,17 @@
         <v>46218</v>
       </c>
       <c r="B116" t="n">
-        <v>1993</v>
+        <v>2245</v>
       </c>
       <c r="C116" t="n">
         <v>8888</v>
       </c>
       <c r="D116" t="n">
-        <v>2875.39</v>
+        <v>361.58</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2649,13 +2649,13 @@
         <v>46218</v>
       </c>
       <c r="B117" t="n">
-        <v>1632</v>
+        <v>132</v>
       </c>
       <c r="C117" t="n">
         <v>8888</v>
       </c>
       <c r="D117" t="n">
-        <v>564.55</v>
+        <v>6522.92</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -2668,17 +2668,17 @@
         <v>46218</v>
       </c>
       <c r="B118" t="n">
-        <v>1890</v>
+        <v>452</v>
       </c>
       <c r="C118" t="n">
-        <v>3449</v>
+        <v>8888</v>
       </c>
       <c r="D118" t="n">
-        <v>3063.24</v>
+        <v>608.78</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2687,13 +2687,13 @@
         <v>46218</v>
       </c>
       <c r="B119" t="n">
-        <v>451</v>
+        <v>1293</v>
       </c>
       <c r="C119" t="n">
-        <v>3403</v>
+        <v>1281</v>
       </c>
       <c r="D119" t="n">
-        <v>445.58</v>
+        <v>1780.93</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -2706,17 +2706,17 @@
         <v>46218</v>
       </c>
       <c r="B120" t="n">
-        <v>2749</v>
+        <v>525</v>
       </c>
       <c r="C120" t="n">
         <v>8888</v>
       </c>
       <c r="D120" t="n">
-        <v>1860.64</v>
+        <v>5658.57</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2725,17 +2725,17 @@
         <v>46218</v>
       </c>
       <c r="B121" t="n">
-        <v>1117</v>
+        <v>609</v>
       </c>
       <c r="C121" t="n">
         <v>8888</v>
       </c>
       <c r="D121" t="n">
-        <v>342.2</v>
+        <v>886.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2744,17 +2744,17 @@
         <v>46218</v>
       </c>
       <c r="B122" t="n">
-        <v>1478</v>
+        <v>619</v>
       </c>
       <c r="C122" t="n">
         <v>8888</v>
       </c>
       <c r="D122" t="n">
-        <v>875.34</v>
+        <v>2330.47</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2763,13 +2763,13 @@
         <v>46218</v>
       </c>
       <c r="B123" t="n">
-        <v>2491</v>
+        <v>58</v>
       </c>
       <c r="C123" t="n">
         <v>8888</v>
       </c>
       <c r="D123" t="n">
-        <v>650.4299999999999</v>
+        <v>1123.87</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -2782,17 +2782,17 @@
         <v>46218</v>
       </c>
       <c r="B124" t="n">
-        <v>2015</v>
+        <v>358</v>
       </c>
       <c r="C124" t="n">
         <v>8888</v>
       </c>
       <c r="D124" t="n">
-        <v>4436.15</v>
+        <v>1675.95</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2801,13 +2801,13 @@
         <v>46218</v>
       </c>
       <c r="B125" t="n">
-        <v>2782</v>
+        <v>2431</v>
       </c>
       <c r="C125" t="n">
         <v>8888</v>
       </c>
       <c r="D125" t="n">
-        <v>1786.32</v>
+        <v>266.89</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -2820,17 +2820,17 @@
         <v>46218</v>
       </c>
       <c r="B126" t="n">
-        <v>483</v>
+        <v>285</v>
       </c>
       <c r="C126" t="n">
-        <v>841</v>
+        <v>8888</v>
       </c>
       <c r="D126" t="n">
-        <v>1393.15</v>
+        <v>2090.81</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2839,17 +2839,17 @@
         <v>46218</v>
       </c>
       <c r="B127" t="n">
-        <v>2648</v>
+        <v>1102</v>
       </c>
       <c r="C127" t="n">
         <v>8888</v>
       </c>
       <c r="D127" t="n">
-        <v>1873.52</v>
+        <v>1119.32</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2858,13 +2858,13 @@
         <v>46218</v>
       </c>
       <c r="B128" t="n">
-        <v>131</v>
+        <v>626</v>
       </c>
       <c r="C128" t="n">
         <v>8888</v>
       </c>
       <c r="D128" t="n">
-        <v>1369.91</v>
+        <v>11337.75</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -2877,17 +2877,17 @@
         <v>46218</v>
       </c>
       <c r="B129" t="n">
-        <v>2109</v>
+        <v>1137</v>
       </c>
       <c r="C129" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D129" t="n">
-        <v>2293.78</v>
+        <v>1370.86</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2896,17 +2896,17 @@
         <v>46218</v>
       </c>
       <c r="B130" t="n">
-        <v>1116</v>
+        <v>1756</v>
       </c>
       <c r="C130" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D130" t="n">
-        <v>2919.53</v>
+        <v>5078.1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2915,13 +2915,13 @@
         <v>46218</v>
       </c>
       <c r="B131" t="n">
-        <v>2250</v>
+        <v>2651</v>
       </c>
       <c r="C131" t="n">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="D131" t="n">
-        <v>1573.32</v>
+        <v>363.7</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -2934,17 +2934,17 @@
         <v>46218</v>
       </c>
       <c r="B132" t="n">
-        <v>2698</v>
+        <v>360</v>
       </c>
       <c r="C132" t="n">
-        <v>874</v>
+        <v>8888</v>
       </c>
       <c r="D132" t="n">
-        <v>1230.43</v>
+        <v>1594.84</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2953,13 +2953,13 @@
         <v>46218</v>
       </c>
       <c r="B133" t="n">
-        <v>42</v>
+        <v>2582</v>
       </c>
       <c r="C133" t="n">
         <v>8888</v>
       </c>
       <c r="D133" t="n">
-        <v>79947.14999999999</v>
+        <v>379.33</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -2972,17 +2972,17 @@
         <v>46218</v>
       </c>
       <c r="B134" t="n">
-        <v>2716</v>
+        <v>1756</v>
       </c>
       <c r="C134" t="n">
-        <v>1929</v>
+        <v>8888</v>
       </c>
       <c r="D134" t="n">
-        <v>750.4299999999999</v>
+        <v>1715.26</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2991,17 +2991,17 @@
         <v>46218</v>
       </c>
       <c r="B135" t="n">
-        <v>2716</v>
+        <v>1254</v>
       </c>
       <c r="C135" t="n">
-        <v>977</v>
+        <v>8888</v>
       </c>
       <c r="D135" t="n">
-        <v>729.29</v>
+        <v>855.76</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3010,17 +3010,17 @@
         <v>46218</v>
       </c>
       <c r="B136" t="n">
-        <v>1993</v>
+        <v>1289</v>
       </c>
       <c r="C136" t="n">
         <v>8888</v>
       </c>
       <c r="D136" t="n">
-        <v>456.62</v>
+        <v>2396.98</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3029,15 +3029,1003 @@
         <v>46218</v>
       </c>
       <c r="B137" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C137" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D137" t="n">
+        <v>315.69</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B138" t="n">
+        <v>1064</v>
+      </c>
+      <c r="C138" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1274.3</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B139" t="n">
+        <v>2698</v>
+      </c>
+      <c r="C139" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D139" t="n">
+        <v>552.15</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B140" t="n">
         <v>629</v>
       </c>
-      <c r="C137" t="n">
+      <c r="C140" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D140" t="n">
+        <v>3035.38</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B141" t="n">
+        <v>664</v>
+      </c>
+      <c r="C141" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D141" t="n">
+        <v>4973.15</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B142" t="n">
+        <v>2686</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1929</v>
+      </c>
+      <c r="D142" t="n">
+        <v>521.79</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B143" t="n">
+        <v>2584</v>
+      </c>
+      <c r="C143" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1852.83</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B144" t="n">
+        <v>2641</v>
+      </c>
+      <c r="C144" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D144" t="n">
+        <v>820</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B145" t="n">
+        <v>816</v>
+      </c>
+      <c r="C145" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D145" t="n">
+        <v>438.24</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B146" t="n">
+        <v>285</v>
+      </c>
+      <c r="C146" t="n">
+        <v>58</v>
+      </c>
+      <c r="D146" t="n">
+        <v>364.99</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B147" t="n">
+        <v>2114</v>
+      </c>
+      <c r="C147" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D147" t="n">
+        <v>2726.04</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B148" t="n">
+        <v>953</v>
+      </c>
+      <c r="C148" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D148" t="n">
+        <v>2618.89</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B149" t="n">
+        <v>1102</v>
+      </c>
+      <c r="C149" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D149" t="n">
+        <v>2344.41</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B150" t="n">
+        <v>619</v>
+      </c>
+      <c r="C150" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D150" t="n">
+        <v>2021.67</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B151" t="n">
+        <v>1465</v>
+      </c>
+      <c r="C151" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D151" t="n">
+        <v>3504</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B152" t="n">
+        <v>2767</v>
+      </c>
+      <c r="C152" t="n">
+        <v>1898</v>
+      </c>
+      <c r="D152" t="n">
+        <v>1135.64</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B153" t="n">
+        <v>2245</v>
+      </c>
+      <c r="C153" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D153" t="n">
+        <v>427.51</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B154" t="n">
+        <v>2197</v>
+      </c>
+      <c r="C154" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D154" t="n">
+        <v>1085.45</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B155" t="n">
+        <v>2657</v>
+      </c>
+      <c r="C155" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D155" t="n">
+        <v>1187.68</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B156" t="n">
+        <v>1277</v>
+      </c>
+      <c r="C156" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D156" t="n">
+        <v>1949</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B157" t="n">
+        <v>131</v>
+      </c>
+      <c r="C157" t="n">
+        <v>27</v>
+      </c>
+      <c r="D157" t="n">
+        <v>1268.57</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B158" t="n">
+        <v>2692</v>
+      </c>
+      <c r="C158" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D158" t="n">
+        <v>731.28</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B159" t="n">
+        <v>1317</v>
+      </c>
+      <c r="C159" t="n">
+        <v>3179</v>
+      </c>
+      <c r="D159" t="n">
+        <v>991.6799999999999</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B160" t="n">
+        <v>1993</v>
+      </c>
+      <c r="C160" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D160" t="n">
+        <v>2875.39</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B161" t="n">
+        <v>1632</v>
+      </c>
+      <c r="C161" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D161" t="n">
+        <v>564.55</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B162" t="n">
+        <v>1890</v>
+      </c>
+      <c r="C162" t="n">
+        <v>3449</v>
+      </c>
+      <c r="D162" t="n">
+        <v>3590.04</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B163" t="n">
+        <v>451</v>
+      </c>
+      <c r="C163" t="n">
+        <v>3403</v>
+      </c>
+      <c r="D163" t="n">
+        <v>445.58</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B164" t="n">
+        <v>2749</v>
+      </c>
+      <c r="C164" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1860.64</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B165" t="n">
+        <v>1117</v>
+      </c>
+      <c r="C165" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D165" t="n">
+        <v>342.2</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B166" t="n">
+        <v>1478</v>
+      </c>
+      <c r="C166" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D166" t="n">
+        <v>875.34</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B167" t="n">
+        <v>2491</v>
+      </c>
+      <c r="C167" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D167" t="n">
+        <v>650.4299999999999</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B168" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C168" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D168" t="n">
+        <v>4436.15</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B169" t="n">
+        <v>1890</v>
+      </c>
+      <c r="C169" t="n">
+        <v>1953</v>
+      </c>
+      <c r="D169" t="n">
+        <v>500.92</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B170" t="n">
+        <v>2782</v>
+      </c>
+      <c r="C170" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D170" t="n">
+        <v>1786.32</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B171" t="n">
+        <v>483</v>
+      </c>
+      <c r="C171" t="n">
+        <v>841</v>
+      </c>
+      <c r="D171" t="n">
+        <v>1393.15</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B172" t="n">
+        <v>2133</v>
+      </c>
+      <c r="C172" t="n">
+        <v>213</v>
+      </c>
+      <c r="D172" t="n">
+        <v>526.8</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B173" t="n">
+        <v>351</v>
+      </c>
+      <c r="C173" t="n">
+        <v>3009</v>
+      </c>
+      <c r="D173" t="n">
+        <v>416.36</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B174" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C174" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D174" t="n">
+        <v>709.46</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B175" t="n">
+        <v>2648</v>
+      </c>
+      <c r="C175" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D175" t="n">
+        <v>1873.52</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B176" t="n">
+        <v>131</v>
+      </c>
+      <c r="C176" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D176" t="n">
+        <v>1369.91</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B177" t="n">
+        <v>2639</v>
+      </c>
+      <c r="C177" t="n">
+        <v>1953</v>
+      </c>
+      <c r="D177" t="n">
+        <v>504.09</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B178" t="n">
+        <v>2109</v>
+      </c>
+      <c r="C178" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D178" t="n">
+        <v>2293.78</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B179" t="n">
+        <v>1116</v>
+      </c>
+      <c r="C179" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D179" t="n">
+        <v>2919.53</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B180" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C180" t="n">
+        <v>27</v>
+      </c>
+      <c r="D180" t="n">
+        <v>1803.76</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B181" t="n">
+        <v>353</v>
+      </c>
+      <c r="C181" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D181" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B182" t="n">
+        <v>2698</v>
+      </c>
+      <c r="C182" t="n">
+        <v>874</v>
+      </c>
+      <c r="D182" t="n">
+        <v>1230.43</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B183" t="n">
+        <v>42</v>
+      </c>
+      <c r="C183" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D183" t="n">
+        <v>79947.14999999999</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B184" t="n">
+        <v>772</v>
+      </c>
+      <c r="C184" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D184" t="n">
+        <v>400.25</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B185" t="n">
+        <v>2728</v>
+      </c>
+      <c r="C185" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D185" t="n">
+        <v>1397.07</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B186" t="n">
+        <v>2716</v>
+      </c>
+      <c r="C186" t="n">
+        <v>1929</v>
+      </c>
+      <c r="D186" t="n">
+        <v>750.4299999999999</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B187" t="n">
+        <v>2716</v>
+      </c>
+      <c r="C187" t="n">
+        <v>977</v>
+      </c>
+      <c r="D187" t="n">
+        <v>729.29</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B188" t="n">
+        <v>1993</v>
+      </c>
+      <c r="C188" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D188" t="n">
+        <v>456.62</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B189" t="n">
+        <v>629</v>
+      </c>
+      <c r="C189" t="n">
         <v>675</v>
       </c>
-      <c r="D137" t="n">
+      <c r="D189" t="n">
         <v>1054.76</v>
       </c>
-      <c r="E137" t="inlineStr">
+      <c r="E189" t="inlineStr">
         <is>
           <t>TELEMARKETING</t>
         </is>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E189"/>
+  <dimension ref="A1:E205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
         <v>8888</v>
       </c>
       <c r="D2" t="n">
-        <v>312.98</v>
+        <v>406.97</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -578,17 +578,17 @@
         <v>46218</v>
       </c>
       <c r="B8" t="n">
-        <v>2015</v>
+        <v>1632</v>
       </c>
       <c r="C8" t="n">
-        <v>2571</v>
+        <v>8888</v>
       </c>
       <c r="D8" t="n">
-        <v>714.53</v>
+        <v>768.84</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -597,13 +597,13 @@
         <v>46218</v>
       </c>
       <c r="B9" t="n">
-        <v>1289</v>
+        <v>2015</v>
       </c>
       <c r="C9" t="n">
-        <v>1929</v>
+        <v>2571</v>
       </c>
       <c r="D9" t="n">
-        <v>727.05</v>
+        <v>3147.53</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -616,13 +616,13 @@
         <v>46218</v>
       </c>
       <c r="B10" t="n">
-        <v>609</v>
+        <v>1289</v>
       </c>
       <c r="C10" t="n">
-        <v>3179</v>
+        <v>1929</v>
       </c>
       <c r="D10" t="n">
-        <v>2603.16</v>
+        <v>727.05</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -635,17 +635,17 @@
         <v>46218</v>
       </c>
       <c r="B11" t="n">
-        <v>2211</v>
+        <v>609</v>
       </c>
       <c r="C11" t="n">
-        <v>8888</v>
+        <v>3179</v>
       </c>
       <c r="D11" t="n">
-        <v>2190.93</v>
+        <v>2603.16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -654,13 +654,13 @@
         <v>46218</v>
       </c>
       <c r="B12" t="n">
-        <v>2660</v>
+        <v>2211</v>
       </c>
       <c r="C12" t="n">
         <v>8888</v>
       </c>
       <c r="D12" t="n">
-        <v>875.61</v>
+        <v>2190.93</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -673,13 +673,13 @@
         <v>46218</v>
       </c>
       <c r="B13" t="n">
-        <v>890</v>
+        <v>2660</v>
       </c>
       <c r="C13" t="n">
         <v>8888</v>
       </c>
       <c r="D13" t="n">
-        <v>1051.23</v>
+        <v>875.61</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -692,13 +692,13 @@
         <v>46218</v>
       </c>
       <c r="B14" t="n">
-        <v>2190</v>
+        <v>890</v>
       </c>
       <c r="C14" t="n">
         <v>8888</v>
       </c>
       <c r="D14" t="n">
-        <v>1307.13</v>
+        <v>1051.23</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -711,17 +711,17 @@
         <v>46218</v>
       </c>
       <c r="B15" t="n">
-        <v>2651</v>
+        <v>2190</v>
       </c>
       <c r="C15" t="n">
         <v>8888</v>
       </c>
       <c r="D15" t="n">
-        <v>660.95</v>
+        <v>1307.13</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -730,17 +730,17 @@
         <v>46218</v>
       </c>
       <c r="B16" t="n">
-        <v>2118</v>
+        <v>2651</v>
       </c>
       <c r="C16" t="n">
         <v>8888</v>
       </c>
       <c r="D16" t="n">
-        <v>5535.71</v>
+        <v>660.95</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
         <v>46218</v>
       </c>
       <c r="B17" t="n">
-        <v>2197</v>
+        <v>2118</v>
       </c>
       <c r="C17" t="n">
         <v>8888</v>
       </c>
       <c r="D17" t="n">
-        <v>892.66</v>
+        <v>5535.71</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -768,13 +768,13 @@
         <v>46218</v>
       </c>
       <c r="B18" t="n">
-        <v>1869</v>
+        <v>2507</v>
       </c>
       <c r="C18" t="n">
         <v>8888</v>
       </c>
       <c r="D18" t="n">
-        <v>1263.2</v>
+        <v>1174.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -787,17 +787,17 @@
         <v>46218</v>
       </c>
       <c r="B19" t="n">
-        <v>2133</v>
+        <v>2197</v>
       </c>
       <c r="C19" t="n">
-        <v>691</v>
+        <v>8888</v>
       </c>
       <c r="D19" t="n">
-        <v>2058.93</v>
+        <v>892.66</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -806,17 +806,17 @@
         <v>46218</v>
       </c>
       <c r="B20" t="n">
-        <v>452</v>
+        <v>363</v>
       </c>
       <c r="C20" t="n">
         <v>8888</v>
       </c>
       <c r="D20" t="n">
-        <v>1832.74</v>
+        <v>836.9400000000001</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -825,13 +825,13 @@
         <v>46218</v>
       </c>
       <c r="B21" t="n">
-        <v>2250</v>
+        <v>1869</v>
       </c>
       <c r="C21" t="n">
         <v>8888</v>
       </c>
       <c r="D21" t="n">
-        <v>1686.37</v>
+        <v>1263.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         <v>46218</v>
       </c>
       <c r="B22" t="n">
-        <v>931</v>
+        <v>2133</v>
       </c>
       <c r="C22" t="n">
-        <v>423</v>
+        <v>691</v>
       </c>
       <c r="D22" t="n">
-        <v>492.34</v>
+        <v>2058.93</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -863,17 +863,17 @@
         <v>46218</v>
       </c>
       <c r="B23" t="n">
-        <v>951</v>
+        <v>452</v>
       </c>
       <c r="C23" t="n">
         <v>8888</v>
       </c>
       <c r="D23" t="n">
-        <v>2171.08</v>
+        <v>1832.74</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
         <v>46218</v>
       </c>
       <c r="B24" t="n">
-        <v>2695</v>
+        <v>2250</v>
       </c>
       <c r="C24" t="n">
         <v>8888</v>
       </c>
       <c r="D24" t="n">
-        <v>411.42</v>
+        <v>1686.37</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
         <v>46218</v>
       </c>
       <c r="B25" t="n">
-        <v>525</v>
+        <v>931</v>
       </c>
       <c r="C25" t="n">
-        <v>8888</v>
+        <v>423</v>
       </c>
       <c r="D25" t="n">
-        <v>408.25</v>
+        <v>492.34</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -920,17 +920,17 @@
         <v>46218</v>
       </c>
       <c r="B26" t="n">
-        <v>1808</v>
+        <v>951</v>
       </c>
       <c r="C26" t="n">
         <v>8888</v>
       </c>
       <c r="D26" t="n">
-        <v>695.3200000000001</v>
+        <v>2171.08</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -939,17 +939,17 @@
         <v>46218</v>
       </c>
       <c r="B27" t="n">
-        <v>949</v>
+        <v>2695</v>
       </c>
       <c r="C27" t="n">
-        <v>1134</v>
+        <v>8888</v>
       </c>
       <c r="D27" t="n">
-        <v>30.46</v>
+        <v>411.42</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
         <v>46218</v>
       </c>
       <c r="B28" t="n">
-        <v>2499</v>
+        <v>525</v>
       </c>
       <c r="C28" t="n">
         <v>8888</v>
       </c>
       <c r="D28" t="n">
-        <v>261.63</v>
+        <v>408.25</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -977,17 +977,17 @@
         <v>46218</v>
       </c>
       <c r="B29" t="n">
-        <v>58</v>
+        <v>1808</v>
       </c>
       <c r="C29" t="n">
         <v>8888</v>
       </c>
       <c r="D29" t="n">
-        <v>499.11</v>
+        <v>695.3200000000001</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -996,17 +996,17 @@
         <v>46218</v>
       </c>
       <c r="B30" t="n">
-        <v>2245</v>
+        <v>1632</v>
       </c>
       <c r="C30" t="n">
-        <v>8888</v>
+        <v>423</v>
       </c>
       <c r="D30" t="n">
-        <v>2740.06</v>
+        <v>1266.17</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1015,17 +1015,17 @@
         <v>46218</v>
       </c>
       <c r="B31" t="n">
-        <v>325</v>
+        <v>949</v>
       </c>
       <c r="C31" t="n">
-        <v>8888</v>
+        <v>1134</v>
       </c>
       <c r="D31" t="n">
-        <v>524.36</v>
+        <v>30.46</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
         <v>46218</v>
       </c>
       <c r="B32" t="n">
-        <v>2383</v>
+        <v>2499</v>
       </c>
       <c r="C32" t="n">
         <v>8888</v>
       </c>
       <c r="D32" t="n">
-        <v>7926.02</v>
+        <v>261.63</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
         <v>46218</v>
       </c>
       <c r="B33" t="n">
-        <v>1117</v>
+        <v>58</v>
       </c>
       <c r="C33" t="n">
-        <v>1139</v>
+        <v>8888</v>
       </c>
       <c r="D33" t="n">
-        <v>916.72</v>
+        <v>499.11</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1072,13 +1072,13 @@
         <v>46218</v>
       </c>
       <c r="B34" t="n">
-        <v>2279</v>
+        <v>2245</v>
       </c>
       <c r="C34" t="n">
         <v>8888</v>
       </c>
       <c r="D34" t="n">
-        <v>712.66</v>
+        <v>2740.06</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1091,17 +1091,17 @@
         <v>46218</v>
       </c>
       <c r="B35" t="n">
-        <v>535</v>
+        <v>325</v>
       </c>
       <c r="C35" t="n">
         <v>8888</v>
       </c>
       <c r="D35" t="n">
-        <v>4810</v>
+        <v>524.36</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1110,17 +1110,17 @@
         <v>46218</v>
       </c>
       <c r="B36" t="n">
-        <v>535</v>
+        <v>2383</v>
       </c>
       <c r="C36" t="n">
         <v>8888</v>
       </c>
       <c r="D36" t="n">
-        <v>1352.51</v>
+        <v>7926.02</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1129,13 +1129,13 @@
         <v>46218</v>
       </c>
       <c r="B37" t="n">
-        <v>2678</v>
+        <v>1117</v>
       </c>
       <c r="C37" t="n">
-        <v>1312</v>
+        <v>1139</v>
       </c>
       <c r="D37" t="n">
-        <v>364.96</v>
+        <v>916.72</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1148,13 +1148,13 @@
         <v>46218</v>
       </c>
       <c r="B38" t="n">
-        <v>2345</v>
+        <v>2279</v>
       </c>
       <c r="C38" t="n">
         <v>8888</v>
       </c>
       <c r="D38" t="n">
-        <v>863.16</v>
+        <v>712.66</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1167,13 +1167,13 @@
         <v>46218</v>
       </c>
       <c r="B39" t="n">
-        <v>438</v>
+        <v>535</v>
       </c>
       <c r="C39" t="n">
         <v>8888</v>
       </c>
       <c r="D39" t="n">
-        <v>220.06</v>
+        <v>4810</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1186,17 +1186,17 @@
         <v>46218</v>
       </c>
       <c r="B40" t="n">
-        <v>353</v>
+        <v>535</v>
       </c>
       <c r="C40" t="n">
-        <v>3179</v>
+        <v>8888</v>
       </c>
       <c r="D40" t="n">
-        <v>495.84</v>
+        <v>1352.51</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1205,17 +1205,17 @@
         <v>46218</v>
       </c>
       <c r="B41" t="n">
-        <v>1293</v>
+        <v>2678</v>
       </c>
       <c r="C41" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D41" t="n">
-        <v>3129.07</v>
+        <v>364.96</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1224,17 +1224,17 @@
         <v>46218</v>
       </c>
       <c r="B42" t="n">
-        <v>2279</v>
+        <v>2345</v>
       </c>
       <c r="C42" t="n">
         <v>8888</v>
       </c>
       <c r="D42" t="n">
-        <v>2753.96</v>
+        <v>863.16</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
         <v>46218</v>
       </c>
       <c r="B43" t="n">
-        <v>1137</v>
+        <v>945</v>
       </c>
       <c r="C43" t="n">
         <v>8888</v>
       </c>
       <c r="D43" t="n">
-        <v>1437.44</v>
+        <v>21973.45</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>PEDIDO ELETRÔNICO</t>
         </is>
       </c>
     </row>
@@ -1262,17 +1262,17 @@
         <v>46218</v>
       </c>
       <c r="B44" t="n">
-        <v>2793</v>
+        <v>438</v>
       </c>
       <c r="C44" t="n">
-        <v>977</v>
+        <v>8888</v>
       </c>
       <c r="D44" t="n">
-        <v>695.72</v>
+        <v>220.06</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1281,17 +1281,17 @@
         <v>46218</v>
       </c>
       <c r="B45" t="n">
-        <v>945</v>
+        <v>353</v>
       </c>
       <c r="C45" t="n">
-        <v>8888</v>
+        <v>3179</v>
       </c>
       <c r="D45" t="n">
-        <v>1934.84</v>
+        <v>495.84</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>PEDIDO ELETRÔNICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1300,17 +1300,17 @@
         <v>46218</v>
       </c>
       <c r="B46" t="n">
-        <v>374</v>
+        <v>1293</v>
       </c>
       <c r="C46" t="n">
         <v>8888</v>
       </c>
       <c r="D46" t="n">
-        <v>22.62</v>
+        <v>3129.07</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1319,13 +1319,13 @@
         <v>46218</v>
       </c>
       <c r="B47" t="n">
-        <v>664</v>
+        <v>2279</v>
       </c>
       <c r="C47" t="n">
         <v>8888</v>
       </c>
       <c r="D47" t="n">
-        <v>1510.56</v>
+        <v>2753.96</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1338,17 +1338,17 @@
         <v>46218</v>
       </c>
       <c r="B48" t="n">
-        <v>703</v>
+        <v>1137</v>
       </c>
       <c r="C48" t="n">
         <v>8888</v>
       </c>
       <c r="D48" t="n">
-        <v>12155.46</v>
+        <v>1947.93</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1357,17 +1357,17 @@
         <v>46218</v>
       </c>
       <c r="B49" t="n">
-        <v>1937</v>
+        <v>374</v>
       </c>
       <c r="C49" t="n">
         <v>8888</v>
       </c>
       <c r="D49" t="n">
-        <v>1032.73</v>
+        <v>712.71</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1376,17 +1376,17 @@
         <v>46218</v>
       </c>
       <c r="B50" t="n">
-        <v>451</v>
+        <v>2686</v>
       </c>
       <c r="C50" t="n">
         <v>8888</v>
       </c>
       <c r="D50" t="n">
-        <v>368.93</v>
+        <v>332.6</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1395,17 +1395,17 @@
         <v>46218</v>
       </c>
       <c r="B51" t="n">
-        <v>1756</v>
+        <v>2793</v>
       </c>
       <c r="C51" t="n">
-        <v>8888</v>
+        <v>977</v>
       </c>
       <c r="D51" t="n">
-        <v>996.17</v>
+        <v>695.72</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1414,17 +1414,17 @@
         <v>46218</v>
       </c>
       <c r="B52" t="n">
-        <v>1956</v>
+        <v>374</v>
       </c>
       <c r="C52" t="n">
         <v>8888</v>
       </c>
       <c r="D52" t="n">
-        <v>4557.34</v>
+        <v>22.62</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1433,13 +1433,13 @@
         <v>46218</v>
       </c>
       <c r="B53" t="n">
-        <v>925</v>
+        <v>664</v>
       </c>
       <c r="C53" t="n">
         <v>8888</v>
       </c>
       <c r="D53" t="n">
-        <v>651.59</v>
+        <v>1510.56</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -1452,17 +1452,17 @@
         <v>46218</v>
       </c>
       <c r="B54" t="n">
-        <v>2631</v>
+        <v>703</v>
       </c>
       <c r="C54" t="n">
-        <v>2853</v>
+        <v>8888</v>
       </c>
       <c r="D54" t="n">
-        <v>509.88</v>
+        <v>12155.46</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1471,17 +1471,17 @@
         <v>46218</v>
       </c>
       <c r="B55" t="n">
-        <v>2648</v>
+        <v>1937</v>
       </c>
       <c r="C55" t="n">
         <v>8888</v>
       </c>
       <c r="D55" t="n">
-        <v>1594.42</v>
+        <v>1032.73</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1490,17 +1490,17 @@
         <v>46218</v>
       </c>
       <c r="B56" t="n">
-        <v>2714</v>
+        <v>451</v>
       </c>
       <c r="C56" t="n">
-        <v>519</v>
+        <v>8888</v>
       </c>
       <c r="D56" t="n">
-        <v>61939.22</v>
+        <v>368.93</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1509,17 +1509,17 @@
         <v>46218</v>
       </c>
       <c r="B57" t="n">
-        <v>483</v>
+        <v>1756</v>
       </c>
       <c r="C57" t="n">
         <v>8888</v>
       </c>
       <c r="D57" t="n">
-        <v>6625.87</v>
+        <v>996.17</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1528,13 +1528,13 @@
         <v>46218</v>
       </c>
       <c r="B58" t="n">
-        <v>1075</v>
+        <v>1956</v>
       </c>
       <c r="C58" t="n">
         <v>8888</v>
       </c>
       <c r="D58" t="n">
-        <v>11607.79</v>
+        <v>4557.34</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -1547,17 +1547,17 @@
         <v>46218</v>
       </c>
       <c r="B59" t="n">
-        <v>629</v>
+        <v>925</v>
       </c>
       <c r="C59" t="n">
         <v>8888</v>
       </c>
       <c r="D59" t="n">
-        <v>9233.719999999999</v>
+        <v>651.59</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1566,13 +1566,13 @@
         <v>46218</v>
       </c>
       <c r="B60" t="n">
-        <v>1983</v>
+        <v>2631</v>
       </c>
       <c r="C60" t="n">
-        <v>841</v>
+        <v>2853</v>
       </c>
       <c r="D60" t="n">
-        <v>243.92</v>
+        <v>509.88</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -1585,17 +1585,17 @@
         <v>46218</v>
       </c>
       <c r="B61" t="n">
-        <v>1137</v>
+        <v>2648</v>
       </c>
       <c r="C61" t="n">
         <v>8888</v>
       </c>
       <c r="D61" t="n">
-        <v>3578.51</v>
+        <v>1594.42</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1604,17 +1604,17 @@
         <v>46218</v>
       </c>
       <c r="B62" t="n">
-        <v>2651</v>
+        <v>2714</v>
       </c>
       <c r="C62" t="n">
-        <v>8888</v>
+        <v>519</v>
       </c>
       <c r="D62" t="n">
-        <v>1296.58</v>
+        <v>61939.22</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
         <v>46218</v>
       </c>
       <c r="B63" t="n">
-        <v>1956</v>
+        <v>483</v>
       </c>
       <c r="C63" t="n">
-        <v>423</v>
+        <v>8888</v>
       </c>
       <c r="D63" t="n">
-        <v>455.37</v>
+        <v>6625.87</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1642,17 +1642,17 @@
         <v>46218</v>
       </c>
       <c r="B64" t="n">
-        <v>2709</v>
+        <v>1075</v>
       </c>
       <c r="C64" t="n">
         <v>8888</v>
       </c>
       <c r="D64" t="n">
-        <v>547.6900000000001</v>
+        <v>11607.79</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1661,13 +1661,13 @@
         <v>46218</v>
       </c>
       <c r="B65" t="n">
-        <v>2026</v>
+        <v>629</v>
       </c>
       <c r="C65" t="n">
         <v>8888</v>
       </c>
       <c r="D65" t="n">
-        <v>2237.62</v>
+        <v>9233.719999999999</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -1680,13 +1680,13 @@
         <v>46218</v>
       </c>
       <c r="B66" t="n">
-        <v>89</v>
+        <v>1983</v>
       </c>
       <c r="C66" t="n">
-        <v>13148</v>
+        <v>841</v>
       </c>
       <c r="D66" t="n">
-        <v>1883.74</v>
+        <v>243.92</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -1699,17 +1699,17 @@
         <v>46218</v>
       </c>
       <c r="B67" t="n">
-        <v>2709</v>
+        <v>1137</v>
       </c>
       <c r="C67" t="n">
-        <v>2220</v>
+        <v>8888</v>
       </c>
       <c r="D67" t="n">
-        <v>390.19</v>
+        <v>3578.51</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
         <v>46218</v>
       </c>
       <c r="B68" t="n">
-        <v>2345</v>
+        <v>2651</v>
       </c>
       <c r="C68" t="n">
         <v>8888</v>
       </c>
       <c r="D68" t="n">
-        <v>748.86</v>
+        <v>1296.58</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1737,17 +1737,17 @@
         <v>46218</v>
       </c>
       <c r="B69" t="n">
-        <v>1308</v>
+        <v>1956</v>
       </c>
       <c r="C69" t="n">
-        <v>8888</v>
+        <v>423</v>
       </c>
       <c r="D69" t="n">
-        <v>276.16</v>
+        <v>455.37</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1756,17 +1756,17 @@
         <v>46218</v>
       </c>
       <c r="B70" t="n">
-        <v>2308</v>
+        <v>2709</v>
       </c>
       <c r="C70" t="n">
         <v>8888</v>
       </c>
       <c r="D70" t="n">
-        <v>488.69</v>
+        <v>547.6900000000001</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1775,17 +1775,17 @@
         <v>46218</v>
       </c>
       <c r="B71" t="n">
-        <v>360</v>
+        <v>2026</v>
       </c>
       <c r="C71" t="n">
-        <v>546</v>
+        <v>8888</v>
       </c>
       <c r="D71" t="n">
-        <v>709.75</v>
+        <v>2237.62</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1794,17 +1794,17 @@
         <v>46218</v>
       </c>
       <c r="B72" t="n">
-        <v>2211</v>
+        <v>2789</v>
       </c>
       <c r="C72" t="n">
-        <v>874</v>
+        <v>8888</v>
       </c>
       <c r="D72" t="n">
-        <v>1526.94</v>
+        <v>747.77</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1813,17 +1813,17 @@
         <v>46218</v>
       </c>
       <c r="B73" t="n">
-        <v>559</v>
+        <v>89</v>
       </c>
       <c r="C73" t="n">
-        <v>8888</v>
+        <v>13148</v>
       </c>
       <c r="D73" t="n">
-        <v>859.92</v>
+        <v>1883.74</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1832,17 +1832,17 @@
         <v>46218</v>
       </c>
       <c r="B74" t="n">
-        <v>569</v>
+        <v>2709</v>
       </c>
       <c r="C74" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D74" t="n">
-        <v>673.01</v>
+        <v>390.19</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1851,17 +1851,17 @@
         <v>46218</v>
       </c>
       <c r="B75" t="n">
-        <v>890</v>
+        <v>2345</v>
       </c>
       <c r="C75" t="n">
         <v>8888</v>
       </c>
       <c r="D75" t="n">
-        <v>387.2</v>
+        <v>748.86</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1870,13 +1870,13 @@
         <v>46218</v>
       </c>
       <c r="B76" t="n">
-        <v>1063</v>
+        <v>1308</v>
       </c>
       <c r="C76" t="n">
         <v>8888</v>
       </c>
       <c r="D76" t="n">
-        <v>4487.11</v>
+        <v>276.16</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -1889,13 +1889,13 @@
         <v>46218</v>
       </c>
       <c r="B77" t="n">
-        <v>2279</v>
+        <v>360</v>
       </c>
       <c r="C77" t="n">
-        <v>1139</v>
+        <v>546</v>
       </c>
       <c r="D77" t="n">
-        <v>652.51</v>
+        <v>1609.68</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -1908,17 +1908,17 @@
         <v>46218</v>
       </c>
       <c r="B78" t="n">
-        <v>1299</v>
+        <v>2308</v>
       </c>
       <c r="C78" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D78" t="n">
-        <v>1435.52</v>
+        <v>488.69</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1927,13 +1927,13 @@
         <v>46218</v>
       </c>
       <c r="B79" t="n">
-        <v>1478</v>
+        <v>2211</v>
       </c>
       <c r="C79" t="n">
-        <v>675</v>
+        <v>874</v>
       </c>
       <c r="D79" t="n">
-        <v>1600.01</v>
+        <v>1526.94</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -1946,17 +1946,17 @@
         <v>46218</v>
       </c>
       <c r="B80" t="n">
-        <v>285</v>
+        <v>559</v>
       </c>
       <c r="C80" t="n">
         <v>8888</v>
       </c>
       <c r="D80" t="n">
-        <v>3349.8</v>
+        <v>859.92</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1965,13 +1965,13 @@
         <v>46218</v>
       </c>
       <c r="B81" t="n">
-        <v>1983</v>
+        <v>569</v>
       </c>
       <c r="C81" t="n">
         <v>8888</v>
       </c>
       <c r="D81" t="n">
-        <v>2451.28</v>
+        <v>673.01</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -1984,17 +1984,17 @@
         <v>46218</v>
       </c>
       <c r="B82" t="n">
-        <v>477</v>
+        <v>890</v>
       </c>
       <c r="C82" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D82" t="n">
-        <v>1540.55</v>
+        <v>387.2</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2009,11 +2009,11 @@
         <v>8888</v>
       </c>
       <c r="D83" t="n">
-        <v>2549.86</v>
+        <v>4487.11</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2022,17 +2022,17 @@
         <v>46218</v>
       </c>
       <c r="B84" t="n">
-        <v>424</v>
+        <v>2279</v>
       </c>
       <c r="C84" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D84" t="n">
-        <v>1035.17</v>
+        <v>652.51</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2041,17 +2041,17 @@
         <v>46218</v>
       </c>
       <c r="B85" t="n">
-        <v>675</v>
+        <v>1299</v>
       </c>
       <c r="C85" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D85" t="n">
-        <v>616.73</v>
+        <v>1435.52</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2060,17 +2060,17 @@
         <v>46218</v>
       </c>
       <c r="B86" t="n">
-        <v>2768</v>
+        <v>1478</v>
       </c>
       <c r="C86" t="n">
-        <v>8888</v>
+        <v>675</v>
       </c>
       <c r="D86" t="n">
-        <v>4245.73</v>
+        <v>1600.01</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2079,17 +2079,17 @@
         <v>46218</v>
       </c>
       <c r="B87" t="n">
-        <v>1993</v>
+        <v>285</v>
       </c>
       <c r="C87" t="n">
         <v>8888</v>
       </c>
       <c r="D87" t="n">
-        <v>362.63</v>
+        <v>3349.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2098,17 +2098,17 @@
         <v>46218</v>
       </c>
       <c r="B88" t="n">
-        <v>1465</v>
+        <v>1983</v>
       </c>
       <c r="C88" t="n">
         <v>8888</v>
       </c>
       <c r="D88" t="n">
-        <v>3373.83</v>
+        <v>2451.28</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2117,17 +2117,17 @@
         <v>46218</v>
       </c>
       <c r="B89" t="n">
-        <v>89</v>
+        <v>477</v>
       </c>
       <c r="C89" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D89" t="n">
-        <v>479</v>
+        <v>1540.55</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2136,17 +2136,17 @@
         <v>46218</v>
       </c>
       <c r="B90" t="n">
-        <v>595</v>
+        <v>1063</v>
       </c>
       <c r="C90" t="n">
         <v>8888</v>
       </c>
       <c r="D90" t="n">
-        <v>18084.5</v>
+        <v>2549.86</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2155,17 +2155,17 @@
         <v>46218</v>
       </c>
       <c r="B91" t="n">
-        <v>2696</v>
+        <v>424</v>
       </c>
       <c r="C91" t="n">
-        <v>1954</v>
+        <v>8888</v>
       </c>
       <c r="D91" t="n">
-        <v>259.97</v>
+        <v>1035.17</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2174,13 +2174,13 @@
         <v>46218</v>
       </c>
       <c r="B92" t="n">
-        <v>360</v>
+        <v>675</v>
       </c>
       <c r="C92" t="n">
         <v>8888</v>
       </c>
       <c r="D92" t="n">
-        <v>2023.17</v>
+        <v>616.73</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -2193,17 +2193,17 @@
         <v>46218</v>
       </c>
       <c r="B93" t="n">
-        <v>1465</v>
+        <v>2768</v>
       </c>
       <c r="C93" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D93" t="n">
-        <v>777.2</v>
+        <v>5607.14</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2212,17 +2212,17 @@
         <v>46218</v>
       </c>
       <c r="B94" t="n">
-        <v>947</v>
+        <v>1993</v>
       </c>
       <c r="C94" t="n">
         <v>8888</v>
       </c>
       <c r="D94" t="n">
-        <v>2087.97</v>
+        <v>362.63</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>PEDIDO ELETRÔNICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2231,17 +2231,17 @@
         <v>46218</v>
       </c>
       <c r="B95" t="n">
-        <v>2178</v>
+        <v>1465</v>
       </c>
       <c r="C95" t="n">
         <v>8888</v>
       </c>
       <c r="D95" t="n">
-        <v>619.92</v>
+        <v>3373.83</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2250,17 +2250,17 @@
         <v>46218</v>
       </c>
       <c r="B96" t="n">
-        <v>630</v>
+        <v>89</v>
       </c>
       <c r="C96" t="n">
-        <v>1929</v>
+        <v>8888</v>
       </c>
       <c r="D96" t="n">
-        <v>1801.63</v>
+        <v>479</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2269,17 +2269,17 @@
         <v>46218</v>
       </c>
       <c r="B97" t="n">
-        <v>1937</v>
+        <v>595</v>
       </c>
       <c r="C97" t="n">
         <v>8888</v>
       </c>
       <c r="D97" t="n">
-        <v>2132.95</v>
+        <v>18084.5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
         <v>46218</v>
       </c>
       <c r="B98" t="n">
-        <v>2577</v>
+        <v>2696</v>
       </c>
       <c r="C98" t="n">
-        <v>8888</v>
+        <v>1954</v>
       </c>
       <c r="D98" t="n">
-        <v>1647.08</v>
+        <v>1597.76</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2307,17 +2307,17 @@
         <v>46218</v>
       </c>
       <c r="B99" t="n">
-        <v>1293</v>
+        <v>360</v>
       </c>
       <c r="C99" t="n">
         <v>8888</v>
       </c>
       <c r="D99" t="n">
-        <v>1607.2</v>
+        <v>4596.89</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2326,17 +2326,17 @@
         <v>46218</v>
       </c>
       <c r="B100" t="n">
-        <v>1317</v>
+        <v>1465</v>
       </c>
       <c r="C100" t="n">
-        <v>8888</v>
+        <v>3403</v>
       </c>
       <c r="D100" t="n">
-        <v>907.72</v>
+        <v>777.2</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2345,17 +2345,17 @@
         <v>46218</v>
       </c>
       <c r="B101" t="n">
-        <v>2571</v>
+        <v>947</v>
       </c>
       <c r="C101" t="n">
-        <v>1312</v>
+        <v>8888</v>
       </c>
       <c r="D101" t="n">
-        <v>268.53</v>
+        <v>2087.97</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>PEDIDO ELETRÔNICO</t>
         </is>
       </c>
     </row>
@@ -2364,17 +2364,17 @@
         <v>46218</v>
       </c>
       <c r="B102" t="n">
-        <v>1937</v>
+        <v>2178</v>
       </c>
       <c r="C102" t="n">
         <v>8888</v>
       </c>
       <c r="D102" t="n">
-        <v>1803.32</v>
+        <v>619.92</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2383,17 +2383,17 @@
         <v>46218</v>
       </c>
       <c r="B103" t="n">
-        <v>1063</v>
+        <v>630</v>
       </c>
       <c r="C103" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D103" t="n">
-        <v>1113.08</v>
+        <v>1801.63</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2402,17 +2402,17 @@
         <v>46218</v>
       </c>
       <c r="B104" t="n">
-        <v>1906</v>
+        <v>1937</v>
       </c>
       <c r="C104" t="n">
         <v>8888</v>
       </c>
       <c r="D104" t="n">
-        <v>990.22</v>
+        <v>2132.95</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2421,13 +2421,13 @@
         <v>46218</v>
       </c>
       <c r="B105" t="n">
-        <v>1756</v>
+        <v>2577</v>
       </c>
       <c r="C105" t="n">
         <v>8888</v>
       </c>
       <c r="D105" t="n">
-        <v>1357.12</v>
+        <v>1647.08</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -2440,17 +2440,17 @@
         <v>46218</v>
       </c>
       <c r="B106" t="n">
-        <v>20</v>
+        <v>1293</v>
       </c>
       <c r="C106" t="n">
         <v>8888</v>
       </c>
       <c r="D106" t="n">
-        <v>276.64</v>
+        <v>2135.89</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2459,17 +2459,17 @@
         <v>46218</v>
       </c>
       <c r="B107" t="n">
-        <v>477</v>
+        <v>2026</v>
       </c>
       <c r="C107" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D107" t="n">
-        <v>372.69</v>
+        <v>1680.89</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2478,17 +2478,17 @@
         <v>46218</v>
       </c>
       <c r="B108" t="n">
-        <v>477</v>
+        <v>2607</v>
       </c>
       <c r="C108" t="n">
         <v>8888</v>
       </c>
       <c r="D108" t="n">
-        <v>707.52</v>
+        <v>490.31</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2497,13 +2497,13 @@
         <v>46218</v>
       </c>
       <c r="B109" t="n">
-        <v>2660</v>
+        <v>1317</v>
       </c>
       <c r="C109" t="n">
         <v>8888</v>
       </c>
       <c r="D109" t="n">
-        <v>2684.97</v>
+        <v>907.72</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -2516,17 +2516,17 @@
         <v>46218</v>
       </c>
       <c r="B110" t="n">
-        <v>569</v>
+        <v>2571</v>
       </c>
       <c r="C110" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D110" t="n">
-        <v>18512.6</v>
+        <v>268.53</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2535,17 +2535,17 @@
         <v>46218</v>
       </c>
       <c r="B111" t="n">
-        <v>2089</v>
+        <v>1937</v>
       </c>
       <c r="C111" t="n">
-        <v>1533</v>
+        <v>8888</v>
       </c>
       <c r="D111" t="n">
-        <v>969.24</v>
+        <v>1803.32</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2554,17 +2554,17 @@
         <v>46218</v>
       </c>
       <c r="B112" t="n">
-        <v>1007</v>
+        <v>1063</v>
       </c>
       <c r="C112" t="n">
         <v>8888</v>
       </c>
       <c r="D112" t="n">
-        <v>241.44</v>
+        <v>1113.08</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2573,17 +2573,17 @@
         <v>46218</v>
       </c>
       <c r="B113" t="n">
-        <v>1380</v>
+        <v>2631</v>
       </c>
       <c r="C113" t="n">
         <v>8888</v>
       </c>
       <c r="D113" t="n">
-        <v>520.2</v>
+        <v>1447.86</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2592,13 +2592,13 @@
         <v>46218</v>
       </c>
       <c r="B114" t="n">
-        <v>1102</v>
+        <v>1906</v>
       </c>
       <c r="C114" t="n">
         <v>8888</v>
       </c>
       <c r="D114" t="n">
-        <v>1137.04</v>
+        <v>2774.84</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -2611,13 +2611,13 @@
         <v>46218</v>
       </c>
       <c r="B115" t="n">
-        <v>1075</v>
+        <v>1756</v>
       </c>
       <c r="C115" t="n">
         <v>8888</v>
       </c>
       <c r="D115" t="n">
-        <v>2179.03</v>
+        <v>1357.12</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -2630,17 +2630,17 @@
         <v>46218</v>
       </c>
       <c r="B116" t="n">
-        <v>2245</v>
+        <v>20</v>
       </c>
       <c r="C116" t="n">
         <v>8888</v>
       </c>
       <c r="D116" t="n">
-        <v>361.58</v>
+        <v>276.64</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2649,17 +2649,17 @@
         <v>46218</v>
       </c>
       <c r="B117" t="n">
-        <v>132</v>
+        <v>477</v>
       </c>
       <c r="C117" t="n">
         <v>8888</v>
       </c>
       <c r="D117" t="n">
-        <v>6522.92</v>
+        <v>372.69</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2668,17 +2668,17 @@
         <v>46218</v>
       </c>
       <c r="B118" t="n">
-        <v>452</v>
+        <v>477</v>
       </c>
       <c r="C118" t="n">
         <v>8888</v>
       </c>
       <c r="D118" t="n">
-        <v>608.78</v>
+        <v>707.52</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2687,17 +2687,17 @@
         <v>46218</v>
       </c>
       <c r="B119" t="n">
-        <v>1293</v>
+        <v>2660</v>
       </c>
       <c r="C119" t="n">
-        <v>1281</v>
+        <v>8888</v>
       </c>
       <c r="D119" t="n">
-        <v>1780.93</v>
+        <v>2684.97</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2706,17 +2706,17 @@
         <v>46218</v>
       </c>
       <c r="B120" t="n">
-        <v>525</v>
+        <v>569</v>
       </c>
       <c r="C120" t="n">
         <v>8888</v>
       </c>
       <c r="D120" t="n">
-        <v>5658.57</v>
+        <v>19352.11</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2725,17 +2725,17 @@
         <v>46218</v>
       </c>
       <c r="B121" t="n">
-        <v>609</v>
+        <v>2089</v>
       </c>
       <c r="C121" t="n">
-        <v>8888</v>
+        <v>1533</v>
       </c>
       <c r="D121" t="n">
-        <v>886.1</v>
+        <v>969.24</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2744,17 +2744,17 @@
         <v>46218</v>
       </c>
       <c r="B122" t="n">
-        <v>619</v>
+        <v>1007</v>
       </c>
       <c r="C122" t="n">
         <v>8888</v>
       </c>
       <c r="D122" t="n">
-        <v>2330.47</v>
+        <v>241.44</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2763,13 +2763,13 @@
         <v>46218</v>
       </c>
       <c r="B123" t="n">
-        <v>58</v>
+        <v>1380</v>
       </c>
       <c r="C123" t="n">
         <v>8888</v>
       </c>
       <c r="D123" t="n">
-        <v>1123.87</v>
+        <v>520.2</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -2782,17 +2782,17 @@
         <v>46218</v>
       </c>
       <c r="B124" t="n">
-        <v>358</v>
+        <v>1102</v>
       </c>
       <c r="C124" t="n">
         <v>8888</v>
       </c>
       <c r="D124" t="n">
-        <v>1675.95</v>
+        <v>1137.04</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2801,13 +2801,13 @@
         <v>46218</v>
       </c>
       <c r="B125" t="n">
-        <v>2431</v>
+        <v>1075</v>
       </c>
       <c r="C125" t="n">
         <v>8888</v>
       </c>
       <c r="D125" t="n">
-        <v>266.89</v>
+        <v>2179.03</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -2820,13 +2820,13 @@
         <v>46218</v>
       </c>
       <c r="B126" t="n">
-        <v>285</v>
+        <v>2245</v>
       </c>
       <c r="C126" t="n">
         <v>8888</v>
       </c>
       <c r="D126" t="n">
-        <v>2090.81</v>
+        <v>361.58</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -2839,17 +2839,17 @@
         <v>46218</v>
       </c>
       <c r="B127" t="n">
-        <v>1102</v>
+        <v>132</v>
       </c>
       <c r="C127" t="n">
         <v>8888</v>
       </c>
       <c r="D127" t="n">
-        <v>1119.32</v>
+        <v>6522.92</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2858,17 +2858,17 @@
         <v>46218</v>
       </c>
       <c r="B128" t="n">
-        <v>626</v>
+        <v>452</v>
       </c>
       <c r="C128" t="n">
         <v>8888</v>
       </c>
       <c r="D128" t="n">
-        <v>11337.75</v>
+        <v>608.78</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2877,13 +2877,13 @@
         <v>46218</v>
       </c>
       <c r="B129" t="n">
-        <v>1137</v>
+        <v>1293</v>
       </c>
       <c r="C129" t="n">
-        <v>2220</v>
+        <v>1281</v>
       </c>
       <c r="D129" t="n">
-        <v>1370.86</v>
+        <v>1780.93</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -2896,17 +2896,17 @@
         <v>46218</v>
       </c>
       <c r="B130" t="n">
-        <v>1756</v>
+        <v>525</v>
       </c>
       <c r="C130" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D130" t="n">
-        <v>5078.1</v>
+        <v>5658.57</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2915,17 +2915,17 @@
         <v>46218</v>
       </c>
       <c r="B131" t="n">
-        <v>2651</v>
+        <v>2641</v>
       </c>
       <c r="C131" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D131" t="n">
-        <v>363.7</v>
+        <v>1720.99</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2934,17 +2934,17 @@
         <v>46218</v>
       </c>
       <c r="B132" t="n">
-        <v>360</v>
+        <v>609</v>
       </c>
       <c r="C132" t="n">
         <v>8888</v>
       </c>
       <c r="D132" t="n">
-        <v>1594.84</v>
+        <v>886.1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2953,17 +2953,17 @@
         <v>46218</v>
       </c>
       <c r="B133" t="n">
-        <v>2582</v>
+        <v>619</v>
       </c>
       <c r="C133" t="n">
         <v>8888</v>
       </c>
       <c r="D133" t="n">
-        <v>379.33</v>
+        <v>2330.47</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2972,17 +2972,17 @@
         <v>46218</v>
       </c>
       <c r="B134" t="n">
-        <v>1756</v>
+        <v>2697</v>
       </c>
       <c r="C134" t="n">
         <v>8888</v>
       </c>
       <c r="D134" t="n">
-        <v>1715.26</v>
+        <v>418.65</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2991,13 +2991,13 @@
         <v>46218</v>
       </c>
       <c r="B135" t="n">
-        <v>1254</v>
+        <v>58</v>
       </c>
       <c r="C135" t="n">
         <v>8888</v>
       </c>
       <c r="D135" t="n">
-        <v>855.76</v>
+        <v>1123.87</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -3010,17 +3010,17 @@
         <v>46218</v>
       </c>
       <c r="B136" t="n">
-        <v>1289</v>
+        <v>358</v>
       </c>
       <c r="C136" t="n">
         <v>8888</v>
       </c>
       <c r="D136" t="n">
-        <v>2396.98</v>
+        <v>1675.95</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3029,17 +3029,17 @@
         <v>46218</v>
       </c>
       <c r="B137" t="n">
-        <v>2015</v>
+        <v>2431</v>
       </c>
       <c r="C137" t="n">
         <v>8888</v>
       </c>
       <c r="D137" t="n">
-        <v>315.69</v>
+        <v>266.89</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3048,17 +3048,17 @@
         <v>46218</v>
       </c>
       <c r="B138" t="n">
-        <v>1064</v>
+        <v>285</v>
       </c>
       <c r="C138" t="n">
         <v>8888</v>
       </c>
       <c r="D138" t="n">
-        <v>1274.3</v>
+        <v>2090.81</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3067,17 +3067,17 @@
         <v>46218</v>
       </c>
       <c r="B139" t="n">
-        <v>2698</v>
+        <v>1102</v>
       </c>
       <c r="C139" t="n">
         <v>8888</v>
       </c>
       <c r="D139" t="n">
-        <v>552.15</v>
+        <v>1119.32</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3086,17 +3086,17 @@
         <v>46218</v>
       </c>
       <c r="B140" t="n">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="C140" t="n">
         <v>8888</v>
       </c>
       <c r="D140" t="n">
-        <v>3035.38</v>
+        <v>11881.87</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3105,17 +3105,17 @@
         <v>46218</v>
       </c>
       <c r="B141" t="n">
-        <v>664</v>
+        <v>1137</v>
       </c>
       <c r="C141" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D141" t="n">
-        <v>4973.15</v>
+        <v>1370.86</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3130,7 @@
         <v>1929</v>
       </c>
       <c r="D142" t="n">
-        <v>521.79</v>
+        <v>2066.36</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -3143,17 +3143,17 @@
         <v>46218</v>
       </c>
       <c r="B143" t="n">
-        <v>2584</v>
+        <v>1756</v>
       </c>
       <c r="C143" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D143" t="n">
-        <v>1852.83</v>
+        <v>5078.1</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3162,17 +3162,17 @@
         <v>46218</v>
       </c>
       <c r="B144" t="n">
-        <v>2641</v>
+        <v>2651</v>
       </c>
       <c r="C144" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D144" t="n">
-        <v>820</v>
+        <v>363.7</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3181,17 +3181,17 @@
         <v>46218</v>
       </c>
       <c r="B145" t="n">
-        <v>816</v>
+        <v>360</v>
       </c>
       <c r="C145" t="n">
         <v>8888</v>
       </c>
       <c r="D145" t="n">
-        <v>438.24</v>
+        <v>1594.84</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3200,17 +3200,17 @@
         <v>46218</v>
       </c>
       <c r="B146" t="n">
-        <v>285</v>
+        <v>2582</v>
       </c>
       <c r="C146" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D146" t="n">
-        <v>364.99</v>
+        <v>379.33</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3219,17 +3219,17 @@
         <v>46218</v>
       </c>
       <c r="B147" t="n">
-        <v>2114</v>
+        <v>1756</v>
       </c>
       <c r="C147" t="n">
         <v>8888</v>
       </c>
       <c r="D147" t="n">
-        <v>2726.04</v>
+        <v>1715.26</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3238,17 +3238,17 @@
         <v>46218</v>
       </c>
       <c r="B148" t="n">
-        <v>953</v>
+        <v>1254</v>
       </c>
       <c r="C148" t="n">
         <v>8888</v>
       </c>
       <c r="D148" t="n">
-        <v>2618.89</v>
+        <v>855.76</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3257,17 +3257,17 @@
         <v>46218</v>
       </c>
       <c r="B149" t="n">
-        <v>1102</v>
+        <v>1289</v>
       </c>
       <c r="C149" t="n">
         <v>8888</v>
       </c>
       <c r="D149" t="n">
-        <v>2344.41</v>
+        <v>2396.98</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3276,13 +3276,13 @@
         <v>46218</v>
       </c>
       <c r="B150" t="n">
-        <v>619</v>
+        <v>2015</v>
       </c>
       <c r="C150" t="n">
         <v>8888</v>
       </c>
       <c r="D150" t="n">
-        <v>2021.67</v>
+        <v>315.69</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -3295,17 +3295,17 @@
         <v>46218</v>
       </c>
       <c r="B151" t="n">
-        <v>1465</v>
+        <v>1064</v>
       </c>
       <c r="C151" t="n">
         <v>8888</v>
       </c>
       <c r="D151" t="n">
-        <v>3504</v>
+        <v>1274.3</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3314,17 +3314,17 @@
         <v>46218</v>
       </c>
       <c r="B152" t="n">
-        <v>2767</v>
+        <v>2698</v>
       </c>
       <c r="C152" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D152" t="n">
-        <v>1135.64</v>
+        <v>552.15</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3333,13 +3333,13 @@
         <v>46218</v>
       </c>
       <c r="B153" t="n">
-        <v>2245</v>
+        <v>629</v>
       </c>
       <c r="C153" t="n">
         <v>8888</v>
       </c>
       <c r="D153" t="n">
-        <v>427.51</v>
+        <v>3035.38</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -3352,13 +3352,13 @@
         <v>46218</v>
       </c>
       <c r="B154" t="n">
-        <v>2197</v>
+        <v>664</v>
       </c>
       <c r="C154" t="n">
         <v>8888</v>
       </c>
       <c r="D154" t="n">
-        <v>1085.45</v>
+        <v>4973.15</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -3371,17 +3371,17 @@
         <v>46218</v>
       </c>
       <c r="B155" t="n">
-        <v>2657</v>
+        <v>2584</v>
       </c>
       <c r="C155" t="n">
         <v>8888</v>
       </c>
       <c r="D155" t="n">
-        <v>1187.68</v>
+        <v>1852.83</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3390,17 +3390,17 @@
         <v>46218</v>
       </c>
       <c r="B156" t="n">
-        <v>1277</v>
+        <v>2641</v>
       </c>
       <c r="C156" t="n">
         <v>8888</v>
       </c>
       <c r="D156" t="n">
-        <v>1949</v>
+        <v>820</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3409,17 +3409,17 @@
         <v>46218</v>
       </c>
       <c r="B157" t="n">
-        <v>131</v>
+        <v>429</v>
       </c>
       <c r="C157" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D157" t="n">
-        <v>1268.57</v>
+        <v>2593.49</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3428,17 +3428,17 @@
         <v>46218</v>
       </c>
       <c r="B158" t="n">
-        <v>2692</v>
+        <v>816</v>
       </c>
       <c r="C158" t="n">
         <v>8888</v>
       </c>
       <c r="D158" t="n">
-        <v>731.28</v>
+        <v>438.24</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3447,17 +3447,17 @@
         <v>46218</v>
       </c>
       <c r="B159" t="n">
-        <v>1317</v>
+        <v>2359</v>
       </c>
       <c r="C159" t="n">
-        <v>3179</v>
+        <v>8888</v>
       </c>
       <c r="D159" t="n">
-        <v>991.6799999999999</v>
+        <v>381.95</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3466,17 +3466,17 @@
         <v>46218</v>
       </c>
       <c r="B160" t="n">
-        <v>1993</v>
+        <v>285</v>
       </c>
       <c r="C160" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D160" t="n">
-        <v>2875.39</v>
+        <v>364.99</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3485,13 +3485,13 @@
         <v>46218</v>
       </c>
       <c r="B161" t="n">
-        <v>1632</v>
+        <v>2114</v>
       </c>
       <c r="C161" t="n">
         <v>8888</v>
       </c>
       <c r="D161" t="n">
-        <v>564.55</v>
+        <v>2726.04</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -3504,17 +3504,17 @@
         <v>46218</v>
       </c>
       <c r="B162" t="n">
-        <v>1890</v>
+        <v>953</v>
       </c>
       <c r="C162" t="n">
-        <v>3449</v>
+        <v>8888</v>
       </c>
       <c r="D162" t="n">
-        <v>3590.04</v>
+        <v>2618.89</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3523,17 +3523,17 @@
         <v>46218</v>
       </c>
       <c r="B163" t="n">
-        <v>451</v>
+        <v>1102</v>
       </c>
       <c r="C163" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D163" t="n">
-        <v>445.58</v>
+        <v>2344.41</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3542,13 +3542,13 @@
         <v>46218</v>
       </c>
       <c r="B164" t="n">
-        <v>2749</v>
+        <v>619</v>
       </c>
       <c r="C164" t="n">
         <v>8888</v>
       </c>
       <c r="D164" t="n">
-        <v>1860.64</v>
+        <v>2021.67</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -3561,17 +3561,17 @@
         <v>46218</v>
       </c>
       <c r="B165" t="n">
-        <v>1117</v>
+        <v>1465</v>
       </c>
       <c r="C165" t="n">
         <v>8888</v>
       </c>
       <c r="D165" t="n">
-        <v>342.2</v>
+        <v>3504</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3580,17 +3580,17 @@
         <v>46218</v>
       </c>
       <c r="B166" t="n">
-        <v>1478</v>
+        <v>2767</v>
       </c>
       <c r="C166" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D166" t="n">
-        <v>875.34</v>
+        <v>1135.64</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3599,13 +3599,13 @@
         <v>46218</v>
       </c>
       <c r="B167" t="n">
-        <v>2491</v>
+        <v>2245</v>
       </c>
       <c r="C167" t="n">
         <v>8888</v>
       </c>
       <c r="D167" t="n">
-        <v>650.4299999999999</v>
+        <v>427.51</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -3618,17 +3618,17 @@
         <v>46218</v>
       </c>
       <c r="B168" t="n">
-        <v>2015</v>
+        <v>2197</v>
       </c>
       <c r="C168" t="n">
         <v>8888</v>
       </c>
       <c r="D168" t="n">
-        <v>4436.15</v>
+        <v>1085.45</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3637,17 +3637,17 @@
         <v>46218</v>
       </c>
       <c r="B169" t="n">
-        <v>1890</v>
+        <v>2657</v>
       </c>
       <c r="C169" t="n">
-        <v>1953</v>
+        <v>8888</v>
       </c>
       <c r="D169" t="n">
-        <v>500.92</v>
+        <v>2683.06</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3656,13 +3656,13 @@
         <v>46218</v>
       </c>
       <c r="B170" t="n">
-        <v>2782</v>
+        <v>1277</v>
       </c>
       <c r="C170" t="n">
         <v>8888</v>
       </c>
       <c r="D170" t="n">
-        <v>1786.32</v>
+        <v>1949</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -3675,13 +3675,13 @@
         <v>46218</v>
       </c>
       <c r="B171" t="n">
-        <v>483</v>
+        <v>131</v>
       </c>
       <c r="C171" t="n">
-        <v>841</v>
+        <v>27</v>
       </c>
       <c r="D171" t="n">
-        <v>1393.15</v>
+        <v>1268.57</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -3694,17 +3694,17 @@
         <v>46218</v>
       </c>
       <c r="B172" t="n">
-        <v>2133</v>
+        <v>2692</v>
       </c>
       <c r="C172" t="n">
-        <v>213</v>
+        <v>8888</v>
       </c>
       <c r="D172" t="n">
-        <v>526.8</v>
+        <v>731.28</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3713,13 +3713,13 @@
         <v>46218</v>
       </c>
       <c r="B173" t="n">
-        <v>351</v>
+        <v>1317</v>
       </c>
       <c r="C173" t="n">
-        <v>3009</v>
+        <v>3179</v>
       </c>
       <c r="D173" t="n">
-        <v>416.36</v>
+        <v>991.6799999999999</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -3732,17 +3732,17 @@
         <v>46218</v>
       </c>
       <c r="B174" t="n">
-        <v>2250</v>
+        <v>1993</v>
       </c>
       <c r="C174" t="n">
         <v>8888</v>
       </c>
       <c r="D174" t="n">
-        <v>709.46</v>
+        <v>2875.39</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3751,13 +3751,13 @@
         <v>46218</v>
       </c>
       <c r="B175" t="n">
-        <v>2648</v>
+        <v>1632</v>
       </c>
       <c r="C175" t="n">
         <v>8888</v>
       </c>
       <c r="D175" t="n">
-        <v>1873.52</v>
+        <v>564.55</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -3770,17 +3770,17 @@
         <v>46218</v>
       </c>
       <c r="B176" t="n">
-        <v>131</v>
+        <v>1890</v>
       </c>
       <c r="C176" t="n">
-        <v>8888</v>
+        <v>3449</v>
       </c>
       <c r="D176" t="n">
-        <v>1369.91</v>
+        <v>3590.04</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3789,13 +3789,13 @@
         <v>46218</v>
       </c>
       <c r="B177" t="n">
-        <v>2639</v>
+        <v>451</v>
       </c>
       <c r="C177" t="n">
-        <v>1953</v>
+        <v>3403</v>
       </c>
       <c r="D177" t="n">
-        <v>504.09</v>
+        <v>445.58</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -3808,17 +3808,17 @@
         <v>46218</v>
       </c>
       <c r="B178" t="n">
-        <v>2109</v>
+        <v>2749</v>
       </c>
       <c r="C178" t="n">
         <v>8888</v>
       </c>
       <c r="D178" t="n">
-        <v>2293.78</v>
+        <v>1860.64</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3827,17 +3827,17 @@
         <v>46218</v>
       </c>
       <c r="B179" t="n">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="C179" t="n">
         <v>8888</v>
       </c>
       <c r="D179" t="n">
-        <v>2919.53</v>
+        <v>342.2</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3846,17 +3846,17 @@
         <v>46218</v>
       </c>
       <c r="B180" t="n">
-        <v>2250</v>
+        <v>1478</v>
       </c>
       <c r="C180" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D180" t="n">
-        <v>1803.76</v>
+        <v>875.34</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3865,13 +3865,13 @@
         <v>46218</v>
       </c>
       <c r="B181" t="n">
-        <v>353</v>
+        <v>2491</v>
       </c>
       <c r="C181" t="n">
         <v>8888</v>
       </c>
       <c r="D181" t="n">
-        <v>108.6</v>
+        <v>650.4299999999999</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -3884,17 +3884,17 @@
         <v>46218</v>
       </c>
       <c r="B182" t="n">
-        <v>2698</v>
+        <v>2015</v>
       </c>
       <c r="C182" t="n">
-        <v>874</v>
+        <v>8888</v>
       </c>
       <c r="D182" t="n">
-        <v>1230.43</v>
+        <v>4436.15</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3903,17 +3903,17 @@
         <v>46218</v>
       </c>
       <c r="B183" t="n">
-        <v>42</v>
+        <v>1890</v>
       </c>
       <c r="C183" t="n">
-        <v>8888</v>
+        <v>1953</v>
       </c>
       <c r="D183" t="n">
-        <v>79947.14999999999</v>
+        <v>1674.57</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3922,13 +3922,13 @@
         <v>46218</v>
       </c>
       <c r="B184" t="n">
-        <v>772</v>
+        <v>2782</v>
       </c>
       <c r="C184" t="n">
         <v>8888</v>
       </c>
       <c r="D184" t="n">
-        <v>400.25</v>
+        <v>1786.32</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -3941,17 +3941,17 @@
         <v>46218</v>
       </c>
       <c r="B185" t="n">
-        <v>2728</v>
+        <v>483</v>
       </c>
       <c r="C185" t="n">
-        <v>8888</v>
+        <v>841</v>
       </c>
       <c r="D185" t="n">
-        <v>1397.07</v>
+        <v>1393.15</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3960,13 +3960,13 @@
         <v>46218</v>
       </c>
       <c r="B186" t="n">
-        <v>2716</v>
+        <v>2133</v>
       </c>
       <c r="C186" t="n">
-        <v>1929</v>
+        <v>213</v>
       </c>
       <c r="D186" t="n">
-        <v>750.4299999999999</v>
+        <v>526.8</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -3979,13 +3979,13 @@
         <v>46218</v>
       </c>
       <c r="B187" t="n">
-        <v>2716</v>
+        <v>351</v>
       </c>
       <c r="C187" t="n">
-        <v>977</v>
+        <v>3009</v>
       </c>
       <c r="D187" t="n">
-        <v>729.29</v>
+        <v>416.36</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -3998,13 +3998,13 @@
         <v>46218</v>
       </c>
       <c r="B188" t="n">
-        <v>1993</v>
+        <v>2250</v>
       </c>
       <c r="C188" t="n">
         <v>8888</v>
       </c>
       <c r="D188" t="n">
-        <v>456.62</v>
+        <v>709.46</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -4017,15 +4017,319 @@
         <v>46218</v>
       </c>
       <c r="B189" t="n">
+        <v>2648</v>
+      </c>
+      <c r="C189" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D189" t="n">
+        <v>1873.52</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B190" t="n">
+        <v>131</v>
+      </c>
+      <c r="C190" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D190" t="n">
+        <v>1369.91</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B191" t="n">
+        <v>2790</v>
+      </c>
+      <c r="C191" t="n">
+        <v>1953</v>
+      </c>
+      <c r="D191" t="n">
+        <v>371.88</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B192" t="n">
+        <v>2639</v>
+      </c>
+      <c r="C192" t="n">
+        <v>1953</v>
+      </c>
+      <c r="D192" t="n">
+        <v>504.09</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B193" t="n">
+        <v>2109</v>
+      </c>
+      <c r="C193" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D193" t="n">
+        <v>2293.78</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B194" t="n">
+        <v>1116</v>
+      </c>
+      <c r="C194" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D194" t="n">
+        <v>2919.53</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B195" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C195" t="n">
+        <v>27</v>
+      </c>
+      <c r="D195" t="n">
+        <v>1803.76</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B196" t="n">
+        <v>353</v>
+      </c>
+      <c r="C196" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D196" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B197" t="n">
+        <v>2698</v>
+      </c>
+      <c r="C197" t="n">
+        <v>874</v>
+      </c>
+      <c r="D197" t="n">
+        <v>1230.43</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B198" t="n">
+        <v>42</v>
+      </c>
+      <c r="C198" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D198" t="n">
+        <v>79947.14999999999</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B199" t="n">
+        <v>772</v>
+      </c>
+      <c r="C199" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D199" t="n">
+        <v>400.25</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B200" t="n">
+        <v>2728</v>
+      </c>
+      <c r="C200" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D200" t="n">
+        <v>1397.07</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B201" t="n">
+        <v>2197</v>
+      </c>
+      <c r="C201" t="n">
+        <v>423</v>
+      </c>
+      <c r="D201" t="n">
+        <v>2267.61</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B202" t="n">
+        <v>2716</v>
+      </c>
+      <c r="C202" t="n">
+        <v>1929</v>
+      </c>
+      <c r="D202" t="n">
+        <v>750.4299999999999</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B203" t="n">
+        <v>2716</v>
+      </c>
+      <c r="C203" t="n">
+        <v>977</v>
+      </c>
+      <c r="D203" t="n">
+        <v>729.29</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B204" t="n">
+        <v>1993</v>
+      </c>
+      <c r="C204" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D204" t="n">
+        <v>456.62</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B205" t="n">
         <v>629</v>
       </c>
-      <c r="C189" t="n">
+      <c r="C205" t="n">
         <v>675</v>
       </c>
-      <c r="D189" t="n">
+      <c r="D205" t="n">
         <v>1054.76</v>
       </c>
-      <c r="E189" t="inlineStr">
+      <c r="E205" t="inlineStr">
         <is>
           <t>TELEMARKETING</t>
         </is>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E205"/>
+  <dimension ref="A1:E213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,17 +464,17 @@
         <v>46218</v>
       </c>
       <c r="B2" t="n">
-        <v>326</v>
+        <v>2507</v>
       </c>
       <c r="C2" t="n">
         <v>8888</v>
       </c>
       <c r="D2" t="n">
-        <v>406.97</v>
+        <v>1988.47</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -483,17 +483,17 @@
         <v>46218</v>
       </c>
       <c r="B3" t="n">
-        <v>1075</v>
+        <v>326</v>
       </c>
       <c r="C3" t="n">
-        <v>675</v>
+        <v>8888</v>
       </c>
       <c r="D3" t="n">
-        <v>638.4299999999999</v>
+        <v>406.97</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -502,17 +502,17 @@
         <v>46218</v>
       </c>
       <c r="B4" t="n">
-        <v>664</v>
+        <v>1075</v>
       </c>
       <c r="C4" t="n">
-        <v>8888</v>
+        <v>675</v>
       </c>
       <c r="D4" t="n">
-        <v>463.88</v>
+        <v>638.4299999999999</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -521,17 +521,17 @@
         <v>46218</v>
       </c>
       <c r="B5" t="n">
-        <v>1364</v>
+        <v>664</v>
       </c>
       <c r="C5" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D5" t="n">
-        <v>1300.54</v>
+        <v>463.88</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -540,17 +540,17 @@
         <v>46218</v>
       </c>
       <c r="B6" t="n">
-        <v>451</v>
+        <v>1364</v>
       </c>
       <c r="C6" t="n">
-        <v>8888</v>
+        <v>3403</v>
       </c>
       <c r="D6" t="n">
-        <v>1103.58</v>
+        <v>1300.54</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -559,17 +559,17 @@
         <v>46218</v>
       </c>
       <c r="B7" t="n">
-        <v>131</v>
+        <v>451</v>
       </c>
       <c r="C7" t="n">
         <v>8888</v>
       </c>
       <c r="D7" t="n">
-        <v>7071.12</v>
+        <v>1103.58</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
         <v>46218</v>
       </c>
       <c r="B8" t="n">
-        <v>1632</v>
+        <v>131</v>
       </c>
       <c r="C8" t="n">
         <v>8888</v>
       </c>
       <c r="D8" t="n">
-        <v>768.84</v>
+        <v>7071.12</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -597,17 +597,17 @@
         <v>46218</v>
       </c>
       <c r="B9" t="n">
-        <v>2015</v>
+        <v>1632</v>
       </c>
       <c r="C9" t="n">
-        <v>2571</v>
+        <v>8888</v>
       </c>
       <c r="D9" t="n">
-        <v>3147.53</v>
+        <v>768.84</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -616,13 +616,13 @@
         <v>46218</v>
       </c>
       <c r="B10" t="n">
-        <v>1289</v>
+        <v>2015</v>
       </c>
       <c r="C10" t="n">
-        <v>1929</v>
+        <v>2571</v>
       </c>
       <c r="D10" t="n">
-        <v>727.05</v>
+        <v>3147.53</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -635,13 +635,13 @@
         <v>46218</v>
       </c>
       <c r="B11" t="n">
-        <v>609</v>
+        <v>1289</v>
       </c>
       <c r="C11" t="n">
-        <v>3179</v>
+        <v>1929</v>
       </c>
       <c r="D11" t="n">
-        <v>2603.16</v>
+        <v>727.05</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -654,17 +654,17 @@
         <v>46218</v>
       </c>
       <c r="B12" t="n">
-        <v>2211</v>
+        <v>609</v>
       </c>
       <c r="C12" t="n">
-        <v>8888</v>
+        <v>3179</v>
       </c>
       <c r="D12" t="n">
-        <v>2190.93</v>
+        <v>2603.16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -673,13 +673,13 @@
         <v>46218</v>
       </c>
       <c r="B13" t="n">
-        <v>2660</v>
+        <v>2211</v>
       </c>
       <c r="C13" t="n">
         <v>8888</v>
       </c>
       <c r="D13" t="n">
-        <v>875.61</v>
+        <v>2706.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -692,13 +692,13 @@
         <v>46218</v>
       </c>
       <c r="B14" t="n">
-        <v>890</v>
+        <v>2660</v>
       </c>
       <c r="C14" t="n">
         <v>8888</v>
       </c>
       <c r="D14" t="n">
-        <v>1051.23</v>
+        <v>875.61</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -711,13 +711,13 @@
         <v>46218</v>
       </c>
       <c r="B15" t="n">
-        <v>2190</v>
+        <v>890</v>
       </c>
       <c r="C15" t="n">
         <v>8888</v>
       </c>
       <c r="D15" t="n">
-        <v>1307.13</v>
+        <v>1051.23</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
         <v>46218</v>
       </c>
       <c r="B16" t="n">
-        <v>2651</v>
+        <v>2190</v>
       </c>
       <c r="C16" t="n">
         <v>8888</v>
       </c>
       <c r="D16" t="n">
-        <v>660.95</v>
+        <v>1307.13</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
         <v>46218</v>
       </c>
       <c r="B17" t="n">
-        <v>2118</v>
+        <v>2651</v>
       </c>
       <c r="C17" t="n">
         <v>8888</v>
       </c>
       <c r="D17" t="n">
-        <v>5535.71</v>
+        <v>660.95</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -768,13 +768,13 @@
         <v>46218</v>
       </c>
       <c r="B18" t="n">
-        <v>2507</v>
+        <v>2118</v>
       </c>
       <c r="C18" t="n">
         <v>8888</v>
       </c>
       <c r="D18" t="n">
-        <v>1174.1</v>
+        <v>5535.71</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>8888</v>
       </c>
       <c r="D19" t="n">
-        <v>892.66</v>
+        <v>1441.76</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -844,17 +844,17 @@
         <v>46218</v>
       </c>
       <c r="B22" t="n">
-        <v>2133</v>
+        <v>1137</v>
       </c>
       <c r="C22" t="n">
-        <v>691</v>
+        <v>8888</v>
       </c>
       <c r="D22" t="n">
-        <v>2058.93</v>
+        <v>359.06</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -863,17 +863,17 @@
         <v>46218</v>
       </c>
       <c r="B23" t="n">
-        <v>452</v>
+        <v>2133</v>
       </c>
       <c r="C23" t="n">
-        <v>8888</v>
+        <v>691</v>
       </c>
       <c r="D23" t="n">
-        <v>1832.74</v>
+        <v>2058.93</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
         <v>46218</v>
       </c>
       <c r="B24" t="n">
-        <v>2250</v>
+        <v>452</v>
       </c>
       <c r="C24" t="n">
         <v>8888</v>
       </c>
       <c r="D24" t="n">
-        <v>1686.37</v>
+        <v>1832.74</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -901,13 +901,13 @@
         <v>46218</v>
       </c>
       <c r="B25" t="n">
-        <v>931</v>
+        <v>1632</v>
       </c>
       <c r="C25" t="n">
         <v>423</v>
       </c>
       <c r="D25" t="n">
-        <v>492.34</v>
+        <v>2811.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -920,13 +920,13 @@
         <v>46218</v>
       </c>
       <c r="B26" t="n">
-        <v>951</v>
+        <v>2250</v>
       </c>
       <c r="C26" t="n">
         <v>8888</v>
       </c>
       <c r="D26" t="n">
-        <v>2171.08</v>
+        <v>1686.37</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -939,17 +939,17 @@
         <v>46218</v>
       </c>
       <c r="B27" t="n">
-        <v>2695</v>
+        <v>931</v>
       </c>
       <c r="C27" t="n">
-        <v>8888</v>
+        <v>423</v>
       </c>
       <c r="D27" t="n">
-        <v>411.42</v>
+        <v>492.34</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -958,13 +958,13 @@
         <v>46218</v>
       </c>
       <c r="B28" t="n">
-        <v>525</v>
+        <v>951</v>
       </c>
       <c r="C28" t="n">
         <v>8888</v>
       </c>
       <c r="D28" t="n">
-        <v>408.25</v>
+        <v>2171.08</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -977,17 +977,17 @@
         <v>46218</v>
       </c>
       <c r="B29" t="n">
-        <v>1808</v>
+        <v>2695</v>
       </c>
       <c r="C29" t="n">
         <v>8888</v>
       </c>
       <c r="D29" t="n">
-        <v>695.3200000000001</v>
+        <v>411.42</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -996,17 +996,17 @@
         <v>46218</v>
       </c>
       <c r="B30" t="n">
-        <v>1632</v>
+        <v>525</v>
       </c>
       <c r="C30" t="n">
-        <v>423</v>
+        <v>8888</v>
       </c>
       <c r="D30" t="n">
-        <v>1266.17</v>
+        <v>408.25</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1015,17 +1015,17 @@
         <v>46218</v>
       </c>
       <c r="B31" t="n">
-        <v>949</v>
+        <v>1808</v>
       </c>
       <c r="C31" t="n">
-        <v>1134</v>
+        <v>8888</v>
       </c>
       <c r="D31" t="n">
-        <v>30.46</v>
+        <v>695.3200000000001</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
         <v>46218</v>
       </c>
       <c r="B32" t="n">
-        <v>2499</v>
+        <v>609</v>
       </c>
       <c r="C32" t="n">
         <v>8888</v>
       </c>
       <c r="D32" t="n">
-        <v>261.63</v>
+        <v>1909.37</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
         <v>46218</v>
       </c>
       <c r="B33" t="n">
-        <v>58</v>
+        <v>949</v>
       </c>
       <c r="C33" t="n">
-        <v>8888</v>
+        <v>1134</v>
       </c>
       <c r="D33" t="n">
-        <v>499.11</v>
+        <v>30.46</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1072,13 +1072,13 @@
         <v>46218</v>
       </c>
       <c r="B34" t="n">
-        <v>2245</v>
+        <v>2499</v>
       </c>
       <c r="C34" t="n">
         <v>8888</v>
       </c>
       <c r="D34" t="n">
-        <v>2740.06</v>
+        <v>261.63</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1091,17 +1091,17 @@
         <v>46218</v>
       </c>
       <c r="B35" t="n">
-        <v>325</v>
+        <v>58</v>
       </c>
       <c r="C35" t="n">
         <v>8888</v>
       </c>
       <c r="D35" t="n">
-        <v>524.36</v>
+        <v>499.11</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1110,17 +1110,17 @@
         <v>46218</v>
       </c>
       <c r="B36" t="n">
-        <v>2383</v>
+        <v>2245</v>
       </c>
       <c r="C36" t="n">
         <v>8888</v>
       </c>
       <c r="D36" t="n">
-        <v>7926.02</v>
+        <v>2740.06</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1129,17 +1129,17 @@
         <v>46218</v>
       </c>
       <c r="B37" t="n">
-        <v>1117</v>
+        <v>325</v>
       </c>
       <c r="C37" t="n">
-        <v>1139</v>
+        <v>8888</v>
       </c>
       <c r="D37" t="n">
-        <v>916.72</v>
+        <v>871.14</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1148,17 +1148,17 @@
         <v>46218</v>
       </c>
       <c r="B38" t="n">
-        <v>2279</v>
+        <v>2383</v>
       </c>
       <c r="C38" t="n">
         <v>8888</v>
       </c>
       <c r="D38" t="n">
-        <v>712.66</v>
+        <v>7926.02</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1167,17 +1167,17 @@
         <v>46218</v>
       </c>
       <c r="B39" t="n">
-        <v>535</v>
+        <v>1117</v>
       </c>
       <c r="C39" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D39" t="n">
-        <v>4810</v>
+        <v>916.72</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1186,13 +1186,13 @@
         <v>46218</v>
       </c>
       <c r="B40" t="n">
-        <v>535</v>
+        <v>2279</v>
       </c>
       <c r="C40" t="n">
         <v>8888</v>
       </c>
       <c r="D40" t="n">
-        <v>1352.51</v>
+        <v>712.66</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1205,17 +1205,17 @@
         <v>46218</v>
       </c>
       <c r="B41" t="n">
-        <v>2678</v>
+        <v>535</v>
       </c>
       <c r="C41" t="n">
-        <v>1312</v>
+        <v>8888</v>
       </c>
       <c r="D41" t="n">
-        <v>364.96</v>
+        <v>5836.12</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1224,13 +1224,13 @@
         <v>46218</v>
       </c>
       <c r="B42" t="n">
-        <v>2345</v>
+        <v>535</v>
       </c>
       <c r="C42" t="n">
         <v>8888</v>
       </c>
       <c r="D42" t="n">
-        <v>863.16</v>
+        <v>1352.51</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1243,17 +1243,17 @@
         <v>46218</v>
       </c>
       <c r="B43" t="n">
-        <v>945</v>
+        <v>2678</v>
       </c>
       <c r="C43" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D43" t="n">
-        <v>21973.45</v>
+        <v>364.96</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PEDIDO ELETRÔNICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1262,17 +1262,17 @@
         <v>46218</v>
       </c>
       <c r="B44" t="n">
-        <v>438</v>
+        <v>2345</v>
       </c>
       <c r="C44" t="n">
         <v>8888</v>
       </c>
       <c r="D44" t="n">
-        <v>220.06</v>
+        <v>863.16</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1281,17 +1281,17 @@
         <v>46218</v>
       </c>
       <c r="B45" t="n">
-        <v>353</v>
+        <v>945</v>
       </c>
       <c r="C45" t="n">
-        <v>3179</v>
+        <v>8888</v>
       </c>
       <c r="D45" t="n">
-        <v>495.84</v>
+        <v>27337.21</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>PEDIDO ELETRÔNICO</t>
         </is>
       </c>
     </row>
@@ -1300,17 +1300,17 @@
         <v>46218</v>
       </c>
       <c r="B46" t="n">
-        <v>1293</v>
+        <v>2686</v>
       </c>
       <c r="C46" t="n">
         <v>8888</v>
       </c>
       <c r="D46" t="n">
-        <v>3129.07</v>
+        <v>684.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1319,13 +1319,13 @@
         <v>46218</v>
       </c>
       <c r="B47" t="n">
-        <v>2279</v>
+        <v>438</v>
       </c>
       <c r="C47" t="n">
         <v>8888</v>
       </c>
       <c r="D47" t="n">
-        <v>2753.96</v>
+        <v>220.06</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1338,17 +1338,17 @@
         <v>46218</v>
       </c>
       <c r="B48" t="n">
-        <v>1137</v>
+        <v>353</v>
       </c>
       <c r="C48" t="n">
-        <v>8888</v>
+        <v>3179</v>
       </c>
       <c r="D48" t="n">
-        <v>1947.93</v>
+        <v>495.84</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1357,17 +1357,17 @@
         <v>46218</v>
       </c>
       <c r="B49" t="n">
-        <v>374</v>
+        <v>1293</v>
       </c>
       <c r="C49" t="n">
         <v>8888</v>
       </c>
       <c r="D49" t="n">
-        <v>712.71</v>
+        <v>3129.07</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1376,17 +1376,17 @@
         <v>46218</v>
       </c>
       <c r="B50" t="n">
-        <v>2686</v>
+        <v>2279</v>
       </c>
       <c r="C50" t="n">
         <v>8888</v>
       </c>
       <c r="D50" t="n">
-        <v>332.6</v>
+        <v>2753.96</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1395,17 +1395,17 @@
         <v>46218</v>
       </c>
       <c r="B51" t="n">
-        <v>2793</v>
+        <v>1137</v>
       </c>
       <c r="C51" t="n">
-        <v>977</v>
+        <v>8888</v>
       </c>
       <c r="D51" t="n">
-        <v>695.72</v>
+        <v>1947.93</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1420,11 +1420,11 @@
         <v>8888</v>
       </c>
       <c r="D52" t="n">
-        <v>22.62</v>
+        <v>1390.6</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1433,17 +1433,17 @@
         <v>46218</v>
       </c>
       <c r="B53" t="n">
-        <v>664</v>
+        <v>2793</v>
       </c>
       <c r="C53" t="n">
-        <v>8888</v>
+        <v>977</v>
       </c>
       <c r="D53" t="n">
-        <v>1510.56</v>
+        <v>695.72</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1452,13 +1452,13 @@
         <v>46218</v>
       </c>
       <c r="B54" t="n">
-        <v>703</v>
+        <v>2802</v>
       </c>
       <c r="C54" t="n">
         <v>8888</v>
       </c>
       <c r="D54" t="n">
-        <v>12155.46</v>
+        <v>1264.57</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -1471,17 +1471,17 @@
         <v>46218</v>
       </c>
       <c r="B55" t="n">
-        <v>1937</v>
+        <v>374</v>
       </c>
       <c r="C55" t="n">
         <v>8888</v>
       </c>
       <c r="D55" t="n">
-        <v>1032.73</v>
+        <v>44.6</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1490,13 +1490,13 @@
         <v>46218</v>
       </c>
       <c r="B56" t="n">
-        <v>451</v>
+        <v>664</v>
       </c>
       <c r="C56" t="n">
         <v>8888</v>
       </c>
       <c r="D56" t="n">
-        <v>368.93</v>
+        <v>1510.56</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -1509,17 +1509,17 @@
         <v>46218</v>
       </c>
       <c r="B57" t="n">
-        <v>1756</v>
+        <v>703</v>
       </c>
       <c r="C57" t="n">
         <v>8888</v>
       </c>
       <c r="D57" t="n">
-        <v>996.17</v>
+        <v>12155.46</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1528,17 +1528,17 @@
         <v>46218</v>
       </c>
       <c r="B58" t="n">
-        <v>1956</v>
+        <v>1937</v>
       </c>
       <c r="C58" t="n">
         <v>8888</v>
       </c>
       <c r="D58" t="n">
-        <v>4557.34</v>
+        <v>1032.73</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1547,13 +1547,13 @@
         <v>46218</v>
       </c>
       <c r="B59" t="n">
-        <v>925</v>
+        <v>451</v>
       </c>
       <c r="C59" t="n">
         <v>8888</v>
       </c>
       <c r="D59" t="n">
-        <v>651.59</v>
+        <v>368.93</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -1566,17 +1566,17 @@
         <v>46218</v>
       </c>
       <c r="B60" t="n">
-        <v>2631</v>
+        <v>1756</v>
       </c>
       <c r="C60" t="n">
-        <v>2853</v>
+        <v>8888</v>
       </c>
       <c r="D60" t="n">
-        <v>509.88</v>
+        <v>996.17</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1585,17 +1585,17 @@
         <v>46218</v>
       </c>
       <c r="B61" t="n">
-        <v>2648</v>
+        <v>1956</v>
       </c>
       <c r="C61" t="n">
         <v>8888</v>
       </c>
       <c r="D61" t="n">
-        <v>1594.42</v>
+        <v>4557.34</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1604,17 +1604,17 @@
         <v>46218</v>
       </c>
       <c r="B62" t="n">
-        <v>2714</v>
+        <v>925</v>
       </c>
       <c r="C62" t="n">
-        <v>519</v>
+        <v>8888</v>
       </c>
       <c r="D62" t="n">
-        <v>61939.22</v>
+        <v>651.59</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
         <v>46218</v>
       </c>
       <c r="B63" t="n">
-        <v>483</v>
+        <v>2631</v>
       </c>
       <c r="C63" t="n">
-        <v>8888</v>
+        <v>2853</v>
       </c>
       <c r="D63" t="n">
-        <v>6625.87</v>
+        <v>509.88</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1642,17 +1642,17 @@
         <v>46218</v>
       </c>
       <c r="B64" t="n">
-        <v>1075</v>
+        <v>2648</v>
       </c>
       <c r="C64" t="n">
         <v>8888</v>
       </c>
       <c r="D64" t="n">
-        <v>11607.79</v>
+        <v>1594.42</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1661,17 +1661,17 @@
         <v>46218</v>
       </c>
       <c r="B65" t="n">
-        <v>629</v>
+        <v>2714</v>
       </c>
       <c r="C65" t="n">
-        <v>8888</v>
+        <v>519</v>
       </c>
       <c r="D65" t="n">
-        <v>9233.719999999999</v>
+        <v>61939.22</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1680,17 +1680,17 @@
         <v>46218</v>
       </c>
       <c r="B66" t="n">
-        <v>1983</v>
+        <v>483</v>
       </c>
       <c r="C66" t="n">
-        <v>841</v>
+        <v>8888</v>
       </c>
       <c r="D66" t="n">
-        <v>243.92</v>
+        <v>6625.87</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1699,17 +1699,17 @@
         <v>46218</v>
       </c>
       <c r="B67" t="n">
-        <v>1137</v>
+        <v>1075</v>
       </c>
       <c r="C67" t="n">
         <v>8888</v>
       </c>
       <c r="D67" t="n">
-        <v>3578.51</v>
+        <v>11607.79</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
         <v>46218</v>
       </c>
       <c r="B68" t="n">
-        <v>2651</v>
+        <v>629</v>
       </c>
       <c r="C68" t="n">
         <v>8888</v>
       </c>
       <c r="D68" t="n">
-        <v>1296.58</v>
+        <v>9233.719999999999</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1737,13 +1737,13 @@
         <v>46218</v>
       </c>
       <c r="B69" t="n">
-        <v>1956</v>
+        <v>1983</v>
       </c>
       <c r="C69" t="n">
-        <v>423</v>
+        <v>841</v>
       </c>
       <c r="D69" t="n">
-        <v>455.37</v>
+        <v>243.92</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -1756,13 +1756,13 @@
         <v>46218</v>
       </c>
       <c r="B70" t="n">
-        <v>2709</v>
+        <v>1137</v>
       </c>
       <c r="C70" t="n">
         <v>8888</v>
       </c>
       <c r="D70" t="n">
-        <v>547.6900000000001</v>
+        <v>3578.51</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -1775,17 +1775,17 @@
         <v>46218</v>
       </c>
       <c r="B71" t="n">
-        <v>2026</v>
+        <v>2651</v>
       </c>
       <c r="C71" t="n">
         <v>8888</v>
       </c>
       <c r="D71" t="n">
-        <v>2237.62</v>
+        <v>1296.58</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1794,17 +1794,17 @@
         <v>46218</v>
       </c>
       <c r="B72" t="n">
-        <v>2789</v>
+        <v>1956</v>
       </c>
       <c r="C72" t="n">
-        <v>8888</v>
+        <v>423</v>
       </c>
       <c r="D72" t="n">
-        <v>747.77</v>
+        <v>1416.35</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1813,17 +1813,17 @@
         <v>46218</v>
       </c>
       <c r="B73" t="n">
-        <v>89</v>
+        <v>2709</v>
       </c>
       <c r="C73" t="n">
-        <v>13148</v>
+        <v>8888</v>
       </c>
       <c r="D73" t="n">
-        <v>1883.74</v>
+        <v>547.6900000000001</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1832,17 +1832,17 @@
         <v>46218</v>
       </c>
       <c r="B74" t="n">
-        <v>2709</v>
+        <v>1308</v>
       </c>
       <c r="C74" t="n">
-        <v>2220</v>
+        <v>8888</v>
       </c>
       <c r="D74" t="n">
-        <v>390.19</v>
+        <v>1460.53</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1851,17 +1851,17 @@
         <v>46218</v>
       </c>
       <c r="B75" t="n">
-        <v>2345</v>
+        <v>2026</v>
       </c>
       <c r="C75" t="n">
         <v>8888</v>
       </c>
       <c r="D75" t="n">
-        <v>748.86</v>
+        <v>2237.62</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1870,17 +1870,17 @@
         <v>46218</v>
       </c>
       <c r="B76" t="n">
-        <v>1308</v>
+        <v>2789</v>
       </c>
       <c r="C76" t="n">
         <v>8888</v>
       </c>
       <c r="D76" t="n">
-        <v>276.16</v>
+        <v>747.77</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1889,13 +1889,13 @@
         <v>46218</v>
       </c>
       <c r="B77" t="n">
-        <v>360</v>
+        <v>89</v>
       </c>
       <c r="C77" t="n">
-        <v>546</v>
+        <v>13148</v>
       </c>
       <c r="D77" t="n">
-        <v>1609.68</v>
+        <v>1883.74</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -1908,17 +1908,17 @@
         <v>46218</v>
       </c>
       <c r="B78" t="n">
-        <v>2308</v>
+        <v>2709</v>
       </c>
       <c r="C78" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D78" t="n">
-        <v>488.69</v>
+        <v>390.19</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1927,17 +1927,17 @@
         <v>46218</v>
       </c>
       <c r="B79" t="n">
-        <v>2211</v>
+        <v>2345</v>
       </c>
       <c r="C79" t="n">
-        <v>874</v>
+        <v>8888</v>
       </c>
       <c r="D79" t="n">
-        <v>1526.94</v>
+        <v>748.86</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1946,13 +1946,13 @@
         <v>46218</v>
       </c>
       <c r="B80" t="n">
-        <v>559</v>
+        <v>569</v>
       </c>
       <c r="C80" t="n">
         <v>8888</v>
       </c>
       <c r="D80" t="n">
-        <v>859.92</v>
+        <v>995.33</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -1965,17 +1965,17 @@
         <v>46218</v>
       </c>
       <c r="B81" t="n">
-        <v>569</v>
+        <v>360</v>
       </c>
       <c r="C81" t="n">
-        <v>8888</v>
+        <v>546</v>
       </c>
       <c r="D81" t="n">
-        <v>673.01</v>
+        <v>1609.68</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1984,13 +1984,13 @@
         <v>46218</v>
       </c>
       <c r="B82" t="n">
-        <v>890</v>
+        <v>2308</v>
       </c>
       <c r="C82" t="n">
         <v>8888</v>
       </c>
       <c r="D82" t="n">
-        <v>387.2</v>
+        <v>488.69</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2003,17 +2003,17 @@
         <v>46218</v>
       </c>
       <c r="B83" t="n">
-        <v>1063</v>
+        <v>2211</v>
       </c>
       <c r="C83" t="n">
-        <v>8888</v>
+        <v>874</v>
       </c>
       <c r="D83" t="n">
-        <v>4487.11</v>
+        <v>1526.94</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2022,17 +2022,17 @@
         <v>46218</v>
       </c>
       <c r="B84" t="n">
-        <v>2279</v>
+        <v>559</v>
       </c>
       <c r="C84" t="n">
-        <v>1139</v>
+        <v>8888</v>
       </c>
       <c r="D84" t="n">
-        <v>652.51</v>
+        <v>859.92</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2041,17 +2041,17 @@
         <v>46218</v>
       </c>
       <c r="B85" t="n">
-        <v>1299</v>
+        <v>890</v>
       </c>
       <c r="C85" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D85" t="n">
-        <v>1435.52</v>
+        <v>387.2</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2060,17 +2060,17 @@
         <v>46218</v>
       </c>
       <c r="B86" t="n">
-        <v>1478</v>
+        <v>2768</v>
       </c>
       <c r="C86" t="n">
-        <v>675</v>
+        <v>8888</v>
       </c>
       <c r="D86" t="n">
-        <v>1600.01</v>
+        <v>6523.26</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2079,17 +2079,17 @@
         <v>46218</v>
       </c>
       <c r="B87" t="n">
-        <v>285</v>
+        <v>1063</v>
       </c>
       <c r="C87" t="n">
         <v>8888</v>
       </c>
       <c r="D87" t="n">
-        <v>3349.8</v>
+        <v>4487.11</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2098,17 +2098,17 @@
         <v>46218</v>
       </c>
       <c r="B88" t="n">
-        <v>1983</v>
+        <v>2279</v>
       </c>
       <c r="C88" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D88" t="n">
-        <v>2451.28</v>
+        <v>652.51</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2117,13 +2117,13 @@
         <v>46218</v>
       </c>
       <c r="B89" t="n">
-        <v>477</v>
+        <v>1299</v>
       </c>
       <c r="C89" t="n">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="D89" t="n">
-        <v>1540.55</v>
+        <v>1435.52</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -2136,17 +2136,17 @@
         <v>46218</v>
       </c>
       <c r="B90" t="n">
-        <v>1063</v>
+        <v>1478</v>
       </c>
       <c r="C90" t="n">
-        <v>8888</v>
+        <v>675</v>
       </c>
       <c r="D90" t="n">
-        <v>2549.86</v>
+        <v>1600.01</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2155,13 +2155,13 @@
         <v>46218</v>
       </c>
       <c r="B91" t="n">
-        <v>424</v>
+        <v>285</v>
       </c>
       <c r="C91" t="n">
         <v>8888</v>
       </c>
       <c r="D91" t="n">
-        <v>1035.17</v>
+        <v>3349.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -2174,17 +2174,17 @@
         <v>46218</v>
       </c>
       <c r="B92" t="n">
-        <v>675</v>
+        <v>1983</v>
       </c>
       <c r="C92" t="n">
         <v>8888</v>
       </c>
       <c r="D92" t="n">
-        <v>616.73</v>
+        <v>2451.28</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2193,17 +2193,17 @@
         <v>46218</v>
       </c>
       <c r="B93" t="n">
-        <v>2768</v>
+        <v>477</v>
       </c>
       <c r="C93" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D93" t="n">
-        <v>5607.14</v>
+        <v>1540.55</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2212,17 +2212,17 @@
         <v>46218</v>
       </c>
       <c r="B94" t="n">
-        <v>1993</v>
+        <v>1063</v>
       </c>
       <c r="C94" t="n">
         <v>8888</v>
       </c>
       <c r="D94" t="n">
-        <v>362.63</v>
+        <v>2549.86</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2231,17 +2231,17 @@
         <v>46218</v>
       </c>
       <c r="B95" t="n">
-        <v>1465</v>
+        <v>424</v>
       </c>
       <c r="C95" t="n">
         <v>8888</v>
       </c>
       <c r="D95" t="n">
-        <v>3373.83</v>
+        <v>1035.17</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2250,17 +2250,17 @@
         <v>46218</v>
       </c>
       <c r="B96" t="n">
-        <v>89</v>
+        <v>675</v>
       </c>
       <c r="C96" t="n">
         <v>8888</v>
       </c>
       <c r="D96" t="n">
-        <v>479</v>
+        <v>616.73</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2269,17 +2269,17 @@
         <v>46218</v>
       </c>
       <c r="B97" t="n">
-        <v>595</v>
+        <v>1993</v>
       </c>
       <c r="C97" t="n">
         <v>8888</v>
       </c>
       <c r="D97" t="n">
-        <v>18084.5</v>
+        <v>362.63</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
         <v>46218</v>
       </c>
       <c r="B98" t="n">
-        <v>2696</v>
+        <v>1465</v>
       </c>
       <c r="C98" t="n">
-        <v>1954</v>
+        <v>8888</v>
       </c>
       <c r="D98" t="n">
-        <v>1597.76</v>
+        <v>3373.83</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2307,17 +2307,17 @@
         <v>46218</v>
       </c>
       <c r="B99" t="n">
-        <v>360</v>
+        <v>89</v>
       </c>
       <c r="C99" t="n">
         <v>8888</v>
       </c>
       <c r="D99" t="n">
-        <v>4596.89</v>
+        <v>479</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2326,17 +2326,17 @@
         <v>46218</v>
       </c>
       <c r="B100" t="n">
-        <v>1465</v>
+        <v>595</v>
       </c>
       <c r="C100" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D100" t="n">
-        <v>777.2</v>
+        <v>18084.5</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2345,17 +2345,17 @@
         <v>46218</v>
       </c>
       <c r="B101" t="n">
-        <v>947</v>
+        <v>2696</v>
       </c>
       <c r="C101" t="n">
-        <v>8888</v>
+        <v>1954</v>
       </c>
       <c r="D101" t="n">
-        <v>2087.97</v>
+        <v>1597.76</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>PEDIDO ELETRÔNICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2364,17 +2364,17 @@
         <v>46218</v>
       </c>
       <c r="B102" t="n">
-        <v>2178</v>
+        <v>360</v>
       </c>
       <c r="C102" t="n">
         <v>8888</v>
       </c>
       <c r="D102" t="n">
-        <v>619.92</v>
+        <v>4596.89</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2383,13 +2383,13 @@
         <v>46218</v>
       </c>
       <c r="B103" t="n">
-        <v>630</v>
+        <v>1465</v>
       </c>
       <c r="C103" t="n">
-        <v>1929</v>
+        <v>3403</v>
       </c>
       <c r="D103" t="n">
-        <v>1801.63</v>
+        <v>777.2</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -2402,17 +2402,17 @@
         <v>46218</v>
       </c>
       <c r="B104" t="n">
-        <v>1937</v>
+        <v>947</v>
       </c>
       <c r="C104" t="n">
         <v>8888</v>
       </c>
       <c r="D104" t="n">
-        <v>2132.95</v>
+        <v>2087.97</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>PEDIDO ELETRÔNICO</t>
         </is>
       </c>
     </row>
@@ -2421,17 +2421,17 @@
         <v>46218</v>
       </c>
       <c r="B105" t="n">
-        <v>2577</v>
+        <v>2178</v>
       </c>
       <c r="C105" t="n">
         <v>8888</v>
       </c>
       <c r="D105" t="n">
-        <v>1647.08</v>
+        <v>619.92</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2440,17 +2440,17 @@
         <v>46218</v>
       </c>
       <c r="B106" t="n">
-        <v>1293</v>
+        <v>630</v>
       </c>
       <c r="C106" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D106" t="n">
-        <v>2135.89</v>
+        <v>1801.63</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2459,17 +2459,17 @@
         <v>46218</v>
       </c>
       <c r="B107" t="n">
-        <v>2026</v>
+        <v>1937</v>
       </c>
       <c r="C107" t="n">
-        <v>1929</v>
+        <v>8888</v>
       </c>
       <c r="D107" t="n">
-        <v>1680.89</v>
+        <v>2132.95</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2478,13 +2478,13 @@
         <v>46218</v>
       </c>
       <c r="B108" t="n">
-        <v>2607</v>
+        <v>2577</v>
       </c>
       <c r="C108" t="n">
         <v>8888</v>
       </c>
       <c r="D108" t="n">
-        <v>490.31</v>
+        <v>1647.08</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -2497,17 +2497,17 @@
         <v>46218</v>
       </c>
       <c r="B109" t="n">
-        <v>1317</v>
+        <v>1293</v>
       </c>
       <c r="C109" t="n">
         <v>8888</v>
       </c>
       <c r="D109" t="n">
-        <v>907.72</v>
+        <v>2135.89</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2516,13 +2516,13 @@
         <v>46218</v>
       </c>
       <c r="B110" t="n">
-        <v>2571</v>
+        <v>2026</v>
       </c>
       <c r="C110" t="n">
-        <v>1312</v>
+        <v>1929</v>
       </c>
       <c r="D110" t="n">
-        <v>268.53</v>
+        <v>1680.89</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -2535,17 +2535,17 @@
         <v>46218</v>
       </c>
       <c r="B111" t="n">
-        <v>1937</v>
+        <v>2607</v>
       </c>
       <c r="C111" t="n">
         <v>8888</v>
       </c>
       <c r="D111" t="n">
-        <v>1803.32</v>
+        <v>490.31</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2554,13 +2554,13 @@
         <v>46218</v>
       </c>
       <c r="B112" t="n">
-        <v>1063</v>
+        <v>1317</v>
       </c>
       <c r="C112" t="n">
         <v>8888</v>
       </c>
       <c r="D112" t="n">
-        <v>1113.08</v>
+        <v>907.72</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -2573,13 +2573,13 @@
         <v>46218</v>
       </c>
       <c r="B113" t="n">
-        <v>2631</v>
+        <v>767</v>
       </c>
       <c r="C113" t="n">
         <v>8888</v>
       </c>
       <c r="D113" t="n">
-        <v>1447.86</v>
+        <v>637.23</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -2592,17 +2592,17 @@
         <v>46218</v>
       </c>
       <c r="B114" t="n">
-        <v>1906</v>
+        <v>2571</v>
       </c>
       <c r="C114" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D114" t="n">
-        <v>2774.84</v>
+        <v>268.53</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2611,17 +2611,17 @@
         <v>46218</v>
       </c>
       <c r="B115" t="n">
-        <v>1756</v>
+        <v>1937</v>
       </c>
       <c r="C115" t="n">
         <v>8888</v>
       </c>
       <c r="D115" t="n">
-        <v>1357.12</v>
+        <v>1803.32</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2630,17 +2630,17 @@
         <v>46218</v>
       </c>
       <c r="B116" t="n">
-        <v>20</v>
+        <v>1063</v>
       </c>
       <c r="C116" t="n">
         <v>8888</v>
       </c>
       <c r="D116" t="n">
-        <v>276.64</v>
+        <v>1113.08</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2649,17 +2649,17 @@
         <v>46218</v>
       </c>
       <c r="B117" t="n">
-        <v>477</v>
+        <v>2631</v>
       </c>
       <c r="C117" t="n">
         <v>8888</v>
       </c>
       <c r="D117" t="n">
-        <v>372.69</v>
+        <v>1447.86</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2668,17 +2668,17 @@
         <v>46218</v>
       </c>
       <c r="B118" t="n">
-        <v>477</v>
+        <v>1906</v>
       </c>
       <c r="C118" t="n">
         <v>8888</v>
       </c>
       <c r="D118" t="n">
-        <v>707.52</v>
+        <v>2774.84</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2687,17 +2687,17 @@
         <v>46218</v>
       </c>
       <c r="B119" t="n">
-        <v>2660</v>
+        <v>1756</v>
       </c>
       <c r="C119" t="n">
         <v>8888</v>
       </c>
       <c r="D119" t="n">
-        <v>2684.97</v>
+        <v>1357.12</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2706,17 +2706,17 @@
         <v>46218</v>
       </c>
       <c r="B120" t="n">
-        <v>569</v>
+        <v>20</v>
       </c>
       <c r="C120" t="n">
         <v>8888</v>
       </c>
       <c r="D120" t="n">
-        <v>19352.11</v>
+        <v>276.64</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2725,17 +2725,17 @@
         <v>46218</v>
       </c>
       <c r="B121" t="n">
-        <v>2089</v>
+        <v>477</v>
       </c>
       <c r="C121" t="n">
-        <v>1533</v>
+        <v>8888</v>
       </c>
       <c r="D121" t="n">
-        <v>969.24</v>
+        <v>372.69</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2744,17 +2744,17 @@
         <v>46218</v>
       </c>
       <c r="B122" t="n">
-        <v>1007</v>
+        <v>477</v>
       </c>
       <c r="C122" t="n">
         <v>8888</v>
       </c>
       <c r="D122" t="n">
-        <v>241.44</v>
+        <v>707.52</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2763,17 +2763,17 @@
         <v>46218</v>
       </c>
       <c r="B123" t="n">
-        <v>1380</v>
+        <v>2660</v>
       </c>
       <c r="C123" t="n">
         <v>8888</v>
       </c>
       <c r="D123" t="n">
-        <v>520.2</v>
+        <v>2684.97</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2782,17 +2782,17 @@
         <v>46218</v>
       </c>
       <c r="B124" t="n">
-        <v>1102</v>
+        <v>569</v>
       </c>
       <c r="C124" t="n">
         <v>8888</v>
       </c>
       <c r="D124" t="n">
-        <v>1137.04</v>
+        <v>23608.83</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2801,17 +2801,17 @@
         <v>46218</v>
       </c>
       <c r="B125" t="n">
-        <v>1075</v>
+        <v>2089</v>
       </c>
       <c r="C125" t="n">
-        <v>8888</v>
+        <v>1533</v>
       </c>
       <c r="D125" t="n">
-        <v>2179.03</v>
+        <v>969.24</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2820,17 +2820,17 @@
         <v>46218</v>
       </c>
       <c r="B126" t="n">
-        <v>2245</v>
+        <v>1007</v>
       </c>
       <c r="C126" t="n">
         <v>8888</v>
       </c>
       <c r="D126" t="n">
-        <v>361.58</v>
+        <v>241.44</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2839,13 +2839,13 @@
         <v>46218</v>
       </c>
       <c r="B127" t="n">
-        <v>132</v>
+        <v>1380</v>
       </c>
       <c r="C127" t="n">
         <v>8888</v>
       </c>
       <c r="D127" t="n">
-        <v>6522.92</v>
+        <v>520.2</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -2858,13 +2858,13 @@
         <v>46218</v>
       </c>
       <c r="B128" t="n">
-        <v>452</v>
+        <v>1102</v>
       </c>
       <c r="C128" t="n">
         <v>8888</v>
       </c>
       <c r="D128" t="n">
-        <v>608.78</v>
+        <v>1137.04</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -2877,17 +2877,17 @@
         <v>46218</v>
       </c>
       <c r="B129" t="n">
-        <v>1293</v>
+        <v>1075</v>
       </c>
       <c r="C129" t="n">
-        <v>1281</v>
+        <v>8888</v>
       </c>
       <c r="D129" t="n">
-        <v>1780.93</v>
+        <v>2179.03</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2896,17 +2896,17 @@
         <v>46218</v>
       </c>
       <c r="B130" t="n">
-        <v>525</v>
+        <v>2681</v>
       </c>
       <c r="C130" t="n">
         <v>8888</v>
       </c>
       <c r="D130" t="n">
-        <v>5658.57</v>
+        <v>729.25</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2915,13 +2915,13 @@
         <v>46218</v>
       </c>
       <c r="B131" t="n">
-        <v>2641</v>
+        <v>2245</v>
       </c>
       <c r="C131" t="n">
         <v>8888</v>
       </c>
       <c r="D131" t="n">
-        <v>1720.99</v>
+        <v>361.58</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -2934,17 +2934,17 @@
         <v>46218</v>
       </c>
       <c r="B132" t="n">
-        <v>609</v>
+        <v>132</v>
       </c>
       <c r="C132" t="n">
         <v>8888</v>
       </c>
       <c r="D132" t="n">
-        <v>886.1</v>
+        <v>6522.92</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2953,17 +2953,17 @@
         <v>46218</v>
       </c>
       <c r="B133" t="n">
-        <v>619</v>
+        <v>452</v>
       </c>
       <c r="C133" t="n">
         <v>8888</v>
       </c>
       <c r="D133" t="n">
-        <v>2330.47</v>
+        <v>608.78</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2972,17 +2972,17 @@
         <v>46218</v>
       </c>
       <c r="B134" t="n">
-        <v>2697</v>
+        <v>1293</v>
       </c>
       <c r="C134" t="n">
-        <v>8888</v>
+        <v>1281</v>
       </c>
       <c r="D134" t="n">
-        <v>418.65</v>
+        <v>1780.93</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2991,17 +2991,17 @@
         <v>46218</v>
       </c>
       <c r="B135" t="n">
-        <v>58</v>
+        <v>525</v>
       </c>
       <c r="C135" t="n">
         <v>8888</v>
       </c>
       <c r="D135" t="n">
-        <v>1123.87</v>
+        <v>5658.57</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3010,17 +3010,17 @@
         <v>46218</v>
       </c>
       <c r="B136" t="n">
-        <v>358</v>
+        <v>2641</v>
       </c>
       <c r="C136" t="n">
         <v>8888</v>
       </c>
       <c r="D136" t="n">
-        <v>1675.95</v>
+        <v>1720.99</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3029,17 +3029,17 @@
         <v>46218</v>
       </c>
       <c r="B137" t="n">
-        <v>2431</v>
+        <v>609</v>
       </c>
       <c r="C137" t="n">
         <v>8888</v>
       </c>
       <c r="D137" t="n">
-        <v>266.89</v>
+        <v>886.1</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3048,13 +3048,13 @@
         <v>46218</v>
       </c>
       <c r="B138" t="n">
-        <v>285</v>
+        <v>619</v>
       </c>
       <c r="C138" t="n">
         <v>8888</v>
       </c>
       <c r="D138" t="n">
-        <v>2090.81</v>
+        <v>2330.47</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -3067,17 +3067,17 @@
         <v>46218</v>
       </c>
       <c r="B139" t="n">
-        <v>1102</v>
+        <v>2697</v>
       </c>
       <c r="C139" t="n">
         <v>8888</v>
       </c>
       <c r="D139" t="n">
-        <v>1119.32</v>
+        <v>418.65</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3086,17 +3086,17 @@
         <v>46218</v>
       </c>
       <c r="B140" t="n">
-        <v>626</v>
+        <v>58</v>
       </c>
       <c r="C140" t="n">
         <v>8888</v>
       </c>
       <c r="D140" t="n">
-        <v>11881.87</v>
+        <v>1123.87</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3105,17 +3105,17 @@
         <v>46218</v>
       </c>
       <c r="B141" t="n">
-        <v>1137</v>
+        <v>358</v>
       </c>
       <c r="C141" t="n">
-        <v>2220</v>
+        <v>8888</v>
       </c>
       <c r="D141" t="n">
-        <v>1370.86</v>
+        <v>1675.95</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3124,17 +3124,17 @@
         <v>46218</v>
       </c>
       <c r="B142" t="n">
-        <v>2686</v>
+        <v>2431</v>
       </c>
       <c r="C142" t="n">
-        <v>1929</v>
+        <v>8888</v>
       </c>
       <c r="D142" t="n">
-        <v>2066.36</v>
+        <v>266.89</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3143,17 +3143,17 @@
         <v>46218</v>
       </c>
       <c r="B143" t="n">
-        <v>1756</v>
+        <v>285</v>
       </c>
       <c r="C143" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D143" t="n">
-        <v>5078.1</v>
+        <v>2090.81</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3162,17 +3162,17 @@
         <v>46218</v>
       </c>
       <c r="B144" t="n">
-        <v>2651</v>
+        <v>1102</v>
       </c>
       <c r="C144" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D144" t="n">
-        <v>363.7</v>
+        <v>1119.32</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3181,17 +3181,17 @@
         <v>46218</v>
       </c>
       <c r="B145" t="n">
-        <v>360</v>
+        <v>626</v>
       </c>
       <c r="C145" t="n">
         <v>8888</v>
       </c>
       <c r="D145" t="n">
-        <v>1594.84</v>
+        <v>12556.19</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3200,17 +3200,17 @@
         <v>46218</v>
       </c>
       <c r="B146" t="n">
-        <v>2582</v>
+        <v>1137</v>
       </c>
       <c r="C146" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D146" t="n">
-        <v>379.33</v>
+        <v>1370.86</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3219,17 +3219,17 @@
         <v>46218</v>
       </c>
       <c r="B147" t="n">
-        <v>1756</v>
+        <v>2686</v>
       </c>
       <c r="C147" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D147" t="n">
-        <v>1715.26</v>
+        <v>2066.36</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3238,17 +3238,17 @@
         <v>46218</v>
       </c>
       <c r="B148" t="n">
-        <v>1254</v>
+        <v>1756</v>
       </c>
       <c r="C148" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D148" t="n">
-        <v>855.76</v>
+        <v>5078.1</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3257,17 +3257,17 @@
         <v>46218</v>
       </c>
       <c r="B149" t="n">
-        <v>1289</v>
+        <v>2651</v>
       </c>
       <c r="C149" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D149" t="n">
-        <v>2396.98</v>
+        <v>363.7</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3276,17 +3276,17 @@
         <v>46218</v>
       </c>
       <c r="B150" t="n">
-        <v>2015</v>
+        <v>360</v>
       </c>
       <c r="C150" t="n">
         <v>8888</v>
       </c>
       <c r="D150" t="n">
-        <v>315.69</v>
+        <v>1594.84</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3295,17 +3295,17 @@
         <v>46218</v>
       </c>
       <c r="B151" t="n">
-        <v>1064</v>
+        <v>2582</v>
       </c>
       <c r="C151" t="n">
         <v>8888</v>
       </c>
       <c r="D151" t="n">
-        <v>1274.3</v>
+        <v>379.33</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3314,17 +3314,17 @@
         <v>46218</v>
       </c>
       <c r="B152" t="n">
-        <v>2698</v>
+        <v>1756</v>
       </c>
       <c r="C152" t="n">
         <v>8888</v>
       </c>
       <c r="D152" t="n">
-        <v>552.15</v>
+        <v>1715.26</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3333,13 +3333,13 @@
         <v>46218</v>
       </c>
       <c r="B153" t="n">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="C153" t="n">
         <v>8888</v>
       </c>
       <c r="D153" t="n">
-        <v>3035.38</v>
+        <v>2447.56</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -3352,17 +3352,17 @@
         <v>46218</v>
       </c>
       <c r="B154" t="n">
-        <v>664</v>
+        <v>1254</v>
       </c>
       <c r="C154" t="n">
         <v>8888</v>
       </c>
       <c r="D154" t="n">
-        <v>4973.15</v>
+        <v>855.76</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3371,17 +3371,17 @@
         <v>46218</v>
       </c>
       <c r="B155" t="n">
-        <v>2584</v>
+        <v>1289</v>
       </c>
       <c r="C155" t="n">
         <v>8888</v>
       </c>
       <c r="D155" t="n">
-        <v>1852.83</v>
+        <v>2396.98</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3390,13 +3390,13 @@
         <v>46218</v>
       </c>
       <c r="B156" t="n">
-        <v>2641</v>
+        <v>2015</v>
       </c>
       <c r="C156" t="n">
         <v>8888</v>
       </c>
       <c r="D156" t="n">
-        <v>820</v>
+        <v>315.69</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -3409,13 +3409,13 @@
         <v>46218</v>
       </c>
       <c r="B157" t="n">
-        <v>429</v>
+        <v>1064</v>
       </c>
       <c r="C157" t="n">
         <v>8888</v>
       </c>
       <c r="D157" t="n">
-        <v>2593.49</v>
+        <v>1274.3</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -3428,13 +3428,13 @@
         <v>46218</v>
       </c>
       <c r="B158" t="n">
-        <v>816</v>
+        <v>2698</v>
       </c>
       <c r="C158" t="n">
         <v>8888</v>
       </c>
       <c r="D158" t="n">
-        <v>438.24</v>
+        <v>552.15</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -3447,13 +3447,13 @@
         <v>46218</v>
       </c>
       <c r="B159" t="n">
-        <v>2359</v>
+        <v>629</v>
       </c>
       <c r="C159" t="n">
         <v>8888</v>
       </c>
       <c r="D159" t="n">
-        <v>381.95</v>
+        <v>3035.38</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -3466,17 +3466,17 @@
         <v>46218</v>
       </c>
       <c r="B160" t="n">
-        <v>285</v>
+        <v>664</v>
       </c>
       <c r="C160" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D160" t="n">
-        <v>364.99</v>
+        <v>4973.15</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3485,17 +3485,17 @@
         <v>46218</v>
       </c>
       <c r="B161" t="n">
-        <v>2114</v>
+        <v>2584</v>
       </c>
       <c r="C161" t="n">
         <v>8888</v>
       </c>
       <c r="D161" t="n">
-        <v>2726.04</v>
+        <v>1852.83</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3504,13 +3504,13 @@
         <v>46218</v>
       </c>
       <c r="B162" t="n">
-        <v>953</v>
+        <v>2641</v>
       </c>
       <c r="C162" t="n">
         <v>8888</v>
       </c>
       <c r="D162" t="n">
-        <v>2618.89</v>
+        <v>820</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -3523,17 +3523,17 @@
         <v>46218</v>
       </c>
       <c r="B163" t="n">
-        <v>1102</v>
+        <v>429</v>
       </c>
       <c r="C163" t="n">
         <v>8888</v>
       </c>
       <c r="D163" t="n">
-        <v>2344.41</v>
+        <v>2593.49</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3542,17 +3542,17 @@
         <v>46218</v>
       </c>
       <c r="B164" t="n">
-        <v>619</v>
+        <v>816</v>
       </c>
       <c r="C164" t="n">
         <v>8888</v>
       </c>
       <c r="D164" t="n">
-        <v>2021.67</v>
+        <v>438.24</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3561,17 +3561,17 @@
         <v>46218</v>
       </c>
       <c r="B165" t="n">
-        <v>1465</v>
+        <v>2793</v>
       </c>
       <c r="C165" t="n">
         <v>8888</v>
       </c>
       <c r="D165" t="n">
-        <v>3504</v>
+        <v>767.58</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3580,17 +3580,17 @@
         <v>46218</v>
       </c>
       <c r="B166" t="n">
-        <v>2767</v>
+        <v>2359</v>
       </c>
       <c r="C166" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D166" t="n">
-        <v>1135.64</v>
+        <v>381.95</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3599,17 +3599,17 @@
         <v>46218</v>
       </c>
       <c r="B167" t="n">
-        <v>2245</v>
+        <v>285</v>
       </c>
       <c r="C167" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D167" t="n">
-        <v>427.51</v>
+        <v>364.99</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3618,17 +3618,17 @@
         <v>46218</v>
       </c>
       <c r="B168" t="n">
-        <v>2197</v>
+        <v>2114</v>
       </c>
       <c r="C168" t="n">
         <v>8888</v>
       </c>
       <c r="D168" t="n">
-        <v>1085.45</v>
+        <v>2726.04</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3637,17 +3637,17 @@
         <v>46218</v>
       </c>
       <c r="B169" t="n">
-        <v>2657</v>
+        <v>953</v>
       </c>
       <c r="C169" t="n">
         <v>8888</v>
       </c>
       <c r="D169" t="n">
-        <v>2683.06</v>
+        <v>2618.89</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3656,17 +3656,17 @@
         <v>46218</v>
       </c>
       <c r="B170" t="n">
-        <v>1277</v>
+        <v>1102</v>
       </c>
       <c r="C170" t="n">
         <v>8888</v>
       </c>
       <c r="D170" t="n">
-        <v>1949</v>
+        <v>2344.41</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3675,17 +3675,17 @@
         <v>46218</v>
       </c>
       <c r="B171" t="n">
-        <v>131</v>
+        <v>619</v>
       </c>
       <c r="C171" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D171" t="n">
-        <v>1268.57</v>
+        <v>2021.67</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3694,13 +3694,13 @@
         <v>46218</v>
       </c>
       <c r="B172" t="n">
-        <v>2692</v>
+        <v>1465</v>
       </c>
       <c r="C172" t="n">
         <v>8888</v>
       </c>
       <c r="D172" t="n">
-        <v>731.28</v>
+        <v>3504</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -3713,13 +3713,13 @@
         <v>46218</v>
       </c>
       <c r="B173" t="n">
-        <v>1317</v>
+        <v>2767</v>
       </c>
       <c r="C173" t="n">
-        <v>3179</v>
+        <v>1898</v>
       </c>
       <c r="D173" t="n">
-        <v>991.6799999999999</v>
+        <v>1135.64</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>46218</v>
       </c>
       <c r="B174" t="n">
-        <v>1993</v>
+        <v>2245</v>
       </c>
       <c r="C174" t="n">
         <v>8888</v>
       </c>
       <c r="D174" t="n">
-        <v>2875.39</v>
+        <v>427.51</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -3751,17 +3751,17 @@
         <v>46218</v>
       </c>
       <c r="B175" t="n">
-        <v>1632</v>
+        <v>2197</v>
       </c>
       <c r="C175" t="n">
         <v>8888</v>
       </c>
       <c r="D175" t="n">
-        <v>564.55</v>
+        <v>1085.45</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3770,17 +3770,17 @@
         <v>46218</v>
       </c>
       <c r="B176" t="n">
-        <v>1890</v>
+        <v>2657</v>
       </c>
       <c r="C176" t="n">
-        <v>3449</v>
+        <v>8888</v>
       </c>
       <c r="D176" t="n">
-        <v>3590.04</v>
+        <v>2683.06</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3789,17 +3789,17 @@
         <v>46218</v>
       </c>
       <c r="B177" t="n">
-        <v>451</v>
+        <v>1277</v>
       </c>
       <c r="C177" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D177" t="n">
-        <v>445.58</v>
+        <v>1949</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3808,17 +3808,17 @@
         <v>46218</v>
       </c>
       <c r="B178" t="n">
-        <v>2749</v>
+        <v>131</v>
       </c>
       <c r="C178" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D178" t="n">
-        <v>1860.64</v>
+        <v>1268.57</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3827,17 +3827,17 @@
         <v>46218</v>
       </c>
       <c r="B179" t="n">
-        <v>1117</v>
+        <v>2692</v>
       </c>
       <c r="C179" t="n">
         <v>8888</v>
       </c>
       <c r="D179" t="n">
-        <v>342.2</v>
+        <v>731.28</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3846,17 +3846,17 @@
         <v>46218</v>
       </c>
       <c r="B180" t="n">
-        <v>1478</v>
+        <v>1317</v>
       </c>
       <c r="C180" t="n">
-        <v>8888</v>
+        <v>3179</v>
       </c>
       <c r="D180" t="n">
-        <v>875.34</v>
+        <v>991.6799999999999</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3865,13 +3865,13 @@
         <v>46218</v>
       </c>
       <c r="B181" t="n">
-        <v>2491</v>
+        <v>1993</v>
       </c>
       <c r="C181" t="n">
         <v>8888</v>
       </c>
       <c r="D181" t="n">
-        <v>650.4299999999999</v>
+        <v>2875.39</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -3884,13 +3884,13 @@
         <v>46218</v>
       </c>
       <c r="B182" t="n">
-        <v>2015</v>
+        <v>1632</v>
       </c>
       <c r="C182" t="n">
         <v>8888</v>
       </c>
       <c r="D182" t="n">
-        <v>4436.15</v>
+        <v>564.55</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -3906,10 +3906,10 @@
         <v>1890</v>
       </c>
       <c r="C183" t="n">
-        <v>1953</v>
+        <v>3449</v>
       </c>
       <c r="D183" t="n">
-        <v>1674.57</v>
+        <v>3590.04</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -3922,17 +3922,17 @@
         <v>46218</v>
       </c>
       <c r="B184" t="n">
-        <v>2782</v>
+        <v>451</v>
       </c>
       <c r="C184" t="n">
-        <v>8888</v>
+        <v>3403</v>
       </c>
       <c r="D184" t="n">
-        <v>1786.32</v>
+        <v>445.58</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3941,17 +3941,17 @@
         <v>46218</v>
       </c>
       <c r="B185" t="n">
-        <v>483</v>
+        <v>2749</v>
       </c>
       <c r="C185" t="n">
-        <v>841</v>
+        <v>8888</v>
       </c>
       <c r="D185" t="n">
-        <v>1393.15</v>
+        <v>1860.64</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3960,17 +3960,17 @@
         <v>46218</v>
       </c>
       <c r="B186" t="n">
-        <v>2133</v>
+        <v>1117</v>
       </c>
       <c r="C186" t="n">
-        <v>213</v>
+        <v>8888</v>
       </c>
       <c r="D186" t="n">
-        <v>526.8</v>
+        <v>342.2</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3979,17 +3979,17 @@
         <v>46218</v>
       </c>
       <c r="B187" t="n">
-        <v>351</v>
+        <v>1478</v>
       </c>
       <c r="C187" t="n">
-        <v>3009</v>
+        <v>8888</v>
       </c>
       <c r="D187" t="n">
-        <v>416.36</v>
+        <v>875.34</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3998,17 +3998,17 @@
         <v>46218</v>
       </c>
       <c r="B188" t="n">
-        <v>2250</v>
+        <v>2491</v>
       </c>
       <c r="C188" t="n">
         <v>8888</v>
       </c>
       <c r="D188" t="n">
-        <v>709.46</v>
+        <v>650.4299999999999</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4017,13 +4017,13 @@
         <v>46218</v>
       </c>
       <c r="B189" t="n">
-        <v>2648</v>
+        <v>2015</v>
       </c>
       <c r="C189" t="n">
         <v>8888</v>
       </c>
       <c r="D189" t="n">
-        <v>1873.52</v>
+        <v>4436.15</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -4036,17 +4036,17 @@
         <v>46218</v>
       </c>
       <c r="B190" t="n">
-        <v>131</v>
+        <v>1890</v>
       </c>
       <c r="C190" t="n">
-        <v>8888</v>
+        <v>1953</v>
       </c>
       <c r="D190" t="n">
-        <v>1369.91</v>
+        <v>1674.57</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4055,17 +4055,17 @@
         <v>46218</v>
       </c>
       <c r="B191" t="n">
-        <v>2790</v>
+        <v>2782</v>
       </c>
       <c r="C191" t="n">
-        <v>1953</v>
+        <v>8888</v>
       </c>
       <c r="D191" t="n">
-        <v>371.88</v>
+        <v>1786.32</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4074,13 +4074,13 @@
         <v>46218</v>
       </c>
       <c r="B192" t="n">
-        <v>2639</v>
+        <v>483</v>
       </c>
       <c r="C192" t="n">
-        <v>1953</v>
+        <v>841</v>
       </c>
       <c r="D192" t="n">
-        <v>504.09</v>
+        <v>1393.15</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -4093,17 +4093,17 @@
         <v>46218</v>
       </c>
       <c r="B193" t="n">
-        <v>2109</v>
+        <v>2133</v>
       </c>
       <c r="C193" t="n">
-        <v>8888</v>
+        <v>213</v>
       </c>
       <c r="D193" t="n">
-        <v>2293.78</v>
+        <v>526.8</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4112,17 +4112,17 @@
         <v>46218</v>
       </c>
       <c r="B194" t="n">
-        <v>1116</v>
+        <v>351</v>
       </c>
       <c r="C194" t="n">
-        <v>8888</v>
+        <v>3009</v>
       </c>
       <c r="D194" t="n">
-        <v>2919.53</v>
+        <v>416.36</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4134,14 +4134,14 @@
         <v>2250</v>
       </c>
       <c r="C195" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D195" t="n">
-        <v>1803.76</v>
+        <v>709.46</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4150,13 +4150,13 @@
         <v>46218</v>
       </c>
       <c r="B196" t="n">
-        <v>353</v>
+        <v>2648</v>
       </c>
       <c r="C196" t="n">
         <v>8888</v>
       </c>
       <c r="D196" t="n">
-        <v>108.6</v>
+        <v>1873.52</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -4169,17 +4169,17 @@
         <v>46218</v>
       </c>
       <c r="B197" t="n">
-        <v>2698</v>
+        <v>131</v>
       </c>
       <c r="C197" t="n">
-        <v>874</v>
+        <v>8888</v>
       </c>
       <c r="D197" t="n">
-        <v>1230.43</v>
+        <v>1369.91</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4188,17 +4188,17 @@
         <v>46218</v>
       </c>
       <c r="B198" t="n">
-        <v>42</v>
+        <v>2790</v>
       </c>
       <c r="C198" t="n">
-        <v>8888</v>
+        <v>1953</v>
       </c>
       <c r="D198" t="n">
-        <v>79947.14999999999</v>
+        <v>371.88</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4207,17 +4207,17 @@
         <v>46218</v>
       </c>
       <c r="B199" t="n">
-        <v>772</v>
+        <v>363</v>
       </c>
       <c r="C199" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D199" t="n">
-        <v>400.25</v>
+        <v>635.1</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4226,17 +4226,17 @@
         <v>46218</v>
       </c>
       <c r="B200" t="n">
-        <v>2728</v>
+        <v>2716</v>
       </c>
       <c r="C200" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D200" t="n">
-        <v>1397.07</v>
+        <v>1073.33</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4245,13 +4245,13 @@
         <v>46218</v>
       </c>
       <c r="B201" t="n">
-        <v>2197</v>
+        <v>2639</v>
       </c>
       <c r="C201" t="n">
-        <v>423</v>
+        <v>1953</v>
       </c>
       <c r="D201" t="n">
-        <v>2267.61</v>
+        <v>504.09</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -4264,17 +4264,17 @@
         <v>46218</v>
       </c>
       <c r="B202" t="n">
-        <v>2716</v>
+        <v>2109</v>
       </c>
       <c r="C202" t="n">
-        <v>1929</v>
+        <v>8888</v>
       </c>
       <c r="D202" t="n">
-        <v>750.4299999999999</v>
+        <v>2293.78</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4283,17 +4283,17 @@
         <v>46218</v>
       </c>
       <c r="B203" t="n">
-        <v>2716</v>
+        <v>1116</v>
       </c>
       <c r="C203" t="n">
-        <v>977</v>
+        <v>8888</v>
       </c>
       <c r="D203" t="n">
-        <v>729.29</v>
+        <v>2919.53</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4302,17 +4302,17 @@
         <v>46218</v>
       </c>
       <c r="B204" t="n">
-        <v>1993</v>
+        <v>2250</v>
       </c>
       <c r="C204" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D204" t="n">
-        <v>456.62</v>
+        <v>1803.76</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4321,15 +4321,167 @@
         <v>46218</v>
       </c>
       <c r="B205" t="n">
+        <v>353</v>
+      </c>
+      <c r="C205" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D205" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B206" t="n">
+        <v>2698</v>
+      </c>
+      <c r="C206" t="n">
+        <v>874</v>
+      </c>
+      <c r="D206" t="n">
+        <v>1230.43</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B207" t="n">
+        <v>42</v>
+      </c>
+      <c r="C207" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D207" t="n">
+        <v>79947.14999999999</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B208" t="n">
+        <v>772</v>
+      </c>
+      <c r="C208" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D208" t="n">
+        <v>400.25</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B209" t="n">
+        <v>2728</v>
+      </c>
+      <c r="C209" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D209" t="n">
+        <v>1397.07</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B210" t="n">
+        <v>2197</v>
+      </c>
+      <c r="C210" t="n">
+        <v>423</v>
+      </c>
+      <c r="D210" t="n">
+        <v>2267.61</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B211" t="n">
+        <v>2716</v>
+      </c>
+      <c r="C211" t="n">
+        <v>977</v>
+      </c>
+      <c r="D211" t="n">
+        <v>729.29</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B212" t="n">
+        <v>1993</v>
+      </c>
+      <c r="C212" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D212" t="n">
+        <v>456.62</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B213" t="n">
         <v>629</v>
       </c>
-      <c r="C205" t="n">
+      <c r="C213" t="n">
         <v>675</v>
       </c>
-      <c r="D205" t="n">
+      <c r="D213" t="n">
         <v>1054.76</v>
       </c>
-      <c r="E205" t="inlineStr">
+      <c r="E213" t="inlineStr">
         <is>
           <t>TELEMARKETING</t>
         </is>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E213"/>
+  <dimension ref="A1:E234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,7 +489,7 @@
         <v>8888</v>
       </c>
       <c r="D3" t="n">
-        <v>406.97</v>
+        <v>544.78</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -768,17 +768,17 @@
         <v>46218</v>
       </c>
       <c r="B18" t="n">
-        <v>2118</v>
+        <v>890</v>
       </c>
       <c r="C18" t="n">
-        <v>8888</v>
+        <v>1533</v>
       </c>
       <c r="D18" t="n">
-        <v>5535.71</v>
+        <v>898.83</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
         <v>46218</v>
       </c>
       <c r="B19" t="n">
-        <v>2197</v>
+        <v>40</v>
       </c>
       <c r="C19" t="n">
         <v>8888</v>
       </c>
       <c r="D19" t="n">
-        <v>1441.76</v>
+        <v>768.78</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -806,17 +806,17 @@
         <v>46218</v>
       </c>
       <c r="B20" t="n">
-        <v>363</v>
+        <v>2118</v>
       </c>
       <c r="C20" t="n">
         <v>8888</v>
       </c>
       <c r="D20" t="n">
-        <v>836.9400000000001</v>
+        <v>5535.71</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -825,17 +825,17 @@
         <v>46218</v>
       </c>
       <c r="B21" t="n">
-        <v>1869</v>
+        <v>2197</v>
       </c>
       <c r="C21" t="n">
         <v>8888</v>
       </c>
       <c r="D21" t="n">
-        <v>1263.2</v>
+        <v>2855.48</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -844,17 +844,17 @@
         <v>46218</v>
       </c>
       <c r="B22" t="n">
-        <v>1137</v>
+        <v>325</v>
       </c>
       <c r="C22" t="n">
-        <v>8888</v>
+        <v>14</v>
       </c>
       <c r="D22" t="n">
-        <v>359.06</v>
+        <v>301.57</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -863,17 +863,17 @@
         <v>46218</v>
       </c>
       <c r="B23" t="n">
-        <v>2133</v>
+        <v>363</v>
       </c>
       <c r="C23" t="n">
-        <v>691</v>
+        <v>8888</v>
       </c>
       <c r="D23" t="n">
-        <v>2058.93</v>
+        <v>836.9400000000001</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
         <v>46218</v>
       </c>
       <c r="B24" t="n">
-        <v>452</v>
+        <v>1869</v>
       </c>
       <c r="C24" t="n">
         <v>8888</v>
       </c>
       <c r="D24" t="n">
-        <v>1832.74</v>
+        <v>1263.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
         <v>46218</v>
       </c>
       <c r="B25" t="n">
-        <v>1632</v>
+        <v>1137</v>
       </c>
       <c r="C25" t="n">
-        <v>423</v>
+        <v>8888</v>
       </c>
       <c r="D25" t="n">
-        <v>2811.9</v>
+        <v>359.06</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -920,17 +920,17 @@
         <v>46218</v>
       </c>
       <c r="B26" t="n">
-        <v>2250</v>
+        <v>2133</v>
       </c>
       <c r="C26" t="n">
-        <v>8888</v>
+        <v>691</v>
       </c>
       <c r="D26" t="n">
-        <v>1686.37</v>
+        <v>2058.93</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -939,17 +939,17 @@
         <v>46218</v>
       </c>
       <c r="B27" t="n">
-        <v>931</v>
+        <v>452</v>
       </c>
       <c r="C27" t="n">
-        <v>423</v>
+        <v>8888</v>
       </c>
       <c r="D27" t="n">
-        <v>492.34</v>
+        <v>1832.74</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
         <v>46218</v>
       </c>
       <c r="B28" t="n">
-        <v>951</v>
+        <v>1632</v>
       </c>
       <c r="C28" t="n">
-        <v>8888</v>
+        <v>423</v>
       </c>
       <c r="D28" t="n">
-        <v>2171.08</v>
+        <v>2811.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -977,17 +977,17 @@
         <v>46218</v>
       </c>
       <c r="B29" t="n">
-        <v>2695</v>
+        <v>2250</v>
       </c>
       <c r="C29" t="n">
         <v>8888</v>
       </c>
       <c r="D29" t="n">
-        <v>411.42</v>
+        <v>1686.37</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -996,17 +996,17 @@
         <v>46218</v>
       </c>
       <c r="B30" t="n">
-        <v>525</v>
+        <v>931</v>
       </c>
       <c r="C30" t="n">
-        <v>8888</v>
+        <v>423</v>
       </c>
       <c r="D30" t="n">
-        <v>408.25</v>
+        <v>492.34</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1015,17 +1015,17 @@
         <v>46218</v>
       </c>
       <c r="B31" t="n">
-        <v>1808</v>
+        <v>951</v>
       </c>
       <c r="C31" t="n">
         <v>8888</v>
       </c>
       <c r="D31" t="n">
-        <v>695.3200000000001</v>
+        <v>2171.08</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
         <v>46218</v>
       </c>
       <c r="B32" t="n">
-        <v>609</v>
+        <v>2695</v>
       </c>
       <c r="C32" t="n">
         <v>8888</v>
       </c>
       <c r="D32" t="n">
-        <v>1909.37</v>
+        <v>411.42</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
         <v>46218</v>
       </c>
       <c r="B33" t="n">
-        <v>949</v>
+        <v>525</v>
       </c>
       <c r="C33" t="n">
-        <v>1134</v>
+        <v>8888</v>
       </c>
       <c r="D33" t="n">
-        <v>30.46</v>
+        <v>408.25</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1072,17 +1072,17 @@
         <v>46218</v>
       </c>
       <c r="B34" t="n">
-        <v>2499</v>
+        <v>1808</v>
       </c>
       <c r="C34" t="n">
         <v>8888</v>
       </c>
       <c r="D34" t="n">
-        <v>261.63</v>
+        <v>695.3200000000001</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1091,17 +1091,17 @@
         <v>46218</v>
       </c>
       <c r="B35" t="n">
-        <v>58</v>
+        <v>609</v>
       </c>
       <c r="C35" t="n">
         <v>8888</v>
       </c>
       <c r="D35" t="n">
-        <v>499.11</v>
+        <v>1909.37</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1110,17 +1110,17 @@
         <v>46218</v>
       </c>
       <c r="B36" t="n">
-        <v>2245</v>
+        <v>949</v>
       </c>
       <c r="C36" t="n">
-        <v>8888</v>
+        <v>1134</v>
       </c>
       <c r="D36" t="n">
-        <v>2740.06</v>
+        <v>30.46</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1129,17 +1129,17 @@
         <v>46218</v>
       </c>
       <c r="B37" t="n">
-        <v>325</v>
+        <v>42</v>
       </c>
       <c r="C37" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D37" t="n">
-        <v>871.14</v>
+        <v>358.97</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1148,17 +1148,17 @@
         <v>46218</v>
       </c>
       <c r="B38" t="n">
-        <v>2383</v>
+        <v>2499</v>
       </c>
       <c r="C38" t="n">
         <v>8888</v>
       </c>
       <c r="D38" t="n">
-        <v>7926.02</v>
+        <v>1049.3</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1167,17 +1167,17 @@
         <v>46218</v>
       </c>
       <c r="B39" t="n">
-        <v>1117</v>
+        <v>58</v>
       </c>
       <c r="C39" t="n">
-        <v>1139</v>
+        <v>8888</v>
       </c>
       <c r="D39" t="n">
-        <v>916.72</v>
+        <v>499.11</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1186,13 +1186,13 @@
         <v>46218</v>
       </c>
       <c r="B40" t="n">
-        <v>2279</v>
+        <v>2245</v>
       </c>
       <c r="C40" t="n">
         <v>8888</v>
       </c>
       <c r="D40" t="n">
-        <v>712.66</v>
+        <v>2740.06</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1205,17 +1205,17 @@
         <v>46218</v>
       </c>
       <c r="B41" t="n">
-        <v>535</v>
+        <v>325</v>
       </c>
       <c r="C41" t="n">
         <v>8888</v>
       </c>
       <c r="D41" t="n">
-        <v>5836.12</v>
+        <v>952.75</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1224,17 +1224,17 @@
         <v>46218</v>
       </c>
       <c r="B42" t="n">
-        <v>535</v>
+        <v>2383</v>
       </c>
       <c r="C42" t="n">
         <v>8888</v>
       </c>
       <c r="D42" t="n">
-        <v>1352.51</v>
+        <v>7926.02</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1243,13 +1243,13 @@
         <v>46218</v>
       </c>
       <c r="B43" t="n">
-        <v>2678</v>
+        <v>1117</v>
       </c>
       <c r="C43" t="n">
-        <v>1312</v>
+        <v>1139</v>
       </c>
       <c r="D43" t="n">
-        <v>364.96</v>
+        <v>916.72</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1262,13 +1262,13 @@
         <v>46218</v>
       </c>
       <c r="B44" t="n">
-        <v>2345</v>
+        <v>2279</v>
       </c>
       <c r="C44" t="n">
         <v>8888</v>
       </c>
       <c r="D44" t="n">
-        <v>863.16</v>
+        <v>712.66</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1281,17 +1281,17 @@
         <v>46218</v>
       </c>
       <c r="B45" t="n">
-        <v>945</v>
+        <v>535</v>
       </c>
       <c r="C45" t="n">
         <v>8888</v>
       </c>
       <c r="D45" t="n">
-        <v>27337.21</v>
+        <v>5836.12</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>PEDIDO ELETRÔNICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1300,17 +1300,17 @@
         <v>46218</v>
       </c>
       <c r="B46" t="n">
-        <v>2686</v>
+        <v>535</v>
       </c>
       <c r="C46" t="n">
         <v>8888</v>
       </c>
       <c r="D46" t="n">
-        <v>684.2</v>
+        <v>1352.51</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1319,17 +1319,17 @@
         <v>46218</v>
       </c>
       <c r="B47" t="n">
-        <v>438</v>
+        <v>2678</v>
       </c>
       <c r="C47" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D47" t="n">
-        <v>220.06</v>
+        <v>364.96</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1338,17 @@
         <v>46218</v>
       </c>
       <c r="B48" t="n">
-        <v>353</v>
+        <v>2345</v>
       </c>
       <c r="C48" t="n">
-        <v>3179</v>
+        <v>8888</v>
       </c>
       <c r="D48" t="n">
-        <v>495.84</v>
+        <v>863.16</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1357,17 +1357,17 @@
         <v>46218</v>
       </c>
       <c r="B49" t="n">
-        <v>1293</v>
+        <v>945</v>
       </c>
       <c r="C49" t="n">
         <v>8888</v>
       </c>
       <c r="D49" t="n">
-        <v>3129.07</v>
+        <v>27337.21</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>PEDIDO ELETRÔNICO</t>
         </is>
       </c>
     </row>
@@ -1376,17 +1376,17 @@
         <v>46218</v>
       </c>
       <c r="B50" t="n">
-        <v>2279</v>
+        <v>2686</v>
       </c>
       <c r="C50" t="n">
         <v>8888</v>
       </c>
       <c r="D50" t="n">
-        <v>2753.96</v>
+        <v>684.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1395,17 +1395,17 @@
         <v>46218</v>
       </c>
       <c r="B51" t="n">
-        <v>1137</v>
+        <v>438</v>
       </c>
       <c r="C51" t="n">
         <v>8888</v>
       </c>
       <c r="D51" t="n">
-        <v>1947.93</v>
+        <v>220.06</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1414,17 +1414,17 @@
         <v>46218</v>
       </c>
       <c r="B52" t="n">
-        <v>374</v>
+        <v>664</v>
       </c>
       <c r="C52" t="n">
         <v>8888</v>
       </c>
       <c r="D52" t="n">
-        <v>1390.6</v>
+        <v>2598.01</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1433,13 +1433,13 @@
         <v>46218</v>
       </c>
       <c r="B53" t="n">
-        <v>2793</v>
+        <v>353</v>
       </c>
       <c r="C53" t="n">
-        <v>977</v>
+        <v>3179</v>
       </c>
       <c r="D53" t="n">
-        <v>695.72</v>
+        <v>495.84</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -1452,13 +1452,13 @@
         <v>46218</v>
       </c>
       <c r="B54" t="n">
-        <v>2802</v>
+        <v>1293</v>
       </c>
       <c r="C54" t="n">
         <v>8888</v>
       </c>
       <c r="D54" t="n">
-        <v>1264.57</v>
+        <v>3129.07</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -1471,17 +1471,17 @@
         <v>46218</v>
       </c>
       <c r="B55" t="n">
-        <v>374</v>
+        <v>2279</v>
       </c>
       <c r="C55" t="n">
         <v>8888</v>
       </c>
       <c r="D55" t="n">
-        <v>44.6</v>
+        <v>2753.96</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1490,13 +1490,13 @@
         <v>46218</v>
       </c>
       <c r="B56" t="n">
-        <v>664</v>
+        <v>1937</v>
       </c>
       <c r="C56" t="n">
         <v>8888</v>
       </c>
       <c r="D56" t="n">
-        <v>1510.56</v>
+        <v>1685.72</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -1509,17 +1509,17 @@
         <v>46218</v>
       </c>
       <c r="B57" t="n">
-        <v>703</v>
+        <v>941</v>
       </c>
       <c r="C57" t="n">
         <v>8888</v>
       </c>
       <c r="D57" t="n">
-        <v>12155.46</v>
+        <v>864.14</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1528,17 +1528,17 @@
         <v>46218</v>
       </c>
       <c r="B58" t="n">
-        <v>1937</v>
+        <v>1137</v>
       </c>
       <c r="C58" t="n">
         <v>8888</v>
       </c>
       <c r="D58" t="n">
-        <v>1032.73</v>
+        <v>1947.93</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1547,17 +1547,17 @@
         <v>46218</v>
       </c>
       <c r="B59" t="n">
-        <v>451</v>
+        <v>2631</v>
       </c>
       <c r="C59" t="n">
-        <v>8888</v>
+        <v>2853</v>
       </c>
       <c r="D59" t="n">
-        <v>368.93</v>
+        <v>1272.12</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1566,17 +1566,17 @@
         <v>46218</v>
       </c>
       <c r="B60" t="n">
-        <v>1756</v>
+        <v>2793</v>
       </c>
       <c r="C60" t="n">
-        <v>8888</v>
+        <v>977</v>
       </c>
       <c r="D60" t="n">
-        <v>996.17</v>
+        <v>1188.59</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1585,13 +1585,13 @@
         <v>46218</v>
       </c>
       <c r="B61" t="n">
-        <v>1956</v>
+        <v>374</v>
       </c>
       <c r="C61" t="n">
         <v>8888</v>
       </c>
       <c r="D61" t="n">
-        <v>4557.34</v>
+        <v>2103.29</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -1604,13 +1604,13 @@
         <v>46218</v>
       </c>
       <c r="B62" t="n">
-        <v>925</v>
+        <v>2802</v>
       </c>
       <c r="C62" t="n">
         <v>8888</v>
       </c>
       <c r="D62" t="n">
-        <v>651.59</v>
+        <v>1264.57</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -1623,17 +1623,17 @@
         <v>46218</v>
       </c>
       <c r="B63" t="n">
-        <v>2631</v>
+        <v>451</v>
       </c>
       <c r="C63" t="n">
-        <v>2853</v>
+        <v>8888</v>
       </c>
       <c r="D63" t="n">
-        <v>509.88</v>
+        <v>757.5700000000001</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1642,13 +1642,13 @@
         <v>46218</v>
       </c>
       <c r="B64" t="n">
-        <v>2648</v>
+        <v>374</v>
       </c>
       <c r="C64" t="n">
         <v>8888</v>
       </c>
       <c r="D64" t="n">
-        <v>1594.42</v>
+        <v>44.6</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -1661,17 +1661,17 @@
         <v>46218</v>
       </c>
       <c r="B65" t="n">
-        <v>2714</v>
+        <v>703</v>
       </c>
       <c r="C65" t="n">
-        <v>519</v>
+        <v>8888</v>
       </c>
       <c r="D65" t="n">
-        <v>61939.22</v>
+        <v>12155.46</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1680,17 +1680,17 @@
         <v>46218</v>
       </c>
       <c r="B66" t="n">
-        <v>483</v>
+        <v>1756</v>
       </c>
       <c r="C66" t="n">
         <v>8888</v>
       </c>
       <c r="D66" t="n">
-        <v>6625.87</v>
+        <v>996.17</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1699,13 +1699,13 @@
         <v>46218</v>
       </c>
       <c r="B67" t="n">
-        <v>1075</v>
+        <v>1956</v>
       </c>
       <c r="C67" t="n">
         <v>8888</v>
       </c>
       <c r="D67" t="n">
-        <v>11607.79</v>
+        <v>4557.34</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -1718,17 +1718,17 @@
         <v>46218</v>
       </c>
       <c r="B68" t="n">
-        <v>629</v>
+        <v>925</v>
       </c>
       <c r="C68" t="n">
         <v>8888</v>
       </c>
       <c r="D68" t="n">
-        <v>9233.719999999999</v>
+        <v>651.59</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1737,17 +1737,17 @@
         <v>46218</v>
       </c>
       <c r="B69" t="n">
-        <v>1983</v>
+        <v>2648</v>
       </c>
       <c r="C69" t="n">
-        <v>841</v>
+        <v>8888</v>
       </c>
       <c r="D69" t="n">
-        <v>243.92</v>
+        <v>1594.42</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1756,17 +1756,17 @@
         <v>46218</v>
       </c>
       <c r="B70" t="n">
-        <v>1137</v>
+        <v>2714</v>
       </c>
       <c r="C70" t="n">
-        <v>8888</v>
+        <v>519</v>
       </c>
       <c r="D70" t="n">
-        <v>3578.51</v>
+        <v>61939.22</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1775,17 +1775,17 @@
         <v>46218</v>
       </c>
       <c r="B71" t="n">
-        <v>2651</v>
+        <v>483</v>
       </c>
       <c r="C71" t="n">
         <v>8888</v>
       </c>
       <c r="D71" t="n">
-        <v>1296.58</v>
+        <v>8624.57</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1794,17 +1794,17 @@
         <v>46218</v>
       </c>
       <c r="B72" t="n">
-        <v>1956</v>
+        <v>1075</v>
       </c>
       <c r="C72" t="n">
-        <v>423</v>
+        <v>8888</v>
       </c>
       <c r="D72" t="n">
-        <v>1416.35</v>
+        <v>11607.79</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1813,17 +1813,17 @@
         <v>46218</v>
       </c>
       <c r="B73" t="n">
-        <v>2709</v>
+        <v>629</v>
       </c>
       <c r="C73" t="n">
         <v>8888</v>
       </c>
       <c r="D73" t="n">
-        <v>547.6900000000001</v>
+        <v>9233.719999999999</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1832,17 +1832,17 @@
         <v>46218</v>
       </c>
       <c r="B74" t="n">
-        <v>1308</v>
+        <v>1983</v>
       </c>
       <c r="C74" t="n">
-        <v>8888</v>
+        <v>841</v>
       </c>
       <c r="D74" t="n">
-        <v>1460.53</v>
+        <v>243.92</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1851,17 +1851,17 @@
         <v>46218</v>
       </c>
       <c r="B75" t="n">
-        <v>2026</v>
+        <v>1137</v>
       </c>
       <c r="C75" t="n">
         <v>8888</v>
       </c>
       <c r="D75" t="n">
-        <v>2237.62</v>
+        <v>3578.51</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1870,17 +1870,17 @@
         <v>46218</v>
       </c>
       <c r="B76" t="n">
-        <v>2789</v>
+        <v>2651</v>
       </c>
       <c r="C76" t="n">
         <v>8888</v>
       </c>
       <c r="D76" t="n">
-        <v>747.77</v>
+        <v>1296.58</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1889,17 +1889,17 @@
         <v>46218</v>
       </c>
       <c r="B77" t="n">
-        <v>89</v>
+        <v>663</v>
       </c>
       <c r="C77" t="n">
-        <v>13148</v>
+        <v>8888</v>
       </c>
       <c r="D77" t="n">
-        <v>1883.74</v>
+        <v>5851.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1908,13 +1908,13 @@
         <v>46218</v>
       </c>
       <c r="B78" t="n">
-        <v>2709</v>
+        <v>1956</v>
       </c>
       <c r="C78" t="n">
-        <v>2220</v>
+        <v>423</v>
       </c>
       <c r="D78" t="n">
-        <v>390.19</v>
+        <v>1416.35</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -1927,13 +1927,13 @@
         <v>46218</v>
       </c>
       <c r="B79" t="n">
-        <v>2345</v>
+        <v>2709</v>
       </c>
       <c r="C79" t="n">
         <v>8888</v>
       </c>
       <c r="D79" t="n">
-        <v>748.86</v>
+        <v>547.6900000000001</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -1946,17 +1946,17 @@
         <v>46218</v>
       </c>
       <c r="B80" t="n">
-        <v>569</v>
+        <v>1308</v>
       </c>
       <c r="C80" t="n">
         <v>8888</v>
       </c>
       <c r="D80" t="n">
-        <v>995.33</v>
+        <v>1460.53</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1965,17 +1965,17 @@
         <v>46218</v>
       </c>
       <c r="B81" t="n">
-        <v>360</v>
+        <v>2026</v>
       </c>
       <c r="C81" t="n">
-        <v>546</v>
+        <v>8888</v>
       </c>
       <c r="D81" t="n">
-        <v>1609.68</v>
+        <v>2237.62</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1984,17 +1984,17 @@
         <v>46218</v>
       </c>
       <c r="B82" t="n">
-        <v>2308</v>
+        <v>2789</v>
       </c>
       <c r="C82" t="n">
         <v>8888</v>
       </c>
       <c r="D82" t="n">
-        <v>488.69</v>
+        <v>747.77</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2003,13 +2003,13 @@
         <v>46218</v>
       </c>
       <c r="B83" t="n">
-        <v>2211</v>
+        <v>89</v>
       </c>
       <c r="C83" t="n">
-        <v>874</v>
+        <v>13148</v>
       </c>
       <c r="D83" t="n">
-        <v>1526.94</v>
+        <v>1883.74</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2022,17 +2022,17 @@
         <v>46218</v>
       </c>
       <c r="B84" t="n">
-        <v>559</v>
+        <v>2709</v>
       </c>
       <c r="C84" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D84" t="n">
-        <v>859.92</v>
+        <v>390.19</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2041,17 +2041,17 @@
         <v>46218</v>
       </c>
       <c r="B85" t="n">
-        <v>890</v>
+        <v>2789</v>
       </c>
       <c r="C85" t="n">
         <v>8888</v>
       </c>
       <c r="D85" t="n">
-        <v>387.2</v>
+        <v>691.37</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2060,13 +2060,13 @@
         <v>46218</v>
       </c>
       <c r="B86" t="n">
-        <v>2768</v>
+        <v>2345</v>
       </c>
       <c r="C86" t="n">
         <v>8888</v>
       </c>
       <c r="D86" t="n">
-        <v>6523.26</v>
+        <v>748.86</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -2079,17 +2079,17 @@
         <v>46218</v>
       </c>
       <c r="B87" t="n">
-        <v>1063</v>
+        <v>2765</v>
       </c>
       <c r="C87" t="n">
-        <v>8888</v>
+        <v>1883</v>
       </c>
       <c r="D87" t="n">
-        <v>4487.11</v>
+        <v>3638.6</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2098,17 +2098,17 @@
         <v>46218</v>
       </c>
       <c r="B88" t="n">
-        <v>2279</v>
+        <v>569</v>
       </c>
       <c r="C88" t="n">
-        <v>1139</v>
+        <v>8888</v>
       </c>
       <c r="D88" t="n">
-        <v>652.51</v>
+        <v>995.33</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2117,13 +2117,13 @@
         <v>46218</v>
       </c>
       <c r="B89" t="n">
-        <v>1299</v>
+        <v>360</v>
       </c>
       <c r="C89" t="n">
-        <v>27</v>
+        <v>546</v>
       </c>
       <c r="D89" t="n">
-        <v>1435.52</v>
+        <v>1609.68</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -2136,17 +2136,17 @@
         <v>46218</v>
       </c>
       <c r="B90" t="n">
-        <v>1478</v>
+        <v>2308</v>
       </c>
       <c r="C90" t="n">
-        <v>675</v>
+        <v>8888</v>
       </c>
       <c r="D90" t="n">
-        <v>1600.01</v>
+        <v>488.69</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2155,17 +2155,17 @@
         <v>46218</v>
       </c>
       <c r="B91" t="n">
-        <v>285</v>
+        <v>2211</v>
       </c>
       <c r="C91" t="n">
-        <v>8888</v>
+        <v>874</v>
       </c>
       <c r="D91" t="n">
-        <v>3349.8</v>
+        <v>1526.94</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2174,13 +2174,13 @@
         <v>46218</v>
       </c>
       <c r="B92" t="n">
-        <v>1983</v>
+        <v>559</v>
       </c>
       <c r="C92" t="n">
         <v>8888</v>
       </c>
       <c r="D92" t="n">
-        <v>2451.28</v>
+        <v>859.92</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -2193,17 +2193,17 @@
         <v>46218</v>
       </c>
       <c r="B93" t="n">
-        <v>477</v>
+        <v>890</v>
       </c>
       <c r="C93" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D93" t="n">
-        <v>1540.55</v>
+        <v>387.2</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2212,17 +2212,17 @@
         <v>46218</v>
       </c>
       <c r="B94" t="n">
-        <v>1063</v>
+        <v>2768</v>
       </c>
       <c r="C94" t="n">
         <v>8888</v>
       </c>
       <c r="D94" t="n">
-        <v>2549.86</v>
+        <v>6523.26</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2231,17 +2231,17 @@
         <v>46218</v>
       </c>
       <c r="B95" t="n">
-        <v>424</v>
+        <v>1063</v>
       </c>
       <c r="C95" t="n">
         <v>8888</v>
       </c>
       <c r="D95" t="n">
-        <v>1035.17</v>
+        <v>4487.11</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2250,17 +2250,17 @@
         <v>46218</v>
       </c>
       <c r="B96" t="n">
-        <v>675</v>
+        <v>2279</v>
       </c>
       <c r="C96" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D96" t="n">
-        <v>616.73</v>
+        <v>652.51</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2269,17 +2269,17 @@
         <v>46218</v>
       </c>
       <c r="B97" t="n">
-        <v>1993</v>
+        <v>1299</v>
       </c>
       <c r="C97" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D97" t="n">
-        <v>362.63</v>
+        <v>1435.52</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
         <v>46218</v>
       </c>
       <c r="B98" t="n">
-        <v>1465</v>
+        <v>1478</v>
       </c>
       <c r="C98" t="n">
-        <v>8888</v>
+        <v>675</v>
       </c>
       <c r="D98" t="n">
-        <v>3373.83</v>
+        <v>1600.01</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2307,17 +2307,17 @@
         <v>46218</v>
       </c>
       <c r="B99" t="n">
-        <v>89</v>
+        <v>285</v>
       </c>
       <c r="C99" t="n">
         <v>8888</v>
       </c>
       <c r="D99" t="n">
-        <v>479</v>
+        <v>3349.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2326,17 +2326,17 @@
         <v>46218</v>
       </c>
       <c r="B100" t="n">
-        <v>595</v>
+        <v>477</v>
       </c>
       <c r="C100" t="n">
         <v>8888</v>
       </c>
       <c r="D100" t="n">
-        <v>18084.5</v>
+        <v>917.33</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2345,17 +2345,17 @@
         <v>46218</v>
       </c>
       <c r="B101" t="n">
-        <v>2696</v>
+        <v>1983</v>
       </c>
       <c r="C101" t="n">
-        <v>1954</v>
+        <v>8888</v>
       </c>
       <c r="D101" t="n">
-        <v>1597.76</v>
+        <v>5115.01</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2364,17 +2364,17 @@
         <v>46218</v>
       </c>
       <c r="B102" t="n">
-        <v>360</v>
+        <v>477</v>
       </c>
       <c r="C102" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D102" t="n">
-        <v>4596.89</v>
+        <v>1540.55</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2383,17 +2383,17 @@
         <v>46218</v>
       </c>
       <c r="B103" t="n">
-        <v>1465</v>
+        <v>1063</v>
       </c>
       <c r="C103" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D103" t="n">
-        <v>777.2</v>
+        <v>2549.86</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2402,17 +2402,17 @@
         <v>46218</v>
       </c>
       <c r="B104" t="n">
-        <v>947</v>
+        <v>424</v>
       </c>
       <c r="C104" t="n">
         <v>8888</v>
       </c>
       <c r="D104" t="n">
-        <v>2087.97</v>
+        <v>1362.42</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>PEDIDO ELETRÔNICO</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2421,17 +2421,17 @@
         <v>46218</v>
       </c>
       <c r="B105" t="n">
-        <v>2178</v>
+        <v>675</v>
       </c>
       <c r="C105" t="n">
         <v>8888</v>
       </c>
       <c r="D105" t="n">
-        <v>619.92</v>
+        <v>616.73</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2440,17 +2440,17 @@
         <v>46218</v>
       </c>
       <c r="B106" t="n">
-        <v>630</v>
+        <v>663</v>
       </c>
       <c r="C106" t="n">
-        <v>1929</v>
+        <v>8888</v>
       </c>
       <c r="D106" t="n">
-        <v>1801.63</v>
+        <v>255.13</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2459,17 +2459,17 @@
         <v>46218</v>
       </c>
       <c r="B107" t="n">
-        <v>1937</v>
+        <v>1993</v>
       </c>
       <c r="C107" t="n">
         <v>8888</v>
       </c>
       <c r="D107" t="n">
-        <v>2132.95</v>
+        <v>362.63</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2478,13 +2478,13 @@
         <v>46218</v>
       </c>
       <c r="B108" t="n">
-        <v>2577</v>
+        <v>1465</v>
       </c>
       <c r="C108" t="n">
         <v>8888</v>
       </c>
       <c r="D108" t="n">
-        <v>1647.08</v>
+        <v>3373.83</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -2497,17 +2497,17 @@
         <v>46218</v>
       </c>
       <c r="B109" t="n">
-        <v>1293</v>
+        <v>89</v>
       </c>
       <c r="C109" t="n">
         <v>8888</v>
       </c>
       <c r="D109" t="n">
-        <v>2135.89</v>
+        <v>479</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2516,17 +2516,17 @@
         <v>46218</v>
       </c>
       <c r="B110" t="n">
-        <v>2026</v>
+        <v>595</v>
       </c>
       <c r="C110" t="n">
-        <v>1929</v>
+        <v>8888</v>
       </c>
       <c r="D110" t="n">
-        <v>1680.89</v>
+        <v>18084.5</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2535,17 +2535,17 @@
         <v>46218</v>
       </c>
       <c r="B111" t="n">
-        <v>2607</v>
+        <v>2696</v>
       </c>
       <c r="C111" t="n">
-        <v>8888</v>
+        <v>1954</v>
       </c>
       <c r="D111" t="n">
-        <v>490.31</v>
+        <v>1597.76</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2554,17 +2554,17 @@
         <v>46218</v>
       </c>
       <c r="B112" t="n">
-        <v>1317</v>
+        <v>360</v>
       </c>
       <c r="C112" t="n">
         <v>8888</v>
       </c>
       <c r="D112" t="n">
-        <v>907.72</v>
+        <v>4596.89</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2573,17 +2573,17 @@
         <v>46218</v>
       </c>
       <c r="B113" t="n">
-        <v>767</v>
+        <v>1465</v>
       </c>
       <c r="C113" t="n">
-        <v>8888</v>
+        <v>3403</v>
       </c>
       <c r="D113" t="n">
-        <v>637.23</v>
+        <v>777.2</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2592,17 +2592,17 @@
         <v>46218</v>
       </c>
       <c r="B114" t="n">
-        <v>2571</v>
+        <v>947</v>
       </c>
       <c r="C114" t="n">
-        <v>1312</v>
+        <v>8888</v>
       </c>
       <c r="D114" t="n">
-        <v>268.53</v>
+        <v>5115.36</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>PEDIDO ELETRÔNICO</t>
         </is>
       </c>
     </row>
@@ -2611,17 +2611,17 @@
         <v>46218</v>
       </c>
       <c r="B115" t="n">
-        <v>1937</v>
+        <v>2178</v>
       </c>
       <c r="C115" t="n">
         <v>8888</v>
       </c>
       <c r="D115" t="n">
-        <v>1803.32</v>
+        <v>619.92</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2630,17 +2630,17 @@
         <v>46218</v>
       </c>
       <c r="B116" t="n">
-        <v>1063</v>
+        <v>2026</v>
       </c>
       <c r="C116" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D116" t="n">
-        <v>1113.08</v>
+        <v>3418.07</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2649,17 +2649,17 @@
         <v>46218</v>
       </c>
       <c r="B117" t="n">
-        <v>2631</v>
+        <v>630</v>
       </c>
       <c r="C117" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D117" t="n">
-        <v>1447.86</v>
+        <v>1801.63</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2668,17 +2668,17 @@
         <v>46218</v>
       </c>
       <c r="B118" t="n">
-        <v>1906</v>
+        <v>1937</v>
       </c>
       <c r="C118" t="n">
         <v>8888</v>
       </c>
       <c r="D118" t="n">
-        <v>2774.84</v>
+        <v>2132.95</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2687,13 +2687,13 @@
         <v>46218</v>
       </c>
       <c r="B119" t="n">
-        <v>1756</v>
+        <v>2577</v>
       </c>
       <c r="C119" t="n">
         <v>8888</v>
       </c>
       <c r="D119" t="n">
-        <v>1357.12</v>
+        <v>1647.08</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -2706,17 +2706,17 @@
         <v>46218</v>
       </c>
       <c r="B120" t="n">
-        <v>20</v>
+        <v>1293</v>
       </c>
       <c r="C120" t="n">
         <v>8888</v>
       </c>
       <c r="D120" t="n">
-        <v>276.64</v>
+        <v>2135.89</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2725,17 +2725,17 @@
         <v>46218</v>
       </c>
       <c r="B121" t="n">
-        <v>477</v>
+        <v>2607</v>
       </c>
       <c r="C121" t="n">
         <v>8888</v>
       </c>
       <c r="D121" t="n">
-        <v>372.69</v>
+        <v>490.31</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2744,13 +2744,13 @@
         <v>46218</v>
       </c>
       <c r="B122" t="n">
-        <v>477</v>
+        <v>1317</v>
       </c>
       <c r="C122" t="n">
         <v>8888</v>
       </c>
       <c r="D122" t="n">
-        <v>707.52</v>
+        <v>907.72</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -2763,13 +2763,13 @@
         <v>46218</v>
       </c>
       <c r="B123" t="n">
-        <v>2660</v>
+        <v>767</v>
       </c>
       <c r="C123" t="n">
         <v>8888</v>
       </c>
       <c r="D123" t="n">
-        <v>2684.97</v>
+        <v>637.23</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -2782,17 +2782,17 @@
         <v>46218</v>
       </c>
       <c r="B124" t="n">
-        <v>569</v>
+        <v>2571</v>
       </c>
       <c r="C124" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D124" t="n">
-        <v>23608.83</v>
+        <v>268.53</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2801,17 +2801,17 @@
         <v>46218</v>
       </c>
       <c r="B125" t="n">
-        <v>2089</v>
+        <v>1937</v>
       </c>
       <c r="C125" t="n">
-        <v>1533</v>
+        <v>8888</v>
       </c>
       <c r="D125" t="n">
-        <v>969.24</v>
+        <v>1803.32</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2820,13 +2820,13 @@
         <v>46218</v>
       </c>
       <c r="B126" t="n">
-        <v>1007</v>
+        <v>20</v>
       </c>
       <c r="C126" t="n">
         <v>8888</v>
       </c>
       <c r="D126" t="n">
-        <v>241.44</v>
+        <v>745.55</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -2839,17 +2839,17 @@
         <v>46218</v>
       </c>
       <c r="B127" t="n">
-        <v>1380</v>
+        <v>1063</v>
       </c>
       <c r="C127" t="n">
         <v>8888</v>
       </c>
       <c r="D127" t="n">
-        <v>520.2</v>
+        <v>1113.08</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2858,17 +2858,17 @@
         <v>46218</v>
       </c>
       <c r="B128" t="n">
-        <v>1102</v>
+        <v>2631</v>
       </c>
       <c r="C128" t="n">
         <v>8888</v>
       </c>
       <c r="D128" t="n">
-        <v>1137.04</v>
+        <v>1447.86</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2877,13 +2877,13 @@
         <v>46218</v>
       </c>
       <c r="B129" t="n">
-        <v>1075</v>
+        <v>1906</v>
       </c>
       <c r="C129" t="n">
         <v>8888</v>
       </c>
       <c r="D129" t="n">
-        <v>2179.03</v>
+        <v>2774.84</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -2896,17 +2896,17 @@
         <v>46218</v>
       </c>
       <c r="B130" t="n">
-        <v>2681</v>
+        <v>1756</v>
       </c>
       <c r="C130" t="n">
         <v>8888</v>
       </c>
       <c r="D130" t="n">
-        <v>729.25</v>
+        <v>2275.21</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2915,13 +2915,13 @@
         <v>46218</v>
       </c>
       <c r="B131" t="n">
-        <v>2245</v>
+        <v>477</v>
       </c>
       <c r="C131" t="n">
         <v>8888</v>
       </c>
       <c r="D131" t="n">
-        <v>361.58</v>
+        <v>707.52</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -2934,17 +2934,17 @@
         <v>46218</v>
       </c>
       <c r="B132" t="n">
-        <v>132</v>
+        <v>2660</v>
       </c>
       <c r="C132" t="n">
         <v>8888</v>
       </c>
       <c r="D132" t="n">
-        <v>6522.92</v>
+        <v>2684.97</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2953,17 +2953,17 @@
         <v>46218</v>
       </c>
       <c r="B133" t="n">
-        <v>452</v>
+        <v>569</v>
       </c>
       <c r="C133" t="n">
         <v>8888</v>
       </c>
       <c r="D133" t="n">
-        <v>608.78</v>
+        <v>33214.39</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2972,17 +2972,17 @@
         <v>46218</v>
       </c>
       <c r="B134" t="n">
-        <v>1293</v>
+        <v>483</v>
       </c>
       <c r="C134" t="n">
-        <v>1281</v>
+        <v>8888</v>
       </c>
       <c r="D134" t="n">
-        <v>1780.93</v>
+        <v>2401.99</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2991,17 +2991,17 @@
         <v>46218</v>
       </c>
       <c r="B135" t="n">
-        <v>525</v>
+        <v>483</v>
       </c>
       <c r="C135" t="n">
         <v>8888</v>
       </c>
       <c r="D135" t="n">
-        <v>5658.57</v>
+        <v>1124.96</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3010,17 +3010,17 @@
         <v>46218</v>
       </c>
       <c r="B136" t="n">
-        <v>2641</v>
+        <v>2089</v>
       </c>
       <c r="C136" t="n">
-        <v>8888</v>
+        <v>1533</v>
       </c>
       <c r="D136" t="n">
-        <v>1720.99</v>
+        <v>1309.01</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3029,17 +3029,17 @@
         <v>46218</v>
       </c>
       <c r="B137" t="n">
-        <v>609</v>
+        <v>1007</v>
       </c>
       <c r="C137" t="n">
         <v>8888</v>
       </c>
       <c r="D137" t="n">
-        <v>886.1</v>
+        <v>241.44</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3048,17 +3048,17 @@
         <v>46218</v>
       </c>
       <c r="B138" t="n">
-        <v>619</v>
+        <v>1380</v>
       </c>
       <c r="C138" t="n">
         <v>8888</v>
       </c>
       <c r="D138" t="n">
-        <v>2330.47</v>
+        <v>520.2</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3067,13 +3067,13 @@
         <v>46218</v>
       </c>
       <c r="B139" t="n">
-        <v>2697</v>
+        <v>1102</v>
       </c>
       <c r="C139" t="n">
         <v>8888</v>
       </c>
       <c r="D139" t="n">
-        <v>418.65</v>
+        <v>1137.04</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -3086,13 +3086,13 @@
         <v>46218</v>
       </c>
       <c r="B140" t="n">
-        <v>58</v>
+        <v>1075</v>
       </c>
       <c r="C140" t="n">
         <v>8888</v>
       </c>
       <c r="D140" t="n">
-        <v>1123.87</v>
+        <v>4194.79</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -3105,13 +3105,13 @@
         <v>46218</v>
       </c>
       <c r="B141" t="n">
-        <v>358</v>
+        <v>2681</v>
       </c>
       <c r="C141" t="n">
         <v>8888</v>
       </c>
       <c r="D141" t="n">
-        <v>1675.95</v>
+        <v>729.25</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -3124,17 +3124,17 @@
         <v>46218</v>
       </c>
       <c r="B142" t="n">
-        <v>2431</v>
+        <v>2245</v>
       </c>
       <c r="C142" t="n">
         <v>8888</v>
       </c>
       <c r="D142" t="n">
-        <v>266.89</v>
+        <v>361.58</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3143,13 +3143,13 @@
         <v>46218</v>
       </c>
       <c r="B143" t="n">
-        <v>285</v>
+        <v>33</v>
       </c>
       <c r="C143" t="n">
         <v>8888</v>
       </c>
       <c r="D143" t="n">
-        <v>2090.81</v>
+        <v>926.97</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -3162,17 +3162,17 @@
         <v>46218</v>
       </c>
       <c r="B144" t="n">
-        <v>1102</v>
+        <v>132</v>
       </c>
       <c r="C144" t="n">
         <v>8888</v>
       </c>
       <c r="D144" t="n">
-        <v>1119.32</v>
+        <v>6522.92</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3181,17 +3181,17 @@
         <v>46218</v>
       </c>
       <c r="B145" t="n">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="C145" t="n">
         <v>8888</v>
       </c>
       <c r="D145" t="n">
-        <v>12556.19</v>
+        <v>2912.89</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3200,17 +3200,17 @@
         <v>46218</v>
       </c>
       <c r="B146" t="n">
-        <v>1137</v>
+        <v>452</v>
       </c>
       <c r="C146" t="n">
-        <v>2220</v>
+        <v>8888</v>
       </c>
       <c r="D146" t="n">
-        <v>1370.86</v>
+        <v>608.78</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3219,17 +3219,17 @@
         <v>46218</v>
       </c>
       <c r="B147" t="n">
-        <v>2686</v>
+        <v>2463</v>
       </c>
       <c r="C147" t="n">
-        <v>1929</v>
+        <v>8888</v>
       </c>
       <c r="D147" t="n">
-        <v>2066.36</v>
+        <v>363.69</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3238,13 +3238,13 @@
         <v>46218</v>
       </c>
       <c r="B148" t="n">
-        <v>1756</v>
+        <v>1293</v>
       </c>
       <c r="C148" t="n">
-        <v>27</v>
+        <v>1281</v>
       </c>
       <c r="D148" t="n">
-        <v>5078.1</v>
+        <v>1780.93</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -3257,17 +3257,17 @@
         <v>46218</v>
       </c>
       <c r="B149" t="n">
-        <v>2651</v>
+        <v>525</v>
       </c>
       <c r="C149" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D149" t="n">
-        <v>363.7</v>
+        <v>5658.57</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3276,13 +3276,13 @@
         <v>46218</v>
       </c>
       <c r="B150" t="n">
-        <v>360</v>
+        <v>2641</v>
       </c>
       <c r="C150" t="n">
         <v>8888</v>
       </c>
       <c r="D150" t="n">
-        <v>1594.84</v>
+        <v>1720.99</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -3295,13 +3295,13 @@
         <v>46218</v>
       </c>
       <c r="B151" t="n">
-        <v>2582</v>
+        <v>609</v>
       </c>
       <c r="C151" t="n">
         <v>8888</v>
       </c>
       <c r="D151" t="n">
-        <v>379.33</v>
+        <v>886.1</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -3314,17 +3314,17 @@
         <v>46218</v>
       </c>
       <c r="B152" t="n">
-        <v>1756</v>
+        <v>2697</v>
       </c>
       <c r="C152" t="n">
         <v>8888</v>
       </c>
       <c r="D152" t="n">
-        <v>1715.26</v>
+        <v>418.65</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3333,13 +3333,13 @@
         <v>46218</v>
       </c>
       <c r="B153" t="n">
-        <v>636</v>
+        <v>58</v>
       </c>
       <c r="C153" t="n">
         <v>8888</v>
       </c>
       <c r="D153" t="n">
-        <v>2447.56</v>
+        <v>1123.87</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -3352,17 +3352,17 @@
         <v>46218</v>
       </c>
       <c r="B154" t="n">
-        <v>1254</v>
+        <v>358</v>
       </c>
       <c r="C154" t="n">
         <v>8888</v>
       </c>
       <c r="D154" t="n">
-        <v>855.76</v>
+        <v>1675.95</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3371,13 +3371,13 @@
         <v>46218</v>
       </c>
       <c r="B155" t="n">
-        <v>1289</v>
+        <v>2431</v>
       </c>
       <c r="C155" t="n">
         <v>8888</v>
       </c>
       <c r="D155" t="n">
-        <v>2396.98</v>
+        <v>266.89</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -3390,17 +3390,17 @@
         <v>46218</v>
       </c>
       <c r="B156" t="n">
-        <v>2015</v>
+        <v>285</v>
       </c>
       <c r="C156" t="n">
         <v>8888</v>
       </c>
       <c r="D156" t="n">
-        <v>315.69</v>
+        <v>5673.85</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3409,17 +3409,17 @@
         <v>46218</v>
       </c>
       <c r="B157" t="n">
-        <v>1064</v>
+        <v>1102</v>
       </c>
       <c r="C157" t="n">
         <v>8888</v>
       </c>
       <c r="D157" t="n">
-        <v>1274.3</v>
+        <v>1119.32</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3428,17 +3428,17 @@
         <v>46218</v>
       </c>
       <c r="B158" t="n">
-        <v>2698</v>
+        <v>626</v>
       </c>
       <c r="C158" t="n">
         <v>8888</v>
       </c>
       <c r="D158" t="n">
-        <v>552.15</v>
+        <v>12556.19</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3447,17 +3447,17 @@
         <v>46218</v>
       </c>
       <c r="B159" t="n">
-        <v>629</v>
+        <v>1137</v>
       </c>
       <c r="C159" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D159" t="n">
-        <v>3035.38</v>
+        <v>1370.86</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3466,17 +3466,17 @@
         <v>46218</v>
       </c>
       <c r="B160" t="n">
-        <v>664</v>
+        <v>2686</v>
       </c>
       <c r="C160" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D160" t="n">
-        <v>4973.15</v>
+        <v>2066.36</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3491,7 @@
         <v>8888</v>
       </c>
       <c r="D161" t="n">
-        <v>1852.83</v>
+        <v>5635.67</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -3504,17 +3504,17 @@
         <v>46218</v>
       </c>
       <c r="B162" t="n">
-        <v>2641</v>
+        <v>1756</v>
       </c>
       <c r="C162" t="n">
         <v>8888</v>
       </c>
       <c r="D162" t="n">
-        <v>820</v>
+        <v>2201.67</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3523,17 +3523,17 @@
         <v>46218</v>
       </c>
       <c r="B163" t="n">
-        <v>429</v>
+        <v>1756</v>
       </c>
       <c r="C163" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D163" t="n">
-        <v>2593.49</v>
+        <v>5078.1</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3542,17 +3542,17 @@
         <v>46218</v>
       </c>
       <c r="B164" t="n">
-        <v>816</v>
+        <v>2651</v>
       </c>
       <c r="C164" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D164" t="n">
-        <v>438.24</v>
+        <v>363.7</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3561,13 +3561,13 @@
         <v>46218</v>
       </c>
       <c r="B165" t="n">
-        <v>2793</v>
+        <v>664</v>
       </c>
       <c r="C165" t="n">
         <v>8888</v>
       </c>
       <c r="D165" t="n">
-        <v>767.58</v>
+        <v>5672.57</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -3580,17 +3580,17 @@
         <v>46218</v>
       </c>
       <c r="B166" t="n">
-        <v>2359</v>
+        <v>360</v>
       </c>
       <c r="C166" t="n">
         <v>8888</v>
       </c>
       <c r="D166" t="n">
-        <v>381.95</v>
+        <v>1594.84</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3599,17 +3599,17 @@
         <v>46218</v>
       </c>
       <c r="B167" t="n">
-        <v>285</v>
+        <v>2582</v>
       </c>
       <c r="C167" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D167" t="n">
-        <v>364.99</v>
+        <v>379.33</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3618,13 +3618,13 @@
         <v>46218</v>
       </c>
       <c r="B168" t="n">
-        <v>2114</v>
+        <v>636</v>
       </c>
       <c r="C168" t="n">
         <v>8888</v>
       </c>
       <c r="D168" t="n">
-        <v>2726.04</v>
+        <v>2447.56</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -3637,17 +3637,17 @@
         <v>46218</v>
       </c>
       <c r="B169" t="n">
-        <v>953</v>
+        <v>1254</v>
       </c>
       <c r="C169" t="n">
         <v>8888</v>
       </c>
       <c r="D169" t="n">
-        <v>2618.89</v>
+        <v>2643.22</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3656,17 +3656,17 @@
         <v>46218</v>
       </c>
       <c r="B170" t="n">
-        <v>1102</v>
+        <v>1289</v>
       </c>
       <c r="C170" t="n">
         <v>8888</v>
       </c>
       <c r="D170" t="n">
-        <v>2344.41</v>
+        <v>2396.98</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3675,17 +3675,17 @@
         <v>46218</v>
       </c>
       <c r="B171" t="n">
-        <v>619</v>
+        <v>2726</v>
       </c>
       <c r="C171" t="n">
-        <v>8888</v>
+        <v>977</v>
       </c>
       <c r="D171" t="n">
-        <v>2021.67</v>
+        <v>586.0599999999999</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3694,13 +3694,13 @@
         <v>46218</v>
       </c>
       <c r="B172" t="n">
-        <v>1465</v>
+        <v>2015</v>
       </c>
       <c r="C172" t="n">
         <v>8888</v>
       </c>
       <c r="D172" t="n">
-        <v>3504</v>
+        <v>315.69</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -3713,17 +3713,17 @@
         <v>46218</v>
       </c>
       <c r="B173" t="n">
-        <v>2767</v>
+        <v>1064</v>
       </c>
       <c r="C173" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D173" t="n">
-        <v>1135.64</v>
+        <v>1274.3</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3732,13 +3732,13 @@
         <v>46218</v>
       </c>
       <c r="B174" t="n">
-        <v>2245</v>
+        <v>2698</v>
       </c>
       <c r="C174" t="n">
         <v>8888</v>
       </c>
       <c r="D174" t="n">
-        <v>427.51</v>
+        <v>552.15</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -3751,17 +3751,17 @@
         <v>46218</v>
       </c>
       <c r="B175" t="n">
-        <v>2197</v>
+        <v>629</v>
       </c>
       <c r="C175" t="n">
         <v>8888</v>
       </c>
       <c r="D175" t="n">
-        <v>1085.45</v>
+        <v>3544.51</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3770,17 +3770,17 @@
         <v>46218</v>
       </c>
       <c r="B176" t="n">
-        <v>2657</v>
+        <v>2641</v>
       </c>
       <c r="C176" t="n">
         <v>8888</v>
       </c>
       <c r="D176" t="n">
-        <v>2683.06</v>
+        <v>820</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3789,13 +3789,13 @@
         <v>46218</v>
       </c>
       <c r="B177" t="n">
-        <v>1277</v>
+        <v>429</v>
       </c>
       <c r="C177" t="n">
         <v>8888</v>
       </c>
       <c r="D177" t="n">
-        <v>1949</v>
+        <v>2593.49</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -3808,17 +3808,17 @@
         <v>46218</v>
       </c>
       <c r="B178" t="n">
-        <v>131</v>
+        <v>816</v>
       </c>
       <c r="C178" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D178" t="n">
-        <v>1268.57</v>
+        <v>438.24</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3827,17 +3827,17 @@
         <v>46218</v>
       </c>
       <c r="B179" t="n">
-        <v>2692</v>
+        <v>2793</v>
       </c>
       <c r="C179" t="n">
         <v>8888</v>
       </c>
       <c r="D179" t="n">
-        <v>731.28</v>
+        <v>767.58</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3846,17 +3846,17 @@
         <v>46218</v>
       </c>
       <c r="B180" t="n">
-        <v>1317</v>
+        <v>2359</v>
       </c>
       <c r="C180" t="n">
-        <v>3179</v>
+        <v>8888</v>
       </c>
       <c r="D180" t="n">
-        <v>991.6799999999999</v>
+        <v>381.95</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3865,17 +3865,17 @@
         <v>46218</v>
       </c>
       <c r="B181" t="n">
-        <v>1993</v>
+        <v>285</v>
       </c>
       <c r="C181" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D181" t="n">
-        <v>2875.39</v>
+        <v>364.99</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3884,13 +3884,13 @@
         <v>46218</v>
       </c>
       <c r="B182" t="n">
-        <v>1632</v>
+        <v>2114</v>
       </c>
       <c r="C182" t="n">
         <v>8888</v>
       </c>
       <c r="D182" t="n">
-        <v>564.55</v>
+        <v>2726.04</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -3903,17 +3903,17 @@
         <v>46218</v>
       </c>
       <c r="B183" t="n">
-        <v>1890</v>
+        <v>953</v>
       </c>
       <c r="C183" t="n">
-        <v>3449</v>
+        <v>8888</v>
       </c>
       <c r="D183" t="n">
-        <v>3590.04</v>
+        <v>2889.63</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3922,17 +3922,17 @@
         <v>46218</v>
       </c>
       <c r="B184" t="n">
-        <v>451</v>
+        <v>1102</v>
       </c>
       <c r="C184" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D184" t="n">
-        <v>445.58</v>
+        <v>3093.73</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3941,13 +3941,13 @@
         <v>46218</v>
       </c>
       <c r="B185" t="n">
-        <v>2749</v>
+        <v>1465</v>
       </c>
       <c r="C185" t="n">
         <v>8888</v>
       </c>
       <c r="D185" t="n">
-        <v>1860.64</v>
+        <v>4281.39</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -3960,17 +3960,17 @@
         <v>46218</v>
       </c>
       <c r="B186" t="n">
-        <v>1117</v>
+        <v>619</v>
       </c>
       <c r="C186" t="n">
         <v>8888</v>
       </c>
       <c r="D186" t="n">
-        <v>342.2</v>
+        <v>2021.67</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3979,13 +3979,13 @@
         <v>46218</v>
       </c>
       <c r="B187" t="n">
-        <v>1478</v>
+        <v>2716</v>
       </c>
       <c r="C187" t="n">
         <v>8888</v>
       </c>
       <c r="D187" t="n">
-        <v>875.34</v>
+        <v>601.58</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -3998,17 +3998,17 @@
         <v>46218</v>
       </c>
       <c r="B188" t="n">
-        <v>2491</v>
+        <v>2767</v>
       </c>
       <c r="C188" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D188" t="n">
-        <v>650.4299999999999</v>
+        <v>1135.64</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4017,13 +4017,13 @@
         <v>46218</v>
       </c>
       <c r="B189" t="n">
-        <v>2015</v>
+        <v>2245</v>
       </c>
       <c r="C189" t="n">
         <v>8888</v>
       </c>
       <c r="D189" t="n">
-        <v>4436.15</v>
+        <v>427.51</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -4036,17 +4036,17 @@
         <v>46218</v>
       </c>
       <c r="B190" t="n">
-        <v>1890</v>
+        <v>2197</v>
       </c>
       <c r="C190" t="n">
-        <v>1953</v>
+        <v>8888</v>
       </c>
       <c r="D190" t="n">
-        <v>1674.57</v>
+        <v>1085.45</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4055,13 +4055,13 @@
         <v>46218</v>
       </c>
       <c r="B191" t="n">
-        <v>2782</v>
+        <v>2657</v>
       </c>
       <c r="C191" t="n">
         <v>8888</v>
       </c>
       <c r="D191" t="n">
-        <v>1786.32</v>
+        <v>2683.06</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -4074,13 +4074,13 @@
         <v>46218</v>
       </c>
       <c r="B192" t="n">
-        <v>483</v>
+        <v>451</v>
       </c>
       <c r="C192" t="n">
-        <v>841</v>
+        <v>3403</v>
       </c>
       <c r="D192" t="n">
-        <v>1393.15</v>
+        <v>2091.77</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -4093,13 +4093,13 @@
         <v>46218</v>
       </c>
       <c r="B193" t="n">
-        <v>2133</v>
+        <v>1116</v>
       </c>
       <c r="C193" t="n">
-        <v>213</v>
+        <v>13148</v>
       </c>
       <c r="D193" t="n">
-        <v>526.8</v>
+        <v>207.91</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -4112,17 +4112,17 @@
         <v>46218</v>
       </c>
       <c r="B194" t="n">
-        <v>351</v>
+        <v>1277</v>
       </c>
       <c r="C194" t="n">
-        <v>3009</v>
+        <v>8888</v>
       </c>
       <c r="D194" t="n">
-        <v>416.36</v>
+        <v>1949</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4131,17 +4131,17 @@
         <v>46218</v>
       </c>
       <c r="B195" t="n">
-        <v>2250</v>
+        <v>131</v>
       </c>
       <c r="C195" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D195" t="n">
-        <v>709.46</v>
+        <v>3850.09</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4150,17 +4150,17 @@
         <v>46218</v>
       </c>
       <c r="B196" t="n">
-        <v>2648</v>
+        <v>2692</v>
       </c>
       <c r="C196" t="n">
         <v>8888</v>
       </c>
       <c r="D196" t="n">
-        <v>1873.52</v>
+        <v>731.28</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4169,17 +4169,17 @@
         <v>46218</v>
       </c>
       <c r="B197" t="n">
-        <v>131</v>
+        <v>1632</v>
       </c>
       <c r="C197" t="n">
         <v>8888</v>
       </c>
       <c r="D197" t="n">
-        <v>1369.91</v>
+        <v>7519.7</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4188,13 +4188,13 @@
         <v>46218</v>
       </c>
       <c r="B198" t="n">
-        <v>2790</v>
+        <v>1317</v>
       </c>
       <c r="C198" t="n">
-        <v>1953</v>
+        <v>3179</v>
       </c>
       <c r="D198" t="n">
-        <v>371.88</v>
+        <v>991.6799999999999</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -4207,17 +4207,17 @@
         <v>46218</v>
       </c>
       <c r="B199" t="n">
-        <v>363</v>
+        <v>1993</v>
       </c>
       <c r="C199" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D199" t="n">
-        <v>635.1</v>
+        <v>2875.39</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4226,13 +4226,13 @@
         <v>46218</v>
       </c>
       <c r="B200" t="n">
-        <v>2716</v>
+        <v>1890</v>
       </c>
       <c r="C200" t="n">
-        <v>1929</v>
+        <v>3449</v>
       </c>
       <c r="D200" t="n">
-        <v>1073.33</v>
+        <v>6313.56</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -4245,17 +4245,17 @@
         <v>46218</v>
       </c>
       <c r="B201" t="n">
-        <v>2639</v>
+        <v>2749</v>
       </c>
       <c r="C201" t="n">
-        <v>1953</v>
+        <v>8888</v>
       </c>
       <c r="D201" t="n">
-        <v>504.09</v>
+        <v>1860.64</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4264,17 +4264,17 @@
         <v>46218</v>
       </c>
       <c r="B202" t="n">
-        <v>2109</v>
+        <v>1117</v>
       </c>
       <c r="C202" t="n">
         <v>8888</v>
       </c>
       <c r="D202" t="n">
-        <v>2293.78</v>
+        <v>342.2</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4283,17 +4283,17 @@
         <v>46218</v>
       </c>
       <c r="B203" t="n">
-        <v>1116</v>
+        <v>42</v>
       </c>
       <c r="C203" t="n">
         <v>8888</v>
       </c>
       <c r="D203" t="n">
-        <v>2919.53</v>
+        <v>280.05</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4302,17 +4302,17 @@
         <v>46218</v>
       </c>
       <c r="B204" t="n">
-        <v>2250</v>
+        <v>1478</v>
       </c>
       <c r="C204" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D204" t="n">
-        <v>1803.76</v>
+        <v>875.34</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4321,13 +4321,13 @@
         <v>46218</v>
       </c>
       <c r="B205" t="n">
-        <v>353</v>
+        <v>2491</v>
       </c>
       <c r="C205" t="n">
         <v>8888</v>
       </c>
       <c r="D205" t="n">
-        <v>108.6</v>
+        <v>650.4299999999999</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -4340,17 +4340,17 @@
         <v>46218</v>
       </c>
       <c r="B206" t="n">
-        <v>2698</v>
+        <v>2015</v>
       </c>
       <c r="C206" t="n">
-        <v>874</v>
+        <v>8888</v>
       </c>
       <c r="D206" t="n">
-        <v>1230.43</v>
+        <v>4436.15</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4359,17 +4359,17 @@
         <v>46218</v>
       </c>
       <c r="B207" t="n">
-        <v>42</v>
+        <v>1890</v>
       </c>
       <c r="C207" t="n">
-        <v>8888</v>
+        <v>1953</v>
       </c>
       <c r="D207" t="n">
-        <v>79947.14999999999</v>
+        <v>1674.57</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4378,17 +4378,17 @@
         <v>46218</v>
       </c>
       <c r="B208" t="n">
-        <v>772</v>
+        <v>1317</v>
       </c>
       <c r="C208" t="n">
         <v>8888</v>
       </c>
       <c r="D208" t="n">
-        <v>400.25</v>
+        <v>1626.02</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4397,17 +4397,17 @@
         <v>46218</v>
       </c>
       <c r="B209" t="n">
-        <v>2728</v>
+        <v>2782</v>
       </c>
       <c r="C209" t="n">
         <v>8888</v>
       </c>
       <c r="D209" t="n">
-        <v>1397.07</v>
+        <v>1786.32</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4416,17 +4416,17 @@
         <v>46218</v>
       </c>
       <c r="B210" t="n">
-        <v>2197</v>
+        <v>953</v>
       </c>
       <c r="C210" t="n">
-        <v>423</v>
+        <v>8888</v>
       </c>
       <c r="D210" t="n">
-        <v>2267.61</v>
+        <v>364.44</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4435,17 +4435,17 @@
         <v>46218</v>
       </c>
       <c r="B211" t="n">
-        <v>2716</v>
+        <v>2251</v>
       </c>
       <c r="C211" t="n">
-        <v>977</v>
+        <v>8888</v>
       </c>
       <c r="D211" t="n">
-        <v>729.29</v>
+        <v>309.22</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4454,17 +4454,17 @@
         <v>46218</v>
       </c>
       <c r="B212" t="n">
-        <v>1993</v>
+        <v>483</v>
       </c>
       <c r="C212" t="n">
-        <v>8888</v>
+        <v>841</v>
       </c>
       <c r="D212" t="n">
-        <v>456.62</v>
+        <v>2085.09</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4473,15 +4473,414 @@
         <v>46218</v>
       </c>
       <c r="B213" t="n">
+        <v>2133</v>
+      </c>
+      <c r="C213" t="n">
+        <v>213</v>
+      </c>
+      <c r="D213" t="n">
+        <v>526.8</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B214" t="n">
+        <v>351</v>
+      </c>
+      <c r="C214" t="n">
+        <v>3009</v>
+      </c>
+      <c r="D214" t="n">
+        <v>416.36</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B215" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C215" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D215" t="n">
+        <v>709.46</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B216" t="n">
+        <v>2648</v>
+      </c>
+      <c r="C216" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D216" t="n">
+        <v>1873.52</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B217" t="n">
+        <v>131</v>
+      </c>
+      <c r="C217" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D217" t="n">
+        <v>1369.91</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B218" t="n">
+        <v>2790</v>
+      </c>
+      <c r="C218" t="n">
+        <v>1953</v>
+      </c>
+      <c r="D218" t="n">
+        <v>371.88</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B219" t="n">
+        <v>363</v>
+      </c>
+      <c r="C219" t="n">
+        <v>1898</v>
+      </c>
+      <c r="D219" t="n">
+        <v>635.1</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B220" t="n">
+        <v>2716</v>
+      </c>
+      <c r="C220" t="n">
+        <v>1929</v>
+      </c>
+      <c r="D220" t="n">
+        <v>1073.33</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B221" t="n">
+        <v>2298</v>
+      </c>
+      <c r="C221" t="n">
+        <v>675</v>
+      </c>
+      <c r="D221" t="n">
+        <v>401.85</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B222" t="n">
+        <v>2639</v>
+      </c>
+      <c r="C222" t="n">
+        <v>1953</v>
+      </c>
+      <c r="D222" t="n">
+        <v>504.09</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B223" t="n">
+        <v>2109</v>
+      </c>
+      <c r="C223" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D223" t="n">
+        <v>2293.78</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B224" t="n">
+        <v>1116</v>
+      </c>
+      <c r="C224" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D224" t="n">
+        <v>2919.53</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B225" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C225" t="n">
+        <v>27</v>
+      </c>
+      <c r="D225" t="n">
+        <v>1803.76</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B226" t="n">
+        <v>353</v>
+      </c>
+      <c r="C226" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D226" t="n">
+        <v>349.33</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B227" t="n">
+        <v>2698</v>
+      </c>
+      <c r="C227" t="n">
+        <v>874</v>
+      </c>
+      <c r="D227" t="n">
+        <v>1230.43</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B228" t="n">
+        <v>42</v>
+      </c>
+      <c r="C228" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D228" t="n">
+        <v>79947.14999999999</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B229" t="n">
+        <v>772</v>
+      </c>
+      <c r="C229" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D229" t="n">
+        <v>400.25</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B230" t="n">
+        <v>2728</v>
+      </c>
+      <c r="C230" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D230" t="n">
+        <v>1397.07</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B231" t="n">
+        <v>2197</v>
+      </c>
+      <c r="C231" t="n">
+        <v>423</v>
+      </c>
+      <c r="D231" t="n">
+        <v>2267.61</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B232" t="n">
+        <v>2716</v>
+      </c>
+      <c r="C232" t="n">
+        <v>977</v>
+      </c>
+      <c r="D232" t="n">
+        <v>729.29</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B233" t="n">
+        <v>1993</v>
+      </c>
+      <c r="C233" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D233" t="n">
+        <v>456.62</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B234" t="n">
         <v>629</v>
       </c>
-      <c r="C213" t="n">
+      <c r="C234" t="n">
         <v>675</v>
       </c>
-      <c r="D213" t="n">
+      <c r="D234" t="n">
         <v>1054.76</v>
       </c>
-      <c r="E213" t="inlineStr">
+      <c r="E234" t="inlineStr">
         <is>
           <t>TELEMARKETING</t>
         </is>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E234"/>
+  <dimension ref="A1:E248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -660,7 +660,7 @@
         <v>3179</v>
       </c>
       <c r="D12" t="n">
-        <v>2603.16</v>
+        <v>4618.88</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1034,17 +1034,17 @@
         <v>46218</v>
       </c>
       <c r="B32" t="n">
-        <v>2695</v>
+        <v>2641</v>
       </c>
       <c r="C32" t="n">
         <v>8888</v>
       </c>
       <c r="D32" t="n">
-        <v>411.42</v>
+        <v>2527.79</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
         <v>46218</v>
       </c>
       <c r="B33" t="n">
-        <v>525</v>
+        <v>2695</v>
       </c>
       <c r="C33" t="n">
         <v>8888</v>
       </c>
       <c r="D33" t="n">
-        <v>408.25</v>
+        <v>411.42</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1072,17 +1072,17 @@
         <v>46218</v>
       </c>
       <c r="B34" t="n">
-        <v>1808</v>
+        <v>525</v>
       </c>
       <c r="C34" t="n">
         <v>8888</v>
       </c>
       <c r="D34" t="n">
-        <v>695.3200000000001</v>
+        <v>408.25</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1091,17 +1091,17 @@
         <v>46218</v>
       </c>
       <c r="B35" t="n">
-        <v>609</v>
+        <v>1808</v>
       </c>
       <c r="C35" t="n">
         <v>8888</v>
       </c>
       <c r="D35" t="n">
-        <v>1909.37</v>
+        <v>695.3200000000001</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1110,17 +1110,17 @@
         <v>46218</v>
       </c>
       <c r="B36" t="n">
-        <v>949</v>
+        <v>609</v>
       </c>
       <c r="C36" t="n">
-        <v>1134</v>
+        <v>8888</v>
       </c>
       <c r="D36" t="n">
-        <v>30.46</v>
+        <v>1909.37</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1129,13 +1129,13 @@
         <v>46218</v>
       </c>
       <c r="B37" t="n">
-        <v>42</v>
+        <v>949</v>
       </c>
       <c r="C37" t="n">
-        <v>1139</v>
+        <v>1134</v>
       </c>
       <c r="D37" t="n">
-        <v>358.97</v>
+        <v>30.46</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1148,17 +1148,17 @@
         <v>46218</v>
       </c>
       <c r="B38" t="n">
-        <v>2499</v>
+        <v>42</v>
       </c>
       <c r="C38" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D38" t="n">
-        <v>1049.3</v>
+        <v>358.97</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1167,13 +1167,13 @@
         <v>46218</v>
       </c>
       <c r="B39" t="n">
-        <v>58</v>
+        <v>2499</v>
       </c>
       <c r="C39" t="n">
         <v>8888</v>
       </c>
       <c r="D39" t="n">
-        <v>499.11</v>
+        <v>1049.3</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1186,13 +1186,13 @@
         <v>46218</v>
       </c>
       <c r="B40" t="n">
-        <v>2245</v>
+        <v>58</v>
       </c>
       <c r="C40" t="n">
         <v>8888</v>
       </c>
       <c r="D40" t="n">
-        <v>2740.06</v>
+        <v>1643.73</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1205,17 +1205,17 @@
         <v>46218</v>
       </c>
       <c r="B41" t="n">
-        <v>325</v>
+        <v>2245</v>
       </c>
       <c r="C41" t="n">
         <v>8888</v>
       </c>
       <c r="D41" t="n">
-        <v>952.75</v>
+        <v>2740.06</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1224,17 +1224,17 @@
         <v>46218</v>
       </c>
       <c r="B42" t="n">
-        <v>2383</v>
+        <v>325</v>
       </c>
       <c r="C42" t="n">
         <v>8888</v>
       </c>
       <c r="D42" t="n">
-        <v>7926.02</v>
+        <v>952.75</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
         <v>46218</v>
       </c>
       <c r="B43" t="n">
-        <v>1117</v>
+        <v>2383</v>
       </c>
       <c r="C43" t="n">
-        <v>1139</v>
+        <v>8888</v>
       </c>
       <c r="D43" t="n">
-        <v>916.72</v>
+        <v>7926.02</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1262,17 +1262,17 @@
         <v>46218</v>
       </c>
       <c r="B44" t="n">
-        <v>2279</v>
+        <v>1117</v>
       </c>
       <c r="C44" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D44" t="n">
-        <v>712.66</v>
+        <v>916.72</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1281,17 +1281,17 @@
         <v>46218</v>
       </c>
       <c r="B45" t="n">
-        <v>535</v>
+        <v>374</v>
       </c>
       <c r="C45" t="n">
         <v>8888</v>
       </c>
       <c r="D45" t="n">
-        <v>5836.12</v>
+        <v>2810.86</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1300,13 +1300,13 @@
         <v>46218</v>
       </c>
       <c r="B46" t="n">
-        <v>535</v>
+        <v>2279</v>
       </c>
       <c r="C46" t="n">
         <v>8888</v>
       </c>
       <c r="D46" t="n">
-        <v>1352.51</v>
+        <v>712.66</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1319,17 +1319,17 @@
         <v>46218</v>
       </c>
       <c r="B47" t="n">
-        <v>2678</v>
+        <v>535</v>
       </c>
       <c r="C47" t="n">
-        <v>1312</v>
+        <v>8888</v>
       </c>
       <c r="D47" t="n">
-        <v>364.96</v>
+        <v>5836.12</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1338,13 +1338,13 @@
         <v>46218</v>
       </c>
       <c r="B48" t="n">
-        <v>2345</v>
+        <v>535</v>
       </c>
       <c r="C48" t="n">
         <v>8888</v>
       </c>
       <c r="D48" t="n">
-        <v>863.16</v>
+        <v>1352.51</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1357,17 +1357,17 @@
         <v>46218</v>
       </c>
       <c r="B49" t="n">
-        <v>945</v>
+        <v>2678</v>
       </c>
       <c r="C49" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D49" t="n">
-        <v>27337.21</v>
+        <v>364.96</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PEDIDO ELETRÔNICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1376,17 +1376,17 @@
         <v>46218</v>
       </c>
       <c r="B50" t="n">
-        <v>2686</v>
+        <v>2345</v>
       </c>
       <c r="C50" t="n">
         <v>8888</v>
       </c>
       <c r="D50" t="n">
-        <v>684.2</v>
+        <v>863.16</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1395,17 +1395,17 @@
         <v>46218</v>
       </c>
       <c r="B51" t="n">
-        <v>438</v>
+        <v>945</v>
       </c>
       <c r="C51" t="n">
         <v>8888</v>
       </c>
       <c r="D51" t="n">
-        <v>220.06</v>
+        <v>27337.21</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>PEDIDO ELETRÔNICO</t>
         </is>
       </c>
     </row>
@@ -1414,17 +1414,17 @@
         <v>46218</v>
       </c>
       <c r="B52" t="n">
-        <v>664</v>
+        <v>2686</v>
       </c>
       <c r="C52" t="n">
         <v>8888</v>
       </c>
       <c r="D52" t="n">
-        <v>2598.01</v>
+        <v>684.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1433,17 +1433,17 @@
         <v>46218</v>
       </c>
       <c r="B53" t="n">
-        <v>353</v>
+        <v>438</v>
       </c>
       <c r="C53" t="n">
-        <v>3179</v>
+        <v>8888</v>
       </c>
       <c r="D53" t="n">
-        <v>495.84</v>
+        <v>220.06</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1452,13 +1452,13 @@
         <v>46218</v>
       </c>
       <c r="B54" t="n">
-        <v>1293</v>
+        <v>664</v>
       </c>
       <c r="C54" t="n">
         <v>8888</v>
       </c>
       <c r="D54" t="n">
-        <v>3129.07</v>
+        <v>6275.01</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -1471,17 +1471,17 @@
         <v>46218</v>
       </c>
       <c r="B55" t="n">
-        <v>2279</v>
+        <v>353</v>
       </c>
       <c r="C55" t="n">
-        <v>8888</v>
+        <v>3179</v>
       </c>
       <c r="D55" t="n">
-        <v>2753.96</v>
+        <v>495.84</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1490,13 +1490,13 @@
         <v>46218</v>
       </c>
       <c r="B56" t="n">
-        <v>1937</v>
+        <v>1293</v>
       </c>
       <c r="C56" t="n">
         <v>8888</v>
       </c>
       <c r="D56" t="n">
-        <v>1685.72</v>
+        <v>3129.07</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -1509,17 +1509,17 @@
         <v>46218</v>
       </c>
       <c r="B57" t="n">
-        <v>941</v>
+        <v>2279</v>
       </c>
       <c r="C57" t="n">
         <v>8888</v>
       </c>
       <c r="D57" t="n">
-        <v>864.14</v>
+        <v>2753.96</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1528,17 +1528,17 @@
         <v>46218</v>
       </c>
       <c r="B58" t="n">
-        <v>1137</v>
+        <v>1937</v>
       </c>
       <c r="C58" t="n">
         <v>8888</v>
       </c>
       <c r="D58" t="n">
-        <v>1947.93</v>
+        <v>1685.72</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1547,17 +1547,17 @@
         <v>46218</v>
       </c>
       <c r="B59" t="n">
-        <v>2631</v>
+        <v>941</v>
       </c>
       <c r="C59" t="n">
-        <v>2853</v>
+        <v>8888</v>
       </c>
       <c r="D59" t="n">
-        <v>1272.12</v>
+        <v>864.14</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1566,17 +1566,17 @@
         <v>46218</v>
       </c>
       <c r="B60" t="n">
-        <v>2793</v>
+        <v>1137</v>
       </c>
       <c r="C60" t="n">
-        <v>977</v>
+        <v>8888</v>
       </c>
       <c r="D60" t="n">
-        <v>1188.59</v>
+        <v>1947.93</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1585,17 +1585,17 @@
         <v>46218</v>
       </c>
       <c r="B61" t="n">
-        <v>374</v>
+        <v>2631</v>
       </c>
       <c r="C61" t="n">
-        <v>8888</v>
+        <v>2853</v>
       </c>
       <c r="D61" t="n">
-        <v>2103.29</v>
+        <v>1272.12</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1604,17 +1604,17 @@
         <v>46218</v>
       </c>
       <c r="B62" t="n">
-        <v>2802</v>
+        <v>2793</v>
       </c>
       <c r="C62" t="n">
-        <v>8888</v>
+        <v>977</v>
       </c>
       <c r="D62" t="n">
-        <v>1264.57</v>
+        <v>1188.59</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1623,13 +1623,13 @@
         <v>46218</v>
       </c>
       <c r="B63" t="n">
-        <v>451</v>
+        <v>2802</v>
       </c>
       <c r="C63" t="n">
         <v>8888</v>
       </c>
       <c r="D63" t="n">
-        <v>757.5700000000001</v>
+        <v>1264.57</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -1642,17 +1642,17 @@
         <v>46218</v>
       </c>
       <c r="B64" t="n">
-        <v>374</v>
+        <v>451</v>
       </c>
       <c r="C64" t="n">
         <v>8888</v>
       </c>
       <c r="D64" t="n">
-        <v>44.6</v>
+        <v>757.5700000000001</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1661,17 +1661,17 @@
         <v>46218</v>
       </c>
       <c r="B65" t="n">
-        <v>703</v>
+        <v>374</v>
       </c>
       <c r="C65" t="n">
         <v>8888</v>
       </c>
       <c r="D65" t="n">
-        <v>12155.46</v>
+        <v>44.6</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1680,17 +1680,17 @@
         <v>46218</v>
       </c>
       <c r="B66" t="n">
-        <v>1756</v>
+        <v>703</v>
       </c>
       <c r="C66" t="n">
         <v>8888</v>
       </c>
       <c r="D66" t="n">
-        <v>996.17</v>
+        <v>12155.46</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1699,13 +1699,13 @@
         <v>46218</v>
       </c>
       <c r="B67" t="n">
-        <v>1956</v>
+        <v>1756</v>
       </c>
       <c r="C67" t="n">
         <v>8888</v>
       </c>
       <c r="D67" t="n">
-        <v>4557.34</v>
+        <v>4416.47</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -1718,17 +1718,17 @@
         <v>46218</v>
       </c>
       <c r="B68" t="n">
-        <v>925</v>
+        <v>1956</v>
       </c>
       <c r="C68" t="n">
         <v>8888</v>
       </c>
       <c r="D68" t="n">
-        <v>651.59</v>
+        <v>4557.34</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1737,17 +1737,17 @@
         <v>46218</v>
       </c>
       <c r="B69" t="n">
-        <v>2648</v>
+        <v>925</v>
       </c>
       <c r="C69" t="n">
         <v>8888</v>
       </c>
       <c r="D69" t="n">
-        <v>1594.42</v>
+        <v>651.59</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1756,13 +1756,13 @@
         <v>46218</v>
       </c>
       <c r="B70" t="n">
-        <v>2714</v>
+        <v>941</v>
       </c>
       <c r="C70" t="n">
-        <v>519</v>
+        <v>977</v>
       </c>
       <c r="D70" t="n">
-        <v>61939.22</v>
+        <v>359.73</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -1775,17 +1775,17 @@
         <v>46218</v>
       </c>
       <c r="B71" t="n">
-        <v>483</v>
+        <v>2648</v>
       </c>
       <c r="C71" t="n">
         <v>8888</v>
       </c>
       <c r="D71" t="n">
-        <v>8624.57</v>
+        <v>1594.42</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1794,17 +1794,17 @@
         <v>46218</v>
       </c>
       <c r="B72" t="n">
-        <v>1075</v>
+        <v>663</v>
       </c>
       <c r="C72" t="n">
         <v>8888</v>
       </c>
       <c r="D72" t="n">
-        <v>11607.79</v>
+        <v>6645.33</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1813,17 +1813,17 @@
         <v>46218</v>
       </c>
       <c r="B73" t="n">
-        <v>629</v>
+        <v>2714</v>
       </c>
       <c r="C73" t="n">
-        <v>8888</v>
+        <v>519</v>
       </c>
       <c r="D73" t="n">
-        <v>9233.719999999999</v>
+        <v>61939.22</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1832,17 +1832,17 @@
         <v>46218</v>
       </c>
       <c r="B74" t="n">
-        <v>1983</v>
+        <v>483</v>
       </c>
       <c r="C74" t="n">
-        <v>841</v>
+        <v>8888</v>
       </c>
       <c r="D74" t="n">
-        <v>243.92</v>
+        <v>11360.2</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1851,17 +1851,17 @@
         <v>46218</v>
       </c>
       <c r="B75" t="n">
-        <v>1137</v>
+        <v>1075</v>
       </c>
       <c r="C75" t="n">
         <v>8888</v>
       </c>
       <c r="D75" t="n">
-        <v>3578.51</v>
+        <v>11607.79</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1870,17 +1870,17 @@
         <v>46218</v>
       </c>
       <c r="B76" t="n">
-        <v>2651</v>
+        <v>629</v>
       </c>
       <c r="C76" t="n">
         <v>8888</v>
       </c>
       <c r="D76" t="n">
-        <v>1296.58</v>
+        <v>9233.719999999999</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1889,17 +1889,17 @@
         <v>46218</v>
       </c>
       <c r="B77" t="n">
-        <v>663</v>
+        <v>1983</v>
       </c>
       <c r="C77" t="n">
-        <v>8888</v>
+        <v>841</v>
       </c>
       <c r="D77" t="n">
-        <v>5851.1</v>
+        <v>243.92</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1908,17 +1908,17 @@
         <v>46218</v>
       </c>
       <c r="B78" t="n">
-        <v>1956</v>
+        <v>1137</v>
       </c>
       <c r="C78" t="n">
-        <v>423</v>
+        <v>8888</v>
       </c>
       <c r="D78" t="n">
-        <v>1416.35</v>
+        <v>3578.51</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1927,17 +1927,17 @@
         <v>46218</v>
       </c>
       <c r="B79" t="n">
-        <v>2709</v>
+        <v>2651</v>
       </c>
       <c r="C79" t="n">
         <v>8888</v>
       </c>
       <c r="D79" t="n">
-        <v>547.6900000000001</v>
+        <v>1296.58</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1946,13 +1946,13 @@
         <v>46218</v>
       </c>
       <c r="B80" t="n">
-        <v>1308</v>
+        <v>2789</v>
       </c>
       <c r="C80" t="n">
         <v>8888</v>
       </c>
       <c r="D80" t="n">
-        <v>1460.53</v>
+        <v>1293.93</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -1965,17 +1965,17 @@
         <v>46218</v>
       </c>
       <c r="B81" t="n">
-        <v>2026</v>
+        <v>1956</v>
       </c>
       <c r="C81" t="n">
-        <v>8888</v>
+        <v>423</v>
       </c>
       <c r="D81" t="n">
-        <v>2237.62</v>
+        <v>1416.35</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1984,17 +1984,17 @@
         <v>46218</v>
       </c>
       <c r="B82" t="n">
-        <v>2789</v>
+        <v>2709</v>
       </c>
       <c r="C82" t="n">
         <v>8888</v>
       </c>
       <c r="D82" t="n">
-        <v>747.77</v>
+        <v>547.6900000000001</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2003,17 +2003,17 @@
         <v>46218</v>
       </c>
       <c r="B83" t="n">
-        <v>89</v>
+        <v>1308</v>
       </c>
       <c r="C83" t="n">
-        <v>13148</v>
+        <v>8888</v>
       </c>
       <c r="D83" t="n">
-        <v>1883.74</v>
+        <v>1460.53</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2022,17 +2022,17 @@
         <v>46218</v>
       </c>
       <c r="B84" t="n">
-        <v>2709</v>
+        <v>2026</v>
       </c>
       <c r="C84" t="n">
-        <v>2220</v>
+        <v>8888</v>
       </c>
       <c r="D84" t="n">
-        <v>390.19</v>
+        <v>2237.62</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2047,11 +2047,11 @@
         <v>8888</v>
       </c>
       <c r="D85" t="n">
-        <v>691.37</v>
+        <v>747.77</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2060,17 +2060,17 @@
         <v>46218</v>
       </c>
       <c r="B86" t="n">
-        <v>2345</v>
+        <v>89</v>
       </c>
       <c r="C86" t="n">
-        <v>8888</v>
+        <v>13148</v>
       </c>
       <c r="D86" t="n">
-        <v>748.86</v>
+        <v>1883.74</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2079,13 +2079,13 @@
         <v>46218</v>
       </c>
       <c r="B87" t="n">
-        <v>2765</v>
+        <v>2709</v>
       </c>
       <c r="C87" t="n">
-        <v>1883</v>
+        <v>2220</v>
       </c>
       <c r="D87" t="n">
-        <v>3638.6</v>
+        <v>390.19</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -2098,17 +2098,17 @@
         <v>46218</v>
       </c>
       <c r="B88" t="n">
-        <v>569</v>
+        <v>2345</v>
       </c>
       <c r="C88" t="n">
         <v>8888</v>
       </c>
       <c r="D88" t="n">
-        <v>995.33</v>
+        <v>748.86</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2117,17 +2117,17 @@
         <v>46218</v>
       </c>
       <c r="B89" t="n">
-        <v>360</v>
+        <v>1983</v>
       </c>
       <c r="C89" t="n">
-        <v>546</v>
+        <v>8888</v>
       </c>
       <c r="D89" t="n">
-        <v>1609.68</v>
+        <v>851.7</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2136,17 +2136,17 @@
         <v>46218</v>
       </c>
       <c r="B90" t="n">
-        <v>2308</v>
+        <v>2765</v>
       </c>
       <c r="C90" t="n">
-        <v>8888</v>
+        <v>1883</v>
       </c>
       <c r="D90" t="n">
-        <v>488.69</v>
+        <v>3638.6</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2155,17 +2155,17 @@
         <v>46218</v>
       </c>
       <c r="B91" t="n">
-        <v>2211</v>
+        <v>569</v>
       </c>
       <c r="C91" t="n">
-        <v>874</v>
+        <v>8888</v>
       </c>
       <c r="D91" t="n">
-        <v>1526.94</v>
+        <v>995.33</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2174,17 +2174,17 @@
         <v>46218</v>
       </c>
       <c r="B92" t="n">
-        <v>559</v>
+        <v>360</v>
       </c>
       <c r="C92" t="n">
-        <v>8888</v>
+        <v>546</v>
       </c>
       <c r="D92" t="n">
-        <v>859.92</v>
+        <v>1609.68</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2193,17 +2193,17 @@
         <v>46218</v>
       </c>
       <c r="B93" t="n">
-        <v>890</v>
+        <v>2711</v>
       </c>
       <c r="C93" t="n">
-        <v>8888</v>
+        <v>1953</v>
       </c>
       <c r="D93" t="n">
-        <v>387.2</v>
+        <v>150.27</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2212,17 +2212,17 @@
         <v>46218</v>
       </c>
       <c r="B94" t="n">
-        <v>2768</v>
+        <v>2308</v>
       </c>
       <c r="C94" t="n">
         <v>8888</v>
       </c>
       <c r="D94" t="n">
-        <v>6523.26</v>
+        <v>488.69</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2231,17 +2231,17 @@
         <v>46218</v>
       </c>
       <c r="B95" t="n">
-        <v>1063</v>
+        <v>2211</v>
       </c>
       <c r="C95" t="n">
-        <v>8888</v>
+        <v>874</v>
       </c>
       <c r="D95" t="n">
-        <v>4487.11</v>
+        <v>1526.94</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2250,17 +2250,17 @@
         <v>46218</v>
       </c>
       <c r="B96" t="n">
-        <v>2279</v>
+        <v>559</v>
       </c>
       <c r="C96" t="n">
-        <v>1139</v>
+        <v>8888</v>
       </c>
       <c r="D96" t="n">
-        <v>652.51</v>
+        <v>859.92</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2269,17 +2269,17 @@
         <v>46218</v>
       </c>
       <c r="B97" t="n">
-        <v>1299</v>
+        <v>890</v>
       </c>
       <c r="C97" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D97" t="n">
-        <v>1435.52</v>
+        <v>387.2</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
         <v>46218</v>
       </c>
       <c r="B98" t="n">
-        <v>1478</v>
+        <v>2768</v>
       </c>
       <c r="C98" t="n">
-        <v>675</v>
+        <v>8888</v>
       </c>
       <c r="D98" t="n">
-        <v>1600.01</v>
+        <v>6523.26</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2307,17 +2307,17 @@
         <v>46218</v>
       </c>
       <c r="B99" t="n">
-        <v>285</v>
+        <v>1063</v>
       </c>
       <c r="C99" t="n">
         <v>8888</v>
       </c>
       <c r="D99" t="n">
-        <v>3349.8</v>
+        <v>4487.11</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2326,17 +2326,17 @@
         <v>46218</v>
       </c>
       <c r="B100" t="n">
-        <v>477</v>
+        <v>2279</v>
       </c>
       <c r="C100" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D100" t="n">
-        <v>917.33</v>
+        <v>652.51</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2345,17 +2345,17 @@
         <v>46218</v>
       </c>
       <c r="B101" t="n">
-        <v>1983</v>
+        <v>1299</v>
       </c>
       <c r="C101" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D101" t="n">
-        <v>5115.01</v>
+        <v>1435.52</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2364,13 +2364,13 @@
         <v>46218</v>
       </c>
       <c r="B102" t="n">
-        <v>477</v>
+        <v>1478</v>
       </c>
       <c r="C102" t="n">
-        <v>58</v>
+        <v>675</v>
       </c>
       <c r="D102" t="n">
-        <v>1540.55</v>
+        <v>1967.85</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -2383,17 +2383,17 @@
         <v>46218</v>
       </c>
       <c r="B103" t="n">
-        <v>1063</v>
+        <v>767</v>
       </c>
       <c r="C103" t="n">
         <v>8888</v>
       </c>
       <c r="D103" t="n">
-        <v>2549.86</v>
+        <v>3292.44</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2402,13 +2402,13 @@
         <v>46218</v>
       </c>
       <c r="B104" t="n">
-        <v>424</v>
+        <v>285</v>
       </c>
       <c r="C104" t="n">
         <v>8888</v>
       </c>
       <c r="D104" t="n">
-        <v>1362.42</v>
+        <v>3349.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -2421,17 +2421,17 @@
         <v>46218</v>
       </c>
       <c r="B105" t="n">
-        <v>675</v>
+        <v>477</v>
       </c>
       <c r="C105" t="n">
         <v>8888</v>
       </c>
       <c r="D105" t="n">
-        <v>616.73</v>
+        <v>917.33</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2440,17 +2440,17 @@
         <v>46218</v>
       </c>
       <c r="B106" t="n">
-        <v>663</v>
+        <v>1983</v>
       </c>
       <c r="C106" t="n">
         <v>8888</v>
       </c>
       <c r="D106" t="n">
-        <v>255.13</v>
+        <v>5115.01</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2459,17 +2459,17 @@
         <v>46218</v>
       </c>
       <c r="B107" t="n">
-        <v>1993</v>
+        <v>477</v>
       </c>
       <c r="C107" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D107" t="n">
-        <v>362.63</v>
+        <v>1540.55</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2478,17 +2478,17 @@
         <v>46218</v>
       </c>
       <c r="B108" t="n">
-        <v>1465</v>
+        <v>1937</v>
       </c>
       <c r="C108" t="n">
         <v>8888</v>
       </c>
       <c r="D108" t="n">
-        <v>3373.83</v>
+        <v>2600.61</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2497,17 +2497,17 @@
         <v>46218</v>
       </c>
       <c r="B109" t="n">
-        <v>89</v>
+        <v>1063</v>
       </c>
       <c r="C109" t="n">
         <v>8888</v>
       </c>
       <c r="D109" t="n">
-        <v>479</v>
+        <v>2549.86</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2516,17 +2516,17 @@
         <v>46218</v>
       </c>
       <c r="B110" t="n">
-        <v>595</v>
+        <v>2584</v>
       </c>
       <c r="C110" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D110" t="n">
-        <v>18084.5</v>
+        <v>756.16</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2535,17 +2535,17 @@
         <v>46218</v>
       </c>
       <c r="B111" t="n">
-        <v>2696</v>
+        <v>58</v>
       </c>
       <c r="C111" t="n">
-        <v>1954</v>
+        <v>8888</v>
       </c>
       <c r="D111" t="n">
-        <v>1597.76</v>
+        <v>558.03</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2554,17 +2554,17 @@
         <v>46218</v>
       </c>
       <c r="B112" t="n">
-        <v>360</v>
+        <v>424</v>
       </c>
       <c r="C112" t="n">
         <v>8888</v>
       </c>
       <c r="D112" t="n">
-        <v>4596.89</v>
+        <v>1362.42</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2573,17 +2573,17 @@
         <v>46218</v>
       </c>
       <c r="B113" t="n">
-        <v>1465</v>
+        <v>675</v>
       </c>
       <c r="C113" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D113" t="n">
-        <v>777.2</v>
+        <v>616.73</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2592,17 +2592,17 @@
         <v>46218</v>
       </c>
       <c r="B114" t="n">
-        <v>947</v>
+        <v>663</v>
       </c>
       <c r="C114" t="n">
         <v>8888</v>
       </c>
       <c r="D114" t="n">
-        <v>5115.36</v>
+        <v>255.13</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>PEDIDO ELETRÔNICO</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2611,17 +2611,17 @@
         <v>46218</v>
       </c>
       <c r="B115" t="n">
-        <v>2178</v>
+        <v>1993</v>
       </c>
       <c r="C115" t="n">
         <v>8888</v>
       </c>
       <c r="D115" t="n">
-        <v>619.92</v>
+        <v>362.63</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2630,17 +2630,17 @@
         <v>46218</v>
       </c>
       <c r="B116" t="n">
-        <v>2026</v>
+        <v>1465</v>
       </c>
       <c r="C116" t="n">
-        <v>1929</v>
+        <v>8888</v>
       </c>
       <c r="D116" t="n">
-        <v>3418.07</v>
+        <v>3373.83</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2649,17 +2649,17 @@
         <v>46218</v>
       </c>
       <c r="B117" t="n">
-        <v>630</v>
+        <v>89</v>
       </c>
       <c r="C117" t="n">
-        <v>1929</v>
+        <v>8888</v>
       </c>
       <c r="D117" t="n">
-        <v>1801.63</v>
+        <v>479</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2668,17 +2668,17 @@
         <v>46218</v>
       </c>
       <c r="B118" t="n">
-        <v>1937</v>
+        <v>595</v>
       </c>
       <c r="C118" t="n">
         <v>8888</v>
       </c>
       <c r="D118" t="n">
-        <v>2132.95</v>
+        <v>18084.5</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2687,17 +2687,17 @@
         <v>46218</v>
       </c>
       <c r="B119" t="n">
-        <v>2577</v>
+        <v>2696</v>
       </c>
       <c r="C119" t="n">
-        <v>8888</v>
+        <v>1954</v>
       </c>
       <c r="D119" t="n">
-        <v>1647.08</v>
+        <v>1597.76</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2706,17 +2706,17 @@
         <v>46218</v>
       </c>
       <c r="B120" t="n">
-        <v>1293</v>
+        <v>360</v>
       </c>
       <c r="C120" t="n">
         <v>8888</v>
       </c>
       <c r="D120" t="n">
-        <v>2135.89</v>
+        <v>4596.89</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2725,17 +2725,17 @@
         <v>46218</v>
       </c>
       <c r="B121" t="n">
-        <v>2607</v>
+        <v>1465</v>
       </c>
       <c r="C121" t="n">
-        <v>8888</v>
+        <v>3403</v>
       </c>
       <c r="D121" t="n">
-        <v>490.31</v>
+        <v>777.2</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2744,17 +2744,17 @@
         <v>46218</v>
       </c>
       <c r="B122" t="n">
-        <v>1317</v>
+        <v>947</v>
       </c>
       <c r="C122" t="n">
         <v>8888</v>
       </c>
       <c r="D122" t="n">
-        <v>907.72</v>
+        <v>5115.36</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>PEDIDO ELETRÔNICO</t>
         </is>
       </c>
     </row>
@@ -2763,17 +2763,17 @@
         <v>46218</v>
       </c>
       <c r="B123" t="n">
-        <v>767</v>
+        <v>2178</v>
       </c>
       <c r="C123" t="n">
         <v>8888</v>
       </c>
       <c r="D123" t="n">
-        <v>637.23</v>
+        <v>619.92</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2782,13 +2782,13 @@
         <v>46218</v>
       </c>
       <c r="B124" t="n">
-        <v>2571</v>
+        <v>2026</v>
       </c>
       <c r="C124" t="n">
-        <v>1312</v>
+        <v>1929</v>
       </c>
       <c r="D124" t="n">
-        <v>268.53</v>
+        <v>5293.13</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -2801,17 +2801,17 @@
         <v>46218</v>
       </c>
       <c r="B125" t="n">
-        <v>1937</v>
+        <v>630</v>
       </c>
       <c r="C125" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D125" t="n">
-        <v>1803.32</v>
+        <v>1801.63</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2820,17 +2820,17 @@
         <v>46218</v>
       </c>
       <c r="B126" t="n">
-        <v>20</v>
+        <v>1937</v>
       </c>
       <c r="C126" t="n">
         <v>8888</v>
       </c>
       <c r="D126" t="n">
-        <v>745.55</v>
+        <v>2132.95</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2839,17 +2839,17 @@
         <v>46218</v>
       </c>
       <c r="B127" t="n">
-        <v>1063</v>
+        <v>2577</v>
       </c>
       <c r="C127" t="n">
         <v>8888</v>
       </c>
       <c r="D127" t="n">
-        <v>1113.08</v>
+        <v>1647.08</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2858,17 +2858,17 @@
         <v>46218</v>
       </c>
       <c r="B128" t="n">
-        <v>2631</v>
+        <v>1293</v>
       </c>
       <c r="C128" t="n">
         <v>8888</v>
       </c>
       <c r="D128" t="n">
-        <v>1447.86</v>
+        <v>2135.89</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2877,13 +2877,13 @@
         <v>46218</v>
       </c>
       <c r="B129" t="n">
-        <v>1906</v>
+        <v>2607</v>
       </c>
       <c r="C129" t="n">
         <v>8888</v>
       </c>
       <c r="D129" t="n">
-        <v>2774.84</v>
+        <v>490.31</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -2896,17 +2896,17 @@
         <v>46218</v>
       </c>
       <c r="B130" t="n">
-        <v>1756</v>
+        <v>1317</v>
       </c>
       <c r="C130" t="n">
         <v>8888</v>
       </c>
       <c r="D130" t="n">
-        <v>2275.21</v>
+        <v>907.72</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2915,17 +2915,17 @@
         <v>46218</v>
       </c>
       <c r="B131" t="n">
-        <v>477</v>
+        <v>619</v>
       </c>
       <c r="C131" t="n">
         <v>8888</v>
       </c>
       <c r="D131" t="n">
-        <v>707.52</v>
+        <v>1081.74</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2934,17 +2934,17 @@
         <v>46218</v>
       </c>
       <c r="B132" t="n">
-        <v>2660</v>
+        <v>2571</v>
       </c>
       <c r="C132" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D132" t="n">
-        <v>2684.97</v>
+        <v>268.53</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2953,17 +2953,17 @@
         <v>46218</v>
       </c>
       <c r="B133" t="n">
-        <v>569</v>
+        <v>20</v>
       </c>
       <c r="C133" t="n">
         <v>8888</v>
       </c>
       <c r="D133" t="n">
-        <v>33214.39</v>
+        <v>745.55</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2972,13 +2972,13 @@
         <v>46218</v>
       </c>
       <c r="B134" t="n">
-        <v>483</v>
+        <v>1063</v>
       </c>
       <c r="C134" t="n">
         <v>8888</v>
       </c>
       <c r="D134" t="n">
-        <v>2401.99</v>
+        <v>1113.08</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -2991,17 +2991,17 @@
         <v>46218</v>
       </c>
       <c r="B135" t="n">
-        <v>483</v>
+        <v>2631</v>
       </c>
       <c r="C135" t="n">
         <v>8888</v>
       </c>
       <c r="D135" t="n">
-        <v>1124.96</v>
+        <v>1447.86</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3010,17 +3010,17 @@
         <v>46218</v>
       </c>
       <c r="B136" t="n">
-        <v>2089</v>
+        <v>1906</v>
       </c>
       <c r="C136" t="n">
-        <v>1533</v>
+        <v>8888</v>
       </c>
       <c r="D136" t="n">
-        <v>1309.01</v>
+        <v>2774.84</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3029,13 +3029,13 @@
         <v>46218</v>
       </c>
       <c r="B137" t="n">
-        <v>1007</v>
+        <v>1756</v>
       </c>
       <c r="C137" t="n">
         <v>8888</v>
       </c>
       <c r="D137" t="n">
-        <v>241.44</v>
+        <v>2275.21</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -3048,17 +3048,17 @@
         <v>46218</v>
       </c>
       <c r="B138" t="n">
-        <v>1380</v>
+        <v>477</v>
       </c>
       <c r="C138" t="n">
         <v>8888</v>
       </c>
       <c r="D138" t="n">
-        <v>520.2</v>
+        <v>707.52</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3067,17 +3067,17 @@
         <v>46218</v>
       </c>
       <c r="B139" t="n">
-        <v>1102</v>
+        <v>2660</v>
       </c>
       <c r="C139" t="n">
         <v>8888</v>
       </c>
       <c r="D139" t="n">
-        <v>1137.04</v>
+        <v>2684.97</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3086,17 +3086,17 @@
         <v>46218</v>
       </c>
       <c r="B140" t="n">
-        <v>1075</v>
+        <v>569</v>
       </c>
       <c r="C140" t="n">
         <v>8888</v>
       </c>
       <c r="D140" t="n">
-        <v>4194.79</v>
+        <v>36782.12</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3105,17 +3105,17 @@
         <v>46218</v>
       </c>
       <c r="B141" t="n">
-        <v>2681</v>
+        <v>483</v>
       </c>
       <c r="C141" t="n">
         <v>8888</v>
       </c>
       <c r="D141" t="n">
-        <v>729.25</v>
+        <v>3102.48</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3124,17 +3124,17 @@
         <v>46218</v>
       </c>
       <c r="B142" t="n">
-        <v>2245</v>
+        <v>609</v>
       </c>
       <c r="C142" t="n">
         <v>8888</v>
       </c>
       <c r="D142" t="n">
-        <v>361.58</v>
+        <v>1633.68</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3143,17 +3143,17 @@
         <v>46218</v>
       </c>
       <c r="B143" t="n">
-        <v>33</v>
+        <v>483</v>
       </c>
       <c r="C143" t="n">
         <v>8888</v>
       </c>
       <c r="D143" t="n">
-        <v>926.97</v>
+        <v>1578.32</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3162,17 +3162,17 @@
         <v>46218</v>
       </c>
       <c r="B144" t="n">
-        <v>132</v>
+        <v>2089</v>
       </c>
       <c r="C144" t="n">
-        <v>8888</v>
+        <v>1533</v>
       </c>
       <c r="D144" t="n">
-        <v>6522.92</v>
+        <v>1309.01</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3181,17 +3181,17 @@
         <v>46218</v>
       </c>
       <c r="B145" t="n">
-        <v>619</v>
+        <v>1007</v>
       </c>
       <c r="C145" t="n">
         <v>8888</v>
       </c>
       <c r="D145" t="n">
-        <v>2912.89</v>
+        <v>241.44</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3200,13 +3200,13 @@
         <v>46218</v>
       </c>
       <c r="B146" t="n">
-        <v>452</v>
+        <v>1380</v>
       </c>
       <c r="C146" t="n">
         <v>8888</v>
       </c>
       <c r="D146" t="n">
-        <v>608.78</v>
+        <v>520.2</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -3219,17 +3219,17 @@
         <v>46218</v>
       </c>
       <c r="B147" t="n">
-        <v>2463</v>
+        <v>1102</v>
       </c>
       <c r="C147" t="n">
         <v>8888</v>
       </c>
       <c r="D147" t="n">
-        <v>363.69</v>
+        <v>1137.04</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3238,17 +3238,17 @@
         <v>46218</v>
       </c>
       <c r="B148" t="n">
-        <v>1293</v>
+        <v>1075</v>
       </c>
       <c r="C148" t="n">
-        <v>1281</v>
+        <v>8888</v>
       </c>
       <c r="D148" t="n">
-        <v>1780.93</v>
+        <v>5710.94</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3257,17 +3257,17 @@
         <v>46218</v>
       </c>
       <c r="B149" t="n">
-        <v>525</v>
+        <v>2681</v>
       </c>
       <c r="C149" t="n">
         <v>8888</v>
       </c>
       <c r="D149" t="n">
-        <v>5658.57</v>
+        <v>729.25</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3276,13 +3276,13 @@
         <v>46218</v>
       </c>
       <c r="B150" t="n">
-        <v>2641</v>
+        <v>2245</v>
       </c>
       <c r="C150" t="n">
         <v>8888</v>
       </c>
       <c r="D150" t="n">
-        <v>1720.99</v>
+        <v>700.2</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -3295,17 +3295,17 @@
         <v>46218</v>
       </c>
       <c r="B151" t="n">
-        <v>609</v>
+        <v>33</v>
       </c>
       <c r="C151" t="n">
         <v>8888</v>
       </c>
       <c r="D151" t="n">
-        <v>886.1</v>
+        <v>926.97</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3314,13 +3314,13 @@
         <v>46218</v>
       </c>
       <c r="B152" t="n">
-        <v>2697</v>
+        <v>132</v>
       </c>
       <c r="C152" t="n">
         <v>8888</v>
       </c>
       <c r="D152" t="n">
-        <v>418.65</v>
+        <v>6522.92</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -3333,17 +3333,17 @@
         <v>46218</v>
       </c>
       <c r="B153" t="n">
-        <v>58</v>
+        <v>619</v>
       </c>
       <c r="C153" t="n">
         <v>8888</v>
       </c>
       <c r="D153" t="n">
-        <v>1123.87</v>
+        <v>2912.89</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
         <v>46218</v>
       </c>
       <c r="B154" t="n">
-        <v>358</v>
+        <v>452</v>
       </c>
       <c r="C154" t="n">
         <v>8888</v>
       </c>
       <c r="D154" t="n">
-        <v>1675.95</v>
+        <v>608.78</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3371,17 +3371,17 @@
         <v>46218</v>
       </c>
       <c r="B155" t="n">
-        <v>2431</v>
+        <v>2463</v>
       </c>
       <c r="C155" t="n">
         <v>8888</v>
       </c>
       <c r="D155" t="n">
-        <v>266.89</v>
+        <v>363.69</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3390,17 +3390,17 @@
         <v>46218</v>
       </c>
       <c r="B156" t="n">
-        <v>285</v>
+        <v>1293</v>
       </c>
       <c r="C156" t="n">
-        <v>8888</v>
+        <v>1281</v>
       </c>
       <c r="D156" t="n">
-        <v>5673.85</v>
+        <v>1780.93</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3409,13 +3409,13 @@
         <v>46218</v>
       </c>
       <c r="B157" t="n">
-        <v>1102</v>
+        <v>525</v>
       </c>
       <c r="C157" t="n">
         <v>8888</v>
       </c>
       <c r="D157" t="n">
-        <v>1119.32</v>
+        <v>5658.57</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -3428,17 +3428,17 @@
         <v>46218</v>
       </c>
       <c r="B158" t="n">
-        <v>626</v>
+        <v>2641</v>
       </c>
       <c r="C158" t="n">
         <v>8888</v>
       </c>
       <c r="D158" t="n">
-        <v>12556.19</v>
+        <v>1720.99</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3447,17 +3447,17 @@
         <v>46218</v>
       </c>
       <c r="B159" t="n">
-        <v>1137</v>
+        <v>2697</v>
       </c>
       <c r="C159" t="n">
-        <v>2220</v>
+        <v>8888</v>
       </c>
       <c r="D159" t="n">
-        <v>1370.86</v>
+        <v>418.65</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3466,13 +3466,13 @@
         <v>46218</v>
       </c>
       <c r="B160" t="n">
-        <v>2686</v>
+        <v>2472</v>
       </c>
       <c r="C160" t="n">
-        <v>1929</v>
+        <v>2853</v>
       </c>
       <c r="D160" t="n">
-        <v>2066.36</v>
+        <v>1402.64</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -3485,17 +3485,17 @@
         <v>46218</v>
       </c>
       <c r="B161" t="n">
-        <v>2584</v>
+        <v>58</v>
       </c>
       <c r="C161" t="n">
         <v>8888</v>
       </c>
       <c r="D161" t="n">
-        <v>5635.67</v>
+        <v>1123.87</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3504,17 +3504,17 @@
         <v>46218</v>
       </c>
       <c r="B162" t="n">
-        <v>1756</v>
+        <v>358</v>
       </c>
       <c r="C162" t="n">
         <v>8888</v>
       </c>
       <c r="D162" t="n">
-        <v>2201.67</v>
+        <v>1675.95</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3523,17 +3523,17 @@
         <v>46218</v>
       </c>
       <c r="B163" t="n">
-        <v>1756</v>
+        <v>2431</v>
       </c>
       <c r="C163" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D163" t="n">
-        <v>5078.1</v>
+        <v>266.89</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3542,17 +3542,17 @@
         <v>46218</v>
       </c>
       <c r="B164" t="n">
-        <v>2651</v>
+        <v>285</v>
       </c>
       <c r="C164" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D164" t="n">
-        <v>363.7</v>
+        <v>5673.85</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3561,13 +3561,13 @@
         <v>46218</v>
       </c>
       <c r="B165" t="n">
-        <v>664</v>
+        <v>1102</v>
       </c>
       <c r="C165" t="n">
         <v>8888</v>
       </c>
       <c r="D165" t="n">
-        <v>5672.57</v>
+        <v>1119.32</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -3580,13 +3580,13 @@
         <v>46218</v>
       </c>
       <c r="B166" t="n">
-        <v>360</v>
+        <v>2793</v>
       </c>
       <c r="C166" t="n">
         <v>8888</v>
       </c>
       <c r="D166" t="n">
-        <v>1594.84</v>
+        <v>1238.11</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -3599,13 +3599,13 @@
         <v>46218</v>
       </c>
       <c r="B167" t="n">
-        <v>2582</v>
+        <v>626</v>
       </c>
       <c r="C167" t="n">
         <v>8888</v>
       </c>
       <c r="D167" t="n">
-        <v>379.33</v>
+        <v>12556.19</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -3618,17 +3618,17 @@
         <v>46218</v>
       </c>
       <c r="B168" t="n">
-        <v>636</v>
+        <v>1137</v>
       </c>
       <c r="C168" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D168" t="n">
-        <v>2447.56</v>
+        <v>1370.86</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3637,13 +3637,13 @@
         <v>46218</v>
       </c>
       <c r="B169" t="n">
-        <v>1254</v>
+        <v>1289</v>
       </c>
       <c r="C169" t="n">
         <v>8888</v>
       </c>
       <c r="D169" t="n">
-        <v>2643.22</v>
+        <v>5565.44</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -3656,17 +3656,17 @@
         <v>46218</v>
       </c>
       <c r="B170" t="n">
-        <v>1289</v>
+        <v>2686</v>
       </c>
       <c r="C170" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D170" t="n">
-        <v>2396.98</v>
+        <v>2066.36</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3675,17 +3675,17 @@
         <v>46218</v>
       </c>
       <c r="B171" t="n">
-        <v>2726</v>
+        <v>629</v>
       </c>
       <c r="C171" t="n">
-        <v>977</v>
+        <v>8888</v>
       </c>
       <c r="D171" t="n">
-        <v>586.0599999999999</v>
+        <v>5212.76</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3694,13 +3694,13 @@
         <v>46218</v>
       </c>
       <c r="B172" t="n">
-        <v>2015</v>
+        <v>2584</v>
       </c>
       <c r="C172" t="n">
         <v>8888</v>
       </c>
       <c r="D172" t="n">
-        <v>315.69</v>
+        <v>5635.67</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -3713,17 +3713,17 @@
         <v>46218</v>
       </c>
       <c r="B173" t="n">
-        <v>1064</v>
+        <v>1756</v>
       </c>
       <c r="C173" t="n">
         <v>8888</v>
       </c>
       <c r="D173" t="n">
-        <v>1274.3</v>
+        <v>2201.67</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3732,17 +3732,17 @@
         <v>46218</v>
       </c>
       <c r="B174" t="n">
-        <v>2698</v>
+        <v>1756</v>
       </c>
       <c r="C174" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D174" t="n">
-        <v>552.15</v>
+        <v>5078.1</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3751,17 +3751,17 @@
         <v>46218</v>
       </c>
       <c r="B175" t="n">
-        <v>629</v>
+        <v>2651</v>
       </c>
       <c r="C175" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D175" t="n">
-        <v>3544.51</v>
+        <v>363.7</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3770,17 +3770,17 @@
         <v>46218</v>
       </c>
       <c r="B176" t="n">
-        <v>2641</v>
+        <v>664</v>
       </c>
       <c r="C176" t="n">
         <v>8888</v>
       </c>
       <c r="D176" t="n">
-        <v>820</v>
+        <v>5672.57</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3789,17 +3789,17 @@
         <v>46218</v>
       </c>
       <c r="B177" t="n">
-        <v>429</v>
+        <v>360</v>
       </c>
       <c r="C177" t="n">
         <v>8888</v>
       </c>
       <c r="D177" t="n">
-        <v>2593.49</v>
+        <v>1594.84</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3808,17 +3808,17 @@
         <v>46218</v>
       </c>
       <c r="B178" t="n">
-        <v>816</v>
+        <v>2582</v>
       </c>
       <c r="C178" t="n">
         <v>8888</v>
       </c>
       <c r="D178" t="n">
-        <v>438.24</v>
+        <v>379.33</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3827,17 +3827,17 @@
         <v>46218</v>
       </c>
       <c r="B179" t="n">
-        <v>2793</v>
+        <v>636</v>
       </c>
       <c r="C179" t="n">
         <v>8888</v>
       </c>
       <c r="D179" t="n">
-        <v>767.58</v>
+        <v>2447.56</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3846,13 +3846,13 @@
         <v>46218</v>
       </c>
       <c r="B180" t="n">
-        <v>2359</v>
+        <v>1254</v>
       </c>
       <c r="C180" t="n">
         <v>8888</v>
       </c>
       <c r="D180" t="n">
-        <v>381.95</v>
+        <v>2643.22</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -3865,13 +3865,13 @@
         <v>46218</v>
       </c>
       <c r="B181" t="n">
-        <v>285</v>
+        <v>2726</v>
       </c>
       <c r="C181" t="n">
-        <v>58</v>
+        <v>977</v>
       </c>
       <c r="D181" t="n">
-        <v>364.99</v>
+        <v>586.0599999999999</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -3884,17 +3884,17 @@
         <v>46218</v>
       </c>
       <c r="B182" t="n">
-        <v>2114</v>
+        <v>2015</v>
       </c>
       <c r="C182" t="n">
         <v>8888</v>
       </c>
       <c r="D182" t="n">
-        <v>2726.04</v>
+        <v>315.69</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3903,17 +3903,17 @@
         <v>46218</v>
       </c>
       <c r="B183" t="n">
-        <v>953</v>
+        <v>1064</v>
       </c>
       <c r="C183" t="n">
         <v>8888</v>
       </c>
       <c r="D183" t="n">
-        <v>2889.63</v>
+        <v>1274.3</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3922,17 +3922,17 @@
         <v>46218</v>
       </c>
       <c r="B184" t="n">
-        <v>1102</v>
+        <v>2698</v>
       </c>
       <c r="C184" t="n">
         <v>8888</v>
       </c>
       <c r="D184" t="n">
-        <v>3093.73</v>
+        <v>552.15</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3941,13 +3941,13 @@
         <v>46218</v>
       </c>
       <c r="B185" t="n">
-        <v>1465</v>
+        <v>2641</v>
       </c>
       <c r="C185" t="n">
         <v>8888</v>
       </c>
       <c r="D185" t="n">
-        <v>4281.39</v>
+        <v>820</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -3960,17 +3960,17 @@
         <v>46218</v>
       </c>
       <c r="B186" t="n">
-        <v>619</v>
+        <v>429</v>
       </c>
       <c r="C186" t="n">
         <v>8888</v>
       </c>
       <c r="D186" t="n">
-        <v>2021.67</v>
+        <v>2593.49</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3979,17 +3979,17 @@
         <v>46218</v>
       </c>
       <c r="B187" t="n">
-        <v>2716</v>
+        <v>1301</v>
       </c>
       <c r="C187" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D187" t="n">
-        <v>601.58</v>
+        <v>750.66</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3998,17 +3998,17 @@
         <v>46218</v>
       </c>
       <c r="B188" t="n">
-        <v>2767</v>
+        <v>816</v>
       </c>
       <c r="C188" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D188" t="n">
-        <v>1135.64</v>
+        <v>438.24</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4017,13 +4017,13 @@
         <v>46218</v>
       </c>
       <c r="B189" t="n">
-        <v>2245</v>
+        <v>2359</v>
       </c>
       <c r="C189" t="n">
         <v>8888</v>
       </c>
       <c r="D189" t="n">
-        <v>427.51</v>
+        <v>381.95</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -4036,17 +4036,17 @@
         <v>46218</v>
       </c>
       <c r="B190" t="n">
-        <v>2197</v>
+        <v>2251</v>
       </c>
       <c r="C190" t="n">
-        <v>8888</v>
+        <v>3403</v>
       </c>
       <c r="D190" t="n">
-        <v>1085.45</v>
+        <v>802.08</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4055,17 +4055,17 @@
         <v>46218</v>
       </c>
       <c r="B191" t="n">
-        <v>2657</v>
+        <v>285</v>
       </c>
       <c r="C191" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D191" t="n">
-        <v>2683.06</v>
+        <v>364.99</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4074,17 +4074,17 @@
         <v>46218</v>
       </c>
       <c r="B192" t="n">
-        <v>451</v>
+        <v>2114</v>
       </c>
       <c r="C192" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D192" t="n">
-        <v>2091.77</v>
+        <v>2726.04</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4093,17 +4093,17 @@
         <v>46218</v>
       </c>
       <c r="B193" t="n">
-        <v>1116</v>
+        <v>953</v>
       </c>
       <c r="C193" t="n">
-        <v>13148</v>
+        <v>8888</v>
       </c>
       <c r="D193" t="n">
-        <v>207.91</v>
+        <v>2889.63</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4112,17 +4112,17 @@
         <v>46218</v>
       </c>
       <c r="B194" t="n">
-        <v>1277</v>
+        <v>1102</v>
       </c>
       <c r="C194" t="n">
         <v>8888</v>
       </c>
       <c r="D194" t="n">
-        <v>1949</v>
+        <v>4637.07</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4131,17 +4131,17 @@
         <v>46218</v>
       </c>
       <c r="B195" t="n">
-        <v>131</v>
+        <v>1465</v>
       </c>
       <c r="C195" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D195" t="n">
-        <v>3850.09</v>
+        <v>4281.39</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4150,13 +4150,13 @@
         <v>46218</v>
       </c>
       <c r="B196" t="n">
-        <v>2692</v>
+        <v>619</v>
       </c>
       <c r="C196" t="n">
         <v>8888</v>
       </c>
       <c r="D196" t="n">
-        <v>731.28</v>
+        <v>2021.67</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -4169,17 +4169,17 @@
         <v>46218</v>
       </c>
       <c r="B197" t="n">
-        <v>1632</v>
+        <v>2716</v>
       </c>
       <c r="C197" t="n">
         <v>8888</v>
       </c>
       <c r="D197" t="n">
-        <v>7519.7</v>
+        <v>1063.42</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4188,13 +4188,13 @@
         <v>46218</v>
       </c>
       <c r="B198" t="n">
-        <v>1317</v>
+        <v>2767</v>
       </c>
       <c r="C198" t="n">
-        <v>3179</v>
+        <v>1898</v>
       </c>
       <c r="D198" t="n">
-        <v>991.6799999999999</v>
+        <v>1135.64</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -4207,13 +4207,13 @@
         <v>46218</v>
       </c>
       <c r="B199" t="n">
-        <v>1993</v>
+        <v>2245</v>
       </c>
       <c r="C199" t="n">
         <v>8888</v>
       </c>
       <c r="D199" t="n">
-        <v>2875.39</v>
+        <v>764.66</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -4226,17 +4226,17 @@
         <v>46218</v>
       </c>
       <c r="B200" t="n">
-        <v>1890</v>
+        <v>2197</v>
       </c>
       <c r="C200" t="n">
-        <v>3449</v>
+        <v>8888</v>
       </c>
       <c r="D200" t="n">
-        <v>6313.56</v>
+        <v>1085.45</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4245,17 +4245,17 @@
         <v>46218</v>
       </c>
       <c r="B201" t="n">
-        <v>2749</v>
+        <v>1064</v>
       </c>
       <c r="C201" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D201" t="n">
-        <v>1860.64</v>
+        <v>574.7</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4264,17 +4264,17 @@
         <v>46218</v>
       </c>
       <c r="B202" t="n">
-        <v>1117</v>
+        <v>2657</v>
       </c>
       <c r="C202" t="n">
         <v>8888</v>
       </c>
       <c r="D202" t="n">
-        <v>342.2</v>
+        <v>2683.06</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4283,17 +4283,17 @@
         <v>46218</v>
       </c>
       <c r="B203" t="n">
-        <v>42</v>
+        <v>451</v>
       </c>
       <c r="C203" t="n">
-        <v>8888</v>
+        <v>3403</v>
       </c>
       <c r="D203" t="n">
-        <v>280.05</v>
+        <v>2091.77</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4302,17 +4302,17 @@
         <v>46218</v>
       </c>
       <c r="B204" t="n">
-        <v>1478</v>
+        <v>1116</v>
       </c>
       <c r="C204" t="n">
-        <v>8888</v>
+        <v>13148</v>
       </c>
       <c r="D204" t="n">
-        <v>875.34</v>
+        <v>207.91</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4321,13 +4321,13 @@
         <v>46218</v>
       </c>
       <c r="B205" t="n">
-        <v>2491</v>
+        <v>1277</v>
       </c>
       <c r="C205" t="n">
         <v>8888</v>
       </c>
       <c r="D205" t="n">
-        <v>650.4299999999999</v>
+        <v>1949</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -4340,17 +4340,17 @@
         <v>46218</v>
       </c>
       <c r="B206" t="n">
-        <v>2015</v>
+        <v>131</v>
       </c>
       <c r="C206" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D206" t="n">
-        <v>4436.15</v>
+        <v>3850.09</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4359,17 +4359,17 @@
         <v>46218</v>
       </c>
       <c r="B207" t="n">
-        <v>1890</v>
+        <v>2692</v>
       </c>
       <c r="C207" t="n">
-        <v>1953</v>
+        <v>8888</v>
       </c>
       <c r="D207" t="n">
-        <v>1674.57</v>
+        <v>731.28</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4378,17 +4378,17 @@
         <v>46218</v>
       </c>
       <c r="B208" t="n">
-        <v>1317</v>
+        <v>1632</v>
       </c>
       <c r="C208" t="n">
         <v>8888</v>
       </c>
       <c r="D208" t="n">
-        <v>1626.02</v>
+        <v>7519.7</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4397,17 +4397,17 @@
         <v>46218</v>
       </c>
       <c r="B209" t="n">
-        <v>2782</v>
+        <v>1317</v>
       </c>
       <c r="C209" t="n">
-        <v>8888</v>
+        <v>3179</v>
       </c>
       <c r="D209" t="n">
-        <v>1786.32</v>
+        <v>991.6799999999999</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4416,13 +4416,13 @@
         <v>46218</v>
       </c>
       <c r="B210" t="n">
-        <v>953</v>
+        <v>1993</v>
       </c>
       <c r="C210" t="n">
         <v>8888</v>
       </c>
       <c r="D210" t="n">
-        <v>364.44</v>
+        <v>2875.39</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -4435,17 +4435,17 @@
         <v>46218</v>
       </c>
       <c r="B211" t="n">
-        <v>2251</v>
+        <v>1890</v>
       </c>
       <c r="C211" t="n">
-        <v>8888</v>
+        <v>3449</v>
       </c>
       <c r="D211" t="n">
-        <v>309.22</v>
+        <v>6313.56</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4454,17 +4454,17 @@
         <v>46218</v>
       </c>
       <c r="B212" t="n">
-        <v>483</v>
+        <v>1800</v>
       </c>
       <c r="C212" t="n">
-        <v>841</v>
+        <v>8888</v>
       </c>
       <c r="D212" t="n">
-        <v>2085.09</v>
+        <v>430.37</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4473,17 +4473,17 @@
         <v>46218</v>
       </c>
       <c r="B213" t="n">
-        <v>2133</v>
+        <v>1117</v>
       </c>
       <c r="C213" t="n">
-        <v>213</v>
+        <v>8888</v>
       </c>
       <c r="D213" t="n">
-        <v>526.8</v>
+        <v>672.47</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4492,17 +4492,17 @@
         <v>46218</v>
       </c>
       <c r="B214" t="n">
-        <v>351</v>
+        <v>2749</v>
       </c>
       <c r="C214" t="n">
-        <v>3009</v>
+        <v>8888</v>
       </c>
       <c r="D214" t="n">
-        <v>416.36</v>
+        <v>1860.64</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4511,17 +4511,17 @@
         <v>46218</v>
       </c>
       <c r="B215" t="n">
-        <v>2250</v>
+        <v>42</v>
       </c>
       <c r="C215" t="n">
         <v>8888</v>
       </c>
       <c r="D215" t="n">
-        <v>709.46</v>
+        <v>280.05</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4530,17 +4530,17 @@
         <v>46218</v>
       </c>
       <c r="B216" t="n">
-        <v>2648</v>
+        <v>1478</v>
       </c>
       <c r="C216" t="n">
         <v>8888</v>
       </c>
       <c r="D216" t="n">
-        <v>1873.52</v>
+        <v>875.34</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4549,17 +4549,17 @@
         <v>46218</v>
       </c>
       <c r="B217" t="n">
-        <v>131</v>
+        <v>2491</v>
       </c>
       <c r="C217" t="n">
         <v>8888</v>
       </c>
       <c r="D217" t="n">
-        <v>1369.91</v>
+        <v>650.4299999999999</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4568,17 +4568,17 @@
         <v>46218</v>
       </c>
       <c r="B218" t="n">
-        <v>2790</v>
+        <v>353</v>
       </c>
       <c r="C218" t="n">
-        <v>1953</v>
+        <v>8888</v>
       </c>
       <c r="D218" t="n">
-        <v>371.88</v>
+        <v>653.13</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4587,17 +4587,17 @@
         <v>46218</v>
       </c>
       <c r="B219" t="n">
-        <v>363</v>
+        <v>2015</v>
       </c>
       <c r="C219" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D219" t="n">
-        <v>635.1</v>
+        <v>4436.15</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4606,17 +4606,17 @@
         <v>46218</v>
       </c>
       <c r="B220" t="n">
-        <v>2716</v>
+        <v>559</v>
       </c>
       <c r="C220" t="n">
-        <v>1929</v>
+        <v>8888</v>
       </c>
       <c r="D220" t="n">
-        <v>1073.33</v>
+        <v>1453.53</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4625,13 +4625,13 @@
         <v>46218</v>
       </c>
       <c r="B221" t="n">
-        <v>2298</v>
+        <v>1890</v>
       </c>
       <c r="C221" t="n">
-        <v>675</v>
+        <v>1953</v>
       </c>
       <c r="D221" t="n">
-        <v>401.85</v>
+        <v>1674.57</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -4644,17 +4644,17 @@
         <v>46218</v>
       </c>
       <c r="B222" t="n">
-        <v>2639</v>
+        <v>1317</v>
       </c>
       <c r="C222" t="n">
-        <v>1953</v>
+        <v>8888</v>
       </c>
       <c r="D222" t="n">
-        <v>504.09</v>
+        <v>1626.02</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4663,13 +4663,13 @@
         <v>46218</v>
       </c>
       <c r="B223" t="n">
-        <v>2109</v>
+        <v>2782</v>
       </c>
       <c r="C223" t="n">
         <v>8888</v>
       </c>
       <c r="D223" t="n">
-        <v>2293.78</v>
+        <v>1786.32</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -4682,17 +4682,17 @@
         <v>46218</v>
       </c>
       <c r="B224" t="n">
-        <v>1116</v>
+        <v>953</v>
       </c>
       <c r="C224" t="n">
         <v>8888</v>
       </c>
       <c r="D224" t="n">
-        <v>2919.53</v>
+        <v>364.44</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4701,17 +4701,17 @@
         <v>46218</v>
       </c>
       <c r="B225" t="n">
-        <v>2250</v>
+        <v>2251</v>
       </c>
       <c r="C225" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D225" t="n">
-        <v>1803.76</v>
+        <v>989.26</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4720,17 +4720,17 @@
         <v>46218</v>
       </c>
       <c r="B226" t="n">
-        <v>353</v>
+        <v>483</v>
       </c>
       <c r="C226" t="n">
-        <v>8888</v>
+        <v>841</v>
       </c>
       <c r="D226" t="n">
-        <v>349.33</v>
+        <v>2085.09</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4739,13 +4739,13 @@
         <v>46218</v>
       </c>
       <c r="B227" t="n">
-        <v>2698</v>
+        <v>2133</v>
       </c>
       <c r="C227" t="n">
-        <v>874</v>
+        <v>213</v>
       </c>
       <c r="D227" t="n">
-        <v>1230.43</v>
+        <v>526.8</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -4758,17 +4758,17 @@
         <v>46218</v>
       </c>
       <c r="B228" t="n">
-        <v>42</v>
+        <v>351</v>
       </c>
       <c r="C228" t="n">
-        <v>8888</v>
+        <v>3009</v>
       </c>
       <c r="D228" t="n">
-        <v>79947.14999999999</v>
+        <v>416.36</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4777,17 +4777,17 @@
         <v>46218</v>
       </c>
       <c r="B229" t="n">
-        <v>772</v>
+        <v>2250</v>
       </c>
       <c r="C229" t="n">
         <v>8888</v>
       </c>
       <c r="D229" t="n">
-        <v>400.25</v>
+        <v>709.46</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4796,17 +4796,17 @@
         <v>46218</v>
       </c>
       <c r="B230" t="n">
-        <v>2728</v>
+        <v>2648</v>
       </c>
       <c r="C230" t="n">
         <v>8888</v>
       </c>
       <c r="D230" t="n">
-        <v>1397.07</v>
+        <v>1873.52</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4815,17 +4815,17 @@
         <v>46218</v>
       </c>
       <c r="B231" t="n">
-        <v>2197</v>
+        <v>131</v>
       </c>
       <c r="C231" t="n">
-        <v>423</v>
+        <v>8888</v>
       </c>
       <c r="D231" t="n">
-        <v>2267.61</v>
+        <v>1369.91</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4834,13 +4834,13 @@
         <v>46218</v>
       </c>
       <c r="B232" t="n">
-        <v>2716</v>
+        <v>2790</v>
       </c>
       <c r="C232" t="n">
-        <v>977</v>
+        <v>1953</v>
       </c>
       <c r="D232" t="n">
-        <v>729.29</v>
+        <v>371.88</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -4853,17 +4853,17 @@
         <v>46218</v>
       </c>
       <c r="B233" t="n">
-        <v>1993</v>
+        <v>363</v>
       </c>
       <c r="C233" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D233" t="n">
-        <v>456.62</v>
+        <v>635.1</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4872,15 +4872,281 @@
         <v>46218</v>
       </c>
       <c r="B234" t="n">
+        <v>2716</v>
+      </c>
+      <c r="C234" t="n">
+        <v>1929</v>
+      </c>
+      <c r="D234" t="n">
+        <v>1073.33</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B235" t="n">
+        <v>2298</v>
+      </c>
+      <c r="C235" t="n">
+        <v>675</v>
+      </c>
+      <c r="D235" t="n">
+        <v>401.85</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B236" t="n">
+        <v>2639</v>
+      </c>
+      <c r="C236" t="n">
+        <v>1953</v>
+      </c>
+      <c r="D236" t="n">
+        <v>504.09</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B237" t="n">
+        <v>619</v>
+      </c>
+      <c r="C237" t="n">
+        <v>1139</v>
+      </c>
+      <c r="D237" t="n">
+        <v>1341.64</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B238" t="n">
+        <v>2109</v>
+      </c>
+      <c r="C238" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D238" t="n">
+        <v>2293.78</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B239" t="n">
+        <v>1116</v>
+      </c>
+      <c r="C239" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D239" t="n">
+        <v>2919.53</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B240" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C240" t="n">
+        <v>27</v>
+      </c>
+      <c r="D240" t="n">
+        <v>1803.76</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B241" t="n">
+        <v>2698</v>
+      </c>
+      <c r="C241" t="n">
+        <v>874</v>
+      </c>
+      <c r="D241" t="n">
+        <v>1230.43</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B242" t="n">
+        <v>42</v>
+      </c>
+      <c r="C242" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D242" t="n">
+        <v>79947.14999999999</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B243" t="n">
+        <v>772</v>
+      </c>
+      <c r="C243" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D243" t="n">
+        <v>400.25</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B244" t="n">
+        <v>2728</v>
+      </c>
+      <c r="C244" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D244" t="n">
+        <v>1397.07</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B245" t="n">
+        <v>2197</v>
+      </c>
+      <c r="C245" t="n">
+        <v>423</v>
+      </c>
+      <c r="D245" t="n">
+        <v>2267.61</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B246" t="n">
+        <v>2716</v>
+      </c>
+      <c r="C246" t="n">
+        <v>977</v>
+      </c>
+      <c r="D246" t="n">
+        <v>729.29</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B247" t="n">
+        <v>1993</v>
+      </c>
+      <c r="C247" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D247" t="n">
+        <v>456.62</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B248" t="n">
         <v>629</v>
       </c>
-      <c r="C234" t="n">
+      <c r="C248" t="n">
         <v>675</v>
       </c>
-      <c r="D234" t="n">
+      <c r="D248" t="n">
         <v>1054.76</v>
       </c>
-      <c r="E234" t="inlineStr">
+      <c r="E248" t="inlineStr">
         <is>
           <t>TELEMARKETING</t>
         </is>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E248"/>
+  <dimension ref="A1:E257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,7 +489,7 @@
         <v>8888</v>
       </c>
       <c r="D3" t="n">
-        <v>544.78</v>
+        <v>651.77</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
         <v>3403</v>
       </c>
       <c r="D6" t="n">
-        <v>1300.54</v>
+        <v>1559.04</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -996,17 +996,17 @@
         <v>46218</v>
       </c>
       <c r="B30" t="n">
-        <v>931</v>
+        <v>2695</v>
       </c>
       <c r="C30" t="n">
-        <v>423</v>
+        <v>8888</v>
       </c>
       <c r="D30" t="n">
-        <v>492.34</v>
+        <v>677.6799999999999</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1015,17 +1015,17 @@
         <v>46218</v>
       </c>
       <c r="B31" t="n">
-        <v>951</v>
+        <v>931</v>
       </c>
       <c r="C31" t="n">
-        <v>8888</v>
+        <v>423</v>
       </c>
       <c r="D31" t="n">
-        <v>2171.08</v>
+        <v>492.34</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1034,13 +1034,13 @@
         <v>46218</v>
       </c>
       <c r="B32" t="n">
-        <v>2641</v>
+        <v>1117</v>
       </c>
       <c r="C32" t="n">
         <v>8888</v>
       </c>
       <c r="D32" t="n">
-        <v>2527.79</v>
+        <v>540.15</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1053,17 +1053,17 @@
         <v>46218</v>
       </c>
       <c r="B33" t="n">
-        <v>2695</v>
+        <v>2641</v>
       </c>
       <c r="C33" t="n">
         <v>8888</v>
       </c>
       <c r="D33" t="n">
-        <v>411.42</v>
+        <v>2527.79</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1072,17 +1072,17 @@
         <v>46218</v>
       </c>
       <c r="B34" t="n">
-        <v>525</v>
+        <v>2251</v>
       </c>
       <c r="C34" t="n">
         <v>8888</v>
       </c>
       <c r="D34" t="n">
-        <v>408.25</v>
+        <v>1010.74</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1091,17 +1091,17 @@
         <v>46218</v>
       </c>
       <c r="B35" t="n">
-        <v>1808</v>
+        <v>951</v>
       </c>
       <c r="C35" t="n">
         <v>8888</v>
       </c>
       <c r="D35" t="n">
-        <v>695.3200000000001</v>
+        <v>2171.08</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1110,13 +1110,13 @@
         <v>46218</v>
       </c>
       <c r="B36" t="n">
-        <v>609</v>
+        <v>525</v>
       </c>
       <c r="C36" t="n">
         <v>8888</v>
       </c>
       <c r="D36" t="n">
-        <v>1909.37</v>
+        <v>408.25</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1129,17 +1129,17 @@
         <v>46218</v>
       </c>
       <c r="B37" t="n">
-        <v>949</v>
+        <v>1808</v>
       </c>
       <c r="C37" t="n">
-        <v>1134</v>
+        <v>8888</v>
       </c>
       <c r="D37" t="n">
-        <v>30.46</v>
+        <v>695.3200000000001</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1148,17 +1148,17 @@
         <v>46218</v>
       </c>
       <c r="B38" t="n">
-        <v>42</v>
+        <v>609</v>
       </c>
       <c r="C38" t="n">
-        <v>1139</v>
+        <v>8888</v>
       </c>
       <c r="D38" t="n">
-        <v>358.97</v>
+        <v>1909.37</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1167,17 +1167,17 @@
         <v>46218</v>
       </c>
       <c r="B39" t="n">
-        <v>2499</v>
+        <v>949</v>
       </c>
       <c r="C39" t="n">
-        <v>8888</v>
+        <v>1134</v>
       </c>
       <c r="D39" t="n">
-        <v>1049.3</v>
+        <v>30.46</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1186,17 +1186,17 @@
         <v>46218</v>
       </c>
       <c r="B40" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="C40" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D40" t="n">
-        <v>1643.73</v>
+        <v>358.97</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1205,13 +1205,13 @@
         <v>46218</v>
       </c>
       <c r="B41" t="n">
-        <v>2245</v>
+        <v>2499</v>
       </c>
       <c r="C41" t="n">
         <v>8888</v>
       </c>
       <c r="D41" t="n">
-        <v>2740.06</v>
+        <v>1049.3</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1224,17 +1224,17 @@
         <v>46218</v>
       </c>
       <c r="B42" t="n">
-        <v>325</v>
+        <v>58</v>
       </c>
       <c r="C42" t="n">
         <v>8888</v>
       </c>
       <c r="D42" t="n">
-        <v>952.75</v>
+        <v>2194.12</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
         <v>46218</v>
       </c>
       <c r="B43" t="n">
-        <v>2383</v>
+        <v>2245</v>
       </c>
       <c r="C43" t="n">
         <v>8888</v>
       </c>
       <c r="D43" t="n">
-        <v>7926.02</v>
+        <v>3382.78</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1262,17 +1262,17 @@
         <v>46218</v>
       </c>
       <c r="B44" t="n">
-        <v>1117</v>
+        <v>325</v>
       </c>
       <c r="C44" t="n">
-        <v>1139</v>
+        <v>8888</v>
       </c>
       <c r="D44" t="n">
-        <v>916.72</v>
+        <v>1079.66</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1281,17 +1281,17 @@
         <v>46218</v>
       </c>
       <c r="B45" t="n">
-        <v>374</v>
+        <v>2383</v>
       </c>
       <c r="C45" t="n">
         <v>8888</v>
       </c>
       <c r="D45" t="n">
-        <v>2810.86</v>
+        <v>7926.02</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1300,17 +1300,17 @@
         <v>46218</v>
       </c>
       <c r="B46" t="n">
-        <v>2279</v>
+        <v>1117</v>
       </c>
       <c r="C46" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D46" t="n">
-        <v>712.66</v>
+        <v>916.72</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1319,17 +1319,17 @@
         <v>46218</v>
       </c>
       <c r="B47" t="n">
-        <v>535</v>
+        <v>374</v>
       </c>
       <c r="C47" t="n">
         <v>8888</v>
       </c>
       <c r="D47" t="n">
-        <v>5836.12</v>
+        <v>2810.86</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1338,13 +1338,13 @@
         <v>46218</v>
       </c>
       <c r="B48" t="n">
-        <v>535</v>
+        <v>2279</v>
       </c>
       <c r="C48" t="n">
         <v>8888</v>
       </c>
       <c r="D48" t="n">
-        <v>1352.51</v>
+        <v>712.66</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1357,17 +1357,17 @@
         <v>46218</v>
       </c>
       <c r="B49" t="n">
-        <v>2678</v>
+        <v>535</v>
       </c>
       <c r="C49" t="n">
-        <v>1312</v>
+        <v>8888</v>
       </c>
       <c r="D49" t="n">
-        <v>364.96</v>
+        <v>5836.12</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1376,13 +1376,13 @@
         <v>46218</v>
       </c>
       <c r="B50" t="n">
-        <v>2345</v>
+        <v>535</v>
       </c>
       <c r="C50" t="n">
         <v>8888</v>
       </c>
       <c r="D50" t="n">
-        <v>863.16</v>
+        <v>1352.51</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1395,17 +1395,17 @@
         <v>46218</v>
       </c>
       <c r="B51" t="n">
-        <v>945</v>
+        <v>2678</v>
       </c>
       <c r="C51" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D51" t="n">
-        <v>27337.21</v>
+        <v>364.96</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>PEDIDO ELETRÔNICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1414,17 +1414,17 @@
         <v>46218</v>
       </c>
       <c r="B52" t="n">
-        <v>2686</v>
+        <v>2345</v>
       </c>
       <c r="C52" t="n">
         <v>8888</v>
       </c>
       <c r="D52" t="n">
-        <v>684.2</v>
+        <v>863.16</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1433,17 +1433,17 @@
         <v>46218</v>
       </c>
       <c r="B53" t="n">
-        <v>438</v>
+        <v>945</v>
       </c>
       <c r="C53" t="n">
         <v>8888</v>
       </c>
       <c r="D53" t="n">
-        <v>220.06</v>
+        <v>27337.21</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>PEDIDO ELETRÔNICO</t>
         </is>
       </c>
     </row>
@@ -1452,17 +1452,17 @@
         <v>46218</v>
       </c>
       <c r="B54" t="n">
-        <v>664</v>
+        <v>2686</v>
       </c>
       <c r="C54" t="n">
         <v>8888</v>
       </c>
       <c r="D54" t="n">
-        <v>6275.01</v>
+        <v>684.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1471,17 +1471,17 @@
         <v>46218</v>
       </c>
       <c r="B55" t="n">
-        <v>353</v>
+        <v>438</v>
       </c>
       <c r="C55" t="n">
-        <v>3179</v>
+        <v>8888</v>
       </c>
       <c r="D55" t="n">
-        <v>495.84</v>
+        <v>220.06</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1490,17 +1490,17 @@
         <v>46218</v>
       </c>
       <c r="B56" t="n">
-        <v>1293</v>
+        <v>1956</v>
       </c>
       <c r="C56" t="n">
         <v>8888</v>
       </c>
       <c r="D56" t="n">
-        <v>3129.07</v>
+        <v>5311.01</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1509,13 +1509,13 @@
         <v>46218</v>
       </c>
       <c r="B57" t="n">
-        <v>2279</v>
+        <v>664</v>
       </c>
       <c r="C57" t="n">
         <v>8888</v>
       </c>
       <c r="D57" t="n">
-        <v>2753.96</v>
+        <v>6275.01</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -1528,17 +1528,17 @@
         <v>46218</v>
       </c>
       <c r="B58" t="n">
-        <v>1937</v>
+        <v>353</v>
       </c>
       <c r="C58" t="n">
-        <v>8888</v>
+        <v>3179</v>
       </c>
       <c r="D58" t="n">
-        <v>1685.72</v>
+        <v>495.84</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1547,17 +1547,17 @@
         <v>46218</v>
       </c>
       <c r="B59" t="n">
-        <v>941</v>
+        <v>1293</v>
       </c>
       <c r="C59" t="n">
         <v>8888</v>
       </c>
       <c r="D59" t="n">
-        <v>864.14</v>
+        <v>3129.07</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1566,17 +1566,17 @@
         <v>46218</v>
       </c>
       <c r="B60" t="n">
-        <v>1137</v>
+        <v>2279</v>
       </c>
       <c r="C60" t="n">
         <v>8888</v>
       </c>
       <c r="D60" t="n">
-        <v>1947.93</v>
+        <v>3900.07</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1585,17 +1585,17 @@
         <v>46218</v>
       </c>
       <c r="B61" t="n">
-        <v>2631</v>
+        <v>1937</v>
       </c>
       <c r="C61" t="n">
-        <v>2853</v>
+        <v>8888</v>
       </c>
       <c r="D61" t="n">
-        <v>1272.12</v>
+        <v>1685.72</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1604,17 +1604,17 @@
         <v>46218</v>
       </c>
       <c r="B62" t="n">
-        <v>2793</v>
+        <v>941</v>
       </c>
       <c r="C62" t="n">
-        <v>977</v>
+        <v>8888</v>
       </c>
       <c r="D62" t="n">
-        <v>1188.59</v>
+        <v>864.14</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
         <v>46218</v>
       </c>
       <c r="B63" t="n">
-        <v>2802</v>
+        <v>1137</v>
       </c>
       <c r="C63" t="n">
         <v>8888</v>
       </c>
       <c r="D63" t="n">
-        <v>1264.57</v>
+        <v>1947.93</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1642,17 +1642,17 @@
         <v>46218</v>
       </c>
       <c r="B64" t="n">
-        <v>451</v>
+        <v>2631</v>
       </c>
       <c r="C64" t="n">
-        <v>8888</v>
+        <v>2853</v>
       </c>
       <c r="D64" t="n">
-        <v>757.5700000000001</v>
+        <v>2418.28</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1661,17 +1661,17 @@
         <v>46218</v>
       </c>
       <c r="B65" t="n">
-        <v>374</v>
+        <v>2793</v>
       </c>
       <c r="C65" t="n">
-        <v>8888</v>
+        <v>977</v>
       </c>
       <c r="D65" t="n">
-        <v>44.6</v>
+        <v>1188.59</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1680,13 +1680,13 @@
         <v>46218</v>
       </c>
       <c r="B66" t="n">
-        <v>703</v>
+        <v>2802</v>
       </c>
       <c r="C66" t="n">
         <v>8888</v>
       </c>
       <c r="D66" t="n">
-        <v>12155.46</v>
+        <v>1264.57</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -1699,17 +1699,17 @@
         <v>46218</v>
       </c>
       <c r="B67" t="n">
-        <v>1756</v>
+        <v>451</v>
       </c>
       <c r="C67" t="n">
         <v>8888</v>
       </c>
       <c r="D67" t="n">
-        <v>4416.47</v>
+        <v>757.5700000000001</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
         <v>46218</v>
       </c>
       <c r="B68" t="n">
-        <v>1956</v>
+        <v>374</v>
       </c>
       <c r="C68" t="n">
         <v>8888</v>
       </c>
       <c r="D68" t="n">
-        <v>4557.34</v>
+        <v>44.6</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1737,13 +1737,13 @@
         <v>46218</v>
       </c>
       <c r="B69" t="n">
-        <v>925</v>
+        <v>703</v>
       </c>
       <c r="C69" t="n">
         <v>8888</v>
       </c>
       <c r="D69" t="n">
-        <v>651.59</v>
+        <v>12155.46</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -1756,17 +1756,17 @@
         <v>46218</v>
       </c>
       <c r="B70" t="n">
-        <v>941</v>
+        <v>1756</v>
       </c>
       <c r="C70" t="n">
-        <v>977</v>
+        <v>8888</v>
       </c>
       <c r="D70" t="n">
-        <v>359.73</v>
+        <v>4416.47</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1775,17 +1775,17 @@
         <v>46218</v>
       </c>
       <c r="B71" t="n">
-        <v>2648</v>
+        <v>925</v>
       </c>
       <c r="C71" t="n">
         <v>8888</v>
       </c>
       <c r="D71" t="n">
-        <v>1594.42</v>
+        <v>651.59</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1794,17 +1794,17 @@
         <v>46218</v>
       </c>
       <c r="B72" t="n">
-        <v>663</v>
+        <v>941</v>
       </c>
       <c r="C72" t="n">
-        <v>8888</v>
+        <v>977</v>
       </c>
       <c r="D72" t="n">
-        <v>6645.33</v>
+        <v>359.73</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1813,17 +1813,17 @@
         <v>46218</v>
       </c>
       <c r="B73" t="n">
-        <v>2714</v>
+        <v>2648</v>
       </c>
       <c r="C73" t="n">
-        <v>519</v>
+        <v>8888</v>
       </c>
       <c r="D73" t="n">
-        <v>61939.22</v>
+        <v>1594.42</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1832,17 +1832,17 @@
         <v>46218</v>
       </c>
       <c r="B74" t="n">
-        <v>483</v>
+        <v>663</v>
       </c>
       <c r="C74" t="n">
         <v>8888</v>
       </c>
       <c r="D74" t="n">
-        <v>11360.2</v>
+        <v>6645.33</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1851,17 +1851,17 @@
         <v>46218</v>
       </c>
       <c r="B75" t="n">
-        <v>1075</v>
+        <v>2714</v>
       </c>
       <c r="C75" t="n">
-        <v>8888</v>
+        <v>519</v>
       </c>
       <c r="D75" t="n">
-        <v>11607.79</v>
+        <v>61939.22</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1870,17 +1870,17 @@
         <v>46218</v>
       </c>
       <c r="B76" t="n">
-        <v>629</v>
+        <v>483</v>
       </c>
       <c r="C76" t="n">
         <v>8888</v>
       </c>
       <c r="D76" t="n">
-        <v>9233.719999999999</v>
+        <v>12405.46</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1889,17 +1889,17 @@
         <v>46218</v>
       </c>
       <c r="B77" t="n">
-        <v>1983</v>
+        <v>1075</v>
       </c>
       <c r="C77" t="n">
-        <v>841</v>
+        <v>8888</v>
       </c>
       <c r="D77" t="n">
-        <v>243.92</v>
+        <v>11607.79</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1908,17 +1908,17 @@
         <v>46218</v>
       </c>
       <c r="B78" t="n">
-        <v>1137</v>
+        <v>629</v>
       </c>
       <c r="C78" t="n">
         <v>8888</v>
       </c>
       <c r="D78" t="n">
-        <v>3578.51</v>
+        <v>9233.719999999999</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1927,17 +1927,17 @@
         <v>46218</v>
       </c>
       <c r="B79" t="n">
-        <v>2651</v>
+        <v>1983</v>
       </c>
       <c r="C79" t="n">
-        <v>8888</v>
+        <v>841</v>
       </c>
       <c r="D79" t="n">
-        <v>1296.58</v>
+        <v>633.79</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1946,13 +1946,13 @@
         <v>46218</v>
       </c>
       <c r="B80" t="n">
-        <v>2789</v>
+        <v>1137</v>
       </c>
       <c r="C80" t="n">
         <v>8888</v>
       </c>
       <c r="D80" t="n">
-        <v>1293.93</v>
+        <v>3578.51</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -1965,17 +1965,17 @@
         <v>46218</v>
       </c>
       <c r="B81" t="n">
-        <v>1956</v>
+        <v>2651</v>
       </c>
       <c r="C81" t="n">
-        <v>423</v>
+        <v>8888</v>
       </c>
       <c r="D81" t="n">
-        <v>1416.35</v>
+        <v>1296.58</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1984,13 +1984,13 @@
         <v>46218</v>
       </c>
       <c r="B82" t="n">
-        <v>2709</v>
+        <v>2789</v>
       </c>
       <c r="C82" t="n">
         <v>8888</v>
       </c>
       <c r="D82" t="n">
-        <v>547.6900000000001</v>
+        <v>1293.93</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2003,17 +2003,17 @@
         <v>46218</v>
       </c>
       <c r="B83" t="n">
-        <v>1308</v>
+        <v>1956</v>
       </c>
       <c r="C83" t="n">
-        <v>8888</v>
+        <v>423</v>
       </c>
       <c r="D83" t="n">
-        <v>1460.53</v>
+        <v>1416.35</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2022,17 +2022,17 @@
         <v>46218</v>
       </c>
       <c r="B84" t="n">
-        <v>2026</v>
+        <v>2709</v>
       </c>
       <c r="C84" t="n">
         <v>8888</v>
       </c>
       <c r="D84" t="n">
-        <v>2237.62</v>
+        <v>547.6900000000001</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2041,17 +2041,17 @@
         <v>46218</v>
       </c>
       <c r="B85" t="n">
-        <v>2789</v>
+        <v>1308</v>
       </c>
       <c r="C85" t="n">
         <v>8888</v>
       </c>
       <c r="D85" t="n">
-        <v>747.77</v>
+        <v>1460.53</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2060,17 +2060,17 @@
         <v>46218</v>
       </c>
       <c r="B86" t="n">
-        <v>89</v>
+        <v>2026</v>
       </c>
       <c r="C86" t="n">
-        <v>13148</v>
+        <v>8888</v>
       </c>
       <c r="D86" t="n">
-        <v>1883.74</v>
+        <v>2237.62</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2079,17 +2079,17 @@
         <v>46218</v>
       </c>
       <c r="B87" t="n">
-        <v>2709</v>
+        <v>2789</v>
       </c>
       <c r="C87" t="n">
-        <v>2220</v>
+        <v>8888</v>
       </c>
       <c r="D87" t="n">
-        <v>390.19</v>
+        <v>747.77</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2098,17 +2098,17 @@
         <v>46218</v>
       </c>
       <c r="B88" t="n">
-        <v>2345</v>
+        <v>89</v>
       </c>
       <c r="C88" t="n">
-        <v>8888</v>
+        <v>13148</v>
       </c>
       <c r="D88" t="n">
-        <v>748.86</v>
+        <v>2842.03</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2117,17 +2117,17 @@
         <v>46218</v>
       </c>
       <c r="B89" t="n">
-        <v>1983</v>
+        <v>1075</v>
       </c>
       <c r="C89" t="n">
         <v>8888</v>
       </c>
       <c r="D89" t="n">
-        <v>851.7</v>
+        <v>698.63</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2136,13 +2136,13 @@
         <v>46218</v>
       </c>
       <c r="B90" t="n">
-        <v>2765</v>
+        <v>2709</v>
       </c>
       <c r="C90" t="n">
-        <v>1883</v>
+        <v>2220</v>
       </c>
       <c r="D90" t="n">
-        <v>3638.6</v>
+        <v>390.19</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -2155,17 +2155,17 @@
         <v>46218</v>
       </c>
       <c r="B91" t="n">
-        <v>569</v>
+        <v>2345</v>
       </c>
       <c r="C91" t="n">
         <v>8888</v>
       </c>
       <c r="D91" t="n">
-        <v>995.33</v>
+        <v>748.86</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2174,17 +2174,17 @@
         <v>46218</v>
       </c>
       <c r="B92" t="n">
-        <v>360</v>
+        <v>1983</v>
       </c>
       <c r="C92" t="n">
-        <v>546</v>
+        <v>8888</v>
       </c>
       <c r="D92" t="n">
-        <v>1609.68</v>
+        <v>2806.44</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2193,13 +2193,13 @@
         <v>46218</v>
       </c>
       <c r="B93" t="n">
-        <v>2711</v>
+        <v>2765</v>
       </c>
       <c r="C93" t="n">
-        <v>1953</v>
+        <v>1883</v>
       </c>
       <c r="D93" t="n">
-        <v>150.27</v>
+        <v>3638.6</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -2212,13 +2212,13 @@
         <v>46218</v>
       </c>
       <c r="B94" t="n">
-        <v>2308</v>
+        <v>569</v>
       </c>
       <c r="C94" t="n">
         <v>8888</v>
       </c>
       <c r="D94" t="n">
-        <v>488.69</v>
+        <v>995.33</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -2231,13 +2231,13 @@
         <v>46218</v>
       </c>
       <c r="B95" t="n">
-        <v>2211</v>
+        <v>360</v>
       </c>
       <c r="C95" t="n">
-        <v>874</v>
+        <v>546</v>
       </c>
       <c r="D95" t="n">
-        <v>1526.94</v>
+        <v>1609.68</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -2250,17 +2250,17 @@
         <v>46218</v>
       </c>
       <c r="B96" t="n">
-        <v>559</v>
+        <v>2711</v>
       </c>
       <c r="C96" t="n">
-        <v>8888</v>
+        <v>1953</v>
       </c>
       <c r="D96" t="n">
-        <v>859.92</v>
+        <v>150.27</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2269,13 +2269,13 @@
         <v>46218</v>
       </c>
       <c r="B97" t="n">
-        <v>890</v>
+        <v>2279</v>
       </c>
       <c r="C97" t="n">
         <v>8888</v>
       </c>
       <c r="D97" t="n">
-        <v>387.2</v>
+        <v>447.5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -2288,17 +2288,17 @@
         <v>46218</v>
       </c>
       <c r="B98" t="n">
-        <v>2768</v>
+        <v>2308</v>
       </c>
       <c r="C98" t="n">
         <v>8888</v>
       </c>
       <c r="D98" t="n">
-        <v>6523.26</v>
+        <v>488.69</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2307,17 +2307,17 @@
         <v>46218</v>
       </c>
       <c r="B99" t="n">
-        <v>1063</v>
+        <v>2211</v>
       </c>
       <c r="C99" t="n">
-        <v>8888</v>
+        <v>874</v>
       </c>
       <c r="D99" t="n">
-        <v>4487.11</v>
+        <v>1526.94</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2326,17 +2326,17 @@
         <v>46218</v>
       </c>
       <c r="B100" t="n">
-        <v>2279</v>
+        <v>559</v>
       </c>
       <c r="C100" t="n">
-        <v>1139</v>
+        <v>8888</v>
       </c>
       <c r="D100" t="n">
-        <v>652.51</v>
+        <v>859.92</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2345,17 +2345,17 @@
         <v>46218</v>
       </c>
       <c r="B101" t="n">
-        <v>1299</v>
+        <v>890</v>
       </c>
       <c r="C101" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D101" t="n">
-        <v>1435.52</v>
+        <v>387.2</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2364,17 +2364,17 @@
         <v>46218</v>
       </c>
       <c r="B102" t="n">
-        <v>1478</v>
+        <v>2768</v>
       </c>
       <c r="C102" t="n">
-        <v>675</v>
+        <v>8888</v>
       </c>
       <c r="D102" t="n">
-        <v>1967.85</v>
+        <v>6523.26</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2383,17 +2383,17 @@
         <v>46218</v>
       </c>
       <c r="B103" t="n">
-        <v>767</v>
+        <v>1063</v>
       </c>
       <c r="C103" t="n">
         <v>8888</v>
       </c>
       <c r="D103" t="n">
-        <v>3292.44</v>
+        <v>4487.11</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2402,17 +2402,17 @@
         <v>46218</v>
       </c>
       <c r="B104" t="n">
-        <v>285</v>
+        <v>947</v>
       </c>
       <c r="C104" t="n">
         <v>8888</v>
       </c>
       <c r="D104" t="n">
-        <v>3349.8</v>
+        <v>5667.85</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>PEDIDO ELETRÔNICO</t>
         </is>
       </c>
     </row>
@@ -2421,17 +2421,17 @@
         <v>46218</v>
       </c>
       <c r="B105" t="n">
-        <v>477</v>
+        <v>2279</v>
       </c>
       <c r="C105" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D105" t="n">
-        <v>917.33</v>
+        <v>1031.06</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2440,17 +2440,17 @@
         <v>46218</v>
       </c>
       <c r="B106" t="n">
-        <v>1983</v>
+        <v>1299</v>
       </c>
       <c r="C106" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D106" t="n">
-        <v>5115.01</v>
+        <v>1435.52</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2459,13 +2459,13 @@
         <v>46218</v>
       </c>
       <c r="B107" t="n">
-        <v>477</v>
+        <v>1478</v>
       </c>
       <c r="C107" t="n">
-        <v>58</v>
+        <v>675</v>
       </c>
       <c r="D107" t="n">
-        <v>1540.55</v>
+        <v>1967.85</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -2478,13 +2478,13 @@
         <v>46218</v>
       </c>
       <c r="B108" t="n">
-        <v>1937</v>
+        <v>767</v>
       </c>
       <c r="C108" t="n">
         <v>8888</v>
       </c>
       <c r="D108" t="n">
-        <v>2600.61</v>
+        <v>3292.44</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -2497,13 +2497,13 @@
         <v>46218</v>
       </c>
       <c r="B109" t="n">
-        <v>1063</v>
+        <v>285</v>
       </c>
       <c r="C109" t="n">
         <v>8888</v>
       </c>
       <c r="D109" t="n">
-        <v>2549.86</v>
+        <v>3349.8</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -2516,17 +2516,17 @@
         <v>46218</v>
       </c>
       <c r="B110" t="n">
-        <v>2584</v>
+        <v>477</v>
       </c>
       <c r="C110" t="n">
-        <v>1929</v>
+        <v>8888</v>
       </c>
       <c r="D110" t="n">
-        <v>756.16</v>
+        <v>917.33</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2535,13 +2535,13 @@
         <v>46218</v>
       </c>
       <c r="B111" t="n">
-        <v>58</v>
+        <v>1983</v>
       </c>
       <c r="C111" t="n">
         <v>8888</v>
       </c>
       <c r="D111" t="n">
-        <v>558.03</v>
+        <v>5115.01</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -2554,17 +2554,17 @@
         <v>46218</v>
       </c>
       <c r="B112" t="n">
-        <v>424</v>
+        <v>477</v>
       </c>
       <c r="C112" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D112" t="n">
-        <v>1362.42</v>
+        <v>3946.44</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2573,17 +2573,17 @@
         <v>46218</v>
       </c>
       <c r="B113" t="n">
-        <v>675</v>
+        <v>1937</v>
       </c>
       <c r="C113" t="n">
         <v>8888</v>
       </c>
       <c r="D113" t="n">
-        <v>616.73</v>
+        <v>2600.61</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2592,13 +2592,13 @@
         <v>46218</v>
       </c>
       <c r="B114" t="n">
-        <v>663</v>
+        <v>1063</v>
       </c>
       <c r="C114" t="n">
         <v>8888</v>
       </c>
       <c r="D114" t="n">
-        <v>255.13</v>
+        <v>2549.86</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -2611,17 +2611,17 @@
         <v>46218</v>
       </c>
       <c r="B115" t="n">
-        <v>1993</v>
+        <v>2584</v>
       </c>
       <c r="C115" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D115" t="n">
-        <v>362.63</v>
+        <v>756.16</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2630,17 +2630,17 @@
         <v>46218</v>
       </c>
       <c r="B116" t="n">
-        <v>1465</v>
+        <v>58</v>
       </c>
       <c r="C116" t="n">
         <v>8888</v>
       </c>
       <c r="D116" t="n">
-        <v>3373.83</v>
+        <v>558.03</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2649,17 +2649,17 @@
         <v>46218</v>
       </c>
       <c r="B117" t="n">
-        <v>89</v>
+        <v>424</v>
       </c>
       <c r="C117" t="n">
         <v>8888</v>
       </c>
       <c r="D117" t="n">
-        <v>479</v>
+        <v>1362.42</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2668,13 +2668,13 @@
         <v>46218</v>
       </c>
       <c r="B118" t="n">
-        <v>595</v>
+        <v>675</v>
       </c>
       <c r="C118" t="n">
         <v>8888</v>
       </c>
       <c r="D118" t="n">
-        <v>18084.5</v>
+        <v>616.73</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -2687,17 +2687,17 @@
         <v>46218</v>
       </c>
       <c r="B119" t="n">
-        <v>2696</v>
+        <v>663</v>
       </c>
       <c r="C119" t="n">
-        <v>1954</v>
+        <v>8888</v>
       </c>
       <c r="D119" t="n">
-        <v>1597.76</v>
+        <v>255.13</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2706,17 +2706,17 @@
         <v>46218</v>
       </c>
       <c r="B120" t="n">
-        <v>360</v>
+        <v>1993</v>
       </c>
       <c r="C120" t="n">
         <v>8888</v>
       </c>
       <c r="D120" t="n">
-        <v>4596.89</v>
+        <v>724.14</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2728,14 +2728,14 @@
         <v>1465</v>
       </c>
       <c r="C121" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D121" t="n">
-        <v>777.2</v>
+        <v>7362.56</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2744,17 +2744,17 @@
         <v>46218</v>
       </c>
       <c r="B122" t="n">
-        <v>947</v>
+        <v>89</v>
       </c>
       <c r="C122" t="n">
         <v>8888</v>
       </c>
       <c r="D122" t="n">
-        <v>5115.36</v>
+        <v>479</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>PEDIDO ELETRÔNICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2763,17 +2763,17 @@
         <v>46218</v>
       </c>
       <c r="B123" t="n">
-        <v>2178</v>
+        <v>595</v>
       </c>
       <c r="C123" t="n">
         <v>8888</v>
       </c>
       <c r="D123" t="n">
-        <v>619.92</v>
+        <v>18084.5</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2782,13 +2782,13 @@
         <v>46218</v>
       </c>
       <c r="B124" t="n">
-        <v>2026</v>
+        <v>2696</v>
       </c>
       <c r="C124" t="n">
-        <v>1929</v>
+        <v>1954</v>
       </c>
       <c r="D124" t="n">
-        <v>5293.13</v>
+        <v>1597.76</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -2801,17 +2801,17 @@
         <v>46218</v>
       </c>
       <c r="B125" t="n">
-        <v>630</v>
+        <v>360</v>
       </c>
       <c r="C125" t="n">
-        <v>1929</v>
+        <v>8888</v>
       </c>
       <c r="D125" t="n">
-        <v>1801.63</v>
+        <v>4596.89</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2820,17 +2820,17 @@
         <v>46218</v>
       </c>
       <c r="B126" t="n">
-        <v>1937</v>
+        <v>1465</v>
       </c>
       <c r="C126" t="n">
-        <v>8888</v>
+        <v>3403</v>
       </c>
       <c r="D126" t="n">
-        <v>2132.95</v>
+        <v>777.2</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2839,17 +2839,17 @@
         <v>46218</v>
       </c>
       <c r="B127" t="n">
-        <v>2577</v>
+        <v>2178</v>
       </c>
       <c r="C127" t="n">
         <v>8888</v>
       </c>
       <c r="D127" t="n">
-        <v>1647.08</v>
+        <v>619.92</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2858,17 +2858,17 @@
         <v>46218</v>
       </c>
       <c r="B128" t="n">
-        <v>1293</v>
+        <v>2026</v>
       </c>
       <c r="C128" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D128" t="n">
-        <v>2135.89</v>
+        <v>6021.92</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2877,17 +2877,17 @@
         <v>46218</v>
       </c>
       <c r="B129" t="n">
-        <v>2607</v>
+        <v>630</v>
       </c>
       <c r="C129" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D129" t="n">
-        <v>490.31</v>
+        <v>1801.63</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2896,17 +2896,17 @@
         <v>46218</v>
       </c>
       <c r="B130" t="n">
-        <v>1317</v>
+        <v>1937</v>
       </c>
       <c r="C130" t="n">
         <v>8888</v>
       </c>
       <c r="D130" t="n">
-        <v>907.72</v>
+        <v>2132.95</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2915,13 +2915,13 @@
         <v>46218</v>
       </c>
       <c r="B131" t="n">
-        <v>619</v>
+        <v>2577</v>
       </c>
       <c r="C131" t="n">
         <v>8888</v>
       </c>
       <c r="D131" t="n">
-        <v>1081.74</v>
+        <v>1647.08</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -2934,17 +2934,17 @@
         <v>46218</v>
       </c>
       <c r="B132" t="n">
-        <v>2571</v>
+        <v>1293</v>
       </c>
       <c r="C132" t="n">
-        <v>1312</v>
+        <v>8888</v>
       </c>
       <c r="D132" t="n">
-        <v>268.53</v>
+        <v>2135.89</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2953,13 +2953,13 @@
         <v>46218</v>
       </c>
       <c r="B133" t="n">
-        <v>20</v>
+        <v>2607</v>
       </c>
       <c r="C133" t="n">
         <v>8888</v>
       </c>
       <c r="D133" t="n">
-        <v>745.55</v>
+        <v>490.31</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -2972,13 +2972,13 @@
         <v>46218</v>
       </c>
       <c r="B134" t="n">
-        <v>1063</v>
+        <v>1317</v>
       </c>
       <c r="C134" t="n">
         <v>8888</v>
       </c>
       <c r="D134" t="n">
-        <v>1113.08</v>
+        <v>907.72</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -2991,17 +2991,17 @@
         <v>46218</v>
       </c>
       <c r="B135" t="n">
-        <v>2631</v>
+        <v>619</v>
       </c>
       <c r="C135" t="n">
         <v>8888</v>
       </c>
       <c r="D135" t="n">
-        <v>1447.86</v>
+        <v>1081.74</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3010,17 +3010,17 @@
         <v>46218</v>
       </c>
       <c r="B136" t="n">
-        <v>1906</v>
+        <v>2571</v>
       </c>
       <c r="C136" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D136" t="n">
-        <v>2774.84</v>
+        <v>268.53</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3029,13 +3029,13 @@
         <v>46218</v>
       </c>
       <c r="B137" t="n">
-        <v>1756</v>
+        <v>20</v>
       </c>
       <c r="C137" t="n">
         <v>8888</v>
       </c>
       <c r="D137" t="n">
-        <v>2275.21</v>
+        <v>745.55</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -3048,13 +3048,13 @@
         <v>46218</v>
       </c>
       <c r="B138" t="n">
-        <v>477</v>
+        <v>1063</v>
       </c>
       <c r="C138" t="n">
         <v>8888</v>
       </c>
       <c r="D138" t="n">
-        <v>707.52</v>
+        <v>1113.08</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -3067,13 +3067,13 @@
         <v>46218</v>
       </c>
       <c r="B139" t="n">
-        <v>2660</v>
+        <v>2631</v>
       </c>
       <c r="C139" t="n">
         <v>8888</v>
       </c>
       <c r="D139" t="n">
-        <v>2684.97</v>
+        <v>1447.86</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -3086,17 +3086,17 @@
         <v>46218</v>
       </c>
       <c r="B140" t="n">
-        <v>569</v>
+        <v>1906</v>
       </c>
       <c r="C140" t="n">
         <v>8888</v>
       </c>
       <c r="D140" t="n">
-        <v>36782.12</v>
+        <v>2774.84</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3105,17 +3105,17 @@
         <v>46218</v>
       </c>
       <c r="B141" t="n">
-        <v>483</v>
+        <v>1756</v>
       </c>
       <c r="C141" t="n">
         <v>8888</v>
       </c>
       <c r="D141" t="n">
-        <v>3102.48</v>
+        <v>2275.21</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3124,17 +3124,17 @@
         <v>46218</v>
       </c>
       <c r="B142" t="n">
-        <v>609</v>
+        <v>477</v>
       </c>
       <c r="C142" t="n">
         <v>8888</v>
       </c>
       <c r="D142" t="n">
-        <v>1633.68</v>
+        <v>707.52</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3143,17 +3143,17 @@
         <v>46218</v>
       </c>
       <c r="B143" t="n">
-        <v>483</v>
+        <v>2660</v>
       </c>
       <c r="C143" t="n">
         <v>8888</v>
       </c>
       <c r="D143" t="n">
-        <v>1578.32</v>
+        <v>2684.97</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3162,17 +3162,17 @@
         <v>46218</v>
       </c>
       <c r="B144" t="n">
-        <v>2089</v>
+        <v>569</v>
       </c>
       <c r="C144" t="n">
-        <v>1533</v>
+        <v>8888</v>
       </c>
       <c r="D144" t="n">
-        <v>1309.01</v>
+        <v>43745.83</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3181,17 +3181,17 @@
         <v>46218</v>
       </c>
       <c r="B145" t="n">
-        <v>1007</v>
+        <v>483</v>
       </c>
       <c r="C145" t="n">
         <v>8888</v>
       </c>
       <c r="D145" t="n">
-        <v>241.44</v>
+        <v>3102.48</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3200,17 +3200,17 @@
         <v>46218</v>
       </c>
       <c r="B146" t="n">
-        <v>1380</v>
+        <v>609</v>
       </c>
       <c r="C146" t="n">
         <v>8888</v>
       </c>
       <c r="D146" t="n">
-        <v>520.2</v>
+        <v>1633.68</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3219,17 +3219,17 @@
         <v>46218</v>
       </c>
       <c r="B147" t="n">
-        <v>1102</v>
+        <v>483</v>
       </c>
       <c r="C147" t="n">
         <v>8888</v>
       </c>
       <c r="D147" t="n">
-        <v>1137.04</v>
+        <v>2011.13</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3238,17 +3238,17 @@
         <v>46218</v>
       </c>
       <c r="B148" t="n">
-        <v>1075</v>
+        <v>2089</v>
       </c>
       <c r="C148" t="n">
-        <v>8888</v>
+        <v>1533</v>
       </c>
       <c r="D148" t="n">
-        <v>5710.94</v>
+        <v>1309.01</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3257,17 +3257,17 @@
         <v>46218</v>
       </c>
       <c r="B149" t="n">
-        <v>2681</v>
+        <v>1007</v>
       </c>
       <c r="C149" t="n">
         <v>8888</v>
       </c>
       <c r="D149" t="n">
-        <v>729.25</v>
+        <v>241.44</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3276,17 +3276,17 @@
         <v>46218</v>
       </c>
       <c r="B150" t="n">
-        <v>2245</v>
+        <v>1380</v>
       </c>
       <c r="C150" t="n">
         <v>8888</v>
       </c>
       <c r="D150" t="n">
-        <v>700.2</v>
+        <v>520.2</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3295,17 +3295,17 @@
         <v>46218</v>
       </c>
       <c r="B151" t="n">
-        <v>33</v>
+        <v>1102</v>
       </c>
       <c r="C151" t="n">
         <v>8888</v>
       </c>
       <c r="D151" t="n">
-        <v>926.97</v>
+        <v>1137.04</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3314,13 +3314,13 @@
         <v>46218</v>
       </c>
       <c r="B152" t="n">
-        <v>132</v>
+        <v>1075</v>
       </c>
       <c r="C152" t="n">
         <v>8888</v>
       </c>
       <c r="D152" t="n">
-        <v>6522.92</v>
+        <v>5710.94</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -3333,17 +3333,17 @@
         <v>46218</v>
       </c>
       <c r="B153" t="n">
-        <v>619</v>
+        <v>2681</v>
       </c>
       <c r="C153" t="n">
         <v>8888</v>
       </c>
       <c r="D153" t="n">
-        <v>2912.89</v>
+        <v>729.25</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
         <v>46218</v>
       </c>
       <c r="B154" t="n">
-        <v>452</v>
+        <v>2245</v>
       </c>
       <c r="C154" t="n">
         <v>8888</v>
       </c>
       <c r="D154" t="n">
-        <v>608.78</v>
+        <v>700.2</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3371,17 +3371,17 @@
         <v>46218</v>
       </c>
       <c r="B155" t="n">
-        <v>2463</v>
+        <v>40</v>
       </c>
       <c r="C155" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D155" t="n">
-        <v>363.69</v>
+        <v>678.21</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3390,17 +3390,17 @@
         <v>46218</v>
       </c>
       <c r="B156" t="n">
-        <v>1293</v>
+        <v>33</v>
       </c>
       <c r="C156" t="n">
-        <v>1281</v>
+        <v>8888</v>
       </c>
       <c r="D156" t="n">
-        <v>1780.93</v>
+        <v>926.97</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3409,17 +3409,17 @@
         <v>46218</v>
       </c>
       <c r="B157" t="n">
-        <v>525</v>
+        <v>132</v>
       </c>
       <c r="C157" t="n">
         <v>8888</v>
       </c>
       <c r="D157" t="n">
-        <v>5658.57</v>
+        <v>6522.92</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3428,13 +3428,13 @@
         <v>46218</v>
       </c>
       <c r="B158" t="n">
-        <v>2641</v>
+        <v>619</v>
       </c>
       <c r="C158" t="n">
         <v>8888</v>
       </c>
       <c r="D158" t="n">
-        <v>1720.99</v>
+        <v>2912.89</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -3447,17 +3447,17 @@
         <v>46218</v>
       </c>
       <c r="B159" t="n">
-        <v>2697</v>
+        <v>2769</v>
       </c>
       <c r="C159" t="n">
-        <v>8888</v>
+        <v>977</v>
       </c>
       <c r="D159" t="n">
-        <v>418.65</v>
+        <v>1116.56</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3466,17 +3466,17 @@
         <v>46218</v>
       </c>
       <c r="B160" t="n">
-        <v>2472</v>
+        <v>452</v>
       </c>
       <c r="C160" t="n">
-        <v>2853</v>
+        <v>8888</v>
       </c>
       <c r="D160" t="n">
-        <v>1402.64</v>
+        <v>608.78</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3485,17 +3485,17 @@
         <v>46218</v>
       </c>
       <c r="B161" t="n">
-        <v>58</v>
+        <v>2463</v>
       </c>
       <c r="C161" t="n">
         <v>8888</v>
       </c>
       <c r="D161" t="n">
-        <v>1123.87</v>
+        <v>363.69</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3504,17 +3504,17 @@
         <v>46218</v>
       </c>
       <c r="B162" t="n">
-        <v>358</v>
+        <v>1293</v>
       </c>
       <c r="C162" t="n">
-        <v>8888</v>
+        <v>1281</v>
       </c>
       <c r="D162" t="n">
-        <v>1675.95</v>
+        <v>1780.93</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3523,17 +3523,17 @@
         <v>46218</v>
       </c>
       <c r="B163" t="n">
-        <v>2431</v>
+        <v>525</v>
       </c>
       <c r="C163" t="n">
         <v>8888</v>
       </c>
       <c r="D163" t="n">
-        <v>266.89</v>
+        <v>5658.57</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3542,13 +3542,13 @@
         <v>46218</v>
       </c>
       <c r="B164" t="n">
-        <v>285</v>
+        <v>2641</v>
       </c>
       <c r="C164" t="n">
         <v>8888</v>
       </c>
       <c r="D164" t="n">
-        <v>5673.85</v>
+        <v>1720.99</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -3561,17 +3561,17 @@
         <v>46218</v>
       </c>
       <c r="B165" t="n">
-        <v>1102</v>
+        <v>58</v>
       </c>
       <c r="C165" t="n">
         <v>8888</v>
       </c>
       <c r="D165" t="n">
-        <v>1119.32</v>
+        <v>4929.8</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3580,17 +3580,17 @@
         <v>46218</v>
       </c>
       <c r="B166" t="n">
-        <v>2793</v>
+        <v>325</v>
       </c>
       <c r="C166" t="n">
-        <v>8888</v>
+        <v>1098</v>
       </c>
       <c r="D166" t="n">
-        <v>1238.11</v>
+        <v>50.06</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3599,17 +3599,17 @@
         <v>46218</v>
       </c>
       <c r="B167" t="n">
-        <v>626</v>
+        <v>2697</v>
       </c>
       <c r="C167" t="n">
         <v>8888</v>
       </c>
       <c r="D167" t="n">
-        <v>12556.19</v>
+        <v>418.65</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3618,13 +3618,13 @@
         <v>46218</v>
       </c>
       <c r="B168" t="n">
-        <v>1137</v>
+        <v>2472</v>
       </c>
       <c r="C168" t="n">
-        <v>2220</v>
+        <v>2853</v>
       </c>
       <c r="D168" t="n">
-        <v>1370.86</v>
+        <v>1402.64</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -3637,17 +3637,17 @@
         <v>46218</v>
       </c>
       <c r="B169" t="n">
-        <v>1289</v>
+        <v>358</v>
       </c>
       <c r="C169" t="n">
         <v>8888</v>
       </c>
       <c r="D169" t="n">
-        <v>5565.44</v>
+        <v>1675.95</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3656,17 +3656,17 @@
         <v>46218</v>
       </c>
       <c r="B170" t="n">
-        <v>2686</v>
+        <v>2431</v>
       </c>
       <c r="C170" t="n">
-        <v>1929</v>
+        <v>8888</v>
       </c>
       <c r="D170" t="n">
-        <v>2066.36</v>
+        <v>266.89</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3675,17 +3675,17 @@
         <v>46218</v>
       </c>
       <c r="B171" t="n">
-        <v>629</v>
+        <v>285</v>
       </c>
       <c r="C171" t="n">
         <v>8888</v>
       </c>
       <c r="D171" t="n">
-        <v>5212.76</v>
+        <v>5673.85</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3694,17 +3694,17 @@
         <v>46218</v>
       </c>
       <c r="B172" t="n">
-        <v>2584</v>
+        <v>1102</v>
       </c>
       <c r="C172" t="n">
         <v>8888</v>
       </c>
       <c r="D172" t="n">
-        <v>5635.67</v>
+        <v>2301.43</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3713,13 +3713,13 @@
         <v>46218</v>
       </c>
       <c r="B173" t="n">
-        <v>1756</v>
+        <v>2793</v>
       </c>
       <c r="C173" t="n">
         <v>8888</v>
       </c>
       <c r="D173" t="n">
-        <v>2201.67</v>
+        <v>1238.11</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -3732,17 +3732,17 @@
         <v>46218</v>
       </c>
       <c r="B174" t="n">
-        <v>1756</v>
+        <v>626</v>
       </c>
       <c r="C174" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D174" t="n">
-        <v>5078.1</v>
+        <v>12556.19</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3751,17 +3751,17 @@
         <v>46218</v>
       </c>
       <c r="B175" t="n">
-        <v>2651</v>
+        <v>424</v>
       </c>
       <c r="C175" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D175" t="n">
-        <v>363.7</v>
+        <v>1124.8</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3770,17 +3770,17 @@
         <v>46218</v>
       </c>
       <c r="B176" t="n">
-        <v>664</v>
+        <v>1137</v>
       </c>
       <c r="C176" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D176" t="n">
-        <v>5672.57</v>
+        <v>1370.86</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3789,17 +3789,17 @@
         <v>46218</v>
       </c>
       <c r="B177" t="n">
-        <v>360</v>
+        <v>1299</v>
       </c>
       <c r="C177" t="n">
-        <v>8888</v>
+        <v>2522</v>
       </c>
       <c r="D177" t="n">
-        <v>1594.84</v>
+        <v>8881.309999999999</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3808,17 +3808,17 @@
         <v>46218</v>
       </c>
       <c r="B178" t="n">
-        <v>2582</v>
+        <v>1289</v>
       </c>
       <c r="C178" t="n">
         <v>8888</v>
       </c>
       <c r="D178" t="n">
-        <v>379.33</v>
+        <v>5565.44</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3827,17 +3827,17 @@
         <v>46218</v>
       </c>
       <c r="B179" t="n">
-        <v>636</v>
+        <v>2686</v>
       </c>
       <c r="C179" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D179" t="n">
-        <v>2447.56</v>
+        <v>2066.36</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3846,13 +3846,13 @@
         <v>46218</v>
       </c>
       <c r="B180" t="n">
-        <v>1254</v>
+        <v>629</v>
       </c>
       <c r="C180" t="n">
         <v>8888</v>
       </c>
       <c r="D180" t="n">
-        <v>2643.22</v>
+        <v>5212.76</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -3865,17 +3865,17 @@
         <v>46218</v>
       </c>
       <c r="B181" t="n">
-        <v>2726</v>
+        <v>2584</v>
       </c>
       <c r="C181" t="n">
-        <v>977</v>
+        <v>8888</v>
       </c>
       <c r="D181" t="n">
-        <v>586.0599999999999</v>
+        <v>5635.67</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3884,17 +3884,17 @@
         <v>46218</v>
       </c>
       <c r="B182" t="n">
-        <v>2015</v>
+        <v>1756</v>
       </c>
       <c r="C182" t="n">
         <v>8888</v>
       </c>
       <c r="D182" t="n">
-        <v>315.69</v>
+        <v>3242.54</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3903,17 +3903,17 @@
         <v>46218</v>
       </c>
       <c r="B183" t="n">
-        <v>1064</v>
+        <v>1756</v>
       </c>
       <c r="C183" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D183" t="n">
-        <v>1274.3</v>
+        <v>5078.1</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3922,17 +3922,17 @@
         <v>46218</v>
       </c>
       <c r="B184" t="n">
-        <v>2698</v>
+        <v>2651</v>
       </c>
       <c r="C184" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D184" t="n">
-        <v>552.15</v>
+        <v>363.7</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3941,17 +3941,17 @@
         <v>46218</v>
       </c>
       <c r="B185" t="n">
-        <v>2641</v>
+        <v>664</v>
       </c>
       <c r="C185" t="n">
         <v>8888</v>
       </c>
       <c r="D185" t="n">
-        <v>820</v>
+        <v>6478.17</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3960,17 +3960,17 @@
         <v>46218</v>
       </c>
       <c r="B186" t="n">
-        <v>429</v>
+        <v>360</v>
       </c>
       <c r="C186" t="n">
         <v>8888</v>
       </c>
       <c r="D186" t="n">
-        <v>2593.49</v>
+        <v>1594.84</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3979,17 +3979,17 @@
         <v>46218</v>
       </c>
       <c r="B187" t="n">
-        <v>1301</v>
+        <v>2582</v>
       </c>
       <c r="C187" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D187" t="n">
-        <v>750.66</v>
+        <v>379.33</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3998,13 +3998,13 @@
         <v>46218</v>
       </c>
       <c r="B188" t="n">
-        <v>816</v>
+        <v>636</v>
       </c>
       <c r="C188" t="n">
         <v>8888</v>
       </c>
       <c r="D188" t="n">
-        <v>438.24</v>
+        <v>2447.56</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -4017,13 +4017,13 @@
         <v>46218</v>
       </c>
       <c r="B189" t="n">
-        <v>2359</v>
+        <v>1254</v>
       </c>
       <c r="C189" t="n">
         <v>8888</v>
       </c>
       <c r="D189" t="n">
-        <v>381.95</v>
+        <v>2643.22</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -4036,13 +4036,13 @@
         <v>46218</v>
       </c>
       <c r="B190" t="n">
-        <v>2251</v>
+        <v>2726</v>
       </c>
       <c r="C190" t="n">
-        <v>3403</v>
+        <v>977</v>
       </c>
       <c r="D190" t="n">
-        <v>802.08</v>
+        <v>586.0599999999999</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -4055,17 +4055,17 @@
         <v>46218</v>
       </c>
       <c r="B191" t="n">
-        <v>285</v>
+        <v>2015</v>
       </c>
       <c r="C191" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D191" t="n">
-        <v>364.99</v>
+        <v>315.69</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4074,13 +4074,13 @@
         <v>46218</v>
       </c>
       <c r="B192" t="n">
-        <v>2114</v>
+        <v>1064</v>
       </c>
       <c r="C192" t="n">
         <v>8888</v>
       </c>
       <c r="D192" t="n">
-        <v>2726.04</v>
+        <v>1274.3</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -4093,17 +4093,17 @@
         <v>46218</v>
       </c>
       <c r="B193" t="n">
-        <v>953</v>
+        <v>2698</v>
       </c>
       <c r="C193" t="n">
         <v>8888</v>
       </c>
       <c r="D193" t="n">
-        <v>2889.63</v>
+        <v>552.15</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4112,13 +4112,13 @@
         <v>46218</v>
       </c>
       <c r="B194" t="n">
-        <v>1102</v>
+        <v>2641</v>
       </c>
       <c r="C194" t="n">
         <v>8888</v>
       </c>
       <c r="D194" t="n">
-        <v>4637.07</v>
+        <v>820</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -4131,17 +4131,17 @@
         <v>46218</v>
       </c>
       <c r="B195" t="n">
-        <v>1465</v>
+        <v>429</v>
       </c>
       <c r="C195" t="n">
         <v>8888</v>
       </c>
       <c r="D195" t="n">
-        <v>4281.39</v>
+        <v>2593.49</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4150,17 +4150,17 @@
         <v>46218</v>
       </c>
       <c r="B196" t="n">
-        <v>619</v>
+        <v>1301</v>
       </c>
       <c r="C196" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D196" t="n">
-        <v>2021.67</v>
+        <v>750.66</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4169,17 +4169,17 @@
         <v>46218</v>
       </c>
       <c r="B197" t="n">
-        <v>2716</v>
+        <v>816</v>
       </c>
       <c r="C197" t="n">
         <v>8888</v>
       </c>
       <c r="D197" t="n">
-        <v>1063.42</v>
+        <v>438.24</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4188,17 +4188,17 @@
         <v>46218</v>
       </c>
       <c r="B198" t="n">
-        <v>2767</v>
+        <v>2359</v>
       </c>
       <c r="C198" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D198" t="n">
-        <v>1135.64</v>
+        <v>381.95</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4207,17 +4207,17 @@
         <v>46218</v>
       </c>
       <c r="B199" t="n">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="C199" t="n">
-        <v>8888</v>
+        <v>3403</v>
       </c>
       <c r="D199" t="n">
-        <v>764.66</v>
+        <v>802.08</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4226,17 +4226,17 @@
         <v>46218</v>
       </c>
       <c r="B200" t="n">
-        <v>2197</v>
+        <v>285</v>
       </c>
       <c r="C200" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D200" t="n">
-        <v>1085.45</v>
+        <v>1797.95</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4245,17 +4245,17 @@
         <v>46218</v>
       </c>
       <c r="B201" t="n">
-        <v>1064</v>
+        <v>2114</v>
       </c>
       <c r="C201" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D201" t="n">
-        <v>574.7</v>
+        <v>2726.04</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4264,17 +4264,17 @@
         <v>46218</v>
       </c>
       <c r="B202" t="n">
-        <v>2657</v>
+        <v>953</v>
       </c>
       <c r="C202" t="n">
         <v>8888</v>
       </c>
       <c r="D202" t="n">
-        <v>2683.06</v>
+        <v>2889.63</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4283,17 +4283,17 @@
         <v>46218</v>
       </c>
       <c r="B203" t="n">
-        <v>451</v>
+        <v>1102</v>
       </c>
       <c r="C203" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D203" t="n">
-        <v>2091.77</v>
+        <v>6347.79</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4302,17 +4302,17 @@
         <v>46218</v>
       </c>
       <c r="B204" t="n">
-        <v>1116</v>
+        <v>1465</v>
       </c>
       <c r="C204" t="n">
-        <v>13148</v>
+        <v>8888</v>
       </c>
       <c r="D204" t="n">
-        <v>207.91</v>
+        <v>4281.39</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4321,17 +4321,17 @@
         <v>46218</v>
       </c>
       <c r="B205" t="n">
-        <v>1277</v>
+        <v>619</v>
       </c>
       <c r="C205" t="n">
         <v>8888</v>
       </c>
       <c r="D205" t="n">
-        <v>1949</v>
+        <v>2021.67</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4340,17 +4340,17 @@
         <v>46218</v>
       </c>
       <c r="B206" t="n">
-        <v>131</v>
+        <v>2716</v>
       </c>
       <c r="C206" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D206" t="n">
-        <v>3850.09</v>
+        <v>1063.42</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4359,17 +4359,17 @@
         <v>46218</v>
       </c>
       <c r="B207" t="n">
-        <v>2692</v>
+        <v>2767</v>
       </c>
       <c r="C207" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D207" t="n">
-        <v>731.28</v>
+        <v>1135.64</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4378,13 +4378,13 @@
         <v>46218</v>
       </c>
       <c r="B208" t="n">
-        <v>1632</v>
+        <v>2657</v>
       </c>
       <c r="C208" t="n">
         <v>8888</v>
       </c>
       <c r="D208" t="n">
-        <v>7519.7</v>
+        <v>3149.7</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -4397,17 +4397,17 @@
         <v>46218</v>
       </c>
       <c r="B209" t="n">
-        <v>1317</v>
+        <v>2245</v>
       </c>
       <c r="C209" t="n">
-        <v>3179</v>
+        <v>8888</v>
       </c>
       <c r="D209" t="n">
-        <v>991.6799999999999</v>
+        <v>764.66</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4416,17 +4416,17 @@
         <v>46218</v>
       </c>
       <c r="B210" t="n">
-        <v>1993</v>
+        <v>2197</v>
       </c>
       <c r="C210" t="n">
         <v>8888</v>
       </c>
       <c r="D210" t="n">
-        <v>2875.39</v>
+        <v>1085.45</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4435,13 +4435,13 @@
         <v>46218</v>
       </c>
       <c r="B211" t="n">
-        <v>1890</v>
+        <v>1064</v>
       </c>
       <c r="C211" t="n">
-        <v>3449</v>
+        <v>27</v>
       </c>
       <c r="D211" t="n">
-        <v>6313.56</v>
+        <v>574.7</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -4454,17 +4454,17 @@
         <v>46218</v>
       </c>
       <c r="B212" t="n">
-        <v>1800</v>
+        <v>451</v>
       </c>
       <c r="C212" t="n">
-        <v>8888</v>
+        <v>3403</v>
       </c>
       <c r="D212" t="n">
-        <v>430.37</v>
+        <v>2091.77</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4473,17 +4473,17 @@
         <v>46218</v>
       </c>
       <c r="B213" t="n">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C213" t="n">
-        <v>8888</v>
+        <v>13148</v>
       </c>
       <c r="D213" t="n">
-        <v>672.47</v>
+        <v>1455.21</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4492,17 +4492,17 @@
         <v>46218</v>
       </c>
       <c r="B214" t="n">
-        <v>2749</v>
+        <v>1277</v>
       </c>
       <c r="C214" t="n">
         <v>8888</v>
       </c>
       <c r="D214" t="n">
-        <v>1860.64</v>
+        <v>1949</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4511,17 +4511,17 @@
         <v>46218</v>
       </c>
       <c r="B215" t="n">
-        <v>42</v>
+        <v>131</v>
       </c>
       <c r="C215" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D215" t="n">
-        <v>280.05</v>
+        <v>3850.09</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4530,13 +4530,13 @@
         <v>46218</v>
       </c>
       <c r="B216" t="n">
-        <v>1478</v>
+        <v>2692</v>
       </c>
       <c r="C216" t="n">
         <v>8888</v>
       </c>
       <c r="D216" t="n">
-        <v>875.34</v>
+        <v>731.28</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -4549,13 +4549,13 @@
         <v>46218</v>
       </c>
       <c r="B217" t="n">
-        <v>2491</v>
+        <v>1632</v>
       </c>
       <c r="C217" t="n">
         <v>8888</v>
       </c>
       <c r="D217" t="n">
-        <v>650.4299999999999</v>
+        <v>7519.7</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -4568,17 +4568,17 @@
         <v>46218</v>
       </c>
       <c r="B218" t="n">
-        <v>353</v>
+        <v>1317</v>
       </c>
       <c r="C218" t="n">
-        <v>8888</v>
+        <v>3179</v>
       </c>
       <c r="D218" t="n">
-        <v>653.13</v>
+        <v>991.6799999999999</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4587,13 +4587,13 @@
         <v>46218</v>
       </c>
       <c r="B219" t="n">
-        <v>2015</v>
+        <v>1993</v>
       </c>
       <c r="C219" t="n">
         <v>8888</v>
       </c>
       <c r="D219" t="n">
-        <v>4436.15</v>
+        <v>3508.59</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -4606,17 +4606,17 @@
         <v>46218</v>
       </c>
       <c r="B220" t="n">
-        <v>559</v>
+        <v>1890</v>
       </c>
       <c r="C220" t="n">
-        <v>8888</v>
+        <v>3449</v>
       </c>
       <c r="D220" t="n">
-        <v>1453.53</v>
+        <v>6313.56</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4625,17 +4625,17 @@
         <v>46218</v>
       </c>
       <c r="B221" t="n">
-        <v>1890</v>
+        <v>1800</v>
       </c>
       <c r="C221" t="n">
-        <v>1953</v>
+        <v>8888</v>
       </c>
       <c r="D221" t="n">
-        <v>1674.57</v>
+        <v>430.37</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4644,17 +4644,17 @@
         <v>46218</v>
       </c>
       <c r="B222" t="n">
-        <v>1317</v>
+        <v>1117</v>
       </c>
       <c r="C222" t="n">
         <v>8888</v>
       </c>
       <c r="D222" t="n">
-        <v>1626.02</v>
+        <v>672.47</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4663,17 +4663,17 @@
         <v>46218</v>
       </c>
       <c r="B223" t="n">
-        <v>2782</v>
+        <v>2749</v>
       </c>
       <c r="C223" t="n">
         <v>8888</v>
       </c>
       <c r="D223" t="n">
-        <v>1786.32</v>
+        <v>1860.64</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4682,13 +4682,13 @@
         <v>46218</v>
       </c>
       <c r="B224" t="n">
-        <v>953</v>
+        <v>42</v>
       </c>
       <c r="C224" t="n">
         <v>8888</v>
       </c>
       <c r="D224" t="n">
-        <v>364.44</v>
+        <v>280.05</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -4701,17 +4701,17 @@
         <v>46218</v>
       </c>
       <c r="B225" t="n">
-        <v>2251</v>
+        <v>1478</v>
       </c>
       <c r="C225" t="n">
         <v>8888</v>
       </c>
       <c r="D225" t="n">
-        <v>989.26</v>
+        <v>875.34</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4720,17 +4720,17 @@
         <v>46218</v>
       </c>
       <c r="B226" t="n">
-        <v>483</v>
+        <v>2491</v>
       </c>
       <c r="C226" t="n">
-        <v>841</v>
+        <v>8888</v>
       </c>
       <c r="D226" t="n">
-        <v>2085.09</v>
+        <v>650.4299999999999</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4739,17 +4739,17 @@
         <v>46218</v>
       </c>
       <c r="B227" t="n">
-        <v>2133</v>
+        <v>353</v>
       </c>
       <c r="C227" t="n">
-        <v>213</v>
+        <v>8888</v>
       </c>
       <c r="D227" t="n">
-        <v>526.8</v>
+        <v>653.13</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4758,17 +4758,17 @@
         <v>46218</v>
       </c>
       <c r="B228" t="n">
-        <v>351</v>
+        <v>2015</v>
       </c>
       <c r="C228" t="n">
-        <v>3009</v>
+        <v>8888</v>
       </c>
       <c r="D228" t="n">
-        <v>416.36</v>
+        <v>4436.15</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4777,17 +4777,17 @@
         <v>46218</v>
       </c>
       <c r="B229" t="n">
-        <v>2250</v>
+        <v>559</v>
       </c>
       <c r="C229" t="n">
         <v>8888</v>
       </c>
       <c r="D229" t="n">
-        <v>709.46</v>
+        <v>3838.57</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4796,17 +4796,17 @@
         <v>46218</v>
       </c>
       <c r="B230" t="n">
-        <v>2648</v>
+        <v>1890</v>
       </c>
       <c r="C230" t="n">
-        <v>8888</v>
+        <v>1953</v>
       </c>
       <c r="D230" t="n">
-        <v>1873.52</v>
+        <v>1674.57</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4815,13 +4815,13 @@
         <v>46218</v>
       </c>
       <c r="B231" t="n">
-        <v>131</v>
+        <v>1317</v>
       </c>
       <c r="C231" t="n">
         <v>8888</v>
       </c>
       <c r="D231" t="n">
-        <v>1369.91</v>
+        <v>1626.02</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -4834,17 +4834,17 @@
         <v>46218</v>
       </c>
       <c r="B232" t="n">
-        <v>2790</v>
+        <v>2782</v>
       </c>
       <c r="C232" t="n">
-        <v>1953</v>
+        <v>8888</v>
       </c>
       <c r="D232" t="n">
-        <v>371.88</v>
+        <v>1786.32</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4853,17 +4853,17 @@
         <v>46218</v>
       </c>
       <c r="B233" t="n">
-        <v>363</v>
+        <v>953</v>
       </c>
       <c r="C233" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D233" t="n">
-        <v>635.1</v>
+        <v>364.44</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4872,17 +4872,17 @@
         <v>46218</v>
       </c>
       <c r="B234" t="n">
-        <v>2716</v>
+        <v>2251</v>
       </c>
       <c r="C234" t="n">
-        <v>1929</v>
+        <v>8888</v>
       </c>
       <c r="D234" t="n">
-        <v>1073.33</v>
+        <v>989.26</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4891,13 +4891,13 @@
         <v>46218</v>
       </c>
       <c r="B235" t="n">
-        <v>2298</v>
+        <v>483</v>
       </c>
       <c r="C235" t="n">
-        <v>675</v>
+        <v>841</v>
       </c>
       <c r="D235" t="n">
-        <v>401.85</v>
+        <v>2564.59</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -4910,13 +4910,13 @@
         <v>46218</v>
       </c>
       <c r="B236" t="n">
-        <v>2639</v>
+        <v>2133</v>
       </c>
       <c r="C236" t="n">
-        <v>1953</v>
+        <v>213</v>
       </c>
       <c r="D236" t="n">
-        <v>504.09</v>
+        <v>526.8</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -4929,13 +4929,13 @@
         <v>46218</v>
       </c>
       <c r="B237" t="n">
-        <v>619</v>
+        <v>351</v>
       </c>
       <c r="C237" t="n">
-        <v>1139</v>
+        <v>3009</v>
       </c>
       <c r="D237" t="n">
-        <v>1341.64</v>
+        <v>416.36</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -4948,17 +4948,17 @@
         <v>46218</v>
       </c>
       <c r="B238" t="n">
-        <v>2109</v>
+        <v>2250</v>
       </c>
       <c r="C238" t="n">
         <v>8888</v>
       </c>
       <c r="D238" t="n">
-        <v>2293.78</v>
+        <v>709.46</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4967,17 +4967,17 @@
         <v>46218</v>
       </c>
       <c r="B239" t="n">
-        <v>1116</v>
+        <v>2648</v>
       </c>
       <c r="C239" t="n">
         <v>8888</v>
       </c>
       <c r="D239" t="n">
-        <v>2919.53</v>
+        <v>1873.52</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4986,17 +4986,17 @@
         <v>46218</v>
       </c>
       <c r="B240" t="n">
-        <v>2250</v>
+        <v>131</v>
       </c>
       <c r="C240" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D240" t="n">
-        <v>1803.76</v>
+        <v>1369.91</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -5005,13 +5005,13 @@
         <v>46218</v>
       </c>
       <c r="B241" t="n">
-        <v>2698</v>
+        <v>2298</v>
       </c>
       <c r="C241" t="n">
-        <v>874</v>
+        <v>675</v>
       </c>
       <c r="D241" t="n">
-        <v>1230.43</v>
+        <v>2301.31</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -5024,17 +5024,17 @@
         <v>46218</v>
       </c>
       <c r="B242" t="n">
-        <v>42</v>
+        <v>2790</v>
       </c>
       <c r="C242" t="n">
-        <v>8888</v>
+        <v>1953</v>
       </c>
       <c r="D242" t="n">
-        <v>79947.14999999999</v>
+        <v>371.88</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -5043,17 +5043,17 @@
         <v>46218</v>
       </c>
       <c r="B243" t="n">
-        <v>772</v>
+        <v>363</v>
       </c>
       <c r="C243" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D243" t="n">
-        <v>400.25</v>
+        <v>635.1</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -5062,17 +5062,17 @@
         <v>46218</v>
       </c>
       <c r="B244" t="n">
-        <v>2728</v>
+        <v>2716</v>
       </c>
       <c r="C244" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D244" t="n">
-        <v>1397.07</v>
+        <v>1073.33</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -5081,13 +5081,13 @@
         <v>46218</v>
       </c>
       <c r="B245" t="n">
-        <v>2197</v>
+        <v>2639</v>
       </c>
       <c r="C245" t="n">
-        <v>423</v>
+        <v>1953</v>
       </c>
       <c r="D245" t="n">
-        <v>2267.61</v>
+        <v>504.09</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -5100,13 +5100,13 @@
         <v>46218</v>
       </c>
       <c r="B246" t="n">
-        <v>2716</v>
+        <v>629</v>
       </c>
       <c r="C246" t="n">
-        <v>977</v>
+        <v>675</v>
       </c>
       <c r="D246" t="n">
-        <v>729.29</v>
+        <v>2419.73</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -5119,17 +5119,17 @@
         <v>46218</v>
       </c>
       <c r="B247" t="n">
-        <v>1993</v>
+        <v>619</v>
       </c>
       <c r="C247" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D247" t="n">
-        <v>456.62</v>
+        <v>1341.64</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -5138,17 +5138,188 @@
         <v>46218</v>
       </c>
       <c r="B248" t="n">
-        <v>629</v>
+        <v>2109</v>
       </c>
       <c r="C248" t="n">
-        <v>675</v>
+        <v>8888</v>
       </c>
       <c r="D248" t="n">
-        <v>1054.76</v>
+        <v>2293.78</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B249" t="n">
+        <v>1116</v>
+      </c>
+      <c r="C249" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D249" t="n">
+        <v>2919.53</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B250" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C250" t="n">
+        <v>27</v>
+      </c>
+      <c r="D250" t="n">
+        <v>1803.76</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B251" t="n">
+        <v>2698</v>
+      </c>
+      <c r="C251" t="n">
+        <v>874</v>
+      </c>
+      <c r="D251" t="n">
+        <v>1230.43</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B252" t="n">
+        <v>42</v>
+      </c>
+      <c r="C252" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D252" t="n">
+        <v>79947.14999999999</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B253" t="n">
+        <v>772</v>
+      </c>
+      <c r="C253" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D253" t="n">
+        <v>400.25</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B254" t="n">
+        <v>2728</v>
+      </c>
+      <c r="C254" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D254" t="n">
+        <v>1397.07</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B255" t="n">
+        <v>2197</v>
+      </c>
+      <c r="C255" t="n">
+        <v>423</v>
+      </c>
+      <c r="D255" t="n">
+        <v>2267.61</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B256" t="n">
+        <v>2716</v>
+      </c>
+      <c r="C256" t="n">
+        <v>977</v>
+      </c>
+      <c r="D256" t="n">
+        <v>729.29</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B257" t="n">
+        <v>1993</v>
+      </c>
+      <c r="C257" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D257" t="n">
+        <v>456.62</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E257"/>
+  <dimension ref="A1:E267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,7 +489,7 @@
         <v>8888</v>
       </c>
       <c r="D3" t="n">
-        <v>651.77</v>
+        <v>769.05</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -673,13 +673,13 @@
         <v>46218</v>
       </c>
       <c r="B13" t="n">
-        <v>2211</v>
+        <v>2118</v>
       </c>
       <c r="C13" t="n">
         <v>8888</v>
       </c>
       <c r="D13" t="n">
-        <v>2706.2</v>
+        <v>5847.19</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -692,13 +692,13 @@
         <v>46218</v>
       </c>
       <c r="B14" t="n">
-        <v>2660</v>
+        <v>2211</v>
       </c>
       <c r="C14" t="n">
         <v>8888</v>
       </c>
       <c r="D14" t="n">
-        <v>875.61</v>
+        <v>2706.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -711,13 +711,13 @@
         <v>46218</v>
       </c>
       <c r="B15" t="n">
-        <v>890</v>
+        <v>2660</v>
       </c>
       <c r="C15" t="n">
         <v>8888</v>
       </c>
       <c r="D15" t="n">
-        <v>1051.23</v>
+        <v>875.61</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -730,13 +730,13 @@
         <v>46218</v>
       </c>
       <c r="B16" t="n">
-        <v>2190</v>
+        <v>890</v>
       </c>
       <c r="C16" t="n">
         <v>8888</v>
       </c>
       <c r="D16" t="n">
-        <v>1307.13</v>
+        <v>1051.23</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -749,17 +749,17 @@
         <v>46218</v>
       </c>
       <c r="B17" t="n">
-        <v>2651</v>
+        <v>2190</v>
       </c>
       <c r="C17" t="n">
         <v>8888</v>
       </c>
       <c r="D17" t="n">
-        <v>660.95</v>
+        <v>1307.13</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -768,17 +768,17 @@
         <v>46218</v>
       </c>
       <c r="B18" t="n">
-        <v>890</v>
+        <v>2651</v>
       </c>
       <c r="C18" t="n">
-        <v>1533</v>
+        <v>8888</v>
       </c>
       <c r="D18" t="n">
-        <v>898.83</v>
+        <v>660.95</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
         <v>46218</v>
       </c>
       <c r="B19" t="n">
-        <v>40</v>
+        <v>890</v>
       </c>
       <c r="C19" t="n">
-        <v>8888</v>
+        <v>1533</v>
       </c>
       <c r="D19" t="n">
-        <v>768.78</v>
+        <v>898.83</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -806,17 +806,17 @@
         <v>46218</v>
       </c>
       <c r="B20" t="n">
-        <v>2118</v>
+        <v>40</v>
       </c>
       <c r="C20" t="n">
         <v>8888</v>
       </c>
       <c r="D20" t="n">
-        <v>5535.71</v>
+        <v>768.78</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -977,13 +977,13 @@
         <v>46218</v>
       </c>
       <c r="B29" t="n">
-        <v>2250</v>
+        <v>2767</v>
       </c>
       <c r="C29" t="n">
         <v>8888</v>
       </c>
       <c r="D29" t="n">
-        <v>1686.37</v>
+        <v>1866.38</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -996,17 +996,17 @@
         <v>46218</v>
       </c>
       <c r="B30" t="n">
-        <v>2695</v>
+        <v>2250</v>
       </c>
       <c r="C30" t="n">
         <v>8888</v>
       </c>
       <c r="D30" t="n">
-        <v>677.6799999999999</v>
+        <v>1686.37</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1015,17 +1015,17 @@
         <v>46218</v>
       </c>
       <c r="B31" t="n">
-        <v>931</v>
+        <v>2695</v>
       </c>
       <c r="C31" t="n">
-        <v>423</v>
+        <v>8888</v>
       </c>
       <c r="D31" t="n">
-        <v>492.34</v>
+        <v>677.6799999999999</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
         <v>46218</v>
       </c>
       <c r="B32" t="n">
-        <v>1117</v>
+        <v>931</v>
       </c>
       <c r="C32" t="n">
-        <v>8888</v>
+        <v>423</v>
       </c>
       <c r="D32" t="n">
-        <v>540.15</v>
+        <v>492.34</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1053,13 +1053,13 @@
         <v>46218</v>
       </c>
       <c r="B33" t="n">
-        <v>2641</v>
+        <v>1117</v>
       </c>
       <c r="C33" t="n">
         <v>8888</v>
       </c>
       <c r="D33" t="n">
-        <v>2527.79</v>
+        <v>540.15</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1110,13 +1110,13 @@
         <v>46218</v>
       </c>
       <c r="B36" t="n">
-        <v>525</v>
+        <v>2641</v>
       </c>
       <c r="C36" t="n">
         <v>8888</v>
       </c>
       <c r="D36" t="n">
-        <v>408.25</v>
+        <v>2527.79</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1129,17 +1129,17 @@
         <v>46218</v>
       </c>
       <c r="B37" t="n">
-        <v>1808</v>
+        <v>525</v>
       </c>
       <c r="C37" t="n">
         <v>8888</v>
       </c>
       <c r="D37" t="n">
-        <v>695.3200000000001</v>
+        <v>408.25</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1148,17 +1148,17 @@
         <v>46218</v>
       </c>
       <c r="B38" t="n">
-        <v>609</v>
+        <v>1808</v>
       </c>
       <c r="C38" t="n">
         <v>8888</v>
       </c>
       <c r="D38" t="n">
-        <v>1909.37</v>
+        <v>695.3200000000001</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1167,17 +1167,17 @@
         <v>46218</v>
       </c>
       <c r="B39" t="n">
-        <v>949</v>
+        <v>609</v>
       </c>
       <c r="C39" t="n">
-        <v>1134</v>
+        <v>8888</v>
       </c>
       <c r="D39" t="n">
-        <v>30.46</v>
+        <v>1909.37</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1186,13 +1186,13 @@
         <v>46218</v>
       </c>
       <c r="B40" t="n">
-        <v>42</v>
+        <v>949</v>
       </c>
       <c r="C40" t="n">
-        <v>1139</v>
+        <v>1134</v>
       </c>
       <c r="D40" t="n">
-        <v>358.97</v>
+        <v>30.46</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1205,17 +1205,17 @@
         <v>46218</v>
       </c>
       <c r="B41" t="n">
-        <v>2499</v>
+        <v>42</v>
       </c>
       <c r="C41" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D41" t="n">
-        <v>1049.3</v>
+        <v>358.97</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1224,13 +1224,13 @@
         <v>46218</v>
       </c>
       <c r="B42" t="n">
-        <v>58</v>
+        <v>2499</v>
       </c>
       <c r="C42" t="n">
         <v>8888</v>
       </c>
       <c r="D42" t="n">
-        <v>2194.12</v>
+        <v>1049.3</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1243,13 +1243,13 @@
         <v>46218</v>
       </c>
       <c r="B43" t="n">
-        <v>2245</v>
+        <v>58</v>
       </c>
       <c r="C43" t="n">
         <v>8888</v>
       </c>
       <c r="D43" t="n">
-        <v>3382.78</v>
+        <v>2194.12</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1262,17 +1262,17 @@
         <v>46218</v>
       </c>
       <c r="B44" t="n">
-        <v>325</v>
+        <v>2245</v>
       </c>
       <c r="C44" t="n">
         <v>8888</v>
       </c>
       <c r="D44" t="n">
-        <v>1079.66</v>
+        <v>3382.78</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1281,17 +1281,17 @@
         <v>46218</v>
       </c>
       <c r="B45" t="n">
-        <v>2383</v>
+        <v>325</v>
       </c>
       <c r="C45" t="n">
         <v>8888</v>
       </c>
       <c r="D45" t="n">
-        <v>7926.02</v>
+        <v>1279.15</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1300,17 +1300,17 @@
         <v>46218</v>
       </c>
       <c r="B46" t="n">
-        <v>1117</v>
+        <v>2383</v>
       </c>
       <c r="C46" t="n">
-        <v>1139</v>
+        <v>8888</v>
       </c>
       <c r="D46" t="n">
-        <v>916.72</v>
+        <v>9004.809999999999</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1319,17 +1319,17 @@
         <v>46218</v>
       </c>
       <c r="B47" t="n">
-        <v>374</v>
+        <v>1117</v>
       </c>
       <c r="C47" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D47" t="n">
-        <v>2810.86</v>
+        <v>916.72</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1338,13 +1338,13 @@
         <v>46218</v>
       </c>
       <c r="B48" t="n">
-        <v>2279</v>
+        <v>374</v>
       </c>
       <c r="C48" t="n">
         <v>8888</v>
       </c>
       <c r="D48" t="n">
-        <v>712.66</v>
+        <v>2810.86</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1357,17 +1357,17 @@
         <v>46218</v>
       </c>
       <c r="B49" t="n">
-        <v>535</v>
+        <v>2279</v>
       </c>
       <c r="C49" t="n">
         <v>8888</v>
       </c>
       <c r="D49" t="n">
-        <v>5836.12</v>
+        <v>712.66</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1382,11 +1382,11 @@
         <v>8888</v>
       </c>
       <c r="D50" t="n">
-        <v>1352.51</v>
+        <v>9291.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1395,17 +1395,17 @@
         <v>46218</v>
       </c>
       <c r="B51" t="n">
-        <v>2678</v>
+        <v>535</v>
       </c>
       <c r="C51" t="n">
-        <v>1312</v>
+        <v>8888</v>
       </c>
       <c r="D51" t="n">
-        <v>364.96</v>
+        <v>1352.51</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1414,17 +1414,17 @@
         <v>46218</v>
       </c>
       <c r="B52" t="n">
-        <v>2345</v>
+        <v>2678</v>
       </c>
       <c r="C52" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D52" t="n">
-        <v>863.16</v>
+        <v>364.96</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1433,17 +1433,17 @@
         <v>46218</v>
       </c>
       <c r="B53" t="n">
-        <v>945</v>
+        <v>2345</v>
       </c>
       <c r="C53" t="n">
         <v>8888</v>
       </c>
       <c r="D53" t="n">
-        <v>27337.21</v>
+        <v>863.16</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PEDIDO ELETRÔNICO</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1452,17 +1452,17 @@
         <v>46218</v>
       </c>
       <c r="B54" t="n">
-        <v>2686</v>
+        <v>945</v>
       </c>
       <c r="C54" t="n">
         <v>8888</v>
       </c>
       <c r="D54" t="n">
-        <v>684.2</v>
+        <v>30706.36</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>PEDIDO ELETRÔNICO</t>
         </is>
       </c>
     </row>
@@ -1471,17 +1471,17 @@
         <v>46218</v>
       </c>
       <c r="B55" t="n">
-        <v>438</v>
+        <v>2686</v>
       </c>
       <c r="C55" t="n">
         <v>8888</v>
       </c>
       <c r="D55" t="n">
-        <v>220.06</v>
+        <v>684.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1490,17 +1490,17 @@
         <v>46218</v>
       </c>
       <c r="B56" t="n">
-        <v>1956</v>
+        <v>438</v>
       </c>
       <c r="C56" t="n">
         <v>8888</v>
       </c>
       <c r="D56" t="n">
-        <v>5311.01</v>
+        <v>220.06</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1509,17 +1509,17 @@
         <v>46218</v>
       </c>
       <c r="B57" t="n">
-        <v>664</v>
+        <v>1956</v>
       </c>
       <c r="C57" t="n">
         <v>8888</v>
       </c>
       <c r="D57" t="n">
-        <v>6275.01</v>
+        <v>5311.01</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1528,17 +1528,17 @@
         <v>46218</v>
       </c>
       <c r="B58" t="n">
-        <v>353</v>
+        <v>664</v>
       </c>
       <c r="C58" t="n">
-        <v>3179</v>
+        <v>8888</v>
       </c>
       <c r="D58" t="n">
-        <v>495.84</v>
+        <v>6275.01</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1547,17 +1547,17 @@
         <v>46218</v>
       </c>
       <c r="B59" t="n">
-        <v>1293</v>
+        <v>353</v>
       </c>
       <c r="C59" t="n">
-        <v>8888</v>
+        <v>3179</v>
       </c>
       <c r="D59" t="n">
-        <v>3129.07</v>
+        <v>495.84</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1566,13 +1566,13 @@
         <v>46218</v>
       </c>
       <c r="B60" t="n">
-        <v>2279</v>
+        <v>1293</v>
       </c>
       <c r="C60" t="n">
         <v>8888</v>
       </c>
       <c r="D60" t="n">
-        <v>3900.07</v>
+        <v>3129.07</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -1585,13 +1585,13 @@
         <v>46218</v>
       </c>
       <c r="B61" t="n">
-        <v>1937</v>
+        <v>2279</v>
       </c>
       <c r="C61" t="n">
         <v>8888</v>
       </c>
       <c r="D61" t="n">
-        <v>1685.72</v>
+        <v>3900.07</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -1604,17 +1604,17 @@
         <v>46218</v>
       </c>
       <c r="B62" t="n">
-        <v>941</v>
+        <v>1937</v>
       </c>
       <c r="C62" t="n">
         <v>8888</v>
       </c>
       <c r="D62" t="n">
-        <v>864.14</v>
+        <v>1685.72</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
         <v>46218</v>
       </c>
       <c r="B63" t="n">
-        <v>1137</v>
+        <v>941</v>
       </c>
       <c r="C63" t="n">
         <v>8888</v>
       </c>
       <c r="D63" t="n">
-        <v>1947.93</v>
+        <v>864.14</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1642,17 +1642,17 @@
         <v>46218</v>
       </c>
       <c r="B64" t="n">
-        <v>2631</v>
+        <v>1137</v>
       </c>
       <c r="C64" t="n">
-        <v>2853</v>
+        <v>8888</v>
       </c>
       <c r="D64" t="n">
-        <v>2418.28</v>
+        <v>3168.9</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1661,13 +1661,13 @@
         <v>46218</v>
       </c>
       <c r="B65" t="n">
-        <v>2793</v>
+        <v>2631</v>
       </c>
       <c r="C65" t="n">
-        <v>977</v>
+        <v>2853</v>
       </c>
       <c r="D65" t="n">
-        <v>1188.59</v>
+        <v>2418.28</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -1680,17 +1680,17 @@
         <v>46218</v>
       </c>
       <c r="B66" t="n">
-        <v>2802</v>
+        <v>2793</v>
       </c>
       <c r="C66" t="n">
-        <v>8888</v>
+        <v>977</v>
       </c>
       <c r="D66" t="n">
-        <v>1264.57</v>
+        <v>1188.59</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1699,13 +1699,13 @@
         <v>46218</v>
       </c>
       <c r="B67" t="n">
-        <v>451</v>
+        <v>2802</v>
       </c>
       <c r="C67" t="n">
         <v>8888</v>
       </c>
       <c r="D67" t="n">
-        <v>757.5700000000001</v>
+        <v>1264.57</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -1718,17 +1718,17 @@
         <v>46218</v>
       </c>
       <c r="B68" t="n">
-        <v>374</v>
+        <v>451</v>
       </c>
       <c r="C68" t="n">
         <v>8888</v>
       </c>
       <c r="D68" t="n">
-        <v>44.6</v>
+        <v>757.5700000000001</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1737,17 +1737,17 @@
         <v>46218</v>
       </c>
       <c r="B69" t="n">
-        <v>703</v>
+        <v>374</v>
       </c>
       <c r="C69" t="n">
         <v>8888</v>
       </c>
       <c r="D69" t="n">
-        <v>12155.46</v>
+        <v>44.6</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1756,17 +1756,17 @@
         <v>46218</v>
       </c>
       <c r="B70" t="n">
-        <v>1756</v>
+        <v>703</v>
       </c>
       <c r="C70" t="n">
         <v>8888</v>
       </c>
       <c r="D70" t="n">
-        <v>4416.47</v>
+        <v>12155.46</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1775,17 +1775,17 @@
         <v>46218</v>
       </c>
       <c r="B71" t="n">
-        <v>925</v>
+        <v>1756</v>
       </c>
       <c r="C71" t="n">
         <v>8888</v>
       </c>
       <c r="D71" t="n">
-        <v>651.59</v>
+        <v>4416.47</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1794,17 +1794,17 @@
         <v>46218</v>
       </c>
       <c r="B72" t="n">
-        <v>941</v>
+        <v>925</v>
       </c>
       <c r="C72" t="n">
-        <v>977</v>
+        <v>8888</v>
       </c>
       <c r="D72" t="n">
-        <v>359.73</v>
+        <v>651.59</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1813,17 +1813,17 @@
         <v>46218</v>
       </c>
       <c r="B73" t="n">
-        <v>2648</v>
+        <v>941</v>
       </c>
       <c r="C73" t="n">
-        <v>8888</v>
+        <v>977</v>
       </c>
       <c r="D73" t="n">
-        <v>1594.42</v>
+        <v>359.73</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1832,13 +1832,13 @@
         <v>46218</v>
       </c>
       <c r="B74" t="n">
-        <v>663</v>
+        <v>2648</v>
       </c>
       <c r="C74" t="n">
         <v>8888</v>
       </c>
       <c r="D74" t="n">
-        <v>6645.33</v>
+        <v>1594.42</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -1851,17 +1851,17 @@
         <v>46218</v>
       </c>
       <c r="B75" t="n">
-        <v>2714</v>
+        <v>663</v>
       </c>
       <c r="C75" t="n">
-        <v>519</v>
+        <v>8888</v>
       </c>
       <c r="D75" t="n">
-        <v>61939.22</v>
+        <v>6645.33</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1870,17 +1870,17 @@
         <v>46218</v>
       </c>
       <c r="B76" t="n">
-        <v>483</v>
+        <v>2714</v>
       </c>
       <c r="C76" t="n">
-        <v>8888</v>
+        <v>519</v>
       </c>
       <c r="D76" t="n">
-        <v>12405.46</v>
+        <v>61939.22</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1889,17 +1889,17 @@
         <v>46218</v>
       </c>
       <c r="B77" t="n">
-        <v>1075</v>
+        <v>483</v>
       </c>
       <c r="C77" t="n">
         <v>8888</v>
       </c>
       <c r="D77" t="n">
-        <v>11607.79</v>
+        <v>12405.46</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1908,13 +1908,13 @@
         <v>46218</v>
       </c>
       <c r="B78" t="n">
-        <v>629</v>
+        <v>1075</v>
       </c>
       <c r="C78" t="n">
         <v>8888</v>
       </c>
       <c r="D78" t="n">
-        <v>9233.719999999999</v>
+        <v>11607.79</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -1927,17 +1927,17 @@
         <v>46218</v>
       </c>
       <c r="B79" t="n">
-        <v>1983</v>
+        <v>629</v>
       </c>
       <c r="C79" t="n">
-        <v>841</v>
+        <v>8888</v>
       </c>
       <c r="D79" t="n">
-        <v>633.79</v>
+        <v>9233.719999999999</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1946,17 +1946,17 @@
         <v>46218</v>
       </c>
       <c r="B80" t="n">
-        <v>1137</v>
+        <v>1983</v>
       </c>
       <c r="C80" t="n">
-        <v>8888</v>
+        <v>841</v>
       </c>
       <c r="D80" t="n">
-        <v>3578.51</v>
+        <v>633.79</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1965,17 +1965,17 @@
         <v>46218</v>
       </c>
       <c r="B81" t="n">
-        <v>2651</v>
+        <v>1137</v>
       </c>
       <c r="C81" t="n">
         <v>8888</v>
       </c>
       <c r="D81" t="n">
-        <v>1296.58</v>
+        <v>4842.54</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1984,17 +1984,17 @@
         <v>46218</v>
       </c>
       <c r="B82" t="n">
-        <v>2789</v>
+        <v>2651</v>
       </c>
       <c r="C82" t="n">
         <v>8888</v>
       </c>
       <c r="D82" t="n">
-        <v>1293.93</v>
+        <v>1296.58</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2003,17 +2003,17 @@
         <v>46218</v>
       </c>
       <c r="B83" t="n">
-        <v>1956</v>
+        <v>2789</v>
       </c>
       <c r="C83" t="n">
-        <v>423</v>
+        <v>8888</v>
       </c>
       <c r="D83" t="n">
-        <v>1416.35</v>
+        <v>1293.93</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2022,17 +2022,17 @@
         <v>46218</v>
       </c>
       <c r="B84" t="n">
-        <v>2709</v>
+        <v>1956</v>
       </c>
       <c r="C84" t="n">
-        <v>8888</v>
+        <v>423</v>
       </c>
       <c r="D84" t="n">
-        <v>547.6900000000001</v>
+        <v>1416.35</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2041,13 +2041,13 @@
         <v>46218</v>
       </c>
       <c r="B85" t="n">
-        <v>1308</v>
+        <v>2709</v>
       </c>
       <c r="C85" t="n">
         <v>8888</v>
       </c>
       <c r="D85" t="n">
-        <v>1460.53</v>
+        <v>547.6900000000001</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -2060,17 +2060,17 @@
         <v>46218</v>
       </c>
       <c r="B86" t="n">
-        <v>2026</v>
+        <v>1308</v>
       </c>
       <c r="C86" t="n">
         <v>8888</v>
       </c>
       <c r="D86" t="n">
-        <v>2237.62</v>
+        <v>2264.86</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2079,13 +2079,13 @@
         <v>46218</v>
       </c>
       <c r="B87" t="n">
-        <v>2789</v>
+        <v>2026</v>
       </c>
       <c r="C87" t="n">
         <v>8888</v>
       </c>
       <c r="D87" t="n">
-        <v>747.77</v>
+        <v>2237.62</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -2098,17 +2098,17 @@
         <v>46218</v>
       </c>
       <c r="B88" t="n">
-        <v>89</v>
+        <v>2789</v>
       </c>
       <c r="C88" t="n">
-        <v>13148</v>
+        <v>8888</v>
       </c>
       <c r="D88" t="n">
-        <v>2842.03</v>
+        <v>747.77</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2117,17 +2117,17 @@
         <v>46218</v>
       </c>
       <c r="B89" t="n">
-        <v>1075</v>
+        <v>89</v>
       </c>
       <c r="C89" t="n">
-        <v>8888</v>
+        <v>13148</v>
       </c>
       <c r="D89" t="n">
-        <v>698.63</v>
+        <v>2842.03</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2136,17 +2136,17 @@
         <v>46218</v>
       </c>
       <c r="B90" t="n">
-        <v>2709</v>
+        <v>1075</v>
       </c>
       <c r="C90" t="n">
-        <v>2220</v>
+        <v>8888</v>
       </c>
       <c r="D90" t="n">
-        <v>390.19</v>
+        <v>698.63</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2155,17 +2155,17 @@
         <v>46218</v>
       </c>
       <c r="B91" t="n">
-        <v>2345</v>
+        <v>2709</v>
       </c>
       <c r="C91" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D91" t="n">
-        <v>748.86</v>
+        <v>390.19</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2174,17 +2174,17 @@
         <v>46218</v>
       </c>
       <c r="B92" t="n">
-        <v>1983</v>
+        <v>2211</v>
       </c>
       <c r="C92" t="n">
-        <v>8888</v>
+        <v>874</v>
       </c>
       <c r="D92" t="n">
-        <v>2806.44</v>
+        <v>2268.78</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2193,17 +2193,17 @@
         <v>46218</v>
       </c>
       <c r="B93" t="n">
-        <v>2765</v>
+        <v>2345</v>
       </c>
       <c r="C93" t="n">
-        <v>1883</v>
+        <v>8888</v>
       </c>
       <c r="D93" t="n">
-        <v>3638.6</v>
+        <v>748.86</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2212,17 +2212,17 @@
         <v>46218</v>
       </c>
       <c r="B94" t="n">
-        <v>569</v>
+        <v>1983</v>
       </c>
       <c r="C94" t="n">
         <v>8888</v>
       </c>
       <c r="D94" t="n">
-        <v>995.33</v>
+        <v>2806.44</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2231,13 +2231,13 @@
         <v>46218</v>
       </c>
       <c r="B95" t="n">
-        <v>360</v>
+        <v>2765</v>
       </c>
       <c r="C95" t="n">
-        <v>546</v>
+        <v>1883</v>
       </c>
       <c r="D95" t="n">
-        <v>1609.68</v>
+        <v>3638.6</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -2250,17 +2250,17 @@
         <v>46218</v>
       </c>
       <c r="B96" t="n">
-        <v>2711</v>
+        <v>569</v>
       </c>
       <c r="C96" t="n">
-        <v>1953</v>
+        <v>8888</v>
       </c>
       <c r="D96" t="n">
-        <v>150.27</v>
+        <v>995.33</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2269,17 +2269,17 @@
         <v>46218</v>
       </c>
       <c r="B97" t="n">
-        <v>2279</v>
+        <v>360</v>
       </c>
       <c r="C97" t="n">
-        <v>8888</v>
+        <v>546</v>
       </c>
       <c r="D97" t="n">
-        <v>447.5</v>
+        <v>1609.68</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
         <v>46218</v>
       </c>
       <c r="B98" t="n">
-        <v>2308</v>
+        <v>2711</v>
       </c>
       <c r="C98" t="n">
-        <v>8888</v>
+        <v>1953</v>
       </c>
       <c r="D98" t="n">
-        <v>488.69</v>
+        <v>150.27</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2307,17 +2307,17 @@
         <v>46218</v>
       </c>
       <c r="B99" t="n">
-        <v>2211</v>
+        <v>2279</v>
       </c>
       <c r="C99" t="n">
-        <v>874</v>
+        <v>8888</v>
       </c>
       <c r="D99" t="n">
-        <v>1526.94</v>
+        <v>447.5</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2326,13 +2326,13 @@
         <v>46218</v>
       </c>
       <c r="B100" t="n">
-        <v>559</v>
+        <v>2308</v>
       </c>
       <c r="C100" t="n">
         <v>8888</v>
       </c>
       <c r="D100" t="n">
-        <v>859.92</v>
+        <v>488.69</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -2345,13 +2345,13 @@
         <v>46218</v>
       </c>
       <c r="B101" t="n">
-        <v>890</v>
+        <v>559</v>
       </c>
       <c r="C101" t="n">
         <v>8888</v>
       </c>
       <c r="D101" t="n">
-        <v>387.2</v>
+        <v>859.92</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -2364,17 +2364,17 @@
         <v>46218</v>
       </c>
       <c r="B102" t="n">
-        <v>2768</v>
+        <v>890</v>
       </c>
       <c r="C102" t="n">
         <v>8888</v>
       </c>
       <c r="D102" t="n">
-        <v>6523.26</v>
+        <v>387.2</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2383,13 +2383,13 @@
         <v>46218</v>
       </c>
       <c r="B103" t="n">
-        <v>1063</v>
+        <v>2768</v>
       </c>
       <c r="C103" t="n">
         <v>8888</v>
       </c>
       <c r="D103" t="n">
-        <v>4487.11</v>
+        <v>7812.09</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -2402,17 +2402,17 @@
         <v>46218</v>
       </c>
       <c r="B104" t="n">
-        <v>947</v>
+        <v>1063</v>
       </c>
       <c r="C104" t="n">
         <v>8888</v>
       </c>
       <c r="D104" t="n">
-        <v>5667.85</v>
+        <v>4487.11</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>PEDIDO ELETRÔNICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2421,17 +2421,17 @@
         <v>46218</v>
       </c>
       <c r="B105" t="n">
-        <v>2279</v>
+        <v>947</v>
       </c>
       <c r="C105" t="n">
-        <v>1139</v>
+        <v>8888</v>
       </c>
       <c r="D105" t="n">
-        <v>1031.06</v>
+        <v>5667.85</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>PEDIDO ELETRÔNICO</t>
         </is>
       </c>
     </row>
@@ -2440,13 +2440,13 @@
         <v>46218</v>
       </c>
       <c r="B106" t="n">
-        <v>1299</v>
+        <v>2279</v>
       </c>
       <c r="C106" t="n">
-        <v>27</v>
+        <v>1139</v>
       </c>
       <c r="D106" t="n">
-        <v>1435.52</v>
+        <v>1031.06</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -2459,13 +2459,13 @@
         <v>46218</v>
       </c>
       <c r="B107" t="n">
-        <v>1478</v>
+        <v>1299</v>
       </c>
       <c r="C107" t="n">
-        <v>675</v>
+        <v>27</v>
       </c>
       <c r="D107" t="n">
-        <v>1967.85</v>
+        <v>1435.52</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -2478,17 +2478,17 @@
         <v>46218</v>
       </c>
       <c r="B108" t="n">
-        <v>767</v>
+        <v>1478</v>
       </c>
       <c r="C108" t="n">
-        <v>8888</v>
+        <v>675</v>
       </c>
       <c r="D108" t="n">
-        <v>3292.44</v>
+        <v>1967.85</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2497,17 +2497,17 @@
         <v>46218</v>
       </c>
       <c r="B109" t="n">
-        <v>285</v>
+        <v>675</v>
       </c>
       <c r="C109" t="n">
         <v>8888</v>
       </c>
       <c r="D109" t="n">
-        <v>3349.8</v>
+        <v>2685.73</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2516,17 +2516,17 @@
         <v>46218</v>
       </c>
       <c r="B110" t="n">
-        <v>477</v>
+        <v>767</v>
       </c>
       <c r="C110" t="n">
         <v>8888</v>
       </c>
       <c r="D110" t="n">
-        <v>917.33</v>
+        <v>3292.44</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2535,17 +2535,17 @@
         <v>46218</v>
       </c>
       <c r="B111" t="n">
-        <v>1983</v>
+        <v>285</v>
       </c>
       <c r="C111" t="n">
         <v>8888</v>
       </c>
       <c r="D111" t="n">
-        <v>5115.01</v>
+        <v>3349.8</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2557,14 +2557,14 @@
         <v>477</v>
       </c>
       <c r="C112" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D112" t="n">
-        <v>3946.44</v>
+        <v>917.33</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2573,13 +2573,13 @@
         <v>46218</v>
       </c>
       <c r="B113" t="n">
-        <v>1937</v>
+        <v>1983</v>
       </c>
       <c r="C113" t="n">
         <v>8888</v>
       </c>
       <c r="D113" t="n">
-        <v>2600.61</v>
+        <v>5115.01</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -2592,17 +2592,17 @@
         <v>46218</v>
       </c>
       <c r="B114" t="n">
-        <v>1063</v>
+        <v>477</v>
       </c>
       <c r="C114" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D114" t="n">
-        <v>2549.86</v>
+        <v>3946.44</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2611,17 +2611,17 @@
         <v>46218</v>
       </c>
       <c r="B115" t="n">
-        <v>2584</v>
+        <v>1937</v>
       </c>
       <c r="C115" t="n">
-        <v>1929</v>
+        <v>8888</v>
       </c>
       <c r="D115" t="n">
-        <v>756.16</v>
+        <v>2600.61</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2630,17 +2630,17 @@
         <v>46218</v>
       </c>
       <c r="B116" t="n">
-        <v>58</v>
+        <v>363</v>
       </c>
       <c r="C116" t="n">
         <v>8888</v>
       </c>
       <c r="D116" t="n">
-        <v>558.03</v>
+        <v>780.35</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2649,13 +2649,13 @@
         <v>46218</v>
       </c>
       <c r="B117" t="n">
-        <v>424</v>
+        <v>1063</v>
       </c>
       <c r="C117" t="n">
         <v>8888</v>
       </c>
       <c r="D117" t="n">
-        <v>1362.42</v>
+        <v>2549.86</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -2668,13 +2668,13 @@
         <v>46218</v>
       </c>
       <c r="B118" t="n">
-        <v>675</v>
+        <v>360</v>
       </c>
       <c r="C118" t="n">
         <v>8888</v>
       </c>
       <c r="D118" t="n">
-        <v>616.73</v>
+        <v>5917.55</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -2687,17 +2687,17 @@
         <v>46218</v>
       </c>
       <c r="B119" t="n">
-        <v>663</v>
+        <v>2584</v>
       </c>
       <c r="C119" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D119" t="n">
-        <v>255.13</v>
+        <v>756.16</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2706,13 +2706,13 @@
         <v>46218</v>
       </c>
       <c r="B120" t="n">
-        <v>1993</v>
+        <v>58</v>
       </c>
       <c r="C120" t="n">
         <v>8888</v>
       </c>
       <c r="D120" t="n">
-        <v>724.14</v>
+        <v>558.03</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -2725,17 +2725,17 @@
         <v>46218</v>
       </c>
       <c r="B121" t="n">
-        <v>1465</v>
+        <v>424</v>
       </c>
       <c r="C121" t="n">
         <v>8888</v>
       </c>
       <c r="D121" t="n">
-        <v>7362.56</v>
+        <v>1362.42</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2744,17 +2744,17 @@
         <v>46218</v>
       </c>
       <c r="B122" t="n">
-        <v>89</v>
+        <v>663</v>
       </c>
       <c r="C122" t="n">
         <v>8888</v>
       </c>
       <c r="D122" t="n">
-        <v>479</v>
+        <v>255.13</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2763,17 +2763,17 @@
         <v>46218</v>
       </c>
       <c r="B123" t="n">
-        <v>595</v>
+        <v>1993</v>
       </c>
       <c r="C123" t="n">
         <v>8888</v>
       </c>
       <c r="D123" t="n">
-        <v>18084.5</v>
+        <v>724.14</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2782,17 +2782,17 @@
         <v>46218</v>
       </c>
       <c r="B124" t="n">
-        <v>2696</v>
+        <v>1465</v>
       </c>
       <c r="C124" t="n">
-        <v>1954</v>
+        <v>8888</v>
       </c>
       <c r="D124" t="n">
-        <v>1597.76</v>
+        <v>7362.56</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2801,17 +2801,17 @@
         <v>46218</v>
       </c>
       <c r="B125" t="n">
-        <v>360</v>
+        <v>89</v>
       </c>
       <c r="C125" t="n">
         <v>8888</v>
       </c>
       <c r="D125" t="n">
-        <v>4596.89</v>
+        <v>479</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2820,17 +2820,17 @@
         <v>46218</v>
       </c>
       <c r="B126" t="n">
-        <v>1465</v>
+        <v>595</v>
       </c>
       <c r="C126" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D126" t="n">
-        <v>777.2</v>
+        <v>18084.5</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2839,17 +2839,17 @@
         <v>46218</v>
       </c>
       <c r="B127" t="n">
-        <v>2178</v>
+        <v>2696</v>
       </c>
       <c r="C127" t="n">
-        <v>8888</v>
+        <v>1954</v>
       </c>
       <c r="D127" t="n">
-        <v>619.92</v>
+        <v>1597.76</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2858,13 +2858,13 @@
         <v>46218</v>
       </c>
       <c r="B128" t="n">
-        <v>2026</v>
+        <v>1465</v>
       </c>
       <c r="C128" t="n">
-        <v>1929</v>
+        <v>3403</v>
       </c>
       <c r="D128" t="n">
-        <v>6021.92</v>
+        <v>777.2</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -2877,17 +2877,17 @@
         <v>46218</v>
       </c>
       <c r="B129" t="n">
-        <v>630</v>
+        <v>2178</v>
       </c>
       <c r="C129" t="n">
-        <v>1929</v>
+        <v>8888</v>
       </c>
       <c r="D129" t="n">
-        <v>1801.63</v>
+        <v>619.92</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2896,17 +2896,17 @@
         <v>46218</v>
       </c>
       <c r="B130" t="n">
-        <v>1937</v>
+        <v>2026</v>
       </c>
       <c r="C130" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D130" t="n">
-        <v>2132.95</v>
+        <v>6021.92</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2915,17 +2915,17 @@
         <v>46218</v>
       </c>
       <c r="B131" t="n">
-        <v>2577</v>
+        <v>630</v>
       </c>
       <c r="C131" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D131" t="n">
-        <v>1647.08</v>
+        <v>1801.63</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2934,13 +2934,13 @@
         <v>46218</v>
       </c>
       <c r="B132" t="n">
-        <v>1293</v>
+        <v>1937</v>
       </c>
       <c r="C132" t="n">
         <v>8888</v>
       </c>
       <c r="D132" t="n">
-        <v>2135.89</v>
+        <v>2132.95</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -2953,13 +2953,13 @@
         <v>46218</v>
       </c>
       <c r="B133" t="n">
-        <v>2607</v>
+        <v>2577</v>
       </c>
       <c r="C133" t="n">
         <v>8888</v>
       </c>
       <c r="D133" t="n">
-        <v>490.31</v>
+        <v>1647.08</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -2972,17 +2972,17 @@
         <v>46218</v>
       </c>
       <c r="B134" t="n">
-        <v>1317</v>
+        <v>1293</v>
       </c>
       <c r="C134" t="n">
         <v>8888</v>
       </c>
       <c r="D134" t="n">
-        <v>907.72</v>
+        <v>2135.89</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2991,13 +2991,13 @@
         <v>46218</v>
       </c>
       <c r="B135" t="n">
-        <v>619</v>
+        <v>2607</v>
       </c>
       <c r="C135" t="n">
         <v>8888</v>
       </c>
       <c r="D135" t="n">
-        <v>1081.74</v>
+        <v>490.31</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -3010,17 +3010,17 @@
         <v>46218</v>
       </c>
       <c r="B136" t="n">
-        <v>2571</v>
+        <v>1317</v>
       </c>
       <c r="C136" t="n">
-        <v>1312</v>
+        <v>8888</v>
       </c>
       <c r="D136" t="n">
-        <v>268.53</v>
+        <v>907.72</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3029,17 +3029,17 @@
         <v>46218</v>
       </c>
       <c r="B137" t="n">
-        <v>20</v>
+        <v>535</v>
       </c>
       <c r="C137" t="n">
-        <v>8888</v>
+        <v>2571</v>
       </c>
       <c r="D137" t="n">
-        <v>745.55</v>
+        <v>1124.46</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3048,13 +3048,13 @@
         <v>46218</v>
       </c>
       <c r="B138" t="n">
-        <v>1063</v>
+        <v>675</v>
       </c>
       <c r="C138" t="n">
         <v>8888</v>
       </c>
       <c r="D138" t="n">
-        <v>1113.08</v>
+        <v>337.89</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -3067,17 +3067,17 @@
         <v>46218</v>
       </c>
       <c r="B139" t="n">
-        <v>2631</v>
+        <v>2571</v>
       </c>
       <c r="C139" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D139" t="n">
-        <v>1447.86</v>
+        <v>743.01</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3086,13 +3086,13 @@
         <v>46218</v>
       </c>
       <c r="B140" t="n">
-        <v>1906</v>
+        <v>619</v>
       </c>
       <c r="C140" t="n">
         <v>8888</v>
       </c>
       <c r="D140" t="n">
-        <v>2774.84</v>
+        <v>1081.74</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -3105,13 +3105,13 @@
         <v>46218</v>
       </c>
       <c r="B141" t="n">
-        <v>1756</v>
+        <v>20</v>
       </c>
       <c r="C141" t="n">
         <v>8888</v>
       </c>
       <c r="D141" t="n">
-        <v>2275.21</v>
+        <v>745.55</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -3124,13 +3124,13 @@
         <v>46218</v>
       </c>
       <c r="B142" t="n">
-        <v>477</v>
+        <v>1063</v>
       </c>
       <c r="C142" t="n">
         <v>8888</v>
       </c>
       <c r="D142" t="n">
-        <v>707.52</v>
+        <v>1113.08</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -3143,13 +3143,13 @@
         <v>46218</v>
       </c>
       <c r="B143" t="n">
-        <v>2660</v>
+        <v>2631</v>
       </c>
       <c r="C143" t="n">
         <v>8888</v>
       </c>
       <c r="D143" t="n">
-        <v>2684.97</v>
+        <v>1447.86</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -3162,17 +3162,17 @@
         <v>46218</v>
       </c>
       <c r="B144" t="n">
-        <v>569</v>
+        <v>1906</v>
       </c>
       <c r="C144" t="n">
         <v>8888</v>
       </c>
       <c r="D144" t="n">
-        <v>43745.83</v>
+        <v>2774.84</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3181,17 +3181,17 @@
         <v>46218</v>
       </c>
       <c r="B145" t="n">
-        <v>483</v>
+        <v>1756</v>
       </c>
       <c r="C145" t="n">
         <v>8888</v>
       </c>
       <c r="D145" t="n">
-        <v>3102.48</v>
+        <v>2275.21</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3200,17 +3200,17 @@
         <v>46218</v>
       </c>
       <c r="B146" t="n">
-        <v>609</v>
+        <v>477</v>
       </c>
       <c r="C146" t="n">
         <v>8888</v>
       </c>
       <c r="D146" t="n">
-        <v>1633.68</v>
+        <v>707.52</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3219,17 +3219,17 @@
         <v>46218</v>
       </c>
       <c r="B147" t="n">
-        <v>483</v>
+        <v>2660</v>
       </c>
       <c r="C147" t="n">
         <v>8888</v>
       </c>
       <c r="D147" t="n">
-        <v>2011.13</v>
+        <v>2684.97</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3238,17 +3238,17 @@
         <v>46218</v>
       </c>
       <c r="B148" t="n">
-        <v>2089</v>
+        <v>569</v>
       </c>
       <c r="C148" t="n">
-        <v>1533</v>
+        <v>8888</v>
       </c>
       <c r="D148" t="n">
-        <v>1309.01</v>
+        <v>43745.83</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3257,17 +3257,17 @@
         <v>46218</v>
       </c>
       <c r="B149" t="n">
-        <v>1007</v>
+        <v>483</v>
       </c>
       <c r="C149" t="n">
         <v>8888</v>
       </c>
       <c r="D149" t="n">
-        <v>241.44</v>
+        <v>3102.48</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3276,17 +3276,17 @@
         <v>46218</v>
       </c>
       <c r="B150" t="n">
-        <v>1380</v>
+        <v>609</v>
       </c>
       <c r="C150" t="n">
         <v>8888</v>
       </c>
       <c r="D150" t="n">
-        <v>520.2</v>
+        <v>1633.68</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3295,17 +3295,17 @@
         <v>46218</v>
       </c>
       <c r="B151" t="n">
-        <v>1102</v>
+        <v>483</v>
       </c>
       <c r="C151" t="n">
         <v>8888</v>
       </c>
       <c r="D151" t="n">
-        <v>1137.04</v>
+        <v>2011.13</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3314,17 +3314,17 @@
         <v>46218</v>
       </c>
       <c r="B152" t="n">
-        <v>1075</v>
+        <v>2089</v>
       </c>
       <c r="C152" t="n">
-        <v>8888</v>
+        <v>1533</v>
       </c>
       <c r="D152" t="n">
-        <v>5710.94</v>
+        <v>1309.01</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3333,17 +3333,17 @@
         <v>46218</v>
       </c>
       <c r="B153" t="n">
-        <v>2681</v>
+        <v>1007</v>
       </c>
       <c r="C153" t="n">
         <v>8888</v>
       </c>
       <c r="D153" t="n">
-        <v>729.25</v>
+        <v>241.44</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
         <v>46218</v>
       </c>
       <c r="B154" t="n">
-        <v>2245</v>
+        <v>1380</v>
       </c>
       <c r="C154" t="n">
         <v>8888</v>
       </c>
       <c r="D154" t="n">
-        <v>700.2</v>
+        <v>520.2</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3371,17 +3371,17 @@
         <v>46218</v>
       </c>
       <c r="B155" t="n">
-        <v>40</v>
+        <v>1102</v>
       </c>
       <c r="C155" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D155" t="n">
-        <v>678.21</v>
+        <v>1137.04</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3390,17 +3390,17 @@
         <v>46218</v>
       </c>
       <c r="B156" t="n">
-        <v>33</v>
+        <v>358</v>
       </c>
       <c r="C156" t="n">
         <v>8888</v>
       </c>
       <c r="D156" t="n">
-        <v>926.97</v>
+        <v>3380.3</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3409,13 +3409,13 @@
         <v>46218</v>
       </c>
       <c r="B157" t="n">
-        <v>132</v>
+        <v>1075</v>
       </c>
       <c r="C157" t="n">
         <v>8888</v>
       </c>
       <c r="D157" t="n">
-        <v>6522.92</v>
+        <v>5710.94</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -3428,17 +3428,17 @@
         <v>46218</v>
       </c>
       <c r="B158" t="n">
-        <v>619</v>
+        <v>2681</v>
       </c>
       <c r="C158" t="n">
         <v>8888</v>
       </c>
       <c r="D158" t="n">
-        <v>2912.89</v>
+        <v>729.25</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3447,17 +3447,17 @@
         <v>46218</v>
       </c>
       <c r="B159" t="n">
-        <v>2769</v>
+        <v>2245</v>
       </c>
       <c r="C159" t="n">
-        <v>977</v>
+        <v>8888</v>
       </c>
       <c r="D159" t="n">
-        <v>1116.56</v>
+        <v>700.2</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3466,17 +3466,17 @@
         <v>46218</v>
       </c>
       <c r="B160" t="n">
-        <v>452</v>
+        <v>40</v>
       </c>
       <c r="C160" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D160" t="n">
-        <v>608.78</v>
+        <v>678.21</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3485,17 +3485,17 @@
         <v>46218</v>
       </c>
       <c r="B161" t="n">
-        <v>2463</v>
+        <v>33</v>
       </c>
       <c r="C161" t="n">
         <v>8888</v>
       </c>
       <c r="D161" t="n">
-        <v>363.69</v>
+        <v>926.97</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3504,17 +3504,17 @@
         <v>46218</v>
       </c>
       <c r="B162" t="n">
-        <v>1293</v>
+        <v>132</v>
       </c>
       <c r="C162" t="n">
-        <v>1281</v>
+        <v>8888</v>
       </c>
       <c r="D162" t="n">
-        <v>1780.93</v>
+        <v>6522.92</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3523,13 +3523,13 @@
         <v>46218</v>
       </c>
       <c r="B163" t="n">
-        <v>525</v>
+        <v>619</v>
       </c>
       <c r="C163" t="n">
         <v>8888</v>
       </c>
       <c r="D163" t="n">
-        <v>5658.57</v>
+        <v>2912.89</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -3542,17 +3542,17 @@
         <v>46218</v>
       </c>
       <c r="B164" t="n">
-        <v>2641</v>
+        <v>2769</v>
       </c>
       <c r="C164" t="n">
-        <v>8888</v>
+        <v>977</v>
       </c>
       <c r="D164" t="n">
-        <v>1720.99</v>
+        <v>1116.56</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3561,13 +3561,13 @@
         <v>46218</v>
       </c>
       <c r="B165" t="n">
-        <v>58</v>
+        <v>452</v>
       </c>
       <c r="C165" t="n">
         <v>8888</v>
       </c>
       <c r="D165" t="n">
-        <v>4929.8</v>
+        <v>608.78</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -3580,17 +3580,17 @@
         <v>46218</v>
       </c>
       <c r="B166" t="n">
-        <v>325</v>
+        <v>2463</v>
       </c>
       <c r="C166" t="n">
-        <v>1098</v>
+        <v>8888</v>
       </c>
       <c r="D166" t="n">
-        <v>50.06</v>
+        <v>363.69</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3599,17 +3599,17 @@
         <v>46218</v>
       </c>
       <c r="B167" t="n">
-        <v>2697</v>
+        <v>1293</v>
       </c>
       <c r="C167" t="n">
-        <v>8888</v>
+        <v>1281</v>
       </c>
       <c r="D167" t="n">
-        <v>418.65</v>
+        <v>1780.93</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3618,17 +3618,17 @@
         <v>46218</v>
       </c>
       <c r="B168" t="n">
-        <v>2472</v>
+        <v>525</v>
       </c>
       <c r="C168" t="n">
-        <v>2853</v>
+        <v>8888</v>
       </c>
       <c r="D168" t="n">
-        <v>1402.64</v>
+        <v>5658.57</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3637,17 +3637,17 @@
         <v>46218</v>
       </c>
       <c r="B169" t="n">
-        <v>358</v>
+        <v>2641</v>
       </c>
       <c r="C169" t="n">
         <v>8888</v>
       </c>
       <c r="D169" t="n">
-        <v>1675.95</v>
+        <v>1720.99</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3656,17 +3656,17 @@
         <v>46218</v>
       </c>
       <c r="B170" t="n">
-        <v>2431</v>
+        <v>675</v>
       </c>
       <c r="C170" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D170" t="n">
-        <v>266.89</v>
+        <v>504.07</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3675,17 +3675,17 @@
         <v>46218</v>
       </c>
       <c r="B171" t="n">
-        <v>285</v>
+        <v>58</v>
       </c>
       <c r="C171" t="n">
         <v>8888</v>
       </c>
       <c r="D171" t="n">
-        <v>5673.85</v>
+        <v>4929.8</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3694,17 +3694,17 @@
         <v>46218</v>
       </c>
       <c r="B172" t="n">
-        <v>1102</v>
+        <v>358</v>
       </c>
       <c r="C172" t="n">
-        <v>8888</v>
+        <v>546</v>
       </c>
       <c r="D172" t="n">
-        <v>2301.43</v>
+        <v>862.4400000000001</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3713,17 +3713,17 @@
         <v>46218</v>
       </c>
       <c r="B173" t="n">
-        <v>2793</v>
+        <v>325</v>
       </c>
       <c r="C173" t="n">
-        <v>8888</v>
+        <v>1098</v>
       </c>
       <c r="D173" t="n">
-        <v>1238.11</v>
+        <v>50.06</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3732,17 +3732,17 @@
         <v>46218</v>
       </c>
       <c r="B174" t="n">
-        <v>626</v>
+        <v>2697</v>
       </c>
       <c r="C174" t="n">
         <v>8888</v>
       </c>
       <c r="D174" t="n">
-        <v>12556.19</v>
+        <v>833.38</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3751,17 +3751,17 @@
         <v>46218</v>
       </c>
       <c r="B175" t="n">
-        <v>424</v>
+        <v>2472</v>
       </c>
       <c r="C175" t="n">
-        <v>8888</v>
+        <v>2853</v>
       </c>
       <c r="D175" t="n">
-        <v>1124.8</v>
+        <v>1402.64</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3770,17 +3770,17 @@
         <v>46218</v>
       </c>
       <c r="B176" t="n">
-        <v>1137</v>
+        <v>2431</v>
       </c>
       <c r="C176" t="n">
-        <v>2220</v>
+        <v>8888</v>
       </c>
       <c r="D176" t="n">
-        <v>1370.86</v>
+        <v>266.89</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3789,17 +3789,17 @@
         <v>46218</v>
       </c>
       <c r="B177" t="n">
-        <v>1299</v>
+        <v>285</v>
       </c>
       <c r="C177" t="n">
-        <v>2522</v>
+        <v>8888</v>
       </c>
       <c r="D177" t="n">
-        <v>8881.309999999999</v>
+        <v>5673.85</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3808,17 +3808,17 @@
         <v>46218</v>
       </c>
       <c r="B178" t="n">
-        <v>1289</v>
+        <v>1102</v>
       </c>
       <c r="C178" t="n">
         <v>8888</v>
       </c>
       <c r="D178" t="n">
-        <v>5565.44</v>
+        <v>2301.43</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3827,17 +3827,17 @@
         <v>46218</v>
       </c>
       <c r="B179" t="n">
-        <v>2686</v>
+        <v>2793</v>
       </c>
       <c r="C179" t="n">
-        <v>1929</v>
+        <v>8888</v>
       </c>
       <c r="D179" t="n">
-        <v>2066.36</v>
+        <v>1238.11</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3846,17 +3846,17 @@
         <v>46218</v>
       </c>
       <c r="B180" t="n">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="C180" t="n">
         <v>8888</v>
       </c>
       <c r="D180" t="n">
-        <v>5212.76</v>
+        <v>23157.24</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3865,17 +3865,17 @@
         <v>46218</v>
       </c>
       <c r="B181" t="n">
-        <v>2584</v>
+        <v>424</v>
       </c>
       <c r="C181" t="n">
         <v>8888</v>
       </c>
       <c r="D181" t="n">
-        <v>5635.67</v>
+        <v>1124.8</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3884,17 +3884,17 @@
         <v>46218</v>
       </c>
       <c r="B182" t="n">
-        <v>1756</v>
+        <v>1137</v>
       </c>
       <c r="C182" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D182" t="n">
-        <v>3242.54</v>
+        <v>3285.55</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3903,13 +3903,13 @@
         <v>46218</v>
       </c>
       <c r="B183" t="n">
-        <v>1756</v>
+        <v>1299</v>
       </c>
       <c r="C183" t="n">
-        <v>27</v>
+        <v>2522</v>
       </c>
       <c r="D183" t="n">
-        <v>5078.1</v>
+        <v>8881.309999999999</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -3922,17 +3922,17 @@
         <v>46218</v>
       </c>
       <c r="B184" t="n">
-        <v>2651</v>
+        <v>1289</v>
       </c>
       <c r="C184" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D184" t="n">
-        <v>363.7</v>
+        <v>5565.44</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3941,17 +3941,17 @@
         <v>46218</v>
       </c>
       <c r="B185" t="n">
-        <v>664</v>
+        <v>2686</v>
       </c>
       <c r="C185" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D185" t="n">
-        <v>6478.17</v>
+        <v>2066.36</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3960,17 +3960,17 @@
         <v>46218</v>
       </c>
       <c r="B186" t="n">
-        <v>360</v>
+        <v>629</v>
       </c>
       <c r="C186" t="n">
         <v>8888</v>
       </c>
       <c r="D186" t="n">
-        <v>1594.84</v>
+        <v>5212.76</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3979,17 +3979,17 @@
         <v>46218</v>
       </c>
       <c r="B187" t="n">
-        <v>2582</v>
+        <v>636</v>
       </c>
       <c r="C187" t="n">
         <v>8888</v>
       </c>
       <c r="D187" t="n">
-        <v>379.33</v>
+        <v>5742.49</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3998,17 +3998,17 @@
         <v>46218</v>
       </c>
       <c r="B188" t="n">
-        <v>636</v>
+        <v>2584</v>
       </c>
       <c r="C188" t="n">
         <v>8888</v>
       </c>
       <c r="D188" t="n">
-        <v>2447.56</v>
+        <v>5635.67</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4017,17 +4017,17 @@
         <v>46218</v>
       </c>
       <c r="B189" t="n">
-        <v>1254</v>
+        <v>1756</v>
       </c>
       <c r="C189" t="n">
         <v>8888</v>
       </c>
       <c r="D189" t="n">
-        <v>2643.22</v>
+        <v>3242.54</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4036,17 +4036,17 @@
         <v>46218</v>
       </c>
       <c r="B190" t="n">
-        <v>2726</v>
+        <v>2698</v>
       </c>
       <c r="C190" t="n">
-        <v>977</v>
+        <v>8888</v>
       </c>
       <c r="D190" t="n">
-        <v>586.0599999999999</v>
+        <v>859.49</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4055,17 +4055,17 @@
         <v>46218</v>
       </c>
       <c r="B191" t="n">
-        <v>2015</v>
+        <v>1756</v>
       </c>
       <c r="C191" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D191" t="n">
-        <v>315.69</v>
+        <v>5078.1</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4074,17 +4074,17 @@
         <v>46218</v>
       </c>
       <c r="B192" t="n">
-        <v>1064</v>
+        <v>2651</v>
       </c>
       <c r="C192" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D192" t="n">
-        <v>1274.3</v>
+        <v>363.7</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4093,17 +4093,17 @@
         <v>46218</v>
       </c>
       <c r="B193" t="n">
-        <v>2698</v>
+        <v>664</v>
       </c>
       <c r="C193" t="n">
         <v>8888</v>
       </c>
       <c r="D193" t="n">
-        <v>552.15</v>
+        <v>6478.17</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4112,17 +4112,17 @@
         <v>46218</v>
       </c>
       <c r="B194" t="n">
-        <v>2641</v>
+        <v>360</v>
       </c>
       <c r="C194" t="n">
         <v>8888</v>
       </c>
       <c r="D194" t="n">
-        <v>820</v>
+        <v>1594.84</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4131,17 +4131,17 @@
         <v>46218</v>
       </c>
       <c r="B195" t="n">
-        <v>429</v>
+        <v>2582</v>
       </c>
       <c r="C195" t="n">
         <v>8888</v>
       </c>
       <c r="D195" t="n">
-        <v>2593.49</v>
+        <v>379.33</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4150,17 +4150,17 @@
         <v>46218</v>
       </c>
       <c r="B196" t="n">
-        <v>1301</v>
+        <v>1254</v>
       </c>
       <c r="C196" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D196" t="n">
-        <v>750.66</v>
+        <v>2643.22</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4169,17 +4169,17 @@
         <v>46218</v>
       </c>
       <c r="B197" t="n">
-        <v>816</v>
+        <v>2726</v>
       </c>
       <c r="C197" t="n">
-        <v>8888</v>
+        <v>977</v>
       </c>
       <c r="D197" t="n">
-        <v>438.24</v>
+        <v>586.0599999999999</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4188,17 +4188,17 @@
         <v>46218</v>
       </c>
       <c r="B198" t="n">
-        <v>2359</v>
+        <v>2015</v>
       </c>
       <c r="C198" t="n">
         <v>8888</v>
       </c>
       <c r="D198" t="n">
-        <v>381.95</v>
+        <v>315.69</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4207,17 +4207,17 @@
         <v>46218</v>
       </c>
       <c r="B199" t="n">
-        <v>2251</v>
+        <v>1064</v>
       </c>
       <c r="C199" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D199" t="n">
-        <v>802.08</v>
+        <v>1274.3</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4226,17 +4226,17 @@
         <v>46218</v>
       </c>
       <c r="B200" t="n">
-        <v>285</v>
+        <v>358</v>
       </c>
       <c r="C200" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D200" t="n">
-        <v>1797.95</v>
+        <v>2619.4</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4245,17 +4245,17 @@
         <v>46218</v>
       </c>
       <c r="B201" t="n">
-        <v>2114</v>
+        <v>2641</v>
       </c>
       <c r="C201" t="n">
         <v>8888</v>
       </c>
       <c r="D201" t="n">
-        <v>2726.04</v>
+        <v>820</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4264,17 +4264,17 @@
         <v>46218</v>
       </c>
       <c r="B202" t="n">
-        <v>953</v>
+        <v>429</v>
       </c>
       <c r="C202" t="n">
         <v>8888</v>
       </c>
       <c r="D202" t="n">
-        <v>2889.63</v>
+        <v>2593.49</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4283,17 +4283,17 @@
         <v>46218</v>
       </c>
       <c r="B203" t="n">
-        <v>1102</v>
+        <v>1301</v>
       </c>
       <c r="C203" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D203" t="n">
-        <v>6347.79</v>
+        <v>750.66</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4302,17 +4302,17 @@
         <v>46218</v>
       </c>
       <c r="B204" t="n">
-        <v>1465</v>
+        <v>816</v>
       </c>
       <c r="C204" t="n">
         <v>8888</v>
       </c>
       <c r="D204" t="n">
-        <v>4281.39</v>
+        <v>438.24</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4321,17 +4321,17 @@
         <v>46218</v>
       </c>
       <c r="B205" t="n">
-        <v>619</v>
+        <v>2359</v>
       </c>
       <c r="C205" t="n">
         <v>8888</v>
       </c>
       <c r="D205" t="n">
-        <v>2021.67</v>
+        <v>381.95</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4340,17 +4340,17 @@
         <v>46218</v>
       </c>
       <c r="B206" t="n">
-        <v>2716</v>
+        <v>2251</v>
       </c>
       <c r="C206" t="n">
-        <v>8888</v>
+        <v>3403</v>
       </c>
       <c r="D206" t="n">
-        <v>1063.42</v>
+        <v>802.08</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4359,13 +4359,13 @@
         <v>46218</v>
       </c>
       <c r="B207" t="n">
-        <v>2767</v>
+        <v>285</v>
       </c>
       <c r="C207" t="n">
-        <v>1898</v>
+        <v>58</v>
       </c>
       <c r="D207" t="n">
-        <v>1135.64</v>
+        <v>1797.95</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -4378,13 +4378,13 @@
         <v>46218</v>
       </c>
       <c r="B208" t="n">
-        <v>2657</v>
+        <v>2114</v>
       </c>
       <c r="C208" t="n">
         <v>8888</v>
       </c>
       <c r="D208" t="n">
-        <v>3149.7</v>
+        <v>2726.04</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -4397,17 +4397,17 @@
         <v>46218</v>
       </c>
       <c r="B209" t="n">
-        <v>2245</v>
+        <v>953</v>
       </c>
       <c r="C209" t="n">
         <v>8888</v>
       </c>
       <c r="D209" t="n">
-        <v>764.66</v>
+        <v>2889.63</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4416,17 +4416,17 @@
         <v>46218</v>
       </c>
       <c r="B210" t="n">
-        <v>2197</v>
+        <v>1102</v>
       </c>
       <c r="C210" t="n">
         <v>8888</v>
       </c>
       <c r="D210" t="n">
-        <v>1085.45</v>
+        <v>6347.79</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4435,17 +4435,17 @@
         <v>46218</v>
       </c>
       <c r="B211" t="n">
-        <v>1064</v>
+        <v>1465</v>
       </c>
       <c r="C211" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D211" t="n">
-        <v>574.7</v>
+        <v>4281.39</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4454,17 +4454,17 @@
         <v>46218</v>
       </c>
       <c r="B212" t="n">
-        <v>451</v>
+        <v>619</v>
       </c>
       <c r="C212" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D212" t="n">
-        <v>2091.77</v>
+        <v>2021.67</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4473,17 +4473,17 @@
         <v>46218</v>
       </c>
       <c r="B213" t="n">
-        <v>1116</v>
+        <v>2716</v>
       </c>
       <c r="C213" t="n">
-        <v>13148</v>
+        <v>8888</v>
       </c>
       <c r="D213" t="n">
-        <v>1455.21</v>
+        <v>1063.42</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4492,17 +4492,17 @@
         <v>46218</v>
       </c>
       <c r="B214" t="n">
-        <v>1277</v>
+        <v>2767</v>
       </c>
       <c r="C214" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D214" t="n">
-        <v>1949</v>
+        <v>1135.64</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4511,17 +4511,17 @@
         <v>46218</v>
       </c>
       <c r="B215" t="n">
-        <v>131</v>
+        <v>2657</v>
       </c>
       <c r="C215" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D215" t="n">
-        <v>3850.09</v>
+        <v>3149.7</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4530,17 +4530,17 @@
         <v>46218</v>
       </c>
       <c r="B216" t="n">
-        <v>2692</v>
+        <v>2245</v>
       </c>
       <c r="C216" t="n">
         <v>8888</v>
       </c>
       <c r="D216" t="n">
-        <v>731.28</v>
+        <v>764.66</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4549,17 +4549,17 @@
         <v>46218</v>
       </c>
       <c r="B217" t="n">
-        <v>1632</v>
+        <v>2197</v>
       </c>
       <c r="C217" t="n">
         <v>8888</v>
       </c>
       <c r="D217" t="n">
-        <v>7519.7</v>
+        <v>1085.45</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4568,13 +4568,13 @@
         <v>46218</v>
       </c>
       <c r="B218" t="n">
-        <v>1317</v>
+        <v>1064</v>
       </c>
       <c r="C218" t="n">
-        <v>3179</v>
+        <v>27</v>
       </c>
       <c r="D218" t="n">
-        <v>991.6799999999999</v>
+        <v>574.7</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -4587,17 +4587,17 @@
         <v>46218</v>
       </c>
       <c r="B219" t="n">
-        <v>1993</v>
+        <v>451</v>
       </c>
       <c r="C219" t="n">
-        <v>8888</v>
+        <v>3403</v>
       </c>
       <c r="D219" t="n">
-        <v>3508.59</v>
+        <v>2091.77</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4606,13 +4606,13 @@
         <v>46218</v>
       </c>
       <c r="B220" t="n">
-        <v>1890</v>
+        <v>1116</v>
       </c>
       <c r="C220" t="n">
-        <v>3449</v>
+        <v>13148</v>
       </c>
       <c r="D220" t="n">
-        <v>6313.56</v>
+        <v>1455.21</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -4625,17 +4625,17 @@
         <v>46218</v>
       </c>
       <c r="B221" t="n">
-        <v>1800</v>
+        <v>1277</v>
       </c>
       <c r="C221" t="n">
         <v>8888</v>
       </c>
       <c r="D221" t="n">
-        <v>430.37</v>
+        <v>1949</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4644,17 +4644,17 @@
         <v>46218</v>
       </c>
       <c r="B222" t="n">
-        <v>1117</v>
+        <v>131</v>
       </c>
       <c r="C222" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D222" t="n">
-        <v>672.47</v>
+        <v>3850.09</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4663,13 +4663,13 @@
         <v>46218</v>
       </c>
       <c r="B223" t="n">
-        <v>2749</v>
+        <v>2692</v>
       </c>
       <c r="C223" t="n">
         <v>8888</v>
       </c>
       <c r="D223" t="n">
-        <v>1860.64</v>
+        <v>731.28</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -4682,13 +4682,13 @@
         <v>46218</v>
       </c>
       <c r="B224" t="n">
-        <v>42</v>
+        <v>1632</v>
       </c>
       <c r="C224" t="n">
         <v>8888</v>
       </c>
       <c r="D224" t="n">
-        <v>280.05</v>
+        <v>7519.7</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -4701,17 +4701,17 @@
         <v>46218</v>
       </c>
       <c r="B225" t="n">
-        <v>1478</v>
+        <v>1317</v>
       </c>
       <c r="C225" t="n">
-        <v>8888</v>
+        <v>3179</v>
       </c>
       <c r="D225" t="n">
-        <v>875.34</v>
+        <v>991.6799999999999</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4720,13 +4720,13 @@
         <v>46218</v>
       </c>
       <c r="B226" t="n">
-        <v>2491</v>
+        <v>1993</v>
       </c>
       <c r="C226" t="n">
         <v>8888</v>
       </c>
       <c r="D226" t="n">
-        <v>650.4299999999999</v>
+        <v>3508.59</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -4739,17 +4739,17 @@
         <v>46218</v>
       </c>
       <c r="B227" t="n">
-        <v>353</v>
+        <v>1890</v>
       </c>
       <c r="C227" t="n">
-        <v>8888</v>
+        <v>3449</v>
       </c>
       <c r="D227" t="n">
-        <v>653.13</v>
+        <v>6313.56</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4758,17 +4758,17 @@
         <v>46218</v>
       </c>
       <c r="B228" t="n">
-        <v>2015</v>
+        <v>1800</v>
       </c>
       <c r="C228" t="n">
         <v>8888</v>
       </c>
       <c r="D228" t="n">
-        <v>4436.15</v>
+        <v>430.37</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4777,17 +4777,17 @@
         <v>46218</v>
       </c>
       <c r="B229" t="n">
-        <v>559</v>
+        <v>1117</v>
       </c>
       <c r="C229" t="n">
         <v>8888</v>
       </c>
       <c r="D229" t="n">
-        <v>3838.57</v>
+        <v>672.47</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4796,17 +4796,17 @@
         <v>46218</v>
       </c>
       <c r="B230" t="n">
-        <v>1890</v>
+        <v>2749</v>
       </c>
       <c r="C230" t="n">
-        <v>1953</v>
+        <v>8888</v>
       </c>
       <c r="D230" t="n">
-        <v>1674.57</v>
+        <v>1860.64</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4815,17 +4815,17 @@
         <v>46218</v>
       </c>
       <c r="B231" t="n">
-        <v>1317</v>
+        <v>716</v>
       </c>
       <c r="C231" t="n">
-        <v>8888</v>
+        <v>15</v>
       </c>
       <c r="D231" t="n">
-        <v>1626.02</v>
+        <v>30000</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4834,13 +4834,13 @@
         <v>46218</v>
       </c>
       <c r="B232" t="n">
-        <v>2782</v>
+        <v>42</v>
       </c>
       <c r="C232" t="n">
         <v>8888</v>
       </c>
       <c r="D232" t="n">
-        <v>1786.32</v>
+        <v>280.05</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -4853,17 +4853,17 @@
         <v>46218</v>
       </c>
       <c r="B233" t="n">
-        <v>953</v>
+        <v>1478</v>
       </c>
       <c r="C233" t="n">
         <v>8888</v>
       </c>
       <c r="D233" t="n">
-        <v>364.44</v>
+        <v>875.34</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4872,13 +4872,13 @@
         <v>46218</v>
       </c>
       <c r="B234" t="n">
-        <v>2251</v>
+        <v>2491</v>
       </c>
       <c r="C234" t="n">
         <v>8888</v>
       </c>
       <c r="D234" t="n">
-        <v>989.26</v>
+        <v>650.4299999999999</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -4891,17 +4891,17 @@
         <v>46218</v>
       </c>
       <c r="B235" t="n">
-        <v>483</v>
+        <v>353</v>
       </c>
       <c r="C235" t="n">
-        <v>841</v>
+        <v>8888</v>
       </c>
       <c r="D235" t="n">
-        <v>2564.59</v>
+        <v>653.13</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4910,17 +4910,17 @@
         <v>46218</v>
       </c>
       <c r="B236" t="n">
-        <v>2133</v>
+        <v>2015</v>
       </c>
       <c r="C236" t="n">
-        <v>213</v>
+        <v>8888</v>
       </c>
       <c r="D236" t="n">
-        <v>526.8</v>
+        <v>4436.15</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4929,17 +4929,17 @@
         <v>46218</v>
       </c>
       <c r="B237" t="n">
-        <v>351</v>
+        <v>559</v>
       </c>
       <c r="C237" t="n">
-        <v>3009</v>
+        <v>8888</v>
       </c>
       <c r="D237" t="n">
-        <v>416.36</v>
+        <v>3838.57</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4948,17 +4948,17 @@
         <v>46218</v>
       </c>
       <c r="B238" t="n">
-        <v>2250</v>
+        <v>1890</v>
       </c>
       <c r="C238" t="n">
-        <v>8888</v>
+        <v>1953</v>
       </c>
       <c r="D238" t="n">
-        <v>709.46</v>
+        <v>2998.69</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4967,17 +4967,17 @@
         <v>46218</v>
       </c>
       <c r="B239" t="n">
-        <v>2648</v>
+        <v>1317</v>
       </c>
       <c r="C239" t="n">
         <v>8888</v>
       </c>
       <c r="D239" t="n">
-        <v>1873.52</v>
+        <v>1626.02</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4986,17 +4986,17 @@
         <v>46218</v>
       </c>
       <c r="B240" t="n">
-        <v>131</v>
+        <v>429</v>
       </c>
       <c r="C240" t="n">
-        <v>8888</v>
+        <v>1281</v>
       </c>
       <c r="D240" t="n">
-        <v>1369.91</v>
+        <v>1000.44</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -5005,17 +5005,17 @@
         <v>46218</v>
       </c>
       <c r="B241" t="n">
-        <v>2298</v>
+        <v>2782</v>
       </c>
       <c r="C241" t="n">
-        <v>675</v>
+        <v>8888</v>
       </c>
       <c r="D241" t="n">
-        <v>2301.31</v>
+        <v>1786.32</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5024,17 +5024,17 @@
         <v>46218</v>
       </c>
       <c r="B242" t="n">
-        <v>2790</v>
+        <v>953</v>
       </c>
       <c r="C242" t="n">
-        <v>1953</v>
+        <v>8888</v>
       </c>
       <c r="D242" t="n">
-        <v>371.88</v>
+        <v>364.44</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5043,17 +5043,17 @@
         <v>46218</v>
       </c>
       <c r="B243" t="n">
-        <v>363</v>
+        <v>2251</v>
       </c>
       <c r="C243" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D243" t="n">
-        <v>635.1</v>
+        <v>989.26</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5062,13 +5062,13 @@
         <v>46218</v>
       </c>
       <c r="B244" t="n">
-        <v>2716</v>
+        <v>483</v>
       </c>
       <c r="C244" t="n">
-        <v>1929</v>
+        <v>841</v>
       </c>
       <c r="D244" t="n">
-        <v>1073.33</v>
+        <v>2564.59</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -5081,13 +5081,13 @@
         <v>46218</v>
       </c>
       <c r="B245" t="n">
-        <v>2639</v>
+        <v>2133</v>
       </c>
       <c r="C245" t="n">
-        <v>1953</v>
+        <v>213</v>
       </c>
       <c r="D245" t="n">
-        <v>504.09</v>
+        <v>526.8</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -5100,13 +5100,13 @@
         <v>46218</v>
       </c>
       <c r="B246" t="n">
-        <v>629</v>
+        <v>351</v>
       </c>
       <c r="C246" t="n">
-        <v>675</v>
+        <v>3009</v>
       </c>
       <c r="D246" t="n">
-        <v>2419.73</v>
+        <v>416.36</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -5119,17 +5119,17 @@
         <v>46218</v>
       </c>
       <c r="B247" t="n">
-        <v>619</v>
+        <v>2250</v>
       </c>
       <c r="C247" t="n">
-        <v>1139</v>
+        <v>8888</v>
       </c>
       <c r="D247" t="n">
-        <v>1341.64</v>
+        <v>709.46</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -5138,13 +5138,13 @@
         <v>46218</v>
       </c>
       <c r="B248" t="n">
-        <v>2109</v>
+        <v>2648</v>
       </c>
       <c r="C248" t="n">
         <v>8888</v>
       </c>
       <c r="D248" t="n">
-        <v>2293.78</v>
+        <v>1873.52</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -5157,13 +5157,13 @@
         <v>46218</v>
       </c>
       <c r="B249" t="n">
-        <v>1116</v>
+        <v>131</v>
       </c>
       <c r="C249" t="n">
         <v>8888</v>
       </c>
       <c r="D249" t="n">
-        <v>2919.53</v>
+        <v>1369.91</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -5176,13 +5176,13 @@
         <v>46218</v>
       </c>
       <c r="B250" t="n">
-        <v>2250</v>
+        <v>2298</v>
       </c>
       <c r="C250" t="n">
-        <v>27</v>
+        <v>675</v>
       </c>
       <c r="D250" t="n">
-        <v>1803.76</v>
+        <v>2301.31</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -5195,13 +5195,13 @@
         <v>46218</v>
       </c>
       <c r="B251" t="n">
-        <v>2698</v>
+        <v>2790</v>
       </c>
       <c r="C251" t="n">
-        <v>874</v>
+        <v>1953</v>
       </c>
       <c r="D251" t="n">
-        <v>1230.43</v>
+        <v>371.88</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -5214,17 +5214,17 @@
         <v>46218</v>
       </c>
       <c r="B252" t="n">
-        <v>42</v>
+        <v>363</v>
       </c>
       <c r="C252" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D252" t="n">
-        <v>79947.14999999999</v>
+        <v>635.1</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -5233,17 +5233,17 @@
         <v>46218</v>
       </c>
       <c r="B253" t="n">
-        <v>772</v>
+        <v>2716</v>
       </c>
       <c r="C253" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D253" t="n">
-        <v>400.25</v>
+        <v>1073.33</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -5252,17 +5252,17 @@
         <v>46218</v>
       </c>
       <c r="B254" t="n">
-        <v>2728</v>
+        <v>2639</v>
       </c>
       <c r="C254" t="n">
-        <v>8888</v>
+        <v>1953</v>
       </c>
       <c r="D254" t="n">
-        <v>1397.07</v>
+        <v>504.09</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -5271,13 +5271,13 @@
         <v>46218</v>
       </c>
       <c r="B255" t="n">
-        <v>2197</v>
+        <v>629</v>
       </c>
       <c r="C255" t="n">
-        <v>423</v>
+        <v>675</v>
       </c>
       <c r="D255" t="n">
-        <v>2267.61</v>
+        <v>2419.73</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -5290,13 +5290,13 @@
         <v>46218</v>
       </c>
       <c r="B256" t="n">
-        <v>2716</v>
+        <v>619</v>
       </c>
       <c r="C256" t="n">
-        <v>977</v>
+        <v>1139</v>
       </c>
       <c r="D256" t="n">
-        <v>729.29</v>
+        <v>1341.64</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -5309,15 +5309,205 @@
         <v>46218</v>
       </c>
       <c r="B257" t="n">
+        <v>2109</v>
+      </c>
+      <c r="C257" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D257" t="n">
+        <v>2293.78</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B258" t="n">
+        <v>1116</v>
+      </c>
+      <c r="C258" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D258" t="n">
+        <v>2919.53</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B259" t="n">
+        <v>1293</v>
+      </c>
+      <c r="C259" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D259" t="n">
+        <v>696.77</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B260" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C260" t="n">
+        <v>27</v>
+      </c>
+      <c r="D260" t="n">
+        <v>1803.76</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B261" t="n">
+        <v>2698</v>
+      </c>
+      <c r="C261" t="n">
+        <v>874</v>
+      </c>
+      <c r="D261" t="n">
+        <v>1556.09</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B262" t="n">
+        <v>42</v>
+      </c>
+      <c r="C262" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D262" t="n">
+        <v>79947.14999999999</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B263" t="n">
+        <v>772</v>
+      </c>
+      <c r="C263" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D263" t="n">
+        <v>400.25</v>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B264" t="n">
+        <v>2728</v>
+      </c>
+      <c r="C264" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D264" t="n">
+        <v>1397.07</v>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B265" t="n">
+        <v>2197</v>
+      </c>
+      <c r="C265" t="n">
+        <v>423</v>
+      </c>
+      <c r="D265" t="n">
+        <v>2267.61</v>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B266" t="n">
+        <v>2716</v>
+      </c>
+      <c r="C266" t="n">
+        <v>977</v>
+      </c>
+      <c r="D266" t="n">
+        <v>729.29</v>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B267" t="n">
         <v>1993</v>
       </c>
-      <c r="C257" t="n">
-        <v>8888</v>
-      </c>
-      <c r="D257" t="n">
+      <c r="C267" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D267" t="n">
         <v>456.62</v>
       </c>
-      <c r="E257" t="inlineStr">
+      <c r="E267" t="inlineStr">
         <is>
           <t>OPERADOR LOGÍSTICO</t>
         </is>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E267"/>
+  <dimension ref="A1:E279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,7 +489,7 @@
         <v>8888</v>
       </c>
       <c r="D3" t="n">
-        <v>769.05</v>
+        <v>814.6900000000001</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1072,17 +1072,17 @@
         <v>46218</v>
       </c>
       <c r="B34" t="n">
-        <v>2251</v>
+        <v>951</v>
       </c>
       <c r="C34" t="n">
         <v>8888</v>
       </c>
       <c r="D34" t="n">
-        <v>1010.74</v>
+        <v>2171.08</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1091,13 +1091,13 @@
         <v>46218</v>
       </c>
       <c r="B35" t="n">
-        <v>951</v>
+        <v>2641</v>
       </c>
       <c r="C35" t="n">
         <v>8888</v>
       </c>
       <c r="D35" t="n">
-        <v>2171.08</v>
+        <v>2527.79</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1110,17 +1110,17 @@
         <v>46218</v>
       </c>
       <c r="B36" t="n">
-        <v>2641</v>
+        <v>2251</v>
       </c>
       <c r="C36" t="n">
         <v>8888</v>
       </c>
       <c r="D36" t="n">
-        <v>2527.79</v>
+        <v>1010.74</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
         <v>8888</v>
       </c>
       <c r="D45" t="n">
-        <v>1279.15</v>
+        <v>1404.58</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>8888</v>
       </c>
       <c r="D54" t="n">
-        <v>30706.36</v>
+        <v>35695.37</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -1528,17 +1528,17 @@
         <v>46218</v>
       </c>
       <c r="B58" t="n">
-        <v>664</v>
+        <v>2631</v>
       </c>
       <c r="C58" t="n">
-        <v>8888</v>
+        <v>2853</v>
       </c>
       <c r="D58" t="n">
-        <v>6275.01</v>
+        <v>3633.39</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1547,17 +1547,17 @@
         <v>46218</v>
       </c>
       <c r="B59" t="n">
-        <v>353</v>
+        <v>664</v>
       </c>
       <c r="C59" t="n">
-        <v>3179</v>
+        <v>8888</v>
       </c>
       <c r="D59" t="n">
-        <v>495.84</v>
+        <v>6275.01</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1566,17 +1566,17 @@
         <v>46218</v>
       </c>
       <c r="B60" t="n">
-        <v>1293</v>
+        <v>353</v>
       </c>
       <c r="C60" t="n">
-        <v>8888</v>
+        <v>3179</v>
       </c>
       <c r="D60" t="n">
-        <v>3129.07</v>
+        <v>495.84</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1585,13 +1585,13 @@
         <v>46218</v>
       </c>
       <c r="B61" t="n">
-        <v>2279</v>
+        <v>1293</v>
       </c>
       <c r="C61" t="n">
         <v>8888</v>
       </c>
       <c r="D61" t="n">
-        <v>3900.07</v>
+        <v>3129.07</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -1604,13 +1604,13 @@
         <v>46218</v>
       </c>
       <c r="B62" t="n">
-        <v>1937</v>
+        <v>2279</v>
       </c>
       <c r="C62" t="n">
         <v>8888</v>
       </c>
       <c r="D62" t="n">
-        <v>1685.72</v>
+        <v>3900.07</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -1623,17 +1623,17 @@
         <v>46218</v>
       </c>
       <c r="B63" t="n">
-        <v>941</v>
+        <v>1937</v>
       </c>
       <c r="C63" t="n">
         <v>8888</v>
       </c>
       <c r="D63" t="n">
-        <v>864.14</v>
+        <v>1685.72</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1642,17 +1642,17 @@
         <v>46218</v>
       </c>
       <c r="B64" t="n">
-        <v>1137</v>
+        <v>941</v>
       </c>
       <c r="C64" t="n">
         <v>8888</v>
       </c>
       <c r="D64" t="n">
-        <v>3168.9</v>
+        <v>864.14</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1661,17 +1661,17 @@
         <v>46218</v>
       </c>
       <c r="B65" t="n">
-        <v>2631</v>
+        <v>1137</v>
       </c>
       <c r="C65" t="n">
-        <v>2853</v>
+        <v>8888</v>
       </c>
       <c r="D65" t="n">
-        <v>2418.28</v>
+        <v>3168.9</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
         <v>8888</v>
       </c>
       <c r="D71" t="n">
-        <v>4416.47</v>
+        <v>4644.88</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -1889,13 +1889,13 @@
         <v>46218</v>
       </c>
       <c r="B77" t="n">
-        <v>483</v>
+        <v>1308</v>
       </c>
       <c r="C77" t="n">
         <v>8888</v>
       </c>
       <c r="D77" t="n">
-        <v>12405.46</v>
+        <v>2702.14</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -1908,17 +1908,17 @@
         <v>46218</v>
       </c>
       <c r="B78" t="n">
-        <v>1075</v>
+        <v>483</v>
       </c>
       <c r="C78" t="n">
         <v>8888</v>
       </c>
       <c r="D78" t="n">
-        <v>11607.79</v>
+        <v>12405.46</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1927,13 +1927,13 @@
         <v>46218</v>
       </c>
       <c r="B79" t="n">
-        <v>629</v>
+        <v>1075</v>
       </c>
       <c r="C79" t="n">
         <v>8888</v>
       </c>
       <c r="D79" t="n">
-        <v>9233.719999999999</v>
+        <v>11607.79</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -1946,17 +1946,17 @@
         <v>46218</v>
       </c>
       <c r="B80" t="n">
-        <v>1983</v>
+        <v>629</v>
       </c>
       <c r="C80" t="n">
-        <v>841</v>
+        <v>8888</v>
       </c>
       <c r="D80" t="n">
-        <v>633.79</v>
+        <v>13218.63</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1965,17 +1965,17 @@
         <v>46218</v>
       </c>
       <c r="B81" t="n">
-        <v>1137</v>
+        <v>1983</v>
       </c>
       <c r="C81" t="n">
-        <v>8888</v>
+        <v>841</v>
       </c>
       <c r="D81" t="n">
-        <v>4842.54</v>
+        <v>633.79</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1984,17 +1984,17 @@
         <v>46218</v>
       </c>
       <c r="B82" t="n">
-        <v>2651</v>
+        <v>1137</v>
       </c>
       <c r="C82" t="n">
         <v>8888</v>
       </c>
       <c r="D82" t="n">
-        <v>1296.58</v>
+        <v>4842.54</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2003,17 +2003,17 @@
         <v>46218</v>
       </c>
       <c r="B83" t="n">
-        <v>2789</v>
+        <v>2651</v>
       </c>
       <c r="C83" t="n">
         <v>8888</v>
       </c>
       <c r="D83" t="n">
-        <v>1293.93</v>
+        <v>1296.58</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2022,17 +2022,17 @@
         <v>46218</v>
       </c>
       <c r="B84" t="n">
-        <v>1956</v>
+        <v>2789</v>
       </c>
       <c r="C84" t="n">
-        <v>423</v>
+        <v>8888</v>
       </c>
       <c r="D84" t="n">
-        <v>1416.35</v>
+        <v>1293.93</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2041,17 +2041,17 @@
         <v>46218</v>
       </c>
       <c r="B85" t="n">
-        <v>2709</v>
+        <v>1956</v>
       </c>
       <c r="C85" t="n">
-        <v>8888</v>
+        <v>423</v>
       </c>
       <c r="D85" t="n">
-        <v>547.6900000000001</v>
+        <v>1416.35</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2060,13 +2060,13 @@
         <v>46218</v>
       </c>
       <c r="B86" t="n">
-        <v>1308</v>
+        <v>2709</v>
       </c>
       <c r="C86" t="n">
         <v>8888</v>
       </c>
       <c r="D86" t="n">
-        <v>2264.86</v>
+        <v>547.6900000000001</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -2383,13 +2383,13 @@
         <v>46218</v>
       </c>
       <c r="B103" t="n">
-        <v>2768</v>
+        <v>2402</v>
       </c>
       <c r="C103" t="n">
         <v>8888</v>
       </c>
       <c r="D103" t="n">
-        <v>7812.09</v>
+        <v>1998.28</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         <v>46218</v>
       </c>
       <c r="B104" t="n">
-        <v>1063</v>
+        <v>1906</v>
       </c>
       <c r="C104" t="n">
         <v>8888</v>
       </c>
       <c r="D104" t="n">
-        <v>4487.11</v>
+        <v>3504.37</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -2421,17 +2421,17 @@
         <v>46218</v>
       </c>
       <c r="B105" t="n">
-        <v>947</v>
+        <v>2768</v>
       </c>
       <c r="C105" t="n">
         <v>8888</v>
       </c>
       <c r="D105" t="n">
-        <v>5667.85</v>
+        <v>7812.09</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>PEDIDO ELETRÔNICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2440,17 +2440,17 @@
         <v>46218</v>
       </c>
       <c r="B106" t="n">
-        <v>2279</v>
+        <v>1063</v>
       </c>
       <c r="C106" t="n">
-        <v>1139</v>
+        <v>8888</v>
       </c>
       <c r="D106" t="n">
-        <v>1031.06</v>
+        <v>4487.11</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2459,17 +2459,17 @@
         <v>46218</v>
       </c>
       <c r="B107" t="n">
-        <v>1299</v>
+        <v>947</v>
       </c>
       <c r="C107" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D107" t="n">
-        <v>1435.52</v>
+        <v>7409.08</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>PEDIDO ELETRÔNICO</t>
         </is>
       </c>
     </row>
@@ -2478,13 +2478,13 @@
         <v>46218</v>
       </c>
       <c r="B108" t="n">
-        <v>1478</v>
+        <v>2279</v>
       </c>
       <c r="C108" t="n">
-        <v>675</v>
+        <v>1139</v>
       </c>
       <c r="D108" t="n">
-        <v>1967.85</v>
+        <v>1031.06</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -2497,17 +2497,17 @@
         <v>46218</v>
       </c>
       <c r="B109" t="n">
-        <v>675</v>
+        <v>1299</v>
       </c>
       <c r="C109" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D109" t="n">
-        <v>2685.73</v>
+        <v>1435.52</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2516,17 +2516,17 @@
         <v>46218</v>
       </c>
       <c r="B110" t="n">
-        <v>767</v>
+        <v>1478</v>
       </c>
       <c r="C110" t="n">
-        <v>8888</v>
+        <v>675</v>
       </c>
       <c r="D110" t="n">
-        <v>3292.44</v>
+        <v>1967.85</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2535,17 +2535,17 @@
         <v>46218</v>
       </c>
       <c r="B111" t="n">
-        <v>285</v>
+        <v>675</v>
       </c>
       <c r="C111" t="n">
         <v>8888</v>
       </c>
       <c r="D111" t="n">
-        <v>3349.8</v>
+        <v>2685.73</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2554,17 +2554,17 @@
         <v>46218</v>
       </c>
       <c r="B112" t="n">
-        <v>477</v>
+        <v>767</v>
       </c>
       <c r="C112" t="n">
         <v>8888</v>
       </c>
       <c r="D112" t="n">
-        <v>917.33</v>
+        <v>3292.44</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2573,17 +2573,17 @@
         <v>46218</v>
       </c>
       <c r="B113" t="n">
-        <v>1983</v>
+        <v>285</v>
       </c>
       <c r="C113" t="n">
         <v>8888</v>
       </c>
       <c r="D113" t="n">
-        <v>5115.01</v>
+        <v>3349.8</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2595,14 +2595,14 @@
         <v>477</v>
       </c>
       <c r="C114" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D114" t="n">
-        <v>3946.44</v>
+        <v>917.33</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2611,13 +2611,13 @@
         <v>46218</v>
       </c>
       <c r="B115" t="n">
-        <v>1937</v>
+        <v>1983</v>
       </c>
       <c r="C115" t="n">
         <v>8888</v>
       </c>
       <c r="D115" t="n">
-        <v>2600.61</v>
+        <v>5115.01</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -2630,17 +2630,17 @@
         <v>46218</v>
       </c>
       <c r="B116" t="n">
-        <v>363</v>
+        <v>477</v>
       </c>
       <c r="C116" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D116" t="n">
-        <v>780.35</v>
+        <v>3946.44</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2649,17 +2649,17 @@
         <v>46218</v>
       </c>
       <c r="B117" t="n">
-        <v>1063</v>
+        <v>1937</v>
       </c>
       <c r="C117" t="n">
         <v>8888</v>
       </c>
       <c r="D117" t="n">
-        <v>2549.86</v>
+        <v>2600.61</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2668,13 +2668,13 @@
         <v>46218</v>
       </c>
       <c r="B118" t="n">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C118" t="n">
         <v>8888</v>
       </c>
       <c r="D118" t="n">
-        <v>5917.55</v>
+        <v>780.35</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -2687,17 +2687,17 @@
         <v>46218</v>
       </c>
       <c r="B119" t="n">
-        <v>2584</v>
+        <v>1063</v>
       </c>
       <c r="C119" t="n">
-        <v>1929</v>
+        <v>8888</v>
       </c>
       <c r="D119" t="n">
-        <v>756.16</v>
+        <v>4359.02</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2706,17 +2706,17 @@
         <v>46218</v>
       </c>
       <c r="B120" t="n">
-        <v>58</v>
+        <v>360</v>
       </c>
       <c r="C120" t="n">
         <v>8888</v>
       </c>
       <c r="D120" t="n">
-        <v>558.03</v>
+        <v>5917.55</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2725,17 +2725,17 @@
         <v>46218</v>
       </c>
       <c r="B121" t="n">
-        <v>424</v>
+        <v>2584</v>
       </c>
       <c r="C121" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D121" t="n">
-        <v>1362.42</v>
+        <v>756.16</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2744,17 +2744,17 @@
         <v>46218</v>
       </c>
       <c r="B122" t="n">
-        <v>663</v>
+        <v>58</v>
       </c>
       <c r="C122" t="n">
         <v>8888</v>
       </c>
       <c r="D122" t="n">
-        <v>255.13</v>
+        <v>558.03</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2763,17 +2763,17 @@
         <v>46218</v>
       </c>
       <c r="B123" t="n">
-        <v>1993</v>
+        <v>424</v>
       </c>
       <c r="C123" t="n">
         <v>8888</v>
       </c>
       <c r="D123" t="n">
-        <v>724.14</v>
+        <v>1362.42</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2782,17 +2782,17 @@
         <v>46218</v>
       </c>
       <c r="B124" t="n">
-        <v>1465</v>
+        <v>663</v>
       </c>
       <c r="C124" t="n">
         <v>8888</v>
       </c>
       <c r="D124" t="n">
-        <v>7362.56</v>
+        <v>255.13</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2801,13 +2801,13 @@
         <v>46218</v>
       </c>
       <c r="B125" t="n">
-        <v>89</v>
+        <v>1993</v>
       </c>
       <c r="C125" t="n">
         <v>8888</v>
       </c>
       <c r="D125" t="n">
-        <v>479</v>
+        <v>724.14</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -2820,13 +2820,13 @@
         <v>46218</v>
       </c>
       <c r="B126" t="n">
-        <v>595</v>
+        <v>1465</v>
       </c>
       <c r="C126" t="n">
         <v>8888</v>
       </c>
       <c r="D126" t="n">
-        <v>18084.5</v>
+        <v>7362.56</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -2839,17 +2839,17 @@
         <v>46218</v>
       </c>
       <c r="B127" t="n">
-        <v>2696</v>
+        <v>89</v>
       </c>
       <c r="C127" t="n">
-        <v>1954</v>
+        <v>8888</v>
       </c>
       <c r="D127" t="n">
-        <v>1597.76</v>
+        <v>479</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2858,17 +2858,17 @@
         <v>46218</v>
       </c>
       <c r="B128" t="n">
-        <v>1465</v>
+        <v>595</v>
       </c>
       <c r="C128" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D128" t="n">
-        <v>777.2</v>
+        <v>18084.5</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2877,17 +2877,17 @@
         <v>46218</v>
       </c>
       <c r="B129" t="n">
-        <v>2178</v>
+        <v>2696</v>
       </c>
       <c r="C129" t="n">
-        <v>8888</v>
+        <v>1954</v>
       </c>
       <c r="D129" t="n">
-        <v>619.92</v>
+        <v>1597.76</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2896,13 +2896,13 @@
         <v>46218</v>
       </c>
       <c r="B130" t="n">
-        <v>2026</v>
+        <v>1465</v>
       </c>
       <c r="C130" t="n">
-        <v>1929</v>
+        <v>3403</v>
       </c>
       <c r="D130" t="n">
-        <v>6021.92</v>
+        <v>777.2</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -2915,17 +2915,17 @@
         <v>46218</v>
       </c>
       <c r="B131" t="n">
-        <v>630</v>
+        <v>2178</v>
       </c>
       <c r="C131" t="n">
-        <v>1929</v>
+        <v>8888</v>
       </c>
       <c r="D131" t="n">
-        <v>1801.63</v>
+        <v>619.92</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2934,17 +2934,17 @@
         <v>46218</v>
       </c>
       <c r="B132" t="n">
-        <v>1937</v>
+        <v>2026</v>
       </c>
       <c r="C132" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D132" t="n">
-        <v>2132.95</v>
+        <v>6021.92</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2953,17 +2953,17 @@
         <v>46218</v>
       </c>
       <c r="B133" t="n">
-        <v>2577</v>
+        <v>630</v>
       </c>
       <c r="C133" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D133" t="n">
-        <v>1647.08</v>
+        <v>1801.63</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2972,13 +2972,13 @@
         <v>46218</v>
       </c>
       <c r="B134" t="n">
-        <v>1293</v>
+        <v>1937</v>
       </c>
       <c r="C134" t="n">
         <v>8888</v>
       </c>
       <c r="D134" t="n">
-        <v>2135.89</v>
+        <v>2132.95</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -2991,13 +2991,13 @@
         <v>46218</v>
       </c>
       <c r="B135" t="n">
-        <v>2607</v>
+        <v>2577</v>
       </c>
       <c r="C135" t="n">
         <v>8888</v>
       </c>
       <c r="D135" t="n">
-        <v>490.31</v>
+        <v>1647.08</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -3010,17 +3010,17 @@
         <v>46218</v>
       </c>
       <c r="B136" t="n">
-        <v>1317</v>
+        <v>1293</v>
       </c>
       <c r="C136" t="n">
         <v>8888</v>
       </c>
       <c r="D136" t="n">
-        <v>907.72</v>
+        <v>2135.89</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3029,13 +3029,13 @@
         <v>46218</v>
       </c>
       <c r="B137" t="n">
-        <v>535</v>
+        <v>2571</v>
       </c>
       <c r="C137" t="n">
-        <v>2571</v>
+        <v>1312</v>
       </c>
       <c r="D137" t="n">
-        <v>1124.46</v>
+        <v>1523.15</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -3048,17 +3048,17 @@
         <v>46218</v>
       </c>
       <c r="B138" t="n">
-        <v>675</v>
+        <v>2607</v>
       </c>
       <c r="C138" t="n">
         <v>8888</v>
       </c>
       <c r="D138" t="n">
-        <v>337.89</v>
+        <v>490.31</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3067,17 +3067,17 @@
         <v>46218</v>
       </c>
       <c r="B139" t="n">
-        <v>2571</v>
+        <v>1317</v>
       </c>
       <c r="C139" t="n">
-        <v>1312</v>
+        <v>8888</v>
       </c>
       <c r="D139" t="n">
-        <v>743.01</v>
+        <v>907.72</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3086,17 +3086,17 @@
         <v>46218</v>
       </c>
       <c r="B140" t="n">
-        <v>619</v>
+        <v>535</v>
       </c>
       <c r="C140" t="n">
-        <v>8888</v>
+        <v>2571</v>
       </c>
       <c r="D140" t="n">
-        <v>1081.74</v>
+        <v>1124.46</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3105,13 +3105,13 @@
         <v>46218</v>
       </c>
       <c r="B141" t="n">
-        <v>20</v>
+        <v>2510</v>
       </c>
       <c r="C141" t="n">
         <v>8888</v>
       </c>
       <c r="D141" t="n">
-        <v>745.55</v>
+        <v>8587.950000000001</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -3124,13 +3124,13 @@
         <v>46218</v>
       </c>
       <c r="B142" t="n">
-        <v>1063</v>
+        <v>675</v>
       </c>
       <c r="C142" t="n">
         <v>8888</v>
       </c>
       <c r="D142" t="n">
-        <v>1113.08</v>
+        <v>337.89</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -3143,17 +3143,17 @@
         <v>46218</v>
       </c>
       <c r="B143" t="n">
-        <v>2631</v>
+        <v>619</v>
       </c>
       <c r="C143" t="n">
         <v>8888</v>
       </c>
       <c r="D143" t="n">
-        <v>1447.86</v>
+        <v>1081.74</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3162,13 +3162,13 @@
         <v>46218</v>
       </c>
       <c r="B144" t="n">
-        <v>1906</v>
+        <v>20</v>
       </c>
       <c r="C144" t="n">
         <v>8888</v>
       </c>
       <c r="D144" t="n">
-        <v>2774.84</v>
+        <v>745.55</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -3181,17 +3181,17 @@
         <v>46218</v>
       </c>
       <c r="B145" t="n">
-        <v>1756</v>
+        <v>2118</v>
       </c>
       <c r="C145" t="n">
-        <v>8888</v>
+        <v>1954</v>
       </c>
       <c r="D145" t="n">
-        <v>2275.21</v>
+        <v>804.16</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3200,13 +3200,13 @@
         <v>46218</v>
       </c>
       <c r="B146" t="n">
-        <v>477</v>
+        <v>1063</v>
       </c>
       <c r="C146" t="n">
         <v>8888</v>
       </c>
       <c r="D146" t="n">
-        <v>707.52</v>
+        <v>1113.08</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -3219,13 +3219,13 @@
         <v>46218</v>
       </c>
       <c r="B147" t="n">
-        <v>2660</v>
+        <v>2631</v>
       </c>
       <c r="C147" t="n">
         <v>8888</v>
       </c>
       <c r="D147" t="n">
-        <v>2684.97</v>
+        <v>1447.86</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -3238,17 +3238,17 @@
         <v>46218</v>
       </c>
       <c r="B148" t="n">
-        <v>569</v>
+        <v>1756</v>
       </c>
       <c r="C148" t="n">
         <v>8888</v>
       </c>
       <c r="D148" t="n">
-        <v>43745.83</v>
+        <v>2275.21</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3257,13 +3257,13 @@
         <v>46218</v>
       </c>
       <c r="B149" t="n">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="C149" t="n">
         <v>8888</v>
       </c>
       <c r="D149" t="n">
-        <v>3102.48</v>
+        <v>707.52</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -3276,17 +3276,17 @@
         <v>46218</v>
       </c>
       <c r="B150" t="n">
-        <v>609</v>
+        <v>2660</v>
       </c>
       <c r="C150" t="n">
         <v>8888</v>
       </c>
       <c r="D150" t="n">
-        <v>1633.68</v>
+        <v>2684.97</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3295,13 +3295,13 @@
         <v>46218</v>
       </c>
       <c r="B151" t="n">
-        <v>483</v>
+        <v>569</v>
       </c>
       <c r="C151" t="n">
         <v>8888</v>
       </c>
       <c r="D151" t="n">
-        <v>2011.13</v>
+        <v>43745.83</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -3314,17 +3314,17 @@
         <v>46218</v>
       </c>
       <c r="B152" t="n">
-        <v>2089</v>
+        <v>483</v>
       </c>
       <c r="C152" t="n">
-        <v>1533</v>
+        <v>8888</v>
       </c>
       <c r="D152" t="n">
-        <v>1309.01</v>
+        <v>3102.48</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3333,17 +3333,17 @@
         <v>46218</v>
       </c>
       <c r="B153" t="n">
-        <v>1007</v>
+        <v>609</v>
       </c>
       <c r="C153" t="n">
         <v>8888</v>
       </c>
       <c r="D153" t="n">
-        <v>241.44</v>
+        <v>1633.68</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
         <v>46218</v>
       </c>
       <c r="B154" t="n">
-        <v>1380</v>
+        <v>483</v>
       </c>
       <c r="C154" t="n">
         <v>8888</v>
       </c>
       <c r="D154" t="n">
-        <v>520.2</v>
+        <v>2011.13</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3371,17 +3371,17 @@
         <v>46218</v>
       </c>
       <c r="B155" t="n">
-        <v>1102</v>
+        <v>2089</v>
       </c>
       <c r="C155" t="n">
-        <v>8888</v>
+        <v>1533</v>
       </c>
       <c r="D155" t="n">
-        <v>1137.04</v>
+        <v>1309.01</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3390,17 +3390,17 @@
         <v>46218</v>
       </c>
       <c r="B156" t="n">
-        <v>358</v>
+        <v>1007</v>
       </c>
       <c r="C156" t="n">
         <v>8888</v>
       </c>
       <c r="D156" t="n">
-        <v>3380.3</v>
+        <v>241.44</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3409,13 +3409,13 @@
         <v>46218</v>
       </c>
       <c r="B157" t="n">
-        <v>1075</v>
+        <v>1380</v>
       </c>
       <c r="C157" t="n">
         <v>8888</v>
       </c>
       <c r="D157" t="n">
-        <v>5710.94</v>
+        <v>520.2</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -3428,17 +3428,17 @@
         <v>46218</v>
       </c>
       <c r="B158" t="n">
-        <v>2681</v>
+        <v>1102</v>
       </c>
       <c r="C158" t="n">
         <v>8888</v>
       </c>
       <c r="D158" t="n">
-        <v>729.25</v>
+        <v>1137.04</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3447,17 +3447,17 @@
         <v>46218</v>
       </c>
       <c r="B159" t="n">
-        <v>2245</v>
+        <v>358</v>
       </c>
       <c r="C159" t="n">
         <v>8888</v>
       </c>
       <c r="D159" t="n">
-        <v>700.2</v>
+        <v>3380.3</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3466,17 +3466,17 @@
         <v>46218</v>
       </c>
       <c r="B160" t="n">
-        <v>40</v>
+        <v>1075</v>
       </c>
       <c r="C160" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D160" t="n">
-        <v>678.21</v>
+        <v>5710.94</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3485,17 +3485,17 @@
         <v>46218</v>
       </c>
       <c r="B161" t="n">
-        <v>33</v>
+        <v>2681</v>
       </c>
       <c r="C161" t="n">
         <v>8888</v>
       </c>
       <c r="D161" t="n">
-        <v>926.97</v>
+        <v>729.25</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3504,17 +3504,17 @@
         <v>46218</v>
       </c>
       <c r="B162" t="n">
-        <v>132</v>
+        <v>2245</v>
       </c>
       <c r="C162" t="n">
         <v>8888</v>
       </c>
       <c r="D162" t="n">
-        <v>6522.92</v>
+        <v>700.2</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3523,17 +3523,17 @@
         <v>46218</v>
       </c>
       <c r="B163" t="n">
-        <v>619</v>
+        <v>40</v>
       </c>
       <c r="C163" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D163" t="n">
-        <v>2912.89</v>
+        <v>678.21</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3542,17 +3542,17 @@
         <v>46218</v>
       </c>
       <c r="B164" t="n">
-        <v>2769</v>
+        <v>33</v>
       </c>
       <c r="C164" t="n">
-        <v>977</v>
+        <v>8888</v>
       </c>
       <c r="D164" t="n">
-        <v>1116.56</v>
+        <v>926.97</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3561,17 +3561,17 @@
         <v>46218</v>
       </c>
       <c r="B165" t="n">
-        <v>452</v>
+        <v>2463</v>
       </c>
       <c r="C165" t="n">
         <v>8888</v>
       </c>
       <c r="D165" t="n">
-        <v>608.78</v>
+        <v>887.74</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3580,17 +3580,17 @@
         <v>46218</v>
       </c>
       <c r="B166" t="n">
-        <v>2463</v>
+        <v>132</v>
       </c>
       <c r="C166" t="n">
         <v>8888</v>
       </c>
       <c r="D166" t="n">
-        <v>363.69</v>
+        <v>6522.92</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3599,17 +3599,17 @@
         <v>46218</v>
       </c>
       <c r="B167" t="n">
-        <v>1293</v>
+        <v>619</v>
       </c>
       <c r="C167" t="n">
-        <v>1281</v>
+        <v>8888</v>
       </c>
       <c r="D167" t="n">
-        <v>1780.93</v>
+        <v>2912.89</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3618,17 +3618,17 @@
         <v>46218</v>
       </c>
       <c r="B168" t="n">
-        <v>525</v>
+        <v>2769</v>
       </c>
       <c r="C168" t="n">
-        <v>8888</v>
+        <v>977</v>
       </c>
       <c r="D168" t="n">
-        <v>5658.57</v>
+        <v>1116.56</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3637,17 +3637,17 @@
         <v>46218</v>
       </c>
       <c r="B169" t="n">
-        <v>2641</v>
+        <v>452</v>
       </c>
       <c r="C169" t="n">
         <v>8888</v>
       </c>
       <c r="D169" t="n">
-        <v>1720.99</v>
+        <v>608.78</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3656,13 +3656,13 @@
         <v>46218</v>
       </c>
       <c r="B170" t="n">
-        <v>675</v>
+        <v>1293</v>
       </c>
       <c r="C170" t="n">
-        <v>1898</v>
+        <v>1281</v>
       </c>
       <c r="D170" t="n">
-        <v>504.07</v>
+        <v>2292.86</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -3675,17 +3675,17 @@
         <v>46218</v>
       </c>
       <c r="B171" t="n">
-        <v>58</v>
+        <v>525</v>
       </c>
       <c r="C171" t="n">
         <v>8888</v>
       </c>
       <c r="D171" t="n">
-        <v>4929.8</v>
+        <v>5658.57</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3694,17 +3694,17 @@
         <v>46218</v>
       </c>
       <c r="B172" t="n">
-        <v>358</v>
+        <v>2641</v>
       </c>
       <c r="C172" t="n">
-        <v>546</v>
+        <v>8888</v>
       </c>
       <c r="D172" t="n">
-        <v>862.4400000000001</v>
+        <v>1720.99</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3713,13 +3713,13 @@
         <v>46218</v>
       </c>
       <c r="B173" t="n">
-        <v>325</v>
+        <v>675</v>
       </c>
       <c r="C173" t="n">
-        <v>1098</v>
+        <v>1898</v>
       </c>
       <c r="D173" t="n">
-        <v>50.06</v>
+        <v>504.07</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>46218</v>
       </c>
       <c r="B174" t="n">
-        <v>2697</v>
+        <v>58</v>
       </c>
       <c r="C174" t="n">
         <v>8888</v>
       </c>
       <c r="D174" t="n">
-        <v>833.38</v>
+        <v>4929.8</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -3751,13 +3751,13 @@
         <v>46218</v>
       </c>
       <c r="B175" t="n">
-        <v>2472</v>
+        <v>358</v>
       </c>
       <c r="C175" t="n">
-        <v>2853</v>
+        <v>546</v>
       </c>
       <c r="D175" t="n">
-        <v>1402.64</v>
+        <v>862.4400000000001</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -3770,13 +3770,13 @@
         <v>46218</v>
       </c>
       <c r="B176" t="n">
-        <v>2431</v>
+        <v>2606</v>
       </c>
       <c r="C176" t="n">
         <v>8888</v>
       </c>
       <c r="D176" t="n">
-        <v>266.89</v>
+        <v>2939.17</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -3789,17 +3789,17 @@
         <v>46218</v>
       </c>
       <c r="B177" t="n">
-        <v>285</v>
+        <v>325</v>
       </c>
       <c r="C177" t="n">
-        <v>8888</v>
+        <v>1098</v>
       </c>
       <c r="D177" t="n">
-        <v>5673.85</v>
+        <v>50.06</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3808,17 +3808,17 @@
         <v>46218</v>
       </c>
       <c r="B178" t="n">
-        <v>1102</v>
+        <v>2697</v>
       </c>
       <c r="C178" t="n">
         <v>8888</v>
       </c>
       <c r="D178" t="n">
-        <v>2301.43</v>
+        <v>833.38</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3827,17 +3827,17 @@
         <v>46218</v>
       </c>
       <c r="B179" t="n">
-        <v>2793</v>
+        <v>2472</v>
       </c>
       <c r="C179" t="n">
-        <v>8888</v>
+        <v>2853</v>
       </c>
       <c r="D179" t="n">
-        <v>1238.11</v>
+        <v>1402.64</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3846,17 +3846,17 @@
         <v>46218</v>
       </c>
       <c r="B180" t="n">
-        <v>626</v>
+        <v>2431</v>
       </c>
       <c r="C180" t="n">
         <v>8888</v>
       </c>
       <c r="D180" t="n">
-        <v>23157.24</v>
+        <v>266.89</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3865,13 +3865,13 @@
         <v>46218</v>
       </c>
       <c r="B181" t="n">
-        <v>424</v>
+        <v>285</v>
       </c>
       <c r="C181" t="n">
         <v>8888</v>
       </c>
       <c r="D181" t="n">
-        <v>1124.8</v>
+        <v>5673.85</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -3884,17 +3884,17 @@
         <v>46218</v>
       </c>
       <c r="B182" t="n">
-        <v>1137</v>
+        <v>1102</v>
       </c>
       <c r="C182" t="n">
-        <v>2220</v>
+        <v>8888</v>
       </c>
       <c r="D182" t="n">
-        <v>3285.55</v>
+        <v>2301.43</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3903,17 +3903,17 @@
         <v>46218</v>
       </c>
       <c r="B183" t="n">
-        <v>1299</v>
+        <v>2793</v>
       </c>
       <c r="C183" t="n">
-        <v>2522</v>
+        <v>8888</v>
       </c>
       <c r="D183" t="n">
-        <v>8881.309999999999</v>
+        <v>1238.11</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3922,17 +3922,17 @@
         <v>46218</v>
       </c>
       <c r="B184" t="n">
-        <v>1289</v>
+        <v>626</v>
       </c>
       <c r="C184" t="n">
         <v>8888</v>
       </c>
       <c r="D184" t="n">
-        <v>5565.44</v>
+        <v>23157.24</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3941,17 +3941,17 @@
         <v>46218</v>
       </c>
       <c r="B185" t="n">
-        <v>2686</v>
+        <v>424</v>
       </c>
       <c r="C185" t="n">
-        <v>1929</v>
+        <v>8888</v>
       </c>
       <c r="D185" t="n">
-        <v>2066.36</v>
+        <v>1124.8</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3960,17 +3960,17 @@
         <v>46218</v>
       </c>
       <c r="B186" t="n">
-        <v>629</v>
+        <v>1137</v>
       </c>
       <c r="C186" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D186" t="n">
-        <v>5212.76</v>
+        <v>3285.55</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3979,17 +3979,17 @@
         <v>46218</v>
       </c>
       <c r="B187" t="n">
-        <v>636</v>
+        <v>1299</v>
       </c>
       <c r="C187" t="n">
-        <v>8888</v>
+        <v>2522</v>
       </c>
       <c r="D187" t="n">
-        <v>5742.49</v>
+        <v>8881.309999999999</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3998,17 +3998,17 @@
         <v>46218</v>
       </c>
       <c r="B188" t="n">
-        <v>2584</v>
+        <v>1289</v>
       </c>
       <c r="C188" t="n">
         <v>8888</v>
       </c>
       <c r="D188" t="n">
-        <v>5635.67</v>
+        <v>5565.44</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4017,17 +4017,17 @@
         <v>46218</v>
       </c>
       <c r="B189" t="n">
-        <v>1756</v>
+        <v>2686</v>
       </c>
       <c r="C189" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D189" t="n">
-        <v>3242.54</v>
+        <v>2066.36</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4036,13 +4036,13 @@
         <v>46218</v>
       </c>
       <c r="B190" t="n">
-        <v>2698</v>
+        <v>629</v>
       </c>
       <c r="C190" t="n">
         <v>8888</v>
       </c>
       <c r="D190" t="n">
-        <v>859.49</v>
+        <v>5212.76</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -4055,17 +4055,17 @@
         <v>46218</v>
       </c>
       <c r="B191" t="n">
-        <v>1756</v>
+        <v>636</v>
       </c>
       <c r="C191" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D191" t="n">
-        <v>5078.1</v>
+        <v>5742.49</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4074,17 +4074,17 @@
         <v>46218</v>
       </c>
       <c r="B192" t="n">
-        <v>2651</v>
+        <v>2584</v>
       </c>
       <c r="C192" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D192" t="n">
-        <v>363.7</v>
+        <v>5635.67</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4093,13 +4093,13 @@
         <v>46218</v>
       </c>
       <c r="B193" t="n">
-        <v>664</v>
+        <v>1756</v>
       </c>
       <c r="C193" t="n">
         <v>8888</v>
       </c>
       <c r="D193" t="n">
-        <v>6478.17</v>
+        <v>3242.54</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -4112,17 +4112,17 @@
         <v>46218</v>
       </c>
       <c r="B194" t="n">
-        <v>360</v>
+        <v>2698</v>
       </c>
       <c r="C194" t="n">
         <v>8888</v>
       </c>
       <c r="D194" t="n">
-        <v>1594.84</v>
+        <v>859.49</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4131,17 +4131,17 @@
         <v>46218</v>
       </c>
       <c r="B195" t="n">
-        <v>2582</v>
+        <v>1756</v>
       </c>
       <c r="C195" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D195" t="n">
-        <v>379.33</v>
+        <v>5078.1</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4150,17 +4150,17 @@
         <v>46218</v>
       </c>
       <c r="B196" t="n">
-        <v>1254</v>
+        <v>2651</v>
       </c>
       <c r="C196" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D196" t="n">
-        <v>2643.22</v>
+        <v>363.7</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4169,17 +4169,17 @@
         <v>46218</v>
       </c>
       <c r="B197" t="n">
-        <v>2726</v>
+        <v>664</v>
       </c>
       <c r="C197" t="n">
-        <v>977</v>
+        <v>8888</v>
       </c>
       <c r="D197" t="n">
-        <v>586.0599999999999</v>
+        <v>6478.17</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4188,17 +4188,17 @@
         <v>46218</v>
       </c>
       <c r="B198" t="n">
-        <v>2015</v>
+        <v>360</v>
       </c>
       <c r="C198" t="n">
         <v>8888</v>
       </c>
       <c r="D198" t="n">
-        <v>315.69</v>
+        <v>1594.84</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4207,17 +4207,17 @@
         <v>46218</v>
       </c>
       <c r="B199" t="n">
-        <v>1064</v>
+        <v>2582</v>
       </c>
       <c r="C199" t="n">
         <v>8888</v>
       </c>
       <c r="D199" t="n">
-        <v>1274.3</v>
+        <v>379.33</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4226,17 +4226,17 @@
         <v>46218</v>
       </c>
       <c r="B200" t="n">
-        <v>358</v>
+        <v>2698</v>
       </c>
       <c r="C200" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D200" t="n">
-        <v>2619.4</v>
+        <v>440.3</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4245,17 +4245,17 @@
         <v>46218</v>
       </c>
       <c r="B201" t="n">
-        <v>2641</v>
+        <v>1254</v>
       </c>
       <c r="C201" t="n">
         <v>8888</v>
       </c>
       <c r="D201" t="n">
-        <v>820</v>
+        <v>2643.22</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4264,17 +4264,17 @@
         <v>46218</v>
       </c>
       <c r="B202" t="n">
-        <v>429</v>
+        <v>2726</v>
       </c>
       <c r="C202" t="n">
-        <v>8888</v>
+        <v>977</v>
       </c>
       <c r="D202" t="n">
-        <v>2593.49</v>
+        <v>586.0599999999999</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4283,17 +4283,17 @@
         <v>46218</v>
       </c>
       <c r="B203" t="n">
-        <v>1301</v>
+        <v>2015</v>
       </c>
       <c r="C203" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D203" t="n">
-        <v>750.66</v>
+        <v>315.69</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4302,13 +4302,13 @@
         <v>46218</v>
       </c>
       <c r="B204" t="n">
-        <v>816</v>
+        <v>1064</v>
       </c>
       <c r="C204" t="n">
         <v>8888</v>
       </c>
       <c r="D204" t="n">
-        <v>438.24</v>
+        <v>1274.3</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -4321,13 +4321,13 @@
         <v>46218</v>
       </c>
       <c r="B205" t="n">
-        <v>2359</v>
+        <v>358</v>
       </c>
       <c r="C205" t="n">
         <v>8888</v>
       </c>
       <c r="D205" t="n">
-        <v>381.95</v>
+        <v>4129.47</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -4340,17 +4340,17 @@
         <v>46218</v>
       </c>
       <c r="B206" t="n">
-        <v>2251</v>
+        <v>2641</v>
       </c>
       <c r="C206" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D206" t="n">
-        <v>802.08</v>
+        <v>820</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4359,17 +4359,17 @@
         <v>46218</v>
       </c>
       <c r="B207" t="n">
-        <v>285</v>
+        <v>429</v>
       </c>
       <c r="C207" t="n">
-        <v>58</v>
+        <v>8888</v>
       </c>
       <c r="D207" t="n">
-        <v>1797.95</v>
+        <v>2593.49</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4378,17 +4378,17 @@
         <v>46218</v>
       </c>
       <c r="B208" t="n">
-        <v>2114</v>
+        <v>1301</v>
       </c>
       <c r="C208" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D208" t="n">
-        <v>2726.04</v>
+        <v>750.66</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4397,17 +4397,17 @@
         <v>46218</v>
       </c>
       <c r="B209" t="n">
-        <v>953</v>
+        <v>816</v>
       </c>
       <c r="C209" t="n">
         <v>8888</v>
       </c>
       <c r="D209" t="n">
-        <v>2889.63</v>
+        <v>438.24</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4416,17 +4416,17 @@
         <v>46218</v>
       </c>
       <c r="B210" t="n">
-        <v>1102</v>
+        <v>2249</v>
       </c>
       <c r="C210" t="n">
         <v>8888</v>
       </c>
       <c r="D210" t="n">
-        <v>6347.79</v>
+        <v>3047.57</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4435,17 +4435,17 @@
         <v>46218</v>
       </c>
       <c r="B211" t="n">
-        <v>1465</v>
+        <v>2359</v>
       </c>
       <c r="C211" t="n">
         <v>8888</v>
       </c>
       <c r="D211" t="n">
-        <v>4281.39</v>
+        <v>381.95</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4454,17 +4454,17 @@
         <v>46218</v>
       </c>
       <c r="B212" t="n">
-        <v>619</v>
+        <v>2251</v>
       </c>
       <c r="C212" t="n">
-        <v>8888</v>
+        <v>3403</v>
       </c>
       <c r="D212" t="n">
-        <v>2021.67</v>
+        <v>802.08</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4473,17 +4473,17 @@
         <v>46218</v>
       </c>
       <c r="B213" t="n">
-        <v>2716</v>
+        <v>285</v>
       </c>
       <c r="C213" t="n">
-        <v>8888</v>
+        <v>58</v>
       </c>
       <c r="D213" t="n">
-        <v>1063.42</v>
+        <v>1797.95</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4492,17 +4492,17 @@
         <v>46218</v>
       </c>
       <c r="B214" t="n">
-        <v>2767</v>
+        <v>2114</v>
       </c>
       <c r="C214" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D214" t="n">
-        <v>1135.64</v>
+        <v>2726.04</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4511,17 +4511,17 @@
         <v>46218</v>
       </c>
       <c r="B215" t="n">
-        <v>2657</v>
+        <v>1137</v>
       </c>
       <c r="C215" t="n">
-        <v>8888</v>
+        <v>874</v>
       </c>
       <c r="D215" t="n">
-        <v>3149.7</v>
+        <v>444.86</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4530,17 +4530,17 @@
         <v>46218</v>
       </c>
       <c r="B216" t="n">
-        <v>2245</v>
+        <v>953</v>
       </c>
       <c r="C216" t="n">
         <v>8888</v>
       </c>
       <c r="D216" t="n">
-        <v>764.66</v>
+        <v>2889.63</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4549,17 +4549,17 @@
         <v>46218</v>
       </c>
       <c r="B217" t="n">
-        <v>2197</v>
+        <v>1102</v>
       </c>
       <c r="C217" t="n">
         <v>8888</v>
       </c>
       <c r="D217" t="n">
-        <v>1085.45</v>
+        <v>6347.79</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4568,17 +4568,17 @@
         <v>46218</v>
       </c>
       <c r="B218" t="n">
-        <v>1064</v>
+        <v>1465</v>
       </c>
       <c r="C218" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D218" t="n">
-        <v>574.7</v>
+        <v>4281.39</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4587,17 +4587,17 @@
         <v>46218</v>
       </c>
       <c r="B219" t="n">
-        <v>451</v>
+        <v>619</v>
       </c>
       <c r="C219" t="n">
-        <v>3403</v>
+        <v>8888</v>
       </c>
       <c r="D219" t="n">
-        <v>2091.77</v>
+        <v>2021.67</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4606,17 +4606,17 @@
         <v>46218</v>
       </c>
       <c r="B220" t="n">
-        <v>1116</v>
+        <v>2716</v>
       </c>
       <c r="C220" t="n">
-        <v>13148</v>
+        <v>8888</v>
       </c>
       <c r="D220" t="n">
-        <v>1455.21</v>
+        <v>1063.42</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4625,17 +4625,17 @@
         <v>46218</v>
       </c>
       <c r="B221" t="n">
-        <v>1277</v>
+        <v>2767</v>
       </c>
       <c r="C221" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D221" t="n">
-        <v>1949</v>
+        <v>1135.64</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4644,17 +4644,17 @@
         <v>46218</v>
       </c>
       <c r="B222" t="n">
-        <v>131</v>
+        <v>2657</v>
       </c>
       <c r="C222" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D222" t="n">
-        <v>3850.09</v>
+        <v>3149.7</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4663,17 +4663,17 @@
         <v>46218</v>
       </c>
       <c r="B223" t="n">
-        <v>2692</v>
+        <v>2245</v>
       </c>
       <c r="C223" t="n">
         <v>8888</v>
       </c>
       <c r="D223" t="n">
-        <v>731.28</v>
+        <v>764.66</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4682,17 +4682,17 @@
         <v>46218</v>
       </c>
       <c r="B224" t="n">
-        <v>1632</v>
+        <v>2197</v>
       </c>
       <c r="C224" t="n">
         <v>8888</v>
       </c>
       <c r="D224" t="n">
-        <v>7519.7</v>
+        <v>1085.45</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4701,13 +4701,13 @@
         <v>46218</v>
       </c>
       <c r="B225" t="n">
-        <v>1317</v>
+        <v>1064</v>
       </c>
       <c r="C225" t="n">
-        <v>3179</v>
+        <v>27</v>
       </c>
       <c r="D225" t="n">
-        <v>991.6799999999999</v>
+        <v>574.7</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -4720,17 +4720,17 @@
         <v>46218</v>
       </c>
       <c r="B226" t="n">
-        <v>1993</v>
+        <v>451</v>
       </c>
       <c r="C226" t="n">
-        <v>8888</v>
+        <v>3403</v>
       </c>
       <c r="D226" t="n">
-        <v>3508.59</v>
+        <v>2443.16</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4739,13 +4739,13 @@
         <v>46218</v>
       </c>
       <c r="B227" t="n">
-        <v>1890</v>
+        <v>1116</v>
       </c>
       <c r="C227" t="n">
-        <v>3449</v>
+        <v>13148</v>
       </c>
       <c r="D227" t="n">
-        <v>6313.56</v>
+        <v>1455.21</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -4758,17 +4758,17 @@
         <v>46218</v>
       </c>
       <c r="B228" t="n">
-        <v>1800</v>
+        <v>1277</v>
       </c>
       <c r="C228" t="n">
         <v>8888</v>
       </c>
       <c r="D228" t="n">
-        <v>430.37</v>
+        <v>1949</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4777,17 +4777,17 @@
         <v>46218</v>
       </c>
       <c r="B229" t="n">
-        <v>1117</v>
+        <v>131</v>
       </c>
       <c r="C229" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D229" t="n">
-        <v>672.47</v>
+        <v>3850.09</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4796,13 +4796,13 @@
         <v>46218</v>
       </c>
       <c r="B230" t="n">
-        <v>2749</v>
+        <v>2692</v>
       </c>
       <c r="C230" t="n">
         <v>8888</v>
       </c>
       <c r="D230" t="n">
-        <v>1860.64</v>
+        <v>731.28</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -4815,17 +4815,17 @@
         <v>46218</v>
       </c>
       <c r="B231" t="n">
-        <v>716</v>
+        <v>1632</v>
       </c>
       <c r="C231" t="n">
-        <v>15</v>
+        <v>8888</v>
       </c>
       <c r="D231" t="n">
-        <v>30000</v>
+        <v>7519.7</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4834,17 +4834,17 @@
         <v>46218</v>
       </c>
       <c r="B232" t="n">
-        <v>42</v>
+        <v>2015</v>
       </c>
       <c r="C232" t="n">
         <v>8888</v>
       </c>
       <c r="D232" t="n">
-        <v>280.05</v>
+        <v>377.84</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4853,17 +4853,17 @@
         <v>46218</v>
       </c>
       <c r="B233" t="n">
-        <v>1478</v>
+        <v>42</v>
       </c>
       <c r="C233" t="n">
         <v>8888</v>
       </c>
       <c r="D233" t="n">
-        <v>875.34</v>
+        <v>371.51</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4872,17 +4872,17 @@
         <v>46218</v>
       </c>
       <c r="B234" t="n">
-        <v>2491</v>
+        <v>1317</v>
       </c>
       <c r="C234" t="n">
-        <v>8888</v>
+        <v>3179</v>
       </c>
       <c r="D234" t="n">
-        <v>650.4299999999999</v>
+        <v>991.6799999999999</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4891,13 +4891,13 @@
         <v>46218</v>
       </c>
       <c r="B235" t="n">
-        <v>353</v>
+        <v>1993</v>
       </c>
       <c r="C235" t="n">
         <v>8888</v>
       </c>
       <c r="D235" t="n">
-        <v>653.13</v>
+        <v>3508.59</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -4910,17 +4910,17 @@
         <v>46218</v>
       </c>
       <c r="B236" t="n">
-        <v>2015</v>
+        <v>2606</v>
       </c>
       <c r="C236" t="n">
-        <v>8888</v>
+        <v>2727</v>
       </c>
       <c r="D236" t="n">
-        <v>4436.15</v>
+        <v>1282.92</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4929,17 +4929,17 @@
         <v>46218</v>
       </c>
       <c r="B237" t="n">
-        <v>559</v>
+        <v>1890</v>
       </c>
       <c r="C237" t="n">
-        <v>8888</v>
+        <v>3449</v>
       </c>
       <c r="D237" t="n">
-        <v>3838.57</v>
+        <v>6313.56</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4948,17 +4948,17 @@
         <v>46218</v>
       </c>
       <c r="B238" t="n">
-        <v>1890</v>
+        <v>1800</v>
       </c>
       <c r="C238" t="n">
-        <v>1953</v>
+        <v>8888</v>
       </c>
       <c r="D238" t="n">
-        <v>2998.69</v>
+        <v>430.37</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4967,17 +4967,17 @@
         <v>46218</v>
       </c>
       <c r="B239" t="n">
-        <v>1317</v>
+        <v>1117</v>
       </c>
       <c r="C239" t="n">
         <v>8888</v>
       </c>
       <c r="D239" t="n">
-        <v>1626.02</v>
+        <v>672.47</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4986,17 +4986,17 @@
         <v>46218</v>
       </c>
       <c r="B240" t="n">
-        <v>429</v>
+        <v>2749</v>
       </c>
       <c r="C240" t="n">
-        <v>1281</v>
+        <v>8888</v>
       </c>
       <c r="D240" t="n">
-        <v>1000.44</v>
+        <v>1860.64</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -5005,17 +5005,17 @@
         <v>46218</v>
       </c>
       <c r="B241" t="n">
-        <v>2782</v>
+        <v>716</v>
       </c>
       <c r="C241" t="n">
-        <v>8888</v>
+        <v>15</v>
       </c>
       <c r="D241" t="n">
-        <v>1786.32</v>
+        <v>30000</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -5024,13 +5024,13 @@
         <v>46218</v>
       </c>
       <c r="B242" t="n">
-        <v>953</v>
+        <v>42</v>
       </c>
       <c r="C242" t="n">
         <v>8888</v>
       </c>
       <c r="D242" t="n">
-        <v>364.44</v>
+        <v>280.05</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -5043,17 +5043,17 @@
         <v>46218</v>
       </c>
       <c r="B243" t="n">
-        <v>2251</v>
+        <v>1478</v>
       </c>
       <c r="C243" t="n">
         <v>8888</v>
       </c>
       <c r="D243" t="n">
-        <v>989.26</v>
+        <v>875.34</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -5062,17 +5062,17 @@
         <v>46218</v>
       </c>
       <c r="B244" t="n">
-        <v>483</v>
+        <v>2491</v>
       </c>
       <c r="C244" t="n">
-        <v>841</v>
+        <v>8888</v>
       </c>
       <c r="D244" t="n">
-        <v>2564.59</v>
+        <v>1690.31</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5081,17 +5081,17 @@
         <v>46218</v>
       </c>
       <c r="B245" t="n">
-        <v>2133</v>
+        <v>353</v>
       </c>
       <c r="C245" t="n">
-        <v>213</v>
+        <v>8888</v>
       </c>
       <c r="D245" t="n">
-        <v>526.8</v>
+        <v>653.13</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5100,17 +5100,17 @@
         <v>46218</v>
       </c>
       <c r="B246" t="n">
-        <v>351</v>
+        <v>2015</v>
       </c>
       <c r="C246" t="n">
-        <v>3009</v>
+        <v>8888</v>
       </c>
       <c r="D246" t="n">
-        <v>416.36</v>
+        <v>4436.15</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5119,17 +5119,17 @@
         <v>46218</v>
       </c>
       <c r="B247" t="n">
-        <v>2250</v>
+        <v>559</v>
       </c>
       <c r="C247" t="n">
         <v>8888</v>
       </c>
       <c r="D247" t="n">
-        <v>709.46</v>
+        <v>3838.57</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5138,17 +5138,17 @@
         <v>46218</v>
       </c>
       <c r="B248" t="n">
-        <v>2648</v>
+        <v>1890</v>
       </c>
       <c r="C248" t="n">
-        <v>8888</v>
+        <v>1953</v>
       </c>
       <c r="D248" t="n">
-        <v>1873.52</v>
+        <v>2998.69</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -5157,13 +5157,13 @@
         <v>46218</v>
       </c>
       <c r="B249" t="n">
-        <v>131</v>
+        <v>1317</v>
       </c>
       <c r="C249" t="n">
         <v>8888</v>
       </c>
       <c r="D249" t="n">
-        <v>1369.91</v>
+        <v>1626.02</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -5176,13 +5176,13 @@
         <v>46218</v>
       </c>
       <c r="B250" t="n">
-        <v>2298</v>
+        <v>429</v>
       </c>
       <c r="C250" t="n">
-        <v>675</v>
+        <v>1281</v>
       </c>
       <c r="D250" t="n">
-        <v>2301.31</v>
+        <v>1000.44</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -5195,17 +5195,17 @@
         <v>46218</v>
       </c>
       <c r="B251" t="n">
-        <v>2790</v>
+        <v>2782</v>
       </c>
       <c r="C251" t="n">
-        <v>1953</v>
+        <v>8888</v>
       </c>
       <c r="D251" t="n">
-        <v>371.88</v>
+        <v>1786.32</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5214,17 +5214,17 @@
         <v>46218</v>
       </c>
       <c r="B252" t="n">
-        <v>363</v>
+        <v>953</v>
       </c>
       <c r="C252" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D252" t="n">
-        <v>635.1</v>
+        <v>364.44</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5233,17 +5233,17 @@
         <v>46218</v>
       </c>
       <c r="B253" t="n">
-        <v>2716</v>
+        <v>2251</v>
       </c>
       <c r="C253" t="n">
-        <v>1929</v>
+        <v>8888</v>
       </c>
       <c r="D253" t="n">
-        <v>1073.33</v>
+        <v>989.26</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5252,13 +5252,13 @@
         <v>46218</v>
       </c>
       <c r="B254" t="n">
-        <v>2639</v>
+        <v>483</v>
       </c>
       <c r="C254" t="n">
-        <v>1953</v>
+        <v>841</v>
       </c>
       <c r="D254" t="n">
-        <v>504.09</v>
+        <v>2564.59</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -5271,13 +5271,13 @@
         <v>46218</v>
       </c>
       <c r="B255" t="n">
-        <v>629</v>
+        <v>2133</v>
       </c>
       <c r="C255" t="n">
-        <v>675</v>
+        <v>213</v>
       </c>
       <c r="D255" t="n">
-        <v>2419.73</v>
+        <v>526.8</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -5290,13 +5290,13 @@
         <v>46218</v>
       </c>
       <c r="B256" t="n">
-        <v>619</v>
+        <v>351</v>
       </c>
       <c r="C256" t="n">
-        <v>1139</v>
+        <v>3009</v>
       </c>
       <c r="D256" t="n">
-        <v>1341.64</v>
+        <v>416.36</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -5309,17 +5309,17 @@
         <v>46218</v>
       </c>
       <c r="B257" t="n">
-        <v>2109</v>
+        <v>2250</v>
       </c>
       <c r="C257" t="n">
         <v>8888</v>
       </c>
       <c r="D257" t="n">
-        <v>2293.78</v>
+        <v>709.46</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -5328,17 +5328,17 @@
         <v>46218</v>
       </c>
       <c r="B258" t="n">
-        <v>1116</v>
+        <v>2141</v>
       </c>
       <c r="C258" t="n">
         <v>8888</v>
       </c>
       <c r="D258" t="n">
-        <v>2919.53</v>
+        <v>1453.86</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5347,17 +5347,17 @@
         <v>46218</v>
       </c>
       <c r="B259" t="n">
-        <v>1293</v>
+        <v>2648</v>
       </c>
       <c r="C259" t="n">
         <v>8888</v>
       </c>
       <c r="D259" t="n">
-        <v>696.77</v>
+        <v>1873.52</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5366,17 +5366,17 @@
         <v>46218</v>
       </c>
       <c r="B260" t="n">
-        <v>2250</v>
+        <v>131</v>
       </c>
       <c r="C260" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D260" t="n">
-        <v>1803.76</v>
+        <v>1369.91</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -5385,13 +5385,13 @@
         <v>46218</v>
       </c>
       <c r="B261" t="n">
-        <v>2698</v>
+        <v>2298</v>
       </c>
       <c r="C261" t="n">
-        <v>874</v>
+        <v>675</v>
       </c>
       <c r="D261" t="n">
-        <v>1556.09</v>
+        <v>2301.31</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -5404,17 +5404,17 @@
         <v>46218</v>
       </c>
       <c r="B262" t="n">
-        <v>42</v>
+        <v>2790</v>
       </c>
       <c r="C262" t="n">
-        <v>8888</v>
+        <v>1953</v>
       </c>
       <c r="D262" t="n">
-        <v>79947.14999999999</v>
+        <v>371.88</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -5423,17 +5423,17 @@
         <v>46218</v>
       </c>
       <c r="B263" t="n">
-        <v>772</v>
+        <v>363</v>
       </c>
       <c r="C263" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D263" t="n">
-        <v>400.25</v>
+        <v>635.1</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -5442,17 +5442,17 @@
         <v>46218</v>
       </c>
       <c r="B264" t="n">
-        <v>2728</v>
+        <v>2716</v>
       </c>
       <c r="C264" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D264" t="n">
-        <v>1397.07</v>
+        <v>1073.33</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -5461,13 +5461,13 @@
         <v>46218</v>
       </c>
       <c r="B265" t="n">
-        <v>2197</v>
+        <v>2639</v>
       </c>
       <c r="C265" t="n">
-        <v>423</v>
+        <v>1953</v>
       </c>
       <c r="D265" t="n">
-        <v>2267.61</v>
+        <v>504.09</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -5480,13 +5480,13 @@
         <v>46218</v>
       </c>
       <c r="B266" t="n">
-        <v>2716</v>
+        <v>629</v>
       </c>
       <c r="C266" t="n">
-        <v>977</v>
+        <v>675</v>
       </c>
       <c r="D266" t="n">
-        <v>729.29</v>
+        <v>2419.73</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -5499,17 +5499,245 @@
         <v>46218</v>
       </c>
       <c r="B267" t="n">
+        <v>619</v>
+      </c>
+      <c r="C267" t="n">
+        <v>1139</v>
+      </c>
+      <c r="D267" t="n">
+        <v>1341.64</v>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B268" t="n">
+        <v>2109</v>
+      </c>
+      <c r="C268" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D268" t="n">
+        <v>2293.78</v>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B269" t="n">
+        <v>1116</v>
+      </c>
+      <c r="C269" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D269" t="n">
+        <v>2919.53</v>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B270" t="n">
+        <v>1293</v>
+      </c>
+      <c r="C270" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D270" t="n">
+        <v>696.77</v>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B271" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C271" t="n">
+        <v>27</v>
+      </c>
+      <c r="D271" t="n">
+        <v>1803.76</v>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B272" t="n">
+        <v>2698</v>
+      </c>
+      <c r="C272" t="n">
+        <v>874</v>
+      </c>
+      <c r="D272" t="n">
+        <v>1556.09</v>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B273" t="n">
+        <v>42</v>
+      </c>
+      <c r="C273" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D273" t="n">
+        <v>79947.14999999999</v>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B274" t="n">
+        <v>772</v>
+      </c>
+      <c r="C274" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D274" t="n">
+        <v>400.25</v>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B275" t="n">
+        <v>2728</v>
+      </c>
+      <c r="C275" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D275" t="n">
+        <v>1397.07</v>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B276" t="n">
+        <v>2197</v>
+      </c>
+      <c r="C276" t="n">
+        <v>423</v>
+      </c>
+      <c r="D276" t="n">
+        <v>2267.61</v>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B277" t="n">
+        <v>2716</v>
+      </c>
+      <c r="C277" t="n">
+        <v>977</v>
+      </c>
+      <c r="D277" t="n">
+        <v>729.29</v>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B278" t="n">
         <v>1993</v>
       </c>
-      <c r="C267" t="n">
-        <v>8888</v>
-      </c>
-      <c r="D267" t="n">
+      <c r="C278" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D278" t="n">
         <v>456.62</v>
       </c>
-      <c r="E267" t="inlineStr">
+      <c r="E278" t="inlineStr">
         <is>
           <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B279" t="n">
+        <v>2767</v>
+      </c>
+      <c r="C279" t="n">
+        <v>2220</v>
+      </c>
+      <c r="D279" t="n">
+        <v>339.66</v>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:F236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,12 +450,4717 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>VALOR_PEDIDO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>VALOR_VENDA</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>ORIGEM_PEDIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B2" t="n">
+        <v>438</v>
+      </c>
+      <c r="C2" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1219.66</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B3" t="n">
+        <v>326</v>
+      </c>
+      <c r="C3" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D3" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2768</v>
+      </c>
+      <c r="C4" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3071.66</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2362</v>
+      </c>
+      <c r="C5" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1594.62</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B6" t="n">
+        <v>675</v>
+      </c>
+      <c r="C6" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D6" t="n">
+        <v>210.71</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1372</v>
+      </c>
+      <c r="C7" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10042.14</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B8" t="n">
+        <v>535</v>
+      </c>
+      <c r="C8" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D8" t="n">
+        <v>12275.79</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B9" t="n">
+        <v>609</v>
+      </c>
+      <c r="C9" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1611.48</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B10" t="n">
+        <v>483</v>
+      </c>
+      <c r="C10" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D10" t="n">
+        <v>685.76</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2190</v>
+      </c>
+      <c r="C11" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D11" t="n">
+        <v>11250.64</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1064</v>
+      </c>
+      <c r="C12" t="n">
+        <v>27</v>
+      </c>
+      <c r="D12" t="n">
+        <v>306.58</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1324</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3009</v>
+      </c>
+      <c r="D13" t="n">
+        <v>178.36</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2362</v>
+      </c>
+      <c r="C14" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2827.89</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B15" t="n">
+        <v>629</v>
+      </c>
+      <c r="C15" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1693.36</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B16" t="n">
+        <v>131</v>
+      </c>
+      <c r="C16" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D16" t="n">
+        <v>623.52</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B17" t="n">
+        <v>609</v>
+      </c>
+      <c r="C17" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D17" t="n">
+        <v>556.35</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B18" t="n">
+        <v>131</v>
+      </c>
+      <c r="C18" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D18" t="n">
+        <v>623.52</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B19" t="n">
+        <v>559</v>
+      </c>
+      <c r="C19" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D19" t="n">
+        <v>9596.75</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B20" t="n">
+        <v>2107</v>
+      </c>
+      <c r="C20" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6978.14</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B21" t="n">
+        <v>131</v>
+      </c>
+      <c r="C21" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D21" t="n">
+        <v>934.3200000000001</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B22" t="n">
+        <v>360</v>
+      </c>
+      <c r="C22" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1990.42</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B23" t="n">
+        <v>768</v>
+      </c>
+      <c r="C23" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3646.68</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B24" t="n">
+        <v>483</v>
+      </c>
+      <c r="C24" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D24" t="n">
+        <v>150.08</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B25" t="n">
+        <v>131</v>
+      </c>
+      <c r="C25" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1742.9</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1756</v>
+      </c>
+      <c r="C26" t="n">
+        <v>27</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1217.45</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B27" t="n">
+        <v>609</v>
+      </c>
+      <c r="C27" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D27" t="n">
+        <v>741.79</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B28" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C28" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1011.48</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B29" t="n">
+        <v>629</v>
+      </c>
+      <c r="C29" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1338.55</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B30" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C30" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1134</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1756</v>
+      </c>
+      <c r="C31" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3007.36</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1064</v>
+      </c>
+      <c r="C32" t="n">
+        <v>27</v>
+      </c>
+      <c r="D32" t="n">
+        <v>954.13</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B33" t="n">
+        <v>629</v>
+      </c>
+      <c r="C33" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1997.38</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1756</v>
+      </c>
+      <c r="C34" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1399.6</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1756</v>
+      </c>
+      <c r="C35" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1383.55</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B36" t="n">
+        <v>131</v>
+      </c>
+      <c r="C36" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D36" t="n">
+        <v>527.52</v>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B37" t="n">
+        <v>816</v>
+      </c>
+      <c r="C37" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2983.2</v>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B38" t="n">
+        <v>767</v>
+      </c>
+      <c r="C38" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D38" t="n">
+        <v>428.17</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B39" t="n">
+        <v>14</v>
+      </c>
+      <c r="C39" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1155.74</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D40" t="n">
+        <v>10866.88</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B41" t="n">
+        <v>629</v>
+      </c>
+      <c r="C41" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D41" t="n">
+        <v>14273.2</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B42" t="n">
+        <v>768</v>
+      </c>
+      <c r="C42" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D42" t="n">
+        <v>14378.8</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1756</v>
+      </c>
+      <c r="C43" t="n">
+        <v>27</v>
+      </c>
+      <c r="D43" t="n">
+        <v>926.13</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58</v>
+      </c>
+      <c r="C44" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1904.76</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B45" t="n">
+        <v>131</v>
+      </c>
+      <c r="C45" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D45" t="n">
+        <v>594.8099999999999</v>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B46" t="n">
+        <v>2452</v>
+      </c>
+      <c r="C46" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D46" t="n">
+        <v>3086.66</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B47" t="n">
+        <v>953</v>
+      </c>
+      <c r="C47" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D47" t="n">
+        <v>604.53</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B48" t="n">
+        <v>768</v>
+      </c>
+      <c r="C48" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1655.28</v>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B49" t="n">
+        <v>768</v>
+      </c>
+      <c r="C49" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D49" t="n">
+        <v>536.16</v>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B50" t="n">
+        <v>629</v>
+      </c>
+      <c r="C50" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1276.58</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B51" t="n">
+        <v>1277</v>
+      </c>
+      <c r="C51" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1591.9</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B52" t="n">
+        <v>2163</v>
+      </c>
+      <c r="C52" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D52" t="n">
+        <v>406.1</v>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B53" t="n">
+        <v>14</v>
+      </c>
+      <c r="C53" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D53" t="n">
+        <v>343.54</v>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B54" t="n">
+        <v>438</v>
+      </c>
+      <c r="C54" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1952.31</v>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B55" t="n">
+        <v>768</v>
+      </c>
+      <c r="C55" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D55" t="n">
+        <v>7813.68</v>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B56" t="n">
+        <v>768</v>
+      </c>
+      <c r="C56" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1291.96</v>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B57" t="n">
+        <v>2190</v>
+      </c>
+      <c r="C57" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D57" t="n">
+        <v>870.03</v>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1518</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1533</v>
+      </c>
+      <c r="D58" t="n">
+        <v>4494.7</v>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B59" t="n">
+        <v>2452</v>
+      </c>
+      <c r="C59" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1253.5</v>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B60" t="n">
+        <v>1756</v>
+      </c>
+      <c r="C60" t="n">
+        <v>27</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1575.17</v>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B61" t="n">
+        <v>768</v>
+      </c>
+      <c r="C61" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D61" t="n">
+        <v>3118.72</v>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B62" t="n">
+        <v>438</v>
+      </c>
+      <c r="C62" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D62" t="n">
+        <v>338.69</v>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B63" t="n">
+        <v>429</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1281</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1867.66</v>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B64" t="n">
+        <v>1075</v>
+      </c>
+      <c r="C64" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1282.67</v>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B65" t="n">
+        <v>1064</v>
+      </c>
+      <c r="C65" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D65" t="n">
+        <v>2550.8</v>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B66" t="n">
+        <v>2131</v>
+      </c>
+      <c r="C66" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1153.68</v>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B67" t="n">
+        <v>609</v>
+      </c>
+      <c r="C67" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1854.48</v>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B68" t="n">
+        <v>438</v>
+      </c>
+      <c r="C68" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D68" t="n">
+        <v>712</v>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B69" t="n">
+        <v>1658</v>
+      </c>
+      <c r="C69" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D69" t="n">
+        <v>311.88</v>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B70" t="n">
+        <v>1293</v>
+      </c>
+      <c r="C70" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1354.46</v>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B71" t="n">
+        <v>816</v>
+      </c>
+      <c r="C71" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D71" t="n">
+        <v>3118.8</v>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B72" t="n">
+        <v>451</v>
+      </c>
+      <c r="C72" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D72" t="n">
+        <v>2231.47</v>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B73" t="n">
+        <v>629</v>
+      </c>
+      <c r="C73" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1178.64</v>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B74" t="n">
+        <v>703</v>
+      </c>
+      <c r="C74" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1431.24</v>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B75" t="n">
+        <v>629</v>
+      </c>
+      <c r="C75" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D75" t="n">
+        <v>761.87</v>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B76" t="n">
+        <v>609</v>
+      </c>
+      <c r="C76" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D76" t="n">
+        <v>2107.32</v>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B77" t="n">
+        <v>1293</v>
+      </c>
+      <c r="C77" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D77" t="n">
+        <v>5342.64</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B78" t="n">
+        <v>609</v>
+      </c>
+      <c r="C78" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1919.68</v>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B79" t="n">
+        <v>1324</v>
+      </c>
+      <c r="C79" t="n">
+        <v>3009</v>
+      </c>
+      <c r="D79" t="n">
+        <v>4396.24</v>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B80" t="n">
+        <v>400</v>
+      </c>
+      <c r="C80" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1953.42</v>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B81" t="n">
+        <v>14</v>
+      </c>
+      <c r="C81" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1006.88</v>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B82" t="n">
+        <v>2362</v>
+      </c>
+      <c r="C82" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D82" t="n">
+        <v>3074.16</v>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B83" t="n">
+        <v>351</v>
+      </c>
+      <c r="C83" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D83" t="n">
+        <v>6142.76</v>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B84" t="n">
+        <v>1299</v>
+      </c>
+      <c r="C84" t="n">
+        <v>27</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1276.32</v>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B85" t="n">
+        <v>2362</v>
+      </c>
+      <c r="C85" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D85" t="n">
+        <v>2291.35</v>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B86" t="n">
+        <v>131</v>
+      </c>
+      <c r="C86" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D86" t="n">
+        <v>857.34</v>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B87" t="n">
+        <v>14</v>
+      </c>
+      <c r="C87" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D87" t="n">
+        <v>311.88</v>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B88" t="n">
+        <v>1372</v>
+      </c>
+      <c r="C88" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D88" t="n">
+        <v>10235.04</v>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B89" t="n">
+        <v>609</v>
+      </c>
+      <c r="C89" t="n">
+        <v>3179</v>
+      </c>
+      <c r="D89" t="n">
+        <v>891.63</v>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B90" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C90" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D90" t="n">
+        <v>3311.6</v>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B91" t="n">
+        <v>1324</v>
+      </c>
+      <c r="C91" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D91" t="n">
+        <v>8134.2</v>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B92" t="n">
+        <v>2211</v>
+      </c>
+      <c r="C92" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D92" t="n">
+        <v>2125.44</v>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B93" t="n">
+        <v>483</v>
+      </c>
+      <c r="C93" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D93" t="n">
+        <v>4217.99</v>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B94" t="n">
+        <v>1937</v>
+      </c>
+      <c r="C94" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D94" t="n">
+        <v>2231.47</v>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B95" t="n">
+        <v>40</v>
+      </c>
+      <c r="C95" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D95" t="n">
+        <v>613.16</v>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B96" t="n">
+        <v>1064</v>
+      </c>
+      <c r="C96" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D96" t="n">
+        <v>720.52</v>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B97" t="n">
+        <v>1873</v>
+      </c>
+      <c r="C97" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D97" t="n">
+        <v>138.39</v>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B98" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C98" t="n">
+        <v>27</v>
+      </c>
+      <c r="D98" t="n">
+        <v>1646.82</v>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B99" t="n">
+        <v>40</v>
+      </c>
+      <c r="C99" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D99" t="n">
+        <v>956.01</v>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B100" t="n">
+        <v>629</v>
+      </c>
+      <c r="C100" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D100" t="n">
+        <v>18471.2</v>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B101" t="n">
+        <v>703</v>
+      </c>
+      <c r="C101" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D101" t="n">
+        <v>2946.27</v>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B102" t="n">
+        <v>629</v>
+      </c>
+      <c r="C102" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1002.21</v>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B103" t="n">
+        <v>1876</v>
+      </c>
+      <c r="C103" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D103" t="n">
+        <v>660.5599999999999</v>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B104" t="n">
+        <v>1075</v>
+      </c>
+      <c r="C104" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D104" t="n">
+        <v>325.49</v>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B105" t="n">
+        <v>451</v>
+      </c>
+      <c r="C105" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D105" t="n">
+        <v>1264.4</v>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B106" t="n">
+        <v>703</v>
+      </c>
+      <c r="C106" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D106" t="n">
+        <v>599.88</v>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B107" t="n">
+        <v>1064</v>
+      </c>
+      <c r="C107" t="n">
+        <v>27</v>
+      </c>
+      <c r="D107" t="n">
+        <v>954.13</v>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B108" t="n">
+        <v>571</v>
+      </c>
+      <c r="C108" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D108" t="n">
+        <v>25609.34</v>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B109" t="n">
+        <v>131</v>
+      </c>
+      <c r="C109" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D109" t="n">
+        <v>934.3200000000001</v>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B110" t="n">
+        <v>2660</v>
+      </c>
+      <c r="C110" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D110" t="n">
+        <v>3419.84</v>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B111" t="n">
+        <v>400</v>
+      </c>
+      <c r="C111" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D111" t="n">
+        <v>346.8</v>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B112" t="n">
+        <v>2362</v>
+      </c>
+      <c r="C112" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D112" t="n">
+        <v>1457.7</v>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B113" t="n">
+        <v>816</v>
+      </c>
+      <c r="C113" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D113" t="n">
+        <v>311.95</v>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B114" t="n">
+        <v>20</v>
+      </c>
+      <c r="C114" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D114" t="n">
+        <v>2247.2</v>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B115" t="n">
+        <v>890</v>
+      </c>
+      <c r="C115" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D115" t="n">
+        <v>310.39</v>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B116" t="n">
+        <v>1293</v>
+      </c>
+      <c r="C116" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D116" t="n">
+        <v>3237.41</v>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B117" t="n">
+        <v>2452</v>
+      </c>
+      <c r="C117" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1632.81</v>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B118" t="n">
+        <v>483</v>
+      </c>
+      <c r="C118" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D118" t="n">
+        <v>2953.24</v>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B119" t="n">
+        <v>131</v>
+      </c>
+      <c r="C119" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1384.39</v>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B120" t="n">
+        <v>2652</v>
+      </c>
+      <c r="C120" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D120" t="n">
+        <v>3419.64</v>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B121" t="n">
+        <v>1117</v>
+      </c>
+      <c r="C121" t="n">
+        <v>1139</v>
+      </c>
+      <c r="D121" t="n">
+        <v>238.55</v>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B122" t="n">
+        <v>2107</v>
+      </c>
+      <c r="C122" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1958.34</v>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B123" t="n">
+        <v>131</v>
+      </c>
+      <c r="C123" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D123" t="n">
+        <v>767.04</v>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B124" t="n">
+        <v>1756</v>
+      </c>
+      <c r="C124" t="n">
+        <v>27</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1939.32</v>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B125" t="n">
+        <v>1372</v>
+      </c>
+      <c r="C125" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D125" t="n">
+        <v>879.6</v>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B126" t="n">
+        <v>360</v>
+      </c>
+      <c r="C126" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1906.67</v>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B127" t="n">
+        <v>131</v>
+      </c>
+      <c r="C127" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D127" t="n">
+        <v>2281.48</v>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B128" t="n">
+        <v>1372</v>
+      </c>
+      <c r="C128" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D128" t="n">
+        <v>839.58</v>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B129" t="n">
+        <v>1996</v>
+      </c>
+      <c r="C129" t="n">
+        <v>691</v>
+      </c>
+      <c r="D129" t="n">
+        <v>2078.56</v>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B130" t="n">
+        <v>1064</v>
+      </c>
+      <c r="C130" t="n">
+        <v>27</v>
+      </c>
+      <c r="D130" t="n">
+        <v>954.13</v>
+      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B131" t="n">
+        <v>559</v>
+      </c>
+      <c r="C131" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D131" t="n">
+        <v>1245.19</v>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B132" t="n">
+        <v>580</v>
+      </c>
+      <c r="C132" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D132" t="n">
+        <v>3020.55</v>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B133" t="n">
+        <v>1064</v>
+      </c>
+      <c r="C133" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1001.61</v>
+      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B134" t="n">
+        <v>325</v>
+      </c>
+      <c r="C134" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D134" t="n">
+        <v>100.62</v>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B135" t="n">
+        <v>1293</v>
+      </c>
+      <c r="C135" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1354.46</v>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B136" t="n">
+        <v>629</v>
+      </c>
+      <c r="C136" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D136" t="n">
+        <v>1804.42</v>
+      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B137" t="n">
+        <v>2245</v>
+      </c>
+      <c r="C137" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D137" t="n">
+        <v>983.59</v>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B138" t="n">
+        <v>131</v>
+      </c>
+      <c r="C138" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D138" t="n">
+        <v>989.47</v>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B139" t="n">
+        <v>131</v>
+      </c>
+      <c r="C139" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D139" t="n">
+        <v>934.3200000000001</v>
+      </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B140" t="n">
+        <v>2362</v>
+      </c>
+      <c r="C140" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D140" t="n">
+        <v>327.61</v>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B141" t="n">
+        <v>325</v>
+      </c>
+      <c r="C141" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D141" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B142" t="n">
+        <v>1756</v>
+      </c>
+      <c r="C142" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D142" t="n">
+        <v>5236.57</v>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B143" t="n">
+        <v>629</v>
+      </c>
+      <c r="C143" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1292.86</v>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B144" t="n">
+        <v>2383</v>
+      </c>
+      <c r="C144" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D144" t="n">
+        <v>5887.04</v>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B145" t="n">
+        <v>131</v>
+      </c>
+      <c r="C145" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D145" t="n">
+        <v>2983.2</v>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B146" t="n">
+        <v>1007</v>
+      </c>
+      <c r="C146" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1664.69</v>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B147" t="n">
+        <v>890</v>
+      </c>
+      <c r="C147" t="n">
+        <v>1533</v>
+      </c>
+      <c r="D147" t="n">
+        <v>670.6799999999999</v>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B148" t="n">
+        <v>325</v>
+      </c>
+      <c r="C148" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D148" t="n">
+        <v>44.59</v>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B149" t="n">
+        <v>2362</v>
+      </c>
+      <c r="C149" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D149" t="n">
+        <v>383.76</v>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B150" t="n">
+        <v>1465</v>
+      </c>
+      <c r="C150" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D150" t="n">
+        <v>2350.22</v>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B151" t="n">
+        <v>483</v>
+      </c>
+      <c r="C151" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D151" t="n">
+        <v>689.02</v>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B152" t="n">
+        <v>2452</v>
+      </c>
+      <c r="C152" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D152" t="n">
+        <v>4530.7</v>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B153" t="n">
+        <v>400</v>
+      </c>
+      <c r="C153" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D153" t="n">
+        <v>1292.32</v>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B154" t="n">
+        <v>2362</v>
+      </c>
+      <c r="C154" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D154" t="n">
+        <v>744.4</v>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B155" t="n">
+        <v>1756</v>
+      </c>
+      <c r="C155" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D155" t="n">
+        <v>462.4</v>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B156" t="n">
+        <v>571</v>
+      </c>
+      <c r="C156" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D156" t="n">
+        <v>1125.6</v>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B157" t="n">
+        <v>571</v>
+      </c>
+      <c r="C157" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D157" t="n">
+        <v>5997.18</v>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B158" t="n">
+        <v>2421</v>
+      </c>
+      <c r="C158" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D158" t="n">
+        <v>2786.14</v>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B159" t="n">
+        <v>953</v>
+      </c>
+      <c r="C159" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D159" t="n">
+        <v>6995.34</v>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B160" t="n">
+        <v>2769</v>
+      </c>
+      <c r="C160" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D160" t="n">
+        <v>620.37</v>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B161" t="n">
+        <v>2362</v>
+      </c>
+      <c r="C161" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D161" t="n">
+        <v>8080.76</v>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B162" t="n">
+        <v>360</v>
+      </c>
+      <c r="C162" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D162" t="n">
+        <v>4617.15</v>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B163" t="n">
+        <v>609</v>
+      </c>
+      <c r="C163" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1112.69</v>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B164" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C164" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D164" t="n">
+        <v>2681.88</v>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B165" t="n">
+        <v>535</v>
+      </c>
+      <c r="C165" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D165" t="n">
+        <v>616.54</v>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B166" t="n">
+        <v>629</v>
+      </c>
+      <c r="C166" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D166" t="n">
+        <v>801.97</v>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B167" t="n">
+        <v>363</v>
+      </c>
+      <c r="C167" t="n">
+        <v>1898</v>
+      </c>
+      <c r="D167" t="n">
+        <v>1618.96</v>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B168" t="n">
+        <v>1064</v>
+      </c>
+      <c r="C168" t="n">
+        <v>27</v>
+      </c>
+      <c r="D168" t="n">
+        <v>2667.18</v>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B169" t="n">
+        <v>609</v>
+      </c>
+      <c r="C169" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D169" t="n">
+        <v>1141.32</v>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B170" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C170" t="n">
+        <v>27</v>
+      </c>
+      <c r="D170" t="n">
+        <v>551.76</v>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B171" t="n">
+        <v>953</v>
+      </c>
+      <c r="C171" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D171" t="n">
+        <v>4366.21</v>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B172" t="n">
+        <v>629</v>
+      </c>
+      <c r="C172" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D172" t="n">
+        <v>1844.39</v>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B173" t="n">
+        <v>1465</v>
+      </c>
+      <c r="C173" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D173" t="n">
+        <v>1220.4</v>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B174" t="n">
+        <v>1869</v>
+      </c>
+      <c r="C174" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D174" t="n">
+        <v>1103.52</v>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B175" t="n">
+        <v>2362</v>
+      </c>
+      <c r="C175" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D175" t="n">
+        <v>3256.49</v>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B176" t="n">
+        <v>2362</v>
+      </c>
+      <c r="C176" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D176" t="n">
+        <v>702.5700000000001</v>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B177" t="n">
+        <v>2652</v>
+      </c>
+      <c r="C177" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D177" t="n">
+        <v>260.03</v>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B178" t="n">
+        <v>1465</v>
+      </c>
+      <c r="C178" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D178" t="n">
+        <v>3283.11</v>
+      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B179" t="n">
+        <v>131</v>
+      </c>
+      <c r="C179" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D179" t="n">
+        <v>233.82</v>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B180" t="n">
+        <v>890</v>
+      </c>
+      <c r="C180" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D180" t="n">
+        <v>950.1799999999999</v>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B181" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C181" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D181" t="n">
+        <v>1596</v>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B182" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C182" t="n">
+        <v>27</v>
+      </c>
+      <c r="D182" t="n">
+        <v>2207.04</v>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B183" t="n">
+        <v>629</v>
+      </c>
+      <c r="C183" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D183" t="n">
+        <v>801.97</v>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B184" t="n">
+        <v>58</v>
+      </c>
+      <c r="C184" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D184" t="n">
+        <v>697.33</v>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B185" t="n">
+        <v>1108</v>
+      </c>
+      <c r="C185" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D185" t="n">
+        <v>341.38</v>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B186" t="n">
+        <v>2363</v>
+      </c>
+      <c r="C186" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D186" t="n">
+        <v>1884.86</v>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B187" t="n">
+        <v>1007</v>
+      </c>
+      <c r="C187" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D187" t="n">
+        <v>1054.68</v>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B188" t="n">
+        <v>1869</v>
+      </c>
+      <c r="C188" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D188" t="n">
+        <v>1698.3</v>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B189" t="n">
+        <v>1996</v>
+      </c>
+      <c r="C189" t="n">
+        <v>691</v>
+      </c>
+      <c r="D189" t="n">
+        <v>2302.2</v>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B190" t="n">
+        <v>2709</v>
+      </c>
+      <c r="C190" t="n">
+        <v>2220</v>
+      </c>
+      <c r="D190" t="n">
+        <v>586.1900000000001</v>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B191" t="n">
+        <v>1064</v>
+      </c>
+      <c r="C191" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D191" t="n">
+        <v>372.95</v>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B192" t="n">
+        <v>40</v>
+      </c>
+      <c r="C192" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D192" t="n">
+        <v>306.58</v>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B193" t="n">
+        <v>1996</v>
+      </c>
+      <c r="C193" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D193" t="n">
+        <v>514.91</v>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B194" t="n">
+        <v>20</v>
+      </c>
+      <c r="C194" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D194" t="n">
+        <v>680.4</v>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B195" t="n">
+        <v>2190</v>
+      </c>
+      <c r="C195" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D195" t="n">
+        <v>1035.41</v>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B196" t="n">
+        <v>781</v>
+      </c>
+      <c r="C196" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D196" t="n">
+        <v>1169.2</v>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B197" t="n">
+        <v>351</v>
+      </c>
+      <c r="C197" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D197" t="n">
+        <v>2207.04</v>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B198" t="n">
+        <v>1064</v>
+      </c>
+      <c r="C198" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D198" t="n">
+        <v>2348.64</v>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B199" t="n">
+        <v>571</v>
+      </c>
+      <c r="C199" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D199" t="n">
+        <v>17843.18</v>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B200" t="n">
+        <v>629</v>
+      </c>
+      <c r="C200" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D200" t="n">
+        <v>1292.86</v>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B201" t="n">
+        <v>535</v>
+      </c>
+      <c r="C201" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D201" t="n">
+        <v>1395.11</v>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B202" t="n">
+        <v>609</v>
+      </c>
+      <c r="C202" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D202" t="n">
+        <v>1487.52</v>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B203" t="n">
+        <v>609</v>
+      </c>
+      <c r="C203" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D203" t="n">
+        <v>1854.48</v>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B204" t="n">
+        <v>2660</v>
+      </c>
+      <c r="C204" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D204" t="n">
+        <v>1481.24</v>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B205" t="n">
+        <v>1293</v>
+      </c>
+      <c r="C205" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D205" t="n">
+        <v>1354.46</v>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B206" t="n">
+        <v>2768</v>
+      </c>
+      <c r="C206" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D206" t="n">
+        <v>3012.32</v>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B207" t="n">
+        <v>1327</v>
+      </c>
+      <c r="C207" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D207" t="n">
+        <v>4134.3</v>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B208" t="n">
+        <v>2628</v>
+      </c>
+      <c r="C208" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D208" t="n">
+        <v>271.2</v>
+      </c>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B209" t="n">
+        <v>2452</v>
+      </c>
+      <c r="C209" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D209" t="n">
+        <v>1208.26</v>
+      </c>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B210" t="n">
+        <v>816</v>
+      </c>
+      <c r="C210" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D210" t="n">
+        <v>4017.6</v>
+      </c>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B211" t="n">
+        <v>1064</v>
+      </c>
+      <c r="C211" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D211" t="n">
+        <v>4291.42</v>
+      </c>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B212" t="n">
+        <v>703</v>
+      </c>
+      <c r="C212" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D212" t="n">
+        <v>3936.87</v>
+      </c>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B213" t="n">
+        <v>1340</v>
+      </c>
+      <c r="C213" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D213" t="n">
+        <v>2774.78</v>
+      </c>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B214" t="n">
+        <v>2107</v>
+      </c>
+      <c r="C214" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D214" t="n">
+        <v>476.47</v>
+      </c>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B215" t="n">
+        <v>400</v>
+      </c>
+      <c r="C215" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D215" t="n">
+        <v>2686.56</v>
+      </c>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B216" t="n">
+        <v>559</v>
+      </c>
+      <c r="C216" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D216" t="n">
+        <v>9867.299999999999</v>
+      </c>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B217" t="n">
+        <v>951</v>
+      </c>
+      <c r="C217" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D217" t="n">
+        <v>6068.2</v>
+      </c>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B218" t="n">
+        <v>571</v>
+      </c>
+      <c r="C218" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D218" t="n">
+        <v>4547.53</v>
+      </c>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B219" t="n">
+        <v>1450</v>
+      </c>
+      <c r="C219" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D219" t="n">
+        <v>692.3200000000001</v>
+      </c>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B220" t="n">
+        <v>2767</v>
+      </c>
+      <c r="C220" t="n">
+        <v>1898</v>
+      </c>
+      <c r="D220" t="n">
+        <v>1706.73</v>
+      </c>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B221" t="n">
+        <v>2810</v>
+      </c>
+      <c r="C221" t="n">
+        <v>3179</v>
+      </c>
+      <c r="D221" t="n">
+        <v>3704.73</v>
+      </c>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B222" t="n">
+        <v>2452</v>
+      </c>
+      <c r="C222" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D222" t="n">
+        <v>1093.58</v>
+      </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B223" t="n">
+        <v>703</v>
+      </c>
+      <c r="C223" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D223" t="n">
+        <v>1829.63</v>
+      </c>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B224" t="n">
+        <v>609</v>
+      </c>
+      <c r="C224" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D224" t="n">
+        <v>1112.69</v>
+      </c>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B225" t="n">
+        <v>2245</v>
+      </c>
+      <c r="C225" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D225" t="n">
+        <v>459.01</v>
+      </c>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B226" t="n">
+        <v>131</v>
+      </c>
+      <c r="C226" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D226" t="n">
+        <v>623.52</v>
+      </c>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B227" t="n">
+        <v>429</v>
+      </c>
+      <c r="C227" t="n">
+        <v>1281</v>
+      </c>
+      <c r="D227" t="n">
+        <v>376.24</v>
+      </c>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B228" t="n">
+        <v>131</v>
+      </c>
+      <c r="C228" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D228" t="n">
+        <v>909.3</v>
+      </c>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B229" t="n">
+        <v>1465</v>
+      </c>
+      <c r="C229" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D229" t="n">
+        <v>3044.97</v>
+      </c>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B230" t="n">
+        <v>1518</v>
+      </c>
+      <c r="C230" t="n">
+        <v>1533</v>
+      </c>
+      <c r="D230" t="n">
+        <v>3838.97</v>
+      </c>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B231" t="n">
+        <v>1756</v>
+      </c>
+      <c r="C231" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D231" t="n">
+        <v>1283.28</v>
+      </c>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B232" t="n">
+        <v>131</v>
+      </c>
+      <c r="C232" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D232" t="n">
+        <v>1035.73</v>
+      </c>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B233" t="n">
+        <v>629</v>
+      </c>
+      <c r="C233" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D233" t="n">
+        <v>2645.87</v>
+      </c>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B234" t="n">
+        <v>351</v>
+      </c>
+      <c r="C234" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D234" t="n">
+        <v>3018</v>
+      </c>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B235" t="n">
+        <v>400</v>
+      </c>
+      <c r="C235" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D235" t="n">
+        <v>688.64</v>
+      </c>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B236" t="n">
+        <v>1324</v>
+      </c>
+      <c r="C236" t="n">
+        <v>3009</v>
+      </c>
+      <c r="D236" t="n">
+        <v>680.4</v>
+      </c>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F248"/>
+  <dimension ref="A1:F257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -729,13 +729,13 @@
         <v>46219</v>
       </c>
       <c r="B15" t="n">
-        <v>2362</v>
+        <v>2660</v>
       </c>
       <c r="C15" t="n">
         <v>8888</v>
       </c>
       <c r="D15" t="n">
-        <v>2827.89</v>
+        <v>832.51</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
@@ -749,13 +749,13 @@
         <v>46219</v>
       </c>
       <c r="B16" t="n">
-        <v>629</v>
+        <v>2362</v>
       </c>
       <c r="C16" t="n">
         <v>8888</v>
       </c>
       <c r="D16" t="n">
-        <v>1693.36</v>
+        <v>2827.89</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
@@ -769,13 +769,13 @@
         <v>46219</v>
       </c>
       <c r="B17" t="n">
-        <v>131</v>
+        <v>629</v>
       </c>
       <c r="C17" t="n">
         <v>8888</v>
       </c>
       <c r="D17" t="n">
-        <v>623.52</v>
+        <v>1693.36</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
@@ -789,13 +789,13 @@
         <v>46219</v>
       </c>
       <c r="B18" t="n">
-        <v>609</v>
+        <v>131</v>
       </c>
       <c r="C18" t="n">
         <v>8888</v>
       </c>
       <c r="D18" t="n">
-        <v>556.35</v>
+        <v>623.52</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
@@ -809,13 +809,13 @@
         <v>46219</v>
       </c>
       <c r="B19" t="n">
-        <v>131</v>
+        <v>609</v>
       </c>
       <c r="C19" t="n">
         <v>8888</v>
       </c>
       <c r="D19" t="n">
-        <v>623.52</v>
+        <v>556.35</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
@@ -829,13 +829,13 @@
         <v>46219</v>
       </c>
       <c r="B20" t="n">
-        <v>559</v>
+        <v>131</v>
       </c>
       <c r="C20" t="n">
         <v>8888</v>
       </c>
       <c r="D20" t="n">
-        <v>9596.75</v>
+        <v>623.52</v>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
@@ -849,13 +849,13 @@
         <v>46219</v>
       </c>
       <c r="B21" t="n">
-        <v>2107</v>
+        <v>559</v>
       </c>
       <c r="C21" t="n">
         <v>8888</v>
       </c>
       <c r="D21" t="n">
-        <v>6978.14</v>
+        <v>9596.75</v>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
@@ -869,13 +869,13 @@
         <v>46219</v>
       </c>
       <c r="B22" t="n">
-        <v>131</v>
+        <v>2107</v>
       </c>
       <c r="C22" t="n">
         <v>8888</v>
       </c>
       <c r="D22" t="n">
-        <v>934.3200000000001</v>
+        <v>6978.14</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
@@ -889,13 +889,13 @@
         <v>46219</v>
       </c>
       <c r="B23" t="n">
-        <v>360</v>
+        <v>131</v>
       </c>
       <c r="C23" t="n">
         <v>8888</v>
       </c>
       <c r="D23" t="n">
-        <v>1990.42</v>
+        <v>934.3200000000001</v>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
@@ -909,13 +909,13 @@
         <v>46219</v>
       </c>
       <c r="B24" t="n">
-        <v>768</v>
+        <v>360</v>
       </c>
       <c r="C24" t="n">
         <v>8888</v>
       </c>
       <c r="D24" t="n">
-        <v>3646.68</v>
+        <v>1990.42</v>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
@@ -929,13 +929,13 @@
         <v>46219</v>
       </c>
       <c r="B25" t="n">
-        <v>483</v>
+        <v>768</v>
       </c>
       <c r="C25" t="n">
         <v>8888</v>
       </c>
       <c r="D25" t="n">
-        <v>150.08</v>
+        <v>3646.68</v>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
@@ -949,13 +949,13 @@
         <v>46219</v>
       </c>
       <c r="B26" t="n">
-        <v>131</v>
+        <v>483</v>
       </c>
       <c r="C26" t="n">
         <v>8888</v>
       </c>
       <c r="D26" t="n">
-        <v>1742.9</v>
+        <v>150.08</v>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
@@ -969,13 +969,13 @@
         <v>46219</v>
       </c>
       <c r="B27" t="n">
-        <v>1478</v>
+        <v>131</v>
       </c>
       <c r="C27" t="n">
         <v>8888</v>
       </c>
       <c r="D27" t="n">
-        <v>4313.2</v>
+        <v>1742.9</v>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
@@ -989,18 +989,18 @@
         <v>46219</v>
       </c>
       <c r="B28" t="n">
-        <v>1756</v>
+        <v>1478</v>
       </c>
       <c r="C28" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D28" t="n">
-        <v>1217.45</v>
+        <v>4313.2</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1009,18 +1009,18 @@
         <v>46219</v>
       </c>
       <c r="B29" t="n">
-        <v>609</v>
+        <v>1756</v>
       </c>
       <c r="C29" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D29" t="n">
-        <v>741.79</v>
+        <v>1217.45</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1029,13 +1029,13 @@
         <v>46219</v>
       </c>
       <c r="B30" t="n">
-        <v>2015</v>
+        <v>609</v>
       </c>
       <c r="C30" t="n">
         <v>8888</v>
       </c>
       <c r="D30" t="n">
-        <v>1011.48</v>
+        <v>741.79</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
@@ -1049,13 +1049,13 @@
         <v>46219</v>
       </c>
       <c r="B31" t="n">
-        <v>629</v>
+        <v>2015</v>
       </c>
       <c r="C31" t="n">
         <v>8888</v>
       </c>
       <c r="D31" t="n">
-        <v>1338.55</v>
+        <v>1011.48</v>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
@@ -1069,18 +1069,18 @@
         <v>46219</v>
       </c>
       <c r="B32" t="n">
-        <v>2250</v>
+        <v>629</v>
       </c>
       <c r="C32" t="n">
         <v>8888</v>
       </c>
       <c r="D32" t="n">
-        <v>1134</v>
+        <v>1338.55</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1089,13 +1089,13 @@
         <v>46219</v>
       </c>
       <c r="B33" t="n">
-        <v>1259</v>
+        <v>2250</v>
       </c>
       <c r="C33" t="n">
         <v>8888</v>
       </c>
       <c r="D33" t="n">
-        <v>213.64</v>
+        <v>1134</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
@@ -1109,13 +1109,13 @@
         <v>46219</v>
       </c>
       <c r="B34" t="n">
-        <v>1756</v>
+        <v>1478</v>
       </c>
       <c r="C34" t="n">
         <v>8888</v>
       </c>
       <c r="D34" t="n">
-        <v>3007.36</v>
+        <v>1224</v>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
@@ -1129,18 +1129,18 @@
         <v>46219</v>
       </c>
       <c r="B35" t="n">
-        <v>1064</v>
+        <v>1259</v>
       </c>
       <c r="C35" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D35" t="n">
-        <v>954.13</v>
+        <v>213.64</v>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1149,13 +1149,13 @@
         <v>46219</v>
       </c>
       <c r="B36" t="n">
-        <v>629</v>
+        <v>1756</v>
       </c>
       <c r="C36" t="n">
         <v>8888</v>
       </c>
       <c r="D36" t="n">
-        <v>1997.38</v>
+        <v>3007.36</v>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
@@ -1169,18 +1169,18 @@
         <v>46219</v>
       </c>
       <c r="B37" t="n">
-        <v>1756</v>
+        <v>131</v>
       </c>
       <c r="C37" t="n">
         <v>8888</v>
       </c>
       <c r="D37" t="n">
-        <v>1399.6</v>
+        <v>425.61</v>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1189,18 +1189,18 @@
         <v>46219</v>
       </c>
       <c r="B38" t="n">
-        <v>1756</v>
+        <v>1064</v>
       </c>
       <c r="C38" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D38" t="n">
-        <v>1383.55</v>
+        <v>954.13</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1209,13 +1209,13 @@
         <v>46219</v>
       </c>
       <c r="B39" t="n">
-        <v>2114</v>
+        <v>629</v>
       </c>
       <c r="C39" t="n">
         <v>8888</v>
       </c>
       <c r="D39" t="n">
-        <v>23987.35</v>
+        <v>1997.38</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
@@ -1229,13 +1229,13 @@
         <v>46219</v>
       </c>
       <c r="B40" t="n">
-        <v>131</v>
+        <v>1756</v>
       </c>
       <c r="C40" t="n">
         <v>8888</v>
       </c>
       <c r="D40" t="n">
-        <v>527.52</v>
+        <v>1399.6</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
@@ -1249,13 +1249,13 @@
         <v>46219</v>
       </c>
       <c r="B41" t="n">
-        <v>816</v>
+        <v>1756</v>
       </c>
       <c r="C41" t="n">
         <v>8888</v>
       </c>
       <c r="D41" t="n">
-        <v>2983.2</v>
+        <v>1383.55</v>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
@@ -1269,13 +1269,13 @@
         <v>46219</v>
       </c>
       <c r="B42" t="n">
-        <v>767</v>
+        <v>2114</v>
       </c>
       <c r="C42" t="n">
         <v>8888</v>
       </c>
       <c r="D42" t="n">
-        <v>428.17</v>
+        <v>23987.35</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
@@ -1289,13 +1289,13 @@
         <v>46219</v>
       </c>
       <c r="B43" t="n">
-        <v>14</v>
+        <v>2190</v>
       </c>
       <c r="C43" t="n">
         <v>8888</v>
       </c>
       <c r="D43" t="n">
-        <v>1155.74</v>
+        <v>1917.4</v>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
@@ -1309,13 +1309,13 @@
         <v>46219</v>
       </c>
       <c r="B44" t="n">
-        <v>20</v>
+        <v>131</v>
       </c>
       <c r="C44" t="n">
         <v>8888</v>
       </c>
       <c r="D44" t="n">
-        <v>10866.88</v>
+        <v>527.52</v>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
@@ -1329,13 +1329,13 @@
         <v>46219</v>
       </c>
       <c r="B45" t="n">
-        <v>629</v>
+        <v>816</v>
       </c>
       <c r="C45" t="n">
         <v>8888</v>
       </c>
       <c r="D45" t="n">
-        <v>14273.2</v>
+        <v>2983.2</v>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
@@ -1349,13 +1349,13 @@
         <v>46219</v>
       </c>
       <c r="B46" t="n">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C46" t="n">
         <v>8888</v>
       </c>
       <c r="D46" t="n">
-        <v>14378.8</v>
+        <v>428.17</v>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
@@ -1369,18 +1369,18 @@
         <v>46219</v>
       </c>
       <c r="B47" t="n">
-        <v>1756</v>
+        <v>14</v>
       </c>
       <c r="C47" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D47" t="n">
-        <v>926.13</v>
+        <v>1155.74</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1389,13 +1389,13 @@
         <v>46219</v>
       </c>
       <c r="B48" t="n">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="C48" t="n">
         <v>8888</v>
       </c>
       <c r="D48" t="n">
-        <v>1904.76</v>
+        <v>10866.88</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
@@ -1409,13 +1409,13 @@
         <v>46219</v>
       </c>
       <c r="B49" t="n">
-        <v>131</v>
+        <v>629</v>
       </c>
       <c r="C49" t="n">
         <v>8888</v>
       </c>
       <c r="D49" t="n">
-        <v>594.8099999999999</v>
+        <v>14273.2</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
@@ -1429,13 +1429,13 @@
         <v>46219</v>
       </c>
       <c r="B50" t="n">
-        <v>2452</v>
+        <v>768</v>
       </c>
       <c r="C50" t="n">
         <v>8888</v>
       </c>
       <c r="D50" t="n">
-        <v>3086.66</v>
+        <v>14378.8</v>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
@@ -1449,18 +1449,18 @@
         <v>46219</v>
       </c>
       <c r="B51" t="n">
-        <v>953</v>
+        <v>1756</v>
       </c>
       <c r="C51" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D51" t="n">
-        <v>604.53</v>
+        <v>926.13</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1469,13 +1469,13 @@
         <v>46219</v>
       </c>
       <c r="B52" t="n">
-        <v>768</v>
+        <v>58</v>
       </c>
       <c r="C52" t="n">
         <v>8888</v>
       </c>
       <c r="D52" t="n">
-        <v>1655.28</v>
+        <v>1904.76</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
@@ -1489,13 +1489,13 @@
         <v>46219</v>
       </c>
       <c r="B53" t="n">
-        <v>768</v>
+        <v>131</v>
       </c>
       <c r="C53" t="n">
         <v>8888</v>
       </c>
       <c r="D53" t="n">
-        <v>536.16</v>
+        <v>594.8099999999999</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
@@ -1509,13 +1509,13 @@
         <v>46219</v>
       </c>
       <c r="B54" t="n">
-        <v>629</v>
+        <v>2452</v>
       </c>
       <c r="C54" t="n">
         <v>8888</v>
       </c>
       <c r="D54" t="n">
-        <v>1276.58</v>
+        <v>3086.66</v>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
@@ -1529,13 +1529,13 @@
         <v>46219</v>
       </c>
       <c r="B55" t="n">
-        <v>1277</v>
+        <v>953</v>
       </c>
       <c r="C55" t="n">
         <v>8888</v>
       </c>
       <c r="D55" t="n">
-        <v>1591.9</v>
+        <v>604.53</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
@@ -1549,13 +1549,13 @@
         <v>46219</v>
       </c>
       <c r="B56" t="n">
-        <v>2163</v>
+        <v>768</v>
       </c>
       <c r="C56" t="n">
         <v>8888</v>
       </c>
       <c r="D56" t="n">
-        <v>406.1</v>
+        <v>1655.28</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
@@ -1569,13 +1569,13 @@
         <v>46219</v>
       </c>
       <c r="B57" t="n">
-        <v>14</v>
+        <v>768</v>
       </c>
       <c r="C57" t="n">
         <v>8888</v>
       </c>
       <c r="D57" t="n">
-        <v>343.54</v>
+        <v>536.16</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
@@ -1589,13 +1589,13 @@
         <v>46219</v>
       </c>
       <c r="B58" t="n">
-        <v>438</v>
+        <v>629</v>
       </c>
       <c r="C58" t="n">
         <v>8888</v>
       </c>
       <c r="D58" t="n">
-        <v>1952.31</v>
+        <v>1276.58</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
@@ -1609,18 +1609,18 @@
         <v>46219</v>
       </c>
       <c r="B59" t="n">
-        <v>768</v>
+        <v>1277</v>
       </c>
       <c r="C59" t="n">
         <v>8888</v>
       </c>
       <c r="D59" t="n">
-        <v>7813.68</v>
+        <v>1591.9</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1629,13 +1629,13 @@
         <v>46219</v>
       </c>
       <c r="B60" t="n">
-        <v>768</v>
+        <v>2163</v>
       </c>
       <c r="C60" t="n">
         <v>8888</v>
       </c>
       <c r="D60" t="n">
-        <v>1291.96</v>
+        <v>406.1</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
@@ -1649,18 +1649,18 @@
         <v>46219</v>
       </c>
       <c r="B61" t="n">
-        <v>1518</v>
+        <v>14</v>
       </c>
       <c r="C61" t="n">
-        <v>1533</v>
+        <v>8888</v>
       </c>
       <c r="D61" t="n">
-        <v>5163.32</v>
+        <v>343.54</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1669,13 +1669,13 @@
         <v>46219</v>
       </c>
       <c r="B62" t="n">
-        <v>2190</v>
+        <v>438</v>
       </c>
       <c r="C62" t="n">
         <v>8888</v>
       </c>
       <c r="D62" t="n">
-        <v>870.03</v>
+        <v>1952.31</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
@@ -1689,18 +1689,18 @@
         <v>46219</v>
       </c>
       <c r="B63" t="n">
-        <v>1518</v>
+        <v>768</v>
       </c>
       <c r="C63" t="n">
-        <v>1533</v>
+        <v>8888</v>
       </c>
       <c r="D63" t="n">
-        <v>4494.7</v>
+        <v>7813.68</v>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1709,13 +1709,13 @@
         <v>46219</v>
       </c>
       <c r="B64" t="n">
-        <v>2452</v>
+        <v>768</v>
       </c>
       <c r="C64" t="n">
         <v>8888</v>
       </c>
       <c r="D64" t="n">
-        <v>1253.5</v>
+        <v>1291.96</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
@@ -1729,13 +1729,13 @@
         <v>46219</v>
       </c>
       <c r="B65" t="n">
-        <v>1756</v>
+        <v>1518</v>
       </c>
       <c r="C65" t="n">
-        <v>27</v>
+        <v>1533</v>
       </c>
       <c r="D65" t="n">
-        <v>1575.17</v>
+        <v>5163.32</v>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
@@ -1749,13 +1749,13 @@
         <v>46219</v>
       </c>
       <c r="B66" t="n">
-        <v>768</v>
+        <v>2190</v>
       </c>
       <c r="C66" t="n">
         <v>8888</v>
       </c>
       <c r="D66" t="n">
-        <v>3118.72</v>
+        <v>870.03</v>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
@@ -1769,18 +1769,18 @@
         <v>46219</v>
       </c>
       <c r="B67" t="n">
-        <v>438</v>
+        <v>1518</v>
       </c>
       <c r="C67" t="n">
-        <v>8888</v>
+        <v>1533</v>
       </c>
       <c r="D67" t="n">
-        <v>338.69</v>
+        <v>4494.7</v>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1789,18 +1789,18 @@
         <v>46219</v>
       </c>
       <c r="B68" t="n">
-        <v>429</v>
+        <v>2452</v>
       </c>
       <c r="C68" t="n">
-        <v>1281</v>
+        <v>8888</v>
       </c>
       <c r="D68" t="n">
-        <v>1867.66</v>
+        <v>1253.5</v>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1809,18 +1809,18 @@
         <v>46219</v>
       </c>
       <c r="B69" t="n">
-        <v>1075</v>
+        <v>1756</v>
       </c>
       <c r="C69" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D69" t="n">
-        <v>1282.67</v>
+        <v>1575.17</v>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1829,13 +1829,13 @@
         <v>46219</v>
       </c>
       <c r="B70" t="n">
-        <v>1064</v>
+        <v>768</v>
       </c>
       <c r="C70" t="n">
         <v>8888</v>
       </c>
       <c r="D70" t="n">
-        <v>2550.8</v>
+        <v>3118.72</v>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
@@ -1849,13 +1849,13 @@
         <v>46219</v>
       </c>
       <c r="B71" t="n">
-        <v>2131</v>
+        <v>438</v>
       </c>
       <c r="C71" t="n">
         <v>8888</v>
       </c>
       <c r="D71" t="n">
-        <v>1153.68</v>
+        <v>338.69</v>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
@@ -1869,18 +1869,18 @@
         <v>46219</v>
       </c>
       <c r="B72" t="n">
-        <v>609</v>
+        <v>429</v>
       </c>
       <c r="C72" t="n">
-        <v>8888</v>
+        <v>1281</v>
       </c>
       <c r="D72" t="n">
-        <v>1854.48</v>
+        <v>1867.66</v>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1889,18 +1889,18 @@
         <v>46219</v>
       </c>
       <c r="B73" t="n">
-        <v>438</v>
+        <v>1075</v>
       </c>
       <c r="C73" t="n">
         <v>8888</v>
       </c>
       <c r="D73" t="n">
-        <v>712</v>
+        <v>1282.67</v>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1909,18 +1909,18 @@
         <v>46219</v>
       </c>
       <c r="B74" t="n">
-        <v>1658</v>
+        <v>1064</v>
       </c>
       <c r="C74" t="n">
         <v>8888</v>
       </c>
       <c r="D74" t="n">
-        <v>311.88</v>
+        <v>2550.8</v>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1929,13 +1929,13 @@
         <v>46219</v>
       </c>
       <c r="B75" t="n">
-        <v>1293</v>
+        <v>2131</v>
       </c>
       <c r="C75" t="n">
         <v>8888</v>
       </c>
       <c r="D75" t="n">
-        <v>1354.46</v>
+        <v>1153.68</v>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
@@ -1949,13 +1949,13 @@
         <v>46219</v>
       </c>
       <c r="B76" t="n">
-        <v>816</v>
+        <v>609</v>
       </c>
       <c r="C76" t="n">
         <v>8888</v>
       </c>
       <c r="D76" t="n">
-        <v>3118.8</v>
+        <v>1854.48</v>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
@@ -1969,13 +1969,13 @@
         <v>46219</v>
       </c>
       <c r="B77" t="n">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="C77" t="n">
         <v>8888</v>
       </c>
       <c r="D77" t="n">
-        <v>2231.47</v>
+        <v>712</v>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
@@ -1989,18 +1989,18 @@
         <v>46219</v>
       </c>
       <c r="B78" t="n">
-        <v>629</v>
+        <v>1658</v>
       </c>
       <c r="C78" t="n">
         <v>8888</v>
       </c>
       <c r="D78" t="n">
-        <v>1178.64</v>
+        <v>311.88</v>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2009,13 +2009,13 @@
         <v>46219</v>
       </c>
       <c r="B79" t="n">
-        <v>703</v>
+        <v>1293</v>
       </c>
       <c r="C79" t="n">
         <v>8888</v>
       </c>
       <c r="D79" t="n">
-        <v>1431.24</v>
+        <v>1354.46</v>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
@@ -2029,13 +2029,13 @@
         <v>46219</v>
       </c>
       <c r="B80" t="n">
-        <v>629</v>
+        <v>816</v>
       </c>
       <c r="C80" t="n">
         <v>8888</v>
       </c>
       <c r="D80" t="n">
-        <v>761.87</v>
+        <v>3118.8</v>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
@@ -2049,13 +2049,13 @@
         <v>46219</v>
       </c>
       <c r="B81" t="n">
-        <v>609</v>
+        <v>451</v>
       </c>
       <c r="C81" t="n">
         <v>8888</v>
       </c>
       <c r="D81" t="n">
-        <v>2107.32</v>
+        <v>2231.47</v>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
@@ -2069,13 +2069,13 @@
         <v>46219</v>
       </c>
       <c r="B82" t="n">
-        <v>1293</v>
+        <v>629</v>
       </c>
       <c r="C82" t="n">
         <v>8888</v>
       </c>
       <c r="D82" t="n">
-        <v>5342.64</v>
+        <v>1178.64</v>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
@@ -2089,13 +2089,13 @@
         <v>46219</v>
       </c>
       <c r="B83" t="n">
-        <v>609</v>
+        <v>703</v>
       </c>
       <c r="C83" t="n">
         <v>8888</v>
       </c>
       <c r="D83" t="n">
-        <v>1919.68</v>
+        <v>1431.24</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
@@ -2109,18 +2109,18 @@
         <v>46219</v>
       </c>
       <c r="B84" t="n">
-        <v>1324</v>
+        <v>629</v>
       </c>
       <c r="C84" t="n">
-        <v>3009</v>
+        <v>8888</v>
       </c>
       <c r="D84" t="n">
-        <v>4396.24</v>
+        <v>761.87</v>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2129,13 +2129,13 @@
         <v>46219</v>
       </c>
       <c r="B85" t="n">
-        <v>400</v>
+        <v>609</v>
       </c>
       <c r="C85" t="n">
         <v>8888</v>
       </c>
       <c r="D85" t="n">
-        <v>1953.42</v>
+        <v>2107.32</v>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
@@ -2149,13 +2149,13 @@
         <v>46219</v>
       </c>
       <c r="B86" t="n">
-        <v>14</v>
+        <v>1293</v>
       </c>
       <c r="C86" t="n">
         <v>8888</v>
       </c>
       <c r="D86" t="n">
-        <v>1006.88</v>
+        <v>5342.64</v>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
@@ -2169,13 +2169,13 @@
         <v>46219</v>
       </c>
       <c r="B87" t="n">
-        <v>2362</v>
+        <v>609</v>
       </c>
       <c r="C87" t="n">
         <v>8888</v>
       </c>
       <c r="D87" t="n">
-        <v>3074.16</v>
+        <v>1919.68</v>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
@@ -2189,13 +2189,13 @@
         <v>46219</v>
       </c>
       <c r="B88" t="n">
-        <v>2279</v>
+        <v>1324</v>
       </c>
       <c r="C88" t="n">
-        <v>1139</v>
+        <v>3009</v>
       </c>
       <c r="D88" t="n">
-        <v>348.16</v>
+        <v>4396.24</v>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
@@ -2209,13 +2209,13 @@
         <v>46219</v>
       </c>
       <c r="B89" t="n">
-        <v>351</v>
+        <v>400</v>
       </c>
       <c r="C89" t="n">
         <v>8888</v>
       </c>
       <c r="D89" t="n">
-        <v>6142.76</v>
+        <v>1953.42</v>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
@@ -2229,18 +2229,18 @@
         <v>46219</v>
       </c>
       <c r="B90" t="n">
-        <v>1299</v>
+        <v>14</v>
       </c>
       <c r="C90" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D90" t="n">
-        <v>1276.32</v>
+        <v>1006.88</v>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2255,7 +2255,7 @@
         <v>8888</v>
       </c>
       <c r="D91" t="n">
-        <v>2291.35</v>
+        <v>3074.16</v>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
@@ -2269,18 +2269,18 @@
         <v>46219</v>
       </c>
       <c r="B92" t="n">
-        <v>131</v>
+        <v>2279</v>
       </c>
       <c r="C92" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D92" t="n">
-        <v>857.34</v>
+        <v>348.16</v>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2289,13 +2289,13 @@
         <v>46219</v>
       </c>
       <c r="B93" t="n">
-        <v>14</v>
+        <v>351</v>
       </c>
       <c r="C93" t="n">
         <v>8888</v>
       </c>
       <c r="D93" t="n">
-        <v>311.88</v>
+        <v>6142.76</v>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
@@ -2309,18 +2309,18 @@
         <v>46219</v>
       </c>
       <c r="B94" t="n">
-        <v>1372</v>
+        <v>1299</v>
       </c>
       <c r="C94" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D94" t="n">
-        <v>10235.04</v>
+        <v>1276.32</v>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2329,13 +2329,13 @@
         <v>46219</v>
       </c>
       <c r="B95" t="n">
-        <v>20</v>
+        <v>2362</v>
       </c>
       <c r="C95" t="n">
         <v>8888</v>
       </c>
       <c r="D95" t="n">
-        <v>4660.07</v>
+        <v>2291.35</v>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
@@ -2349,18 +2349,18 @@
         <v>46219</v>
       </c>
       <c r="B96" t="n">
-        <v>609</v>
+        <v>131</v>
       </c>
       <c r="C96" t="n">
-        <v>3179</v>
+        <v>8888</v>
       </c>
       <c r="D96" t="n">
-        <v>891.63</v>
+        <v>857.34</v>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2369,18 +2369,18 @@
         <v>46219</v>
       </c>
       <c r="B97" t="n">
-        <v>2250</v>
+        <v>14</v>
       </c>
       <c r="C97" t="n">
         <v>8888</v>
       </c>
       <c r="D97" t="n">
-        <v>3311.6</v>
+        <v>311.88</v>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2389,13 +2389,13 @@
         <v>46219</v>
       </c>
       <c r="B98" t="n">
-        <v>1324</v>
+        <v>1372</v>
       </c>
       <c r="C98" t="n">
         <v>8888</v>
       </c>
       <c r="D98" t="n">
-        <v>8134.2</v>
+        <v>10235.04</v>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
@@ -2409,13 +2409,13 @@
         <v>46219</v>
       </c>
       <c r="B99" t="n">
-        <v>2211</v>
+        <v>20</v>
       </c>
       <c r="C99" t="n">
         <v>8888</v>
       </c>
       <c r="D99" t="n">
-        <v>2125.44</v>
+        <v>4660.07</v>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
@@ -2429,18 +2429,18 @@
         <v>46219</v>
       </c>
       <c r="B100" t="n">
-        <v>483</v>
+        <v>609</v>
       </c>
       <c r="C100" t="n">
-        <v>8888</v>
+        <v>3179</v>
       </c>
       <c r="D100" t="n">
-        <v>4217.99</v>
+        <v>891.63</v>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2449,13 +2449,13 @@
         <v>46219</v>
       </c>
       <c r="B101" t="n">
-        <v>1937</v>
+        <v>2250</v>
       </c>
       <c r="C101" t="n">
         <v>8888</v>
       </c>
       <c r="D101" t="n">
-        <v>2231.47</v>
+        <v>3311.6</v>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
@@ -2469,13 +2469,13 @@
         <v>46219</v>
       </c>
       <c r="B102" t="n">
-        <v>40</v>
+        <v>1324</v>
       </c>
       <c r="C102" t="n">
         <v>8888</v>
       </c>
       <c r="D102" t="n">
-        <v>613.16</v>
+        <v>8134.2</v>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
@@ -2489,13 +2489,13 @@
         <v>46219</v>
       </c>
       <c r="B103" t="n">
-        <v>1064</v>
+        <v>2211</v>
       </c>
       <c r="C103" t="n">
         <v>8888</v>
       </c>
       <c r="D103" t="n">
-        <v>720.52</v>
+        <v>2125.44</v>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
@@ -2509,13 +2509,13 @@
         <v>46219</v>
       </c>
       <c r="B104" t="n">
-        <v>1873</v>
+        <v>483</v>
       </c>
       <c r="C104" t="n">
         <v>8888</v>
       </c>
       <c r="D104" t="n">
-        <v>138.39</v>
+        <v>4217.99</v>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
@@ -2529,18 +2529,18 @@
         <v>46219</v>
       </c>
       <c r="B105" t="n">
-        <v>2250</v>
+        <v>1937</v>
       </c>
       <c r="C105" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D105" t="n">
-        <v>1646.82</v>
+        <v>2231.47</v>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2555,12 +2555,12 @@
         <v>8888</v>
       </c>
       <c r="D106" t="n">
-        <v>956.01</v>
+        <v>613.16</v>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2569,13 +2569,13 @@
         <v>46219</v>
       </c>
       <c r="B107" t="n">
-        <v>629</v>
+        <v>1064</v>
       </c>
       <c r="C107" t="n">
         <v>8888</v>
       </c>
       <c r="D107" t="n">
-        <v>18471.2</v>
+        <v>720.52</v>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
@@ -2589,13 +2589,13 @@
         <v>46219</v>
       </c>
       <c r="B108" t="n">
-        <v>703</v>
+        <v>1873</v>
       </c>
       <c r="C108" t="n">
         <v>8888</v>
       </c>
       <c r="D108" t="n">
-        <v>2946.27</v>
+        <v>138.39</v>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
@@ -2609,18 +2609,18 @@
         <v>46219</v>
       </c>
       <c r="B109" t="n">
-        <v>629</v>
+        <v>2250</v>
       </c>
       <c r="C109" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D109" t="n">
-        <v>1002.21</v>
+        <v>1646.82</v>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2629,13 +2629,13 @@
         <v>46219</v>
       </c>
       <c r="B110" t="n">
-        <v>1876</v>
+        <v>40</v>
       </c>
       <c r="C110" t="n">
         <v>8888</v>
       </c>
       <c r="D110" t="n">
-        <v>660.5599999999999</v>
+        <v>956.01</v>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
@@ -2649,18 +2649,18 @@
         <v>46219</v>
       </c>
       <c r="B111" t="n">
-        <v>1075</v>
+        <v>629</v>
       </c>
       <c r="C111" t="n">
         <v>8888</v>
       </c>
       <c r="D111" t="n">
-        <v>325.49</v>
+        <v>18471.2</v>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2669,13 +2669,13 @@
         <v>46219</v>
       </c>
       <c r="B112" t="n">
-        <v>451</v>
+        <v>703</v>
       </c>
       <c r="C112" t="n">
         <v>8888</v>
       </c>
       <c r="D112" t="n">
-        <v>1264.4</v>
+        <v>2946.27</v>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
@@ -2689,18 +2689,18 @@
         <v>46219</v>
       </c>
       <c r="B113" t="n">
-        <v>619</v>
+        <v>629</v>
       </c>
       <c r="C113" t="n">
-        <v>1139</v>
+        <v>8888</v>
       </c>
       <c r="D113" t="n">
-        <v>1169.16</v>
+        <v>1002.21</v>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2709,13 +2709,13 @@
         <v>46219</v>
       </c>
       <c r="B114" t="n">
-        <v>703</v>
+        <v>20</v>
       </c>
       <c r="C114" t="n">
         <v>8888</v>
       </c>
       <c r="D114" t="n">
-        <v>599.88</v>
+        <v>7233.04</v>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
@@ -2729,18 +2729,18 @@
         <v>46219</v>
       </c>
       <c r="B115" t="n">
-        <v>1064</v>
+        <v>1876</v>
       </c>
       <c r="C115" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D115" t="n">
-        <v>954.13</v>
+        <v>660.5599999999999</v>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2749,18 +2749,18 @@
         <v>46219</v>
       </c>
       <c r="B116" t="n">
-        <v>571</v>
+        <v>1075</v>
       </c>
       <c r="C116" t="n">
         <v>8888</v>
       </c>
       <c r="D116" t="n">
-        <v>25609.34</v>
+        <v>325.49</v>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2769,13 +2769,13 @@
         <v>46219</v>
       </c>
       <c r="B117" t="n">
-        <v>131</v>
+        <v>451</v>
       </c>
       <c r="C117" t="n">
         <v>8888</v>
       </c>
       <c r="D117" t="n">
-        <v>934.3200000000001</v>
+        <v>1264.4</v>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
@@ -2789,18 +2789,18 @@
         <v>46219</v>
       </c>
       <c r="B118" t="n">
-        <v>2660</v>
+        <v>619</v>
       </c>
       <c r="C118" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D118" t="n">
-        <v>3419.84</v>
+        <v>1169.16</v>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2809,13 +2809,13 @@
         <v>46219</v>
       </c>
       <c r="B119" t="n">
-        <v>400</v>
+        <v>703</v>
       </c>
       <c r="C119" t="n">
         <v>8888</v>
       </c>
       <c r="D119" t="n">
-        <v>346.8</v>
+        <v>599.88</v>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
@@ -2829,18 +2829,18 @@
         <v>46219</v>
       </c>
       <c r="B120" t="n">
-        <v>2362</v>
+        <v>1064</v>
       </c>
       <c r="C120" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D120" t="n">
-        <v>1457.7</v>
+        <v>954.13</v>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2849,13 +2849,13 @@
         <v>46219</v>
       </c>
       <c r="B121" t="n">
-        <v>816</v>
+        <v>571</v>
       </c>
       <c r="C121" t="n">
         <v>8888</v>
       </c>
       <c r="D121" t="n">
-        <v>311.95</v>
+        <v>25609.34</v>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
@@ -2869,13 +2869,13 @@
         <v>46219</v>
       </c>
       <c r="B122" t="n">
-        <v>20</v>
+        <v>1277</v>
       </c>
       <c r="C122" t="n">
         <v>8888</v>
       </c>
       <c r="D122" t="n">
-        <v>2247.2</v>
+        <v>2666.71</v>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
@@ -2889,13 +2889,13 @@
         <v>46219</v>
       </c>
       <c r="B123" t="n">
-        <v>890</v>
+        <v>131</v>
       </c>
       <c r="C123" t="n">
         <v>8888</v>
       </c>
       <c r="D123" t="n">
-        <v>310.39</v>
+        <v>934.3200000000001</v>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
@@ -2909,13 +2909,13 @@
         <v>46219</v>
       </c>
       <c r="B124" t="n">
-        <v>1293</v>
+        <v>2660</v>
       </c>
       <c r="C124" t="n">
         <v>8888</v>
       </c>
       <c r="D124" t="n">
-        <v>3237.41</v>
+        <v>3419.84</v>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
@@ -2929,13 +2929,13 @@
         <v>46219</v>
       </c>
       <c r="B125" t="n">
-        <v>2452</v>
+        <v>400</v>
       </c>
       <c r="C125" t="n">
         <v>8888</v>
       </c>
       <c r="D125" t="n">
-        <v>1632.81</v>
+        <v>346.8</v>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
@@ -2949,13 +2949,13 @@
         <v>46219</v>
       </c>
       <c r="B126" t="n">
-        <v>483</v>
+        <v>2362</v>
       </c>
       <c r="C126" t="n">
         <v>8888</v>
       </c>
       <c r="D126" t="n">
-        <v>2953.24</v>
+        <v>1457.7</v>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
@@ -2969,13 +2969,13 @@
         <v>46219</v>
       </c>
       <c r="B127" t="n">
-        <v>131</v>
+        <v>816</v>
       </c>
       <c r="C127" t="n">
         <v>8888</v>
       </c>
       <c r="D127" t="n">
-        <v>1384.39</v>
+        <v>311.95</v>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
@@ -2989,13 +2989,13 @@
         <v>46219</v>
       </c>
       <c r="B128" t="n">
-        <v>2652</v>
+        <v>20</v>
       </c>
       <c r="C128" t="n">
         <v>8888</v>
       </c>
       <c r="D128" t="n">
-        <v>3419.64</v>
+        <v>2247.2</v>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
@@ -3009,18 +3009,18 @@
         <v>46219</v>
       </c>
       <c r="B129" t="n">
-        <v>1117</v>
+        <v>890</v>
       </c>
       <c r="C129" t="n">
-        <v>1139</v>
+        <v>8888</v>
       </c>
       <c r="D129" t="n">
-        <v>238.55</v>
+        <v>310.39</v>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3029,13 +3029,13 @@
         <v>46219</v>
       </c>
       <c r="B130" t="n">
-        <v>2107</v>
+        <v>1293</v>
       </c>
       <c r="C130" t="n">
         <v>8888</v>
       </c>
       <c r="D130" t="n">
-        <v>1958.34</v>
+        <v>3237.41</v>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
@@ -3049,13 +3049,13 @@
         <v>46219</v>
       </c>
       <c r="B131" t="n">
-        <v>131</v>
+        <v>2452</v>
       </c>
       <c r="C131" t="n">
         <v>8888</v>
       </c>
       <c r="D131" t="n">
-        <v>767.04</v>
+        <v>1632.81</v>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
@@ -3069,18 +3069,18 @@
         <v>46219</v>
       </c>
       <c r="B132" t="n">
-        <v>1756</v>
+        <v>483</v>
       </c>
       <c r="C132" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D132" t="n">
-        <v>1939.32</v>
+        <v>2953.24</v>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3089,13 +3089,13 @@
         <v>46219</v>
       </c>
       <c r="B133" t="n">
-        <v>1372</v>
+        <v>131</v>
       </c>
       <c r="C133" t="n">
         <v>8888</v>
       </c>
       <c r="D133" t="n">
-        <v>879.6</v>
+        <v>1384.39</v>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
@@ -3109,13 +3109,13 @@
         <v>46219</v>
       </c>
       <c r="B134" t="n">
-        <v>360</v>
+        <v>2652</v>
       </c>
       <c r="C134" t="n">
         <v>8888</v>
       </c>
       <c r="D134" t="n">
-        <v>1906.67</v>
+        <v>3419.64</v>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
@@ -3129,18 +3129,18 @@
         <v>46219</v>
       </c>
       <c r="B135" t="n">
-        <v>131</v>
+        <v>1117</v>
       </c>
       <c r="C135" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D135" t="n">
-        <v>2281.48</v>
+        <v>238.55</v>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3149,13 +3149,13 @@
         <v>46219</v>
       </c>
       <c r="B136" t="n">
-        <v>1372</v>
+        <v>2107</v>
       </c>
       <c r="C136" t="n">
         <v>8888</v>
       </c>
       <c r="D136" t="n">
-        <v>839.58</v>
+        <v>1958.34</v>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
@@ -3169,18 +3169,18 @@
         <v>46219</v>
       </c>
       <c r="B137" t="n">
-        <v>1996</v>
+        <v>131</v>
       </c>
       <c r="C137" t="n">
-        <v>691</v>
+        <v>8888</v>
       </c>
       <c r="D137" t="n">
-        <v>2078.56</v>
+        <v>767.04</v>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3189,13 +3189,13 @@
         <v>46219</v>
       </c>
       <c r="B138" t="n">
-        <v>1064</v>
+        <v>1756</v>
       </c>
       <c r="C138" t="n">
         <v>27</v>
       </c>
       <c r="D138" t="n">
-        <v>954.13</v>
+        <v>1939.32</v>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
@@ -3209,13 +3209,13 @@
         <v>46219</v>
       </c>
       <c r="B139" t="n">
-        <v>559</v>
+        <v>1372</v>
       </c>
       <c r="C139" t="n">
         <v>8888</v>
       </c>
       <c r="D139" t="n">
-        <v>1245.19</v>
+        <v>879.6</v>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
@@ -3229,13 +3229,13 @@
         <v>46219</v>
       </c>
       <c r="B140" t="n">
-        <v>580</v>
+        <v>360</v>
       </c>
       <c r="C140" t="n">
         <v>8888</v>
       </c>
       <c r="D140" t="n">
-        <v>3020.55</v>
+        <v>1906.67</v>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
@@ -3249,13 +3249,13 @@
         <v>46219</v>
       </c>
       <c r="B141" t="n">
-        <v>1064</v>
+        <v>131</v>
       </c>
       <c r="C141" t="n">
         <v>8888</v>
       </c>
       <c r="D141" t="n">
-        <v>1001.61</v>
+        <v>2281.48</v>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
@@ -3269,18 +3269,18 @@
         <v>46219</v>
       </c>
       <c r="B142" t="n">
-        <v>325</v>
+        <v>1372</v>
       </c>
       <c r="C142" t="n">
         <v>8888</v>
       </c>
       <c r="D142" t="n">
-        <v>100.62</v>
+        <v>839.58</v>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3289,18 +3289,18 @@
         <v>46219</v>
       </c>
       <c r="B143" t="n">
-        <v>1293</v>
+        <v>1996</v>
       </c>
       <c r="C143" t="n">
-        <v>8888</v>
+        <v>691</v>
       </c>
       <c r="D143" t="n">
-        <v>1354.46</v>
+        <v>2078.56</v>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3309,18 +3309,18 @@
         <v>46219</v>
       </c>
       <c r="B144" t="n">
-        <v>629</v>
+        <v>1064</v>
       </c>
       <c r="C144" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D144" t="n">
-        <v>1804.42</v>
+        <v>954.13</v>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3329,13 +3329,13 @@
         <v>46219</v>
       </c>
       <c r="B145" t="n">
-        <v>2245</v>
+        <v>559</v>
       </c>
       <c r="C145" t="n">
         <v>8888</v>
       </c>
       <c r="D145" t="n">
-        <v>983.59</v>
+        <v>1245.19</v>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
@@ -3349,13 +3349,13 @@
         <v>46219</v>
       </c>
       <c r="B146" t="n">
-        <v>131</v>
+        <v>580</v>
       </c>
       <c r="C146" t="n">
         <v>8888</v>
       </c>
       <c r="D146" t="n">
-        <v>989.47</v>
+        <v>3020.55</v>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
@@ -3369,13 +3369,13 @@
         <v>46219</v>
       </c>
       <c r="B147" t="n">
-        <v>131</v>
+        <v>1064</v>
       </c>
       <c r="C147" t="n">
         <v>8888</v>
       </c>
       <c r="D147" t="n">
-        <v>934.3200000000001</v>
+        <v>1001.61</v>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
@@ -3389,18 +3389,18 @@
         <v>46219</v>
       </c>
       <c r="B148" t="n">
-        <v>2362</v>
+        <v>325</v>
       </c>
       <c r="C148" t="n">
         <v>8888</v>
       </c>
       <c r="D148" t="n">
-        <v>327.61</v>
+        <v>100.62</v>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3409,18 +3409,18 @@
         <v>46219</v>
       </c>
       <c r="B149" t="n">
-        <v>325</v>
+        <v>1293</v>
       </c>
       <c r="C149" t="n">
         <v>8888</v>
       </c>
       <c r="D149" t="n">
-        <v>25.9</v>
+        <v>1354.46</v>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3429,13 +3429,13 @@
         <v>46219</v>
       </c>
       <c r="B150" t="n">
-        <v>1756</v>
+        <v>629</v>
       </c>
       <c r="C150" t="n">
         <v>8888</v>
       </c>
       <c r="D150" t="n">
-        <v>5236.57</v>
+        <v>1804.42</v>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
@@ -3449,13 +3449,13 @@
         <v>46219</v>
       </c>
       <c r="B151" t="n">
-        <v>20</v>
+        <v>2245</v>
       </c>
       <c r="C151" t="n">
         <v>8888</v>
       </c>
       <c r="D151" t="n">
-        <v>5859.38</v>
+        <v>983.59</v>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
@@ -3469,13 +3469,13 @@
         <v>46219</v>
       </c>
       <c r="B152" t="n">
-        <v>629</v>
+        <v>131</v>
       </c>
       <c r="C152" t="n">
         <v>8888</v>
       </c>
       <c r="D152" t="n">
-        <v>1292.86</v>
+        <v>989.47</v>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
@@ -3489,13 +3489,13 @@
         <v>46219</v>
       </c>
       <c r="B153" t="n">
-        <v>2383</v>
+        <v>131</v>
       </c>
       <c r="C153" t="n">
         <v>8888</v>
       </c>
       <c r="D153" t="n">
-        <v>5887.04</v>
+        <v>934.3200000000001</v>
       </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
@@ -3509,13 +3509,13 @@
         <v>46219</v>
       </c>
       <c r="B154" t="n">
-        <v>131</v>
+        <v>2362</v>
       </c>
       <c r="C154" t="n">
         <v>8888</v>
       </c>
       <c r="D154" t="n">
-        <v>2983.2</v>
+        <v>327.61</v>
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
@@ -3529,18 +3529,18 @@
         <v>46219</v>
       </c>
       <c r="B155" t="n">
-        <v>1007</v>
+        <v>325</v>
       </c>
       <c r="C155" t="n">
         <v>8888</v>
       </c>
       <c r="D155" t="n">
-        <v>1664.69</v>
+        <v>25.9</v>
       </c>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3549,18 +3549,18 @@
         <v>46219</v>
       </c>
       <c r="B156" t="n">
-        <v>890</v>
+        <v>1756</v>
       </c>
       <c r="C156" t="n">
-        <v>1533</v>
+        <v>8888</v>
       </c>
       <c r="D156" t="n">
-        <v>670.6799999999999</v>
+        <v>5236.57</v>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3569,18 +3569,18 @@
         <v>46219</v>
       </c>
       <c r="B157" t="n">
-        <v>325</v>
+        <v>20</v>
       </c>
       <c r="C157" t="n">
         <v>8888</v>
       </c>
       <c r="D157" t="n">
-        <v>44.59</v>
+        <v>5859.38</v>
       </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3589,13 +3589,13 @@
         <v>46219</v>
       </c>
       <c r="B158" t="n">
-        <v>2362</v>
+        <v>629</v>
       </c>
       <c r="C158" t="n">
         <v>8888</v>
       </c>
       <c r="D158" t="n">
-        <v>383.76</v>
+        <v>1292.86</v>
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
@@ -3609,13 +3609,13 @@
         <v>46219</v>
       </c>
       <c r="B159" t="n">
-        <v>1465</v>
+        <v>2383</v>
       </c>
       <c r="C159" t="n">
         <v>8888</v>
       </c>
       <c r="D159" t="n">
-        <v>2350.22</v>
+        <v>5887.04</v>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
@@ -3629,13 +3629,13 @@
         <v>46219</v>
       </c>
       <c r="B160" t="n">
-        <v>483</v>
+        <v>131</v>
       </c>
       <c r="C160" t="n">
         <v>8888</v>
       </c>
       <c r="D160" t="n">
-        <v>689.02</v>
+        <v>2983.2</v>
       </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
@@ -3649,13 +3649,13 @@
         <v>46219</v>
       </c>
       <c r="B161" t="n">
-        <v>2452</v>
+        <v>1007</v>
       </c>
       <c r="C161" t="n">
         <v>8888</v>
       </c>
       <c r="D161" t="n">
-        <v>4530.7</v>
+        <v>1664.69</v>
       </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
@@ -3669,18 +3669,18 @@
         <v>46219</v>
       </c>
       <c r="B162" t="n">
-        <v>400</v>
+        <v>890</v>
       </c>
       <c r="C162" t="n">
-        <v>8888</v>
+        <v>1533</v>
       </c>
       <c r="D162" t="n">
-        <v>1292.32</v>
+        <v>670.6799999999999</v>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3689,18 +3689,18 @@
         <v>46219</v>
       </c>
       <c r="B163" t="n">
-        <v>2362</v>
+        <v>325</v>
       </c>
       <c r="C163" t="n">
         <v>8888</v>
       </c>
       <c r="D163" t="n">
-        <v>744.4</v>
+        <v>44.59</v>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3709,13 +3709,13 @@
         <v>46219</v>
       </c>
       <c r="B164" t="n">
-        <v>1756</v>
+        <v>2362</v>
       </c>
       <c r="C164" t="n">
         <v>8888</v>
       </c>
       <c r="D164" t="n">
-        <v>462.4</v>
+        <v>383.76</v>
       </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
@@ -3729,13 +3729,13 @@
         <v>46219</v>
       </c>
       <c r="B165" t="n">
-        <v>571</v>
+        <v>1465</v>
       </c>
       <c r="C165" t="n">
         <v>8888</v>
       </c>
       <c r="D165" t="n">
-        <v>1125.6</v>
+        <v>2350.22</v>
       </c>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
@@ -3749,13 +3749,13 @@
         <v>46219</v>
       </c>
       <c r="B166" t="n">
-        <v>571</v>
+        <v>483</v>
       </c>
       <c r="C166" t="n">
         <v>8888</v>
       </c>
       <c r="D166" t="n">
-        <v>5997.18</v>
+        <v>689.02</v>
       </c>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
@@ -3769,13 +3769,13 @@
         <v>46219</v>
       </c>
       <c r="B167" t="n">
-        <v>2421</v>
+        <v>2452</v>
       </c>
       <c r="C167" t="n">
         <v>8888</v>
       </c>
       <c r="D167" t="n">
-        <v>2786.14</v>
+        <v>4530.7</v>
       </c>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
@@ -3789,13 +3789,13 @@
         <v>46219</v>
       </c>
       <c r="B168" t="n">
-        <v>953</v>
+        <v>400</v>
       </c>
       <c r="C168" t="n">
         <v>8888</v>
       </c>
       <c r="D168" t="n">
-        <v>6995.34</v>
+        <v>1292.32</v>
       </c>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
@@ -3809,18 +3809,18 @@
         <v>46219</v>
       </c>
       <c r="B169" t="n">
-        <v>2769</v>
+        <v>2362</v>
       </c>
       <c r="C169" t="n">
         <v>8888</v>
       </c>
       <c r="D169" t="n">
-        <v>620.37</v>
+        <v>744.4</v>
       </c>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3829,13 +3829,13 @@
         <v>46219</v>
       </c>
       <c r="B170" t="n">
-        <v>2362</v>
+        <v>1478</v>
       </c>
       <c r="C170" t="n">
         <v>8888</v>
       </c>
       <c r="D170" t="n">
-        <v>8080.76</v>
+        <v>1123.2</v>
       </c>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
@@ -3849,13 +3849,13 @@
         <v>46219</v>
       </c>
       <c r="B171" t="n">
-        <v>629</v>
+        <v>1756</v>
       </c>
       <c r="C171" t="n">
         <v>8888</v>
       </c>
       <c r="D171" t="n">
-        <v>10075.2</v>
+        <v>462.4</v>
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
@@ -3869,13 +3869,13 @@
         <v>46219</v>
       </c>
       <c r="B172" t="n">
-        <v>360</v>
+        <v>571</v>
       </c>
       <c r="C172" t="n">
         <v>8888</v>
       </c>
       <c r="D172" t="n">
-        <v>4617.15</v>
+        <v>1125.6</v>
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
@@ -3889,13 +3889,13 @@
         <v>46219</v>
       </c>
       <c r="B173" t="n">
-        <v>609</v>
+        <v>571</v>
       </c>
       <c r="C173" t="n">
         <v>8888</v>
       </c>
       <c r="D173" t="n">
-        <v>1112.69</v>
+        <v>5997.18</v>
       </c>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
@@ -3909,18 +3909,18 @@
         <v>46219</v>
       </c>
       <c r="B174" t="n">
-        <v>2250</v>
+        <v>2421</v>
       </c>
       <c r="C174" t="n">
         <v>8888</v>
       </c>
       <c r="D174" t="n">
-        <v>2681.88</v>
+        <v>2786.14</v>
       </c>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3929,13 +3929,13 @@
         <v>46219</v>
       </c>
       <c r="B175" t="n">
-        <v>535</v>
+        <v>953</v>
       </c>
       <c r="C175" t="n">
         <v>8888</v>
       </c>
       <c r="D175" t="n">
-        <v>616.54</v>
+        <v>6995.34</v>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
@@ -3949,18 +3949,18 @@
         <v>46219</v>
       </c>
       <c r="B176" t="n">
-        <v>629</v>
+        <v>2769</v>
       </c>
       <c r="C176" t="n">
         <v>8888</v>
       </c>
       <c r="D176" t="n">
-        <v>801.97</v>
+        <v>620.37</v>
       </c>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3969,18 +3969,18 @@
         <v>46219</v>
       </c>
       <c r="B177" t="n">
-        <v>363</v>
+        <v>2362</v>
       </c>
       <c r="C177" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D177" t="n">
-        <v>1618.96</v>
+        <v>8080.76</v>
       </c>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3989,18 +3989,18 @@
         <v>46219</v>
       </c>
       <c r="B178" t="n">
-        <v>1064</v>
+        <v>629</v>
       </c>
       <c r="C178" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D178" t="n">
-        <v>2667.18</v>
+        <v>10075.2</v>
       </c>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4009,13 +4009,13 @@
         <v>46219</v>
       </c>
       <c r="B179" t="n">
-        <v>609</v>
+        <v>360</v>
       </c>
       <c r="C179" t="n">
         <v>8888</v>
       </c>
       <c r="D179" t="n">
-        <v>1141.32</v>
+        <v>4617.15</v>
       </c>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
@@ -4029,18 +4029,18 @@
         <v>46219</v>
       </c>
       <c r="B180" t="n">
-        <v>2250</v>
+        <v>609</v>
       </c>
       <c r="C180" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D180" t="n">
-        <v>551.76</v>
+        <v>1112.69</v>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4049,18 +4049,18 @@
         <v>46219</v>
       </c>
       <c r="B181" t="n">
-        <v>953</v>
+        <v>2250</v>
       </c>
       <c r="C181" t="n">
         <v>8888</v>
       </c>
       <c r="D181" t="n">
-        <v>4366.21</v>
+        <v>2681.88</v>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4069,13 +4069,13 @@
         <v>46219</v>
       </c>
       <c r="B182" t="n">
-        <v>629</v>
+        <v>535</v>
       </c>
       <c r="C182" t="n">
         <v>8888</v>
       </c>
       <c r="D182" t="n">
-        <v>1844.39</v>
+        <v>616.54</v>
       </c>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
@@ -4089,13 +4089,13 @@
         <v>46219</v>
       </c>
       <c r="B183" t="n">
-        <v>1465</v>
+        <v>629</v>
       </c>
       <c r="C183" t="n">
         <v>8888</v>
       </c>
       <c r="D183" t="n">
-        <v>1220.4</v>
+        <v>801.97</v>
       </c>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
@@ -4109,18 +4109,18 @@
         <v>46219</v>
       </c>
       <c r="B184" t="n">
-        <v>1869</v>
+        <v>363</v>
       </c>
       <c r="C184" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D184" t="n">
-        <v>1103.52</v>
+        <v>1618.96</v>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4129,18 +4129,18 @@
         <v>46219</v>
       </c>
       <c r="B185" t="n">
-        <v>2362</v>
+        <v>1064</v>
       </c>
       <c r="C185" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D185" t="n">
-        <v>3256.49</v>
+        <v>2667.18</v>
       </c>
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4149,13 +4149,13 @@
         <v>46219</v>
       </c>
       <c r="B186" t="n">
-        <v>2362</v>
+        <v>609</v>
       </c>
       <c r="C186" t="n">
         <v>8888</v>
       </c>
       <c r="D186" t="n">
-        <v>702.5700000000001</v>
+        <v>1141.32</v>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
@@ -4169,18 +4169,18 @@
         <v>46219</v>
       </c>
       <c r="B187" t="n">
-        <v>2652</v>
+        <v>2250</v>
       </c>
       <c r="C187" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D187" t="n">
-        <v>260.03</v>
+        <v>551.76</v>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4189,13 +4189,13 @@
         <v>46219</v>
       </c>
       <c r="B188" t="n">
-        <v>1465</v>
+        <v>953</v>
       </c>
       <c r="C188" t="n">
         <v>8888</v>
       </c>
       <c r="D188" t="n">
-        <v>3283.11</v>
+        <v>4366.21</v>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
@@ -4209,13 +4209,13 @@
         <v>46219</v>
       </c>
       <c r="B189" t="n">
-        <v>131</v>
+        <v>629</v>
       </c>
       <c r="C189" t="n">
         <v>8888</v>
       </c>
       <c r="D189" t="n">
-        <v>233.82</v>
+        <v>1844.39</v>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
@@ -4229,13 +4229,13 @@
         <v>46219</v>
       </c>
       <c r="B190" t="n">
-        <v>890</v>
+        <v>1465</v>
       </c>
       <c r="C190" t="n">
         <v>8888</v>
       </c>
       <c r="D190" t="n">
-        <v>950.1799999999999</v>
+        <v>1220.4</v>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
@@ -4249,13 +4249,13 @@
         <v>46219</v>
       </c>
       <c r="B191" t="n">
-        <v>2250</v>
+        <v>1869</v>
       </c>
       <c r="C191" t="n">
         <v>8888</v>
       </c>
       <c r="D191" t="n">
-        <v>1596</v>
+        <v>1103.52</v>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
@@ -4269,18 +4269,18 @@
         <v>46219</v>
       </c>
       <c r="B192" t="n">
-        <v>2250</v>
+        <v>2362</v>
       </c>
       <c r="C192" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D192" t="n">
-        <v>2207.04</v>
+        <v>3256.49</v>
       </c>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4289,13 +4289,13 @@
         <v>46219</v>
       </c>
       <c r="B193" t="n">
-        <v>559</v>
+        <v>2362</v>
       </c>
       <c r="C193" t="n">
         <v>8888</v>
       </c>
       <c r="D193" t="n">
-        <v>3594</v>
+        <v>702.5700000000001</v>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
@@ -4309,13 +4309,13 @@
         <v>46219</v>
       </c>
       <c r="B194" t="n">
-        <v>629</v>
+        <v>2652</v>
       </c>
       <c r="C194" t="n">
         <v>8888</v>
       </c>
       <c r="D194" t="n">
-        <v>801.97</v>
+        <v>260.03</v>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
@@ -4329,13 +4329,13 @@
         <v>46219</v>
       </c>
       <c r="B195" t="n">
-        <v>58</v>
+        <v>1465</v>
       </c>
       <c r="C195" t="n">
         <v>8888</v>
       </c>
       <c r="D195" t="n">
-        <v>697.33</v>
+        <v>3283.11</v>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
@@ -4349,18 +4349,18 @@
         <v>46219</v>
       </c>
       <c r="B196" t="n">
-        <v>1108</v>
+        <v>131</v>
       </c>
       <c r="C196" t="n">
         <v>8888</v>
       </c>
       <c r="D196" t="n">
-        <v>341.38</v>
+        <v>233.82</v>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4369,13 +4369,13 @@
         <v>46219</v>
       </c>
       <c r="B197" t="n">
-        <v>2363</v>
+        <v>890</v>
       </c>
       <c r="C197" t="n">
         <v>8888</v>
       </c>
       <c r="D197" t="n">
-        <v>1884.86</v>
+        <v>950.1799999999999</v>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
@@ -4389,13 +4389,13 @@
         <v>46219</v>
       </c>
       <c r="B198" t="n">
-        <v>1007</v>
+        <v>2250</v>
       </c>
       <c r="C198" t="n">
         <v>8888</v>
       </c>
       <c r="D198" t="n">
-        <v>1054.68</v>
+        <v>1596</v>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
@@ -4409,18 +4409,18 @@
         <v>46219</v>
       </c>
       <c r="B199" t="n">
-        <v>1869</v>
+        <v>2250</v>
       </c>
       <c r="C199" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D199" t="n">
-        <v>1698.3</v>
+        <v>2207.04</v>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4429,18 +4429,18 @@
         <v>46219</v>
       </c>
       <c r="B200" t="n">
-        <v>1996</v>
+        <v>559</v>
       </c>
       <c r="C200" t="n">
-        <v>691</v>
+        <v>8888</v>
       </c>
       <c r="D200" t="n">
-        <v>2302.2</v>
+        <v>3594</v>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4449,18 +4449,18 @@
         <v>46219</v>
       </c>
       <c r="B201" t="n">
-        <v>2709</v>
+        <v>629</v>
       </c>
       <c r="C201" t="n">
-        <v>2220</v>
+        <v>8888</v>
       </c>
       <c r="D201" t="n">
-        <v>586.1900000000001</v>
+        <v>801.97</v>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4469,13 +4469,13 @@
         <v>46219</v>
       </c>
       <c r="B202" t="n">
-        <v>1064</v>
+        <v>58</v>
       </c>
       <c r="C202" t="n">
         <v>8888</v>
       </c>
       <c r="D202" t="n">
-        <v>372.95</v>
+        <v>697.33</v>
       </c>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
@@ -4489,18 +4489,18 @@
         <v>46219</v>
       </c>
       <c r="B203" t="n">
-        <v>40</v>
+        <v>1108</v>
       </c>
       <c r="C203" t="n">
         <v>8888</v>
       </c>
       <c r="D203" t="n">
-        <v>306.58</v>
+        <v>341.38</v>
       </c>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4509,18 +4509,18 @@
         <v>46219</v>
       </c>
       <c r="B204" t="n">
-        <v>1996</v>
+        <v>2363</v>
       </c>
       <c r="C204" t="n">
         <v>8888</v>
       </c>
       <c r="D204" t="n">
-        <v>514.91</v>
+        <v>1884.86</v>
       </c>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4529,13 +4529,13 @@
         <v>46219</v>
       </c>
       <c r="B205" t="n">
-        <v>20</v>
+        <v>1007</v>
       </c>
       <c r="C205" t="n">
         <v>8888</v>
       </c>
       <c r="D205" t="n">
-        <v>680.4</v>
+        <v>1054.68</v>
       </c>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
@@ -4549,13 +4549,13 @@
         <v>46219</v>
       </c>
       <c r="B206" t="n">
-        <v>2190</v>
+        <v>1869</v>
       </c>
       <c r="C206" t="n">
         <v>8888</v>
       </c>
       <c r="D206" t="n">
-        <v>1035.41</v>
+        <v>1698.3</v>
       </c>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
@@ -4569,18 +4569,18 @@
         <v>46219</v>
       </c>
       <c r="B207" t="n">
-        <v>781</v>
+        <v>1996</v>
       </c>
       <c r="C207" t="n">
-        <v>8888</v>
+        <v>691</v>
       </c>
       <c r="D207" t="n">
-        <v>1169.2</v>
+        <v>2302.2</v>
       </c>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4589,18 +4589,18 @@
         <v>46219</v>
       </c>
       <c r="B208" t="n">
-        <v>351</v>
+        <v>2709</v>
       </c>
       <c r="C208" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D208" t="n">
-        <v>2207.04</v>
+        <v>586.1900000000001</v>
       </c>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4615,7 +4615,7 @@
         <v>8888</v>
       </c>
       <c r="D209" t="n">
-        <v>2348.64</v>
+        <v>372.95</v>
       </c>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
@@ -4629,13 +4629,13 @@
         <v>46219</v>
       </c>
       <c r="B210" t="n">
-        <v>571</v>
+        <v>40</v>
       </c>
       <c r="C210" t="n">
         <v>8888</v>
       </c>
       <c r="D210" t="n">
-        <v>17843.18</v>
+        <v>306.58</v>
       </c>
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
@@ -4649,18 +4649,18 @@
         <v>46219</v>
       </c>
       <c r="B211" t="n">
-        <v>629</v>
+        <v>1996</v>
       </c>
       <c r="C211" t="n">
         <v>8888</v>
       </c>
       <c r="D211" t="n">
-        <v>1292.86</v>
+        <v>514.91</v>
       </c>
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4669,13 +4669,13 @@
         <v>46219</v>
       </c>
       <c r="B212" t="n">
-        <v>535</v>
+        <v>20</v>
       </c>
       <c r="C212" t="n">
         <v>8888</v>
       </c>
       <c r="D212" t="n">
-        <v>1395.11</v>
+        <v>680.4</v>
       </c>
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
@@ -4689,13 +4689,13 @@
         <v>46219</v>
       </c>
       <c r="B213" t="n">
-        <v>609</v>
+        <v>2190</v>
       </c>
       <c r="C213" t="n">
         <v>8888</v>
       </c>
       <c r="D213" t="n">
-        <v>1487.52</v>
+        <v>1035.41</v>
       </c>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
@@ -4709,13 +4709,13 @@
         <v>46219</v>
       </c>
       <c r="B214" t="n">
-        <v>609</v>
+        <v>781</v>
       </c>
       <c r="C214" t="n">
         <v>8888</v>
       </c>
       <c r="D214" t="n">
-        <v>1854.48</v>
+        <v>1169.2</v>
       </c>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
@@ -4729,13 +4729,13 @@
         <v>46219</v>
       </c>
       <c r="B215" t="n">
-        <v>2660</v>
+        <v>351</v>
       </c>
       <c r="C215" t="n">
         <v>8888</v>
       </c>
       <c r="D215" t="n">
-        <v>1481.24</v>
+        <v>2207.04</v>
       </c>
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
@@ -4749,13 +4749,13 @@
         <v>46219</v>
       </c>
       <c r="B216" t="n">
-        <v>1293</v>
+        <v>1064</v>
       </c>
       <c r="C216" t="n">
         <v>8888</v>
       </c>
       <c r="D216" t="n">
-        <v>1354.46</v>
+        <v>2348.64</v>
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
@@ -4769,13 +4769,13 @@
         <v>46219</v>
       </c>
       <c r="B217" t="n">
-        <v>2768</v>
+        <v>571</v>
       </c>
       <c r="C217" t="n">
         <v>8888</v>
       </c>
       <c r="D217" t="n">
-        <v>2979.54</v>
+        <v>17843.18</v>
       </c>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
@@ -4789,13 +4789,13 @@
         <v>46219</v>
       </c>
       <c r="B218" t="n">
-        <v>1327</v>
+        <v>629</v>
       </c>
       <c r="C218" t="n">
         <v>8888</v>
       </c>
       <c r="D218" t="n">
-        <v>4134.3</v>
+        <v>1292.86</v>
       </c>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
@@ -4809,18 +4809,18 @@
         <v>46219</v>
       </c>
       <c r="B219" t="n">
-        <v>2628</v>
+        <v>535</v>
       </c>
       <c r="C219" t="n">
         <v>8888</v>
       </c>
       <c r="D219" t="n">
-        <v>271.2</v>
+        <v>1395.11</v>
       </c>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4829,13 +4829,13 @@
         <v>46219</v>
       </c>
       <c r="B220" t="n">
-        <v>2452</v>
+        <v>609</v>
       </c>
       <c r="C220" t="n">
         <v>8888</v>
       </c>
       <c r="D220" t="n">
-        <v>1208.26</v>
+        <v>1487.52</v>
       </c>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
@@ -4849,13 +4849,13 @@
         <v>46219</v>
       </c>
       <c r="B221" t="n">
-        <v>131</v>
+        <v>609</v>
       </c>
       <c r="C221" t="n">
         <v>8888</v>
       </c>
       <c r="D221" t="n">
-        <v>848.54</v>
+        <v>1854.48</v>
       </c>
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
@@ -4869,13 +4869,13 @@
         <v>46219</v>
       </c>
       <c r="B222" t="n">
-        <v>816</v>
+        <v>2660</v>
       </c>
       <c r="C222" t="n">
         <v>8888</v>
       </c>
       <c r="D222" t="n">
-        <v>4017.6</v>
+        <v>1481.24</v>
       </c>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
@@ -4889,13 +4889,13 @@
         <v>46219</v>
       </c>
       <c r="B223" t="n">
-        <v>1064</v>
+        <v>1293</v>
       </c>
       <c r="C223" t="n">
         <v>8888</v>
       </c>
       <c r="D223" t="n">
-        <v>4291.42</v>
+        <v>1354.46</v>
       </c>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
@@ -4909,13 +4909,13 @@
         <v>46219</v>
       </c>
       <c r="B224" t="n">
-        <v>703</v>
+        <v>2768</v>
       </c>
       <c r="C224" t="n">
         <v>8888</v>
       </c>
       <c r="D224" t="n">
-        <v>3936.87</v>
+        <v>2979.54</v>
       </c>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
@@ -4929,13 +4929,13 @@
         <v>46219</v>
       </c>
       <c r="B225" t="n">
-        <v>1340</v>
+        <v>1327</v>
       </c>
       <c r="C225" t="n">
         <v>8888</v>
       </c>
       <c r="D225" t="n">
-        <v>2774.78</v>
+        <v>4134.3</v>
       </c>
       <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
@@ -4949,18 +4949,18 @@
         <v>46219</v>
       </c>
       <c r="B226" t="n">
-        <v>2107</v>
+        <v>2628</v>
       </c>
       <c r="C226" t="n">
         <v>8888</v>
       </c>
       <c r="D226" t="n">
-        <v>476.47</v>
+        <v>271.2</v>
       </c>
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4969,13 +4969,13 @@
         <v>46219</v>
       </c>
       <c r="B227" t="n">
-        <v>400</v>
+        <v>2452</v>
       </c>
       <c r="C227" t="n">
         <v>8888</v>
       </c>
       <c r="D227" t="n">
-        <v>2686.56</v>
+        <v>1208.26</v>
       </c>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
@@ -4989,13 +4989,13 @@
         <v>46219</v>
       </c>
       <c r="B228" t="n">
-        <v>559</v>
+        <v>131</v>
       </c>
       <c r="C228" t="n">
         <v>8888</v>
       </c>
       <c r="D228" t="n">
-        <v>9867.299999999999</v>
+        <v>848.54</v>
       </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
@@ -5009,13 +5009,13 @@
         <v>46219</v>
       </c>
       <c r="B229" t="n">
-        <v>951</v>
+        <v>816</v>
       </c>
       <c r="C229" t="n">
         <v>8888</v>
       </c>
       <c r="D229" t="n">
-        <v>6068.2</v>
+        <v>4017.6</v>
       </c>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
@@ -5029,13 +5029,13 @@
         <v>46219</v>
       </c>
       <c r="B230" t="n">
-        <v>571</v>
+        <v>1064</v>
       </c>
       <c r="C230" t="n">
         <v>8888</v>
       </c>
       <c r="D230" t="n">
-        <v>4547.53</v>
+        <v>4291.42</v>
       </c>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
@@ -5049,18 +5049,18 @@
         <v>46219</v>
       </c>
       <c r="B231" t="n">
-        <v>1450</v>
+        <v>703</v>
       </c>
       <c r="C231" t="n">
         <v>8888</v>
       </c>
       <c r="D231" t="n">
-        <v>692.3200000000001</v>
+        <v>3936.87</v>
       </c>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5069,18 +5069,18 @@
         <v>46219</v>
       </c>
       <c r="B232" t="n">
-        <v>2767</v>
+        <v>1340</v>
       </c>
       <c r="C232" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D232" t="n">
-        <v>1706.73</v>
+        <v>2774.78</v>
       </c>
       <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5089,18 +5089,18 @@
         <v>46219</v>
       </c>
       <c r="B233" t="n">
-        <v>2810</v>
+        <v>2107</v>
       </c>
       <c r="C233" t="n">
-        <v>3179</v>
+        <v>8888</v>
       </c>
       <c r="D233" t="n">
-        <v>3704.73</v>
+        <v>476.47</v>
       </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5109,13 +5109,13 @@
         <v>46219</v>
       </c>
       <c r="B234" t="n">
-        <v>2452</v>
+        <v>400</v>
       </c>
       <c r="C234" t="n">
         <v>8888</v>
       </c>
       <c r="D234" t="n">
-        <v>1093.58</v>
+        <v>2686.56</v>
       </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
@@ -5129,13 +5129,13 @@
         <v>46219</v>
       </c>
       <c r="B235" t="n">
-        <v>703</v>
+        <v>559</v>
       </c>
       <c r="C235" t="n">
         <v>8888</v>
       </c>
       <c r="D235" t="n">
-        <v>1829.63</v>
+        <v>9867.299999999999</v>
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
@@ -5149,13 +5149,13 @@
         <v>46219</v>
       </c>
       <c r="B236" t="n">
-        <v>609</v>
+        <v>451</v>
       </c>
       <c r="C236" t="n">
         <v>8888</v>
       </c>
       <c r="D236" t="n">
-        <v>1112.69</v>
+        <v>2131.88</v>
       </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
@@ -5169,13 +5169,13 @@
         <v>46219</v>
       </c>
       <c r="B237" t="n">
-        <v>2245</v>
+        <v>951</v>
       </c>
       <c r="C237" t="n">
         <v>8888</v>
       </c>
       <c r="D237" t="n">
-        <v>459.01</v>
+        <v>6068.2</v>
       </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
@@ -5189,13 +5189,13 @@
         <v>46219</v>
       </c>
       <c r="B238" t="n">
-        <v>131</v>
+        <v>571</v>
       </c>
       <c r="C238" t="n">
         <v>8888</v>
       </c>
       <c r="D238" t="n">
-        <v>623.52</v>
+        <v>4547.53</v>
       </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
@@ -5209,18 +5209,18 @@
         <v>46219</v>
       </c>
       <c r="B239" t="n">
-        <v>429</v>
+        <v>619</v>
       </c>
       <c r="C239" t="n">
-        <v>1281</v>
+        <v>8888</v>
       </c>
       <c r="D239" t="n">
-        <v>376.24</v>
+        <v>1872.16</v>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5229,18 +5229,18 @@
         <v>46219</v>
       </c>
       <c r="B240" t="n">
-        <v>131</v>
+        <v>1450</v>
       </c>
       <c r="C240" t="n">
         <v>8888</v>
       </c>
       <c r="D240" t="n">
-        <v>909.3</v>
+        <v>692.3200000000001</v>
       </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -5249,18 +5249,18 @@
         <v>46219</v>
       </c>
       <c r="B241" t="n">
-        <v>1465</v>
+        <v>2767</v>
       </c>
       <c r="C241" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D241" t="n">
-        <v>3044.97</v>
+        <v>1706.73</v>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -5269,13 +5269,13 @@
         <v>46219</v>
       </c>
       <c r="B242" t="n">
-        <v>1518</v>
+        <v>2810</v>
       </c>
       <c r="C242" t="n">
-        <v>1533</v>
+        <v>3179</v>
       </c>
       <c r="D242" t="n">
-        <v>3838.97</v>
+        <v>3704.73</v>
       </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
@@ -5289,13 +5289,13 @@
         <v>46219</v>
       </c>
       <c r="B243" t="n">
-        <v>1756</v>
+        <v>2452</v>
       </c>
       <c r="C243" t="n">
         <v>8888</v>
       </c>
       <c r="D243" t="n">
-        <v>1283.28</v>
+        <v>1093.58</v>
       </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
@@ -5309,13 +5309,13 @@
         <v>46219</v>
       </c>
       <c r="B244" t="n">
-        <v>131</v>
+        <v>703</v>
       </c>
       <c r="C244" t="n">
         <v>8888</v>
       </c>
       <c r="D244" t="n">
-        <v>1035.73</v>
+        <v>1829.63</v>
       </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
@@ -5329,13 +5329,13 @@
         <v>46219</v>
       </c>
       <c r="B245" t="n">
-        <v>629</v>
+        <v>609</v>
       </c>
       <c r="C245" t="n">
         <v>8888</v>
       </c>
       <c r="D245" t="n">
-        <v>2645.87</v>
+        <v>1112.69</v>
       </c>
       <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr">
@@ -5349,13 +5349,13 @@
         <v>46219</v>
       </c>
       <c r="B246" t="n">
-        <v>351</v>
+        <v>2245</v>
       </c>
       <c r="C246" t="n">
         <v>8888</v>
       </c>
       <c r="D246" t="n">
-        <v>3018</v>
+        <v>459.01</v>
       </c>
       <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
@@ -5369,13 +5369,13 @@
         <v>46219</v>
       </c>
       <c r="B247" t="n">
-        <v>400</v>
+        <v>131</v>
       </c>
       <c r="C247" t="n">
         <v>8888</v>
       </c>
       <c r="D247" t="n">
-        <v>688.64</v>
+        <v>623.52</v>
       </c>
       <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
@@ -5389,16 +5389,196 @@
         <v>46219</v>
       </c>
       <c r="B248" t="n">
-        <v>1324</v>
+        <v>429</v>
       </c>
       <c r="C248" t="n">
-        <v>3009</v>
+        <v>1281</v>
       </c>
       <c r="D248" t="n">
-        <v>680.4</v>
+        <v>376.24</v>
       </c>
       <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B249" t="n">
+        <v>131</v>
+      </c>
+      <c r="C249" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D249" t="n">
+        <v>909.3</v>
+      </c>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B250" t="n">
+        <v>1465</v>
+      </c>
+      <c r="C250" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D250" t="n">
+        <v>3044.97</v>
+      </c>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B251" t="n">
+        <v>1518</v>
+      </c>
+      <c r="C251" t="n">
+        <v>1533</v>
+      </c>
+      <c r="D251" t="n">
+        <v>3838.97</v>
+      </c>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B252" t="n">
+        <v>1756</v>
+      </c>
+      <c r="C252" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D252" t="n">
+        <v>1283.28</v>
+      </c>
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B253" t="n">
+        <v>131</v>
+      </c>
+      <c r="C253" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D253" t="n">
+        <v>1035.73</v>
+      </c>
+      <c r="E253" t="inlineStr"/>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B254" t="n">
+        <v>629</v>
+      </c>
+      <c r="C254" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D254" t="n">
+        <v>2645.87</v>
+      </c>
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B255" t="n">
+        <v>351</v>
+      </c>
+      <c r="C255" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D255" t="n">
+        <v>3018</v>
+      </c>
+      <c r="E255" t="inlineStr"/>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B256" t="n">
+        <v>400</v>
+      </c>
+      <c r="C256" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D256" t="n">
+        <v>688.64</v>
+      </c>
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B257" t="n">
+        <v>1324</v>
+      </c>
+      <c r="C257" t="n">
+        <v>3009</v>
+      </c>
+      <c r="D257" t="n">
+        <v>680.4</v>
+      </c>
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="inlineStr">
         <is>
           <t>TELEMARKETING</t>
         </is>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F257"/>
+  <dimension ref="A1:F323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,18 +489,18 @@
         <v>46219</v>
       </c>
       <c r="B3" t="n">
-        <v>326</v>
+        <v>2696</v>
       </c>
       <c r="C3" t="n">
         <v>8888</v>
       </c>
       <c r="D3" t="n">
-        <v>15.7</v>
+        <v>1811.65</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -509,13 +509,13 @@
         <v>46219</v>
       </c>
       <c r="B4" t="n">
-        <v>1277</v>
+        <v>2698</v>
       </c>
       <c r="C4" t="n">
         <v>8888</v>
       </c>
       <c r="D4" t="n">
-        <v>12007.6</v>
+        <v>369.28</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
@@ -529,18 +529,18 @@
         <v>46219</v>
       </c>
       <c r="B5" t="n">
-        <v>2768</v>
+        <v>326</v>
       </c>
       <c r="C5" t="n">
         <v>8888</v>
       </c>
       <c r="D5" t="n">
-        <v>3071.66</v>
+        <v>15.7</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -549,13 +549,13 @@
         <v>46219</v>
       </c>
       <c r="B6" t="n">
-        <v>2362</v>
+        <v>1277</v>
       </c>
       <c r="C6" t="n">
         <v>8888</v>
       </c>
       <c r="D6" t="n">
-        <v>1594.62</v>
+        <v>12007.6</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
@@ -569,13 +569,13 @@
         <v>46219</v>
       </c>
       <c r="B7" t="n">
-        <v>675</v>
+        <v>2768</v>
       </c>
       <c r="C7" t="n">
         <v>8888</v>
       </c>
       <c r="D7" t="n">
-        <v>210.71</v>
+        <v>3071.66</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
@@ -589,13 +589,13 @@
         <v>46219</v>
       </c>
       <c r="B8" t="n">
-        <v>1372</v>
+        <v>2362</v>
       </c>
       <c r="C8" t="n">
         <v>8888</v>
       </c>
       <c r="D8" t="n">
-        <v>10042.14</v>
+        <v>1594.62</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
@@ -609,18 +609,18 @@
         <v>46219</v>
       </c>
       <c r="B9" t="n">
-        <v>535</v>
+        <v>1299</v>
       </c>
       <c r="C9" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D9" t="n">
-        <v>12275.79</v>
+        <v>481.99</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -629,13 +629,13 @@
         <v>46219</v>
       </c>
       <c r="B10" t="n">
-        <v>609</v>
+        <v>675</v>
       </c>
       <c r="C10" t="n">
         <v>8888</v>
       </c>
       <c r="D10" t="n">
-        <v>1611.48</v>
+        <v>210.71</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
@@ -649,13 +649,13 @@
         <v>46219</v>
       </c>
       <c r="B11" t="n">
-        <v>483</v>
+        <v>1372</v>
       </c>
       <c r="C11" t="n">
         <v>8888</v>
       </c>
       <c r="D11" t="n">
-        <v>685.76</v>
+        <v>10042.14</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
@@ -669,13 +669,13 @@
         <v>46219</v>
       </c>
       <c r="B12" t="n">
-        <v>2190</v>
+        <v>535</v>
       </c>
       <c r="C12" t="n">
         <v>8888</v>
       </c>
       <c r="D12" t="n">
-        <v>11250.64</v>
+        <v>12275.79</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
@@ -689,18 +689,18 @@
         <v>46219</v>
       </c>
       <c r="B13" t="n">
-        <v>1064</v>
+        <v>609</v>
       </c>
       <c r="C13" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D13" t="n">
-        <v>306.58</v>
+        <v>1611.48</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -709,18 +709,18 @@
         <v>46219</v>
       </c>
       <c r="B14" t="n">
-        <v>1324</v>
+        <v>483</v>
       </c>
       <c r="C14" t="n">
-        <v>3009</v>
+        <v>8888</v>
       </c>
       <c r="D14" t="n">
-        <v>178.36</v>
+        <v>685.76</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -729,13 +729,13 @@
         <v>46219</v>
       </c>
       <c r="B15" t="n">
-        <v>2660</v>
+        <v>2190</v>
       </c>
       <c r="C15" t="n">
         <v>8888</v>
       </c>
       <c r="D15" t="n">
-        <v>832.51</v>
+        <v>11250.64</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
@@ -749,18 +749,18 @@
         <v>46219</v>
       </c>
       <c r="B16" t="n">
-        <v>2362</v>
+        <v>1064</v>
       </c>
       <c r="C16" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D16" t="n">
-        <v>2827.89</v>
+        <v>306.58</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -769,18 +769,18 @@
         <v>46219</v>
       </c>
       <c r="B17" t="n">
-        <v>629</v>
+        <v>1324</v>
       </c>
       <c r="C17" t="n">
-        <v>8888</v>
+        <v>3009</v>
       </c>
       <c r="D17" t="n">
-        <v>1693.36</v>
+        <v>178.36</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -789,13 +789,13 @@
         <v>46219</v>
       </c>
       <c r="B18" t="n">
-        <v>131</v>
+        <v>2660</v>
       </c>
       <c r="C18" t="n">
         <v>8888</v>
       </c>
       <c r="D18" t="n">
-        <v>623.52</v>
+        <v>832.51</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
@@ -809,13 +809,13 @@
         <v>46219</v>
       </c>
       <c r="B19" t="n">
-        <v>609</v>
+        <v>2362</v>
       </c>
       <c r="C19" t="n">
         <v>8888</v>
       </c>
       <c r="D19" t="n">
-        <v>556.35</v>
+        <v>2827.89</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
@@ -829,13 +829,13 @@
         <v>46219</v>
       </c>
       <c r="B20" t="n">
-        <v>131</v>
+        <v>629</v>
       </c>
       <c r="C20" t="n">
         <v>8888</v>
       </c>
       <c r="D20" t="n">
-        <v>623.52</v>
+        <v>1693.36</v>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
@@ -849,13 +849,13 @@
         <v>46219</v>
       </c>
       <c r="B21" t="n">
-        <v>559</v>
+        <v>131</v>
       </c>
       <c r="C21" t="n">
         <v>8888</v>
       </c>
       <c r="D21" t="n">
-        <v>9596.75</v>
+        <v>623.52</v>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
@@ -869,13 +869,13 @@
         <v>46219</v>
       </c>
       <c r="B22" t="n">
-        <v>2107</v>
+        <v>609</v>
       </c>
       <c r="C22" t="n">
         <v>8888</v>
       </c>
       <c r="D22" t="n">
-        <v>6978.14</v>
+        <v>556.35</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
@@ -895,7 +895,7 @@
         <v>8888</v>
       </c>
       <c r="D23" t="n">
-        <v>934.3200000000001</v>
+        <v>623.52</v>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
@@ -909,13 +909,13 @@
         <v>46219</v>
       </c>
       <c r="B24" t="n">
-        <v>360</v>
+        <v>559</v>
       </c>
       <c r="C24" t="n">
         <v>8888</v>
       </c>
       <c r="D24" t="n">
-        <v>1990.42</v>
+        <v>9596.75</v>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
@@ -929,13 +929,13 @@
         <v>46219</v>
       </c>
       <c r="B25" t="n">
-        <v>768</v>
+        <v>2250</v>
       </c>
       <c r="C25" t="n">
         <v>8888</v>
       </c>
       <c r="D25" t="n">
-        <v>3646.68</v>
+        <v>1656.98</v>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
@@ -949,13 +949,13 @@
         <v>46219</v>
       </c>
       <c r="B26" t="n">
-        <v>483</v>
+        <v>2107</v>
       </c>
       <c r="C26" t="n">
         <v>8888</v>
       </c>
       <c r="D26" t="n">
-        <v>150.08</v>
+        <v>6978.14</v>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
@@ -975,7 +975,7 @@
         <v>8888</v>
       </c>
       <c r="D27" t="n">
-        <v>1742.9</v>
+        <v>934.3200000000001</v>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
@@ -989,13 +989,13 @@
         <v>46219</v>
       </c>
       <c r="B28" t="n">
-        <v>1478</v>
+        <v>360</v>
       </c>
       <c r="C28" t="n">
         <v>8888</v>
       </c>
       <c r="D28" t="n">
-        <v>4313.2</v>
+        <v>1990.42</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
@@ -1009,18 +1009,18 @@
         <v>46219</v>
       </c>
       <c r="B29" t="n">
-        <v>1756</v>
+        <v>20</v>
       </c>
       <c r="C29" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D29" t="n">
-        <v>1217.45</v>
+        <v>1943.54</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1029,13 +1029,13 @@
         <v>46219</v>
       </c>
       <c r="B30" t="n">
-        <v>609</v>
+        <v>768</v>
       </c>
       <c r="C30" t="n">
         <v>8888</v>
       </c>
       <c r="D30" t="n">
-        <v>741.79</v>
+        <v>3646.68</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
@@ -1049,13 +1049,13 @@
         <v>46219</v>
       </c>
       <c r="B31" t="n">
-        <v>2015</v>
+        <v>483</v>
       </c>
       <c r="C31" t="n">
         <v>8888</v>
       </c>
       <c r="D31" t="n">
-        <v>1011.48</v>
+        <v>150.08</v>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
@@ -1069,13 +1069,13 @@
         <v>46219</v>
       </c>
       <c r="B32" t="n">
-        <v>629</v>
+        <v>131</v>
       </c>
       <c r="C32" t="n">
         <v>8888</v>
       </c>
       <c r="D32" t="n">
-        <v>1338.55</v>
+        <v>1742.9</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
@@ -1089,18 +1089,18 @@
         <v>46219</v>
       </c>
       <c r="B33" t="n">
-        <v>2250</v>
+        <v>1478</v>
       </c>
       <c r="C33" t="n">
         <v>8888</v>
       </c>
       <c r="D33" t="n">
-        <v>1134</v>
+        <v>4313.2</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1109,18 +1109,18 @@
         <v>46219</v>
       </c>
       <c r="B34" t="n">
-        <v>1478</v>
+        <v>1756</v>
       </c>
       <c r="C34" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D34" t="n">
-        <v>1224</v>
+        <v>1217.45</v>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1129,18 +1129,18 @@
         <v>46219</v>
       </c>
       <c r="B35" t="n">
-        <v>1259</v>
+        <v>609</v>
       </c>
       <c r="C35" t="n">
         <v>8888</v>
       </c>
       <c r="D35" t="n">
-        <v>213.64</v>
+        <v>741.79</v>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1149,18 +1149,18 @@
         <v>46219</v>
       </c>
       <c r="B36" t="n">
-        <v>1756</v>
+        <v>285</v>
       </c>
       <c r="C36" t="n">
         <v>8888</v>
       </c>
       <c r="D36" t="n">
-        <v>3007.36</v>
+        <v>701.74</v>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1169,18 +1169,18 @@
         <v>46219</v>
       </c>
       <c r="B37" t="n">
-        <v>131</v>
+        <v>2015</v>
       </c>
       <c r="C37" t="n">
         <v>8888</v>
       </c>
       <c r="D37" t="n">
-        <v>425.61</v>
+        <v>1011.48</v>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1189,18 +1189,18 @@
         <v>46219</v>
       </c>
       <c r="B38" t="n">
-        <v>1064</v>
+        <v>629</v>
       </c>
       <c r="C38" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D38" t="n">
-        <v>954.13</v>
+        <v>1338.55</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1209,18 +1209,18 @@
         <v>46219</v>
       </c>
       <c r="B39" t="n">
-        <v>629</v>
+        <v>2250</v>
       </c>
       <c r="C39" t="n">
         <v>8888</v>
       </c>
       <c r="D39" t="n">
-        <v>1997.38</v>
+        <v>1134</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1229,13 +1229,13 @@
         <v>46219</v>
       </c>
       <c r="B40" t="n">
-        <v>1756</v>
+        <v>1478</v>
       </c>
       <c r="C40" t="n">
         <v>8888</v>
       </c>
       <c r="D40" t="n">
-        <v>1399.6</v>
+        <v>1224</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
@@ -1249,18 +1249,18 @@
         <v>46219</v>
       </c>
       <c r="B41" t="n">
-        <v>1756</v>
+        <v>1259</v>
       </c>
       <c r="C41" t="n">
         <v>8888</v>
       </c>
       <c r="D41" t="n">
-        <v>1383.55</v>
+        <v>213.64</v>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1269,18 +1269,18 @@
         <v>46219</v>
       </c>
       <c r="B42" t="n">
-        <v>2114</v>
+        <v>58</v>
       </c>
       <c r="C42" t="n">
         <v>8888</v>
       </c>
       <c r="D42" t="n">
-        <v>23987.35</v>
+        <v>2254.73</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1289,13 +1289,13 @@
         <v>46219</v>
       </c>
       <c r="B43" t="n">
-        <v>2190</v>
+        <v>1756</v>
       </c>
       <c r="C43" t="n">
         <v>8888</v>
       </c>
       <c r="D43" t="n">
-        <v>1917.4</v>
+        <v>3007.36</v>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
@@ -1315,12 +1315,12 @@
         <v>8888</v>
       </c>
       <c r="D44" t="n">
-        <v>527.52</v>
+        <v>425.61</v>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1329,18 +1329,18 @@
         <v>46219</v>
       </c>
       <c r="B45" t="n">
-        <v>816</v>
+        <v>1937</v>
       </c>
       <c r="C45" t="n">
         <v>8888</v>
       </c>
       <c r="D45" t="n">
-        <v>2983.2</v>
+        <v>1504.37</v>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1349,18 +1349,18 @@
         <v>46219</v>
       </c>
       <c r="B46" t="n">
-        <v>767</v>
+        <v>483</v>
       </c>
       <c r="C46" t="n">
         <v>8888</v>
       </c>
       <c r="D46" t="n">
-        <v>428.17</v>
+        <v>859.24</v>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1369,18 +1369,18 @@
         <v>46219</v>
       </c>
       <c r="B47" t="n">
-        <v>14</v>
+        <v>1064</v>
       </c>
       <c r="C47" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D47" t="n">
-        <v>1155.74</v>
+        <v>954.13</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1389,13 +1389,13 @@
         <v>46219</v>
       </c>
       <c r="B48" t="n">
-        <v>20</v>
+        <v>629</v>
       </c>
       <c r="C48" t="n">
         <v>8888</v>
       </c>
       <c r="D48" t="n">
-        <v>10866.88</v>
+        <v>1997.38</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
@@ -1409,13 +1409,13 @@
         <v>46219</v>
       </c>
       <c r="B49" t="n">
-        <v>629</v>
+        <v>1756</v>
       </c>
       <c r="C49" t="n">
         <v>8888</v>
       </c>
       <c r="D49" t="n">
-        <v>14273.2</v>
+        <v>1399.6</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
@@ -1429,13 +1429,13 @@
         <v>46219</v>
       </c>
       <c r="B50" t="n">
-        <v>768</v>
+        <v>1756</v>
       </c>
       <c r="C50" t="n">
         <v>8888</v>
       </c>
       <c r="D50" t="n">
-        <v>14378.8</v>
+        <v>1383.55</v>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
@@ -1449,18 +1449,18 @@
         <v>46219</v>
       </c>
       <c r="B51" t="n">
-        <v>1756</v>
+        <v>2114</v>
       </c>
       <c r="C51" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D51" t="n">
-        <v>926.13</v>
+        <v>23987.35</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1469,13 +1469,13 @@
         <v>46219</v>
       </c>
       <c r="B52" t="n">
-        <v>58</v>
+        <v>2190</v>
       </c>
       <c r="C52" t="n">
         <v>8888</v>
       </c>
       <c r="D52" t="n">
-        <v>1904.76</v>
+        <v>1181.72</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
@@ -1495,7 +1495,7 @@
         <v>8888</v>
       </c>
       <c r="D53" t="n">
-        <v>594.8099999999999</v>
+        <v>527.52</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
@@ -1509,13 +1509,13 @@
         <v>46219</v>
       </c>
       <c r="B54" t="n">
-        <v>2452</v>
+        <v>816</v>
       </c>
       <c r="C54" t="n">
         <v>8888</v>
       </c>
       <c r="D54" t="n">
-        <v>3086.66</v>
+        <v>2983.2</v>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
@@ -1529,18 +1529,18 @@
         <v>46219</v>
       </c>
       <c r="B55" t="n">
-        <v>953</v>
+        <v>767</v>
       </c>
       <c r="C55" t="n">
         <v>8888</v>
       </c>
       <c r="D55" t="n">
-        <v>604.53</v>
+        <v>428.17</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1549,13 +1549,13 @@
         <v>46219</v>
       </c>
       <c r="B56" t="n">
-        <v>768</v>
+        <v>14</v>
       </c>
       <c r="C56" t="n">
         <v>8888</v>
       </c>
       <c r="D56" t="n">
-        <v>1655.28</v>
+        <v>1155.74</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
@@ -1569,13 +1569,13 @@
         <v>46219</v>
       </c>
       <c r="B57" t="n">
-        <v>768</v>
+        <v>20</v>
       </c>
       <c r="C57" t="n">
         <v>8888</v>
       </c>
       <c r="D57" t="n">
-        <v>536.16</v>
+        <v>10866.88</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
@@ -1589,18 +1589,18 @@
         <v>46219</v>
       </c>
       <c r="B58" t="n">
-        <v>629</v>
+        <v>2547</v>
       </c>
       <c r="C58" t="n">
         <v>8888</v>
       </c>
       <c r="D58" t="n">
-        <v>1276.58</v>
+        <v>2027.52</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1609,18 +1609,18 @@
         <v>46219</v>
       </c>
       <c r="B59" t="n">
-        <v>1277</v>
+        <v>629</v>
       </c>
       <c r="C59" t="n">
         <v>8888</v>
       </c>
       <c r="D59" t="n">
-        <v>1591.9</v>
+        <v>14273.2</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1629,18 +1629,18 @@
         <v>46219</v>
       </c>
       <c r="B60" t="n">
-        <v>2163</v>
+        <v>559</v>
       </c>
       <c r="C60" t="n">
         <v>8888</v>
       </c>
       <c r="D60" t="n">
-        <v>406.1</v>
+        <v>562.45</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1649,13 +1649,13 @@
         <v>46219</v>
       </c>
       <c r="B61" t="n">
-        <v>14</v>
+        <v>768</v>
       </c>
       <c r="C61" t="n">
         <v>8888</v>
       </c>
       <c r="D61" t="n">
-        <v>343.54</v>
+        <v>14378.8</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
@@ -1669,18 +1669,18 @@
         <v>46219</v>
       </c>
       <c r="B62" t="n">
-        <v>438</v>
+        <v>1756</v>
       </c>
       <c r="C62" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D62" t="n">
-        <v>1952.31</v>
+        <v>926.13</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1689,13 +1689,13 @@
         <v>46219</v>
       </c>
       <c r="B63" t="n">
-        <v>768</v>
+        <v>58</v>
       </c>
       <c r="C63" t="n">
         <v>8888</v>
       </c>
       <c r="D63" t="n">
-        <v>7813.68</v>
+        <v>1904.76</v>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
@@ -1709,13 +1709,13 @@
         <v>46219</v>
       </c>
       <c r="B64" t="n">
-        <v>768</v>
+        <v>131</v>
       </c>
       <c r="C64" t="n">
         <v>8888</v>
       </c>
       <c r="D64" t="n">
-        <v>1291.96</v>
+        <v>594.8099999999999</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
@@ -1729,18 +1729,18 @@
         <v>46219</v>
       </c>
       <c r="B65" t="n">
-        <v>1518</v>
+        <v>58</v>
       </c>
       <c r="C65" t="n">
-        <v>1533</v>
+        <v>8888</v>
       </c>
       <c r="D65" t="n">
-        <v>5163.32</v>
+        <v>4308.9</v>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1749,13 +1749,13 @@
         <v>46219</v>
       </c>
       <c r="B66" t="n">
-        <v>2190</v>
+        <v>2452</v>
       </c>
       <c r="C66" t="n">
         <v>8888</v>
       </c>
       <c r="D66" t="n">
-        <v>870.03</v>
+        <v>3086.66</v>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
@@ -1769,18 +1769,18 @@
         <v>46219</v>
       </c>
       <c r="B67" t="n">
-        <v>1518</v>
+        <v>953</v>
       </c>
       <c r="C67" t="n">
-        <v>1533</v>
+        <v>8888</v>
       </c>
       <c r="D67" t="n">
-        <v>4494.7</v>
+        <v>604.53</v>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1789,13 +1789,13 @@
         <v>46219</v>
       </c>
       <c r="B68" t="n">
-        <v>2452</v>
+        <v>768</v>
       </c>
       <c r="C68" t="n">
         <v>8888</v>
       </c>
       <c r="D68" t="n">
-        <v>1253.5</v>
+        <v>1655.28</v>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
@@ -1809,18 +1809,18 @@
         <v>46219</v>
       </c>
       <c r="B69" t="n">
-        <v>1756</v>
+        <v>768</v>
       </c>
       <c r="C69" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D69" t="n">
-        <v>1575.17</v>
+        <v>536.16</v>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1829,18 +1829,18 @@
         <v>46219</v>
       </c>
       <c r="B70" t="n">
-        <v>768</v>
+        <v>2547</v>
       </c>
       <c r="C70" t="n">
         <v>8888</v>
       </c>
       <c r="D70" t="n">
-        <v>3118.72</v>
+        <v>740.08</v>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1849,13 +1849,13 @@
         <v>46219</v>
       </c>
       <c r="B71" t="n">
-        <v>438</v>
+        <v>629</v>
       </c>
       <c r="C71" t="n">
         <v>8888</v>
       </c>
       <c r="D71" t="n">
-        <v>338.69</v>
+        <v>1276.58</v>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
@@ -1869,18 +1869,18 @@
         <v>46219</v>
       </c>
       <c r="B72" t="n">
-        <v>429</v>
+        <v>131</v>
       </c>
       <c r="C72" t="n">
-        <v>1281</v>
+        <v>8888</v>
       </c>
       <c r="D72" t="n">
-        <v>1867.66</v>
+        <v>783.86</v>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1889,13 +1889,13 @@
         <v>46219</v>
       </c>
       <c r="B73" t="n">
-        <v>1075</v>
+        <v>1277</v>
       </c>
       <c r="C73" t="n">
         <v>8888</v>
       </c>
       <c r="D73" t="n">
-        <v>1282.67</v>
+        <v>1591.9</v>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
@@ -1909,13 +1909,13 @@
         <v>46219</v>
       </c>
       <c r="B74" t="n">
-        <v>1064</v>
+        <v>2163</v>
       </c>
       <c r="C74" t="n">
         <v>8888</v>
       </c>
       <c r="D74" t="n">
-        <v>2550.8</v>
+        <v>406.1</v>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
@@ -1929,13 +1929,13 @@
         <v>46219</v>
       </c>
       <c r="B75" t="n">
-        <v>2131</v>
+        <v>14</v>
       </c>
       <c r="C75" t="n">
         <v>8888</v>
       </c>
       <c r="D75" t="n">
-        <v>1153.68</v>
+        <v>343.54</v>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
@@ -1949,18 +1949,18 @@
         <v>46219</v>
       </c>
       <c r="B76" t="n">
-        <v>609</v>
+        <v>2516</v>
       </c>
       <c r="C76" t="n">
         <v>8888</v>
       </c>
       <c r="D76" t="n">
-        <v>1854.48</v>
+        <v>529.88</v>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1975,7 +1975,7 @@
         <v>8888</v>
       </c>
       <c r="D77" t="n">
-        <v>712</v>
+        <v>1952.31</v>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
@@ -1989,18 +1989,18 @@
         <v>46219</v>
       </c>
       <c r="B78" t="n">
-        <v>1658</v>
+        <v>768</v>
       </c>
       <c r="C78" t="n">
         <v>8888</v>
       </c>
       <c r="D78" t="n">
-        <v>311.88</v>
+        <v>7813.68</v>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2009,13 +2009,13 @@
         <v>46219</v>
       </c>
       <c r="B79" t="n">
-        <v>1293</v>
+        <v>768</v>
       </c>
       <c r="C79" t="n">
         <v>8888</v>
       </c>
       <c r="D79" t="n">
-        <v>1354.46</v>
+        <v>1291.96</v>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
@@ -2029,18 +2029,18 @@
         <v>46219</v>
       </c>
       <c r="B80" t="n">
-        <v>816</v>
+        <v>1518</v>
       </c>
       <c r="C80" t="n">
-        <v>8888</v>
+        <v>1533</v>
       </c>
       <c r="D80" t="n">
-        <v>3118.8</v>
+        <v>5163.32</v>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2049,13 +2049,13 @@
         <v>46219</v>
       </c>
       <c r="B81" t="n">
-        <v>451</v>
+        <v>2190</v>
       </c>
       <c r="C81" t="n">
         <v>8888</v>
       </c>
       <c r="D81" t="n">
-        <v>2231.47</v>
+        <v>870.03</v>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
@@ -2069,18 +2069,18 @@
         <v>46219</v>
       </c>
       <c r="B82" t="n">
-        <v>629</v>
+        <v>1478</v>
       </c>
       <c r="C82" t="n">
         <v>8888</v>
       </c>
       <c r="D82" t="n">
-        <v>1178.64</v>
+        <v>10946.54</v>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2089,13 +2089,13 @@
         <v>46219</v>
       </c>
       <c r="B83" t="n">
-        <v>703</v>
+        <v>2729</v>
       </c>
       <c r="C83" t="n">
         <v>8888</v>
       </c>
       <c r="D83" t="n">
-        <v>1431.24</v>
+        <v>585.41</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
@@ -2109,18 +2109,18 @@
         <v>46219</v>
       </c>
       <c r="B84" t="n">
-        <v>629</v>
+        <v>1518</v>
       </c>
       <c r="C84" t="n">
-        <v>8888</v>
+        <v>1533</v>
       </c>
       <c r="D84" t="n">
-        <v>761.87</v>
+        <v>4494.7</v>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2129,13 +2129,13 @@
         <v>46219</v>
       </c>
       <c r="B85" t="n">
-        <v>609</v>
+        <v>2452</v>
       </c>
       <c r="C85" t="n">
         <v>8888</v>
       </c>
       <c r="D85" t="n">
-        <v>2107.32</v>
+        <v>1253.5</v>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
@@ -2149,18 +2149,18 @@
         <v>46219</v>
       </c>
       <c r="B86" t="n">
-        <v>1293</v>
+        <v>1756</v>
       </c>
       <c r="C86" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D86" t="n">
-        <v>5342.64</v>
+        <v>1575.17</v>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2169,13 +2169,13 @@
         <v>46219</v>
       </c>
       <c r="B87" t="n">
-        <v>609</v>
+        <v>768</v>
       </c>
       <c r="C87" t="n">
         <v>8888</v>
       </c>
       <c r="D87" t="n">
-        <v>1919.68</v>
+        <v>3118.72</v>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
@@ -2189,18 +2189,18 @@
         <v>46219</v>
       </c>
       <c r="B88" t="n">
-        <v>1324</v>
+        <v>768</v>
       </c>
       <c r="C88" t="n">
-        <v>3009</v>
+        <v>8888</v>
       </c>
       <c r="D88" t="n">
-        <v>4396.24</v>
+        <v>2849.76</v>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2209,13 +2209,13 @@
         <v>46219</v>
       </c>
       <c r="B89" t="n">
-        <v>400</v>
+        <v>438</v>
       </c>
       <c r="C89" t="n">
         <v>8888</v>
       </c>
       <c r="D89" t="n">
-        <v>1953.42</v>
+        <v>338.69</v>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
@@ -2229,18 +2229,18 @@
         <v>46219</v>
       </c>
       <c r="B90" t="n">
-        <v>14</v>
+        <v>429</v>
       </c>
       <c r="C90" t="n">
-        <v>8888</v>
+        <v>1281</v>
       </c>
       <c r="D90" t="n">
-        <v>1006.88</v>
+        <v>1867.66</v>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2249,18 +2249,18 @@
         <v>46219</v>
       </c>
       <c r="B91" t="n">
-        <v>2362</v>
+        <v>1075</v>
       </c>
       <c r="C91" t="n">
         <v>8888</v>
       </c>
       <c r="D91" t="n">
-        <v>3074.16</v>
+        <v>1282.67</v>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2269,18 +2269,18 @@
         <v>46219</v>
       </c>
       <c r="B92" t="n">
-        <v>2279</v>
+        <v>1372</v>
       </c>
       <c r="C92" t="n">
-        <v>1139</v>
+        <v>8888</v>
       </c>
       <c r="D92" t="n">
-        <v>348.16</v>
+        <v>1119.6</v>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2289,13 +2289,13 @@
         <v>46219</v>
       </c>
       <c r="B93" t="n">
-        <v>351</v>
+        <v>1064</v>
       </c>
       <c r="C93" t="n">
         <v>8888</v>
       </c>
       <c r="D93" t="n">
-        <v>6142.76</v>
+        <v>2550.8</v>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
@@ -2309,18 +2309,18 @@
         <v>46219</v>
       </c>
       <c r="B94" t="n">
-        <v>1299</v>
+        <v>2131</v>
       </c>
       <c r="C94" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D94" t="n">
-        <v>1276.32</v>
+        <v>1153.68</v>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2329,13 +2329,13 @@
         <v>46219</v>
       </c>
       <c r="B95" t="n">
-        <v>2362</v>
+        <v>609</v>
       </c>
       <c r="C95" t="n">
         <v>8888</v>
       </c>
       <c r="D95" t="n">
-        <v>2291.35</v>
+        <v>1854.48</v>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
@@ -2349,13 +2349,13 @@
         <v>46219</v>
       </c>
       <c r="B96" t="n">
-        <v>131</v>
+        <v>438</v>
       </c>
       <c r="C96" t="n">
         <v>8888</v>
       </c>
       <c r="D96" t="n">
-        <v>857.34</v>
+        <v>712</v>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
@@ -2369,7 +2369,7 @@
         <v>46219</v>
       </c>
       <c r="B97" t="n">
-        <v>14</v>
+        <v>1658</v>
       </c>
       <c r="C97" t="n">
         <v>8888</v>
@@ -2380,7 +2380,7 @@
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2389,13 +2389,13 @@
         <v>46219</v>
       </c>
       <c r="B98" t="n">
-        <v>1372</v>
+        <v>1293</v>
       </c>
       <c r="C98" t="n">
         <v>8888</v>
       </c>
       <c r="D98" t="n">
-        <v>10235.04</v>
+        <v>1354.46</v>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
@@ -2409,13 +2409,13 @@
         <v>46219</v>
       </c>
       <c r="B99" t="n">
-        <v>20</v>
+        <v>816</v>
       </c>
       <c r="C99" t="n">
         <v>8888</v>
       </c>
       <c r="D99" t="n">
-        <v>4660.07</v>
+        <v>3118.8</v>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
@@ -2429,18 +2429,18 @@
         <v>46219</v>
       </c>
       <c r="B100" t="n">
-        <v>609</v>
+        <v>451</v>
       </c>
       <c r="C100" t="n">
-        <v>3179</v>
+        <v>8888</v>
       </c>
       <c r="D100" t="n">
-        <v>891.63</v>
+        <v>2231.47</v>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2449,18 +2449,18 @@
         <v>46219</v>
       </c>
       <c r="B101" t="n">
-        <v>2250</v>
+        <v>629</v>
       </c>
       <c r="C101" t="n">
         <v>8888</v>
       </c>
       <c r="D101" t="n">
-        <v>3311.6</v>
+        <v>1178.64</v>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2469,13 +2469,13 @@
         <v>46219</v>
       </c>
       <c r="B102" t="n">
-        <v>1324</v>
+        <v>703</v>
       </c>
       <c r="C102" t="n">
         <v>8888</v>
       </c>
       <c r="D102" t="n">
-        <v>8134.2</v>
+        <v>1431.24</v>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
@@ -2489,13 +2489,13 @@
         <v>46219</v>
       </c>
       <c r="B103" t="n">
-        <v>2211</v>
+        <v>629</v>
       </c>
       <c r="C103" t="n">
         <v>8888</v>
       </c>
       <c r="D103" t="n">
-        <v>2125.44</v>
+        <v>761.87</v>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
@@ -2509,13 +2509,13 @@
         <v>46219</v>
       </c>
       <c r="B104" t="n">
-        <v>483</v>
+        <v>609</v>
       </c>
       <c r="C104" t="n">
         <v>8888</v>
       </c>
       <c r="D104" t="n">
-        <v>4217.99</v>
+        <v>2107.32</v>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
@@ -2529,18 +2529,18 @@
         <v>46219</v>
       </c>
       <c r="B105" t="n">
-        <v>1937</v>
+        <v>1293</v>
       </c>
       <c r="C105" t="n">
         <v>8888</v>
       </c>
       <c r="D105" t="n">
-        <v>2231.47</v>
+        <v>5342.64</v>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2549,13 +2549,13 @@
         <v>46219</v>
       </c>
       <c r="B106" t="n">
-        <v>40</v>
+        <v>609</v>
       </c>
       <c r="C106" t="n">
         <v>8888</v>
       </c>
       <c r="D106" t="n">
-        <v>613.16</v>
+        <v>1919.68</v>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
@@ -2569,18 +2569,18 @@
         <v>46219</v>
       </c>
       <c r="B107" t="n">
-        <v>1064</v>
+        <v>1324</v>
       </c>
       <c r="C107" t="n">
-        <v>8888</v>
+        <v>3009</v>
       </c>
       <c r="D107" t="n">
-        <v>720.52</v>
+        <v>4396.24</v>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2589,13 +2589,13 @@
         <v>46219</v>
       </c>
       <c r="B108" t="n">
-        <v>1873</v>
+        <v>400</v>
       </c>
       <c r="C108" t="n">
         <v>8888</v>
       </c>
       <c r="D108" t="n">
-        <v>138.39</v>
+        <v>1953.42</v>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
@@ -2609,18 +2609,18 @@
         <v>46219</v>
       </c>
       <c r="B109" t="n">
-        <v>2250</v>
+        <v>14</v>
       </c>
       <c r="C109" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D109" t="n">
-        <v>1646.82</v>
+        <v>1006.88</v>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2629,18 +2629,18 @@
         <v>46219</v>
       </c>
       <c r="B110" t="n">
-        <v>40</v>
+        <v>451</v>
       </c>
       <c r="C110" t="n">
         <v>8888</v>
       </c>
       <c r="D110" t="n">
-        <v>956.01</v>
+        <v>554.15</v>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2649,13 +2649,13 @@
         <v>46219</v>
       </c>
       <c r="B111" t="n">
-        <v>629</v>
+        <v>2362</v>
       </c>
       <c r="C111" t="n">
         <v>8888</v>
       </c>
       <c r="D111" t="n">
-        <v>18471.2</v>
+        <v>3074.16</v>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
@@ -2669,18 +2669,18 @@
         <v>46219</v>
       </c>
       <c r="B112" t="n">
-        <v>703</v>
+        <v>2279</v>
       </c>
       <c r="C112" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D112" t="n">
-        <v>2946.27</v>
+        <v>348.16</v>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2689,13 +2689,13 @@
         <v>46219</v>
       </c>
       <c r="B113" t="n">
-        <v>629</v>
+        <v>351</v>
       </c>
       <c r="C113" t="n">
         <v>8888</v>
       </c>
       <c r="D113" t="n">
-        <v>1002.21</v>
+        <v>6142.76</v>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
@@ -2709,18 +2709,18 @@
         <v>46219</v>
       </c>
       <c r="B114" t="n">
-        <v>20</v>
+        <v>1299</v>
       </c>
       <c r="C114" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D114" t="n">
-        <v>7233.04</v>
+        <v>1276.32</v>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2729,18 +2729,18 @@
         <v>46219</v>
       </c>
       <c r="B115" t="n">
-        <v>1876</v>
+        <v>2362</v>
       </c>
       <c r="C115" t="n">
         <v>8888</v>
       </c>
       <c r="D115" t="n">
-        <v>660.5599999999999</v>
+        <v>2291.35</v>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2749,18 +2749,18 @@
         <v>46219</v>
       </c>
       <c r="B116" t="n">
-        <v>1075</v>
+        <v>2279</v>
       </c>
       <c r="C116" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D116" t="n">
-        <v>325.49</v>
+        <v>1241.07</v>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2769,13 +2769,13 @@
         <v>46219</v>
       </c>
       <c r="B117" t="n">
-        <v>451</v>
+        <v>131</v>
       </c>
       <c r="C117" t="n">
         <v>8888</v>
       </c>
       <c r="D117" t="n">
-        <v>1264.4</v>
+        <v>857.34</v>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
@@ -2789,18 +2789,18 @@
         <v>46219</v>
       </c>
       <c r="B118" t="n">
-        <v>619</v>
+        <v>14</v>
       </c>
       <c r="C118" t="n">
-        <v>1139</v>
+        <v>8888</v>
       </c>
       <c r="D118" t="n">
-        <v>1169.16</v>
+        <v>311.88</v>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2809,18 +2809,18 @@
         <v>46219</v>
       </c>
       <c r="B119" t="n">
-        <v>703</v>
+        <v>569</v>
       </c>
       <c r="C119" t="n">
         <v>8888</v>
       </c>
       <c r="D119" t="n">
-        <v>599.88</v>
+        <v>710</v>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2829,18 +2829,18 @@
         <v>46219</v>
       </c>
       <c r="B120" t="n">
-        <v>1064</v>
+        <v>1372</v>
       </c>
       <c r="C120" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D120" t="n">
-        <v>954.13</v>
+        <v>10235.04</v>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2849,13 +2849,13 @@
         <v>46219</v>
       </c>
       <c r="B121" t="n">
-        <v>571</v>
+        <v>20</v>
       </c>
       <c r="C121" t="n">
         <v>8888</v>
       </c>
       <c r="D121" t="n">
-        <v>25609.34</v>
+        <v>4660.07</v>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
@@ -2869,18 +2869,18 @@
         <v>46219</v>
       </c>
       <c r="B122" t="n">
-        <v>1277</v>
+        <v>131</v>
       </c>
       <c r="C122" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D122" t="n">
-        <v>2666.71</v>
+        <v>671.6799999999999</v>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2889,18 +2889,18 @@
         <v>46219</v>
       </c>
       <c r="B123" t="n">
-        <v>131</v>
+        <v>609</v>
       </c>
       <c r="C123" t="n">
-        <v>8888</v>
+        <v>3179</v>
       </c>
       <c r="D123" t="n">
-        <v>934.3200000000001</v>
+        <v>891.63</v>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -2909,18 +2909,18 @@
         <v>46219</v>
       </c>
       <c r="B124" t="n">
-        <v>2660</v>
+        <v>2250</v>
       </c>
       <c r="C124" t="n">
         <v>8888</v>
       </c>
       <c r="D124" t="n">
-        <v>3419.84</v>
+        <v>3311.6</v>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2929,13 +2929,13 @@
         <v>46219</v>
       </c>
       <c r="B125" t="n">
-        <v>400</v>
+        <v>1324</v>
       </c>
       <c r="C125" t="n">
         <v>8888</v>
       </c>
       <c r="D125" t="n">
-        <v>346.8</v>
+        <v>8134.2</v>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
@@ -2949,13 +2949,13 @@
         <v>46219</v>
       </c>
       <c r="B126" t="n">
-        <v>2362</v>
+        <v>2211</v>
       </c>
       <c r="C126" t="n">
         <v>8888</v>
       </c>
       <c r="D126" t="n">
-        <v>1457.7</v>
+        <v>2125.44</v>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
@@ -2969,13 +2969,13 @@
         <v>46219</v>
       </c>
       <c r="B127" t="n">
-        <v>816</v>
+        <v>483</v>
       </c>
       <c r="C127" t="n">
         <v>8888</v>
       </c>
       <c r="D127" t="n">
-        <v>311.95</v>
+        <v>4217.99</v>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
@@ -2989,18 +2989,18 @@
         <v>46219</v>
       </c>
       <c r="B128" t="n">
-        <v>20</v>
+        <v>477</v>
       </c>
       <c r="C128" t="n">
         <v>8888</v>
       </c>
       <c r="D128" t="n">
-        <v>2247.2</v>
+        <v>4414.87</v>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3009,18 +3009,18 @@
         <v>46219</v>
       </c>
       <c r="B129" t="n">
-        <v>890</v>
+        <v>1937</v>
       </c>
       <c r="C129" t="n">
         <v>8888</v>
       </c>
       <c r="D129" t="n">
-        <v>310.39</v>
+        <v>2231.47</v>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3029,13 +3029,13 @@
         <v>46219</v>
       </c>
       <c r="B130" t="n">
-        <v>1293</v>
+        <v>40</v>
       </c>
       <c r="C130" t="n">
         <v>8888</v>
       </c>
       <c r="D130" t="n">
-        <v>3237.41</v>
+        <v>613.16</v>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
@@ -3049,13 +3049,13 @@
         <v>46219</v>
       </c>
       <c r="B131" t="n">
-        <v>2452</v>
+        <v>1064</v>
       </c>
       <c r="C131" t="n">
         <v>8888</v>
       </c>
       <c r="D131" t="n">
-        <v>1632.81</v>
+        <v>720.52</v>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
@@ -3069,13 +3069,13 @@
         <v>46219</v>
       </c>
       <c r="B132" t="n">
-        <v>483</v>
+        <v>1873</v>
       </c>
       <c r="C132" t="n">
         <v>8888</v>
       </c>
       <c r="D132" t="n">
-        <v>2953.24</v>
+        <v>138.39</v>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
@@ -3089,18 +3089,18 @@
         <v>46219</v>
       </c>
       <c r="B133" t="n">
-        <v>131</v>
+        <v>2250</v>
       </c>
       <c r="C133" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D133" t="n">
-        <v>1384.39</v>
+        <v>1646.82</v>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3109,18 +3109,18 @@
         <v>46219</v>
       </c>
       <c r="B134" t="n">
-        <v>2652</v>
+        <v>40</v>
       </c>
       <c r="C134" t="n">
         <v>8888</v>
       </c>
       <c r="D134" t="n">
-        <v>3419.64</v>
+        <v>956.01</v>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3129,18 +3129,18 @@
         <v>46219</v>
       </c>
       <c r="B135" t="n">
-        <v>1117</v>
+        <v>629</v>
       </c>
       <c r="C135" t="n">
-        <v>1139</v>
+        <v>8888</v>
       </c>
       <c r="D135" t="n">
-        <v>238.55</v>
+        <v>18471.2</v>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3149,13 +3149,13 @@
         <v>46219</v>
       </c>
       <c r="B136" t="n">
-        <v>2107</v>
+        <v>703</v>
       </c>
       <c r="C136" t="n">
         <v>8888</v>
       </c>
       <c r="D136" t="n">
-        <v>1958.34</v>
+        <v>2946.27</v>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
@@ -3169,13 +3169,13 @@
         <v>46219</v>
       </c>
       <c r="B137" t="n">
-        <v>131</v>
+        <v>629</v>
       </c>
       <c r="C137" t="n">
         <v>8888</v>
       </c>
       <c r="D137" t="n">
-        <v>767.04</v>
+        <v>1002.21</v>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
@@ -3189,18 +3189,18 @@
         <v>46219</v>
       </c>
       <c r="B138" t="n">
-        <v>1756</v>
+        <v>20</v>
       </c>
       <c r="C138" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D138" t="n">
-        <v>1939.32</v>
+        <v>7233.04</v>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3209,18 +3209,18 @@
         <v>46219</v>
       </c>
       <c r="B139" t="n">
-        <v>1372</v>
+        <v>1876</v>
       </c>
       <c r="C139" t="n">
         <v>8888</v>
       </c>
       <c r="D139" t="n">
-        <v>879.6</v>
+        <v>660.5599999999999</v>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3229,18 +3229,18 @@
         <v>46219</v>
       </c>
       <c r="B140" t="n">
-        <v>360</v>
+        <v>1075</v>
       </c>
       <c r="C140" t="n">
         <v>8888</v>
       </c>
       <c r="D140" t="n">
-        <v>1906.67</v>
+        <v>325.49</v>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3249,13 +3249,13 @@
         <v>46219</v>
       </c>
       <c r="B141" t="n">
-        <v>131</v>
+        <v>451</v>
       </c>
       <c r="C141" t="n">
         <v>8888</v>
       </c>
       <c r="D141" t="n">
-        <v>2281.48</v>
+        <v>1264.4</v>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
@@ -3269,18 +3269,18 @@
         <v>46219</v>
       </c>
       <c r="B142" t="n">
-        <v>1372</v>
+        <v>619</v>
       </c>
       <c r="C142" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D142" t="n">
-        <v>839.58</v>
+        <v>1169.16</v>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3289,18 +3289,18 @@
         <v>46219</v>
       </c>
       <c r="B143" t="n">
-        <v>1996</v>
+        <v>89</v>
       </c>
       <c r="C143" t="n">
-        <v>691</v>
+        <v>8888</v>
       </c>
       <c r="D143" t="n">
-        <v>2078.56</v>
+        <v>1211.73</v>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3309,18 +3309,18 @@
         <v>46219</v>
       </c>
       <c r="B144" t="n">
-        <v>1064</v>
+        <v>703</v>
       </c>
       <c r="C144" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D144" t="n">
-        <v>954.13</v>
+        <v>599.88</v>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3329,18 +3329,18 @@
         <v>46219</v>
       </c>
       <c r="B145" t="n">
-        <v>559</v>
+        <v>477</v>
       </c>
       <c r="C145" t="n">
         <v>8888</v>
       </c>
       <c r="D145" t="n">
-        <v>1245.19</v>
+        <v>2239.02</v>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -3349,18 +3349,18 @@
         <v>46219</v>
       </c>
       <c r="B146" t="n">
-        <v>580</v>
+        <v>1064</v>
       </c>
       <c r="C146" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D146" t="n">
-        <v>3020.55</v>
+        <v>954.13</v>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3369,13 +3369,13 @@
         <v>46219</v>
       </c>
       <c r="B147" t="n">
-        <v>1064</v>
+        <v>571</v>
       </c>
       <c r="C147" t="n">
         <v>8888</v>
       </c>
       <c r="D147" t="n">
-        <v>1001.61</v>
+        <v>25609.34</v>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
@@ -3389,18 +3389,18 @@
         <v>46219</v>
       </c>
       <c r="B148" t="n">
-        <v>325</v>
+        <v>1277</v>
       </c>
       <c r="C148" t="n">
         <v>8888</v>
       </c>
       <c r="D148" t="n">
-        <v>100.62</v>
+        <v>2666.71</v>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3409,13 +3409,13 @@
         <v>46219</v>
       </c>
       <c r="B149" t="n">
-        <v>1293</v>
+        <v>131</v>
       </c>
       <c r="C149" t="n">
         <v>8888</v>
       </c>
       <c r="D149" t="n">
-        <v>1354.46</v>
+        <v>934.3200000000001</v>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
@@ -3429,13 +3429,13 @@
         <v>46219</v>
       </c>
       <c r="B150" t="n">
-        <v>629</v>
+        <v>2660</v>
       </c>
       <c r="C150" t="n">
         <v>8888</v>
       </c>
       <c r="D150" t="n">
-        <v>1804.42</v>
+        <v>3419.84</v>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
@@ -3449,13 +3449,13 @@
         <v>46219</v>
       </c>
       <c r="B151" t="n">
-        <v>2245</v>
+        <v>2729</v>
       </c>
       <c r="C151" t="n">
         <v>8888</v>
       </c>
       <c r="D151" t="n">
-        <v>983.59</v>
+        <v>625.89</v>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
@@ -3469,13 +3469,13 @@
         <v>46219</v>
       </c>
       <c r="B152" t="n">
-        <v>131</v>
+        <v>400</v>
       </c>
       <c r="C152" t="n">
         <v>8888</v>
       </c>
       <c r="D152" t="n">
-        <v>989.47</v>
+        <v>346.8</v>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
@@ -3489,13 +3489,13 @@
         <v>46219</v>
       </c>
       <c r="B153" t="n">
-        <v>131</v>
+        <v>2362</v>
       </c>
       <c r="C153" t="n">
         <v>8888</v>
       </c>
       <c r="D153" t="n">
-        <v>934.3200000000001</v>
+        <v>1457.7</v>
       </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
@@ -3509,13 +3509,13 @@
         <v>46219</v>
       </c>
       <c r="B154" t="n">
-        <v>2362</v>
+        <v>816</v>
       </c>
       <c r="C154" t="n">
         <v>8888</v>
       </c>
       <c r="D154" t="n">
-        <v>327.61</v>
+        <v>311.95</v>
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
@@ -3529,18 +3529,18 @@
         <v>46219</v>
       </c>
       <c r="B155" t="n">
-        <v>325</v>
+        <v>20</v>
       </c>
       <c r="C155" t="n">
         <v>8888</v>
       </c>
       <c r="D155" t="n">
-        <v>25.9</v>
+        <v>2247.2</v>
       </c>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3549,13 +3549,13 @@
         <v>46219</v>
       </c>
       <c r="B156" t="n">
-        <v>1756</v>
+        <v>890</v>
       </c>
       <c r="C156" t="n">
         <v>8888</v>
       </c>
       <c r="D156" t="n">
-        <v>5236.57</v>
+        <v>310.39</v>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
@@ -3569,13 +3569,13 @@
         <v>46219</v>
       </c>
       <c r="B157" t="n">
-        <v>20</v>
+        <v>1293</v>
       </c>
       <c r="C157" t="n">
         <v>8888</v>
       </c>
       <c r="D157" t="n">
-        <v>5859.38</v>
+        <v>3237.41</v>
       </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
@@ -3589,13 +3589,13 @@
         <v>46219</v>
       </c>
       <c r="B158" t="n">
-        <v>629</v>
+        <v>2452</v>
       </c>
       <c r="C158" t="n">
         <v>8888</v>
       </c>
       <c r="D158" t="n">
-        <v>1292.86</v>
+        <v>1632.81</v>
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
@@ -3609,13 +3609,13 @@
         <v>46219</v>
       </c>
       <c r="B159" t="n">
-        <v>2383</v>
+        <v>2657</v>
       </c>
       <c r="C159" t="n">
         <v>8888</v>
       </c>
       <c r="D159" t="n">
-        <v>5887.04</v>
+        <v>551.8</v>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
@@ -3629,13 +3629,13 @@
         <v>46219</v>
       </c>
       <c r="B160" t="n">
-        <v>131</v>
+        <v>483</v>
       </c>
       <c r="C160" t="n">
         <v>8888</v>
       </c>
       <c r="D160" t="n">
-        <v>2983.2</v>
+        <v>2953.24</v>
       </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
@@ -3649,13 +3649,13 @@
         <v>46219</v>
       </c>
       <c r="B161" t="n">
-        <v>1007</v>
+        <v>816</v>
       </c>
       <c r="C161" t="n">
         <v>8888</v>
       </c>
       <c r="D161" t="n">
-        <v>1664.69</v>
+        <v>6309.13</v>
       </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
@@ -3669,18 +3669,18 @@
         <v>46219</v>
       </c>
       <c r="B162" t="n">
-        <v>890</v>
+        <v>131</v>
       </c>
       <c r="C162" t="n">
-        <v>1533</v>
+        <v>8888</v>
       </c>
       <c r="D162" t="n">
-        <v>670.6799999999999</v>
+        <v>1384.39</v>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3689,18 +3689,18 @@
         <v>46219</v>
       </c>
       <c r="B163" t="n">
-        <v>325</v>
+        <v>2652</v>
       </c>
       <c r="C163" t="n">
         <v>8888</v>
       </c>
       <c r="D163" t="n">
-        <v>44.59</v>
+        <v>3419.64</v>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -3709,18 +3709,18 @@
         <v>46219</v>
       </c>
       <c r="B164" t="n">
-        <v>2362</v>
+        <v>1117</v>
       </c>
       <c r="C164" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D164" t="n">
-        <v>383.76</v>
+        <v>238.55</v>
       </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3729,13 +3729,13 @@
         <v>46219</v>
       </c>
       <c r="B165" t="n">
-        <v>1465</v>
+        <v>2107</v>
       </c>
       <c r="C165" t="n">
         <v>8888</v>
       </c>
       <c r="D165" t="n">
-        <v>2350.22</v>
+        <v>1958.34</v>
       </c>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
@@ -3749,18 +3749,18 @@
         <v>46219</v>
       </c>
       <c r="B166" t="n">
-        <v>483</v>
+        <v>2769</v>
       </c>
       <c r="C166" t="n">
-        <v>8888</v>
+        <v>977</v>
       </c>
       <c r="D166" t="n">
-        <v>689.02</v>
+        <v>5186.62</v>
       </c>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3769,13 +3769,13 @@
         <v>46219</v>
       </c>
       <c r="B167" t="n">
-        <v>2452</v>
+        <v>131</v>
       </c>
       <c r="C167" t="n">
         <v>8888</v>
       </c>
       <c r="D167" t="n">
-        <v>4530.7</v>
+        <v>767.04</v>
       </c>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
@@ -3789,13 +3789,13 @@
         <v>46219</v>
       </c>
       <c r="B168" t="n">
-        <v>400</v>
+        <v>1324</v>
       </c>
       <c r="C168" t="n">
         <v>8888</v>
       </c>
       <c r="D168" t="n">
-        <v>1292.32</v>
+        <v>18508.02</v>
       </c>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
@@ -3809,18 +3809,18 @@
         <v>46219</v>
       </c>
       <c r="B169" t="n">
-        <v>2362</v>
+        <v>1756</v>
       </c>
       <c r="C169" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D169" t="n">
-        <v>744.4</v>
+        <v>1939.32</v>
       </c>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3829,13 +3829,13 @@
         <v>46219</v>
       </c>
       <c r="B170" t="n">
-        <v>1478</v>
+        <v>1372</v>
       </c>
       <c r="C170" t="n">
         <v>8888</v>
       </c>
       <c r="D170" t="n">
-        <v>1123.2</v>
+        <v>879.6</v>
       </c>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
@@ -3849,13 +3849,13 @@
         <v>46219</v>
       </c>
       <c r="B171" t="n">
-        <v>1756</v>
+        <v>1344</v>
       </c>
       <c r="C171" t="n">
         <v>8888</v>
       </c>
       <c r="D171" t="n">
-        <v>462.4</v>
+        <v>21471.41</v>
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
@@ -3869,18 +3869,18 @@
         <v>46219</v>
       </c>
       <c r="B172" t="n">
-        <v>571</v>
+        <v>325</v>
       </c>
       <c r="C172" t="n">
         <v>8888</v>
       </c>
       <c r="D172" t="n">
-        <v>1125.6</v>
+        <v>62.69</v>
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -3889,13 +3889,13 @@
         <v>46219</v>
       </c>
       <c r="B173" t="n">
-        <v>571</v>
+        <v>360</v>
       </c>
       <c r="C173" t="n">
         <v>8888</v>
       </c>
       <c r="D173" t="n">
-        <v>5997.18</v>
+        <v>1906.67</v>
       </c>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
@@ -3909,13 +3909,13 @@
         <v>46219</v>
       </c>
       <c r="B174" t="n">
-        <v>2421</v>
+        <v>131</v>
       </c>
       <c r="C174" t="n">
         <v>8888</v>
       </c>
       <c r="D174" t="n">
-        <v>2786.14</v>
+        <v>2281.48</v>
       </c>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
@@ -3929,13 +3929,13 @@
         <v>46219</v>
       </c>
       <c r="B175" t="n">
-        <v>953</v>
+        <v>1372</v>
       </c>
       <c r="C175" t="n">
         <v>8888</v>
       </c>
       <c r="D175" t="n">
-        <v>6995.34</v>
+        <v>839.58</v>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
@@ -3949,18 +3949,18 @@
         <v>46219</v>
       </c>
       <c r="B176" t="n">
-        <v>2769</v>
+        <v>1996</v>
       </c>
       <c r="C176" t="n">
-        <v>8888</v>
+        <v>691</v>
       </c>
       <c r="D176" t="n">
-        <v>620.37</v>
+        <v>2078.56</v>
       </c>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -3969,13 +3969,13 @@
         <v>46219</v>
       </c>
       <c r="B177" t="n">
-        <v>2362</v>
+        <v>2124</v>
       </c>
       <c r="C177" t="n">
         <v>8888</v>
       </c>
       <c r="D177" t="n">
-        <v>8080.76</v>
+        <v>2751.74</v>
       </c>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
@@ -3989,18 +3989,18 @@
         <v>46219</v>
       </c>
       <c r="B178" t="n">
-        <v>629</v>
+        <v>1064</v>
       </c>
       <c r="C178" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D178" t="n">
-        <v>10075.2</v>
+        <v>954.13</v>
       </c>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4009,18 +4009,18 @@
         <v>46219</v>
       </c>
       <c r="B179" t="n">
-        <v>360</v>
+        <v>2726</v>
       </c>
       <c r="C179" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D179" t="n">
-        <v>4617.15</v>
+        <v>1428.22</v>
       </c>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4029,13 +4029,13 @@
         <v>46219</v>
       </c>
       <c r="B180" t="n">
-        <v>609</v>
+        <v>559</v>
       </c>
       <c r="C180" t="n">
         <v>8888</v>
       </c>
       <c r="D180" t="n">
-        <v>1112.69</v>
+        <v>1245.19</v>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
@@ -4049,18 +4049,18 @@
         <v>46219</v>
       </c>
       <c r="B181" t="n">
-        <v>2250</v>
+        <v>580</v>
       </c>
       <c r="C181" t="n">
         <v>8888</v>
       </c>
       <c r="D181" t="n">
-        <v>2681.88</v>
+        <v>3020.55</v>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4069,13 +4069,13 @@
         <v>46219</v>
       </c>
       <c r="B182" t="n">
-        <v>535</v>
+        <v>1064</v>
       </c>
       <c r="C182" t="n">
         <v>8888</v>
       </c>
       <c r="D182" t="n">
-        <v>616.54</v>
+        <v>1001.61</v>
       </c>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
@@ -4089,18 +4089,18 @@
         <v>46219</v>
       </c>
       <c r="B183" t="n">
-        <v>629</v>
+        <v>325</v>
       </c>
       <c r="C183" t="n">
         <v>8888</v>
       </c>
       <c r="D183" t="n">
-        <v>801.97</v>
+        <v>100.62</v>
       </c>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4109,18 +4109,18 @@
         <v>46219</v>
       </c>
       <c r="B184" t="n">
-        <v>363</v>
+        <v>1293</v>
       </c>
       <c r="C184" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D184" t="n">
-        <v>1618.96</v>
+        <v>1354.46</v>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4129,18 +4129,18 @@
         <v>46219</v>
       </c>
       <c r="B185" t="n">
-        <v>1064</v>
+        <v>629</v>
       </c>
       <c r="C185" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D185" t="n">
-        <v>2667.18</v>
+        <v>1804.42</v>
       </c>
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4149,18 +4149,18 @@
         <v>46219</v>
       </c>
       <c r="B186" t="n">
-        <v>609</v>
+        <v>451</v>
       </c>
       <c r="C186" t="n">
         <v>8888</v>
       </c>
       <c r="D186" t="n">
-        <v>1141.32</v>
+        <v>580.47</v>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4169,18 +4169,18 @@
         <v>46219</v>
       </c>
       <c r="B187" t="n">
-        <v>2250</v>
+        <v>2245</v>
       </c>
       <c r="C187" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D187" t="n">
-        <v>551.76</v>
+        <v>983.59</v>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4189,18 +4189,18 @@
         <v>46219</v>
       </c>
       <c r="B188" t="n">
-        <v>953</v>
+        <v>1518</v>
       </c>
       <c r="C188" t="n">
-        <v>8888</v>
+        <v>1533</v>
       </c>
       <c r="D188" t="n">
-        <v>4366.21</v>
+        <v>1522.88</v>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4209,13 +4209,13 @@
         <v>46219</v>
       </c>
       <c r="B189" t="n">
-        <v>629</v>
+        <v>131</v>
       </c>
       <c r="C189" t="n">
         <v>8888</v>
       </c>
       <c r="D189" t="n">
-        <v>1844.39</v>
+        <v>989.47</v>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
@@ -4229,18 +4229,18 @@
         <v>46219</v>
       </c>
       <c r="B190" t="n">
-        <v>1465</v>
+        <v>131</v>
       </c>
       <c r="C190" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D190" t="n">
-        <v>1220.4</v>
+        <v>839.6</v>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4249,13 +4249,13 @@
         <v>46219</v>
       </c>
       <c r="B191" t="n">
-        <v>1869</v>
+        <v>131</v>
       </c>
       <c r="C191" t="n">
         <v>8888</v>
       </c>
       <c r="D191" t="n">
-        <v>1103.52</v>
+        <v>934.3200000000001</v>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
@@ -4275,7 +4275,7 @@
         <v>8888</v>
       </c>
       <c r="D192" t="n">
-        <v>3256.49</v>
+        <v>327.61</v>
       </c>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
@@ -4289,13 +4289,13 @@
         <v>46219</v>
       </c>
       <c r="B193" t="n">
-        <v>2362</v>
+        <v>781</v>
       </c>
       <c r="C193" t="n">
         <v>8888</v>
       </c>
       <c r="D193" t="n">
-        <v>702.5700000000001</v>
+        <v>2632.08</v>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
@@ -4309,18 +4309,18 @@
         <v>46219</v>
       </c>
       <c r="B194" t="n">
-        <v>2652</v>
+        <v>325</v>
       </c>
       <c r="C194" t="n">
         <v>8888</v>
       </c>
       <c r="D194" t="n">
-        <v>260.03</v>
+        <v>25.9</v>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4329,13 +4329,13 @@
         <v>46219</v>
       </c>
       <c r="B195" t="n">
-        <v>1465</v>
+        <v>1756</v>
       </c>
       <c r="C195" t="n">
         <v>8888</v>
       </c>
       <c r="D195" t="n">
-        <v>3283.11</v>
+        <v>5236.57</v>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
@@ -4349,13 +4349,13 @@
         <v>46219</v>
       </c>
       <c r="B196" t="n">
-        <v>131</v>
+        <v>20</v>
       </c>
       <c r="C196" t="n">
         <v>8888</v>
       </c>
       <c r="D196" t="n">
-        <v>233.82</v>
+        <v>5859.38</v>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
@@ -4369,13 +4369,13 @@
         <v>46219</v>
       </c>
       <c r="B197" t="n">
-        <v>890</v>
+        <v>629</v>
       </c>
       <c r="C197" t="n">
         <v>8888</v>
       </c>
       <c r="D197" t="n">
-        <v>950.1799999999999</v>
+        <v>1292.86</v>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
@@ -4389,18 +4389,18 @@
         <v>46219</v>
       </c>
       <c r="B198" t="n">
-        <v>2250</v>
+        <v>2686</v>
       </c>
       <c r="C198" t="n">
-        <v>8888</v>
+        <v>1929</v>
       </c>
       <c r="D198" t="n">
-        <v>1596</v>
+        <v>1295.86</v>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4409,18 +4409,18 @@
         <v>46219</v>
       </c>
       <c r="B199" t="n">
-        <v>2250</v>
+        <v>2383</v>
       </c>
       <c r="C199" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D199" t="n">
-        <v>2207.04</v>
+        <v>5887.04</v>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4429,13 +4429,13 @@
         <v>46219</v>
       </c>
       <c r="B200" t="n">
-        <v>559</v>
+        <v>131</v>
       </c>
       <c r="C200" t="n">
         <v>8888</v>
       </c>
       <c r="D200" t="n">
-        <v>3594</v>
+        <v>2983.2</v>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
@@ -4449,13 +4449,13 @@
         <v>46219</v>
       </c>
       <c r="B201" t="n">
-        <v>629</v>
+        <v>1007</v>
       </c>
       <c r="C201" t="n">
         <v>8888</v>
       </c>
       <c r="D201" t="n">
-        <v>801.97</v>
+        <v>1664.69</v>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
@@ -4469,18 +4469,18 @@
         <v>46219</v>
       </c>
       <c r="B202" t="n">
-        <v>58</v>
+        <v>890</v>
       </c>
       <c r="C202" t="n">
-        <v>8888</v>
+        <v>1533</v>
       </c>
       <c r="D202" t="n">
-        <v>697.33</v>
+        <v>670.6799999999999</v>
       </c>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4489,18 +4489,18 @@
         <v>46219</v>
       </c>
       <c r="B203" t="n">
-        <v>1108</v>
+        <v>131</v>
       </c>
       <c r="C203" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D203" t="n">
-        <v>341.38</v>
+        <v>2350.88</v>
       </c>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4509,18 +4509,18 @@
         <v>46219</v>
       </c>
       <c r="B204" t="n">
-        <v>2363</v>
+        <v>325</v>
       </c>
       <c r="C204" t="n">
         <v>8888</v>
       </c>
       <c r="D204" t="n">
-        <v>1884.86</v>
+        <v>44.59</v>
       </c>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4529,18 +4529,18 @@
         <v>46219</v>
       </c>
       <c r="B205" t="n">
-        <v>1007</v>
+        <v>1465</v>
       </c>
       <c r="C205" t="n">
         <v>8888</v>
       </c>
       <c r="D205" t="n">
-        <v>1054.68</v>
+        <v>370.41</v>
       </c>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4549,13 +4549,13 @@
         <v>46219</v>
       </c>
       <c r="B206" t="n">
-        <v>1869</v>
+        <v>2362</v>
       </c>
       <c r="C206" t="n">
         <v>8888</v>
       </c>
       <c r="D206" t="n">
-        <v>1698.3</v>
+        <v>383.76</v>
       </c>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
@@ -4569,18 +4569,18 @@
         <v>46219</v>
       </c>
       <c r="B207" t="n">
-        <v>1996</v>
+        <v>1064</v>
       </c>
       <c r="C207" t="n">
-        <v>691</v>
+        <v>8888</v>
       </c>
       <c r="D207" t="n">
-        <v>2302.2</v>
+        <v>3753.45</v>
       </c>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4589,18 +4589,18 @@
         <v>46219</v>
       </c>
       <c r="B208" t="n">
-        <v>2709</v>
+        <v>1465</v>
       </c>
       <c r="C208" t="n">
-        <v>2220</v>
+        <v>8888</v>
       </c>
       <c r="D208" t="n">
-        <v>586.1900000000001</v>
+        <v>2350.22</v>
       </c>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4609,13 +4609,13 @@
         <v>46219</v>
       </c>
       <c r="B209" t="n">
-        <v>1064</v>
+        <v>20</v>
       </c>
       <c r="C209" t="n">
         <v>8888</v>
       </c>
       <c r="D209" t="n">
-        <v>372.95</v>
+        <v>1679.4</v>
       </c>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
@@ -4629,18 +4629,18 @@
         <v>46219</v>
       </c>
       <c r="B210" t="n">
-        <v>40</v>
+        <v>2709</v>
       </c>
       <c r="C210" t="n">
-        <v>8888</v>
+        <v>2220</v>
       </c>
       <c r="D210" t="n">
-        <v>306.58</v>
+        <v>2155.8</v>
       </c>
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4649,18 +4649,18 @@
         <v>46219</v>
       </c>
       <c r="B211" t="n">
-        <v>1996</v>
+        <v>483</v>
       </c>
       <c r="C211" t="n">
         <v>8888</v>
       </c>
       <c r="D211" t="n">
-        <v>514.91</v>
+        <v>689.02</v>
       </c>
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4669,18 +4669,18 @@
         <v>46219</v>
       </c>
       <c r="B212" t="n">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="C212" t="n">
         <v>8888</v>
       </c>
       <c r="D212" t="n">
-        <v>680.4</v>
+        <v>2882.97</v>
       </c>
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4689,13 +4689,13 @@
         <v>46219</v>
       </c>
       <c r="B213" t="n">
-        <v>2190</v>
+        <v>2452</v>
       </c>
       <c r="C213" t="n">
         <v>8888</v>
       </c>
       <c r="D213" t="n">
-        <v>1035.41</v>
+        <v>4530.7</v>
       </c>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
@@ -4709,13 +4709,13 @@
         <v>46219</v>
       </c>
       <c r="B214" t="n">
-        <v>781</v>
+        <v>400</v>
       </c>
       <c r="C214" t="n">
         <v>8888</v>
       </c>
       <c r="D214" t="n">
-        <v>1169.2</v>
+        <v>1292.32</v>
       </c>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
@@ -4729,13 +4729,13 @@
         <v>46219</v>
       </c>
       <c r="B215" t="n">
-        <v>351</v>
+        <v>2362</v>
       </c>
       <c r="C215" t="n">
         <v>8888</v>
       </c>
       <c r="D215" t="n">
-        <v>2207.04</v>
+        <v>744.4</v>
       </c>
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
@@ -4749,13 +4749,13 @@
         <v>46219</v>
       </c>
       <c r="B216" t="n">
-        <v>1064</v>
+        <v>1478</v>
       </c>
       <c r="C216" t="n">
         <v>8888</v>
       </c>
       <c r="D216" t="n">
-        <v>2348.64</v>
+        <v>1123.2</v>
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
@@ -4769,13 +4769,13 @@
         <v>46219</v>
       </c>
       <c r="B217" t="n">
-        <v>571</v>
+        <v>1756</v>
       </c>
       <c r="C217" t="n">
         <v>8888</v>
       </c>
       <c r="D217" t="n">
-        <v>17843.18</v>
+        <v>462.4</v>
       </c>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
@@ -4789,13 +4789,13 @@
         <v>46219</v>
       </c>
       <c r="B218" t="n">
-        <v>629</v>
+        <v>571</v>
       </c>
       <c r="C218" t="n">
         <v>8888</v>
       </c>
       <c r="D218" t="n">
-        <v>1292.86</v>
+        <v>1125.6</v>
       </c>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
@@ -4809,13 +4809,13 @@
         <v>46219</v>
       </c>
       <c r="B219" t="n">
-        <v>535</v>
+        <v>571</v>
       </c>
       <c r="C219" t="n">
         <v>8888</v>
       </c>
       <c r="D219" t="n">
-        <v>1395.11</v>
+        <v>5997.18</v>
       </c>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
@@ -4829,13 +4829,13 @@
         <v>46219</v>
       </c>
       <c r="B220" t="n">
-        <v>609</v>
+        <v>2362</v>
       </c>
       <c r="C220" t="n">
         <v>8888</v>
       </c>
       <c r="D220" t="n">
-        <v>1487.52</v>
+        <v>1000.8</v>
       </c>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
@@ -4849,13 +4849,13 @@
         <v>46219</v>
       </c>
       <c r="B221" t="n">
-        <v>609</v>
+        <v>2421</v>
       </c>
       <c r="C221" t="n">
         <v>8888</v>
       </c>
       <c r="D221" t="n">
-        <v>1854.48</v>
+        <v>2786.14</v>
       </c>
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
@@ -4869,13 +4869,13 @@
         <v>46219</v>
       </c>
       <c r="B222" t="n">
-        <v>2660</v>
+        <v>953</v>
       </c>
       <c r="C222" t="n">
         <v>8888</v>
       </c>
       <c r="D222" t="n">
-        <v>1481.24</v>
+        <v>6995.34</v>
       </c>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
@@ -4889,18 +4889,18 @@
         <v>46219</v>
       </c>
       <c r="B223" t="n">
-        <v>1293</v>
+        <v>2769</v>
       </c>
       <c r="C223" t="n">
         <v>8888</v>
       </c>
       <c r="D223" t="n">
-        <v>1354.46</v>
+        <v>620.37</v>
       </c>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -4909,18 +4909,18 @@
         <v>46219</v>
       </c>
       <c r="B224" t="n">
-        <v>2768</v>
+        <v>1324</v>
       </c>
       <c r="C224" t="n">
-        <v>8888</v>
+        <v>3009</v>
       </c>
       <c r="D224" t="n">
-        <v>2979.54</v>
+        <v>3337.22</v>
       </c>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -4929,18 +4929,18 @@
         <v>46219</v>
       </c>
       <c r="B225" t="n">
-        <v>1327</v>
+        <v>2547</v>
       </c>
       <c r="C225" t="n">
         <v>8888</v>
       </c>
       <c r="D225" t="n">
-        <v>4134.3</v>
+        <v>265.54</v>
       </c>
       <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -4949,18 +4949,18 @@
         <v>46219</v>
       </c>
       <c r="B226" t="n">
-        <v>2628</v>
+        <v>2362</v>
       </c>
       <c r="C226" t="n">
         <v>8888</v>
       </c>
       <c r="D226" t="n">
-        <v>271.2</v>
+        <v>8080.76</v>
       </c>
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -4969,13 +4969,13 @@
         <v>46219</v>
       </c>
       <c r="B227" t="n">
-        <v>2452</v>
+        <v>629</v>
       </c>
       <c r="C227" t="n">
         <v>8888</v>
       </c>
       <c r="D227" t="n">
-        <v>1208.26</v>
+        <v>10075.2</v>
       </c>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
@@ -4989,13 +4989,13 @@
         <v>46219</v>
       </c>
       <c r="B228" t="n">
-        <v>131</v>
+        <v>360</v>
       </c>
       <c r="C228" t="n">
         <v>8888</v>
       </c>
       <c r="D228" t="n">
-        <v>848.54</v>
+        <v>4617.15</v>
       </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
@@ -5009,13 +5009,13 @@
         <v>46219</v>
       </c>
       <c r="B229" t="n">
-        <v>816</v>
+        <v>2696</v>
       </c>
       <c r="C229" t="n">
         <v>8888</v>
       </c>
       <c r="D229" t="n">
-        <v>4017.6</v>
+        <v>3799.37</v>
       </c>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
@@ -5029,13 +5029,13 @@
         <v>46219</v>
       </c>
       <c r="B230" t="n">
-        <v>1064</v>
+        <v>609</v>
       </c>
       <c r="C230" t="n">
         <v>8888</v>
       </c>
       <c r="D230" t="n">
-        <v>4291.42</v>
+        <v>1112.69</v>
       </c>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
@@ -5049,18 +5049,18 @@
         <v>46219</v>
       </c>
       <c r="B231" t="n">
-        <v>703</v>
+        <v>2250</v>
       </c>
       <c r="C231" t="n">
         <v>8888</v>
       </c>
       <c r="D231" t="n">
-        <v>3936.87</v>
+        <v>2681.88</v>
       </c>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -5069,13 +5069,13 @@
         <v>46219</v>
       </c>
       <c r="B232" t="n">
-        <v>1340</v>
+        <v>535</v>
       </c>
       <c r="C232" t="n">
         <v>8888</v>
       </c>
       <c r="D232" t="n">
-        <v>2774.78</v>
+        <v>616.54</v>
       </c>
       <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
@@ -5089,13 +5089,13 @@
         <v>46219</v>
       </c>
       <c r="B233" t="n">
-        <v>2107</v>
+        <v>629</v>
       </c>
       <c r="C233" t="n">
         <v>8888</v>
       </c>
       <c r="D233" t="n">
-        <v>476.47</v>
+        <v>801.97</v>
       </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
@@ -5109,18 +5109,18 @@
         <v>46219</v>
       </c>
       <c r="B234" t="n">
-        <v>400</v>
+        <v>363</v>
       </c>
       <c r="C234" t="n">
-        <v>8888</v>
+        <v>1898</v>
       </c>
       <c r="D234" t="n">
-        <v>2686.56</v>
+        <v>1618.96</v>
       </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -5129,18 +5129,18 @@
         <v>46219</v>
       </c>
       <c r="B235" t="n">
-        <v>559</v>
+        <v>1064</v>
       </c>
       <c r="C235" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D235" t="n">
-        <v>9867.299999999999</v>
+        <v>2667.18</v>
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -5149,13 +5149,13 @@
         <v>46219</v>
       </c>
       <c r="B236" t="n">
-        <v>451</v>
+        <v>609</v>
       </c>
       <c r="C236" t="n">
         <v>8888</v>
       </c>
       <c r="D236" t="n">
-        <v>2131.88</v>
+        <v>1141.32</v>
       </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
@@ -5169,18 +5169,18 @@
         <v>46219</v>
       </c>
       <c r="B237" t="n">
-        <v>951</v>
+        <v>2250</v>
       </c>
       <c r="C237" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D237" t="n">
-        <v>6068.2</v>
+        <v>551.76</v>
       </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -5189,18 +5189,18 @@
         <v>46219</v>
       </c>
       <c r="B238" t="n">
-        <v>571</v>
+        <v>1116</v>
       </c>
       <c r="C238" t="n">
         <v>8888</v>
       </c>
       <c r="D238" t="n">
-        <v>4547.53</v>
+        <v>3426.37</v>
       </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -5209,13 +5209,13 @@
         <v>46219</v>
       </c>
       <c r="B239" t="n">
-        <v>619</v>
+        <v>953</v>
       </c>
       <c r="C239" t="n">
         <v>8888</v>
       </c>
       <c r="D239" t="n">
-        <v>1872.16</v>
+        <v>4366.21</v>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
@@ -5229,18 +5229,18 @@
         <v>46219</v>
       </c>
       <c r="B240" t="n">
-        <v>1450</v>
+        <v>629</v>
       </c>
       <c r="C240" t="n">
         <v>8888</v>
       </c>
       <c r="D240" t="n">
-        <v>692.3200000000001</v>
+        <v>1844.39</v>
       </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5249,18 +5249,18 @@
         <v>46219</v>
       </c>
       <c r="B241" t="n">
-        <v>2767</v>
+        <v>1465</v>
       </c>
       <c r="C241" t="n">
-        <v>1898</v>
+        <v>8888</v>
       </c>
       <c r="D241" t="n">
-        <v>1706.73</v>
+        <v>1220.4</v>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5269,18 +5269,18 @@
         <v>46219</v>
       </c>
       <c r="B242" t="n">
-        <v>2810</v>
+        <v>1869</v>
       </c>
       <c r="C242" t="n">
-        <v>3179</v>
+        <v>8888</v>
       </c>
       <c r="D242" t="n">
-        <v>3704.73</v>
+        <v>1103.52</v>
       </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5289,13 +5289,13 @@
         <v>46219</v>
       </c>
       <c r="B243" t="n">
-        <v>2452</v>
+        <v>2362</v>
       </c>
       <c r="C243" t="n">
         <v>8888</v>
       </c>
       <c r="D243" t="n">
-        <v>1093.58</v>
+        <v>3256.49</v>
       </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
@@ -5309,13 +5309,13 @@
         <v>46219</v>
       </c>
       <c r="B244" t="n">
-        <v>703</v>
+        <v>2362</v>
       </c>
       <c r="C244" t="n">
         <v>8888</v>
       </c>
       <c r="D244" t="n">
-        <v>1829.63</v>
+        <v>702.5700000000001</v>
       </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
@@ -5329,18 +5329,18 @@
         <v>46219</v>
       </c>
       <c r="B245" t="n">
-        <v>609</v>
+        <v>1478</v>
       </c>
       <c r="C245" t="n">
         <v>8888</v>
       </c>
       <c r="D245" t="n">
-        <v>1112.69</v>
+        <v>676.12</v>
       </c>
       <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -5349,13 +5349,13 @@
         <v>46219</v>
       </c>
       <c r="B246" t="n">
-        <v>2245</v>
+        <v>2652</v>
       </c>
       <c r="C246" t="n">
         <v>8888</v>
       </c>
       <c r="D246" t="n">
-        <v>459.01</v>
+        <v>260.03</v>
       </c>
       <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
@@ -5369,18 +5369,18 @@
         <v>46219</v>
       </c>
       <c r="B247" t="n">
-        <v>131</v>
+        <v>953</v>
       </c>
       <c r="C247" t="n">
         <v>8888</v>
       </c>
       <c r="D247" t="n">
-        <v>623.52</v>
+        <v>13313.87</v>
       </c>
       <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -5389,18 +5389,18 @@
         <v>46219</v>
       </c>
       <c r="B248" t="n">
-        <v>429</v>
+        <v>559</v>
       </c>
       <c r="C248" t="n">
-        <v>1281</v>
+        <v>8888</v>
       </c>
       <c r="D248" t="n">
-        <v>376.24</v>
+        <v>1580.83</v>
       </c>
       <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -5409,13 +5409,13 @@
         <v>46219</v>
       </c>
       <c r="B249" t="n">
-        <v>131</v>
+        <v>1465</v>
       </c>
       <c r="C249" t="n">
         <v>8888</v>
       </c>
       <c r="D249" t="n">
-        <v>909.3</v>
+        <v>3283.11</v>
       </c>
       <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
@@ -5429,13 +5429,13 @@
         <v>46219</v>
       </c>
       <c r="B250" t="n">
-        <v>1465</v>
+        <v>131</v>
       </c>
       <c r="C250" t="n">
         <v>8888</v>
       </c>
       <c r="D250" t="n">
-        <v>3044.97</v>
+        <v>233.82</v>
       </c>
       <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
@@ -5449,18 +5449,18 @@
         <v>46219</v>
       </c>
       <c r="B251" t="n">
-        <v>1518</v>
+        <v>890</v>
       </c>
       <c r="C251" t="n">
-        <v>1533</v>
+        <v>8888</v>
       </c>
       <c r="D251" t="n">
-        <v>3838.97</v>
+        <v>950.1799999999999</v>
       </c>
       <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -5469,13 +5469,13 @@
         <v>46219</v>
       </c>
       <c r="B252" t="n">
-        <v>1756</v>
+        <v>2178</v>
       </c>
       <c r="C252" t="n">
         <v>8888</v>
       </c>
       <c r="D252" t="n">
-        <v>1283.28</v>
+        <v>1055.97</v>
       </c>
       <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
@@ -5489,13 +5489,13 @@
         <v>46219</v>
       </c>
       <c r="B253" t="n">
-        <v>131</v>
+        <v>2250</v>
       </c>
       <c r="C253" t="n">
         <v>8888</v>
       </c>
       <c r="D253" t="n">
-        <v>1035.73</v>
+        <v>1596</v>
       </c>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
@@ -5509,18 +5509,18 @@
         <v>46219</v>
       </c>
       <c r="B254" t="n">
-        <v>629</v>
+        <v>2250</v>
       </c>
       <c r="C254" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D254" t="n">
-        <v>2645.87</v>
+        <v>2207.04</v>
       </c>
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -5529,13 +5529,13 @@
         <v>46219</v>
       </c>
       <c r="B255" t="n">
-        <v>351</v>
+        <v>559</v>
       </c>
       <c r="C255" t="n">
         <v>8888</v>
       </c>
       <c r="D255" t="n">
-        <v>3018</v>
+        <v>3594</v>
       </c>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
@@ -5549,13 +5549,13 @@
         <v>46219</v>
       </c>
       <c r="B256" t="n">
-        <v>400</v>
+        <v>629</v>
       </c>
       <c r="C256" t="n">
         <v>8888</v>
       </c>
       <c r="D256" t="n">
-        <v>688.64</v>
+        <v>801.97</v>
       </c>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
@@ -5569,16 +5569,1336 @@
         <v>46219</v>
       </c>
       <c r="B257" t="n">
-        <v>1324</v>
+        <v>58</v>
       </c>
       <c r="C257" t="n">
-        <v>3009</v>
+        <v>8888</v>
       </c>
       <c r="D257" t="n">
-        <v>680.4</v>
+        <v>697.33</v>
       </c>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B258" t="n">
+        <v>131</v>
+      </c>
+      <c r="C258" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D258" t="n">
+        <v>203.56</v>
+      </c>
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B259" t="n">
+        <v>1108</v>
+      </c>
+      <c r="C259" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D259" t="n">
+        <v>341.38</v>
+      </c>
+      <c r="E259" t="inlineStr"/>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B260" t="n">
+        <v>1327</v>
+      </c>
+      <c r="C260" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D260" t="n">
+        <v>473.49</v>
+      </c>
+      <c r="E260" t="inlineStr"/>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B261" t="n">
+        <v>953</v>
+      </c>
+      <c r="C261" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D261" t="n">
+        <v>984.59</v>
+      </c>
+      <c r="E261" t="inlineStr"/>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B262" t="n">
+        <v>2363</v>
+      </c>
+      <c r="C262" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D262" t="n">
+        <v>1884.86</v>
+      </c>
+      <c r="E262" t="inlineStr"/>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B263" t="n">
+        <v>1007</v>
+      </c>
+      <c r="C263" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D263" t="n">
+        <v>1054.68</v>
+      </c>
+      <c r="E263" t="inlineStr"/>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B264" t="n">
+        <v>1869</v>
+      </c>
+      <c r="C264" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D264" t="n">
+        <v>1698.3</v>
+      </c>
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B265" t="n">
+        <v>1996</v>
+      </c>
+      <c r="C265" t="n">
+        <v>691</v>
+      </c>
+      <c r="D265" t="n">
+        <v>2302.2</v>
+      </c>
+      <c r="E265" t="inlineStr"/>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B266" t="n">
+        <v>2709</v>
+      </c>
+      <c r="C266" t="n">
+        <v>2220</v>
+      </c>
+      <c r="D266" t="n">
+        <v>586.1900000000001</v>
+      </c>
+      <c r="E266" t="inlineStr"/>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B267" t="n">
+        <v>1064</v>
+      </c>
+      <c r="C267" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D267" t="n">
+        <v>372.95</v>
+      </c>
+      <c r="E267" t="inlineStr"/>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B268" t="n">
+        <v>477</v>
+      </c>
+      <c r="C268" t="n">
+        <v>58</v>
+      </c>
+      <c r="D268" t="n">
+        <v>4680.69</v>
+      </c>
+      <c r="E268" t="inlineStr"/>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B269" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C269" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D269" t="n">
+        <v>1518.02</v>
+      </c>
+      <c r="E269" t="inlineStr"/>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B270" t="n">
+        <v>40</v>
+      </c>
+      <c r="C270" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D270" t="n">
+        <v>306.58</v>
+      </c>
+      <c r="E270" t="inlineStr"/>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B271" t="n">
+        <v>1996</v>
+      </c>
+      <c r="C271" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D271" t="n">
+        <v>514.91</v>
+      </c>
+      <c r="E271" t="inlineStr"/>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B272" t="n">
+        <v>20</v>
+      </c>
+      <c r="C272" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D272" t="n">
+        <v>680.4</v>
+      </c>
+      <c r="E272" t="inlineStr"/>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B273" t="n">
+        <v>2190</v>
+      </c>
+      <c r="C273" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D273" t="n">
+        <v>1035.41</v>
+      </c>
+      <c r="E273" t="inlineStr"/>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B274" t="n">
+        <v>781</v>
+      </c>
+      <c r="C274" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D274" t="n">
+        <v>1169.2</v>
+      </c>
+      <c r="E274" t="inlineStr"/>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B275" t="n">
+        <v>351</v>
+      </c>
+      <c r="C275" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D275" t="n">
+        <v>2207.04</v>
+      </c>
+      <c r="E275" t="inlineStr"/>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B276" t="n">
+        <v>1064</v>
+      </c>
+      <c r="C276" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D276" t="n">
+        <v>2348.64</v>
+      </c>
+      <c r="E276" t="inlineStr"/>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B277" t="n">
+        <v>571</v>
+      </c>
+      <c r="C277" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D277" t="n">
+        <v>17843.18</v>
+      </c>
+      <c r="E277" t="inlineStr"/>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B278" t="n">
+        <v>629</v>
+      </c>
+      <c r="C278" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D278" t="n">
+        <v>1292.86</v>
+      </c>
+      <c r="E278" t="inlineStr"/>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B279" t="n">
+        <v>535</v>
+      </c>
+      <c r="C279" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D279" t="n">
+        <v>1395.11</v>
+      </c>
+      <c r="E279" t="inlineStr"/>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B280" t="n">
+        <v>609</v>
+      </c>
+      <c r="C280" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D280" t="n">
+        <v>1487.52</v>
+      </c>
+      <c r="E280" t="inlineStr"/>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B281" t="n">
+        <v>609</v>
+      </c>
+      <c r="C281" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D281" t="n">
+        <v>1854.48</v>
+      </c>
+      <c r="E281" t="inlineStr"/>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B282" t="n">
+        <v>2660</v>
+      </c>
+      <c r="C282" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D282" t="n">
+        <v>1481.24</v>
+      </c>
+      <c r="E282" t="inlineStr"/>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B283" t="n">
+        <v>1293</v>
+      </c>
+      <c r="C283" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D283" t="n">
+        <v>1354.46</v>
+      </c>
+      <c r="E283" t="inlineStr"/>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B284" t="n">
+        <v>2768</v>
+      </c>
+      <c r="C284" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D284" t="n">
+        <v>2979.54</v>
+      </c>
+      <c r="E284" t="inlineStr"/>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B285" t="n">
+        <v>1327</v>
+      </c>
+      <c r="C285" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D285" t="n">
+        <v>4134.3</v>
+      </c>
+      <c r="E285" t="inlineStr"/>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B286" t="n">
+        <v>2628</v>
+      </c>
+      <c r="C286" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D286" t="n">
+        <v>271.2</v>
+      </c>
+      <c r="E286" t="inlineStr"/>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B287" t="n">
+        <v>2452</v>
+      </c>
+      <c r="C287" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D287" t="n">
+        <v>1208.26</v>
+      </c>
+      <c r="E287" t="inlineStr"/>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B288" t="n">
+        <v>768</v>
+      </c>
+      <c r="C288" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D288" t="n">
+        <v>3199.8</v>
+      </c>
+      <c r="E288" t="inlineStr"/>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B289" t="n">
+        <v>131</v>
+      </c>
+      <c r="C289" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D289" t="n">
+        <v>848.54</v>
+      </c>
+      <c r="E289" t="inlineStr"/>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B290" t="n">
+        <v>816</v>
+      </c>
+      <c r="C290" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D290" t="n">
+        <v>4017.6</v>
+      </c>
+      <c r="E290" t="inlineStr"/>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B291" t="n">
+        <v>1478</v>
+      </c>
+      <c r="C291" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D291" t="n">
+        <v>2159.76</v>
+      </c>
+      <c r="E291" t="inlineStr"/>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B292" t="n">
+        <v>1064</v>
+      </c>
+      <c r="C292" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D292" t="n">
+        <v>4291.42</v>
+      </c>
+      <c r="E292" t="inlineStr"/>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B293" t="n">
+        <v>703</v>
+      </c>
+      <c r="C293" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D293" t="n">
+        <v>3936.87</v>
+      </c>
+      <c r="E293" t="inlineStr"/>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B294" t="n">
+        <v>1340</v>
+      </c>
+      <c r="C294" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D294" t="n">
+        <v>2774.78</v>
+      </c>
+      <c r="E294" t="inlineStr"/>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B295" t="n">
+        <v>2107</v>
+      </c>
+      <c r="C295" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D295" t="n">
+        <v>476.47</v>
+      </c>
+      <c r="E295" t="inlineStr"/>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B296" t="n">
+        <v>400</v>
+      </c>
+      <c r="C296" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D296" t="n">
+        <v>2686.56</v>
+      </c>
+      <c r="E296" t="inlineStr"/>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B297" t="n">
+        <v>1317</v>
+      </c>
+      <c r="C297" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D297" t="n">
+        <v>2074.65</v>
+      </c>
+      <c r="E297" t="inlineStr"/>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B298" t="n">
+        <v>559</v>
+      </c>
+      <c r="C298" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D298" t="n">
+        <v>9867.299999999999</v>
+      </c>
+      <c r="E298" t="inlineStr"/>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B299" t="n">
+        <v>1478</v>
+      </c>
+      <c r="C299" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D299" t="n">
+        <v>5039.4</v>
+      </c>
+      <c r="E299" t="inlineStr"/>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B300" t="n">
+        <v>451</v>
+      </c>
+      <c r="C300" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D300" t="n">
+        <v>2131.88</v>
+      </c>
+      <c r="E300" t="inlineStr"/>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B301" t="n">
+        <v>951</v>
+      </c>
+      <c r="C301" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D301" t="n">
+        <v>6068.2</v>
+      </c>
+      <c r="E301" t="inlineStr"/>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B302" t="n">
+        <v>571</v>
+      </c>
+      <c r="C302" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D302" t="n">
+        <v>4547.53</v>
+      </c>
+      <c r="E302" t="inlineStr"/>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B303" t="n">
+        <v>619</v>
+      </c>
+      <c r="C303" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D303" t="n">
+        <v>1872.16</v>
+      </c>
+      <c r="E303" t="inlineStr"/>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B304" t="n">
+        <v>1450</v>
+      </c>
+      <c r="C304" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D304" t="n">
+        <v>692.3200000000001</v>
+      </c>
+      <c r="E304" t="inlineStr"/>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>E-COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B305" t="n">
+        <v>2767</v>
+      </c>
+      <c r="C305" t="n">
+        <v>1898</v>
+      </c>
+      <c r="D305" t="n">
+        <v>1706.73</v>
+      </c>
+      <c r="E305" t="inlineStr"/>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B306" t="n">
+        <v>2810</v>
+      </c>
+      <c r="C306" t="n">
+        <v>3179</v>
+      </c>
+      <c r="D306" t="n">
+        <v>3704.73</v>
+      </c>
+      <c r="E306" t="inlineStr"/>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B307" t="n">
+        <v>2452</v>
+      </c>
+      <c r="C307" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D307" t="n">
+        <v>1093.58</v>
+      </c>
+      <c r="E307" t="inlineStr"/>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B308" t="n">
+        <v>703</v>
+      </c>
+      <c r="C308" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D308" t="n">
+        <v>1829.63</v>
+      </c>
+      <c r="E308" t="inlineStr"/>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B309" t="n">
+        <v>609</v>
+      </c>
+      <c r="C309" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D309" t="n">
+        <v>1112.69</v>
+      </c>
+      <c r="E309" t="inlineStr"/>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B310" t="n">
+        <v>2695</v>
+      </c>
+      <c r="C310" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D310" t="n">
+        <v>2435.91</v>
+      </c>
+      <c r="E310" t="inlineStr"/>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B311" t="n">
+        <v>131</v>
+      </c>
+      <c r="C311" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D311" t="n">
+        <v>623.52</v>
+      </c>
+      <c r="E311" t="inlineStr"/>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B312" t="n">
+        <v>429</v>
+      </c>
+      <c r="C312" t="n">
+        <v>1281</v>
+      </c>
+      <c r="D312" t="n">
+        <v>376.24</v>
+      </c>
+      <c r="E312" t="inlineStr"/>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B313" t="n">
+        <v>131</v>
+      </c>
+      <c r="C313" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D313" t="n">
+        <v>909.3</v>
+      </c>
+      <c r="E313" t="inlineStr"/>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B314" t="n">
+        <v>1465</v>
+      </c>
+      <c r="C314" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D314" t="n">
+        <v>3044.97</v>
+      </c>
+      <c r="E314" t="inlineStr"/>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B315" t="n">
+        <v>1518</v>
+      </c>
+      <c r="C315" t="n">
+        <v>1533</v>
+      </c>
+      <c r="D315" t="n">
+        <v>3838.97</v>
+      </c>
+      <c r="E315" t="inlineStr"/>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>TELEMARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B316" t="n">
+        <v>569</v>
+      </c>
+      <c r="C316" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D316" t="n">
+        <v>2176.48</v>
+      </c>
+      <c r="E316" t="inlineStr"/>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B317" t="n">
+        <v>2216</v>
+      </c>
+      <c r="C317" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D317" t="n">
+        <v>827.86</v>
+      </c>
+      <c r="E317" t="inlineStr"/>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>OPERADOR LOGÍSTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B318" t="n">
+        <v>1756</v>
+      </c>
+      <c r="C318" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D318" t="n">
+        <v>1283.28</v>
+      </c>
+      <c r="E318" t="inlineStr"/>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B319" t="n">
+        <v>131</v>
+      </c>
+      <c r="C319" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D319" t="n">
+        <v>1035.73</v>
+      </c>
+      <c r="E319" t="inlineStr"/>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B320" t="n">
+        <v>629</v>
+      </c>
+      <c r="C320" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D320" t="n">
+        <v>2645.87</v>
+      </c>
+      <c r="E320" t="inlineStr"/>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B321" t="n">
+        <v>351</v>
+      </c>
+      <c r="C321" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D321" t="n">
+        <v>3018</v>
+      </c>
+      <c r="E321" t="inlineStr"/>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B322" t="n">
+        <v>400</v>
+      </c>
+      <c r="C322" t="n">
+        <v>8888</v>
+      </c>
+      <c r="D322" t="n">
+        <v>688.64</v>
+      </c>
+      <c r="E322" t="inlineStr"/>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>FORÇA DE VENDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B323" t="n">
+        <v>1324</v>
+      </c>
+      <c r="C323" t="n">
+        <v>3009</v>
+      </c>
+      <c r="D323" t="n">
+        <v>680.4</v>
+      </c>
+      <c r="E323" t="inlineStr"/>
+      <c r="F323" t="inlineStr">
         <is>
           <t>TELEMARKETING</t>
         </is>

--- a/data/fat_total_day.xlsx
+++ b/data/fat_total_day.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F323"/>
+  <dimension ref="A1:F408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -849,13 +849,13 @@
         <v>46219</v>
       </c>
       <c r="B21" t="n">
-        <v>131</v>
+        <v>2613</v>
       </c>
       <c r="C21" t="n">
         <v>8888</v>
       </c>
       <c r="D21" t="n">
-        <v>623.52</v>
+        <v>632.1900000000001</v>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
@@ -869,13 +869,13 @@
         <v>46219</v>
       </c>
       <c r="B22" t="n">
-        <v>609</v>
+        <v>663</v>
       </c>
       <c r="C22" t="n">
         <v>8888</v>
       </c>
       <c r="D22" t="n">
-        <v>556.35</v>
+        <v>719.9400000000001</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
@@ -909,13 +909,13 @@
         <v>46219</v>
       </c>
       <c r="B24" t="n">
-        <v>559</v>
+        <v>2613</v>
       </c>
       <c r="C24" t="n">
         <v>8888</v>
       </c>
       <c r="D24" t="n">
-        <v>9596.75</v>
+        <v>289.4</v>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
@@ -929,13 +929,13 @@
         <v>46219</v>
       </c>
       <c r="B25" t="n">
-        <v>2250</v>
+        <v>609</v>
       </c>
       <c r="C25" t="n">
         <v>8888</v>
       </c>
       <c r="D25" t="n">
-        <v>1656.98</v>
+        <v>556.35</v>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
@@ -949,18 +949,18 @@
         <v>46219</v>
       </c>
       <c r="B26" t="n">
-        <v>2107</v>
+        <v>559</v>
       </c>
       <c r="C26" t="n">
         <v>8888</v>
       </c>
       <c r="D26" t="n">
-        <v>6978.14</v>
+        <v>5984.59</v>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -969,18 +969,18 @@
         <v>46219</v>
       </c>
       <c r="B27" t="n">
-        <v>131</v>
+        <v>2810</v>
       </c>
       <c r="C27" t="n">
         <v>8888</v>
       </c>
       <c r="D27" t="n">
-        <v>934.3200000000001</v>
+        <v>548.3200000000001</v>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -989,13 +989,13 @@
         <v>46219</v>
       </c>
       <c r="B28" t="n">
-        <v>360</v>
+        <v>131</v>
       </c>
       <c r="C28" t="n">
         <v>8888</v>
       </c>
       <c r="D28" t="n">
-        <v>1990.42</v>
+        <v>623.52</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
@@ -1009,13 +1009,13 @@
         <v>46219</v>
       </c>
       <c r="B29" t="n">
-        <v>20</v>
+        <v>2363</v>
       </c>
       <c r="C29" t="n">
         <v>8888</v>
       </c>
       <c r="D29" t="n">
-        <v>1943.54</v>
+        <v>3265.22</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
@@ -1029,13 +1029,13 @@
         <v>46219</v>
       </c>
       <c r="B30" t="n">
-        <v>768</v>
+        <v>559</v>
       </c>
       <c r="C30" t="n">
         <v>8888</v>
       </c>
       <c r="D30" t="n">
-        <v>3646.68</v>
+        <v>9596.75</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
@@ -1049,13 +1049,13 @@
         <v>46219</v>
       </c>
       <c r="B31" t="n">
-        <v>483</v>
+        <v>2250</v>
       </c>
       <c r="C31" t="n">
         <v>8888</v>
       </c>
       <c r="D31" t="n">
-        <v>150.08</v>
+        <v>1656.98</v>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
@@ -1069,13 +1069,13 @@
         <v>46219</v>
       </c>
       <c r="B32" t="n">
-        <v>131</v>
+        <v>2107</v>
       </c>
       <c r="C32" t="n">
         <v>8888</v>
       </c>
       <c r="D32" t="n">
-        <v>1742.9</v>
+        <v>6978.14</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
@@ -1089,13 +1089,13 @@
         <v>46219</v>
       </c>
       <c r="B33" t="n">
-        <v>1478</v>
+        <v>131</v>
       </c>
       <c r="C33" t="n">
         <v>8888</v>
       </c>
       <c r="D33" t="n">
-        <v>4313.2</v>
+        <v>934.3200000000001</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
@@ -1109,18 +1109,18 @@
         <v>46219</v>
       </c>
       <c r="B34" t="n">
-        <v>1756</v>
+        <v>360</v>
       </c>
       <c r="C34" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D34" t="n">
-        <v>1217.45</v>
+        <v>1990.42</v>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1129,13 +1129,13 @@
         <v>46219</v>
       </c>
       <c r="B35" t="n">
-        <v>609</v>
+        <v>20</v>
       </c>
       <c r="C35" t="n">
         <v>8888</v>
       </c>
       <c r="D35" t="n">
-        <v>741.79</v>
+        <v>1943.54</v>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
@@ -1149,18 +1149,18 @@
         <v>46219</v>
       </c>
       <c r="B36" t="n">
-        <v>285</v>
+        <v>768</v>
       </c>
       <c r="C36" t="n">
         <v>8888</v>
       </c>
       <c r="D36" t="n">
-        <v>701.74</v>
+        <v>3646.68</v>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1169,13 +1169,13 @@
         <v>46219</v>
       </c>
       <c r="B37" t="n">
-        <v>2015</v>
+        <v>483</v>
       </c>
       <c r="C37" t="n">
         <v>8888</v>
       </c>
       <c r="D37" t="n">
-        <v>1011.48</v>
+        <v>150.08</v>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
@@ -1189,13 +1189,13 @@
         <v>46219</v>
       </c>
       <c r="B38" t="n">
-        <v>629</v>
+        <v>131</v>
       </c>
       <c r="C38" t="n">
         <v>8888</v>
       </c>
       <c r="D38" t="n">
-        <v>1338.55</v>
+        <v>1742.9</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
@@ -1209,18 +1209,18 @@
         <v>46219</v>
       </c>
       <c r="B39" t="n">
-        <v>2250</v>
+        <v>1478</v>
       </c>
       <c r="C39" t="n">
         <v>8888</v>
       </c>
       <c r="D39" t="n">
-        <v>1134</v>
+        <v>4313.2</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1229,18 +1229,18 @@
         <v>46219</v>
       </c>
       <c r="B40" t="n">
-        <v>1478</v>
+        <v>1756</v>
       </c>
       <c r="C40" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D40" t="n">
-        <v>1224</v>
+        <v>1217.45</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1249,18 +1249,18 @@
         <v>46219</v>
       </c>
       <c r="B41" t="n">
-        <v>1259</v>
+        <v>609</v>
       </c>
       <c r="C41" t="n">
         <v>8888</v>
       </c>
       <c r="D41" t="n">
-        <v>213.64</v>
+        <v>741.79</v>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1269,13 +1269,13 @@
         <v>46219</v>
       </c>
       <c r="B42" t="n">
-        <v>58</v>
+        <v>285</v>
       </c>
       <c r="C42" t="n">
         <v>8888</v>
       </c>
       <c r="D42" t="n">
-        <v>2254.73</v>
+        <v>701.74</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
@@ -1289,13 +1289,13 @@
         <v>46219</v>
       </c>
       <c r="B43" t="n">
-        <v>1756</v>
+        <v>2015</v>
       </c>
       <c r="C43" t="n">
         <v>8888</v>
       </c>
       <c r="D43" t="n">
-        <v>3007.36</v>
+        <v>1011.48</v>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
@@ -1309,18 +1309,18 @@
         <v>46219</v>
       </c>
       <c r="B44" t="n">
-        <v>131</v>
+        <v>629</v>
       </c>
       <c r="C44" t="n">
         <v>8888</v>
       </c>
       <c r="D44" t="n">
-        <v>425.61</v>
+        <v>1338.55</v>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1329,18 +1329,18 @@
         <v>46219</v>
       </c>
       <c r="B45" t="n">
-        <v>1937</v>
+        <v>2697</v>
       </c>
       <c r="C45" t="n">
-        <v>8888</v>
+        <v>1312</v>
       </c>
       <c r="D45" t="n">
-        <v>1504.37</v>
+        <v>1792.47</v>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1349,18 +1349,18 @@
         <v>46219</v>
       </c>
       <c r="B46" t="n">
-        <v>483</v>
+        <v>2250</v>
       </c>
       <c r="C46" t="n">
         <v>8888</v>
       </c>
       <c r="D46" t="n">
-        <v>859.24</v>
+        <v>1134</v>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1369,18 +1369,18 @@
         <v>46219</v>
       </c>
       <c r="B47" t="n">
-        <v>1064</v>
+        <v>1478</v>
       </c>
       <c r="C47" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D47" t="n">
-        <v>954.13</v>
+        <v>1224</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1389,18 +1389,18 @@
         <v>46219</v>
       </c>
       <c r="B48" t="n">
-        <v>629</v>
+        <v>1259</v>
       </c>
       <c r="C48" t="n">
         <v>8888</v>
       </c>
       <c r="D48" t="n">
-        <v>1997.38</v>
+        <v>213.64</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1409,18 +1409,18 @@
         <v>46219</v>
       </c>
       <c r="B49" t="n">
-        <v>1756</v>
+        <v>58</v>
       </c>
       <c r="C49" t="n">
         <v>8888</v>
       </c>
       <c r="D49" t="n">
-        <v>1399.6</v>
+        <v>2254.73</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
         <v>8888</v>
       </c>
       <c r="D50" t="n">
-        <v>1383.55</v>
+        <v>3007.36</v>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
@@ -1449,18 +1449,18 @@
         <v>46219</v>
       </c>
       <c r="B51" t="n">
-        <v>2114</v>
+        <v>131</v>
       </c>
       <c r="C51" t="n">
         <v>8888</v>
       </c>
       <c r="D51" t="n">
-        <v>23987.35</v>
+        <v>425.61</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -1469,18 +1469,18 @@
         <v>46219</v>
       </c>
       <c r="B52" t="n">
-        <v>2190</v>
+        <v>1937</v>
       </c>
       <c r="C52" t="n">
         <v>8888</v>
       </c>
       <c r="D52" t="n">
-        <v>1181.72</v>
+        <v>1504.37</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1489,18 +1489,18 @@
         <v>46219</v>
       </c>
       <c r="B53" t="n">
-        <v>131</v>
+        <v>2463</v>
       </c>
       <c r="C53" t="n">
-        <v>8888</v>
+        <v>1139</v>
       </c>
       <c r="D53" t="n">
-        <v>527.52</v>
+        <v>1347.91</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1509,18 +1509,18 @@
         <v>46219</v>
       </c>
       <c r="B54" t="n">
-        <v>816</v>
+        <v>483</v>
       </c>
       <c r="C54" t="n">
         <v>8888</v>
       </c>
       <c r="D54" t="n">
-        <v>2983.2</v>
+        <v>859.24</v>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1529,18 +1529,18 @@
         <v>46219</v>
       </c>
       <c r="B55" t="n">
-        <v>767</v>
+        <v>1064</v>
       </c>
       <c r="C55" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D55" t="n">
-        <v>428.17</v>
+        <v>954.13</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1549,13 +1549,13 @@
         <v>46219</v>
       </c>
       <c r="B56" t="n">
-        <v>14</v>
+        <v>629</v>
       </c>
       <c r="C56" t="n">
         <v>8888</v>
       </c>
       <c r="D56" t="n">
-        <v>1155.74</v>
+        <v>1997.38</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
@@ -1569,18 +1569,18 @@
         <v>46219</v>
       </c>
       <c r="B57" t="n">
-        <v>20</v>
+        <v>1996</v>
       </c>
       <c r="C57" t="n">
-        <v>8888</v>
+        <v>213</v>
       </c>
       <c r="D57" t="n">
-        <v>10866.88</v>
+        <v>11047.7</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1589,18 +1589,18 @@
         <v>46219</v>
       </c>
       <c r="B58" t="n">
-        <v>2547</v>
+        <v>1756</v>
       </c>
       <c r="C58" t="n">
         <v>8888</v>
       </c>
       <c r="D58" t="n">
-        <v>2027.52</v>
+        <v>1399.6</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1609,13 +1609,13 @@
         <v>46219</v>
       </c>
       <c r="B59" t="n">
-        <v>629</v>
+        <v>816</v>
       </c>
       <c r="C59" t="n">
         <v>8888</v>
       </c>
       <c r="D59" t="n">
-        <v>14273.2</v>
+        <v>4747.52</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
@@ -1629,18 +1629,18 @@
         <v>46219</v>
       </c>
       <c r="B60" t="n">
-        <v>559</v>
+        <v>1756</v>
       </c>
       <c r="C60" t="n">
         <v>8888</v>
       </c>
       <c r="D60" t="n">
-        <v>562.45</v>
+        <v>1383.55</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1649,13 +1649,13 @@
         <v>46219</v>
       </c>
       <c r="B61" t="n">
-        <v>768</v>
+        <v>2114</v>
       </c>
       <c r="C61" t="n">
         <v>8888</v>
       </c>
       <c r="D61" t="n">
-        <v>14378.8</v>
+        <v>23987.35</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
@@ -1669,18 +1669,18 @@
         <v>46219</v>
       </c>
       <c r="B62" t="n">
-        <v>1756</v>
+        <v>2190</v>
       </c>
       <c r="C62" t="n">
-        <v>27</v>
+        <v>8888</v>
       </c>
       <c r="D62" t="n">
-        <v>926.13</v>
+        <v>1181.72</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1689,13 +1689,13 @@
         <v>46219</v>
       </c>
       <c r="B63" t="n">
-        <v>58</v>
+        <v>131</v>
       </c>
       <c r="C63" t="n">
         <v>8888</v>
       </c>
       <c r="D63" t="n">
-        <v>1904.76</v>
+        <v>331.56</v>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
@@ -1709,13 +1709,13 @@
         <v>46219</v>
       </c>
       <c r="B64" t="n">
-        <v>131</v>
+        <v>816</v>
       </c>
       <c r="C64" t="n">
         <v>8888</v>
       </c>
       <c r="D64" t="n">
-        <v>594.8099999999999</v>
+        <v>2983.2</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
@@ -1729,18 +1729,18 @@
         <v>46219</v>
       </c>
       <c r="B65" t="n">
-        <v>58</v>
+        <v>767</v>
       </c>
       <c r="C65" t="n">
         <v>8888</v>
       </c>
       <c r="D65" t="n">
-        <v>4308.9</v>
+        <v>428.17</v>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1749,13 +1749,13 @@
         <v>46219</v>
       </c>
       <c r="B66" t="n">
-        <v>2452</v>
+        <v>14</v>
       </c>
       <c r="C66" t="n">
         <v>8888</v>
       </c>
       <c r="D66" t="n">
-        <v>3086.66</v>
+        <v>1155.74</v>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
@@ -1769,18 +1769,18 @@
         <v>46219</v>
       </c>
       <c r="B67" t="n">
-        <v>953</v>
+        <v>20</v>
       </c>
       <c r="C67" t="n">
         <v>8888</v>
       </c>
       <c r="D67" t="n">
-        <v>604.53</v>
+        <v>10866.88</v>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1789,18 +1789,18 @@
         <v>46219</v>
       </c>
       <c r="B68" t="n">
-        <v>768</v>
+        <v>2547</v>
       </c>
       <c r="C68" t="n">
         <v>8888</v>
       </c>
       <c r="D68" t="n">
-        <v>1655.28</v>
+        <v>2027.52</v>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1809,13 +1809,13 @@
         <v>46219</v>
       </c>
       <c r="B69" t="n">
-        <v>768</v>
+        <v>629</v>
       </c>
       <c r="C69" t="n">
         <v>8888</v>
       </c>
       <c r="D69" t="n">
-        <v>536.16</v>
+        <v>14273.2</v>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
@@ -1829,13 +1829,13 @@
         <v>46219</v>
       </c>
       <c r="B70" t="n">
-        <v>2547</v>
+        <v>358</v>
       </c>
       <c r="C70" t="n">
         <v>8888</v>
       </c>
       <c r="D70" t="n">
-        <v>740.08</v>
+        <v>760.9400000000001</v>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
@@ -1849,18 +1849,18 @@
         <v>46219</v>
       </c>
       <c r="B71" t="n">
-        <v>629</v>
+        <v>559</v>
       </c>
       <c r="C71" t="n">
         <v>8888</v>
       </c>
       <c r="D71" t="n">
-        <v>1276.58</v>
+        <v>562.45</v>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1869,18 +1869,18 @@
         <v>46219</v>
       </c>
       <c r="B72" t="n">
-        <v>131</v>
+        <v>768</v>
       </c>
       <c r="C72" t="n">
         <v>8888</v>
       </c>
       <c r="D72" t="n">
-        <v>783.86</v>
+        <v>14378.8</v>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -1889,18 +1889,18 @@
         <v>46219</v>
       </c>
       <c r="B73" t="n">
-        <v>1277</v>
+        <v>1756</v>
       </c>
       <c r="C73" t="n">
-        <v>8888</v>
+        <v>27</v>
       </c>
       <c r="D73" t="n">
-        <v>1591.9</v>
+        <v>926.13</v>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1909,13 +1909,13 @@
         <v>46219</v>
       </c>
       <c r="B74" t="n">
-        <v>2163</v>
+        <v>58</v>
       </c>
       <c r="C74" t="n">
         <v>8888</v>
       </c>
       <c r="D74" t="n">
-        <v>406.1</v>
+        <v>1904.76</v>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
@@ -1929,13 +1929,13 @@
         <v>46219</v>
       </c>
       <c r="B75" t="n">
-        <v>14</v>
+        <v>131</v>
       </c>
       <c r="C75" t="n">
         <v>8888</v>
       </c>
       <c r="D75" t="n">
-        <v>343.54</v>
+        <v>594.8099999999999</v>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
@@ -1949,18 +1949,18 @@
         <v>46219</v>
       </c>
       <c r="B76" t="n">
-        <v>2516</v>
+        <v>2641</v>
       </c>
       <c r="C76" t="n">
-        <v>8888</v>
+        <v>1087</v>
       </c>
       <c r="D76" t="n">
-        <v>529.88</v>
+        <v>5484.23</v>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>E-COMMERCE</t>
+          <t>TELEMARKETING</t>
         </is>
       </c>
     </row>
@@ -1969,18 +1969,18 @@
         <v>46219</v>
       </c>
       <c r="B77" t="n">
-        <v>438</v>
+        <v>58</v>
       </c>
       <c r="C77" t="n">
         <v>8888</v>
       </c>
       <c r="D77" t="n">
-        <v>1952.31</v>
+        <v>4308.9</v>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -1989,13 +1989,13 @@
         <v>46219</v>
       </c>
       <c r="B78" t="n">
-        <v>768</v>
+        <v>2452</v>
       </c>
       <c r="C78" t="n">
         <v>8888</v>
       </c>
       <c r="D78" t="n">
-        <v>7813.68</v>
+        <v>3086.66</v>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
@@ -2009,18 +2009,18 @@
         <v>46219</v>
       </c>
       <c r="B79" t="n">
-        <v>768</v>
+        <v>953</v>
       </c>
       <c r="C79" t="n">
         <v>8888</v>
       </c>
       <c r="D79" t="n">
-        <v>1291.96</v>
+        <v>604.53</v>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>E-COMMERCE</t>
         </is>
       </c>
     </row>
@@ -2029,18 +2029,18 @@
         <v>46219</v>
       </c>
       <c r="B80" t="n">
-        <v>1518</v>
+        <v>768</v>
       </c>
       <c r="C80" t="n">
-        <v>1533</v>
+        <v>8888</v>
       </c>
       <c r="D80" t="n">
-        <v>5163.32</v>
+        <v>1655.28</v>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2049,13 +2049,13 @@
         <v>46219</v>
       </c>
       <c r="B81" t="n">
-        <v>2190</v>
+        <v>768</v>
       </c>
       <c r="C81" t="n">
         <v>8888</v>
       </c>
       <c r="D81" t="n">
-        <v>870.03</v>
+        <v>536.16</v>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
@@ -2069,18 +2069,18 @@
         <v>46219</v>
       </c>
       <c r="B82" t="n">
-        <v>1478</v>
+        <v>1075</v>
       </c>
       <c r="C82" t="n">
         <v>8888</v>
       </c>
       <c r="D82" t="n">
-        <v>10946.54</v>
+        <v>1366.8</v>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2089,18 +2089,18 @@
         <v>46219</v>
       </c>
       <c r="B83" t="n">
-        <v>2729</v>
+        <v>2547</v>
       </c>
       <c r="C83" t="n">
         <v>8888</v>
       </c>
       <c r="D83" t="n">
-        <v>585.41</v>
+        <v>740.08</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>FORÇA DE VENDAS</t>
+          <t>OPERADOR LOGÍSTICO</t>
         </is>
       </c>
     </row>
@@ -2109,18 +2109,18 @@
         <v>46219</v>
       </c>
       <c r="B84" t="n">
-        <v>1518</v>
+        <v>629</v>
       </c>
       <c r="C84" t="n">
-        <v>1533</v>
+        <v>8888</v>
       </c>
       <c r="D84" t="n">
-        <v>4494.7</v>
+        <v>1276.58</v>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>TELEMARKETING</t>
+          <t>FORÇA DE VENDAS</t>
         </is>
       </c>
     </row>
@@ -2129,18 +2129,18 @@
         <v>46219</v>
       </c>
       <c r="B85" t="n">
-        <v>2452</v>
+        <v>131</v>
       </c>
       <c r="C85" t="n">
         <v>8888</v>
       </c>
       <c r="D85" t="n">
-        <v>1253